--- a/replication/final_instrument/questionnaire/Question_register.xlsx
+++ b/replication/final_instrument/questionnaire/Question_register.xlsx
@@ -2663,7 +2663,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>yes/no</t>
+          <t>select one</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -2678,7 +2678,7 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>0 No | 1 Yes</t>
+          <t>1 Month by month | 0 One total for the whole year</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr"/>

--- a/replication/final_instrument/questionnaire/Question_register.xlsx
+++ b/replication/final_instrument/questionnaire/Question_register.xlsx
@@ -13,9 +13,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Modules" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Questions'!$A$1:$J$199</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Questions'!$A$1:$J$202</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Constructed variables'!$A$1:$F$124</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Literature'!$A$1:$C$118</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Literature'!$A$1:$C$121</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Modules'!$A$1:$C$15</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J199"/>
+  <dimension ref="A1:J202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2126,7 +2126,7 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1 Yatra work (main occupation) | 2 Agriculture | 3 Animal husbandry | 4 Wage labour elsewhere | 5 Migrated for work | 6 Petty trade/other | 7 Salaried job | 8 No paid work</t>
+          <t>1 Yatra work (main occupation) | 2 Farming (crops) | 3 Livestock (animals) | 4 Wage labour, staying at home | 5 Went away from home for work | 6 Own small shop, stall or trade | 7 Salaried job | 8 No paid work</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr"/>
@@ -2172,7 +2172,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>1 Yatra work (main occupation) | 2 Agriculture | 3 Animal husbandry | 4 Wage labour elsewhere | 5 Migrated for work | 6 Petty trade/other | 7 Salaried job | 8 No paid work</t>
+          <t>1 Yatra work (main occupation) | 2 Farming (crops) | 3 Livestock (animals) | 4 Wage labour, staying at home | 5 Went away from home for work | 6 Own small shop, stall or trade | 7 Salaried job | 8 No paid work</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr"/>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>1 Yatra work (main occupation) | 2 Agriculture | 3 Animal husbandry | 4 Wage labour elsewhere | 5 Migrated for work | 6 Petty trade/other | 7 Salaried job | 8 No paid work</t>
+          <t>1 Yatra work (main occupation) | 2 Farming (crops) | 3 Livestock (animals) | 4 Wage labour, staying at home | 5 Went away from home for work | 6 Own small shop, stall or trade | 7 Salaried job | 8 No paid work</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr"/>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>1 Yatra work (main occupation) | 2 Agriculture | 3 Animal husbandry | 4 Wage labour elsewhere | 5 Migrated for work | 6 Petty trade/other | 7 Salaried job | 8 No paid work</t>
+          <t>1 Yatra work (main occupation) | 2 Farming (crops) | 3 Livestock (animals) | 4 Wage labour, staying at home | 5 Went away from home for work | 6 Own small shop, stall or trade | 7 Salaried job | 8 No paid work</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr"/>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>1 Yatra work (main occupation) | 2 Agriculture | 3 Animal husbandry | 4 Wage labour elsewhere | 5 Migrated for work | 6 Petty trade/other | 7 Salaried job | 8 No paid work</t>
+          <t>1 Yatra work (main occupation) | 2 Farming (crops) | 3 Livestock (animals) | 4 Wage labour, staying at home | 5 Went away from home for work | 6 Own small shop, stall or trade | 7 Salaried job | 8 No paid work</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr"/>
@@ -2356,7 +2356,7 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>1 Yatra work (main occupation) | 2 Agriculture | 3 Animal husbandry | 4 Wage labour elsewhere | 5 Migrated for work | 6 Petty trade/other | 7 Salaried job | 8 No paid work</t>
+          <t>1 Yatra work (main occupation) | 2 Farming (crops) | 3 Livestock (animals) | 4 Wage labour, staying at home | 5 Went away from home for work | 6 Own small shop, stall or trade | 7 Salaried job | 8 No paid work</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr"/>
@@ -2402,7 +2402,7 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>1 Yatra work (main occupation) | 2 Agriculture | 3 Animal husbandry | 4 Wage labour elsewhere | 5 Migrated for work | 6 Petty trade/other | 7 Salaried job | 8 No paid work</t>
+          <t>1 Yatra work (main occupation) | 2 Farming (crops) | 3 Livestock (animals) | 4 Wage labour, staying at home | 5 Went away from home for work | 6 Own small shop, stall or trade | 7 Salaried job | 8 No paid work</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr"/>
@@ -2448,7 +2448,7 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>1 Yatra work (main occupation) | 2 Agriculture | 3 Animal husbandry | 4 Wage labour elsewhere | 5 Migrated for work | 6 Petty trade/other | 7 Salaried job | 8 No paid work</t>
+          <t>1 Yatra work (main occupation) | 2 Farming (crops) | 3 Livestock (animals) | 4 Wage labour, staying at home | 5 Went away from home for work | 6 Own small shop, stall or trade | 7 Salaried job | 8 No paid work</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr"/>
@@ -2494,7 +2494,7 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>1 Yatra work (main occupation) | 2 Agriculture | 3 Animal husbandry | 4 Wage labour elsewhere | 5 Migrated for work | 6 Petty trade/other | 7 Salaried job | 8 No paid work</t>
+          <t>1 Yatra work (main occupation) | 2 Farming (crops) | 3 Livestock (animals) | 4 Wage labour, staying at home | 5 Went away from home for work | 6 Own small shop, stall or trade | 7 Salaried job | 8 No paid work</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr"/>
@@ -2540,7 +2540,7 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>1 Yatra work (main occupation) | 2 Agriculture | 3 Animal husbandry | 4 Wage labour elsewhere | 5 Migrated for work | 6 Petty trade/other | 7 Salaried job | 8 No paid work</t>
+          <t>1 Yatra work (main occupation) | 2 Farming (crops) | 3 Livestock (animals) | 4 Wage labour, staying at home | 5 Went away from home for work | 6 Own small shop, stall or trade | 7 Salaried job | 8 No paid work</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr"/>
@@ -2586,7 +2586,7 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>1 Yatra work (main occupation) | 2 Agriculture | 3 Animal husbandry | 4 Wage labour elsewhere | 5 Migrated for work | 6 Petty trade/other | 7 Salaried job | 8 No paid work</t>
+          <t>1 Yatra work (main occupation) | 2 Farming (crops) | 3 Livestock (animals) | 4 Wage labour, staying at home | 5 Went away from home for work | 6 Own small shop, stall or trade | 7 Salaried job | 8 No paid work</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr"/>
@@ -2632,7 +2632,7 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>1 Yatra work (main occupation) | 2 Agriculture | 3 Animal husbandry | 4 Wage labour elsewhere | 5 Migrated for work | 6 Petty trade/other | 7 Salaried job | 8 No paid work</t>
+          <t>1 Yatra work (main occupation) | 2 Farming (crops) | 3 Livestock (animals) | 4 Wage labour, staying at home | 5 Went away from home for work | 6 Own small shop, stall or trade | 7 Salaried job | 8 No paid work</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr"/>
@@ -3668,17 +3668,17 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>Is that home in a village, a small town, a larger town, or a city?</t>
+          <t>Is that home in a village, a town, or a city?</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>वह घर गाँव में है, छोटे क़स्बे में, बड़े क़स्बे में, या शहर में?</t>
+          <t>वह घर गाँव में है, क़स्बे में, या शहर में?</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>1 Village (gram panchayat) | 2 Small town / nagar panchayat | 3 Town / nagar palika | 4 City / municipal corporation</t>
+          <t>1 Village (gram panchayat) | 2 Town | 3 City</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr"/>
@@ -3850,29 +3850,33 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>cons_staples_yatra_pm</t>
+          <t>spend_differs_by_season</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>amount (Rs)</t>
+          <t>yes/no</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on cereals (rice, wheat, other grains), pulses, sugar and salt, bought or from your own stock? (Rs)</t>
+          <t>Leaving aside money you send home -- is what your household spends in a normal month during the Yatra season different from what it spends when the Yatra is closed?</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) अनाज (चावल, गेहूँ, दूसरा अनाज), दाल, चीनी और नमक पर, ख़रीदा हुआ या अपने घर का कितना ख़र्च करते हैं? (रुपये)</t>
-        </is>
-      </c>
-      <c r="H75" s="2" t="inlineStr"/>
+          <t>घर भेजे जाने वाले पैसे को छोड़कर — यात्रा के मौसम में आपके घर का महीने का ख़र्च, और जब यात्रा बंद रहती है तब का ख़र्च, क्या अलग-अलग होता है?</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>0 No | 1 Yes</t>
+        </is>
+      </c>
       <c r="I75" s="2" t="inlineStr"/>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>HCES 2022-23, MoSPI Appendix A, Sections 5.1-5.3 (30-day); IHDS-II Income and Social Capital Questionnaire, Q14 14.1-14.6 (30-day, same items)</t>
+          <t>Project design (respondent-gated seasonal recall); the underlying two-season design follows Beegle et al. 2012 and Deaton and Grosh 2000 on usual-period recall</t>
         </is>
       </c>
     </row>
@@ -3892,7 +3896,7 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>cons_staples_offseason_pm</t>
+          <t>cons_staples_yatra_pm</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -3902,12 +3906,12 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>In a normal month when the Yatra is closed, how much does your household spend on cereals (rice, wheat, other grains), pulses, sugar and salt, bought or from your own stock? (Rs)</t>
+          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on cereals (rice, wheat, other grains), pulses, sugar and salt, bought or from your own stock? (Rs)</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर अनाज (चावल, गेहूँ, दूसरा अनाज), दाल, चीनी और नमक पर, ख़रीदा हुआ या अपने घर का कितना ख़र्च करता है? (रुपये)</t>
+          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) अनाज (चावल, गेहूँ, दूसरा अनाज), दाल, चीनी और नमक पर, ख़रीदा हुआ या अपने घर का कितना ख़र्च करते हैं? (रुपये)</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr"/>
@@ -3934,7 +3938,7 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>cons_perishables_yatra_pm</t>
+          <t>cons_staples_offseason_pm</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -3944,19 +3948,23 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on milk and milk products, vegetables, fruit, egg/fish/meat, cooking oil, spices, and tea or coffee, bought or from your own stock? (Rs)</t>
+          <t>In a normal month when the Yatra is closed, how much does your household spend on cereals (rice, wheat, other grains), pulses, sugar and salt, bought or from your own stock? (Rs)</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) दूध और दूध की चीज़ें, सब्ज़ी, फल, अंडा/मछली/मांस, तेल, मसाले, और चाय पर कितना ख़र्च करते हैं? (रुपये)</t>
+          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर अनाज (चावल, गेहूँ, दूसरा अनाज), दाल, चीनी और नमक पर, ख़रीदा हुआ या अपने घर का कितना ख़र्च करता है? (रुपये)</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr"/>
-      <c r="I77" s="2" t="inlineStr"/>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if spend_differs_by_season = 1</t>
+        </is>
+      </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>HCES 2022-23, MoSPI Appendix A, Sections 6.1-6.8 (7-day actual recall in HCES; asked here as a usual monthly figure instead, for the reason above)</t>
+          <t>HCES 2022-23, MoSPI Appendix A, Sections 5.1-5.3 (30-day); IHDS-II Income and Social Capital Questionnaire, Q14 14.1-14.6 (30-day, same items)</t>
         </is>
       </c>
     </row>
@@ -3976,7 +3984,7 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>cons_perishables_offseason_pm</t>
+          <t>cons_perishables_yatra_pm</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -3986,12 +3994,12 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>In a normal month when the Yatra is closed, how much does your household spend on milk and milk products, vegetables, fruit, egg/fish/meat, cooking oil, spices, and tea or coffee, bought or from your own stock? (Rs)</t>
+          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on milk and milk products, vegetables, fruit, egg/fish/meat, cooking oil, spices, and tea or coffee, bought or from your own stock? (Rs)</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर दूध और दूध की चीज़ें, सब्ज़ी, फल, अंडा/मछली/मांस, तेल, मसाले, और चाय पर कितना ख़र्च करता है? (रुपये)</t>
+          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) दूध और दूध की चीज़ें, सब्ज़ी, फल, अंडा/मछली/मांस, तेल, मसाले, और चाय पर कितना ख़र्च करते हैं? (रुपये)</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr"/>
@@ -4018,7 +4026,7 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>cons_food_own_yatra_pm</t>
+          <t>cons_perishables_offseason_pm</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
@@ -4028,19 +4036,23 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>If you (and anyone staying with you here) had not grown, raised or been given any of your food, about how much would it have cost to buy in a normal month during the Yatra season? (Rs, 0 if you buy everything)</t>
+          <t>In a normal month when the Yatra is closed, how much does your household spend on milk and milk products, vegetables, fruit, egg/fish/meat, cooking oil, spices, and tea or coffee, bought or from your own stock? (Rs)</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>अगर आप (और जो यहाँ आपके साथ रहते हैं) अपना खाना ख़ुद न उगाते, न पालते और न किसी से मिलता, तो यात्रा के मौसम के आम महीने में उसे ख़रीदने में लगभग कितना लगता? (रुपये, सब ख़रीदते हों तो 0)</t>
+          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर दूध और दूध की चीज़ें, सब्ज़ी, फल, अंडा/मछली/मांस, तेल, मसाले, और चाय पर कितना ख़र्च करता है? (रुपये)</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr"/>
-      <c r="I79" s="2" t="inlineStr"/>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if spend_differs_by_season = 1</t>
+        </is>
+      </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>Calvo and Dercon 2007; Eze and Iheonu 2025 (non-purchased food, aggregate approach)</t>
+          <t>HCES 2022-23, MoSPI Appendix A, Sections 6.1-6.8 (7-day actual recall in HCES; asked here as a usual monthly figure instead, for the reason above)</t>
         </is>
       </c>
     </row>
@@ -4060,7 +4072,7 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>cons_food_own_offseason_pm</t>
+          <t>cons_food_own_yatra_pm</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -4070,12 +4082,12 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>If your household had not grown, raised or been given any of your food, about how much would it have cost to buy in a normal month when the Yatra is closed? (Rs, 0 if you buy everything)</t>
+          <t>If you (and anyone staying with you here) had not grown, raised or been given any of your food, about how much would it have cost to buy in a normal month during the Yatra season? (Rs, 0 if you buy everything)</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>अगर आपका घर अपना खाना ख़ुद न उगाता, न पालता और न किसी से मिलता, तो जब यात्रा बंद रहती है उस आम महीने में उसे ख़रीदने में लगभग कितना लगता? (रुपये, सब ख़रीदते हों तो 0)</t>
+          <t>अगर आप (और जो यहाँ आपके साथ रहते हैं) अपना खाना ख़ुद न उगाते, न पालते और न किसी से मिलता, तो यात्रा के मौसम के आम महीने में उसे ख़रीदने में लगभग कितना लगता? (रुपये, सब ख़रीदते हों तो 0)</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr"/>
@@ -4102,7 +4114,7 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>cons_food_out_yatra_pm</t>
+          <t>cons_food_own_offseason_pm</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -4112,19 +4124,23 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on meals, tea and snacks eaten outside the home, including any an employer gave free, at their market value? (Rs)</t>
+          <t>If your household had not grown, raised or been given any of your food, about how much would it have cost to buy in a normal month when the Yatra is closed? (Rs, 0 if you buy everything)</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) बाहर खाए गए खाने, चाय और नाश्ते पर, मालिक ने मुफ़्त दिया हो तो उसकी क़ीमत मिलाकर कितना ख़र्च करते हैं? (रुपये)</t>
+          <t>अगर आपका घर अपना खाना ख़ुद न उगाता, न पालता और न किसी से मिलता, तो जब यात्रा बंद रहती है उस आम महीने में उसे ख़रीदने में लगभग कितना लगता? (रुपये, सब ख़रीदते हों तो 0)</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr"/>
-      <c r="I81" s="2" t="inlineStr"/>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if spend_differs_by_season = 1</t>
+        </is>
+      </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>HCES 2022-23, MoSPI Appendix A, Section 7.1 'served processed food' (7-day in HCES; usual monthly here)</t>
+          <t>Calvo and Dercon 2007; Eze and Iheonu 2025 (non-purchased food, aggregate approach)</t>
         </is>
       </c>
     </row>
@@ -4144,7 +4160,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>cons_food_out_offseason_pm</t>
+          <t>cons_food_out_yatra_pm</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -4154,12 +4170,12 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>In a normal month when the Yatra is closed, how much does your household spend on meals, tea and snacks eaten outside the home, including any an employer gave free, at their market value? (Rs)</t>
+          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on meals, tea and snacks eaten outside the home, including any an employer gave free, at their market value? (Rs)</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर बाहर खाए गए खाने, चाय और नाश्ते पर, मालिक ने मुफ़्त दिया हो तो उसकी क़ीमत मिलाकर कितना ख़र्च करता है? (रुपये)</t>
+          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) बाहर खाए गए खाने, चाय और नाश्ते पर, मालिक ने मुफ़्त दिया हो तो उसकी क़ीमत मिलाकर कितना ख़र्च करते हैं? (रुपये)</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr"/>
@@ -4186,7 +4202,7 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>cons_fuel_yatra_pm</t>
+          <t>cons_food_out_offseason_pm</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
@@ -4196,19 +4212,23 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on fuel and light: cooking fuel, firewood, electricity, kerosene, candles? (Rs)</t>
+          <t>In a normal month when the Yatra is closed, how much does your household spend on meals, tea and snacks eaten outside the home, including any an employer gave free, at their market value? (Rs)</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) ईंधन और रोशनी पर: खाना बनाने की गैस, लकड़ी, बिजली, मिट्टी का तेल, मोमबत्ती कितना ख़र्च करते हैं? (रुपये)</t>
+          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर बाहर खाए गए खाने, चाय और नाश्ते पर, मालिक ने मुफ़्त दिया हो तो उसकी क़ीमत मिलाकर कितना ख़र्च करता है? (रुपये)</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr"/>
-      <c r="I83" s="2" t="inlineStr"/>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if spend_differs_by_season = 1</t>
+        </is>
+      </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>HCES 2022-23, MoSPI Appendix A, Section 8.1 (30-day). IHDS-II Income and Social Capital Questionnaire, Q14 14.21-14.22. Nigeria GHS-Panel Wave 3, Household Questionnaire, Sections 10B/11 (30-day tier)</t>
+          <t>HCES 2022-23, MoSPI Appendix A, Section 7.1 'served processed food' (7-day in HCES; usual monthly here)</t>
         </is>
       </c>
     </row>
@@ -4228,7 +4248,7 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>cons_fuel_offseason_pm</t>
+          <t>cons_fuel_yatra_pm</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -4238,12 +4258,12 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>In a normal month when the Yatra is closed, how much does your household spend on fuel and light: cooking fuel, firewood, electricity, kerosene, candles? (Rs)</t>
+          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on fuel and light: cooking fuel, firewood, electricity, kerosene, candles? (Rs)</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर ईंधन और रोशनी पर: खाना बनाने की गैस, लकड़ी, बिजली, मिट्टी का तेल, मोमबत्ती कितना ख़र्च करता है? (रुपये)</t>
+          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) ईंधन और रोशनी पर: खाना बनाने की गैस, लकड़ी, बिजली, मिट्टी का तेल, मोमबत्ती कितना ख़र्च करते हैं? (रुपये)</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr"/>
@@ -4270,7 +4290,7 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>cons_routine_misc_yatra_pm</t>
+          <t>cons_fuel_offseason_pm</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
@@ -4280,19 +4300,23 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on soap, toiletries, cleaning goods and other small household items? (Rs)</t>
+          <t>In a normal month when the Yatra is closed, how much does your household spend on fuel and light: cooking fuel, firewood, electricity, kerosene, candles? (Rs)</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) साबुन, नहाने-धोने का सामान, सफ़ाई का सामान और घर की दूसरी छोटी चीज़ों पर कितना ख़र्च करते हैं? (रुपये)</t>
+          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर ईंधन और रोशनी पर: खाना बनाने की गैस, लकड़ी, बिजली, मिट्टी का तेल, मोमबत्ती कितना ख़र्च करता है? (रुपये)</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr"/>
-      <c r="I85" s="2" t="inlineStr"/>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if spend_differs_by_season = 1</t>
+        </is>
+      </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>HCES 2022-23, MoSPI Appendix A, Sections 9.1-9.2 (30-day). IHDS-II Income and Social Capital Questionnaire, Q14 14.25-14.27. Nigeria GHS-Panel Wave 3, Household Questionnaire, Sections 10B/11 (30-day tier)</t>
+          <t>HCES 2022-23, MoSPI Appendix A, Section 8.1 (30-day). IHDS-II Income and Social Capital Questionnaire, Q14 14.21-14.22. Nigeria GHS-Panel Wave 3, Household Questionnaire, Sections 10B/11 (30-day tier)</t>
         </is>
       </c>
     </row>
@@ -4312,7 +4336,7 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>cons_routine_misc_offseason_pm</t>
+          <t>cons_routine_misc_yatra_pm</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -4322,12 +4346,12 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>In a normal month when the Yatra is closed, how much does your household spend on soap, toiletries, cleaning goods and other small household items? (Rs)</t>
+          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on soap, toiletries, cleaning goods and other small household items? (Rs)</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर साबुन, नहाने-धोने का सामान, सफ़ाई का सामान और घर की दूसरी छोटी चीज़ों पर कितना ख़र्च करता है? (रुपये)</t>
+          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) साबुन, नहाने-धोने का सामान, सफ़ाई का सामान और घर की दूसरी छोटी चीज़ों पर कितना ख़र्च करते हैं? (रुपये)</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr"/>
@@ -4354,7 +4378,7 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>cons_transport_comm_yatra_pm</t>
+          <t>cons_routine_misc_offseason_pm</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
@@ -4364,19 +4388,23 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on local transport (bus, shared jeep, auto) and phone or internet charges? (Rs)</t>
+          <t>In a normal month when the Yatra is closed, how much does your household spend on soap, toiletries, cleaning goods and other small household items? (Rs)</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) आने-जाने (बस, जीप, ऑटो) और फ़ोन या इंटरनेट पर कितना ख़र्च करते हैं? (रुपये)</t>
+          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर साबुन, नहाने-धोने का सामान, सफ़ाई का सामान और घर की दूसरी छोटी चीज़ों पर कितना ख़र्च करता है? (रुपये)</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr"/>
-      <c r="I87" s="2" t="inlineStr"/>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if spend_differs_by_season = 1</t>
+        </is>
+      </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>HCES 2022-23, MoSPI Appendix A, Sections 11.1-11.2 (30-day). IHDS-II Income and Social Capital Questionnaire, Q14 14.24/14.28. Nigeria GHS-Panel Wave 3, Household Questionnaire, Sections 10B/11 (30-day tier)</t>
+          <t>HCES 2022-23, MoSPI Appendix A, Sections 9.1-9.2 (30-day). IHDS-II Income and Social Capital Questionnaire, Q14 14.25-14.27. Nigeria GHS-Panel Wave 3, Household Questionnaire, Sections 10B/11 (30-day tier)</t>
         </is>
       </c>
     </row>
@@ -4396,7 +4424,7 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>cons_transport_comm_offseason_pm</t>
+          <t>cons_transport_comm_yatra_pm</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -4406,12 +4434,12 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>In a normal month when the Yatra is closed, how much does your household spend on local transport (bus, shared jeep, auto) and phone or internet charges? (Rs)</t>
+          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on local transport (bus, shared jeep, auto) and phone or internet charges? (Rs)</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर आने-जाने (बस, जीप, ऑटो) और फ़ोन या इंटरनेट पर कितना ख़र्च करता है? (रुपये)</t>
+          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) आने-जाने (बस, जीप, ऑटो) और फ़ोन या इंटरनेट पर कितना ख़र्च करते हैं? (रुपये)</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr"/>
@@ -4438,7 +4466,7 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>cons_rent_yatra_pm</t>
+          <t>cons_transport_comm_offseason_pm</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
@@ -4448,19 +4476,23 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on rent for the home (0 if owned, and 0 for any period spent living for free)? (Rs)</t>
+          <t>In a normal month when the Yatra is closed, how much does your household spend on local transport (bus, shared jeep, auto) and phone or internet charges? (Rs)</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) घर के किराये पर (अपना घर हो तो 0, और मुफ़्त रहे हों तो भी 0) कितना ख़र्च करते हैं? (रुपये)</t>
+          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर आने-जाने (बस, जीप, ऑटो) और फ़ोन या इंटरनेट पर कितना ख़र्च करता है? (रुपये)</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr"/>
-      <c r="I89" s="2" t="inlineStr"/>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if spend_differs_by_season = 1</t>
+        </is>
+      </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>HCES 2022-23, MoSPI Appendix A, Section 11.4 (30-day). IHDS-II Income and Social Capital Questionnaire, Q14 14.30. Nigeria GHS-Panel Wave 3, Household Questionnaire, Sections 10B/11 (30-day tier)</t>
+          <t>HCES 2022-23, MoSPI Appendix A, Sections 11.1-11.2 (30-day). IHDS-II Income and Social Capital Questionnaire, Q14 14.24/14.28. Nigeria GHS-Panel Wave 3, Household Questionnaire, Sections 10B/11 (30-day tier)</t>
         </is>
       </c>
     </row>
@@ -4480,7 +4512,7 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>cons_rent_offseason_pm</t>
+          <t>cons_rent_yatra_pm</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -4490,12 +4522,12 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>In a normal month when the Yatra is closed, how much does your household spend on rent for the home (0 if owned, and 0 for any period spent living for free)? (Rs)</t>
+          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on rent for the home (0 if owned, and 0 for any period spent living for free)? (Rs)</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर घर के किराये पर (अपना घर हो तो 0, और मुफ़्त रहे हों तो भी 0) कितना ख़र्च करता है? (रुपये)</t>
+          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) घर के किराये पर (अपना घर हो तो 0, और मुफ़्त रहे हों तो भी 0) कितना ख़र्च करते हैं? (रुपये)</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr"/>
@@ -4522,7 +4554,7 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>cons_med_nonhosp_yatra_pm</t>
+          <t>cons_rent_offseason_pm</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
@@ -4532,19 +4564,23 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on medicine, doctor's or clinic fees and tests, not counting a hospital stay? (Rs)</t>
+          <t>In a normal month when the Yatra is closed, how much does your household spend on rent for the home (0 if owned, and 0 for any period spent living for free)? (Rs)</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) दवाई, डॉक्टर या क्लीनिक की फ़ीस और जाँच पर, अस्पताल में भर्ती को छोड़कर कितना ख़र्च करते हैं? (रुपये)</t>
+          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर घर के किराये पर (अपना घर हो तो 0, और मुफ़्त रहे हों तो भी 0) कितना ख़र्च करता है? (रुपये)</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr"/>
-      <c r="I91" s="2" t="inlineStr"/>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if spend_differs_by_season = 1</t>
+        </is>
+      </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>HCES 2022-23, MoSPI Appendix A, Section 10.3 (30-day). IHDS-II Income and Social Capital Questionnaire, Q14 14.33 (30-day, out-patient)</t>
+          <t>HCES 2022-23, MoSPI Appendix A, Section 11.4 (30-day). IHDS-II Income and Social Capital Questionnaire, Q14 14.30. Nigeria GHS-Panel Wave 3, Household Questionnaire, Sections 10B/11 (30-day tier)</t>
         </is>
       </c>
     </row>
@@ -4564,7 +4600,7 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>cons_med_nonhosp_offseason_pm</t>
+          <t>cons_med_nonhosp_yatra_pm</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -4574,12 +4610,12 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>In a normal month when the Yatra is closed, how much does your household spend on medicine, doctor's or clinic fees and tests, not counting a hospital stay? (Rs)</t>
+          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on medicine, doctor's or clinic fees and tests, not counting a hospital stay? (Rs)</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर दवाई, डॉक्टर या क्लीनिक की फ़ीस और जाँच पर, अस्पताल में भर्ती को छोड़कर कितना ख़र्च करता है? (रुपये)</t>
+          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) दवाई, डॉक्टर या क्लीनिक की फ़ीस और जाँच पर, अस्पताल में भर्ती को छोड़कर कितना ख़र्च करते हैं? (रुपये)</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr"/>
@@ -4606,33 +4642,33 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>cooks_own_meals_here</t>
+          <t>cons_med_nonhosp_offseason_pm</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>select one</t>
+          <t>amount (Rs)</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>While you are here for the season, do you cook your own meals, or do you buy them?</t>
+          <t>In a normal month when the Yatra is closed, how much does your household spend on medicine, doctor's or clinic fees and tests, not counting a hospital stay? (Rs)</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>यहाँ सीज़न में रहते हुए, आप अपना खाना ख़ुद बनाते हैं, ख़रीदकर खाते हैं, या दोनों?</t>
-        </is>
-      </c>
-      <c r="H93" s="2" t="inlineStr">
-        <is>
-          <t>1 Cooks their own | 2 Buys them | 3 Some of each</t>
-        </is>
-      </c>
-      <c r="I93" s="2" t="inlineStr"/>
+          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर दवाई, डॉक्टर या क्लीनिक की फ़ीस और जाँच पर, अस्पताल में भर्ती को छोड़कर कितना ख़र्च करता है? (रुपये)</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr"/>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if spend_differs_by_season = 1</t>
+        </is>
+      </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>Project design (migrant worksite subsistence)</t>
+          <t>HCES 2022-23, MoSPI Appendix A, Section 10.3 (30-day). IHDS-II Income and Social Capital Questionnaire, Q14 14.33 (30-day, out-patient)</t>
         </is>
       </c>
     </row>
@@ -4652,30 +4688,30 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>meal_spend_day_self</t>
+          <t>cooks_own_meals_here</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>amount (Rs)</t>
+          <t>select one</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>On a normal working day here, about how much do you spend on your own food and tea altogether? (Rs)</t>
+          <t>While you are here for the season, do you cook your own meals, or do you buy them?</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>यहाँ आम काम के दिन में, अपने खाने और चाय पर कुल कितना ख़र्च होता है? (रुपये)</t>
-        </is>
-      </c>
-      <c r="H94" s="2" t="inlineStr"/>
-      <c r="I94" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if cooks_own_meals_here is 2 (buys) or 3 (some of each)</t>
-        </is>
-      </c>
+          <t>यहाँ सीज़न में रहते हुए, आप अपना खाना ख़ुद बनाते हैं, ख़रीदकर खाते हैं, या दोनों?</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>1 Cooks their own | 2 Buys them | 3 Some of each</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr"/>
       <c r="J94" s="2" t="inlineStr">
         <is>
           <t>Project design (migrant worksite subsistence)</t>
@@ -4698,7 +4734,7 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>cons_packaged_food_yatra_pm</t>
+          <t>meal_spend_day_self</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
@@ -4708,19 +4744,23 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on biscuits, namkeen, chips, packaged snacks, cold drinks or bottled water? (Rs)</t>
+          <t>On a normal working day here, about how much do you spend on your own food and tea altogether? (Rs)</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) बिस्किट, नमकीन, चिप्स, पैकेट वाले नाश्ते, कोल्ड ड्रिंक या बोतलबंद पानी पर कितना ख़र्च करते हैं? (रुपये)</t>
+          <t>यहाँ आम काम के दिन में, अपने खाने और चाय पर कुल कितना ख़र्च होता है? (रुपये)</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr"/>
-      <c r="I95" s="2" t="inlineStr"/>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if cooks_own_meals_here is 2 (buys) or 3 (some of each)</t>
+        </is>
+      </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>HCES 2022-23, MoSPI Appendix A, Section 7.2 (7-day in HCES; usual monthly here, as for every other seasonal item)</t>
+          <t>Project design (migrant worksite subsistence)</t>
         </is>
       </c>
     </row>
@@ -4740,7 +4780,7 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>cons_packaged_food_offseason_pm</t>
+          <t>cons_packaged_food_yatra_pm</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -4750,12 +4790,12 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>In a normal month when the Yatra is closed, how much does your household spend on biscuits, namkeen, chips, packaged snacks, cold drinks or bottled water? (Rs)</t>
+          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on biscuits, namkeen, chips, packaged snacks, cold drinks or bottled water? (Rs)</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर बिस्किट, नमकीन, चिप्स, पैकेट वाले नाश्ते, कोल्ड ड्रिंक या बोतलबंद पानी पर कितना ख़र्च करता है? (रुपये)</t>
+          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) बिस्किट, नमकीन, चिप्स, पैकेट वाले नाश्ते, कोल्ड ड्रिंक या बोतलबंद पानी पर कितना ख़र्च करते हैं? (रुपये)</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr"/>
@@ -4782,7 +4822,7 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>cons_pan_tobacco_yatra_pm</t>
+          <t>cons_packaged_food_offseason_pm</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
@@ -4792,19 +4832,23 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on pan, gutka, bidi, cigarettes, tobacco or alcohol? (Rs)</t>
+          <t>In a normal month when the Yatra is closed, how much does your household spend on biscuits, namkeen, chips, packaged snacks, cold drinks or bottled water? (Rs)</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) पान, गुटका, बीड़ी, सिगरेट, तंबाकू या शराब पर कितना ख़र्च करते हैं? (रुपये)</t>
+          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर बिस्किट, नमकीन, चिप्स, पैकेट वाले नाश्ते, कोल्ड ड्रिंक या बोतलबंद पानी पर कितना ख़र्च करता है? (रुपये)</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr"/>
-      <c r="I97" s="2" t="inlineStr"/>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if spend_differs_by_season = 1</t>
+        </is>
+      </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>HCES 2022-23, MoSPI Appendix A, Sections 12.1-12.3 (7-day in HCES; usual monthly here, and combined into one figure)</t>
+          <t>HCES 2022-23, MoSPI Appendix A, Section 7.2 (7-day in HCES; usual monthly here, as for every other seasonal item)</t>
         </is>
       </c>
     </row>
@@ -4824,7 +4868,7 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>cons_pan_tobacco_offseason_pm</t>
+          <t>cons_pan_tobacco_yatra_pm</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
@@ -4834,12 +4878,12 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>In a normal month when the Yatra is closed, how much does your household spend on pan, gutka, bidi, cigarettes, tobacco or alcohol? (Rs)</t>
+          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on pan, gutka, bidi, cigarettes, tobacco or alcohol? (Rs)</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर पान, गुटका, बीड़ी, सिगरेट, तंबाकू या शराब पर कितना ख़र्च करता है? (रुपये)</t>
+          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) पान, गुटका, बीड़ी, सिगरेट, तंबाकू या शराब पर कितना ख़र्च करते हैं? (रुपये)</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr"/>
@@ -4866,7 +4910,7 @@
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>cons_clothing_12m</t>
+          <t>cons_pan_tobacco_offseason_pm</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
@@ -4876,19 +4920,23 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>In the last 12 months, how much did your household spend on clothes and footwear? (Rs)</t>
+          <t>In a normal month when the Yatra is closed, how much does your household spend on pan, gutka, bidi, cigarettes, tobacco or alcohol? (Rs)</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>पिछले 12 महीनों में आपके घर ने कपड़ों और जूते-चप्पल पर कितना ख़र्च किया? (रुपये)</t>
+          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर पान, गुटका, बीड़ी, सिगरेट, तंबाकू या शराब पर कितना ख़र्च करता है? (रुपये)</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr"/>
-      <c r="I99" s="2" t="inlineStr"/>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if spend_differs_by_season = 1</t>
+        </is>
+      </c>
       <c r="J99" s="2" t="inlineStr">
         <is>
-          <t>HCES 2022-23, MoSPI Appendix A, Sections 13.1-13.2 (365-day). IHDS-II Income and Social Capital Questionnaire, Q14 14.38-14.39 (365-day). Nigeria GHS-Panel Wave 3, Household Questionnaire, Sections 10B/11 instead uses a 6-month recall for clothing (items 401-441); we follow the two India sources, since one of them (HCES) underlies our poverty line</t>
+          <t>HCES 2022-23, MoSPI Appendix A, Sections 12.1-12.3 (7-day in HCES; usual monthly here, and combined into one figure)</t>
         </is>
       </c>
     </row>
@@ -4908,7 +4956,7 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>cons_education_12m</t>
+          <t>cons_clothing_12m</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -4918,19 +4966,19 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>In the last 12 months, how much on education: fees, books, uniforms, tuition? (Rs)</t>
+          <t>In the last 12 months, how much did your household spend on clothes and footwear? (Rs)</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>पिछले 12 महीनों में पढ़ाई पर कितना ख़र्च हुआ: फ़ीस, किताबें, ड्रेस, ट्यूशन? (रुपये)</t>
+          <t>पिछले 12 महीनों में आपके घर ने कपड़ों और जूते-चप्पल पर कितना ख़र्च किया? (रुपये)</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr"/>
       <c r="I100" s="2" t="inlineStr"/>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t>HCES 2022-23, MoSPI Appendix A, Section 10.1 (365-day). IHDS-II Income and Social Capital Questionnaire, Q14 14.35-14.37 (365-day, same items). Nigeria GHS-Panel Wave 3, Household Questionnaire, Sections 10B/11 asks school fees inside its education/roster module, per child, not as a household total, so it is not directly comparable</t>
+          <t>HCES 2022-23, MoSPI Appendix A, Sections 13.1-13.2 (365-day). IHDS-II Income and Social Capital Questionnaire, Q14 14.38-14.39 (365-day). Nigeria GHS-Panel Wave 3, Household Questionnaire, Sections 10B/11 instead uses a 6-month recall for clothing (items 401-441); we follow the two India sources, since one of them (HCES) underlies our poverty line</t>
         </is>
       </c>
     </row>
@@ -4950,7 +4998,7 @@
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>cons_medical_hosp_12m</t>
+          <t>cons_education_12m</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
@@ -4960,19 +5008,19 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>In the last 12 months, how much did your household pay for any hospital admission or stay? (Rs, 0 if none)</t>
+          <t>In the last 12 months, how much on education: fees, books, uniforms, tuition? (Rs)</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>पिछले 12 महीनों में अस्पताल में भर्ती होने पर आपके घर का कितना ख़र्च हुआ? (रुपये, न हुआ हो तो 0)</t>
+          <t>पिछले 12 महीनों में पढ़ाई पर कितना ख़र्च हुआ: फ़ीस, किताबें, ड्रेस, ट्यूशन? (रुपये)</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr"/>
       <c r="I101" s="2" t="inlineStr"/>
       <c r="J101" s="2" t="inlineStr">
         <is>
-          <t>HCES 2022-23, MoSPI Appendix A, Section 10.2 (365-day, hospitalisation). IHDS-II Income and Social Capital Questionnaire, Q14 14.34 (365-day, in-patient). Nigeria GHS-Panel Wave 3, Household Questionnaire, Sections 10B/11 instead uses one combined 6-month medical item (less detail); we follow the matching HCES/IHDS split</t>
+          <t>HCES 2022-23, MoSPI Appendix A, Section 10.1 (365-day). IHDS-II Income and Social Capital Questionnaire, Q14 14.35-14.37 (365-day, same items). Nigeria GHS-Panel Wave 3, Household Questionnaire, Sections 10B/11 asks school fees inside its education/roster module, per child, not as a household total, so it is not directly comparable</t>
         </is>
       </c>
     </row>
@@ -4992,7 +5040,7 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>cons_durables_12m</t>
+          <t>cons_medical_hosp_12m</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
@@ -5002,19 +5050,19 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>In the last 12 months, how much on durable goods: furniture, utensils, appliances, phone, bicycle or motorcycle parts? (Rs)</t>
+          <t>In the last 12 months, how much did your household pay for any hospital admission or stay? (Rs, 0 if none)</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>पिछले 12 महीनों में सामान पर कितना ख़र्च हुआ: फ़र्नीचर, बर्तन, मशीनें, फ़ोन, साइकिल या गाड़ी के पुर्ज़े? (रुपये)</t>
+          <t>पिछले 12 महीनों में अस्पताल में भर्ती होने पर आपके घर का कितना ख़र्च हुआ? (रुपये, न हुआ हो तो 0)</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr"/>
       <c r="I102" s="2" t="inlineStr"/>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>HCES 2022-23, MoSPI Appendix A, Section 14 (365-day, 10 sub-groups). IHDS-II Income and Social Capital Questionnaire, Q14 14.40-14.48 (365-day). Nigeria GHS-Panel Wave 3, Household Questionnaire, Sections 10B/11 (12-month tier: durables, appliances, building materials). All three agree on the 12-month recall; insurance premiums, which IHDS (14.50) and the Nigeria survey (items 510-513) count here, are excluded, following HCES and standard national-accounts practice (insurance is a financial item, not consumption) -- premiums are covered instead by the insurance items in Module G</t>
+          <t>HCES 2022-23, MoSPI Appendix A, Section 10.2 (365-day, hospitalisation). IHDS-II Income and Social Capital Questionnaire, Q14 14.34 (365-day, in-patient). Nigeria GHS-Panel Wave 3, Household Questionnaire, Sections 10B/11 instead uses one combined 6-month medical item (less detail); we follow the matching HCES/IHDS split</t>
         </is>
       </c>
     </row>
@@ -5024,43 +5072,39 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>Housing, amenities and assets</t>
+          <t>Household consumption</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>floor_material</t>
+          <t>cons_durables_12m</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>select one</t>
+          <t>amount (Rs)</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>What is the main material of the floor at your usual home?</t>
+          <t>In the last 12 months, how much on durable goods: furniture, utensils, cooking appliances, phone, jewellery or ornaments, bicycle or vehicle parts? (Rs)</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>आपके असली घर में फ़र्श मुख्य रूप से किस चीज़ का है?</t>
-        </is>
-      </c>
-      <c r="H103" s="2" t="inlineStr">
-        <is>
-          <t>1 Mud/kaccha | 2 Cement/mud-cement | 3 Tile/mosaic/marble</t>
-        </is>
-      </c>
+          <t>पिछले 12 महीनों में सामान पर कितना ख़र्च हुआ: फ़र्नीचर, बर्तन, चूल्हा-मशीन, फ़ोन, गहने, साइकिल या गाड़ी के पुर्ज़े? (रुपये)</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr"/>
       <c r="I103" s="2" t="inlineStr"/>
       <c r="J103" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI housing indicator</t>
+          <t>HCES 2022-23, MoSPI Appendix A, Section 14 (365-day, 10 sub-groups). IHDS-II Income and Social Capital Questionnaire, Q14 14.40-14.48 (365-day). Nigeria GHS-Panel Wave 3, Household Questionnaire, Sections 10B/11 (12-month tier: durables, appliances, building materials). All three agree on the 12-month recall; insurance premiums, which IHDS (14.50) and the Nigeria survey (items 510-513) count here, are excluded, following HCES and standard national-accounts practice (insurance is a financial item, not consumption) -- premiums are covered instead by the insurance items in Module G</t>
         </is>
       </c>
     </row>
@@ -5080,7 +5124,7 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>roof_material</t>
+          <t>floor_material</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
@@ -5090,17 +5134,17 @@
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>What is the main material of the roof at your usual home?</t>
+          <t>What is the main material of the floor at your usual home?</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>आपके असली घर की छत मुख्य रूप से किस चीज़ की है?</t>
+          <t>आपके असली घर में फ़र्श मुख्य रूप से किस चीज़ का है?</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>1 Thatch/wood/mud | 2 Tin/GI sheet | 3 Concrete/RCC</t>
+          <t>1 Mud/kaccha | 2 Cement/mud-cement | 3 Tile/mosaic/marble</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr"/>
@@ -5126,7 +5170,7 @@
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>wall_material</t>
+          <t>roof_material</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
@@ -5136,23 +5180,23 @@
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>What are the walls of your usual home mainly made of?</t>
+          <t>What is the main material of the roof at your usual home?</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>आपके असली घर की दीवारें मुख्य रूप से किस चीज़ की बनी हैं?</t>
+          <t>आपके असली घर की छत मुख्य रूप से किस चीज़ की है?</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>1 Mud, thatch, bamboo or other natural material | 2 Unburnt brick, wood or tin | 3 Burnt brick, cement, concrete or stone</t>
+          <t>1 Thatch/wood/mud | 2 Tin/GI sheet | 3 Concrete/RCC</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr"/>
       <c r="J105" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI housing indicator (wall limb)</t>
+          <t>NITI Aayog National MPI housing indicator</t>
         </is>
       </c>
     </row>
@@ -5172,7 +5216,7 @@
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>house_type</t>
+          <t>wall_material</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
@@ -5182,23 +5226,23 @@
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>Would you describe your usual home as kaccha (mud/thatch, temporary), semi-pucca (part-concrete) or pucca (solid, permanent)?</t>
+          <t>What are the walls of your usual home mainly made of?</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>अपने असली घर को आप क्या कहेंगे: कच्चा (मिट्टी/फूस का, कामचलाऊ), अधपक्का, या पक्का (मज़बूत, स्थायी)?</t>
+          <t>आपके असली घर की दीवारें मुख्य रूप से किस चीज़ की बनी हैं?</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>1 Kaccha | 2 Semi-pucca | 3 Pucca</t>
+          <t>1 Mud, thatch, bamboo or other natural material | 2 Unburnt brick, wood or tin | 3 Burnt brick, cement, concrete or stone</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr"/>
       <c r="J106" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI housing indicator</t>
+          <t>NITI Aayog National MPI housing indicator (wall limb)</t>
         </is>
       </c>
     </row>
@@ -5218,33 +5262,33 @@
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>electricity</t>
+          <t>house_type</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>yes/no</t>
+          <t>select one</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>Does your usual home have an electricity connection?</t>
+          <t>Would you describe your usual home as kaccha (mud/thatch, temporary), semi-pucca (part-concrete) or pucca (solid, permanent)?</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>क्या आपके असली घर में बिजली का कनेक्शन है?</t>
+          <t>अपने असली घर को आप क्या कहेंगे: कच्चा (मिट्टी/फूस का, कामचलाऊ), अधपक्का, या पक्का (मज़बूत, स्थायी)?</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>0 No | 1 Yes</t>
+          <t>1 Kaccha | 2 Semi-pucca | 3 Pucca</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr"/>
       <c r="J107" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI</t>
+          <t>NITI Aayog National MPI housing indicator</t>
         </is>
       </c>
     </row>
@@ -5264,33 +5308,33 @@
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>toilet_type</t>
+          <t>electricity</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>select one</t>
+          <t>yes/no</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>What kind of toilet does your household use at your usual home?</t>
+          <t>Does your usual home have an electricity connection?</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>आपका घर अपने असली घर में किस तरह का शौचालय इस्तेमाल करता है?</t>
+          <t>क्या आपके असली घर में बिजली का कनेक्शन है?</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>1 No toilet / open defecation | 2 Pit latrine without slab or open pit | 3 Improved toilet, but shared with other households | 4 Improved toilet, used only by this household</t>
+          <t>0 No | 1 Yes</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr"/>
       <c r="J108" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI sanitation indicator (improved/unimproved and shared/not)</t>
+          <t>NITI Aayog National MPI</t>
         </is>
       </c>
     </row>
@@ -5310,7 +5354,7 @@
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>drinking_water</t>
+          <t>toilet_type</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
@@ -5320,23 +5364,23 @@
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>What is your main source of drinking water at your usual home?</t>
+          <t>What kind of toilet does your household use at your usual home?</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>आपके असली घर में पीने का पानी मुख्य रूप से कहाँ से आता है?</t>
+          <t>आपका घर अपने असली घर में किस तरह का शौचालय इस्तेमाल करता है?</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>1 Piped into the house or yard | 2 Public tap or standpipe | 3 Handpump, tubewell or borewell | 4 Protected well or protected spring | 5 Rainwater collection | 6 Bottled, packaged or community RO | 7 Unprotected well or unprotected spring | 8 River, stream, pond or canal | 9 Tanker truck or cart with drum</t>
+          <t>1 No toilet / open defecation | 2 Pit latrine without slab or open pit | 3 Improved toilet, but shared with other households | 4 Improved toilet, used only by this household</t>
         </is>
       </c>
       <c r="I109" s="2" t="inlineStr"/>
       <c r="J109" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI drinking-water indicator (JMP improved/unimproved taxonomy)</t>
+          <t>NITI Aayog National MPI sanitation indicator (improved/unimproved and shared/not)</t>
         </is>
       </c>
     </row>
@@ -5356,33 +5400,33 @@
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>water_on_premises</t>
+          <t>drinking_water</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>yes/no</t>
+          <t>select one</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>Is that water available at the house itself, or does someone have to go and fetch it?</t>
+          <t>What is your main source of drinking water at your usual home?</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>क्या वह पानी घर पर ही मिल जाता है, या किसी को लाने जाना पड़ता है?</t>
+          <t>आपके असली घर में पीने का पानी मुख्य रूप से कहाँ से आता है?</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>0 No | 1 Yes</t>
+          <t>1 Piped into the house or yard | 2 Public tap or standpipe | 3 Handpump, tubewell or borewell | 4 Protected well or protected spring | 5 Rainwater collection | 6 Bottled, packaged or community RO | 7 Unprotected well or unprotected spring | 8 River, stream, pond or canal | 9 Tanker truck or cart with drum</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr"/>
       <c r="J110" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI drinking-water indicator (30-minute round-trip rule)</t>
+          <t>NITI Aayog National MPI drinking-water indicator (JMP improved/unimproved taxonomy)</t>
         </is>
       </c>
     </row>
@@ -5402,30 +5446,30 @@
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>water_fetch_minutes</t>
+          <t>water_on_premises</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>whole number</t>
+          <t>yes/no</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>How long does it take to go there, get the water and come back? (minutes, round trip)</t>
+          <t>Is that water available at the house itself, or does someone have to go and fetch it?</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>वहाँ जाने, पानी भरने और लौटने में कुल कितना समय लगता है? (मिनट)</t>
-        </is>
-      </c>
-      <c r="H111" s="2" t="inlineStr"/>
-      <c r="I111" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if water_on_premises = 0</t>
-        </is>
-      </c>
+          <t>क्या वह पानी घर पर ही मिल जाता है, या किसी को लाने जाना पड़ता है?</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>0 No | 1 Yes</t>
+        </is>
+      </c>
+      <c r="I111" s="2" t="inlineStr"/>
       <c r="J111" s="2" t="inlineStr">
         <is>
           <t>NITI Aayog National MPI drinking-water indicator (30-minute round-trip rule)</t>
@@ -5448,29 +5492,25 @@
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>water_fetched_by</t>
+          <t>water_fetch_minutes</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>select one</t>
+          <t>whole number</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>Who in the household usually goes to fetch it?</t>
+          <t>How long does it take to go there, get the water and come back? (minutes, round trip)</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>घर में आम तौर पर पानी कौन लाता है?</t>
-        </is>
-      </c>
-      <c r="H112" s="2" t="inlineStr">
-        <is>
-          <t>1 An adult woman | 2 An adult man | 3 A girl under 15 | 4 A boy under 15 | 5 It varies / more than one person</t>
-        </is>
-      </c>
+          <t>वहाँ जाने, पानी भरने और लौटने में कुल कितना समय लगता है? (मिनट)</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="inlineStr"/>
       <c r="I112" s="2" t="inlineStr">
         <is>
           <t>Ask only if water_on_premises = 0</t>
@@ -5478,7 +5518,7 @@
       </c>
       <c r="J112" s="2" t="inlineStr">
         <is>
-          <t>Project design (intra-household burden of water collection; DHS/NFHS ask the same item)</t>
+          <t>NITI Aayog National MPI drinking-water indicator (30-minute round-trip rule)</t>
         </is>
       </c>
     </row>
@@ -5498,7 +5538,7 @@
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>cooking_fuel</t>
+          <t>water_fetched_by</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
@@ -5508,23 +5548,27 @@
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>What does your household mainly use to cook at your usual home?</t>
+          <t>Who in the household usually goes to fetch it?</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>आपके असली घर में खाना मुख्य रूप से किस चीज़ पर बनता है?</t>
+          <t>घर में आम तौर पर पानी कौन लाता है?</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>1 LPG or cylinder gas | 2 Piped natural gas | 3 Electricity | 4 Biogas (gobar gas plant) | 5 Kerosene | 6 Firewood | 7 Dung cakes (gobar) | 8 Crop residue, straw or shrubs | 9 Charcoal | 10 Coal or lignite</t>
-        </is>
-      </c>
-      <c r="I113" s="2" t="inlineStr"/>
+          <t>1 An adult woman | 2 An adult man | 3 A girl under 15 | 4 A boy under 15 | 5 It varies / more than one person</t>
+        </is>
+      </c>
+      <c r="I113" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if water_on_premises = 0</t>
+        </is>
+      </c>
       <c r="J113" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI cooking-fuel indicator (its own list of dirty fuels)</t>
+          <t>Project design (intra-household burden of water collection; DHS/NFHS ask the same item)</t>
         </is>
       </c>
     </row>
@@ -5544,33 +5588,33 @@
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>owns_tv</t>
+          <t>cooking_fuel</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>yes/no</t>
+          <t>select one</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>Does your household own: a television?</t>
+          <t>What does your household mainly use to cook at your usual home?</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>क्या आपके घर में टीवी है?</t>
+          <t>आपके असली घर में खाना मुख्य रूप से किस चीज़ पर बनता है?</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>0 No | 1 Yes</t>
+          <t>1 LPG or cylinder gas | 2 Piped natural gas | 3 Electricity | 4 Biogas (gobar gas plant) | 5 Kerosene | 6 Firewood | 7 Dung cakes (gobar) | 8 Crop residue, straw or shrubs | 9 Charcoal | 10 Coal or lignite</t>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr"/>
       <c r="J114" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI assets indicator</t>
+          <t>NITI Aayog National MPI cooking-fuel indicator (its own list of dirty fuels)</t>
         </is>
       </c>
     </row>
@@ -5590,7 +5634,7 @@
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>owns_radio</t>
+          <t>owns_tv</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
@@ -5600,12 +5644,12 @@
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>... a radio?</t>
+          <t>Does your household own: a television?</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>...रेडियो?</t>
+          <t>क्या आपके घर में टीवी है?</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
@@ -5636,7 +5680,7 @@
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>owns_bicycle</t>
+          <t>owns_radio</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
@@ -5646,12 +5690,12 @@
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>... a bicycle?</t>
+          <t>... a radio?</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>...साइकिल?</t>
+          <t>...रेडियो?</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
@@ -5682,7 +5726,7 @@
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>owns_motorcycle</t>
+          <t>owns_bicycle</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
@@ -5692,12 +5736,12 @@
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>... a motorcycle or scooter?</t>
+          <t>... a bicycle?</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>...मोटरसाइकिल या स्कूटर?</t>
+          <t>...साइकिल?</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr">
@@ -5728,7 +5772,7 @@
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>owns_car</t>
+          <t>owns_motorcycle</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
@@ -5738,12 +5782,12 @@
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>... a car, jeep or truck?</t>
+          <t>... a motorcycle or scooter?</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>...कार, जीप या ट्रक?</t>
+          <t>...मोटरसाइकिल या स्कूटर?</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
@@ -5754,7 +5798,7 @@
       <c r="I118" s="2" t="inlineStr"/>
       <c r="J118" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI assets indicator (car or truck limb)</t>
+          <t>NITI Aayog National MPI assets indicator</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5818,7 @@
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>owns_phone</t>
+          <t>owns_car</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
@@ -5784,12 +5828,12 @@
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>... a telephone of any kind, mobile or landline?</t>
+          <t>... a car, jeep or truck?</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>...कोई फ़ोन, मोबाइल या लैंडलाइन?</t>
+          <t>...कार, जीप या ट्रक?</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
@@ -5800,7 +5844,7 @@
       <c r="I119" s="2" t="inlineStr"/>
       <c r="J119" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI assets indicator</t>
+          <t>NITI Aayog National MPI assets indicator (car or truck limb)</t>
         </is>
       </c>
     </row>
@@ -5820,7 +5864,7 @@
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>owns_computer</t>
+          <t>owns_phone</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
@@ -5830,12 +5874,12 @@
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>... a computer or laptop?</t>
+          <t>... a telephone of any kind, mobile or landline?</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>...कंप्यूटर या लैपटॉप?</t>
+          <t>...कोई फ़ोन, मोबाइल या लैंडलाइन?</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
@@ -5866,7 +5910,7 @@
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>owns_animal_cart</t>
+          <t>owns_computer</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
@@ -5876,12 +5920,12 @@
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>... a cart pulled by an animal?</t>
+          <t>... a computer or laptop?</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>...जानवर से खींची जाने वाली गाड़ी?</t>
+          <t>...कंप्यूटर या लैपटॉप?</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
@@ -5912,7 +5956,7 @@
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>owns_fridge</t>
+          <t>owns_animal_cart</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
@@ -5922,12 +5966,12 @@
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>... a refrigerator?</t>
+          <t>... a cart pulled by an animal?</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>...फ़्रिज?</t>
+          <t>...जानवर से खींची जाने वाली गाड़ी?</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
@@ -5958,29 +6002,33 @@
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>land_cultivable_acres</t>
+          <t>owns_fridge</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>yes/no</t>
         </is>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>How much CULTIVABLE land does your household own or cultivate, in acres? Do not count the land the house stands on. (0 if none)</t>
+          <t>... a refrigerator?</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>आपके घर के पास कितनी जोतने लायक़ ज़मीन है, अपनी या जोतने की, एकड़ में? जिस ज़मीन पर घर बना है उसे मत गिनिए। (न हो तो 0)</t>
-        </is>
-      </c>
-      <c r="H123" s="2" t="inlineStr"/>
+          <t>...फ़्रिज?</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="inlineStr">
+        <is>
+          <t>0 No | 1 Yes</t>
+        </is>
+      </c>
       <c r="I123" s="2" t="inlineStr"/>
       <c r="J123" s="2" t="inlineStr">
         <is>
-          <t>Chaudhuri et al. 2002 asset covariate</t>
+          <t>NITI Aayog National MPI assets indicator</t>
         </is>
       </c>
     </row>
@@ -6000,29 +6048,25 @@
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>owns_cow_buffalo</t>
+          <t>land_cultivable_acres</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>yes/no</t>
+          <t>number</t>
         </is>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>Does your household own any cows or buffaloes?</t>
+          <t>How much CULTIVABLE land does your household own or cultivate, in acres? Do not count the land the house stands on. (0 if none)</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>क्या आपके घर में गाय या भैंस है?</t>
-        </is>
-      </c>
-      <c r="H124" s="2" t="inlineStr">
-        <is>
-          <t>0 No | 1 Yes</t>
-        </is>
-      </c>
+          <t>आपके घर के पास कितनी जोतने लायक़ ज़मीन है, अपनी या जोतने की, एकड़ में? जिस ज़मीन पर घर बना है उसे मत गिनिए। (न हो तो 0)</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="inlineStr"/>
       <c r="I124" s="2" t="inlineStr"/>
       <c r="J124" s="2" t="inlineStr">
         <is>
@@ -6046,7 +6090,7 @@
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>owns_goat_sheep</t>
+          <t>owns_cow_buffalo</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
@@ -6056,12 +6100,12 @@
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>Does your household own any goats or sheep?</t>
+          <t>Does your household own any cows or buffaloes?</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>क्या आपके घर में बकरी या भेड़ है?</t>
+          <t>क्या आपके घर में गाय या भैंस है?</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
@@ -6092,7 +6136,7 @@
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>owns_pony_mule</t>
+          <t>owns_goat_sheep</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
@@ -6102,12 +6146,12 @@
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>Does your household own any ponies or mules?</t>
+          <t>Does your household own any goats or sheep?</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>क्या आपके घर में घोड़ा या खच्चर है?</t>
+          <t>क्या आपके घर में बकरी या भेड़ है?</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr">
@@ -6118,7 +6162,7 @@
       <c r="I126" s="2" t="inlineStr"/>
       <c r="J126" s="2" t="inlineStr">
         <is>
-          <t>Project design (pilot livelihood survey)</t>
+          <t>Chaudhuri et al. 2002 asset covariate</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6182,7 @@
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>owns_shop_stall</t>
+          <t>owns_pony_mule</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
@@ -6148,12 +6192,12 @@
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>Does your household own a shop or stall that you use to earn?</t>
+          <t>Does your household own any ponies or mules?</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>क्या आपके घर की अपनी दुकान या खोखा है जिससे आप कमाते हैं?</t>
+          <t>क्या आपके घर में घोड़ा या खच्चर है?</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
@@ -6164,7 +6208,7 @@
       <c r="I127" s="2" t="inlineStr"/>
       <c r="J127" s="2" t="inlineStr">
         <is>
-          <t>Chaudhuri et al. 2002 asset covariate</t>
+          <t>Project design (pilot livelihood survey)</t>
         </is>
       </c>
     </row>
@@ -6184,7 +6228,7 @@
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>owns_work_vehicle</t>
+          <t>owns_shop_stall</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
@@ -6194,12 +6238,12 @@
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>Does your household own a vehicle you use to earn (for example a jeep, truck or taxi)?</t>
+          <t>Does your household own a shop or stall that you use to earn?</t>
         </is>
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>क्या आपके घर की अपनी गाड़ी है जिससे आप कमाते हैं (जैसे जीप, ट्रक या टैक्सी)?</t>
+          <t>क्या आपके घर की अपनी दुकान या खोखा है जिससे आप कमाते हैं?</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr">
@@ -6230,7 +6274,7 @@
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>owns_work_equipment</t>
+          <t>owns_work_vehicle</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
@@ -6240,12 +6284,12 @@
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>Does your household own equipment or tools that you use to earn?</t>
+          <t>Does your household own a vehicle you use to earn (for example a jeep, truck or taxi)?</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>क्या आपके घर के पास काम के औज़ार या मशीन है जिससे आप कमाते हैं?</t>
+          <t>क्या आपके घर की अपनी गाड़ी है जिससे आप कमाते हैं (जैसे जीप, ट्रक या टैक्सी)?</t>
         </is>
       </c>
       <c r="H129" s="2" t="inlineStr">
@@ -6276,33 +6320,33 @@
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>work_equipment_detail</t>
+          <t>owns_work_equipment</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>free text</t>
+          <t>yes/no</t>
         </is>
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>What are they? Write what they say. Leave blank if they cannot say.</t>
+          <t>Does your household own equipment or tools that you use to earn?</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>वे क्या हैं? जैसा वे बताएँ वैसा लिख लीजिए। न बता पाएँ तो खाली छोड़ दीजिए।</t>
-        </is>
-      </c>
-      <c r="H130" s="2" t="inlineStr"/>
-      <c r="I130" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if owns_work_equipment = 1; may be left blank</t>
-        </is>
-      </c>
+          <t>क्या आपके घर के पास काम के औज़ार या मशीन है जिससे आप कमाते हैं?</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>0 No | 1 Yes</t>
+        </is>
+      </c>
+      <c r="I130" s="2" t="inlineStr"/>
       <c r="J130" s="2" t="inlineStr">
         <is>
-          <t>Standard household-survey item</t>
+          <t>Chaudhuri et al. 2002 asset covariate</t>
         </is>
       </c>
     </row>
@@ -6312,43 +6356,43 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>Finance, insurance and schemes</t>
+          <t>Housing, amenities and assets</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>has_bank_account</t>
+          <t>work_equipment_detail</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>yes/no</t>
+          <t>free text</t>
         </is>
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t>Does anyone in your household have a bank account or a post office account?</t>
+          <t>What are they? Write what they say. Leave blank if they cannot say.</t>
         </is>
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>क्या आपके घर में किसी का बैंक खाता या डाकघर का खाता है?</t>
-        </is>
-      </c>
-      <c r="H131" s="2" t="inlineStr">
-        <is>
-          <t>0 No | 1 Yes</t>
-        </is>
-      </c>
-      <c r="I131" s="2" t="inlineStr"/>
+          <t>वे क्या हैं? जैसा वे बताएँ वैसा लिख लीजिए। न बता पाएँ तो खाली छोड़ दीजिए।</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="inlineStr"/>
+      <c r="I131" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if owns_work_equipment = 1; may be left blank</t>
+        </is>
+      </c>
       <c r="J131" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI bank-account indicator; VEP adaptive-capacity covariate</t>
+          <t>Standard household-survey item</t>
         </is>
       </c>
     </row>
@@ -6368,7 +6412,7 @@
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>has_jandhan_account</t>
+          <t>has_bank_account</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
@@ -6378,12 +6422,12 @@
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>Is any of these a Jan Dhan account?</t>
+          <t>Does anyone in your household have a bank account or a post office account?</t>
         </is>
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>क्या उनमें से कोई जन धन खाता है?</t>
+          <t>क्या आपके घर में किसी का बैंक खाता या डाकघर का खाता है?</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
@@ -6391,14 +6435,10 @@
           <t>0 No | 1 Yes</t>
         </is>
       </c>
-      <c r="I132" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if has_bank_account = 1</t>
-        </is>
-      </c>
+      <c r="I132" s="2" t="inlineStr"/>
       <c r="J132" s="2" t="inlineStr">
         <is>
-          <t>Standard household-survey item</t>
+          <t>NITI Aayog National MPI bank-account indicator; VEP adaptive-capacity covariate</t>
         </is>
       </c>
     </row>
@@ -6418,7 +6458,7 @@
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>took_loan_12m</t>
+          <t>has_jandhan_account</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
@@ -6428,12 +6468,12 @@
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>In the last 12 months, did you or anyone in your household borrow money?</t>
+          <t>Is any of these a Jan Dhan account?</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>पिछले 12 महीनों में क्या आपने या आपके घर के किसी सदस्य ने पैसा उधार लिया?</t>
+          <t>क्या उनमें से कोई जन धन खाता है?</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
@@ -6441,10 +6481,14 @@
           <t>0 No | 1 Yes</t>
         </is>
       </c>
-      <c r="I133" s="2" t="inlineStr"/>
+      <c r="I133" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if has_bank_account = 1</t>
+        </is>
+      </c>
       <c r="J133" s="2" t="inlineStr">
         <is>
-          <t>VEP adaptive-capacity covariate</t>
+          <t>Standard household-survey item</t>
         </is>
       </c>
     </row>
@@ -6464,37 +6508,33 @@
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>credit_source</t>
+          <t>took_loan_12m</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>select one</t>
+          <t>yes/no</t>
         </is>
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>Who was the main lender?</t>
+          <t>In the last 12 months, did you or anyone in your household borrow money?</t>
         </is>
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>मुख्य रूप से किससे उधार लिया?</t>
+          <t>पिछले 12 महीनों में क्या आपने या आपके घर के किसी सदस्य ने पैसा उधार लिया?</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
-          <t>1 Nationalised or public-sector bank | 2 Private bank | 3 Cooperative bank or RRB | 4 Microfinance institution or SHG | 5 Moneylender | 6 Relative or friend | 7 Employer or contractor (advance) | 8 Other</t>
-        </is>
-      </c>
-      <c r="I134" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if took_loan_12m = 1</t>
-        </is>
-      </c>
+          <t>0 No | 1 Yes</t>
+        </is>
+      </c>
+      <c r="I134" s="2" t="inlineStr"/>
       <c r="J134" s="2" t="inlineStr">
         <is>
-          <t>VEP adaptive-capacity covariate (lender type)</t>
+          <t>VEP adaptive-capacity covariate</t>
         </is>
       </c>
     </row>
@@ -6514,25 +6554,29 @@
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>loan_amount</t>
+          <t>credit_source</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>amount (Rs)</t>
+          <t>select one</t>
         </is>
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>How much do you still owe on it altogether? (Rs)</t>
+          <t>Who was the main lender?</t>
         </is>
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>उसमें से अब भी कुल कितना बाक़ी है? (रुपये)</t>
-        </is>
-      </c>
-      <c r="H135" s="2" t="inlineStr"/>
+          <t>मुख्य रूप से किससे उधार लिया?</t>
+        </is>
+      </c>
+      <c r="H135" s="2" t="inlineStr">
+        <is>
+          <t>1 Nationalised or public-sector bank | 2 Private bank | 3 Cooperative bank or RRB | 4 Microfinance institution or SHG | 5 Moneylender | 6 Relative or friend | 7 Employer or contractor (advance) | 8 Other</t>
+        </is>
+      </c>
       <c r="I135" s="2" t="inlineStr">
         <is>
           <t>Ask only if took_loan_12m = 1</t>
@@ -6540,7 +6584,7 @@
       </c>
       <c r="J135" s="2" t="inlineStr">
         <is>
-          <t>Islam and Chowdhury 2025 (financial distress and household vulnerability to poverty)</t>
+          <t>VEP adaptive-capacity covariate (lender type)</t>
         </is>
       </c>
     </row>
@@ -6560,33 +6604,33 @@
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>loan_interest_per100_pm</t>
+          <t>loan_amount</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>amount (Rs)</t>
         </is>
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>On every 100 rupees you borrowed, about how much interest do you pay in a month? (Rs; 0 if none, leave blank if not known)</t>
+          <t>How much of that loan is still left to repay? (Rs)</t>
         </is>
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>आपने जो 100 रुपये उधार लिए, उन पर महीने का कितना ब्याज देते हैं? (रुपये; न हो तो 0, पता न हो तो खाली छोड़ दें)</t>
+          <t>उस क़र्ज़ में से अब भी कितना चुकाना बाक़ी है? (रुपये)</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr"/>
       <c r="I136" s="2" t="inlineStr">
         <is>
-          <t>Ask only if took_loan_12m = 1; may be left blank</t>
+          <t>Ask only if took_loan_12m = 1</t>
         </is>
       </c>
       <c r="J136" s="2" t="inlineStr">
         <is>
-          <t>Project design (informal-credit pricing as locally quoted)</t>
+          <t>Islam and Chowdhury 2025 (financial distress and household vulnerability to poverty)</t>
         </is>
       </c>
     </row>
@@ -6606,7 +6650,7 @@
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>loan_against_asset</t>
+          <t>pays_interest</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
@@ -6616,12 +6660,12 @@
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>Did you have to give something as security for it -- an animal, a vehicle, jewellery, land or your business?</t>
+          <t>Do you pay interest on it?</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>क्या उसके बदले कुछ गिरवी रखना पड़ा — जानवर, गाड़ी, गहने, ज़मीन या आपका धंधा?</t>
+          <t>क्या आप उस पर ब्याज देते हैं?</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr">
@@ -6636,7 +6680,7 @@
       </c>
       <c r="J137" s="2" t="inlineStr">
         <is>
-          <t>Carter and Zimmerman 2000; Chiwaula et al. 2011 (asset-based vulnerability)</t>
+          <t>Project design (informal lending is often interest-free)</t>
         </is>
       </c>
     </row>
@@ -6656,29 +6700,33 @@
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>n_health_insured</t>
+          <t>loan_interest_per100_pm</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>whole number</t>
+          <t>number</t>
         </is>
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>How many people in your household are covered by any health insurance or health scheme, including government ones? (0 if none)</t>
+          <t>On every 100 rupees you borrowed, about how much interest do you pay in a month? (Rs; 0 if none, leave blank if not known)</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>आपके घर में कितने लोगों का कोई स्वास्थ्य बीमा या स्वास्थ्य योजना है, सरकारी भी मिलाकर? (कोई नहीं तो 0)</t>
+          <t>आपने जो 100 रुपये उधार लिए, उन पर महीने का कितना ब्याज देते हैं? (रुपये; दर पता न हो तो खाली छोड़ दें)</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr"/>
-      <c r="I138" s="2" t="inlineStr"/>
+      <c r="I138" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if took_loan_12m = 1; may be left blank</t>
+        </is>
+      </c>
       <c r="J138" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI health-insurance indicator; Lyons et al. 2023</t>
+          <t>Project design (informal-credit pricing as locally quoted)</t>
         </is>
       </c>
     </row>
@@ -6698,29 +6746,37 @@
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>n_life_insured</t>
+          <t>loan_collateral</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>whole number</t>
+          <t>select one</t>
         </is>
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>How many people in your household have life insurance? (0 if none)</t>
+          <t>What did you have to give as security?</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>आपके घर में कितने लोगों का जीवन बीमा है? (कोई नहीं तो 0)</t>
-        </is>
-      </c>
-      <c r="H139" s="2" t="inlineStr"/>
-      <c r="I139" s="2" t="inlineStr"/>
+          <t>आपको क्या गिरवी रखना पड़ा?</t>
+        </is>
+      </c>
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t>1 Jewellery or ornaments | 2 Land | 3 Animals | 4 A vehicle | 5 Shop stock or business goods | 6 House or building | 7 Something else</t>
+        </is>
+      </c>
+      <c r="I139" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if loan_against_asset = 1</t>
+        </is>
+      </c>
       <c r="J139" s="2" t="inlineStr">
         <is>
-          <t>Standard household-survey item</t>
+          <t>Carter and Zimmerman 2000; Zimmerman and Carter 2003 (asset-based coping)</t>
         </is>
       </c>
     </row>
@@ -6740,7 +6796,7 @@
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>has_crop_insurance</t>
+          <t>loan_against_asset</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
@@ -6750,12 +6806,12 @@
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>Is your crop insured?</t>
+          <t>Did you have to give something as security for it -- an animal, a vehicle, jewellery, land or your business?</t>
         </is>
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>क्या आपकी फ़सल का बीमा है?</t>
+          <t>क्या उसके बदले कुछ गिरवी रखना पड़ा — जानवर, गाड़ी, गहने, ज़मीन या आपका धंधा?</t>
         </is>
       </c>
       <c r="H140" s="2" t="inlineStr">
@@ -6765,12 +6821,12 @@
       </c>
       <c r="I140" s="2" t="inlineStr">
         <is>
-          <t>Ask only if land_cultivable_acres &gt; 0</t>
+          <t>Ask only if took_loan_12m = 1</t>
         </is>
       </c>
       <c r="J140" s="2" t="inlineStr">
         <is>
-          <t>Standard household-survey item</t>
+          <t>Carter and Zimmerman 2000; Chiwaula et al. 2011 (asset-based vulnerability)</t>
         </is>
       </c>
     </row>
@@ -6790,33 +6846,29 @@
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>govt_scheme_beneficiary</t>
+          <t>n_health_insured</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>yes/no</t>
+          <t>whole number</t>
         </is>
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t>In the last 12 months, did your household receive benefits from any government scheme (for example ration, pension, cash transfer)?</t>
+          <t>How many people in your household are covered by any health insurance or health scheme, including government ones? (0 if none)</t>
         </is>
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>पिछले 12 महीनों में क्या आपके घर को किसी सरकारी योजना से कुछ मिला (जैसे राशन, पेंशन, पैसा)?</t>
-        </is>
-      </c>
-      <c r="H141" s="2" t="inlineStr">
-        <is>
-          <t>0 No | 1 Yes</t>
-        </is>
-      </c>
+          <t>आपके घर में कितने लोगों का कोई स्वास्थ्य बीमा या स्वास्थ्य योजना है, सरकारी भी मिलाकर? (कोई नहीं तो 0)</t>
+        </is>
+      </c>
+      <c r="H141" s="2" t="inlineStr"/>
       <c r="I141" s="2" t="inlineStr"/>
       <c r="J141" s="2" t="inlineStr">
         <is>
-          <t>Standard household-survey item</t>
+          <t>NITI Aayog National MPI health-insurance indicator; Lyons et al. 2023</t>
         </is>
       </c>
     </row>
@@ -6836,30 +6888,26 @@
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>govt_scheme_which</t>
+          <t>n_life_insured</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>free text</t>
+          <t>whole number</t>
         </is>
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>Which ones? Write what they say. If they cannot name it, leave this blank and move on.</t>
+          <t>How many people in your household have life insurance? (0 if none)</t>
         </is>
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>कौन सी? जैसा वे बताएँ वैसा लिख लीजिए। अगर नाम न बता पाएँ तो खाली छोड़ दीजिए।</t>
+          <t>आपके घर में कितने लोगों का जीवन बीमा है? (कोई नहीं तो 0)</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr"/>
-      <c r="I142" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if govt_scheme_beneficiary = 1; may be left blank</t>
-        </is>
-      </c>
+      <c r="I142" s="2" t="inlineStr"/>
       <c r="J142" s="2" t="inlineStr">
         <is>
           <t>Standard household-survey item</t>
@@ -6882,7 +6930,7 @@
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>smartphone_owned</t>
+          <t>has_crop_insurance</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
@@ -6892,12 +6940,12 @@
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
-          <t>Do you own a smartphone?</t>
+          <t>Is your crop insured?</t>
         </is>
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>क्या आपके पास स्मार्टफ़ोन है?</t>
+          <t>क्या आपकी फ़सल का बीमा है?</t>
         </is>
       </c>
       <c r="H143" s="2" t="inlineStr">
@@ -6905,10 +6953,14 @@
           <t>0 No | 1 Yes</t>
         </is>
       </c>
-      <c r="I143" s="2" t="inlineStr"/>
+      <c r="I143" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if land_cultivable_acres &gt; 0</t>
+        </is>
+      </c>
       <c r="J143" s="2" t="inlineStr">
         <is>
-          <t>VEP adaptive-capacity covariate; STEP digital items</t>
+          <t>Standard household-survey item</t>
         </is>
       </c>
     </row>
@@ -6928,7 +6980,7 @@
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>uses_digital_payment</t>
+          <t>govt_scheme_beneficiary</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
@@ -6938,12 +6990,12 @@
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>Do you ever use UPI or another way of paying by phone?</t>
+          <t>In the last 12 months, did your household receive benefits from any government scheme (for example ration, pension, cash transfer)?</t>
         </is>
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>क्या आप कभी UPI या फ़ोन से पैसे का लेन-देन करते हैं?</t>
+          <t>पिछले 12 महीनों में क्या आपके घर को किसी सरकारी योजना से कुछ मिला (जैसे राशन, पेंशन, पैसा)?</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
@@ -6954,7 +7006,7 @@
       <c r="I144" s="2" t="inlineStr"/>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>VEP adaptive-capacity covariate; STEP digital items</t>
+          <t>Standard household-survey item</t>
         </is>
       </c>
     </row>
@@ -6974,29 +7026,33 @@
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>n_can_transact_online</t>
+          <t>govt_scheme_which</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>whole number</t>
+          <t>free text</t>
         </is>
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
-          <t>How many people in your household can make a payment by phone themselves, without help? (0 if none)</t>
+          <t>Which ones? Write what they say. If they cannot name it, leave this blank and move on.</t>
         </is>
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>आपके घर में कितने लोग बिना किसी की मदद के फ़ोन से पैसे भेज सकते हैं? (कोई नहीं तो 0)</t>
+          <t>कौन सी? जैसा वे बताएँ वैसा लिख लीजिए। अगर नाम न बता पाएँ तो खाली छोड़ दीजिए।</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr"/>
-      <c r="I145" s="2" t="inlineStr"/>
+      <c r="I145" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if govt_scheme_beneficiary = 1; may be left blank</t>
+        </is>
+      </c>
       <c r="J145" s="2" t="inlineStr">
         <is>
-          <t>Project design (intra-household financial capability)</t>
+          <t>Standard household-survey item</t>
         </is>
       </c>
     </row>
@@ -7006,17 +7062,17 @@
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Finance, insurance and schemes</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>morbidity_15d</t>
+          <t>smartphone_owned</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
@@ -7026,12 +7082,12 @@
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t>In the last 15 days, was anyone in your household ill?</t>
+          <t>Do you own a smartphone?</t>
         </is>
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>पिछले 15 दिनों में क्या आपके घर में कोई बीमार पड़ा?</t>
+          <t>क्या आपके पास स्मार्टफ़ोन है?</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
@@ -7042,7 +7098,7 @@
       <c r="I146" s="2" t="inlineStr"/>
       <c r="J146" s="2" t="inlineStr">
         <is>
-          <t>NSS health module (15-day recall)</t>
+          <t>VEP adaptive-capacity covariate; STEP digital items</t>
         </is>
       </c>
     </row>
@@ -7052,47 +7108,43 @@
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Finance, insurance and schemes</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>morbidity_coping_15d</t>
+          <t>uses_digital_payment</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>select one</t>
+          <t>yes/no</t>
         </is>
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
-          <t>How did the household mainly cope with the cost of this: used savings; borrowed money; sold or pawned assets; cut other consumption; got help from relatives or community; or something else?</t>
+          <t>Do you ever use UPI or another way of paying by phone?</t>
         </is>
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>इसका ख़र्च आपके घर ने मुख्य रूप से कैसे उठाया: जमा पैसे से; उधार लेकर; कुछ बेचकर या गिरवी रखकर; बाकी ख़र्च घटाकर; रिश्तेदारों या गाँव वालों की मदद से; या किसी और तरह?</t>
+          <t>क्या आप कभी UPI या फ़ोन से पैसे का लेन-देन करते हैं?</t>
         </is>
       </c>
       <c r="H147" s="2" t="inlineStr">
         <is>
-          <t>1 Used savings | 2 Borrowed money | 3 Sold or pawned assets | 4 Cut consumption | 5 Help from relatives/community | 6 Did nothing/other</t>
-        </is>
-      </c>
-      <c r="I147" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if morbidity_15d = 1</t>
-        </is>
-      </c>
+          <t>0 No | 1 Yes</t>
+        </is>
+      </c>
+      <c r="I147" s="2" t="inlineStr"/>
       <c r="J147" s="2" t="inlineStr">
         <is>
-          <t>Project design (a reported illness with no cost/coping follow-up said nothing about its burden)</t>
+          <t>VEP adaptive-capacity covariate; STEP digital items</t>
         </is>
       </c>
     </row>
@@ -7102,43 +7154,39 @@
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Finance, insurance and schemes</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>morbidity_cost_15d</t>
+          <t>n_can_transact_online</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>amount (Rs)</t>
+          <t>whole number</t>
         </is>
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
-          <t>About how much did the household spend on this in the last 15 days (medicine, doctor or clinic fees, travel for care)? (Rs)</t>
+          <t>How many people in your household can make a payment by phone themselves, without help? (0 if none)</t>
         </is>
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>पिछले 15 दिनों में इस पर घर का लगभग कितना ख़र्च हुआ (दवाई, डॉक्टर या क्लीनिक की फ़ीस, आने-जाने का ख़र्च)? (रुपये)</t>
+          <t>आपके घर में कितने लोग बिना किसी की मदद के फ़ोन से पैसे भेज सकते हैं? (कोई नहीं तो 0)</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr"/>
-      <c r="I148" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if morbidity_15d = 1</t>
-        </is>
-      </c>
+      <c r="I148" s="2" t="inlineStr"/>
       <c r="J148" s="2" t="inlineStr">
         <is>
-          <t>Project design</t>
+          <t>Project design (intra-household financial capability)</t>
         </is>
       </c>
     </row>
@@ -7158,7 +7206,7 @@
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>hospitalization_365d</t>
+          <t>morbidity_15d</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
@@ -7168,12 +7216,12 @@
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
-          <t>In the last 12 months, was anyone in your household admitted to hospital overnight?</t>
+          <t>In the last 15 days, was anyone in your household ill?</t>
         </is>
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>पिछले 12 महीनों में क्या आपके घर का कोई रात भर के लिए अस्पताल में भर्ती हुआ?</t>
+          <t>पिछले 15 दिनों में क्या आपके घर में कोई बीमार पड़ा?</t>
         </is>
       </c>
       <c r="H149" s="2" t="inlineStr">
@@ -7184,7 +7232,7 @@
       <c r="I149" s="2" t="inlineStr"/>
       <c r="J149" s="2" t="inlineStr">
         <is>
-          <t>NSS health module (365-day recall)</t>
+          <t>NSS health module (15-day recall)</t>
         </is>
       </c>
     </row>
@@ -7204,33 +7252,37 @@
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>health_access_barrier_3m</t>
+          <t>morbidity_coping_15d</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>yes/no</t>
+          <t>select one</t>
         </is>
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>In the last 3 months, was there a time when someone in your household needed medical care but could not get it?</t>
+          <t>How did the household mainly cope with the cost of this: used savings; borrowed money; sold or pawned assets; cut other consumption; got help from relatives or community; or something else?</t>
         </is>
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>पिछले 3 महीनों में क्या कभी ऐसा हुआ कि आपके घर में किसी को इलाज की ज़रूरत थी पर मिल नहीं पाया?</t>
+          <t>इसका ख़र्च आपके घर ने मुख्य रूप से कैसे उठाया: जमा पैसे से; उधार लेकर; कुछ बेचकर या गिरवी रखकर; बाकी ख़र्च घटाकर; रिश्तेदारों या गाँव वालों की मदद से; या किसी और तरह?</t>
         </is>
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
-          <t>0 No | 1 Yes</t>
-        </is>
-      </c>
-      <c r="I150" s="2" t="inlineStr"/>
+          <t>1 Used savings | 2 Borrowed money | 3 Sold or pawned assets | 4 Cut consumption | 5 Help from relatives/community | 6 Did nothing/other</t>
+        </is>
+      </c>
+      <c r="I150" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if morbidity_15d = 1</t>
+        </is>
+      </c>
       <c r="J150" s="2" t="inlineStr">
         <is>
-          <t>VASyR 2025 barriers_health_case_access_phc_m (primary-care access barriers); Lyons et al. 2023 Table 2 indicator 2 'healthcare access'</t>
+          <t>Project design (a reported illness with no cost/coping follow-up said nothing about its burden)</t>
         </is>
       </c>
     </row>
@@ -7250,33 +7302,33 @@
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>child_death_5y</t>
+          <t>morbidity_cost_15d</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>yes/no</t>
+          <t>amount (Rs)</t>
         </is>
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
-          <t>In the last five years, has any child or young person under 18 in your household died?</t>
+          <t>About how much did the household spend on this in the last 15 days (medicine, doctor or clinic fees, travel for care)? (Rs)</t>
         </is>
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>पिछले पाँच साल में क्या आपके घर के 18 साल से छोटे किसी बच्चे या किशोर की मृत्यु हुई?</t>
-        </is>
-      </c>
-      <c r="H151" s="2" t="inlineStr">
-        <is>
-          <t>0 No | 1 Yes</t>
-        </is>
-      </c>
-      <c r="I151" s="2" t="inlineStr"/>
+          <t>पिछले 15 दिनों में इस पर घर का लगभग कितना ख़र्च हुआ (दवाई, डॉक्टर या क्लीनिक की फ़ीस, आने-जाने का ख़र्च)? (रुपये)</t>
+        </is>
+      </c>
+      <c r="H151" s="2" t="inlineStr"/>
+      <c r="I151" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if morbidity_15d = 1</t>
+        </is>
+      </c>
       <c r="J151" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI, Child and Adolescent Mortality (weight 1/12)</t>
+          <t>Project design</t>
         </is>
       </c>
     </row>
@@ -7296,7 +7348,7 @@
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>birth_last_5y</t>
+          <t>hospitalization_365d</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
@@ -7306,12 +7358,12 @@
       </c>
       <c r="F152" s="2" t="inlineStr">
         <is>
-          <t>In the last five years, did any woman in your household give birth?</t>
+          <t>In the last 12 months, was anyone in your household admitted to hospital overnight?</t>
         </is>
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>पिछले पाँच साल में क्या आपके घर की किसी महिला ने बच्चे को जन्म दिया?</t>
+          <t>पिछले 12 महीनों में क्या आपके घर का कोई रात भर के लिए अस्पताल में भर्ती हुआ?</t>
         </is>
       </c>
       <c r="H152" s="2" t="inlineStr">
@@ -7322,7 +7374,7 @@
       <c r="I152" s="2" t="inlineStr"/>
       <c r="J152" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI, Maternal Health (weight 1/12)</t>
+          <t>NSS health module (365-day recall)</t>
         </is>
       </c>
     </row>
@@ -7342,37 +7394,33 @@
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>anc_4_visits</t>
+          <t>health_access_barrier_3m</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>select one</t>
+          <t>yes/no</t>
         </is>
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
-          <t>For the most recent birth, did she have at least four check-ups before the delivery?</t>
+          <t>In the last 3 months, was there a time when someone in your household needed medical care but could not get it?</t>
         </is>
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>सबसे हाल के जन्म के लिए, क्या डिलीवरी से पहले उनकी कम से कम चार बार जाँच हुई थी?</t>
+          <t>पिछले 3 महीनों में क्या कभी ऐसा हुआ कि आपके घर में किसी को इलाज की ज़रूरत थी पर मिल नहीं पाया?</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr">
         <is>
-          <t>0 No | 1 Yes | 97 Don't know</t>
-        </is>
-      </c>
-      <c r="I153" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if birth_last_5y = 1</t>
-        </is>
-      </c>
+          <t>0 No | 1 Yes</t>
+        </is>
+      </c>
+      <c r="I153" s="2" t="inlineStr"/>
       <c r="J153" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI, Maternal Health (antenatal care limb)</t>
+          <t>VASyR 2025 barriers_health_case_access_phc_m (primary-care access barriers); Lyons et al. 2023 Table 2 indicator 2 'healthcare access'</t>
         </is>
       </c>
     </row>
@@ -7392,37 +7440,33 @@
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>skilled_birth_attendant</t>
+          <t>child_death_5y</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>select one</t>
+          <t>yes/no</t>
         </is>
       </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
-          <t>Was that delivery done with the help of a doctor, nurse or trained midwife?</t>
+          <t>In the last five years, has any child or young person under 18 in your household died?</t>
         </is>
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>क्या वह डिलीवरी डॉक्टर, नर्स या प्रशिक्षित दाई की मदद से हुई थी?</t>
+          <t>पिछले पाँच साल में क्या आपके घर के 18 साल से छोटे किसी बच्चे या किशोर की मृत्यु हुई?</t>
         </is>
       </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
-          <t>0 No | 1 Yes | 97 Don't know</t>
-        </is>
-      </c>
-      <c r="I154" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if birth_last_5y = 1</t>
-        </is>
-      </c>
+          <t>0 No | 1 Yes</t>
+        </is>
+      </c>
+      <c r="I154" s="2" t="inlineStr"/>
       <c r="J154" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI, Maternal Health (assisted delivery limb)</t>
+          <t>NITI Aayog National MPI, Child and Adolescent Mortality (weight 1/12)</t>
         </is>
       </c>
     </row>
@@ -7432,43 +7476,43 @@
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>Food security, shocks and coping</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>distress_event_last365d</t>
+          <t>birth_last_5y</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>select multiple</t>
+          <t>yes/no</t>
         </is>
       </c>
       <c r="F155" s="2" t="inlineStr">
         <is>
-          <t>In the last 12 months, did any of these happen to your household? Check every one that applies.</t>
+          <t>In the last five years, did any woman in your household give birth?</t>
         </is>
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>पिछले 12 महीनों में आपके घर के साथ इनमें से क्या-क्या हुआ? जो-जो हुआ, सब चुनिए।</t>
+          <t>पिछले पाँच साल में क्या आपके घर की किसी महिला ने बच्चे को जन्म दिया?</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr">
         <is>
-          <t>1 Serious illness or death of an earning member | 2 Crop failure or livestock loss | 3 Damage from a natural disaster (flood, landslide, fire) | 4 Loss of business, goods or assets | 5 Road or bridge blocked, route closed | 6 Yatra stopped early or badly disrupted | 7 Sharp fall in customers or prices | 8 Lost the work or the work stopped</t>
+          <t>0 No | 1 Yes</t>
         </is>
       </c>
       <c r="I155" s="2" t="inlineStr"/>
       <c r="J155" s="2" t="inlineStr">
         <is>
-          <t>VEP exposure covariate (Azeem et al. 2016); shock inventory following Gunther and Harttgen 2009, via Fujii 2016 section 4</t>
+          <t>NITI Aayog National MPI, Maternal Health (weight 1/12)</t>
         </is>
       </c>
     </row>
@@ -7478,47 +7522,47 @@
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>Food security, shocks and coping</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>shock_coping</t>
+          <t>anc_4_visits</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>select multiple</t>
+          <t>select one</t>
         </is>
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
-          <t>How did your household manage? Check every one they used.</t>
+          <t>For the most recent birth, did she have at least four check-ups before the delivery?</t>
         </is>
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>आपके घर ने कैसे सँभाला? उन्होंने जो-जो किया, सब चुनिए।</t>
+          <t>सबसे हाल के जन्म के लिए, क्या डिलीवरी से पहले उनकी कम से कम चार बार जाँच हुई थी?</t>
         </is>
       </c>
       <c r="H156" s="2" t="inlineStr">
         <is>
-          <t>1 Used savings | 2 Borrowed money | 3 Sold or pawned assets | 4 Cut consumption | 5 Help from relatives/community | 6 Did nothing/other</t>
+          <t>0 No | 1 Yes | 97 Don't know</t>
         </is>
       </c>
       <c r="I156" s="2" t="inlineStr">
         <is>
-          <t>Ask only if any shock was reported</t>
+          <t>Ask only if birth_last_5y = 1</t>
         </is>
       </c>
       <c r="J156" s="2" t="inlineStr">
         <is>
-          <t>Coping strategies in VEP studies; Carter and Zimmerman 2000 on asset versus consumption smoothing</t>
+          <t>NITI Aayog National MPI, Maternal Health (antenatal care limb)</t>
         </is>
       </c>
     </row>
@@ -7528,39 +7572,47 @@
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>Food security, shocks and coping</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>cope_less_pref_food_yatra_wk</t>
+          <t>skilled_birth_attendant</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>whole number</t>
+          <t>select one</t>
         </is>
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
-          <t>In a normal week during the Yatra season, to cope with a lack of food or money to buy it, how many days did your household rely on less expensive/less preferred food? (0-7 days)</t>
+          <t>Was that delivery done with the help of a doctor, nurse or trained midwife?</t>
         </is>
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम हफ़्ते में, खाने की या खाना ख़रीदने के पैसे की कमी से निपटने के लिए आपके घर ने कितने दिन सस्ता या कम पसंद का खाना खाया? (0-7 दिन)</t>
-        </is>
-      </c>
-      <c r="H157" s="2" t="inlineStr"/>
-      <c r="I157" s="2" t="inlineStr"/>
+          <t>क्या वह डिलीवरी डॉक्टर, नर्स या प्रशिक्षित दाई की मदद से हुई थी?</t>
+        </is>
+      </c>
+      <c r="H157" s="2" t="inlineStr">
+        <is>
+          <t>0 No | 1 Yes | 97 Don't know</t>
+        </is>
+      </c>
+      <c r="I157" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if birth_last_5y = 1</t>
+        </is>
+      </c>
       <c r="J157" s="2" t="inlineStr">
         <is>
-          <t>VASyR 2025 (exact item wording); WFP rCSI; The reduced Coping Strategy Index (rCSI): five food-coping questions, standard WFP weights (1, 2, 1, 1, 3) applied when the index is built. The Kedarnath instrument otherwise has no food-security module, which is a gap for a poverty-vulnerability survey; these five short questions close it at low cost instead of a full dietary-diversity module, left out to stay inside the 45-minute limit. Kept as day-counts (0-7), not collapsed to yes/no: this is the standard, validated WFP/FAO specification (frequency x severity), and no comparably-standard binary version was found on checking; a day-count also takes about as long to answer as a yes/no in practice, so little interview time is saved by simplifying it.</t>
+          <t>NITI Aayog National MPI, Maternal Health (assisted delivery limb)</t>
         </is>
       </c>
     </row>
@@ -7580,29 +7632,33 @@
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>cope_less_pref_food_offseason_wk</t>
+          <t>distress_event_last365d</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>whole number</t>
+          <t>select multiple</t>
         </is>
       </c>
       <c r="F158" s="2" t="inlineStr">
         <is>
-          <t>In a normal week when the Yatra is closed, to cope with a lack of food or money to buy it, how many days did your household rely on less expensive/less preferred food? (0-7 days)</t>
+          <t>In the last 12 months, did any of these happen -- to your household, or to the Yatra route you work on? Check every one that applies.</t>
         </is>
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम हफ़्ते में आपके घर ने कितने दिन सस्ता या कम पसंद का खाना खाया? (0-7 दिन)</t>
-        </is>
-      </c>
-      <c r="H158" s="2" t="inlineStr"/>
+          <t>पिछले 12 महीनों में इनमें से क्या-क्या हुआ — आपके घर के साथ, या जिस यात्रा मार्ग पर आप काम करते हैं उस पर? जो-जो हुआ, सब चुनिए।</t>
+        </is>
+      </c>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t>1 Serious illness or death of an earning member | 2 Crop failure or livestock loss | 3 Damage from a natural disaster (flood, landslide, fire) | 4 Loss of business, goods or assets | 5 Road or bridge blocked, route closed | 6 Yatra stopped early or badly disrupted | 7 Sharp fall in customers or prices | 8 Lost the work or the work stopped</t>
+        </is>
+      </c>
       <c r="I158" s="2" t="inlineStr"/>
       <c r="J158" s="2" t="inlineStr">
         <is>
-          <t>VASyR 2025 (exact item wording); WFP rCSI; The reduced Coping Strategy Index (rCSI): five food-coping questions, standard WFP weights (1, 2, 1, 1, 3) applied when the index is built. The Kedarnath instrument otherwise has no food-security module, which is a gap for a poverty-vulnerability survey; these five short questions close it at low cost instead of a full dietary-diversity module, left out to stay inside the 45-minute limit. Kept as day-counts (0-7), not collapsed to yes/no: this is the standard, validated WFP/FAO specification (frequency x severity), and no comparably-standard binary version was found on checking; a day-count also takes about as long to answer as a yes/no in practice, so little interview time is saved by simplifying it.</t>
+          <t>VEP exposure covariate (Azeem et al. 2016); shock inventory following Gunther and Harttgen 2009, via Fujii 2016 section 4</t>
         </is>
       </c>
     </row>
@@ -7622,29 +7678,37 @@
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>cope_borrow_food_yatra_wk</t>
+          <t>shock_coping</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>whole number</t>
+          <t>select multiple</t>
         </is>
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
-          <t>In a normal week during the Yatra season, to cope with a lack of food or money to buy it, how many days did your household borrow food and/or rely on help from friends/relatives? (0-7 days)</t>
+          <t>How did your household manage? Check every one they used.</t>
         </is>
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम हफ़्ते में, खाने की या खाना ख़रीदने के पैसे की कमी से निपटने के लिए आपके घर ने कितने दिन खाना उधार लिया या दोस्तों/रिश्तेदारों की मदद ली? (0-7 दिन)</t>
-        </is>
-      </c>
-      <c r="H159" s="2" t="inlineStr"/>
-      <c r="I159" s="2" t="inlineStr"/>
+          <t>आपके घर ने कैसे सँभाला? उन्होंने जो-जो किया, सब चुनिए।</t>
+        </is>
+      </c>
+      <c r="H159" s="2" t="inlineStr">
+        <is>
+          <t>1 Used savings | 2 Borrowed money | 3 Sold or pawned assets | 4 Cut consumption | 5 Help from relatives/community | 6 Did nothing/other</t>
+        </is>
+      </c>
+      <c r="I159" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if any shock was reported</t>
+        </is>
+      </c>
       <c r="J159" s="2" t="inlineStr">
         <is>
-          <t>VASyR 2025 (exact item wording); WFP rCSI; The reduced Coping Strategy Index (rCSI): five food-coping questions, standard WFP weights (1, 2, 1, 1, 3) applied when the index is built. The Kedarnath instrument otherwise has no food-security module, which is a gap for a poverty-vulnerability survey; these five short questions close it at low cost instead of a full dietary-diversity module, left out to stay inside the 45-minute limit. Kept as day-counts (0-7), not collapsed to yes/no: this is the standard, validated WFP/FAO specification (frequency x severity), and no comparably-standard binary version was found on checking; a day-count also takes about as long to answer as a yes/no in practice, so little interview time is saved by simplifying it.</t>
+          <t>Coping strategies in VEP studies; Carter and Zimmerman 2000 on asset versus consumption smoothing</t>
         </is>
       </c>
     </row>
@@ -7664,7 +7728,7 @@
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>cope_borrow_food_offseason_wk</t>
+          <t>cope_less_pref_food_yatra_wk</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
@@ -7674,12 +7738,12 @@
       </c>
       <c r="F160" s="2" t="inlineStr">
         <is>
-          <t>In a normal week when the Yatra is closed, to cope with a lack of food or money to buy it, how many days did your household borrow food and/or rely on help from friends/relatives? (0-7 days)</t>
+          <t>In a normal week during the Yatra season, to cope with a lack of food or money to buy it, how many days did your household rely on less expensive/less preferred food? (0-7 days)</t>
         </is>
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम हफ़्ते में आपके घर ने कितने दिन खाना उधार लिया या दोस्तों/रिश्तेदारों की मदद ली? (0-7 दिन)</t>
+          <t>यात्रा के मौसम के आम हफ़्ते में, खाने की या खाना ख़रीदने के पैसे की कमी से निपटने के लिए आपके घर ने कितने दिन सस्ता या कम पसंद का खाना खाया? (0-7 दिन)</t>
         </is>
       </c>
       <c r="H160" s="2" t="inlineStr"/>
@@ -7706,7 +7770,7 @@
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>cope_reduce_meals_yatra_wk</t>
+          <t>cope_less_pref_food_offseason_wk</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
@@ -7716,12 +7780,12 @@
       </c>
       <c r="F161" s="2" t="inlineStr">
         <is>
-          <t>In a normal week during the Yatra season, to cope with a lack of food or money to buy it, how many days did your household reduce the number of meals eaten per day? (0-7 days)</t>
+          <t>In a normal week when the Yatra is closed, to cope with a lack of food or money to buy it, how many days did your household rely on less expensive/less preferred food? (0-7 days)</t>
         </is>
       </c>
       <c r="G161" s="2" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम हफ़्ते में, खाने की या खाना ख़रीदने के पैसे की कमी से निपटने के लिए आपके घर ने कितने दिन दिन में कम बार खाना खाया? (0-7 दिन)</t>
+          <t>जब यात्रा बंद रहती है, उस आम हफ़्ते में आपके घर ने कितने दिन सस्ता या कम पसंद का खाना खाया? (0-7 दिन)</t>
         </is>
       </c>
       <c r="H161" s="2" t="inlineStr"/>
@@ -7748,7 +7812,7 @@
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>cope_reduce_meals_offseason_wk</t>
+          <t>cope_borrow_food_yatra_wk</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
@@ -7758,12 +7822,12 @@
       </c>
       <c r="F162" s="2" t="inlineStr">
         <is>
-          <t>In a normal week when the Yatra is closed, to cope with a lack of food or money to buy it, how many days did your household reduce the number of meals eaten per day? (0-7 days)</t>
+          <t>In a normal week during the Yatra season, to cope with a lack of food or money to buy it, how many days did your household borrow food and/or rely on help from friends/relatives? (0-7 days)</t>
         </is>
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम हफ़्ते में आपके घर ने कितने दिन दिन में कम बार खाना खाया? (0-7 दिन)</t>
+          <t>यात्रा के मौसम के आम हफ़्ते में, खाने की या खाना ख़रीदने के पैसे की कमी से निपटने के लिए आपके घर ने कितने दिन खाना उधार लिया या दोस्तों/रिश्तेदारों की मदद ली? (0-7 दिन)</t>
         </is>
       </c>
       <c r="H162" s="2" t="inlineStr"/>
@@ -7790,7 +7854,7 @@
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>cope_reduce_portion_yatra_wk</t>
+          <t>cope_borrow_food_offseason_wk</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
@@ -7800,12 +7864,12 @@
       </c>
       <c r="F163" s="2" t="inlineStr">
         <is>
-          <t>In a normal week during the Yatra season, to cope with a lack of food or money to buy it, how many days did your household reduce portion size of meals? (0-7 days)</t>
+          <t>In a normal week when the Yatra is closed, to cope with a lack of food or money to buy it, how many days did your household borrow food and/or rely on help from friends/relatives? (0-7 days)</t>
         </is>
       </c>
       <c r="G163" s="2" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम हफ़्ते में, खाने की या खाना ख़रीदने के पैसे की कमी से निपटने के लिए आपके घर ने कितने दिन खाने की मात्रा घटाई? (0-7 दिन)</t>
+          <t>जब यात्रा बंद रहती है, उस आम हफ़्ते में आपके घर ने कितने दिन खाना उधार लिया या दोस्तों/रिश्तेदारों की मदद ली? (0-7 दिन)</t>
         </is>
       </c>
       <c r="H163" s="2" t="inlineStr"/>
@@ -7832,7 +7896,7 @@
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>cope_reduce_portion_offseason_wk</t>
+          <t>cope_reduce_meals_yatra_wk</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
@@ -7842,12 +7906,12 @@
       </c>
       <c r="F164" s="2" t="inlineStr">
         <is>
-          <t>In a normal week when the Yatra is closed, to cope with a lack of food or money to buy it, how many days did your household reduce portion size of meals? (0-7 days)</t>
+          <t>In a normal week during the Yatra season, to cope with a lack of food or money to buy it, how many days did your household reduce the number of meals eaten per day? (0-7 days)</t>
         </is>
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम हफ़्ते में आपके घर ने कितने दिन खाने की मात्रा घटाई? (0-7 दिन)</t>
+          <t>यात्रा के मौसम के आम हफ़्ते में, खाने की या खाना ख़रीदने के पैसे की कमी से निपटने के लिए आपके घर ने कितने दिन दिन में कम बार खाना खाया? (0-7 दिन)</t>
         </is>
       </c>
       <c r="H164" s="2" t="inlineStr"/>
@@ -7874,7 +7938,7 @@
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t>cope_restrict_adult_yatra_wk</t>
+          <t>cope_reduce_meals_offseason_wk</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr">
@@ -7884,12 +7948,12 @@
       </c>
       <c r="F165" s="2" t="inlineStr">
         <is>
-          <t>In a normal week during the Yatra season, to cope with a lack of food or money to buy it, how many days did your household restrict consumption of adults/mothers in order for young children to eat? (0-7 days)</t>
+          <t>In a normal week when the Yatra is closed, to cope with a lack of food or money to buy it, how many days did your household reduce the number of meals eaten per day? (0-7 days)</t>
         </is>
       </c>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम हफ़्ते में, खाने की या खाना ख़रीदने के पैसे की कमी से निपटने के लिए आपके घर ने कितने दिन बड़ों ने कम खाया ताकि छोटे बच्चे खा सकें? (0-7 दिन)</t>
+          <t>जब यात्रा बंद रहती है, उस आम हफ़्ते में आपके घर ने कितने दिन दिन में कम बार खाना खाया? (0-7 दिन)</t>
         </is>
       </c>
       <c r="H165" s="2" t="inlineStr"/>
@@ -7916,7 +7980,7 @@
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>cope_restrict_adult_offseason_wk</t>
+          <t>cope_reduce_portion_yatra_wk</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
@@ -7926,12 +7990,12 @@
       </c>
       <c r="F166" s="2" t="inlineStr">
         <is>
-          <t>In a normal week when the Yatra is closed, to cope with a lack of food or money to buy it, how many days did your household restrict consumption of adults/mothers in order for young children to eat? (0-7 days)</t>
+          <t>In a normal week during the Yatra season, to cope with a lack of food or money to buy it, how many days did your household reduce portion size of meals? (0-7 days)</t>
         </is>
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम हफ़्ते में आपके घर ने कितने दिन बड़ों ने कम खाया ताकि छोटे बच्चे खा सकें? (0-7 दिन)</t>
+          <t>यात्रा के मौसम के आम हफ़्ते में, खाने की या खाना ख़रीदने के पैसे की कमी से निपटने के लिए आपके घर ने कितने दिन खाने की मात्रा घटाई? (0-7 दिन)</t>
         </is>
       </c>
       <c r="H166" s="2" t="inlineStr"/>
@@ -7948,43 +8012,39 @@
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t>Ropeway</t>
+          <t>Food security, shocks and coping</t>
         </is>
       </c>
       <c r="D167" s="2" t="inlineStr">
         <is>
-          <t>ropeway_stance</t>
+          <t>cope_reduce_portion_offseason_wk</t>
         </is>
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>select one</t>
+          <t>whole number</t>
         </is>
       </c>
       <c r="F167" s="2" t="inlineStr">
         <is>
-          <t>A ropeway is proposed between Gaurikund and Kedarnath. Are you in favour, neutral, or against?</t>
+          <t>In a normal week when the Yatra is closed, to cope with a lack of food or money to buy it, how many days did your household reduce portion size of meals? (0-7 days)</t>
         </is>
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>गौरीकुंड से केदारनाथ तक रोपवे बनाने की बात चल रही है। आप इसके पक्ष में हैं, बीच में हैं, या ख़िलाफ़ हैं?</t>
-        </is>
-      </c>
-      <c r="H167" s="2" t="inlineStr">
-        <is>
-          <t>1 Support | 2 Neutral | 3 Oppose | 98 Don't know / prefer not to say</t>
-        </is>
-      </c>
+          <t>जब यात्रा बंद रहती है, उस आम हफ़्ते में आपके घर ने कितने दिन खाने की मात्रा घटाई? (0-7 दिन)</t>
+        </is>
+      </c>
+      <c r="H167" s="2" t="inlineStr"/>
       <c r="I167" s="2" t="inlineStr"/>
       <c r="J167" s="2" t="inlineStr">
         <is>
-          <t>Project design</t>
+          <t>VASyR 2025 (exact item wording); WFP rCSI; The reduced Coping Strategy Index (rCSI): five food-coping questions, standard WFP weights (1, 2, 1, 1, 3) applied when the index is built. The Kedarnath instrument otherwise has no food-security module, which is a gap for a poverty-vulnerability survey; these five short questions close it at low cost instead of a full dietary-diversity module, left out to stay inside the 45-minute limit. Kept as day-counts (0-7), not collapsed to yes/no: this is the standard, validated WFP/FAO specification (frequency x severity), and no comparably-standard binary version was found on checking; a day-count also takes about as long to answer as a yes/no in practice, so little interview time is saved by simplifying it.</t>
         </is>
       </c>
     </row>
@@ -7994,43 +8054,39 @@
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>Ropeway</t>
+          <t>Food security, shocks and coping</t>
         </is>
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>trek_dependent</t>
+          <t>cope_restrict_adult_yatra_wk</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>yes/no</t>
+          <t>whole number</t>
         </is>
       </c>
       <c r="F168" s="2" t="inlineStr">
         <is>
-          <t>Is your main Yatra work carrying, transporting or guiding people or goods on the Gaurikund to Kedarnath trek?</t>
+          <t>In a normal week during the Yatra season, to cope with a lack of food or money to buy it, how many days did your household restrict consumption of adults/mothers in order for young children to eat? (0-7 days)</t>
         </is>
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>क्या आपका मुख्य यात्रा-काम गौरीकुंड से केदारनाथ के पैदल रास्ते पर लोगों या सामान को ले जाना, पहुँचाना या रास्ता दिखाना है?</t>
-        </is>
-      </c>
-      <c r="H168" s="2" t="inlineStr">
-        <is>
-          <t>0 No | 1 Yes</t>
-        </is>
-      </c>
+          <t>यात्रा के मौसम के आम हफ़्ते में, खाने की या खाना ख़रीदने के पैसे की कमी से निपटने के लिए आपके घर ने कितने दिन बड़ों ने कम खाया ताकि छोटे बच्चे खा सकें? (0-7 दिन)</t>
+        </is>
+      </c>
+      <c r="H168" s="2" t="inlineStr"/>
       <c r="I168" s="2" t="inlineStr"/>
       <c r="J168" s="2" t="inlineStr">
         <is>
-          <t>Project design (see tasks_module W4: exposure must be asked directly)</t>
+          <t>VASyR 2025 (exact item wording); WFP rCSI; The reduced Coping Strategy Index (rCSI): five food-coping questions, standard WFP weights (1, 2, 1, 1, 3) applied when the index is built. The Kedarnath instrument otherwise has no food-security module, which is a gap for a poverty-vulnerability survey; these five short questions close it at low cost instead of a full dietary-diversity module, left out to stay inside the 45-minute limit. Kept as day-counts (0-7), not collapsed to yes/no: this is the standard, validated WFP/FAO specification (frequency x severity), and no comparably-standard binary version was found on checking; a day-count also takes about as long to answer as a yes/no in practice, so little interview time is saved by simplifying it.</t>
         </is>
       </c>
     </row>
@@ -8040,43 +8096,39 @@
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t>Job quality (Apablaza et al. 2026 questions)</t>
+          <t>Food security, shocks and coping</t>
         </is>
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t>job_situation</t>
+          <t>cope_restrict_adult_offseason_wk</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>select one</t>
+          <t>whole number</t>
         </is>
       </c>
       <c r="F169" s="2" t="inlineStr">
         <is>
-          <t>Which best describes your situation during the last month: you work for pay full-time; you work for pay part-time or do occasional jobs; you study and work; you only study; you are only being trained for work; you are retired or pensioned; you do unpaid household tasks or care for others; you are unemployed and actively looking for work; you are sick or disabled and cannot work; or none of these?</t>
+          <t>In a normal week when the Yatra is closed, to cope with a lack of food or money to buy it, how many days did your household restrict consumption of adults/mothers in order for young children to eat? (0-7 days)</t>
         </is>
       </c>
       <c r="G169" s="2" t="inlineStr">
         <is>
-          <t>पिछले महीने आपकी हालत इनमें से किससे सबसे मिलती है: पूरे समय पैसे के लिए काम; कुछ समय या कभी-कभार का काम; पढ़ाई के साथ काम; सिर्फ़ पढ़ाई; सिर्फ़ काम की ट्रेनिंग; रिटायर या पेंशन पर; घर का बिना पैसे का काम या किसी की देखभाल; काम नहीं है और ढूँढ रहे हैं; बीमारी या विकलांगता से काम नहीं कर सकते; या इनमें से कुछ नहीं?</t>
-        </is>
-      </c>
-      <c r="H169" s="2" t="inlineStr">
-        <is>
-          <t>1 Works for pay full-time | 2 Works for pay part-time or occasional jobs | 3 Studies and works | 4 Only studies | 5 Being trained for work only | 6 Retired or pensioned | 7 Unpaid household tasks or caring for others | 8 Unemployed, actively seeking work | 9 Sick or disabled, cannot work | 10 Neither studying, working nor seeking work | 97 Does not know</t>
-        </is>
-      </c>
+          <t>जब यात्रा बंद रहती है, उस आम हफ़्ते में आपके घर ने कितने दिन बड़ों ने कम खाया ताकि छोटे बच्चे खा सकें? (0-7 दिन)</t>
+        </is>
+      </c>
+      <c r="H169" s="2" t="inlineStr"/>
       <c r="I169" s="2" t="inlineStr"/>
       <c r="J169" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q5 (all eleven categories, with its own three-way routing)</t>
+          <t>VASyR 2025 (exact item wording); WFP rCSI; The reduced Coping Strategy Index (rCSI): five food-coping questions, standard WFP weights (1, 2, 1, 1, 3) applied when the index is built. The Kedarnath instrument otherwise has no food-security module, which is a gap for a poverty-vulnerability survey; these five short questions close it at low cost instead of a full dietary-diversity module, left out to stay inside the 45-minute limit. Kept as day-counts (0-7), not collapsed to yes/no: this is the standard, validated WFP/FAO specification (frequency x severity), and no comparably-standard binary version was found on checking; a day-count also takes about as long to answer as a yes/no in practice, so little interview time is saved by simplifying it.</t>
         </is>
       </c>
     </row>
@@ -8086,17 +8138,17 @@
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>Job quality (Apablaza et al. 2026 questions)</t>
+          <t>Ropeway</t>
         </is>
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>employer_type</t>
+          <t>ropeway_stance</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr">
@@ -8106,27 +8158,23 @@
       </c>
       <c r="F170" s="2" t="inlineStr">
         <is>
-          <t>In your current work, are you: an employee of a private company; an employee of the public sector or government; a member of the armed forces or law enforcement; an employer or business owner who hires others; working alone with no employees; an unpaid family worker; or a domestic service worker?</t>
+          <t>A ropeway is proposed between Gaurikund and Kedarnath. Are you in favour, neutral, or against?</t>
         </is>
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>अपने अभी के काम में आप क्या हैं: किसी प्राइवेट कंपनी के कर्मचारी; सरकारी विभाग के कर्मचारी; फ़ौज या पुलिस में; मालिक जो दूसरों को काम पर रखते हैं; अकेले काम करते हैं, कोई नौकर नहीं; घर के काम में बिना पैसे के हाथ बँटाते हैं; या किसी के घर में काम करते हैं?</t>
+          <t>गौरीकुंड से केदारनाथ तक रोपवे बनाने की बात चल रही है। आप इसके पक्ष में हैं, बीच में हैं, या ख़िलाफ़ हैं?</t>
         </is>
       </c>
       <c r="H170" s="2" t="inlineStr">
         <is>
-          <t>1 Employee, private company | 2 Employee, public sector/government | 3 Armed forces or law enforcement | 4 Employer/business owner (hires others) | 5 Works alone, no employees | 6 Unpaid family worker | 7 Domestic service worker</t>
-        </is>
-      </c>
-      <c r="I170" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if job_situation is 1, 2 or 3 (currently working)</t>
-        </is>
-      </c>
+          <t>1 Support | 2 Neutral | 3 Oppose | 98 Prefer not to say</t>
+        </is>
+      </c>
+      <c r="I170" s="2" t="inlineStr"/>
       <c r="J170" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q8</t>
+          <t>Project design</t>
         </is>
       </c>
     </row>
@@ -8136,47 +8184,43 @@
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t>Job quality (Apablaza et al. 2026 questions)</t>
+          <t>Ropeway</t>
         </is>
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t>job_permanence</t>
+          <t>trek_dependent</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
-          <t>select one</t>
+          <t>yes/no</t>
         </is>
       </c>
       <c r="F171" s="2" t="inlineStr">
         <is>
-          <t>Is your job: permanent; seasonal or temporary; occasional or casual; on probation; or fixed-term?</t>
+          <t>Is your main Yatra work carrying, transporting or guiding people or goods on the Gaurikund to Kedarnath trek?</t>
         </is>
       </c>
       <c r="G171" s="2" t="inlineStr">
         <is>
-          <t>आपका काम कैसा है: पक्का; मौसमी या कुछ समय का; कभी-कभार का; परखने की अवधि पर; या तय समय के लिए?</t>
+          <t>क्या आपका मुख्य यात्रा-काम गौरीकुंड से केदारनाथ के पैदल रास्ते पर लोगों या सामान को ले जाना, पहुँचाना या रास्ता दिखाना है?</t>
         </is>
       </c>
       <c r="H171" s="2" t="inlineStr">
         <is>
-          <t>1 Permanent | 2 Seasonal or temporary | 3 Occasional or casual | 4 On probation | 5 Fixed-term</t>
-        </is>
-      </c>
-      <c r="I171" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if job_situation is 1, 2 or 3 (currently working)</t>
-        </is>
-      </c>
+          <t>0 No | 1 Yes</t>
+        </is>
+      </c>
+      <c r="I171" s="2" t="inlineStr"/>
       <c r="J171" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q9</t>
+          <t>Project design (see tasks_module W4: exposure must be asked directly)</t>
         </is>
       </c>
     </row>
@@ -8196,7 +8240,7 @@
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>contract_status</t>
+          <t>job_situation</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr">
@@ -8206,27 +8250,23 @@
       </c>
       <c r="F172" s="2" t="inlineStr">
         <is>
-          <t>Do you have a signed contract? Yes, signed; yes but not yet signed; no contract.</t>
+          <t>Which best describes your situation during the last month: you work for pay full-time; you work for pay part-time or do occasional jobs; you study and work; you only study; you are only being trained for work; you are retired or pensioned; you do unpaid household tasks or care for others; you are unemployed and actively looking for work; you are sick or disabled and cannot work; or none of these?</t>
         </is>
       </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t>क्या आपका दस्तख़त किया हुआ अनुबंध (कॉन्ट्रैक्ट) है? हाँ, दस्तख़त किया; हाँ, पर अभी दस्तख़त नहीं हुआ; कोई अनुबंध नहीं।</t>
+          <t>पिछले महीने आपकी हालत इनमें से किससे सबसे मिलती है: पूरे समय पैसे के लिए काम; कुछ समय या कभी-कभार का काम; पढ़ाई के साथ काम; सिर्फ़ पढ़ाई; सिर्फ़ काम की ट्रेनिंग; रिटायर या पेंशन पर; घर का बिना पैसे का काम या किसी की देखभाल; काम नहीं है और ढूँढ रहे हैं; बीमारी या विकलांगता से काम नहीं कर सकते; या इनमें से कुछ नहीं?</t>
         </is>
       </c>
       <c r="H172" s="2" t="inlineStr">
         <is>
-          <t>1 Yes, signed | 2 Yes, but not yet signed | 3 No contract</t>
-        </is>
-      </c>
-      <c r="I172" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if job_situation is 1, 2 or 3 (currently working); and employment_type is 3 or 4 (wage workers) -- self-employed skip to the next question</t>
-        </is>
-      </c>
+          <t>1 Works for pay full-time | 2 Works for pay part-time or occasional jobs | 3 Studies and works | 4 Only studies | 5 Being trained for work only | 6 Retired or pensioned | 7 Unpaid household tasks or caring for others | 8 Unemployed, actively seeking work | 9 Sick or disabled, cannot work | 10 Neither studying, working nor seeking work | 97 Does not know</t>
+        </is>
+      </c>
+      <c r="I172" s="2" t="inlineStr"/>
       <c r="J172" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q11</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q5 (all eleven categories, with its own three-way routing)</t>
         </is>
       </c>
     </row>
@@ -8246,27 +8286,27 @@
       </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t>workplace_registered</t>
+          <t>employer_type</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr">
         <is>
-          <t>yes/no</t>
+          <t>select one</t>
         </is>
       </c>
       <c r="F173" s="2" t="inlineStr">
         <is>
-          <t>Is your workplace or business registered, for example with a taxpayer or GST number, a shop or trade licence, the Yatra registration, or a union?</t>
+          <t>In your current work, are you: an employee of a private company; an employee of the public sector or government; a member of the armed forces or law enforcement; an employer or business owner who hires others; working alone with no employees; an unpaid family worker; or a domestic service worker?</t>
         </is>
       </c>
       <c r="G173" s="2" t="inlineStr">
         <is>
-          <t>क्या आपका काम या धंधा रजिस्टर्ड है, जैसे GST या टैक्स नंबर, दुकान का लाइसेंस, यात्रा का रजिस्ट्रेशन, या कोई यूनियन?</t>
+          <t>अपने अभी के काम में आप क्या हैं: किसी प्राइवेट कंपनी के कर्मचारी; सरकारी विभाग के कर्मचारी; फ़ौज या पुलिस में; मालिक जो दूसरों को काम पर रखते हैं; अकेले काम करते हैं, कोई नौकर नहीं; घर के काम में बिना पैसे के हाथ बँटाते हैं; या किसी के घर में काम करते हैं?</t>
         </is>
       </c>
       <c r="H173" s="2" t="inlineStr">
         <is>
-          <t>0 No | 1 Yes</t>
+          <t>1 Employee, private company | 2 Employee, public sector/government | 3 Armed forces or law enforcement | 4 Employer/business owner (hires others) | 5 Works alone, no employees | 6 Unpaid family worker | 7 Domestic service worker</t>
         </is>
       </c>
       <c r="I173" s="2" t="inlineStr">
@@ -8276,7 +8316,7 @@
       </c>
       <c r="J173" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q12 (widened to local registrations)</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q8</t>
         </is>
       </c>
     </row>
@@ -8296,7 +8336,7 @@
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>pension_contrib</t>
+          <t>job_permanence</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
@@ -8306,17 +8346,17 @@
       </c>
       <c r="F174" s="2" t="inlineStr">
         <is>
-          <t>Do you contribute to any pension system? Yes, the employer deducts it; yes, voluntarily; no.</t>
+          <t>Is your job: permanent; seasonal or temporary; occasional or casual; on probation; or fixed-term?</t>
         </is>
       </c>
       <c r="G174" s="2" t="inlineStr">
         <is>
-          <t>क्या आप किसी पेंशन में पैसा डालते हैं? हाँ, मालिक तनख़्वाह से काटता है; हाँ, अपनी मर्ज़ी से डालते हैं; नहीं।</t>
+          <t>आपका काम कैसा है: पक्का; मौसमी या कुछ समय का; कभी-कभार का; परखने की अवधि पर; या तय समय के लिए?</t>
         </is>
       </c>
       <c r="H174" s="2" t="inlineStr">
         <is>
-          <t>1 Yes, employer deducts it | 2 Yes, contributes voluntarily | 3 No</t>
+          <t>1 Permanent | 2 Seasonal or temporary | 3 Occasional or casual | 4 On probation | 5 Fixed-term</t>
         </is>
       </c>
       <c r="I174" s="2" t="inlineStr">
@@ -8326,7 +8366,7 @@
       </c>
       <c r="J174" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q16</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q9</t>
         </is>
       </c>
     </row>
@@ -8346,7 +8386,7 @@
       </c>
       <c r="D175" s="2" t="inlineStr">
         <is>
-          <t>work_health_ins</t>
+          <t>contract_status</t>
         </is>
       </c>
       <c r="E175" s="2" t="inlineStr">
@@ -8356,27 +8396,27 @@
       </c>
       <c r="F175" s="2" t="inlineStr">
         <is>
-          <t>Do you have health insurance through your work? Yes; only private or other insurance; none; don't know.</t>
+          <t>Do you have a signed contract? Yes, signed; yes but not yet signed; no contract.</t>
         </is>
       </c>
       <c r="G175" s="2" t="inlineStr">
         <is>
-          <t>क्या काम की तरफ़ से आपका स्वास्थ्य बीमा है? हाँ; सिर्फ़ अपना या कोई और बीमा; कोई नहीं; पता नहीं।</t>
+          <t>क्या आपका दस्तख़त किया हुआ अनुबंध (कॉन्ट्रैक्ट) है? हाँ, दस्तख़त किया; हाँ, पर अभी दस्तख़त नहीं हुआ; कोई अनुबंध नहीं।</t>
         </is>
       </c>
       <c r="H175" s="2" t="inlineStr">
         <is>
-          <t>1 Yes, through work | 2 Only private or other insurance | 3 None | 4 Don't know</t>
+          <t>1 Yes, signed | 2 Yes, but not yet signed | 3 No contract</t>
         </is>
       </c>
       <c r="I175" s="2" t="inlineStr">
         <is>
-          <t>Ask only if job_situation is 1, 2 or 3 (currently working)</t>
+          <t>Ask only if job_situation is 1, 2 or 3 (currently working); and employment_type is 3 or 4 (wage workers) -- self-employed skip to the next question</t>
         </is>
       </c>
       <c r="J175" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q17</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q11</t>
         </is>
       </c>
     </row>
@@ -8396,27 +8436,27 @@
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>leave_rights</t>
+          <t>workplace_registered</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>select one</t>
+          <t>yes/no</t>
         </is>
       </c>
       <c r="F176" s="2" t="inlineStr">
         <is>
-          <t>Do you have the right to paid holiday, sick or maternity leave?</t>
+          <t>Is your workplace or business registered, for example with a taxpayer or GST number, a shop or trade licence, the Yatra registration, or a union?</t>
         </is>
       </c>
       <c r="G176" s="2" t="inlineStr">
         <is>
-          <t>क्या आपको पैसे वाली छुट्टी मिलती है — त्योहार, बीमारी या ज़च्चगी की?</t>
+          <t>क्या आपका काम या धंधा रजिस्टर्ड है, जैसे GST या टैक्स नंबर, दुकान का लाइसेंस, यात्रा का रजिस्ट्रेशन, या कोई यूनियन?</t>
         </is>
       </c>
       <c r="H176" s="2" t="inlineStr">
         <is>
-          <t>0 No | 1 Yes | 97 Don't know</t>
+          <t>0 No | 1 Yes</t>
         </is>
       </c>
       <c r="I176" s="2" t="inlineStr">
@@ -8426,7 +8466,7 @@
       </c>
       <c r="J176" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q18</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q12 (widened to local registrations)</t>
         </is>
       </c>
     </row>
@@ -8446,7 +8486,7 @@
       </c>
       <c r="D177" s="2" t="inlineStr">
         <is>
-          <t>injured_ever</t>
+          <t>pension_contrib</t>
         </is>
       </c>
       <c r="E177" s="2" t="inlineStr">
@@ -8456,17 +8496,17 @@
       </c>
       <c r="F177" s="2" t="inlineStr">
         <is>
-          <t>Have you ever been physically injured at your workplace?</t>
+          <t>Do you contribute to any pension system? Yes, the employer deducts it; yes, voluntarily; no.</t>
         </is>
       </c>
       <c r="G177" s="2" t="inlineStr">
         <is>
-          <t>क्या आपको कभी काम की जगह पर चोट लगी है?</t>
+          <t>क्या आप किसी पेंशन में पैसा डालते हैं? हाँ, मालिक तनख़्वाह से काटता है; हाँ, अपनी मर्ज़ी से डालते हैं; नहीं।</t>
         </is>
       </c>
       <c r="H177" s="2" t="inlineStr">
         <is>
-          <t>0 No | 1 Yes | 97 Don't know</t>
+          <t>1 Yes, employer deducts it | 2 Yes, contributes voluntarily | 3 No</t>
         </is>
       </c>
       <c r="I177" s="2" t="inlineStr">
@@ -8476,7 +8516,7 @@
       </c>
       <c r="J177" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q19</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q16</t>
         </is>
       </c>
     </row>
@@ -8496,7 +8536,7 @@
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>workplace_injury_12m</t>
+          <t>work_health_ins</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr">
@@ -8506,17 +8546,17 @@
       </c>
       <c r="F178" s="2" t="inlineStr">
         <is>
-          <t>In the last 12 months, was anyone physically injured or killed at your workplace because of work?</t>
+          <t>Do you have health insurance through your work? Yes; only private or other insurance; none; don't know.</t>
         </is>
       </c>
       <c r="G178" s="2" t="inlineStr">
         <is>
-          <t>पिछले 12 महीनों में क्या आपके काम की जगह पर काम की वजह से किसी को चोट लगी या किसी की मौत हुई?</t>
+          <t>क्या काम की तरफ़ से आपका स्वास्थ्य बीमा है? हाँ; सिर्फ़ अपना या कोई और बीमा; कोई नहीं; पता नहीं।</t>
         </is>
       </c>
       <c r="H178" s="2" t="inlineStr">
         <is>
-          <t>0 No | 1 Yes | 97 Don't know</t>
+          <t>1 Yes, through work | 2 Only private or other insurance | 3 None | 4 Don't know</t>
         </is>
       </c>
       <c r="I178" s="2" t="inlineStr">
@@ -8526,7 +8566,7 @@
       </c>
       <c r="J178" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q20</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q17</t>
         </is>
       </c>
     </row>
@@ -8546,7 +8586,7 @@
       </c>
       <c r="D179" s="2" t="inlineStr">
         <is>
-          <t>wants_more_work</t>
+          <t>leave_rights</t>
         </is>
       </c>
       <c r="E179" s="2" t="inlineStr">
@@ -8556,12 +8596,12 @@
       </c>
       <c r="F179" s="2" t="inlineStr">
         <is>
-          <t>Would you like to work more hours than you do?</t>
+          <t>Do you have the right to paid holiday, sick or maternity leave?</t>
         </is>
       </c>
       <c r="G179" s="2" t="inlineStr">
         <is>
-          <t>क्या आप अभी से ज़्यादा घंटे काम करना चाहेंगे?</t>
+          <t>क्या आपको पैसे वाली छुट्टी मिलती है — त्योहार, बीमारी या ज़च्चगी की?</t>
         </is>
       </c>
       <c r="H179" s="2" t="inlineStr">
@@ -8571,12 +8611,12 @@
       </c>
       <c r="I179" s="2" t="inlineStr">
         <is>
-          <t>Ask if job_situation is 1 to 7 (Apablaza routes codes 4-7 straight to this question)</t>
+          <t>Ask only if job_situation is 1, 2 or 3 (currently working)</t>
         </is>
       </c>
       <c r="J179" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q21</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q18</t>
         </is>
       </c>
     </row>
@@ -8596,33 +8636,37 @@
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>more_hours_week</t>
+          <t>injured_ever</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>whole number</t>
+          <t>select one</t>
         </is>
       </c>
       <c r="F180" s="2" t="inlineStr">
         <is>
-          <t>How many more hours a week would you like to work?</t>
+          <t>Have you ever been physically injured at your workplace?</t>
         </is>
       </c>
       <c r="G180" s="2" t="inlineStr">
         <is>
-          <t>हफ़्ते में कितने घंटे और काम करना चाहेंगे?</t>
-        </is>
-      </c>
-      <c r="H180" s="2" t="inlineStr"/>
+          <t>क्या आपको कभी काम की जगह पर चोट लगी है?</t>
+        </is>
+      </c>
+      <c r="H180" s="2" t="inlineStr">
+        <is>
+          <t>0 No | 1 Yes | 97 Don't know</t>
+        </is>
+      </c>
       <c r="I180" s="2" t="inlineStr">
         <is>
-          <t>Ask if wants_more_work = 1, or if job_situation = 8 (Apablaza routes the unemployed-and-seeking category here directly)</t>
+          <t>Ask only if job_situation is 1, 2 or 3 (currently working)</t>
         </is>
       </c>
       <c r="J180" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q22</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q19</t>
         </is>
       </c>
     </row>
@@ -8642,33 +8686,37 @@
       </c>
       <c r="D181" s="2" t="inlineStr">
         <is>
-          <t>weeks_looked_for_work</t>
+          <t>workplace_injury_12m</t>
         </is>
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
-          <t>whole number</t>
+          <t>select one</t>
         </is>
       </c>
       <c r="F181" s="2" t="inlineStr">
         <is>
-          <t>Across the months in the calendar when you had no paid work, roughly how many weeks in total did you spend looking for work?</t>
+          <t>In the last 12 months, was anyone physically injured or killed at your workplace because of work?</t>
         </is>
       </c>
       <c r="G181" s="2" t="inlineStr">
         <is>
-          <t>साल के जिन महीनों में आपके पास कोई पैसे वाला काम नहीं था, उनमें कुल मिलाकर लगभग कितने हफ़्ते आपने काम ढूँढा?</t>
-        </is>
-      </c>
-      <c r="H181" s="2" t="inlineStr"/>
+          <t>पिछले 12 महीनों में क्या आपके काम की जगह पर काम की वजह से किसी को चोट लगी या किसी की मौत हुई?</t>
+        </is>
+      </c>
+      <c r="H181" s="2" t="inlineStr">
+        <is>
+          <t>0 No | 1 Yes | 97 Don't know</t>
+        </is>
+      </c>
       <c r="I181" s="2" t="inlineStr">
         <is>
-          <t>Ask if any month in the calendar is 'No paid work', or if job_situation = 8</t>
+          <t>Ask only if job_situation is 1, 2 or 3 (currently working)</t>
         </is>
       </c>
       <c r="J181" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q23 (duration in weeks, tied to the calendar instead of a single point in time)</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q20</t>
         </is>
       </c>
     </row>
@@ -8688,7 +8736,7 @@
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>first_job_ever</t>
+          <t>wants_more_work</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr">
@@ -8698,12 +8746,12 @@
       </c>
       <c r="F182" s="2" t="inlineStr">
         <is>
-          <t>Was your current work the first paid job you ever had?</t>
+          <t>Would you like to work more hours than you do?</t>
         </is>
       </c>
       <c r="G182" s="2" t="inlineStr">
         <is>
-          <t>क्या यह आपका पहला पैसे वाला काम है?</t>
+          <t>क्या आप अभी से ज़्यादा घंटे काम करना चाहेंगे?</t>
         </is>
       </c>
       <c r="H182" s="2" t="inlineStr">
@@ -8711,10 +8759,14 @@
           <t>0 No | 1 Yes | 97 Don't know</t>
         </is>
       </c>
-      <c r="I182" s="2" t="inlineStr"/>
+      <c r="I182" s="2" t="inlineStr">
+        <is>
+          <t>Ask if job_situation is 1 to 7 (Apablaza routes codes 4-7 straight to this question)</t>
+        </is>
+      </c>
       <c r="J182" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q24</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q21</t>
         </is>
       </c>
     </row>
@@ -8724,43 +8776,43 @@
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t>Tasks and skills (short block)</t>
+          <t>Job quality (Apablaza et al. 2026 questions)</t>
         </is>
       </c>
       <c r="D183" s="2" t="inlineStr">
         <is>
-          <t>tk_load</t>
+          <t>more_hours_day</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>select one</t>
+          <t>whole number</t>
         </is>
       </c>
       <c r="F183" s="2" t="inlineStr">
         <is>
-          <t>Do you load, unload, stack or count goods? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
+          <t>On a working day, how many MORE hours would you like to work?</t>
         </is>
       </c>
       <c r="G183" s="2" t="inlineStr">
         <is>
-          <t>क्या आप सामान चढ़ाना-उतारना, लगाना या गिनना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
-        </is>
-      </c>
-      <c r="H183" s="2" t="inlineStr">
-        <is>
-          <t>1 Yes, regularly in my main Yatra work | 2 Not in my main work, but done before elsewhere | 3 Never done</t>
-        </is>
-      </c>
-      <c r="I183" s="2" t="inlineStr"/>
+          <t>काम के दिन में आप कितने घंटे और काम करना चाहेंगे?</t>
+        </is>
+      </c>
+      <c r="H183" s="2" t="inlineStr"/>
+      <c r="I183" s="2" t="inlineStr">
+        <is>
+          <t>Ask if wants_more_work = 1, or if job_situation = 8 (Apablaza routes the unemployed-and-seeking category here directly)</t>
+        </is>
+      </c>
       <c r="J183" s="2" t="inlineStr">
         <is>
-          <t>Gathmann and Schonberg 2010; NCO 9333.0100 loader</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q22</t>
         </is>
       </c>
     </row>
@@ -8770,43 +8822,43 @@
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>Tasks and skills (short block)</t>
+          <t>Job quality (Apablaza et al. 2026 questions)</t>
         </is>
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t>tk_drive</t>
+          <t>months_looked_for_work</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>select one</t>
+          <t>whole number</t>
         </is>
       </c>
       <c r="F184" s="2" t="inlineStr">
         <is>
-          <t>Do you drive a motor vehicle? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
+          <t>Across the months when you had no paid work, about how many MONTHS in total were you looking for work?</t>
         </is>
       </c>
       <c r="G184" s="2" t="inlineStr">
         <is>
-          <t>क्या आप गाड़ी चलाना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
-        </is>
-      </c>
-      <c r="H184" s="2" t="inlineStr">
-        <is>
-          <t>1 Yes, regularly in my main Yatra work | 2 Not in my main work, but done before elsewhere | 3 Never done</t>
-        </is>
-      </c>
-      <c r="I184" s="2" t="inlineStr"/>
+          <t>जिन महीनों में आपके पास कोई पैसे वाला काम नहीं था, उनमें कुल मिलाकर लगभग कितने महीने आप काम ढूँढते रहे?</t>
+        </is>
+      </c>
+      <c r="H184" s="2" t="inlineStr"/>
+      <c r="I184" s="2" t="inlineStr">
+        <is>
+          <t>Ask if any month in the calendar is 'No paid work', or if job_situation = 8</t>
+        </is>
+      </c>
       <c r="J184" s="2" t="inlineStr">
         <is>
-          <t>Spitz-Oener 2006 / STEP; NCO 8322.0100</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q23 (duration in weeks, tied to the calendar instead of a single point in time)</t>
         </is>
       </c>
     </row>
@@ -8816,17 +8868,17 @@
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C185" s="2" t="inlineStr">
         <is>
-          <t>Tasks and skills (short block)</t>
+          <t>Job quality (Apablaza et al. 2026 questions)</t>
         </is>
       </c>
       <c r="D185" s="2" t="inlineStr">
         <is>
-          <t>tk_engine</t>
+          <t>first_job_ever</t>
         </is>
       </c>
       <c r="E185" s="2" t="inlineStr">
@@ -8836,23 +8888,23 @@
       </c>
       <c r="F185" s="2" t="inlineStr">
         <is>
-          <t>Do you operate an engine or machine? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
+          <t>Was your current work the first paid job you ever had?</t>
         </is>
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>क्या आप इंजन या मशीन चलाना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या यह आपका पहला पैसे वाला काम है?</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
         <is>
-          <t>1 Yes, regularly in my main Yatra work | 2 Not in my main work, but done before elsewhere | 3 Never done</t>
+          <t>0 No | 1 Yes | 97 Don't know</t>
         </is>
       </c>
       <c r="I185" s="2" t="inlineStr"/>
       <c r="J185" s="2" t="inlineStr">
         <is>
-          <t>Gathmann and Schonberg 2010; NCO 8343.1700 ropeway operator</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q24</t>
         </is>
       </c>
     </row>
@@ -8872,7 +8924,7 @@
       </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
-          <t>tk_electric</t>
+          <t>tk_load</t>
         </is>
       </c>
       <c r="E186" s="2" t="inlineStr">
@@ -8882,12 +8934,12 @@
       </c>
       <c r="F186" s="2" t="inlineStr">
         <is>
-          <t>Do you do electrical or wiring work? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
+          <t>Do you load, unload, stack or count goods? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
         </is>
       </c>
       <c r="G186" s="2" t="inlineStr">
         <is>
-          <t>क्या आप बिजली या तार का काम करना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप सामान चढ़ाना-उतारना, लगाना या गिनना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="H186" s="2" t="inlineStr">
@@ -8898,7 +8950,7 @@
       <c r="I186" s="2" t="inlineStr"/>
       <c r="J186" s="2" t="inlineStr">
         <is>
-          <t>Spitz-Oener 2006; NCO 7411.0301 wireman</t>
+          <t>Gathmann and Schonberg 2010; NCO 9333.0100 loader</t>
         </is>
       </c>
     </row>
@@ -8918,7 +8970,7 @@
       </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t>tk_safety</t>
+          <t>tk_drive</t>
         </is>
       </c>
       <c r="E187" s="2" t="inlineStr">
@@ -8928,12 +8980,12 @@
       </c>
       <c r="F187" s="2" t="inlineStr">
         <is>
-          <t>Do you check equipment or the route for safety? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
+          <t>Do you drive a motor vehicle? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
         </is>
       </c>
       <c r="G187" s="2" t="inlineStr">
         <is>
-          <t>क्या आप सामान या रास्ते की सुरक्षा जाँचना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप गाड़ी चलाना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="H187" s="2" t="inlineStr">
@@ -8944,7 +8996,7 @@
       <c r="I187" s="2" t="inlineStr"/>
       <c r="J187" s="2" t="inlineStr">
         <is>
-          <t>Gathmann and Schonberg 2010; NCO 8343.1700</t>
+          <t>Spitz-Oener 2006 / STEP; NCO 8322.0100</t>
         </is>
       </c>
     </row>
@@ -8964,7 +9016,7 @@
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
-          <t>tk_sell</t>
+          <t>tk_engine</t>
         </is>
       </c>
       <c r="E188" s="2" t="inlineStr">
@@ -8974,12 +9026,12 @@
       </c>
       <c r="F188" s="2" t="inlineStr">
         <is>
-          <t>Do you sell goods or services? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
+          <t>Do you operate an engine or machine? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
         </is>
       </c>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t>क्या आप सामान या सेवा बेचना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप इंजन या मशीन चलाना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="H188" s="2" t="inlineStr">
@@ -8990,7 +9042,7 @@
       <c r="I188" s="2" t="inlineStr"/>
       <c r="J188" s="2" t="inlineStr">
         <is>
-          <t>Gathmann and Schonberg 2010; NCO 5223.0200</t>
+          <t>Gathmann and Schonberg 2010; NCO 8343.1700 ropeway operator</t>
         </is>
       </c>
     </row>
@@ -9010,7 +9062,7 @@
       </c>
       <c r="D189" s="2" t="inlineStr">
         <is>
-          <t>tk_cash</t>
+          <t>tk_electric</t>
         </is>
       </c>
       <c r="E189" s="2" t="inlineStr">
@@ -9020,12 +9072,12 @@
       </c>
       <c r="F189" s="2" t="inlineStr">
         <is>
-          <t>Do you handle cash and payments? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
+          <t>Do you do electrical or wiring work? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
         </is>
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>क्या आप पैसे और भुगतान सँभालना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप बिजली या तार का काम करना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr">
@@ -9036,7 +9088,7 @@
       <c r="I189" s="2" t="inlineStr"/>
       <c r="J189" s="2" t="inlineStr">
         <is>
-          <t>Autor and Handel 2013; NCO 5131.0401</t>
+          <t>Spitz-Oener 2006; NCO 7411.0301 wireman</t>
         </is>
       </c>
     </row>
@@ -9056,7 +9108,7 @@
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>tk_cook</t>
+          <t>tk_safety</t>
         </is>
       </c>
       <c r="E190" s="2" t="inlineStr">
@@ -9066,12 +9118,12 @@
       </c>
       <c r="F190" s="2" t="inlineStr">
         <is>
-          <t>Do you cook or prepare food or drink? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
+          <t>Do you check equipment or the route for safety? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
         </is>
       </c>
       <c r="G190" s="2" t="inlineStr">
         <is>
-          <t>क्या आप खाना या पीने की चीज़ बनाना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप सामान या रास्ते की सुरक्षा जाँचना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="H190" s="2" t="inlineStr">
@@ -9082,7 +9134,7 @@
       <c r="I190" s="2" t="inlineStr"/>
       <c r="J190" s="2" t="inlineStr">
         <is>
-          <t>NCO 5120.0300 cook</t>
+          <t>Gathmann and Schonberg 2010; NCO 8343.1700</t>
         </is>
       </c>
     </row>
@@ -9102,7 +9154,7 @@
       </c>
       <c r="D191" s="2" t="inlineStr">
         <is>
-          <t>tk_serve</t>
+          <t>tk_sell</t>
         </is>
       </c>
       <c r="E191" s="2" t="inlineStr">
@@ -9112,12 +9164,12 @@
       </c>
       <c r="F191" s="2" t="inlineStr">
         <is>
-          <t>Do you serve guests or customers? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
+          <t>Do you sell goods or services? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
         </is>
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>क्या आप मेहमानों या ग्राहकों की सेवा करना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप सामान या सेवा बेचना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
@@ -9128,7 +9180,7 @@
       <c r="I191" s="2" t="inlineStr"/>
       <c r="J191" s="2" t="inlineStr">
         <is>
-          <t>NCO 5131.0401 waiter; Pal et al. 2026</t>
+          <t>Gathmann and Schonberg 2010; NCO 5223.0200</t>
         </is>
       </c>
     </row>
@@ -9148,7 +9200,7 @@
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>tk_clean</t>
+          <t>tk_cash</t>
         </is>
       </c>
       <c r="E192" s="2" t="inlineStr">
@@ -9158,12 +9210,12 @@
       </c>
       <c r="F192" s="2" t="inlineStr">
         <is>
-          <t>Do you clean rooms or public areas? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
+          <t>Do you handle cash and payments? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
         </is>
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>क्या आप कमरे या सार्वजनिक जगह साफ़ करना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप पैसे और भुगतान सँभालना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
@@ -9174,7 +9226,7 @@
       <c r="I192" s="2" t="inlineStr"/>
       <c r="J192" s="2" t="inlineStr">
         <is>
-          <t>NCO 5151.0202 room attendant; Autor-Levy-Murnane 2003 (janitorial)</t>
+          <t>Autor and Handel 2013; NCO 5131.0401</t>
         </is>
       </c>
     </row>
@@ -9194,7 +9246,7 @@
       </c>
       <c r="D193" s="2" t="inlineStr">
         <is>
-          <t>tk_guide</t>
+          <t>tk_cook</t>
         </is>
       </c>
       <c r="E193" s="2" t="inlineStr">
@@ -9204,12 +9256,12 @@
       </c>
       <c r="F193" s="2" t="inlineStr">
         <is>
-          <t>Do you guide or explain things to visitors? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
+          <t>Do you cook or prepare food or drink? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
         </is>
       </c>
       <c r="G193" s="2" t="inlineStr">
         <is>
-          <t>क्या आप आने वालों को रास्ता या बात समझाना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप खाना या पीने की चीज़ बनाना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="H193" s="2" t="inlineStr">
@@ -9220,7 +9272,7 @@
       <c r="I193" s="2" t="inlineStr"/>
       <c r="J193" s="2" t="inlineStr">
         <is>
-          <t>Gathmann and Schonberg 2010; NCO 5113.0200</t>
+          <t>NCO 5120.0300 cook</t>
         </is>
       </c>
     </row>
@@ -9240,7 +9292,7 @@
       </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
-          <t>tk_coord</t>
+          <t>tk_serve</t>
         </is>
       </c>
       <c r="E194" s="2" t="inlineStr">
@@ -9250,12 +9302,12 @@
       </c>
       <c r="F194" s="2" t="inlineStr">
         <is>
-          <t>Do you coordinate work by phone, radio or signals? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
+          <t>Do you serve guests or customers? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
         </is>
       </c>
       <c r="G194" s="2" t="inlineStr">
         <is>
-          <t>क्या आप फ़ोन, रेडियो या इशारों से दूसरों के साथ तालमेल करना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप मेहमानों या ग्राहकों की सेवा करना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="H194" s="2" t="inlineStr">
@@ -9266,7 +9318,7 @@
       <c r="I194" s="2" t="inlineStr"/>
       <c r="J194" s="2" t="inlineStr">
         <is>
-          <t>NCO 8343.1700 ropeway operator</t>
+          <t>NCO 5131.0401 waiter; Pal et al. 2026</t>
         </is>
       </c>
     </row>
@@ -9286,37 +9338,33 @@
       </c>
       <c r="D195" s="2" t="inlineStr">
         <is>
-          <t>drove_twowheeler</t>
+          <t>tk_clean</t>
         </is>
       </c>
       <c r="E195" s="2" t="inlineStr">
         <is>
-          <t>yes/no</t>
+          <t>select one</t>
         </is>
       </c>
       <c r="F195" s="2" t="inlineStr">
         <is>
-          <t>Have you ever driven a motorcycle or scooter, with or without a licence?</t>
+          <t>Do you clean rooms or public areas? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
         </is>
       </c>
       <c r="G195" s="2" t="inlineStr">
         <is>
-          <t>क्या आपने कभी मोटरसाइकिल या स्कूटर चलाई है, लाइसेंस हो या न हो?</t>
+          <t>क्या आप कमरे या सार्वजनिक जगह साफ़ करना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="H195" s="2" t="inlineStr">
         <is>
-          <t>0 No | 1 Yes</t>
-        </is>
-      </c>
-      <c r="I195" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if tk_drive is 1 or 2</t>
-        </is>
-      </c>
+          <t>1 Yes, regularly in my main Yatra work | 2 Not in my main work, but done before elsewhere | 3 Never done</t>
+        </is>
+      </c>
+      <c r="I195" s="2" t="inlineStr"/>
       <c r="J195" s="2" t="inlineStr">
         <is>
-          <t>Level ladder without licences: people drive without holding a licence</t>
+          <t>NCO 5151.0202 room attendant; Autor-Levy-Murnane 2003 (janitorial)</t>
         </is>
       </c>
     </row>
@@ -9336,37 +9384,33 @@
       </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
-          <t>drove_car</t>
+          <t>tk_guide</t>
         </is>
       </c>
       <c r="E196" s="2" t="inlineStr">
         <is>
-          <t>yes/no</t>
+          <t>select one</t>
         </is>
       </c>
       <c r="F196" s="2" t="inlineStr">
         <is>
-          <t>... a car or jeep?</t>
+          <t>Do you guide or explain things to visitors? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
         </is>
       </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>...कार या जीप?</t>
+          <t>क्या आप आने वालों को रास्ता या बात समझाना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="H196" s="2" t="inlineStr">
         <is>
-          <t>0 No | 1 Yes</t>
-        </is>
-      </c>
-      <c r="I196" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if tk_drive is 1 or 2</t>
-        </is>
-      </c>
+          <t>1 Yes, regularly in my main Yatra work | 2 Not in my main work, but done before elsewhere | 3 Never done</t>
+        </is>
+      </c>
+      <c r="I196" s="2" t="inlineStr"/>
       <c r="J196" s="2" t="inlineStr">
         <is>
-          <t>Level ladder without licences</t>
+          <t>Gathmann and Schonberg 2010; NCO 5113.0200</t>
         </is>
       </c>
     </row>
@@ -9386,37 +9430,33 @@
       </c>
       <c r="D197" s="2" t="inlineStr">
         <is>
-          <t>drove_heavy</t>
+          <t>tk_coord</t>
         </is>
       </c>
       <c r="E197" s="2" t="inlineStr">
         <is>
-          <t>yes/no</t>
+          <t>select one</t>
         </is>
       </c>
       <c r="F197" s="2" t="inlineStr">
         <is>
-          <t>... a truck or bus?</t>
+          <t>Do you coordinate work by phone, radio or signals? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
         </is>
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>...ट्रक या बस?</t>
+          <t>क्या आप फ़ोन, रेडियो या इशारों से दूसरों के साथ तालमेल करना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="H197" s="2" t="inlineStr">
         <is>
-          <t>0 No | 1 Yes</t>
-        </is>
-      </c>
-      <c r="I197" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if tk_drive is 1 or 2</t>
-        </is>
-      </c>
+          <t>1 Yes, regularly in my main Yatra work | 2 Not in my main work, but done before elsewhere | 3 Never done</t>
+        </is>
+      </c>
+      <c r="I197" s="2" t="inlineStr"/>
       <c r="J197" s="2" t="inlineStr">
         <is>
-          <t>Level ladder without licences</t>
+          <t>NCO 8343.1700 ropeway operator</t>
         </is>
       </c>
     </row>
@@ -9436,7 +9476,7 @@
       </c>
       <c r="D198" s="2" t="inlineStr">
         <is>
-          <t>read_at_work</t>
+          <t>drove_twowheeler</t>
         </is>
       </c>
       <c r="E198" s="2" t="inlineStr">
@@ -9446,12 +9486,12 @@
       </c>
       <c r="F198" s="2" t="inlineStr">
         <is>
-          <t>In your work, do you read anything (notes, rate lists, tickets, messages)?</t>
+          <t>Have you ever driven a motorcycle or scooter, with or without a licence?</t>
         </is>
       </c>
       <c r="G198" s="2" t="inlineStr">
         <is>
-          <t>अपने काम में क्या आप कुछ पढ़ते हैं (पर्ची, रेट लिस्ट, टिकट, मैसेज)?</t>
+          <t>क्या आपने कभी मोटरसाइकिल या स्कूटर चलाई है, लाइसेंस हो या न हो?</t>
         </is>
       </c>
       <c r="H198" s="2" t="inlineStr">
@@ -9459,10 +9499,14 @@
           <t>0 No | 1 Yes</t>
         </is>
       </c>
-      <c r="I198" s="2" t="inlineStr"/>
+      <c r="I198" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if tk_drive is 1 or 2</t>
+        </is>
+      </c>
       <c r="J198" s="2" t="inlineStr">
         <is>
-          <t>STEP module 6A</t>
+          <t>Level ladder without licences: people drive without holding a licence</t>
         </is>
       </c>
     </row>
@@ -9482,38 +9526,184 @@
       </c>
       <c r="D199" s="2" t="inlineStr">
         <is>
+          <t>drove_car</t>
+        </is>
+      </c>
+      <c r="E199" s="2" t="inlineStr">
+        <is>
+          <t>yes/no</t>
+        </is>
+      </c>
+      <c r="F199" s="2" t="inlineStr">
+        <is>
+          <t>... a car or jeep?</t>
+        </is>
+      </c>
+      <c r="G199" s="2" t="inlineStr">
+        <is>
+          <t>...कार या जीप?</t>
+        </is>
+      </c>
+      <c r="H199" s="2" t="inlineStr">
+        <is>
+          <t>0 No | 1 Yes</t>
+        </is>
+      </c>
+      <c r="I199" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if tk_drive is 1 or 2</t>
+        </is>
+      </c>
+      <c r="J199" s="2" t="inlineStr">
+        <is>
+          <t>Level ladder without licences</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="n">
+        <v>199</v>
+      </c>
+      <c r="B200" s="2" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="C200" s="2" t="inlineStr">
+        <is>
+          <t>Tasks and skills (short block)</t>
+        </is>
+      </c>
+      <c r="D200" s="2" t="inlineStr">
+        <is>
+          <t>drove_heavy</t>
+        </is>
+      </c>
+      <c r="E200" s="2" t="inlineStr">
+        <is>
+          <t>yes/no</t>
+        </is>
+      </c>
+      <c r="F200" s="2" t="inlineStr">
+        <is>
+          <t>... a truck or bus?</t>
+        </is>
+      </c>
+      <c r="G200" s="2" t="inlineStr">
+        <is>
+          <t>...ट्रक या बस?</t>
+        </is>
+      </c>
+      <c r="H200" s="2" t="inlineStr">
+        <is>
+          <t>0 No | 1 Yes</t>
+        </is>
+      </c>
+      <c r="I200" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if tk_drive is 1 or 2</t>
+        </is>
+      </c>
+      <c r="J200" s="2" t="inlineStr">
+        <is>
+          <t>Level ladder without licences</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="B201" s="2" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="C201" s="2" t="inlineStr">
+        <is>
+          <t>Tasks and skills (short block)</t>
+        </is>
+      </c>
+      <c r="D201" s="2" t="inlineStr">
+        <is>
+          <t>read_at_work</t>
+        </is>
+      </c>
+      <c r="E201" s="2" t="inlineStr">
+        <is>
+          <t>yes/no</t>
+        </is>
+      </c>
+      <c r="F201" s="2" t="inlineStr">
+        <is>
+          <t>In your work, do you read anything (notes, rate lists, tickets, messages)?</t>
+        </is>
+      </c>
+      <c r="G201" s="2" t="inlineStr">
+        <is>
+          <t>अपने काम में क्या आप कुछ पढ़ते हैं (पर्ची, रेट लिस्ट, टिकट, मैसेज)?</t>
+        </is>
+      </c>
+      <c r="H201" s="2" t="inlineStr">
+        <is>
+          <t>0 No | 1 Yes</t>
+        </is>
+      </c>
+      <c r="I201" s="2" t="inlineStr"/>
+      <c r="J201" s="2" t="inlineStr">
+        <is>
+          <t>STEP module 6A</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="n">
+        <v>201</v>
+      </c>
+      <c r="B202" s="2" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="C202" s="2" t="inlineStr">
+        <is>
+          <t>Tasks and skills (short block)</t>
+        </is>
+      </c>
+      <c r="D202" s="2" t="inlineStr">
+        <is>
           <t>calc_at_work</t>
         </is>
       </c>
-      <c r="E199" s="2" t="inlineStr">
+      <c r="E202" s="2" t="inlineStr">
         <is>
           <t>yes/no</t>
         </is>
       </c>
-      <c r="F199" s="2" t="inlineStr">
+      <c r="F202" s="2" t="inlineStr">
         <is>
           <t>In your work, do you work out prices or costs?</t>
         </is>
       </c>
-      <c r="G199" s="2" t="inlineStr">
+      <c r="G202" s="2" t="inlineStr">
         <is>
           <t>अपने काम में क्या आप दाम या ख़र्चा जोड़ते-घटाते हैं?</t>
         </is>
       </c>
-      <c r="H199" s="2" t="inlineStr">
+      <c r="H202" s="2" t="inlineStr">
         <is>
           <t>0 No | 1 Yes</t>
         </is>
       </c>
-      <c r="I199" s="2" t="inlineStr"/>
-      <c r="J199" s="2" t="inlineStr">
+      <c r="I202" s="2" t="inlineStr"/>
+      <c r="J202" s="2" t="inlineStr">
         <is>
           <t>STEP module 6A</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J199"/>
+  <autoFilter ref="A1:J202"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -13269,7 +13459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C118"/>
+  <dimension ref="A1:C121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="78" customWidth="1" min="1" max="1"/>
@@ -14182,7 +14372,7 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>HCES 2022-23, MoSPI Appendix A, Sections 13.1-13.2 (365-day). IHDS-II Income and Social Capital Questionnaire, Q14 14.38-14.39 (365-day). Nigeria GHS-Panel Wave 3, Household Questionnaire, Sections 10B/11 instead uses a 6-month recall for clothing (items 401-441); we follow the two India sources, since one of them (HCES) underlies our poverty line</t>
+          <t>Project design (respondent-gated seasonal recall); the underlying two-season design follows Beegle et al. 2012 and Deaton and Grosh 2000 on usual-period recall</t>
         </is>
       </c>
       <c r="B61" s="2" t="n">
@@ -14190,14 +14380,14 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>cons_clothing_12m</t>
+          <t>spend_differs_by_season</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>HCES 2022-23, MoSPI Appendix A, Section 10.1 (365-day). IHDS-II Income and Social Capital Questionnaire, Q14 14.35-14.37 (365-day, same items). Nigeria GHS-Panel Wave 3, Household Questionnaire, Sections 10B/11 asks school fees inside its education/roster module, per child, not as a household total, so it is not directly comparable</t>
+          <t>HCES 2022-23, MoSPI Appendix A, Sections 13.1-13.2 (365-day). IHDS-II Income and Social Capital Questionnaire, Q14 14.38-14.39 (365-day). Nigeria GHS-Panel Wave 3, Household Questionnaire, Sections 10B/11 instead uses a 6-month recall for clothing (items 401-441); we follow the two India sources, since one of them (HCES) underlies our poverty line</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
@@ -14205,14 +14395,14 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>cons_education_12m</t>
+          <t>cons_clothing_12m</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>HCES 2022-23, MoSPI Appendix A, Section 10.2 (365-day, hospitalisation). IHDS-II Income and Social Capital Questionnaire, Q14 14.34 (365-day, in-patient). Nigeria GHS-Panel Wave 3, Household Questionnaire, Sections 10B/11 instead uses one combined 6-month medical item (less detail); we follow the matching HCES/IHDS split</t>
+          <t>HCES 2022-23, MoSPI Appendix A, Section 10.1 (365-day). IHDS-II Income and Social Capital Questionnaire, Q14 14.35-14.37 (365-day, same items). Nigeria GHS-Panel Wave 3, Household Questionnaire, Sections 10B/11 asks school fees inside its education/roster module, per child, not as a household total, so it is not directly comparable</t>
         </is>
       </c>
       <c r="B63" s="2" t="n">
@@ -14220,14 +14410,14 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>cons_medical_hosp_12m</t>
+          <t>cons_education_12m</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>HCES 2022-23, MoSPI Appendix A, Section 14 (365-day, 10 sub-groups). IHDS-II Income and Social Capital Questionnaire, Q14 14.40-14.48 (365-day). Nigeria GHS-Panel Wave 3, Household Questionnaire, Sections 10B/11 (12-month tier: durables, appliances, building materials). All three agree on the 12-month recall; insurance premiums, which IHDS (14.50) and the Nigeria survey (items 510-513) count here, are excluded, following HCES and standard national-accounts practice (insurance is a financial item, not consumption) -- premiums are covered instead by the insurance items in Module G</t>
+          <t>HCES 2022-23, MoSPI Appendix A, Section 10.2 (365-day, hospitalisation). IHDS-II Income and Social Capital Questionnaire, Q14 14.34 (365-day, in-patient). Nigeria GHS-Panel Wave 3, Household Questionnaire, Sections 10B/11 instead uses one combined 6-month medical item (less detail); we follow the matching HCES/IHDS split</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
@@ -14235,14 +14425,14 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>cons_durables_12m</t>
+          <t>cons_medical_hosp_12m</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI housing indicator (wall limb)</t>
+          <t>HCES 2022-23, MoSPI Appendix A, Section 14 (365-day, 10 sub-groups). IHDS-II Income and Social Capital Questionnaire, Q14 14.40-14.48 (365-day). Nigeria GHS-Panel Wave 3, Household Questionnaire, Sections 10B/11 (12-month tier: durables, appliances, building materials). All three agree on the 12-month recall; insurance premiums, which IHDS (14.50) and the Nigeria survey (items 510-513) count here, are excluded, following HCES and standard national-accounts practice (insurance is a financial item, not consumption) -- premiums are covered instead by the insurance items in Module G</t>
         </is>
       </c>
       <c r="B65" s="2" t="n">
@@ -14250,14 +14440,14 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>wall_material</t>
+          <t>cons_durables_12m</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI</t>
+          <t>NITI Aayog National MPI housing indicator (wall limb)</t>
         </is>
       </c>
       <c r="B66" s="2" t="n">
@@ -14265,14 +14455,14 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>electricity</t>
+          <t>wall_material</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI sanitation indicator (improved/unimproved and shared/not)</t>
+          <t>NITI Aayog National MPI</t>
         </is>
       </c>
       <c r="B67" s="2" t="n">
@@ -14280,14 +14470,14 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>toilet_type</t>
+          <t>electricity</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI drinking-water indicator (JMP improved/unimproved taxonomy)</t>
+          <t>NITI Aayog National MPI sanitation indicator (improved/unimproved and shared/not)</t>
         </is>
       </c>
       <c r="B68" s="2" t="n">
@@ -14295,14 +14485,14 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>drinking_water</t>
+          <t>toilet_type</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>Project design (intra-household burden of water collection; DHS/NFHS ask the same item)</t>
+          <t>NITI Aayog National MPI drinking-water indicator (JMP improved/unimproved taxonomy)</t>
         </is>
       </c>
       <c r="B69" s="2" t="n">
@@ -14310,14 +14500,14 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>water_fetched_by</t>
+          <t>drinking_water</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI cooking-fuel indicator (its own list of dirty fuels)</t>
+          <t>Project design (intra-household burden of water collection; DHS/NFHS ask the same item)</t>
         </is>
       </c>
       <c r="B70" s="2" t="n">
@@ -14325,14 +14515,14 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>cooking_fuel</t>
+          <t>water_fetched_by</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI assets indicator (car or truck limb)</t>
+          <t>NITI Aayog National MPI cooking-fuel indicator (its own list of dirty fuels)</t>
         </is>
       </c>
       <c r="B71" s="2" t="n">
@@ -14340,14 +14530,14 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>owns_car</t>
+          <t>cooking_fuel</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>Project design (pilot livelihood survey)</t>
+          <t>NITI Aayog National MPI assets indicator (car or truck limb)</t>
         </is>
       </c>
       <c r="B72" s="2" t="n">
@@ -14355,14 +14545,14 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>owns_pony_mule</t>
+          <t>owns_car</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI bank-account indicator; VEP adaptive-capacity covariate</t>
+          <t>Project design (pilot livelihood survey)</t>
         </is>
       </c>
       <c r="B73" s="2" t="n">
@@ -14370,14 +14560,14 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>has_bank_account</t>
+          <t>owns_pony_mule</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>VEP adaptive-capacity covariate</t>
+          <t>NITI Aayog National MPI bank-account indicator; VEP adaptive-capacity covariate</t>
         </is>
       </c>
       <c r="B74" s="2" t="n">
@@ -14385,14 +14575,14 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>took_loan_12m</t>
+          <t>has_bank_account</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>VEP adaptive-capacity covariate (lender type)</t>
+          <t>VEP adaptive-capacity covariate</t>
         </is>
       </c>
       <c r="B75" s="2" t="n">
@@ -14400,14 +14590,14 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>credit_source</t>
+          <t>took_loan_12m</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>Islam and Chowdhury 2025 (financial distress and household vulnerability to poverty)</t>
+          <t>VEP adaptive-capacity covariate (lender type)</t>
         </is>
       </c>
       <c r="B76" s="2" t="n">
@@ -14415,14 +14605,14 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>loan_amount</t>
+          <t>credit_source</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>Project design (informal-credit pricing as locally quoted)</t>
+          <t>Islam and Chowdhury 2025 (financial distress and household vulnerability to poverty)</t>
         </is>
       </c>
       <c r="B77" s="2" t="n">
@@ -14430,14 +14620,14 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>loan_interest_per100_pm</t>
+          <t>loan_amount</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>Carter and Zimmerman 2000; Chiwaula et al. 2011 (asset-based vulnerability)</t>
+          <t>Project design (informal lending is often interest-free)</t>
         </is>
       </c>
       <c r="B78" s="2" t="n">
@@ -14445,14 +14635,14 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>loan_against_asset</t>
+          <t>pays_interest</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI health-insurance indicator; Lyons et al. 2023</t>
+          <t>Project design (informal-credit pricing as locally quoted)</t>
         </is>
       </c>
       <c r="B79" s="2" t="n">
@@ -14460,14 +14650,14 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>n_health_insured</t>
+          <t>loan_interest_per100_pm</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>Project design (intra-household financial capability)</t>
+          <t>Carter and Zimmerman 2000; Zimmerman and Carter 2003 (asset-based coping)</t>
         </is>
       </c>
       <c r="B80" s="2" t="n">
@@ -14475,14 +14665,14 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>n_can_transact_online</t>
+          <t>loan_collateral</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>NSS health module (15-day recall)</t>
+          <t>Carter and Zimmerman 2000; Chiwaula et al. 2011 (asset-based vulnerability)</t>
         </is>
       </c>
       <c r="B81" s="2" t="n">
@@ -14490,14 +14680,14 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>morbidity_15d</t>
+          <t>loan_against_asset</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>Project design (a reported illness with no cost/coping follow-up said nothing about its burden)</t>
+          <t>NITI Aayog National MPI health-insurance indicator; Lyons et al. 2023</t>
         </is>
       </c>
       <c r="B82" s="2" t="n">
@@ -14505,14 +14695,14 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>morbidity_coping_15d</t>
+          <t>n_health_insured</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>NSS health module (365-day recall)</t>
+          <t>Project design (intra-household financial capability)</t>
         </is>
       </c>
       <c r="B83" s="2" t="n">
@@ -14520,14 +14710,14 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>hospitalization_365d</t>
+          <t>n_can_transact_online</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>VASyR 2025 barriers_health_case_access_phc_m (primary-care access barriers); Lyons et al. 2023 Table 2 indicator 2 'healthcare access'</t>
+          <t>NSS health module (15-day recall)</t>
         </is>
       </c>
       <c r="B84" s="2" t="n">
@@ -14535,14 +14725,14 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>health_access_barrier_3m</t>
+          <t>morbidity_15d</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI, Child and Adolescent Mortality (weight 1/12)</t>
+          <t>Project design (a reported illness with no cost/coping follow-up said nothing about its burden)</t>
         </is>
       </c>
       <c r="B85" s="2" t="n">
@@ -14550,14 +14740,14 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>child_death_5y</t>
+          <t>morbidity_coping_15d</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI, Maternal Health (weight 1/12)</t>
+          <t>NSS health module (365-day recall)</t>
         </is>
       </c>
       <c r="B86" s="2" t="n">
@@ -14565,14 +14755,14 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>birth_last_5y</t>
+          <t>hospitalization_365d</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI, Maternal Health (antenatal care limb)</t>
+          <t>VASyR 2025 barriers_health_case_access_phc_m (primary-care access barriers); Lyons et al. 2023 Table 2 indicator 2 'healthcare access'</t>
         </is>
       </c>
       <c r="B87" s="2" t="n">
@@ -14580,14 +14770,14 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>anc_4_visits</t>
+          <t>health_access_barrier_3m</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI, Maternal Health (assisted delivery limb)</t>
+          <t>NITI Aayog National MPI, Child and Adolescent Mortality (weight 1/12)</t>
         </is>
       </c>
       <c r="B88" s="2" t="n">
@@ -14595,14 +14785,14 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>skilled_birth_attendant</t>
+          <t>child_death_5y</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>VEP exposure covariate (Azeem et al. 2016); shock inventory following Gunther and Harttgen 2009, via Fujii 2016 section 4</t>
+          <t>NITI Aayog National MPI, Maternal Health (weight 1/12)</t>
         </is>
       </c>
       <c r="B89" s="2" t="n">
@@ -14610,14 +14800,14 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>distress_event_last365d</t>
+          <t>birth_last_5y</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>Coping strategies in VEP studies; Carter and Zimmerman 2000 on asset versus consumption smoothing</t>
+          <t>NITI Aayog National MPI, Maternal Health (antenatal care limb)</t>
         </is>
       </c>
       <c r="B90" s="2" t="n">
@@ -14625,14 +14815,14 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>shock_coping</t>
+          <t>anc_4_visits</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>Project design (see tasks_module W4: exposure must be asked directly)</t>
+          <t>NITI Aayog National MPI, Maternal Health (assisted delivery limb)</t>
         </is>
       </c>
       <c r="B91" s="2" t="n">
@@ -14640,14 +14830,14 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>trek_dependent</t>
+          <t>skilled_birth_attendant</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q5 (all eleven categories, with its own three-way routing)</t>
+          <t>VEP exposure covariate (Azeem et al. 2016); shock inventory following Gunther and Harttgen 2009, via Fujii 2016 section 4</t>
         </is>
       </c>
       <c r="B92" s="2" t="n">
@@ -14655,14 +14845,14 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>job_situation</t>
+          <t>distress_event_last365d</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q8</t>
+          <t>Coping strategies in VEP studies; Carter and Zimmerman 2000 on asset versus consumption smoothing</t>
         </is>
       </c>
       <c r="B93" s="2" t="n">
@@ -14670,14 +14860,14 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>employer_type</t>
+          <t>shock_coping</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q9</t>
+          <t>Project design (see tasks_module W4: exposure must be asked directly)</t>
         </is>
       </c>
       <c r="B94" s="2" t="n">
@@ -14685,14 +14875,14 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>job_permanence</t>
+          <t>trek_dependent</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q11</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q5 (all eleven categories, with its own three-way routing)</t>
         </is>
       </c>
       <c r="B95" s="2" t="n">
@@ -14700,14 +14890,14 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>contract_status</t>
+          <t>job_situation</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q12 (widened to local registrations)</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q8</t>
         </is>
       </c>
       <c r="B96" s="2" t="n">
@@ -14715,14 +14905,14 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>workplace_registered</t>
+          <t>employer_type</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q16</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q9</t>
         </is>
       </c>
       <c r="B97" s="2" t="n">
@@ -14730,14 +14920,14 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>pension_contrib</t>
+          <t>job_permanence</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q17</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q11</t>
         </is>
       </c>
       <c r="B98" s="2" t="n">
@@ -14745,14 +14935,14 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>work_health_ins</t>
+          <t>contract_status</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q18</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q12 (widened to local registrations)</t>
         </is>
       </c>
       <c r="B99" s="2" t="n">
@@ -14760,14 +14950,14 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>leave_rights</t>
+          <t>workplace_registered</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q19</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q16</t>
         </is>
       </c>
       <c r="B100" s="2" t="n">
@@ -14775,14 +14965,14 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>injured_ever</t>
+          <t>pension_contrib</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q20</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q17</t>
         </is>
       </c>
       <c r="B101" s="2" t="n">
@@ -14790,14 +14980,14 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>workplace_injury_12m</t>
+          <t>work_health_ins</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q21</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q18</t>
         </is>
       </c>
       <c r="B102" s="2" t="n">
@@ -14805,14 +14995,14 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>wants_more_work</t>
+          <t>leave_rights</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q22</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q19</t>
         </is>
       </c>
       <c r="B103" s="2" t="n">
@@ -14820,14 +15010,14 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>more_hours_week</t>
+          <t>injured_ever</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q23 (duration in weeks, tied to the calendar instead of a single point in time)</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q20</t>
         </is>
       </c>
       <c r="B104" s="2" t="n">
@@ -14835,14 +15025,14 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>weeks_looked_for_work</t>
+          <t>workplace_injury_12m</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q24</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q21</t>
         </is>
       </c>
       <c r="B105" s="2" t="n">
@@ -14850,14 +15040,14 @@
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>first_job_ever</t>
+          <t>wants_more_work</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>Gathmann and Schonberg 2010; NCO 9333.0100 loader</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q22</t>
         </is>
       </c>
       <c r="B106" s="2" t="n">
@@ -14865,14 +15055,14 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>tk_load</t>
+          <t>more_hours_day</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>Spitz-Oener 2006 / STEP; NCO 8322.0100</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q23 (duration in weeks, tied to the calendar instead of a single point in time)</t>
         </is>
       </c>
       <c r="B107" s="2" t="n">
@@ -14880,14 +15070,14 @@
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>tk_drive</t>
+          <t>months_looked_for_work</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>Gathmann and Schonberg 2010; NCO 8343.1700 ropeway operator</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q24</t>
         </is>
       </c>
       <c r="B108" s="2" t="n">
@@ -14895,14 +15085,14 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>tk_engine</t>
+          <t>first_job_ever</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>Spitz-Oener 2006; NCO 7411.0301 wireman</t>
+          <t>Gathmann and Schonberg 2010; NCO 9333.0100 loader</t>
         </is>
       </c>
       <c r="B109" s="2" t="n">
@@ -14910,14 +15100,14 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>tk_electric</t>
+          <t>tk_load</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>Gathmann and Schonberg 2010; NCO 8343.1700</t>
+          <t>Spitz-Oener 2006 / STEP; NCO 8322.0100</t>
         </is>
       </c>
       <c r="B110" s="2" t="n">
@@ -14925,14 +15115,14 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>tk_safety</t>
+          <t>tk_drive</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>Gathmann and Schonberg 2010; NCO 5223.0200</t>
+          <t>Gathmann and Schonberg 2010; NCO 8343.1700 ropeway operator</t>
         </is>
       </c>
       <c r="B111" s="2" t="n">
@@ -14940,14 +15130,14 @@
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>tk_sell</t>
+          <t>tk_engine</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>Autor and Handel 2013; NCO 5131.0401</t>
+          <t>Spitz-Oener 2006; NCO 7411.0301 wireman</t>
         </is>
       </c>
       <c r="B112" s="2" t="n">
@@ -14955,14 +15145,14 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>tk_cash</t>
+          <t>tk_electric</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>NCO 5120.0300 cook</t>
+          <t>Gathmann and Schonberg 2010; NCO 8343.1700</t>
         </is>
       </c>
       <c r="B113" s="2" t="n">
@@ -14970,14 +15160,14 @@
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>tk_cook</t>
+          <t>tk_safety</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>NCO 5131.0401 waiter; Pal et al. 2026</t>
+          <t>Gathmann and Schonberg 2010; NCO 5223.0200</t>
         </is>
       </c>
       <c r="B114" s="2" t="n">
@@ -14985,14 +15175,14 @@
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>tk_serve</t>
+          <t>tk_sell</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>NCO 5151.0202 room attendant; Autor-Levy-Murnane 2003 (janitorial)</t>
+          <t>Autor and Handel 2013; NCO 5131.0401</t>
         </is>
       </c>
       <c r="B115" s="2" t="n">
@@ -15000,14 +15190,14 @@
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>tk_clean</t>
+          <t>tk_cash</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>Gathmann and Schonberg 2010; NCO 5113.0200</t>
+          <t>NCO 5120.0300 cook</t>
         </is>
       </c>
       <c r="B116" s="2" t="n">
@@ -15015,14 +15205,14 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>tk_guide</t>
+          <t>tk_cook</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>NCO 8343.1700 ropeway operator</t>
+          <t>NCO 5131.0401 waiter; Pal et al. 2026</t>
         </is>
       </c>
       <c r="B117" s="2" t="n">
@@ -15030,14 +15220,14 @@
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>tk_coord</t>
+          <t>tk_serve</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>Level ladder without licences: people drive without holding a licence</t>
+          <t>NCO 5151.0202 room attendant; Autor-Levy-Murnane 2003 (janitorial)</t>
         </is>
       </c>
       <c r="B118" s="2" t="n">
@@ -15045,12 +15235,57 @@
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
+          <t>tk_clean</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>Gathmann and Schonberg 2010; NCO 5113.0200</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>tk_guide</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>NCO 8343.1700 ropeway operator</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>tk_coord</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>Level ladder without licences: people drive without holding a licence</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
           <t>drove_twowheeler</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C118"/>
+  <autoFilter ref="A1:C121"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -15173,7 +15408,7 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8">
@@ -15203,7 +15438,7 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
@@ -15289,7 +15524,7 @@
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>198</v>
+        <v>201</v>
       </c>
     </row>
   </sheetData>

--- a/replication/final_instrument/questionnaire/Question_register.xlsx
+++ b/replication/final_instrument/questionnaire/Question_register.xlsx
@@ -1688,33 +1688,33 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>hours_day_offseason</t>
+          <t>prev_occ_change</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>whole number</t>
+          <t>yes/no</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>In the months when the Yatra is closed and you are doing other work, on a normal working day, how many hours do you work in total?</t>
+          <t>In the last ten years, did you change your main kind of work?</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>जिन महीनों में यात्रा बंद रहती है और आप कोई दूसरा काम करते हैं, उनमें आम दिन में आप कुल कितने घंटे काम करते हैं?</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr"/>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if any month in the calendar is other paid work (status 2 to 7)</t>
-        </is>
-      </c>
+          <t>पिछले दस साल में, क्या आपने अपना मुख्य काम बदला?</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>0 No | 1 Yes</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr"/>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026 Q13, asked a second time for the off-season (decomposed as hours/day x days/week, as in the Yatra-season pair)</t>
+          <t>Occupational mobility check; job-history item</t>
         </is>
       </c>
     </row>
@@ -1734,33 +1734,33 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>days_week_offseason</t>
+          <t>prev_occ</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>whole number</t>
+          <t>free text</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>In those months, how many days a week do you usually work?</t>
+          <t>What was your previous main work? Write down exactly what they say, in their words -- do not pick from a list.</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>उन महीनों में आप हफ़्ते में कितने दिन काम करते हैं?</t>
+          <t>इससे पहले आपका मुख्य काम क्या था?</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr"/>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>Ask only if any month in the calendar is other paid work (status 2 to 7)</t>
+          <t>Ask only if prev_occ_change = 1</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026 Q13, asked a second time for the off-season</t>
+          <t>Gathmann and Schonberg 2010 (observed moves are systematically shorter than random moves -- the validation test for a task-distance measure); coded to NCO-2015 in the office</t>
         </is>
       </c>
     </row>
@@ -1780,33 +1780,29 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>prev_occ_change</t>
+          <t>target_occ</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>yes/no</t>
+          <t>free text</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>In the last ten years, did you change your main kind of work?</t>
+          <t>If you could not continue this work at all, what work would you move to instead? Write down exactly what they say, in their words -- do not pick from a list, and do not prompt with examples.</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>पिछले दस साल में, क्या आपने अपना मुख्य काम बदला?</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>0 No | 1 Yes</t>
-        </is>
-      </c>
+          <t>अगर यह काम बिल्कुल बंद हो जाए, तो आप कौन सा काम करेंगे?</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr"/>
       <c r="I30" s="2" t="inlineStr"/>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>Occupational mobility check; job-history item</t>
+          <t>Project design (stated destination, for the structural-displacement analysis); coded to NCO-2015 in the office</t>
         </is>
       </c>
     </row>
@@ -1826,25 +1822,29 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>prev_occ</t>
+          <t>prev_occ_reason</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>free text</t>
+          <t>select one</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>What was your previous main work? Write down exactly what they say, in their words -- do not pick from a list.</t>
+          <t>What was the main reason you changed?</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>इससे पहले आपका मुख्य काम क्या था?</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr"/>
+          <t>काम बदलने की मुख्य वजह क्या थी?</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>1 Better income | 2 Lost the previous work | 3 Family or seasonal reasons | 4 Moved to this area | 5 Other</t>
+        </is>
+      </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
           <t>Ask only if prev_occ_change = 1</t>
@@ -1852,7 +1852,7 @@
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>Gathmann and Schonberg 2010 (observed moves are systematically shorter than random moves -- the validation test for a task-distance measure); coded to NCO-2015 in the office</t>
+          <t>Job-history item</t>
         </is>
       </c>
     </row>
@@ -1872,29 +1872,33 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>target_occ</t>
+          <t>training_received</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>free text</t>
+          <t>yes/no</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>If you could not continue this work at all, what work would you move to instead? Write down exactly what they say, in their words -- do not pick from a list, and do not prompt with examples.</t>
+          <t>Apart from school and college, have you ever completed any training course or apprenticeship?</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>अगर यह काम बिल्कुल बंद हो जाए, तो आप कौन सा काम करेंगे?</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr"/>
+          <t>स्कूल और कॉलेज की पढ़ाई छोड़कर, क्या आपने कभी कोई ट्रेनिंग या सीखने का कोर्स पूरा किया है?</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>0 No | 1 Yes</t>
+        </is>
+      </c>
       <c r="I32" s="2" t="inlineStr"/>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>Project design (stated destination, for the structural-displacement analysis); coded to NCO-2015 in the office</t>
+          <t>STEP module 2; Chaudhuri et al. 2002 adaptive-capacity covariate</t>
         </is>
       </c>
     </row>
@@ -1914,7 +1918,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>prev_occ_reason</t>
+          <t>training_type</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -1924,27 +1928,27 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>What was the main reason you changed?</t>
+          <t>What kind of course or training was it?</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>काम बदलने की मुख्य वजह क्या थी?</t>
+          <t>वह किस तरह का कोर्स या ट्रेनिंग थी?</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>1 Better income | 2 Lost the previous work | 3 Family or seasonal reasons | 4 Moved to this area | 5 Other</t>
+          <t>1 ITI or other trade course | 2 Hotel, catering or tourism | 3 Driving | 4 Mobile, computer or electrical repair | 5 Tailoring or handicraft | 6 Animal handling or veterinary | 7 Construction trade (mason, carpenter, plumber) | 8 Health or first aid | 9 Other</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>Ask only if prev_occ_change = 1</t>
+          <t>Ask only if training_received = 1</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>Job-history item</t>
+          <t>STEP module 2</t>
         </is>
       </c>
     </row>
@@ -1964,33 +1968,33 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>training_received</t>
+          <t>training_type_other</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>yes/no</t>
+          <t>free text</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Apart from school and college, have you ever completed any training course or apprenticeship?</t>
+          <t>What was it? Write what they say.</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>स्कूल और कॉलेज की पढ़ाई छोड़कर, क्या आपने कभी कोई ट्रेनिंग या सीखने का कोर्स पूरा किया है?</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>0 No | 1 Yes</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr"/>
+          <t>वह क्या थी? जैसा वे बताएँ वैसा लिख लीजिए।</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr"/>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if training_type = 9 (Other); may be left blank</t>
+        </is>
+      </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>STEP module 2; Chaudhuri et al. 2002 adaptive-capacity covariate</t>
+          <t>STEP module 2</t>
         </is>
       </c>
     </row>
@@ -2000,17 +2004,17 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Work and work history</t>
+          <t>Monthly calendar of work and income; remittances</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>training_type</t>
+          <t>status_m1</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -2020,27 +2024,23 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>What kind of course or training was it?</t>
+          <t>In January, what was your main work or activity? (Fill the Yatra months first, then the others.)</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>वह किस तरह का कोर्स या ट्रेनिंग थी?</t>
+          <t>जनवरी में आपका मुख्य काम या काम-धंधा क्या था?</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>1 ITI or other trade course | 2 Hotel, catering or tourism | 3 Driving | 4 Mobile, computer or electrical repair | 5 Tailoring or handicraft | 6 Animal handling or veterinary | 7 Construction trade (mason, carpenter, plumber) | 8 Health or first aid | 9 Other</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if training_received = 1</t>
-        </is>
-      </c>
+          <t>1 Yatra work (main occupation) | 2 Farming (crops) | 3 Livestock (animals) | 4 Wage labour, staying at home | 5 Went away from home for work | 6 Own small shop, stall or trade | 7 Salaried job | 8 No paid work</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr"/>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>STEP module 2</t>
+          <t>Monthly work calendar (Dercon and Krishnan 2000 measure seasonality month by month)</t>
         </is>
       </c>
     </row>
@@ -2050,43 +2050,43 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Work and work history</t>
+          <t>Monthly calendar of work and income; remittances</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>training_type_other</t>
+          <t>status_m2</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>free text</t>
+          <t>select one</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>What was it? Write what they say.</t>
+          <t>In February, what was your main work or activity? (Fill the Yatra months first, then the others.)</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>वह क्या थी? जैसा वे बताएँ वैसा लिख लीजिए।</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr"/>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if training_type = 9 (Other); may be left blank</t>
-        </is>
-      </c>
+          <t>फ़रवरी में आपका मुख्य काम या काम-धंधा क्या था?</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>1 Yatra work (main occupation) | 2 Farming (crops) | 3 Livestock (animals) | 4 Wage labour, staying at home | 5 Went away from home for work | 6 Own small shop, stall or trade | 7 Salaried job | 8 No paid work</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr"/>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>STEP module 2</t>
+          <t>Monthly work calendar (Dercon and Krishnan 2000 measure seasonality month by month)</t>
         </is>
       </c>
     </row>
@@ -2106,7 +2106,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>status_m1</t>
+          <t>status_m3</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>In January, what was your main work or activity? (Fill the Yatra months first, then the others.)</t>
+          <t>In March, what was your main work or activity? (Fill the Yatra months first, then the others.)</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>जनवरी में आपका मुख्य काम या काम-धंधा क्या था?</t>
+          <t>मार्च में आपका मुख्य काम या काम-धंधा क्या था?</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>status_m2</t>
+          <t>status_m4</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -2162,12 +2162,12 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>In February, what was your main work or activity? (Fill the Yatra months first, then the others.)</t>
+          <t>In April, what was your main work or activity? (Fill the Yatra months first, then the others.)</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>फ़रवरी में आपका मुख्य काम या काम-धंधा क्या था?</t>
+          <t>अप्रैल में आपका मुख्य काम या काम-धंधा क्या था?</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -2198,7 +2198,7 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>status_m3</t>
+          <t>status_m5</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -2208,12 +2208,12 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>In March, what was your main work or activity? (Fill the Yatra months first, then the others.)</t>
+          <t>In May, what was your main work or activity? (Fill the Yatra months first, then the others.)</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>मार्च में आपका मुख्य काम या काम-धंधा क्या था?</t>
+          <t>मई में आपका मुख्य काम या काम-धंधा क्या था?</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -2244,7 +2244,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>status_m4</t>
+          <t>status_m6</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -2254,12 +2254,12 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>In April, what was your main work or activity? (Fill the Yatra months first, then the others.)</t>
+          <t>In June, what was your main work or activity? (Fill the Yatra months first, then the others.)</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>अप्रैल में आपका मुख्य काम या काम-धंधा क्या था?</t>
+          <t>जून में आपका मुख्य काम या काम-धंधा क्या था?</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -2290,7 +2290,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>status_m5</t>
+          <t>status_m7</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>In May, what was your main work or activity? (Fill the Yatra months first, then the others.)</t>
+          <t>In July, what was your main work or activity? (Fill the Yatra months first, then the others.)</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>मई में आपका मुख्य काम या काम-धंधा क्या था?</t>
+          <t>जुलाई में आपका मुख्य काम या काम-धंधा क्या था?</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -2336,7 +2336,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>status_m6</t>
+          <t>status_m8</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -2346,12 +2346,12 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>In June, what was your main work or activity? (Fill the Yatra months first, then the others.)</t>
+          <t>In August, what was your main work or activity? (Fill the Yatra months first, then the others.)</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>जून में आपका मुख्य काम या काम-धंधा क्या था?</t>
+          <t>अगस्त में आपका मुख्य काम या काम-धंधा क्या था?</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>status_m7</t>
+          <t>status_m9</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>In July, what was your main work or activity? (Fill the Yatra months first, then the others.)</t>
+          <t>In September, what was your main work or activity? (Fill the Yatra months first, then the others.)</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>जुलाई में आपका मुख्य काम या काम-धंधा क्या था?</t>
+          <t>सितंबर में आपका मुख्य काम या काम-धंधा क्या था?</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -2428,7 +2428,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>status_m8</t>
+          <t>status_m10</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -2438,12 +2438,12 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>In August, what was your main work or activity? (Fill the Yatra months first, then the others.)</t>
+          <t>In October, what was your main work or activity? (Fill the Yatra months first, then the others.)</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>अगस्त में आपका मुख्य काम या काम-धंधा क्या था?</t>
+          <t>अक्टूबर में आपका मुख्य काम या काम-धंधा क्या था?</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>status_m9</t>
+          <t>status_m11</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>In September, what was your main work or activity? (Fill the Yatra months first, then the others.)</t>
+          <t>In November, what was your main work or activity? (Fill the Yatra months first, then the others.)</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>सितंबर में आपका मुख्य काम या काम-धंधा क्या था?</t>
+          <t>नवंबर में आपका मुख्य काम या काम-धंधा क्या था?</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -2520,7 +2520,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>status_m10</t>
+          <t>status_m12</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>In October, what was your main work or activity? (Fill the Yatra months first, then the others.)</t>
+          <t>In December, what was your main work or activity? (Fill the Yatra months first, then the others.)</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>अक्टूबर में आपका मुख्य काम या काम-धंधा क्या था?</t>
+          <t>दिसंबर में आपका मुख्य काम या काम-धंधा क्या था?</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>status_m11</t>
+          <t>knows_monthly_income</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -2576,23 +2576,23 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>In November, what was your main work or activity? (Fill the Yatra months first, then the others.)</t>
+          <t>Can you tell me roughly what you earned in each month of the past year, or would it be easier to give one total for the whole year?</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>नवंबर में आपका मुख्य काम या काम-धंधा क्या था?</t>
+          <t>क्या आप हर महीने की कमाई अलग-अलग बता सकते हैं, या पूरे साल का एक जोड़ बताना आसान रहेगा?</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>1 Yatra work (main occupation) | 2 Farming (crops) | 3 Livestock (animals) | 4 Wage labour, staying at home | 5 Went away from home for work | 6 Own small shop, stall or trade | 7 Salaried job | 8 No paid work</t>
+          <t>1 Month by month | 0 One total for the whole year</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr"/>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>Monthly work calendar (Dercon and Krishnan 2000 measure seasonality month by month)</t>
+          <t>Apablaza et al. 2026 Q14/Q15 (the 'does not know' route out of monthly earnings)</t>
         </is>
       </c>
     </row>
@@ -2612,33 +2612,33 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>status_m12</t>
+          <t>income_m1</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>select one</t>
+          <t>amount (Rs)</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>In December, what was your main work or activity? (Fill the Yatra months first, then the others.)</t>
+          <t>How much did you earn from all your work in January, after costs? (Rs)</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>दिसंबर में आपका मुख्य काम या काम-धंधा क्या था?</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>1 Yatra work (main occupation) | 2 Farming (crops) | 3 Livestock (animals) | 4 Wage labour, staying at home | 5 Went away from home for work | 6 Own small shop, stall or trade | 7 Salaried job | 8 No paid work</t>
-        </is>
-      </c>
-      <c r="I48" s="2" t="inlineStr"/>
+          <t>जनवरी में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr"/>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if knows_monthly_income = 1; automatic 0 if status_m1 = 8 (no paid work)</t>
+        </is>
+      </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>Monthly work calendar (Dercon and Krishnan 2000 measure seasonality month by month)</t>
+          <t>Apablaza et al. 2026 Q14 (monthly earnings), asked month by month to avoid heaping on one typical figure</t>
         </is>
       </c>
     </row>
@@ -2658,33 +2658,33 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>knows_monthly_income</t>
+          <t>income_m2</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>select one</t>
+          <t>amount (Rs)</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>Can you tell me roughly what you earned in each month of the past year, or would it be easier to give one total for the whole year?</t>
+          <t>How much did you earn from all your work in February, after costs? (Rs)</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>क्या आप हर महीने की कमाई अलग-अलग बता सकते हैं, या पूरे साल का एक जोड़ बताना आसान रहेगा?</t>
-        </is>
-      </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>1 Month by month | 0 One total for the whole year</t>
-        </is>
-      </c>
-      <c r="I49" s="2" t="inlineStr"/>
+          <t>फ़रवरी में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr"/>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if knows_monthly_income = 1; automatic 0 if status_m2 = 8 (no paid work)</t>
+        </is>
+      </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026 Q14/Q15 (the 'does not know' route out of monthly earnings)</t>
+          <t>Apablaza et al. 2026 Q14 (monthly earnings), asked month by month to avoid heaping on one typical figure</t>
         </is>
       </c>
     </row>
@@ -2704,7 +2704,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>income_m1</t>
+          <t>income_m3</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -2714,18 +2714,18 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>How much did you earn from all your work in January, after costs? (Rs)</t>
+          <t>How much did you earn from all your work in March, after costs? (Rs)</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>जनवरी में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
+          <t>मार्च में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr"/>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>Ask only if knows_monthly_income = 1; automatic 0 if status_m1 = 8 (no paid work)</t>
+          <t>Ask only if knows_monthly_income = 1; automatic 0 if status_m3 = 8 (no paid work)</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>income_m2</t>
+          <t>income_m4</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -2760,18 +2760,18 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>How much did you earn from all your work in February, after costs? (Rs)</t>
+          <t>How much did you earn from all your work in April, after costs? (Rs)</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>फ़रवरी में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
+          <t>अप्रैल में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr"/>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>Ask only if knows_monthly_income = 1; automatic 0 if status_m2 = 8 (no paid work)</t>
+          <t>Ask only if knows_monthly_income = 1; automatic 0 if status_m4 = 8 (no paid work)</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>income_m3</t>
+          <t>income_m5</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -2806,18 +2806,18 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>How much did you earn from all your work in March, after costs? (Rs)</t>
+          <t>How much did you earn from all your work in May, after costs? (Rs)</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>मार्च में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
+          <t>मई में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr"/>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>Ask only if knows_monthly_income = 1; automatic 0 if status_m3 = 8 (no paid work)</t>
+          <t>Ask only if knows_monthly_income = 1; automatic 0 if status_m5 = 8 (no paid work)</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -2842,7 +2842,7 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>income_m4</t>
+          <t>income_m6</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -2852,18 +2852,18 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>How much did you earn from all your work in April, after costs? (Rs)</t>
+          <t>How much did you earn from all your work in June, after costs? (Rs)</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>अप्रैल में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
+          <t>जून में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr"/>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>Ask only if knows_monthly_income = 1; automatic 0 if status_m4 = 8 (no paid work)</t>
+          <t>Ask only if knows_monthly_income = 1; automatic 0 if status_m6 = 8 (no paid work)</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -2888,7 +2888,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>income_m5</t>
+          <t>income_m7</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -2898,18 +2898,18 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>How much did you earn from all your work in May, after costs? (Rs)</t>
+          <t>How much did you earn from all your work in July, after costs? (Rs)</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>मई में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
+          <t>जुलाई में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr"/>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>Ask only if knows_monthly_income = 1; automatic 0 if status_m5 = 8 (no paid work)</t>
+          <t>Ask only if knows_monthly_income = 1; automatic 0 if status_m7 = 8 (no paid work)</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>income_m6</t>
+          <t>income_m8</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -2944,18 +2944,18 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>How much did you earn from all your work in June, after costs? (Rs)</t>
+          <t>How much did you earn from all your work in August, after costs? (Rs)</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>जून में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
+          <t>अगस्त में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr"/>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>Ask only if knows_monthly_income = 1; automatic 0 if status_m6 = 8 (no paid work)</t>
+          <t>Ask only if knows_monthly_income = 1; automatic 0 if status_m8 = 8 (no paid work)</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -2980,7 +2980,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>income_m7</t>
+          <t>income_m9</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -2990,18 +2990,18 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>How much did you earn from all your work in July, after costs? (Rs)</t>
+          <t>How much did you earn from all your work in September, after costs? (Rs)</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>जुलाई में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
+          <t>सितंबर में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr"/>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>Ask only if knows_monthly_income = 1; automatic 0 if status_m7 = 8 (no paid work)</t>
+          <t>Ask only if knows_monthly_income = 1; automatic 0 if status_m9 = 8 (no paid work)</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -3026,7 +3026,7 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>income_m8</t>
+          <t>income_m10</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -3036,18 +3036,18 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>How much did you earn from all your work in August, after costs? (Rs)</t>
+          <t>How much did you earn from all your work in October, after costs? (Rs)</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>अगस्त में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
+          <t>अक्टूबर में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr"/>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>Ask only if knows_monthly_income = 1; automatic 0 if status_m8 = 8 (no paid work)</t>
+          <t>Ask only if knows_monthly_income = 1; automatic 0 if status_m10 = 8 (no paid work)</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -3072,7 +3072,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>income_m9</t>
+          <t>income_m11</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -3082,18 +3082,18 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>How much did you earn from all your work in September, after costs? (Rs)</t>
+          <t>How much did you earn from all your work in November, after costs? (Rs)</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>सितंबर में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
+          <t>नवंबर में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr"/>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>Ask only if knows_monthly_income = 1; automatic 0 if status_m9 = 8 (no paid work)</t>
+          <t>Ask only if knows_monthly_income = 1; automatic 0 if status_m11 = 8 (no paid work)</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -3118,7 +3118,7 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>income_m10</t>
+          <t>income_m12</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -3128,18 +3128,18 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>How much did you earn from all your work in October, after costs? (Rs)</t>
+          <t>How much did you earn from all your work in December, after costs? (Rs)</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>अक्टूबर में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
+          <t>दिसंबर में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr"/>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>Ask only if knows_monthly_income = 1; automatic 0 if status_m10 = 8 (no paid work)</t>
+          <t>Ask only if knows_monthly_income = 1; automatic 0 if status_m12 = 8 (no paid work)</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>income_m11</t>
+          <t>income_annual_total</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -3174,23 +3174,23 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>How much did you earn from all your work in November, after costs? (Rs)</t>
+          <t>Thinking of the whole past year, about how much did you earn in total from all your work, after costs? (Rs)</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>नवंबर में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
+          <t>पूरे पिछले साल को मिलाकर, सारे काम से ख़र्चा निकालकर आपने कुल कितना कमाया? (रुपये)</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr"/>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>Ask only if knows_monthly_income = 1; automatic 0 if status_m11 = 8 (no paid work)</t>
+          <t>Ask only if knows_monthly_income = 0</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026 Q14 (monthly earnings), asked month by month to avoid heaping on one typical figure</t>
+          <t>Apablaza et al. 2026 Q15 (fallback when monthly earnings are not known), adapted to an annual total for a seasonal workforce</t>
         </is>
       </c>
     </row>
@@ -3210,33 +3210,33 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>income_m12</t>
+          <t>pct_income_yatra</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>amount (Rs)</t>
+          <t>whole number</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>How much did you earn from all your work in December, after costs? (Rs)</t>
+          <t>Out of every 100 rupees you earned in the whole year, how many came from your Yatra work? (The rest is counted as coming from your other work.)</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>दिसंबर में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
+          <t>पूरे साल में आपने जो 100 रुपये कमाए, उनमें से कितने यात्रा के काम से आए? (बाकी दूसरे काम का माना जाएगा।)</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr"/>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>Ask only if knows_monthly_income = 1; automatic 0 if status_m12 = 8 (no paid work)</t>
+          <t>Ask only if knows_monthly_income = 0</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026 Q14 (monthly earnings), asked month by month to avoid heaping on one typical figure</t>
+          <t>Project design (the Yatra / non-Yatra split needed to reweight an annual total onto the work calendar)</t>
         </is>
       </c>
     </row>
@@ -3256,7 +3256,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>income_annual_total</t>
+          <t>remit_out_yatra_pm</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -3266,23 +3266,19 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>Thinking of the whole past year, about how much did you earn in total from all your work, after costs? (Rs)</t>
+          <t>In a normal month during the Yatra season, how much money do you usually send to family or others living elsewhere? (Rs, 0 if none)</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>पूरे पिछले साल को मिलाकर, सारे काम से ख़र्चा निकालकर आपने कुल कितना कमाया? (रुपये)</t>
+          <t>यात्रा के मौसम के आम महीने में, आप घर या कहीं और रहने वालों को कितना पैसा भेजते हैं? (रुपये, न भेजते हों तो 0)</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr"/>
-      <c r="I62" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if knows_monthly_income = 0</t>
-        </is>
-      </c>
+      <c r="I62" s="2" t="inlineStr"/>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026 Q15 (fallback when monthly earnings are not known), adapted to an annual total for a seasonal workforce</t>
+          <t>NSS 64th Round practice (amount); frequency dropped for length</t>
         </is>
       </c>
     </row>
@@ -3302,33 +3298,29 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>pct_income_yatra</t>
+          <t>remit_out_offseason_pm</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>whole number</t>
+          <t>amount (Rs)</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>Out of every 100 rupees you earned in the whole year, how many came from your Yatra work? (The rest is counted as coming from your other work.)</t>
+          <t>In a normal month when the Yatra is closed, how much do you usually send? (Rs, 0 if none)</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>पूरे साल में आपने जो 100 रुपये कमाए, उनमें से कितने यात्रा के काम से आए? (बाकी दूसरे काम का माना जाएगा।)</t>
+          <t>जब यात्रा बंद रहती है, उस आम महीने में कितना भेजते हैं? (रुपये, न भेजते हों तो 0)</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr"/>
-      <c r="I63" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if knows_monthly_income = 0</t>
-        </is>
-      </c>
+      <c r="I63" s="2" t="inlineStr"/>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>Project design (the Yatra / non-Yatra split needed to reweight an annual total onto the work calendar)</t>
+          <t>NSS 64th Round practice (amount); frequency dropped for length</t>
         </is>
       </c>
     </row>
@@ -3348,29 +3340,37 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>remit_out_yatra_pm</t>
+          <t>remit_mode</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>amount (Rs)</t>
+          <t>select one</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>In a normal month during the Yatra season, how much money do you usually send to family or others living elsewhere? (Rs, 0 if none)</t>
+          <t>How do you usually send it?</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम महीने में, आप घर या कहीं और रहने वालों को कितना पैसा भेजते हैं? (रुपये, न भेजते हों तो 0)</t>
-        </is>
-      </c>
-      <c r="H64" s="2" t="inlineStr"/>
-      <c r="I64" s="2" t="inlineStr"/>
+          <t>आप पैसा आम तौर पर कैसे भेजते हैं?</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>1 Bank transfer | 2 UPI or phone payment | 3 Money order or post office | 4 Sent with someone going home | 5 Carried it myself | 6 Other</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if remit_out_yatra_pm &gt; 0 or remit_out_offseason_pm &gt; 0</t>
+        </is>
+      </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>NSS 64th Round practice (amount); frequency dropped for length</t>
+          <t>Project design (remittance channel as a financial-inclusion and cost measure)</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>remit_out_offseason_pm</t>
+          <t>remit_in_yatra_pm</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>In a normal month when the Yatra is closed, how much do you usually send? (Rs, 0 if none)</t>
+          <t>In a normal month during the Yatra season, how much money do you usually receive from family or others? (Rs, 0 if none)</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम महीने में कितना भेजते हैं? (रुपये, न भेजते हों तो 0)</t>
+          <t>यात्रा के मौसम के आम महीने में, घरवालों या किसी और से आपको कितना पैसा मिलता है? (रुपये, न मिलता हो तो 0)</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr"/>
@@ -3432,37 +3432,29 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>remit_mode</t>
+          <t>remit_in_offseason_pm</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>select one</t>
+          <t>amount (Rs)</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>How do you usually send it?</t>
+          <t>In a normal month when the Yatra is closed, how much do you usually receive? (Rs, 0 if none)</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>आप पैसा आम तौर पर कैसे भेजते हैं?</t>
-        </is>
-      </c>
-      <c r="H66" s="2" t="inlineStr">
-        <is>
-          <t>1 Bank transfer | 2 UPI or phone payment | 3 Money order or post office | 4 Sent with someone going home | 5 Carried it myself | 6 Other</t>
-        </is>
-      </c>
-      <c r="I66" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if remit_out_yatra_pm &gt; 0 or remit_out_offseason_pm &gt; 0</t>
-        </is>
-      </c>
+          <t>जब यात्रा बंद रहती है, उस आम महीने में कितना मिलता है? (रुपये, न मिलता हो तो 0)</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr"/>
+      <c r="I66" s="2" t="inlineStr"/>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>Project design (remittance channel as a financial-inclusion and cost measure)</t>
+          <t>NSS 64th Round practice (amount); frequency dropped for length</t>
         </is>
       </c>
     </row>
@@ -3482,29 +3474,33 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>remit_in_yatra_pm</t>
+          <t>hours_day_offseason</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>amount (Rs)</t>
+          <t>whole number</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>In a normal month during the Yatra season, how much money do you usually receive from family or others? (Rs, 0 if none)</t>
+          <t>In the months when the Yatra is closed and you are doing other work, on a normal working day, how many hours do you work in total?</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम महीने में, घरवालों या किसी और से आपको कितना पैसा मिलता है? (रुपये, न मिलता हो तो 0)</t>
+          <t>जिन महीनों में यात्रा बंद रहती है और आप कोई दूसरा काम करते हैं, उनमें आम दिन में आप कुल कितने घंटे काम करते हैं?</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr"/>
-      <c r="I67" s="2" t="inlineStr"/>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if any month in the calendar is other paid work (status 2 to 7)</t>
+        </is>
+      </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>NSS 64th Round practice (amount); frequency dropped for length</t>
+          <t>Apablaza et al. 2026 Q13, asked a second time for the off-season (decomposed as hours/day x days/week, as in the Yatra-season pair)</t>
         </is>
       </c>
     </row>
@@ -3524,29 +3520,33 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>remit_in_offseason_pm</t>
+          <t>days_week_offseason</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>amount (Rs)</t>
+          <t>whole number</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>In a normal month when the Yatra is closed, how much do you usually receive? (Rs, 0 if none)</t>
+          <t>In those months, how many days a week do you usually work?</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम महीने में कितना मिलता है? (रुपये, न मिलता हो तो 0)</t>
+          <t>उन महीनों में आप हफ़्ते में कितने दिन काम करते हैं?</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr"/>
-      <c r="I68" s="2" t="inlineStr"/>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if any month in the calendar is other paid work (status 2 to 7)</t>
+        </is>
+      </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>NSS 64th Round practice (amount); frequency dropped for length</t>
+          <t>Apablaza et al. 2026 Q13, asked a second time for the off-season</t>
         </is>
       </c>
     </row>
@@ -6746,37 +6746,37 @@
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>loan_collateral</t>
+          <t>loan_against_asset</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>select one</t>
+          <t>yes/no</t>
         </is>
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>What did you have to give as security?</t>
+          <t>Did you have to give something as security for it -- an animal, a vehicle, jewellery, land or your business?</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>आपको क्या गिरवी रखना पड़ा?</t>
+          <t>क्या उसके बदले कुछ गिरवी रखना पड़ा — जानवर, गाड़ी, गहने, ज़मीन या आपका धंधा?</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
-          <t>1 Jewellery or ornaments | 2 Land | 3 Animals | 4 A vehicle | 5 Shop stock or business goods | 6 House or building | 7 Something else</t>
+          <t>0 No | 1 Yes</t>
         </is>
       </c>
       <c r="I139" s="2" t="inlineStr">
         <is>
-          <t>Ask only if loan_against_asset = 1</t>
+          <t>Ask only if took_loan_12m = 1</t>
         </is>
       </c>
       <c r="J139" s="2" t="inlineStr">
         <is>
-          <t>Carter and Zimmerman 2000; Zimmerman and Carter 2003 (asset-based coping)</t>
+          <t>Carter and Zimmerman 2000; Chiwaula et al. 2011 (asset-based vulnerability)</t>
         </is>
       </c>
     </row>
@@ -6796,37 +6796,37 @@
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>loan_against_asset</t>
+          <t>loan_collateral</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>yes/no</t>
+          <t>select one</t>
         </is>
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>Did you have to give something as security for it -- an animal, a vehicle, jewellery, land or your business?</t>
+          <t>What did you have to give as security?</t>
         </is>
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>क्या उसके बदले कुछ गिरवी रखना पड़ा — जानवर, गाड़ी, गहने, ज़मीन या आपका धंधा?</t>
+          <t>आपको क्या गिरवी रखना पड़ा?</t>
         </is>
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
-          <t>0 No | 1 Yes</t>
+          <t>1 Jewellery or ornaments | 2 Land | 3 Animals | 4 A vehicle | 5 Shop stock or business goods | 6 House or building | 7 Something else</t>
         </is>
       </c>
       <c r="I140" s="2" t="inlineStr">
         <is>
-          <t>Ask only if took_loan_12m = 1</t>
+          <t>Ask only if loan_against_asset = 1</t>
         </is>
       </c>
       <c r="J140" s="2" t="inlineStr">
         <is>
-          <t>Carter and Zimmerman 2000; Chiwaula et al. 2011 (asset-based vulnerability)</t>
+          <t>Carter and Zimmerman 2000; Zimmerman and Carter 2003 (asset-based coping)</t>
         </is>
       </c>
     </row>
@@ -14132,7 +14132,7 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026 Q13, asked a second time for the off-season (decomposed as hours/day x days/week, as in the Yatra-season pair)</t>
+          <t>Occupational mobility check; job-history item</t>
         </is>
       </c>
       <c r="B45" s="2" t="n">
@@ -14140,14 +14140,14 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>hours_day_offseason</t>
+          <t>prev_occ_change</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026 Q13, asked a second time for the off-season</t>
+          <t>Gathmann and Schonberg 2010 (observed moves are systematically shorter than random moves -- the validation test for a task-distance measure); coded to NCO-2015 in the office</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -14155,14 +14155,14 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>days_week_offseason</t>
+          <t>prev_occ</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Occupational mobility check; job-history item</t>
+          <t>Project design (stated destination, for the structural-displacement analysis); coded to NCO-2015 in the office</t>
         </is>
       </c>
       <c r="B47" s="2" t="n">
@@ -14170,14 +14170,14 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>prev_occ_change</t>
+          <t>target_occ</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Gathmann and Schonberg 2010 (observed moves are systematically shorter than random moves -- the validation test for a task-distance measure); coded to NCO-2015 in the office</t>
+          <t>Job-history item</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -14185,14 +14185,14 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>prev_occ</t>
+          <t>prev_occ_reason</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Project design (stated destination, for the structural-displacement analysis); coded to NCO-2015 in the office</t>
+          <t>STEP module 2; Chaudhuri et al. 2002 adaptive-capacity covariate</t>
         </is>
       </c>
       <c r="B49" s="2" t="n">
@@ -14200,14 +14200,14 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>target_occ</t>
+          <t>training_received</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Job-history item</t>
+          <t>Apablaza et al. 2026 Q14/Q15 (the 'does not know' route out of monthly earnings)</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -14215,14 +14215,14 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>prev_occ_reason</t>
+          <t>knows_monthly_income</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>STEP module 2; Chaudhuri et al. 2002 adaptive-capacity covariate</t>
+          <t>Apablaza et al. 2026 Q15 (fallback when monthly earnings are not known), adapted to an annual total for a seasonal workforce</t>
         </is>
       </c>
       <c r="B51" s="2" t="n">
@@ -14230,14 +14230,14 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>training_received</t>
+          <t>income_annual_total</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026 Q14/Q15 (the 'does not know' route out of monthly earnings)</t>
+          <t>Project design (the Yatra / non-Yatra split needed to reweight an annual total onto the work calendar)</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
@@ -14245,14 +14245,14 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>knows_monthly_income</t>
+          <t>pct_income_yatra</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026 Q15 (fallback when monthly earnings are not known), adapted to an annual total for a seasonal workforce</t>
+          <t>Project design (remittance channel as a financial-inclusion and cost measure)</t>
         </is>
       </c>
       <c r="B53" s="2" t="n">
@@ -14260,14 +14260,14 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>income_annual_total</t>
+          <t>remit_mode</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Project design (the Yatra / non-Yatra split needed to reweight an annual total onto the work calendar)</t>
+          <t>Apablaza et al. 2026 Q13, asked a second time for the off-season (decomposed as hours/day x days/week, as in the Yatra-season pair)</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
@@ -14275,14 +14275,14 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>pct_income_yatra</t>
+          <t>hours_day_offseason</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>Project design (remittance channel as a financial-inclusion and cost measure)</t>
+          <t>Apablaza et al. 2026 Q13, asked a second time for the off-season</t>
         </is>
       </c>
       <c r="B55" s="2" t="n">
@@ -14290,7 +14290,7 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>remit_mode</t>
+          <t>days_week_offseason</t>
         </is>
       </c>
     </row>
@@ -14657,7 +14657,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>Carter and Zimmerman 2000; Zimmerman and Carter 2003 (asset-based coping)</t>
+          <t>Carter and Zimmerman 2000; Chiwaula et al. 2011 (asset-based vulnerability)</t>
         </is>
       </c>
       <c r="B80" s="2" t="n">
@@ -14665,14 +14665,14 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>loan_collateral</t>
+          <t>loan_against_asset</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>Carter and Zimmerman 2000; Chiwaula et al. 2011 (asset-based vulnerability)</t>
+          <t>Carter and Zimmerman 2000; Zimmerman and Carter 2003 (asset-based coping)</t>
         </is>
       </c>
       <c r="B81" s="2" t="n">
@@ -14680,7 +14680,7 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>loan_against_asset</t>
+          <t>loan_collateral</t>
         </is>
       </c>
     </row>
@@ -15363,7 +15363,7 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5">
@@ -15378,7 +15378,7 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6">

--- a/replication/final_instrument/questionnaire/Question_register.xlsx
+++ b/replication/final_instrument/questionnaire/Question_register.xlsx
@@ -2034,7 +2034,7 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>1 Yatra work (main occupation) | 2 Farming (crops) | 3 Livestock (animals) | 4 Casual or daily wage labour | 5 Construction work | 6 Own small shop, stall or trade | 7 Salaried job | 8 No paid work</t>
+          <t>1 Yatra work, or getting ready for the season | 2 Farming (crops) | 3 Livestock (animals) | 4 Casual or daily wage labour | 5 Construction work | 6 Own small shop, stall or trade | 7 Salaried job | 8 No paid work</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr"/>
@@ -2080,7 +2080,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>1 Yatra work (main occupation) | 2 Farming (crops) | 3 Livestock (animals) | 4 Casual or daily wage labour | 5 Construction work | 6 Own small shop, stall or trade | 7 Salaried job | 8 No paid work</t>
+          <t>1 Yatra work, or getting ready for the season | 2 Farming (crops) | 3 Livestock (animals) | 4 Casual or daily wage labour | 5 Construction work | 6 Own small shop, stall or trade | 7 Salaried job | 8 No paid work</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr"/>
@@ -2126,7 +2126,7 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1 Yatra work (main occupation) | 2 Farming (crops) | 3 Livestock (animals) | 4 Casual or daily wage labour | 5 Construction work | 6 Own small shop, stall or trade | 7 Salaried job | 8 No paid work</t>
+          <t>1 Yatra work, or getting ready for the season | 2 Farming (crops) | 3 Livestock (animals) | 4 Casual or daily wage labour | 5 Construction work | 6 Own small shop, stall or trade | 7 Salaried job | 8 No paid work</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr"/>
@@ -2172,7 +2172,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>1 Yatra work (main occupation) | 2 Farming (crops) | 3 Livestock (animals) | 4 Casual or daily wage labour | 5 Construction work | 6 Own small shop, stall or trade | 7 Salaried job | 8 No paid work</t>
+          <t>1 Yatra work, or getting ready for the season | 2 Farming (crops) | 3 Livestock (animals) | 4 Casual or daily wage labour | 5 Construction work | 6 Own small shop, stall or trade | 7 Salaried job | 8 No paid work</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr"/>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>1 Yatra work (main occupation) | 2 Farming (crops) | 3 Livestock (animals) | 4 Casual or daily wage labour | 5 Construction work | 6 Own small shop, stall or trade | 7 Salaried job | 8 No paid work</t>
+          <t>1 Yatra work, or getting ready for the season | 2 Farming (crops) | 3 Livestock (animals) | 4 Casual or daily wage labour | 5 Construction work | 6 Own small shop, stall or trade | 7 Salaried job | 8 No paid work</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr"/>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>1 Yatra work (main occupation) | 2 Farming (crops) | 3 Livestock (animals) | 4 Casual or daily wage labour | 5 Construction work | 6 Own small shop, stall or trade | 7 Salaried job | 8 No paid work</t>
+          <t>1 Yatra work, or getting ready for the season | 2 Farming (crops) | 3 Livestock (animals) | 4 Casual or daily wage labour | 5 Construction work | 6 Own small shop, stall or trade | 7 Salaried job | 8 No paid work</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr"/>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>1 Yatra work (main occupation) | 2 Farming (crops) | 3 Livestock (animals) | 4 Casual or daily wage labour | 5 Construction work | 6 Own small shop, stall or trade | 7 Salaried job | 8 No paid work</t>
+          <t>1 Yatra work, or getting ready for the season | 2 Farming (crops) | 3 Livestock (animals) | 4 Casual or daily wage labour | 5 Construction work | 6 Own small shop, stall or trade | 7 Salaried job | 8 No paid work</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr"/>
@@ -2356,7 +2356,7 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>1 Yatra work (main occupation) | 2 Farming (crops) | 3 Livestock (animals) | 4 Casual or daily wage labour | 5 Construction work | 6 Own small shop, stall or trade | 7 Salaried job | 8 No paid work</t>
+          <t>1 Yatra work, or getting ready for the season | 2 Farming (crops) | 3 Livestock (animals) | 4 Casual or daily wage labour | 5 Construction work | 6 Own small shop, stall or trade | 7 Salaried job | 8 No paid work</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr"/>
@@ -2402,7 +2402,7 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>1 Yatra work (main occupation) | 2 Farming (crops) | 3 Livestock (animals) | 4 Casual or daily wage labour | 5 Construction work | 6 Own small shop, stall or trade | 7 Salaried job | 8 No paid work</t>
+          <t>1 Yatra work, or getting ready for the season | 2 Farming (crops) | 3 Livestock (animals) | 4 Casual or daily wage labour | 5 Construction work | 6 Own small shop, stall or trade | 7 Salaried job | 8 No paid work</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr"/>
@@ -2448,7 +2448,7 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>1 Yatra work (main occupation) | 2 Farming (crops) | 3 Livestock (animals) | 4 Casual or daily wage labour | 5 Construction work | 6 Own small shop, stall or trade | 7 Salaried job | 8 No paid work</t>
+          <t>1 Yatra work, or getting ready for the season | 2 Farming (crops) | 3 Livestock (animals) | 4 Casual or daily wage labour | 5 Construction work | 6 Own small shop, stall or trade | 7 Salaried job | 8 No paid work</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr"/>
@@ -2494,7 +2494,7 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>1 Yatra work (main occupation) | 2 Farming (crops) | 3 Livestock (animals) | 4 Casual or daily wage labour | 5 Construction work | 6 Own small shop, stall or trade | 7 Salaried job | 8 No paid work</t>
+          <t>1 Yatra work, or getting ready for the season | 2 Farming (crops) | 3 Livestock (animals) | 4 Casual or daily wage labour | 5 Construction work | 6 Own small shop, stall or trade | 7 Salaried job | 8 No paid work</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr"/>
@@ -2540,7 +2540,7 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>1 Yatra work (main occupation) | 2 Farming (crops) | 3 Livestock (animals) | 4 Casual or daily wage labour | 5 Construction work | 6 Own small shop, stall or trade | 7 Salaried job | 8 No paid work</t>
+          <t>1 Yatra work, or getting ready for the season | 2 Farming (crops) | 3 Livestock (animals) | 4 Casual or daily wage labour | 5 Construction work | 6 Own small shop, stall or trade | 7 Salaried job | 8 No paid work</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr"/>

--- a/replication/final_instrument/questionnaire/Question_register.xlsx
+++ b/replication/final_instrument/questionnaire/Question_register.xlsx
@@ -13,9 +13,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Modules" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Questions'!$A$1:$J$211</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Questions'!$A$1:$J$217</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Constructed variables'!$A$1:$F$130</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Literature'!$A$1:$C$129</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Literature'!$A$1:$C$135</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Modules'!$A$1:$C$15</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J211"/>
+  <dimension ref="A1:J217"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -5772,33 +5772,33 @@
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>electricity</t>
+          <t>accom_type_here</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>yes/no</t>
+          <t>select one</t>
         </is>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>Does your usual home have an electricity connection?</t>
+          <t>While you are here for the season, where do you sleep?</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>क्या आपके असली घर में बिजली का कनेक्शन है?</t>
+          <t>सीज़न में यहाँ रहते हुए आप कहाँ सोते हैं?</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>0 No | 1 Yes</t>
+          <t>1 Own house here | 2 Rented room or house | 3 Room or dormitory the employer provides | 4 Sleeps at the shop, dhaba or workplace | 5 Tent or temporary shelter | 6 Lodge, dharamshala or ashram | 7 In the open, or a verandah | 8 Somewhere else</t>
         </is>
       </c>
       <c r="I118" s="2" t="inlineStr"/>
       <c r="J118" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI</t>
+          <t>Lyons et al. 2023, Table 2 (area/settlement conditions), adapted to a labour-migrant setting</t>
         </is>
       </c>
     </row>
@@ -5818,33 +5818,33 @@
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>toilet_type</t>
+          <t>electricity</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>select one</t>
+          <t>yes/no</t>
         </is>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>What kind of toilet does your household use at your usual home?</t>
+          <t>Does your usual home have an electricity connection?</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>आपका घर अपने असली घर में किस तरह का शौचालय इस्तेमाल करता है?</t>
+          <t>क्या आपके असली घर में बिजली का कनेक्शन है?</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>1 No toilet / open defecation | 2 Pit latrine without slab or open pit | 3 Improved toilet, but shared with other households | 4 Improved toilet, used only by this household</t>
+          <t>0 No | 1 Yes</t>
         </is>
       </c>
       <c r="I119" s="2" t="inlineStr"/>
       <c r="J119" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI sanitation indicator (improved/unimproved and shared/not)</t>
+          <t>NITI Aayog National MPI</t>
         </is>
       </c>
     </row>
@@ -5864,7 +5864,7 @@
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>drinking_water</t>
+          <t>toilet_type</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
@@ -5874,23 +5874,23 @@
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>What is your main source of drinking water at your usual home?</t>
+          <t>What kind of toilet does your household use at your usual home?</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>आपके असली घर में पीने का पानी मुख्य रूप से कहाँ से आता है?</t>
+          <t>आपका घर अपने असली घर में किस तरह का शौचालय इस्तेमाल करता है?</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>1 Piped into the house or yard | 2 Public tap or standpipe | 3 Handpump, tubewell or borewell | 4 Protected well or protected spring | 5 Rainwater collection | 6 Bottled, packaged or community RO | 7 Unprotected well or unprotected spring | 8 River, stream, pond or canal | 9 Tanker truck or cart with drum</t>
+          <t>1 No toilet / open defecation | 2 Pit latrine without slab or open pit | 3 Improved toilet, but shared with other households | 4 Improved toilet, used only by this household</t>
         </is>
       </c>
       <c r="I120" s="2" t="inlineStr"/>
       <c r="J120" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI drinking-water indicator (JMP improved/unimproved taxonomy)</t>
+          <t>NITI Aayog National MPI sanitation indicator (improved/unimproved and shared/not)</t>
         </is>
       </c>
     </row>
@@ -5910,33 +5910,33 @@
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>water_on_premises</t>
+          <t>drinking_water</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>yes/no</t>
+          <t>select one</t>
         </is>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>Is the drinking water available at the house itself?</t>
+          <t>What is your main source of drinking water at your usual home?</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>क्या पीने का पानी घर पर ही मिल जाता है?</t>
+          <t>आपके असली घर में पीने का पानी मुख्य रूप से कहाँ से आता है?</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>0 No | 1 Yes</t>
+          <t>1 Piped into the house or yard | 2 Public tap or standpipe | 3 Handpump, tubewell or borewell | 4 Protected well or protected spring | 5 Rainwater collection | 6 Bottled, packaged or community RO | 7 Unprotected well or unprotected spring | 8 River, stream, pond or canal | 9 Tanker truck or cart with drum</t>
         </is>
       </c>
       <c r="I121" s="2" t="inlineStr"/>
       <c r="J121" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI drinking-water indicator (30-minute round-trip rule)</t>
+          <t>NITI Aayog National MPI drinking-water indicator (JMP improved/unimproved taxonomy)</t>
         </is>
       </c>
     </row>
@@ -5956,30 +5956,30 @@
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>water_fetch_minutes</t>
+          <t>water_on_premises</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>whole number</t>
+          <t>yes/no</t>
         </is>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>How long does it take to go there, get the water and come back? (minutes, round trip)</t>
+          <t>Is the drinking water available at the house itself?</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>वहाँ जाने, पानी भरने और लौटने में कुल कितना समय लगता है? (मिनट)</t>
-        </is>
-      </c>
-      <c r="H122" s="2" t="inlineStr"/>
-      <c r="I122" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if water_on_premises = 0</t>
-        </is>
-      </c>
+          <t>क्या पीने का पानी घर पर ही मिल जाता है?</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>0 No | 1 Yes</t>
+        </is>
+      </c>
+      <c r="I122" s="2" t="inlineStr"/>
       <c r="J122" s="2" t="inlineStr">
         <is>
           <t>NITI Aayog National MPI drinking-water indicator (30-minute round-trip rule)</t>
@@ -6002,29 +6002,25 @@
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>water_fetched_by</t>
+          <t>water_fetch_minutes</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>select one</t>
+          <t>whole number</t>
         </is>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>Who in the household usually goes to fetch it?</t>
+          <t>How long does it take to go there, get the water and come back? (minutes, round trip)</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>घर में आम तौर पर पानी कौन लाता है?</t>
-        </is>
-      </c>
-      <c r="H123" s="2" t="inlineStr">
-        <is>
-          <t>1 An adult woman | 2 An adult man | 3 A girl under 15 | 4 A boy under 15 | 5 It varies / more than one person</t>
-        </is>
-      </c>
+          <t>वहाँ जाने, पानी भरने और लौटने में कुल कितना समय लगता है? (मिनट)</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="inlineStr"/>
       <c r="I123" s="2" t="inlineStr">
         <is>
           <t>Ask only if water_on_premises = 0</t>
@@ -6032,7 +6028,7 @@
       </c>
       <c r="J123" s="2" t="inlineStr">
         <is>
-          <t>Project design (intra-household burden of water collection; DHS/NFHS ask the same item)</t>
+          <t>NITI Aayog National MPI drinking-water indicator (30-minute round-trip rule)</t>
         </is>
       </c>
     </row>
@@ -6052,7 +6048,7 @@
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>cooking_fuel</t>
+          <t>water_fetched_by</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
@@ -6062,23 +6058,27 @@
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>What does your household mainly use to cook at your usual home?</t>
+          <t>Who in the household usually goes to fetch it?</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>आपके असली घर में खाना मुख्य रूप से किस चीज़ पर बनता है?</t>
+          <t>घर में आम तौर पर पानी कौन लाता है?</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>1 LPG or cylinder gas | 2 Piped natural gas | 3 Electricity | 4 Biogas (gobar gas plant) | 5 Kerosene | 6 Firewood | 7 Dung cakes (gobar) | 8 Crop residue, straw or shrubs | 9 Charcoal | 10 Coal or lignite</t>
-        </is>
-      </c>
-      <c r="I124" s="2" t="inlineStr"/>
+          <t>1 An adult woman | 2 An adult man | 3 A girl under 15 | 4 A boy under 15 | 5 It varies / more than one person</t>
+        </is>
+      </c>
+      <c r="I124" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if water_on_premises = 0</t>
+        </is>
+      </c>
       <c r="J124" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI cooking-fuel indicator (its own list of dirty fuels)</t>
+          <t>Project design (intra-household burden of water collection; DHS/NFHS ask the same item)</t>
         </is>
       </c>
     </row>
@@ -6098,33 +6098,33 @@
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>owns_tv</t>
+          <t>cooking_fuel</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>yes/no</t>
+          <t>select one</t>
         </is>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>Does your household own: a television?</t>
+          <t>What does your household mainly use to cook at your usual home?</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>क्या आपके घर में टीवी है?</t>
+          <t>आपके असली घर में खाना मुख्य रूप से किस चीज़ पर बनता है?</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>0 No | 1 Yes</t>
+          <t>1 LPG or cylinder gas | 2 Piped natural gas | 3 Electricity | 4 Biogas (gobar gas plant) | 5 Kerosene | 6 Firewood | 7 Dung cakes (gobar) | 8 Crop residue, straw or shrubs | 9 Charcoal | 10 Coal or lignite</t>
         </is>
       </c>
       <c r="I125" s="2" t="inlineStr"/>
       <c r="J125" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI assets indicator</t>
+          <t>NITI Aayog National MPI cooking-fuel indicator (its own list of dirty fuels)</t>
         </is>
       </c>
     </row>
@@ -6144,7 +6144,7 @@
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>owns_radio</t>
+          <t>owns_tv</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
@@ -6154,12 +6154,12 @@
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>... a radio?</t>
+          <t>Does your household own: a television?</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>...रेडियो?</t>
+          <t>क्या आपके घर में टीवी है?</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr">
@@ -6190,7 +6190,7 @@
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>owns_bicycle</t>
+          <t>owns_radio</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
@@ -6200,12 +6200,12 @@
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>... a bicycle?</t>
+          <t>... a radio?</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>...साइकिल?</t>
+          <t>...रेडियो?</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>owns_motorcycle</t>
+          <t>owns_bicycle</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
@@ -6246,12 +6246,12 @@
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>... a motorcycle or scooter?</t>
+          <t>... a bicycle?</t>
         </is>
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>...मोटरसाइकिल या स्कूटर?</t>
+          <t>...साइकिल?</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr">
@@ -6282,7 +6282,7 @@
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>owns_car</t>
+          <t>owns_motorcycle</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
@@ -6292,12 +6292,12 @@
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>... a car, jeep or truck?</t>
+          <t>... a motorcycle or scooter?</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>...कार, जीप या ट्रक?</t>
+          <t>...मोटरसाइकिल या स्कूटर?</t>
         </is>
       </c>
       <c r="H129" s="2" t="inlineStr">
@@ -6308,7 +6308,7 @@
       <c r="I129" s="2" t="inlineStr"/>
       <c r="J129" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI assets indicator (car or truck limb)</t>
+          <t>NITI Aayog National MPI assets indicator</t>
         </is>
       </c>
     </row>
@@ -6328,7 +6328,7 @@
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>owns_phone</t>
+          <t>owns_car</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
@@ -6338,12 +6338,12 @@
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>... a telephone of any kind, mobile or landline?</t>
+          <t>... a car, jeep or truck?</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>...कोई फ़ोन, मोबाइल या लैंडलाइन?</t>
+          <t>...कार, जीप या ट्रक?</t>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr">
@@ -6354,7 +6354,7 @@
       <c r="I130" s="2" t="inlineStr"/>
       <c r="J130" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI assets indicator</t>
+          <t>NITI Aayog National MPI assets indicator (car or truck limb)</t>
         </is>
       </c>
     </row>
@@ -6374,7 +6374,7 @@
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>owns_computer</t>
+          <t>owns_phone</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
@@ -6384,12 +6384,12 @@
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t>... a computer or laptop?</t>
+          <t>... a telephone of any kind, mobile or landline?</t>
         </is>
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>...कंप्यूटर या लैपटॉप?</t>
+          <t>...कोई फ़ोन, मोबाइल या लैंडलाइन?</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr">
@@ -6420,7 +6420,7 @@
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>owns_animal_cart</t>
+          <t>owns_computer</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
@@ -6430,12 +6430,12 @@
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>... a cart pulled by an animal?</t>
+          <t>... a computer or laptop?</t>
         </is>
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>...जानवर से खींची जाने वाली गाड़ी?</t>
+          <t>...कंप्यूटर या लैपटॉप?</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>owns_fridge</t>
+          <t>owns_animal_cart</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>... a refrigerator?</t>
+          <t>... a cart pulled by an animal?</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>...फ़्रिज?</t>
+          <t>...जानवर से खींची जाने वाली गाड़ी?</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
@@ -6512,29 +6512,33 @@
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>land_cultivable_acres</t>
+          <t>owns_fridge</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>yes/no</t>
         </is>
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>How much CULTIVABLE land does your household own or cultivate, in acres? Do not count the land the house stands on. (0 if none)</t>
+          <t>... a refrigerator?</t>
         </is>
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>आपके घर के पास कितनी जोतने लायक़ ज़मीन है, अपनी या जोतने की, एकड़ में? जिस ज़मीन पर घर बना है उसे मत गिनिए। (न हो तो 0)</t>
-        </is>
-      </c>
-      <c r="H134" s="2" t="inlineStr"/>
+          <t>...फ़्रिज?</t>
+        </is>
+      </c>
+      <c r="H134" s="2" t="inlineStr">
+        <is>
+          <t>0 No | 1 Yes</t>
+        </is>
+      </c>
       <c r="I134" s="2" t="inlineStr"/>
       <c r="J134" s="2" t="inlineStr">
         <is>
-          <t>Chaudhuri et al. 2002 asset covariate</t>
+          <t>NITI Aayog National MPI assets indicator</t>
         </is>
       </c>
     </row>
@@ -6554,29 +6558,25 @@
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>owns_cow_buffalo</t>
+          <t>land_cultivable_acres</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>yes/no</t>
+          <t>number</t>
         </is>
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>Does your household own any cows or buffaloes?</t>
+          <t>How much CULTIVABLE land does your household own or cultivate, in acres? Do not count the land the house stands on. (0 if none)</t>
         </is>
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>क्या आपके घर में गाय या भैंस है?</t>
-        </is>
-      </c>
-      <c r="H135" s="2" t="inlineStr">
-        <is>
-          <t>0 No | 1 Yes</t>
-        </is>
-      </c>
+          <t>आपके घर के पास कितनी जोतने लायक़ ज़मीन है, अपनी या जोतने की, एकड़ में? जिस ज़मीन पर घर बना है उसे मत गिनिए। (न हो तो 0)</t>
+        </is>
+      </c>
+      <c r="H135" s="2" t="inlineStr"/>
       <c r="I135" s="2" t="inlineStr"/>
       <c r="J135" s="2" t="inlineStr">
         <is>
@@ -6600,7 +6600,7 @@
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>owns_goat_sheep</t>
+          <t>owns_cow_buffalo</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
@@ -6610,12 +6610,12 @@
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>Does your household own any goats or sheep?</t>
+          <t>Does your household own any cows or buffaloes?</t>
         </is>
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>क्या आपके घर में बकरी या भेड़ है?</t>
+          <t>क्या आपके घर में गाय या भैंस है?</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr">
@@ -6646,7 +6646,7 @@
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>owns_pony_mule</t>
+          <t>owns_goat_sheep</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>Does your household own any ponies or mules?</t>
+          <t>Does your household own any goats or sheep?</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>क्या आपके घर में घोड़ा या खच्चर है?</t>
+          <t>क्या आपके घर में बकरी या भेड़ है?</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr">
@@ -6672,7 +6672,7 @@
       <c r="I137" s="2" t="inlineStr"/>
       <c r="J137" s="2" t="inlineStr">
         <is>
-          <t>Project design (pilot livelihood survey)</t>
+          <t>Chaudhuri et al. 2002 asset covariate</t>
         </is>
       </c>
     </row>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>owns_shop_stall</t>
+          <t>owns_pony_mule</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>Does your household own a shop or stall that you use to earn?</t>
+          <t>Does your household own any ponies or mules?</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>क्या आपके घर की अपनी दुकान या खोखा है जिससे आप कमाते हैं?</t>
+          <t>क्या आपके घर में घोड़ा या खच्चर है?</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
@@ -6718,7 +6718,7 @@
       <c r="I138" s="2" t="inlineStr"/>
       <c r="J138" s="2" t="inlineStr">
         <is>
-          <t>Chaudhuri et al. 2002 asset covariate</t>
+          <t>Project design (pilot livelihood survey)</t>
         </is>
       </c>
     </row>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>owns_work_vehicle</t>
+          <t>owns_shop_stall</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
@@ -6748,12 +6748,12 @@
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>Does your household own a vehicle you use to earn (for example a jeep, truck or taxi)?</t>
+          <t>Does your household own a shop or stall that you use to earn?</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>क्या आपके घर की अपनी गाड़ी है जिससे आप कमाते हैं (जैसे जीप, ट्रक या टैक्सी)?</t>
+          <t>क्या आपके घर की अपनी दुकान या खोखा है जिससे आप कमाते हैं?</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">
@@ -6784,7 +6784,7 @@
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>owns_work_equipment</t>
+          <t>owns_work_vehicle</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
@@ -6794,12 +6794,12 @@
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>Does your household own equipment or tools that you use to earn?</t>
+          <t>Does your household own a vehicle you use to earn (for example a jeep, truck or taxi)?</t>
         </is>
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>क्या आपके घर के पास काम के औज़ार या मशीन है जिससे आप कमाते हैं?</t>
+          <t>क्या आपके घर की अपनी गाड़ी है जिससे आप कमाते हैं (जैसे जीप, ट्रक या टैक्सी)?</t>
         </is>
       </c>
       <c r="H140" s="2" t="inlineStr">
@@ -6830,33 +6830,33 @@
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>work_equipment_detail</t>
+          <t>owns_work_equipment</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>free text</t>
+          <t>yes/no</t>
         </is>
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t>What are they? Write what they say. Leave blank if they cannot say.</t>
+          <t>Does your household own equipment or tools that you use to earn?</t>
         </is>
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>वे क्या हैं? जैसा वे बताएँ वैसा लिख लीजिए। न बता पाएँ तो खाली छोड़ दीजिए।</t>
-        </is>
-      </c>
-      <c r="H141" s="2" t="inlineStr"/>
-      <c r="I141" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if owns_work_equipment = 1; may be left blank</t>
-        </is>
-      </c>
+          <t>क्या आपके घर के पास काम के औज़ार या मशीन है जिससे आप कमाते हैं?</t>
+        </is>
+      </c>
+      <c r="H141" s="2" t="inlineStr">
+        <is>
+          <t>0 No | 1 Yes</t>
+        </is>
+      </c>
+      <c r="I141" s="2" t="inlineStr"/>
       <c r="J141" s="2" t="inlineStr">
         <is>
-          <t>Standard household-survey item</t>
+          <t>Chaudhuri et al. 2002 asset covariate</t>
         </is>
       </c>
     </row>
@@ -6866,43 +6866,43 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>Finance, insurance and schemes</t>
+          <t>Housing, amenities and assets</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>has_bank_account</t>
+          <t>work_equipment_detail</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>yes/no</t>
+          <t>free text</t>
         </is>
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>Does anyone in your household have a bank account or a post office account?</t>
+          <t>What are they? Write what they say. Leave blank if they cannot say.</t>
         </is>
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>क्या आपके घर में किसी का बैंक खाता या डाकघर का खाता है?</t>
-        </is>
-      </c>
-      <c r="H142" s="2" t="inlineStr">
-        <is>
-          <t>0 No | 1 Yes</t>
-        </is>
-      </c>
-      <c r="I142" s="2" t="inlineStr"/>
+          <t>वे क्या हैं? जैसा वे बताएँ वैसा लिख लीजिए। न बता पाएँ तो खाली छोड़ दीजिए।</t>
+        </is>
+      </c>
+      <c r="H142" s="2" t="inlineStr"/>
+      <c r="I142" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if owns_work_equipment = 1; may be left blank</t>
+        </is>
+      </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI bank-account indicator; VEP adaptive-capacity covariate</t>
+          <t>Standard household-survey item</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>has_jandhan_account</t>
+          <t>has_bank_account</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
-          <t>Is any of these a Jan Dhan account?</t>
+          <t>Does anyone in your household have a bank account or a post office account?</t>
         </is>
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>क्या उनमें से कोई जन धन खाता है?</t>
+          <t>क्या आपके घर में किसी का बैंक खाता या डाकघर का खाता है?</t>
         </is>
       </c>
       <c r="H143" s="2" t="inlineStr">
@@ -6945,14 +6945,10 @@
           <t>0 No | 1 Yes</t>
         </is>
       </c>
-      <c r="I143" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if has_bank_account = 1</t>
-        </is>
-      </c>
+      <c r="I143" s="2" t="inlineStr"/>
       <c r="J143" s="2" t="inlineStr">
         <is>
-          <t>Standard household-survey item</t>
+          <t>NITI Aayog National MPI bank-account indicator; VEP adaptive-capacity covariate</t>
         </is>
       </c>
     </row>
@@ -6972,7 +6968,7 @@
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>took_loan_12m</t>
+          <t>has_jandhan_account</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
@@ -6982,12 +6978,12 @@
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>In the last 12 months, did you or anyone in your household borrow money?</t>
+          <t>Is any of these a Jan Dhan account?</t>
         </is>
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>पिछले 12 महीनों में क्या आपने या आपके घर के किसी सदस्य ने पैसा उधार लिया?</t>
+          <t>क्या उनमें से कोई जन धन खाता है?</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
@@ -6995,10 +6991,14 @@
           <t>0 No | 1 Yes</t>
         </is>
       </c>
-      <c r="I144" s="2" t="inlineStr"/>
+      <c r="I144" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if has_bank_account = 1</t>
+        </is>
+      </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>VEP adaptive-capacity covariate</t>
+          <t>Standard household-survey item</t>
         </is>
       </c>
     </row>
@@ -7018,37 +7018,33 @@
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>credit_source</t>
+          <t>took_loan_12m</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>select one</t>
+          <t>yes/no</t>
         </is>
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
-          <t>Who was the main lender?</t>
+          <t>In the last 12 months, did you or anyone in your household borrow money?</t>
         </is>
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>मुख्य रूप से किससे उधार लिया?</t>
+          <t>पिछले 12 महीनों में क्या आपने या आपके घर के किसी सदस्य ने पैसा उधार लिया?</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
-          <t>1 Nationalised or public-sector bank | 2 Private bank | 3 Cooperative bank or RRB | 4 Microfinance institution or SHG | 5 Moneylender | 6 Relative or friend | 7 Employer or contractor (advance) | 8 Other</t>
-        </is>
-      </c>
-      <c r="I145" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if took_loan_12m = 1</t>
-        </is>
-      </c>
+          <t>0 No | 1 Yes</t>
+        </is>
+      </c>
+      <c r="I145" s="2" t="inlineStr"/>
       <c r="J145" s="2" t="inlineStr">
         <is>
-          <t>VEP adaptive-capacity covariate (lender type)</t>
+          <t>VEP adaptive-capacity covariate</t>
         </is>
       </c>
     </row>
@@ -7068,25 +7064,29 @@
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>loan_amount</t>
+          <t>credit_source</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>amount (Rs)</t>
+          <t>select one</t>
         </is>
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t>How much of that loan is still left to repay? (Rs)</t>
+          <t>Who was the main lender?</t>
         </is>
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>उस क़र्ज़ में से अब भी कितना चुकाना बाक़ी है? (रुपये)</t>
-        </is>
-      </c>
-      <c r="H146" s="2" t="inlineStr"/>
+          <t>मुख्य रूप से किससे उधार लिया?</t>
+        </is>
+      </c>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>1 Nationalised or public-sector bank | 2 Private bank | 3 Cooperative bank or RRB | 4 Microfinance institution or SHG | 5 Moneylender | 6 Relative or friend | 7 Employer or contractor (advance) | 8 Other</t>
+        </is>
+      </c>
       <c r="I146" s="2" t="inlineStr">
         <is>
           <t>Ask only if took_loan_12m = 1</t>
@@ -7094,7 +7094,7 @@
       </c>
       <c r="J146" s="2" t="inlineStr">
         <is>
-          <t>Islam and Chowdhury 2025 (financial distress and household vulnerability to poverty)</t>
+          <t>VEP adaptive-capacity covariate (lender type)</t>
         </is>
       </c>
     </row>
@@ -7114,29 +7114,25 @@
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>pays_interest</t>
+          <t>loan_amount</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>yes/no</t>
+          <t>amount (Rs)</t>
         </is>
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
-          <t>Do you pay interest on it?</t>
+          <t>How much of that loan is still left to repay? (Rs)</t>
         </is>
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>क्या आप उस पर ब्याज देते हैं?</t>
-        </is>
-      </c>
-      <c r="H147" s="2" t="inlineStr">
-        <is>
-          <t>0 No | 1 Yes</t>
-        </is>
-      </c>
+          <t>उस क़र्ज़ में से अब भी कितना चुकाना बाक़ी है? (रुपये)</t>
+        </is>
+      </c>
+      <c r="H147" s="2" t="inlineStr"/>
       <c r="I147" s="2" t="inlineStr">
         <is>
           <t>Ask only if took_loan_12m = 1</t>
@@ -7144,7 +7140,7 @@
       </c>
       <c r="J147" s="2" t="inlineStr">
         <is>
-          <t>Project design (informal lending is often interest-free)</t>
+          <t>Islam and Chowdhury 2025 (financial distress and household vulnerability to poverty)</t>
         </is>
       </c>
     </row>
@@ -7164,33 +7160,37 @@
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>loan_interest_per100_pm</t>
+          <t>pays_interest</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>yes/no</t>
         </is>
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
-          <t>On every 100 rupees you borrowed, about how much interest do you pay in a month? (Rs; 0 if none, leave blank if not known)</t>
+          <t>Do you pay interest on it?</t>
         </is>
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>आपने जो 100 रुपये उधार लिए, उन पर महीने का कितना ब्याज देते हैं? (रुपये; दर पता न हो तो खाली छोड़ दें)</t>
-        </is>
-      </c>
-      <c r="H148" s="2" t="inlineStr"/>
+          <t>क्या आप उस पर ब्याज देते हैं?</t>
+        </is>
+      </c>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>0 No | 1 Yes</t>
+        </is>
+      </c>
       <c r="I148" s="2" t="inlineStr">
         <is>
-          <t>Ask only if took_loan_12m = 1; may be left blank</t>
+          <t>Ask only if took_loan_12m = 1</t>
         </is>
       </c>
       <c r="J148" s="2" t="inlineStr">
         <is>
-          <t>Project design (informal-credit pricing as locally quoted)</t>
+          <t>Project design (informal lending is often interest-free)</t>
         </is>
       </c>
     </row>
@@ -7210,37 +7210,33 @@
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>loan_against_asset</t>
+          <t>loan_interest_per100_pm</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>yes/no</t>
+          <t>number</t>
         </is>
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
-          <t>Did you have to give something as security for it -- an animal, a vehicle, jewellery, land or your business?</t>
+          <t>On every 100 rupees you borrowed, about how much interest do you pay in a month? (Rs; 0 if none, leave blank if not known)</t>
         </is>
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>क्या उसके बदले कुछ गिरवी रखना पड़ा — जानवर, गाड़ी, गहने, ज़मीन या आपका धंधा?</t>
-        </is>
-      </c>
-      <c r="H149" s="2" t="inlineStr">
-        <is>
-          <t>0 No | 1 Yes</t>
-        </is>
-      </c>
+          <t>आपने जो 100 रुपये उधार लिए, उन पर महीने का कितना ब्याज देते हैं? (रुपये; दर पता न हो तो खाली छोड़ दें)</t>
+        </is>
+      </c>
+      <c r="H149" s="2" t="inlineStr"/>
       <c r="I149" s="2" t="inlineStr">
         <is>
-          <t>Ask only if took_loan_12m = 1</t>
+          <t>Ask only if took_loan_12m = 1; may be left blank</t>
         </is>
       </c>
       <c r="J149" s="2" t="inlineStr">
         <is>
-          <t>Carter and Zimmerman 2000; Chiwaula et al. 2011 (asset-based vulnerability)</t>
+          <t>Project design (informal-credit pricing as locally quoted)</t>
         </is>
       </c>
     </row>
@@ -7260,37 +7256,37 @@
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>loan_collateral</t>
+          <t>loan_against_asset</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>select one</t>
+          <t>yes/no</t>
         </is>
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>What did you have to give as security?</t>
+          <t>Did you have to give something as security for it -- an animal, a vehicle, jewellery, land or your business?</t>
         </is>
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>आपको क्या गिरवी रखना पड़ा?</t>
+          <t>क्या उसके बदले कुछ गिरवी रखना पड़ा — जानवर, गाड़ी, गहने, ज़मीन या आपका धंधा?</t>
         </is>
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
-          <t>1 Jewellery or ornaments | 2 Land | 3 Animals | 4 A vehicle | 5 Shop stock or business goods | 6 House or building | 7 Something else</t>
+          <t>0 No | 1 Yes</t>
         </is>
       </c>
       <c r="I150" s="2" t="inlineStr">
         <is>
-          <t>Ask only if loan_against_asset = 1</t>
+          <t>Ask only if took_loan_12m = 1</t>
         </is>
       </c>
       <c r="J150" s="2" t="inlineStr">
         <is>
-          <t>Carter and Zimmerman 2000; Zimmerman and Carter 2003 (asset-based coping)</t>
+          <t>Carter and Zimmerman 2000; Chiwaula et al. 2011 (asset-based vulnerability)</t>
         </is>
       </c>
     </row>
@@ -7310,29 +7306,37 @@
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>n_health_insured</t>
+          <t>loan_collateral</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>whole number</t>
+          <t>select one</t>
         </is>
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
-          <t>How many people in your household are covered by any health insurance or health scheme, including government ones? (0 if none)</t>
+          <t>What did you have to give as security?</t>
         </is>
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>आपके घर में कितने लोगों का कोई स्वास्थ्य बीमा या स्वास्थ्य योजना है, सरकारी भी मिलाकर? (कोई नहीं तो 0)</t>
-        </is>
-      </c>
-      <c r="H151" s="2" t="inlineStr"/>
-      <c r="I151" s="2" t="inlineStr"/>
+          <t>आपको क्या गिरवी रखना पड़ा?</t>
+        </is>
+      </c>
+      <c r="H151" s="2" t="inlineStr">
+        <is>
+          <t>1 Jewellery or ornaments | 2 Land | 3 Animals | 4 A vehicle | 5 Shop stock or business goods | 6 House or building | 7 Something else</t>
+        </is>
+      </c>
+      <c r="I151" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if loan_against_asset = 1</t>
+        </is>
+      </c>
       <c r="J151" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI health-insurance indicator; Lyons et al. 2023</t>
+          <t>Carter and Zimmerman 2000; Zimmerman and Carter 2003 (asset-based coping)</t>
         </is>
       </c>
     </row>
@@ -7352,7 +7356,7 @@
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>n_life_insured</t>
+          <t>n_health_insured</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
@@ -7362,19 +7366,19 @@
       </c>
       <c r="F152" s="2" t="inlineStr">
         <is>
-          <t>How many people in your household have life insurance? (0 if none)</t>
+          <t>How many people in your household are covered by any health insurance or health scheme, including government ones? (0 if none)</t>
         </is>
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>आपके घर में कितने लोगों का जीवन बीमा है? (कोई नहीं तो 0)</t>
+          <t>आपके घर में कितने लोगों का कोई स्वास्थ्य बीमा या स्वास्थ्य योजना है, सरकारी भी मिलाकर? (कोई नहीं तो 0)</t>
         </is>
       </c>
       <c r="H152" s="2" t="inlineStr"/>
       <c r="I152" s="2" t="inlineStr"/>
       <c r="J152" s="2" t="inlineStr">
         <is>
-          <t>Standard household-survey item</t>
+          <t>NITI Aayog National MPI health-insurance indicator; Lyons et al. 2023</t>
         </is>
       </c>
     </row>
@@ -7394,34 +7398,26 @@
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>has_crop_insurance</t>
+          <t>n_life_insured</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>yes/no</t>
+          <t>whole number</t>
         </is>
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
-          <t>Is your crop insured?</t>
+          <t>How many people in your household have life insurance? (0 if none)</t>
         </is>
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>क्या आपकी फ़सल का बीमा है?</t>
-        </is>
-      </c>
-      <c r="H153" s="2" t="inlineStr">
-        <is>
-          <t>0 No | 1 Yes</t>
-        </is>
-      </c>
-      <c r="I153" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if land_cultivable_acres &gt; 0</t>
-        </is>
-      </c>
+          <t>आपके घर में कितने लोगों का जीवन बीमा है? (कोई नहीं तो 0)</t>
+        </is>
+      </c>
+      <c r="H153" s="2" t="inlineStr"/>
+      <c r="I153" s="2" t="inlineStr"/>
       <c r="J153" s="2" t="inlineStr">
         <is>
           <t>Standard household-survey item</t>
@@ -7444,33 +7440,37 @@
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>govt_schemes</t>
+          <t>has_crop_insurance</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>select multiple</t>
+          <t>yes/no</t>
         </is>
       </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
-          <t>In the last 12 months, did your household get anything from any of these? Read the list out and check every one they say yes to.</t>
+          <t>Is your crop insured?</t>
         </is>
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>पिछले 12 महीनों में इनमें से किसी से आपके घर को कुछ मिला? सूची पढ़कर सुनाइए और जिन-जिन पर वे हाँ कहें, सब पर निशान लगाइए।</t>
+          <t>क्या आपकी फ़सल का बीमा है?</t>
         </is>
       </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
-          <t>1 Ration card / PDS food grain | 2 MGNREGA work or job card | 3 Old-age, widow or disability pension | 4 PM-KISAN (farmer cash transfer) | 5 Ujjwala LPG connection | 6 PM-SYM or Atal Pension Yojana | 7 Ayushman Bharat / health insurance card | 8 Housing scheme (PMAY or state) | 9 Some other scheme | 10 None of these</t>
-        </is>
-      </c>
-      <c r="I154" s="2" t="inlineStr"/>
+          <t>0 No | 1 Yes</t>
+        </is>
+      </c>
+      <c r="I154" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if land_cultivable_acres &gt; 0</t>
+        </is>
+      </c>
       <c r="J154" s="2" t="inlineStr">
         <is>
-          <t>Project design; scheme names as administered in Uttarakhand</t>
+          <t>Standard household-survey item</t>
         </is>
       </c>
     </row>
@@ -7490,33 +7490,33 @@
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>govt_scheme_other</t>
+          <t>govt_schemes</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>free text</t>
+          <t>select multiple</t>
         </is>
       </c>
       <c r="F155" s="2" t="inlineStr">
         <is>
-          <t>Which scheme was that? Write what they say.</t>
+          <t>In the last 12 months, did your household get anything from any of these? Read the list out and check every one they say yes to.</t>
         </is>
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>वह कौन सी योजना थी? जैसा वे बताएँ वैसा लिख लीजिए।</t>
-        </is>
-      </c>
-      <c r="H155" s="2" t="inlineStr"/>
-      <c r="I155" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if govt_schemes includes 9 (Some other scheme); may be left blank</t>
-        </is>
-      </c>
+          <t>पिछले 12 महीनों में इनमें से किसी से आपके घर को कुछ मिला? सूची पढ़कर सुनाइए और जिन-जिन पर वे हाँ कहें, सब पर निशान लगाइए।</t>
+        </is>
+      </c>
+      <c r="H155" s="2" t="inlineStr">
+        <is>
+          <t>1 Ration card / PDS food grain | 2 MGNREGA work or job card | 3 Old-age, widow or disability pension | 4 PM-KISAN (farmer cash transfer) | 5 Ujjwala LPG connection | 6 PM-SYM or Atal Pension Yojana | 7 Ayushman Bharat / health insurance card | 8 Housing scheme (PMAY or state) | 9 Some other scheme | 10 None of these</t>
+        </is>
+      </c>
+      <c r="I155" s="2" t="inlineStr"/>
       <c r="J155" s="2" t="inlineStr">
         <is>
-          <t>Standard household-survey item</t>
+          <t>Project design; scheme names as administered in Uttarakhand</t>
         </is>
       </c>
     </row>
@@ -7536,33 +7536,33 @@
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>smartphone_owned</t>
+          <t>govt_scheme_other</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>yes/no</t>
+          <t>free text</t>
         </is>
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
-          <t>Do you own a smartphone?</t>
+          <t>Which scheme was that? Write what they say.</t>
         </is>
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>क्या आपके पास स्मार्टफ़ोन है?</t>
-        </is>
-      </c>
-      <c r="H156" s="2" t="inlineStr">
-        <is>
-          <t>0 No | 1 Yes</t>
-        </is>
-      </c>
-      <c r="I156" s="2" t="inlineStr"/>
+          <t>वह कौन सी योजना थी? जैसा वे बताएँ वैसा लिख लीजिए।</t>
+        </is>
+      </c>
+      <c r="H156" s="2" t="inlineStr"/>
+      <c r="I156" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if govt_schemes includes 9 (Some other scheme); may be left blank</t>
+        </is>
+      </c>
       <c r="J156" s="2" t="inlineStr">
         <is>
-          <t>VEP adaptive-capacity covariate; STEP digital items</t>
+          <t>Standard household-survey item</t>
         </is>
       </c>
     </row>
@@ -7582,33 +7582,37 @@
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>uses_digital_payment</t>
+          <t>ration_portable_here</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>yes/no</t>
+          <t>select one</t>
         </is>
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
-          <t>Do you ever use UPI or another way of paying by phone?</t>
+          <t>Can you draw your ration here, or only at your home place?</t>
         </is>
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>क्या आप कभी UPI या फ़ोन से पैसे का लेन-देन करते हैं?</t>
+          <t>क्या आप अपना राशन यहाँ ले सकते हैं, या सिर्फ़ अपने घर वाली जगह पर?</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
         <is>
-          <t>0 No | 1 Yes</t>
-        </is>
-      </c>
-      <c r="I157" s="2" t="inlineStr"/>
+          <t>1 Yes, can draw it here | 2 No, only at the home place | 3 Has never tried | 97 Does not know</t>
+        </is>
+      </c>
+      <c r="I157" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if govt_schemes includes 1 (ration card)</t>
+        </is>
+      </c>
       <c r="J157" s="2" t="inlineStr">
         <is>
-          <t>VEP adaptive-capacity covariate; STEP digital items</t>
+          <t>Lyons et al. 2023, Table 2 (legal residency), adapted; One Nation One Ration Card</t>
         </is>
       </c>
     </row>
@@ -7628,29 +7632,33 @@
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>n_can_transact_online</t>
+          <t>smartphone_owned</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>whole number</t>
+          <t>yes/no</t>
         </is>
       </c>
       <c r="F158" s="2" t="inlineStr">
         <is>
-          <t>How many people in your household can make a payment by phone themselves, without help? (0 if none)</t>
+          <t>Do you own a smartphone?</t>
         </is>
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>आपके घर में कितने लोग बिना किसी की मदद के फ़ोन से पैसे भेज सकते हैं? (कोई नहीं तो 0)</t>
-        </is>
-      </c>
-      <c r="H158" s="2" t="inlineStr"/>
+          <t>क्या आपके पास स्मार्टफ़ोन है?</t>
+        </is>
+      </c>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t>0 No | 1 Yes</t>
+        </is>
+      </c>
       <c r="I158" s="2" t="inlineStr"/>
       <c r="J158" s="2" t="inlineStr">
         <is>
-          <t>Project design (intra-household financial capability)</t>
+          <t>VEP adaptive-capacity covariate; STEP digital items</t>
         </is>
       </c>
     </row>
@@ -7660,17 +7668,17 @@
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Finance, insurance and schemes</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>morbidity_15d</t>
+          <t>uses_digital_payment</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
@@ -7680,12 +7688,12 @@
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
-          <t>In the last 15 days, was anyone in your household ill?</t>
+          <t>Do you ever use UPI or another way of paying by phone?</t>
         </is>
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>पिछले 15 दिनों में क्या आपके घर में कोई बीमार पड़ा?</t>
+          <t>क्या आप कभी UPI या फ़ोन से पैसे का लेन-देन करते हैं?</t>
         </is>
       </c>
       <c r="H159" s="2" t="inlineStr">
@@ -7696,7 +7704,7 @@
       <c r="I159" s="2" t="inlineStr"/>
       <c r="J159" s="2" t="inlineStr">
         <is>
-          <t>NSS health module (15-day recall) [source not held by this project; citation unverified as of 2026-09-28]</t>
+          <t>VEP adaptive-capacity covariate; STEP digital items</t>
         </is>
       </c>
     </row>
@@ -7706,47 +7714,39 @@
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Finance, insurance and schemes</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>morbidity_coping_15d</t>
+          <t>n_can_transact_online</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>select one</t>
+          <t>whole number</t>
         </is>
       </c>
       <c r="F160" s="2" t="inlineStr">
         <is>
-          <t>How did the household mainly cope with the cost of this: used savings; borrowed money; sold or pawned assets; cut other consumption; got help from relatives or community; or something else?</t>
+          <t>How many people in your household can make a payment by phone themselves, without help? (0 if none)</t>
         </is>
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>इसका ख़र्च आपके घर ने मुख्य रूप से कैसे उठाया: जमा पैसे से; उधार लेकर; कुछ बेचकर या गिरवी रखकर; बाकी ख़र्च घटाकर; रिश्तेदारों या गाँव वालों की मदद से; या किसी और तरह?</t>
-        </is>
-      </c>
-      <c r="H160" s="2" t="inlineStr">
-        <is>
-          <t>1 Used savings | 2 Borrowed money | 3 Sold or pawned assets | 4 Cut consumption | 5 Help from relatives/community | 6 Did nothing/other</t>
-        </is>
-      </c>
-      <c r="I160" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if morbidity_15d = 1</t>
-        </is>
-      </c>
+          <t>आपके घर में कितने लोग बिना किसी की मदद के फ़ोन से पैसे भेज सकते हैं? (कोई नहीं तो 0)</t>
+        </is>
+      </c>
+      <c r="H160" s="2" t="inlineStr"/>
+      <c r="I160" s="2" t="inlineStr"/>
       <c r="J160" s="2" t="inlineStr">
         <is>
-          <t>Project design (a reported illness with no cost/coping follow-up said nothing about its burden)</t>
+          <t>Project design (intra-household financial capability)</t>
         </is>
       </c>
     </row>
@@ -7766,33 +7766,33 @@
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>morbidity_cost_15d</t>
+          <t>morbidity_15d</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>amount (Rs)</t>
+          <t>yes/no</t>
         </is>
       </c>
       <c r="F161" s="2" t="inlineStr">
         <is>
-          <t>About how much did the household spend on this in the last 15 days (medicine, doctor or clinic fees, travel for care)? (Rs)</t>
+          <t>In the last 15 days, was anyone in your household ill?</t>
         </is>
       </c>
       <c r="G161" s="2" t="inlineStr">
         <is>
-          <t>पिछले 15 दिनों में इस पर घर का लगभग कितना ख़र्च हुआ (दवाई, डॉक्टर या क्लीनिक की फ़ीस, आने-जाने का ख़र्च)? (रुपये)</t>
-        </is>
-      </c>
-      <c r="H161" s="2" t="inlineStr"/>
-      <c r="I161" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if morbidity_15d = 1</t>
-        </is>
-      </c>
+          <t>पिछले 15 दिनों में क्या आपके घर में कोई बीमार पड़ा?</t>
+        </is>
+      </c>
+      <c r="H161" s="2" t="inlineStr">
+        <is>
+          <t>0 No | 1 Yes</t>
+        </is>
+      </c>
+      <c r="I161" s="2" t="inlineStr"/>
       <c r="J161" s="2" t="inlineStr">
         <is>
-          <t>Project design</t>
+          <t>NSS health module (15-day recall) [source not held by this project; citation unverified as of 2026-09-28]</t>
         </is>
       </c>
     </row>
@@ -7812,33 +7812,37 @@
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>hospitalization_365d</t>
+          <t>morbidity_coping_15d</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>yes/no</t>
+          <t>select one</t>
         </is>
       </c>
       <c r="F162" s="2" t="inlineStr">
         <is>
-          <t>In the last 12 months, was anyone in your household admitted to hospital overnight?</t>
+          <t>How did the household mainly cope with the cost of this: used savings; borrowed money; sold or pawned assets; cut other consumption; got help from relatives or community; or something else?</t>
         </is>
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>पिछले 12 महीनों में क्या आपके घर का कोई रात भर के लिए अस्पताल में भर्ती हुआ?</t>
+          <t>इसका ख़र्च आपके घर ने मुख्य रूप से कैसे उठाया: जमा पैसे से; उधार लेकर; कुछ बेचकर या गिरवी रखकर; बाकी ख़र्च घटाकर; रिश्तेदारों या गाँव वालों की मदद से; या किसी और तरह?</t>
         </is>
       </c>
       <c r="H162" s="2" t="inlineStr">
         <is>
-          <t>0 No | 1 Yes</t>
-        </is>
-      </c>
-      <c r="I162" s="2" t="inlineStr"/>
+          <t>1 Used savings | 2 Borrowed money | 3 Sold or pawned assets | 4 Cut consumption | 5 Help from relatives/community | 6 Did nothing/other</t>
+        </is>
+      </c>
+      <c r="I162" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if morbidity_15d = 1</t>
+        </is>
+      </c>
       <c r="J162" s="2" t="inlineStr">
         <is>
-          <t>NSS health module (365-day recall) [source not held by this project; citation unverified as of 2026-09-28]</t>
+          <t>Project design (a reported illness with no cost/coping follow-up said nothing about its burden)</t>
         </is>
       </c>
     </row>
@@ -7858,33 +7862,33 @@
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>health_access_barrier_3m</t>
+          <t>morbidity_cost_15d</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>yes/no</t>
+          <t>amount (Rs)</t>
         </is>
       </c>
       <c r="F163" s="2" t="inlineStr">
         <is>
-          <t>In the last 3 months, was there a time when someone in your household needed medical care but could not get it?</t>
+          <t>About how much did the household spend on this in the last 15 days (medicine, doctor or clinic fees, travel for care)? (Rs)</t>
         </is>
       </c>
       <c r="G163" s="2" t="inlineStr">
         <is>
-          <t>पिछले 3 महीनों में क्या कभी ऐसा हुआ कि आपके घर में किसी को इलाज की ज़रूरत थी पर मिल नहीं पाया?</t>
-        </is>
-      </c>
-      <c r="H163" s="2" t="inlineStr">
-        <is>
-          <t>0 No | 1 Yes</t>
-        </is>
-      </c>
-      <c r="I163" s="2" t="inlineStr"/>
+          <t>पिछले 15 दिनों में इस पर घर का लगभग कितना ख़र्च हुआ (दवाई, डॉक्टर या क्लीनिक की फ़ीस, आने-जाने का ख़र्च)? (रुपये)</t>
+        </is>
+      </c>
+      <c r="H163" s="2" t="inlineStr"/>
+      <c r="I163" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if morbidity_15d = 1</t>
+        </is>
+      </c>
       <c r="J163" s="2" t="inlineStr">
         <is>
-          <t>VASyR 2025 barriers_health_case_access_phc_m (primary-care access barriers); Lyons et al. 2023 Table 2 indicator 2 'healthcare access'</t>
+          <t>Project design</t>
         </is>
       </c>
     </row>
@@ -7904,33 +7908,33 @@
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>child_death_5y</t>
+          <t>func_limitation</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>yes/no</t>
+          <t>select one</t>
         </is>
       </c>
       <c r="F164" s="2" t="inlineStr">
         <is>
-          <t>In the last five years, has any child or young person under 18 in your household died?</t>
+          <t>Do you have difficulty walking or climbing steps?</t>
         </is>
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>पिछले पाँच साल में क्या आपके घर के 18 साल से छोटे किसी बच्चे या किशोर की मृत्यु हुई?</t>
+          <t>क्या आपको चलने या सीढ़ियाँ चढ़ने में दिक़्क़त होती है?</t>
         </is>
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
-          <t>0 No | 1 Yes</t>
+          <t>1 No difficulty | 2 Some difficulty | 3 A lot of difficulty | 4 Cannot do it at all</t>
         </is>
       </c>
       <c r="I164" s="2" t="inlineStr"/>
       <c r="J164" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI, Child and Adolescent Mortality (weight 1/12)</t>
+          <t>Washington Group on Disability Statistics, Short Set item 3 (mobility), verbatim; Lyons et al. 2023 health dimension</t>
         </is>
       </c>
     </row>
@@ -7950,7 +7954,7 @@
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t>birth_last_5y</t>
+          <t>hospitalization_365d</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr">
@@ -7960,12 +7964,12 @@
       </c>
       <c r="F165" s="2" t="inlineStr">
         <is>
-          <t>In the last five years, did any woman in your household give birth?</t>
+          <t>In the last 12 months, was anyone in your household admitted to hospital overnight?</t>
         </is>
       </c>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>पिछले पाँच साल में क्या आपके घर की किसी महिला ने बच्चे को जन्म दिया?</t>
+          <t>पिछले 12 महीनों में क्या आपके घर का कोई रात भर के लिए अस्पताल में भर्ती हुआ?</t>
         </is>
       </c>
       <c r="H165" s="2" t="inlineStr">
@@ -7976,7 +7980,7 @@
       <c r="I165" s="2" t="inlineStr"/>
       <c r="J165" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI, Maternal Health (weight 1/12)</t>
+          <t>NSS health module (365-day recall) [source not held by this project; citation unverified as of 2026-09-28]</t>
         </is>
       </c>
     </row>
@@ -7996,37 +8000,33 @@
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>anc_4_visits</t>
+          <t>health_access_barrier_3m</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>select one</t>
+          <t>yes/no</t>
         </is>
       </c>
       <c r="F166" s="2" t="inlineStr">
         <is>
-          <t>For the most recent birth, did she have at least four check-ups before the delivery?</t>
+          <t>In the last 3 months, was there a time when someone in your household needed medical care but could not get it?</t>
         </is>
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>सबसे हाल के जन्म के लिए, क्या डिलीवरी से पहले उनकी कम से कम चार बार जाँच हुई थी?</t>
+          <t>पिछले 3 महीनों में क्या कभी ऐसा हुआ कि आपके घर में किसी को इलाज की ज़रूरत थी पर मिल नहीं पाया?</t>
         </is>
       </c>
       <c r="H166" s="2" t="inlineStr">
         <is>
-          <t>0 No | 1 Yes | 97 Don't know</t>
-        </is>
-      </c>
-      <c r="I166" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if birth_last_5y = 1</t>
-        </is>
-      </c>
+          <t>0 No | 1 Yes</t>
+        </is>
+      </c>
+      <c r="I166" s="2" t="inlineStr"/>
       <c r="J166" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI, Maternal Health (antenatal care limb)</t>
+          <t>VASyR 2025 barriers_health_case_access_phc_m (primary-care access barriers); Lyons et al. 2023 Table 2 indicator 2 'healthcare access'</t>
         </is>
       </c>
     </row>
@@ -8046,37 +8046,33 @@
       </c>
       <c r="D167" s="2" t="inlineStr">
         <is>
-          <t>skilled_birth_attendant</t>
+          <t>child_death_5y</t>
         </is>
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>select one</t>
+          <t>yes/no</t>
         </is>
       </c>
       <c r="F167" s="2" t="inlineStr">
         <is>
-          <t>Was that delivery done with the help of a doctor, nurse or trained midwife?</t>
+          <t>In the last five years, has any child or young person under 18 in your household died?</t>
         </is>
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>क्या वह डिलीवरी डॉक्टर, नर्स या प्रशिक्षित दाई की मदद से हुई थी?</t>
+          <t>पिछले पाँच साल में क्या आपके घर के 18 साल से छोटे किसी बच्चे या किशोर की मृत्यु हुई?</t>
         </is>
       </c>
       <c r="H167" s="2" t="inlineStr">
         <is>
-          <t>0 No | 1 Yes | 97 Don't know</t>
-        </is>
-      </c>
-      <c r="I167" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if birth_last_5y = 1</t>
-        </is>
-      </c>
+          <t>0 No | 1 Yes</t>
+        </is>
+      </c>
+      <c r="I167" s="2" t="inlineStr"/>
       <c r="J167" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI, Maternal Health (assisted delivery limb)</t>
+          <t>NITI Aayog National MPI, Child and Adolescent Mortality (weight 1/12)</t>
         </is>
       </c>
     </row>
@@ -8086,43 +8082,43 @@
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>Food security, shocks and coping</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>distress_event_last365d</t>
+          <t>birth_last_5y</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>select multiple</t>
+          <t>yes/no</t>
         </is>
       </c>
       <c r="F168" s="2" t="inlineStr">
         <is>
-          <t>In the last 12 months, did any of these happen -- to your household, or to the Yatra route you work on? Check every one that applies.</t>
+          <t>In the last five years, did any woman in your household give birth?</t>
         </is>
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>पिछले 12 महीनों में इनमें से क्या-क्या हुआ — आपके घर के साथ, या जिस यात्रा मार्ग पर आप काम करते हैं उस पर? जो-जो हुआ, सब चुनिए।</t>
+          <t>पिछले पाँच साल में क्या आपके घर की किसी महिला ने बच्चे को जन्म दिया?</t>
         </is>
       </c>
       <c r="H168" s="2" t="inlineStr">
         <is>
-          <t>1 Serious illness or death of an earning member | 2 Crop failure or livestock loss | 3 Damage from a natural disaster (flood, landslide, fire) | 4 Loss of business, goods or assets | 5 Road or bridge blocked, route closed | 6 Yatra stopped early or badly disrupted | 7 Sharp fall in customers or prices | 8 Lost the work or the work stopped</t>
+          <t>0 No | 1 Yes</t>
         </is>
       </c>
       <c r="I168" s="2" t="inlineStr"/>
       <c r="J168" s="2" t="inlineStr">
         <is>
-          <t>VEP exposure covariate (Azeem et al. 2016); shock inventory following Gunther and Harttgen 2009, via Fujii 2016 section 4</t>
+          <t>NITI Aayog National MPI, Maternal Health (weight 1/12)</t>
         </is>
       </c>
     </row>
@@ -8132,47 +8128,47 @@
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t>Food security, shocks and coping</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t>shock_coping</t>
+          <t>anc_4_visits</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>select multiple</t>
+          <t>select one</t>
         </is>
       </c>
       <c r="F169" s="2" t="inlineStr">
         <is>
-          <t>How did your household manage? Check every one they used.</t>
+          <t>For the most recent birth, did she have at least four check-ups before the delivery?</t>
         </is>
       </c>
       <c r="G169" s="2" t="inlineStr">
         <is>
-          <t>आपके घर ने कैसे सँभाला? उन्होंने जो-जो किया, सब चुनिए।</t>
+          <t>सबसे हाल के जन्म के लिए, क्या डिलीवरी से पहले उनकी कम से कम चार बार जाँच हुई थी?</t>
         </is>
       </c>
       <c r="H169" s="2" t="inlineStr">
         <is>
-          <t>1 Used savings | 2 Borrowed money | 3 Sold or pawned assets | 4 Cut consumption | 5 Help from relatives/community | 6 Did nothing/other</t>
+          <t>0 No | 1 Yes | 97 Don't know</t>
         </is>
       </c>
       <c r="I169" s="2" t="inlineStr">
         <is>
-          <t>Ask only if any shock was reported</t>
+          <t>Ask only if birth_last_5y = 1</t>
         </is>
       </c>
       <c r="J169" s="2" t="inlineStr">
         <is>
-          <t>Coping strategies in VEP studies; Carter and Zimmerman 2000 on asset versus consumption smoothing</t>
+          <t>NITI Aayog National MPI, Maternal Health (antenatal care limb)</t>
         </is>
       </c>
     </row>
@@ -8182,39 +8178,47 @@
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>Food security, shocks and coping</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>cope_less_pref_food_yatra_wk</t>
+          <t>skilled_birth_attendant</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>whole number</t>
+          <t>select one</t>
         </is>
       </c>
       <c r="F170" s="2" t="inlineStr">
         <is>
-          <t>In a normal week during the Yatra season, to cope with a lack of food or money to buy it, how many days did your household rely on less expensive/less preferred food? (0-7 days)</t>
+          <t>Was that delivery done with the help of a doctor, nurse or trained midwife?</t>
         </is>
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम हफ़्ते में, खाने की या खाना ख़रीदने के पैसे की कमी से निपटने के लिए आपके घर ने कितने दिन सस्ता या कम पसंद का खाना खाया? (0-7 दिन)</t>
-        </is>
-      </c>
-      <c r="H170" s="2" t="inlineStr"/>
-      <c r="I170" s="2" t="inlineStr"/>
+          <t>क्या वह डिलीवरी डॉक्टर, नर्स या प्रशिक्षित दाई की मदद से हुई थी?</t>
+        </is>
+      </c>
+      <c r="H170" s="2" t="inlineStr">
+        <is>
+          <t>0 No | 1 Yes | 97 Don't know</t>
+        </is>
+      </c>
+      <c r="I170" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if birth_last_5y = 1</t>
+        </is>
+      </c>
       <c r="J170" s="2" t="inlineStr">
         <is>
-          <t>VASyR 2025 (exact item wording); WFP rCSI; The reduced Coping Strategy Index (rCSI): five food-coping questions, standard WFP weights (1, 2, 1, 1, 3) applied when the index is built. The Kedarnath instrument otherwise has no food-security module, which is a gap for a poverty-vulnerability survey; these five short questions close it at low cost instead of a full dietary-diversity module, left out to stay inside the 45-minute limit. Kept as day-counts (0-7), not collapsed to yes/no: this is the standard, validated WFP/FAO specification (frequency x severity), and no comparably-standard binary version was found on checking; a day-count also takes about as long to answer as a yes/no in practice, so little interview time is saved by simplifying it.</t>
+          <t>NITI Aayog National MPI, Maternal Health (assisted delivery limb)</t>
         </is>
       </c>
     </row>
@@ -8234,29 +8238,33 @@
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t>cope_less_pref_food_offseason_wk</t>
+          <t>distress_event_last365d</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
-          <t>whole number</t>
+          <t>select multiple</t>
         </is>
       </c>
       <c r="F171" s="2" t="inlineStr">
         <is>
-          <t>In a normal week when the Yatra is closed, to cope with a lack of food or money to buy it, how many days did your household rely on less expensive/less preferred food? (0-7 days)</t>
+          <t>In the last 12 months, did any of these happen -- to your household, or to the Yatra route you work on? Check every one that applies.</t>
         </is>
       </c>
       <c r="G171" s="2" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम हफ़्ते में आपके घर ने कितने दिन सस्ता या कम पसंद का खाना खाया? (0-7 दिन)</t>
-        </is>
-      </c>
-      <c r="H171" s="2" t="inlineStr"/>
+          <t>पिछले 12 महीनों में इनमें से क्या-क्या हुआ — आपके घर के साथ, या जिस यात्रा मार्ग पर आप काम करते हैं उस पर? जो-जो हुआ, सब चुनिए।</t>
+        </is>
+      </c>
+      <c r="H171" s="2" t="inlineStr">
+        <is>
+          <t>1 Serious illness or death of an earning member | 2 Crop failure or livestock loss | 3 Damage from a natural disaster (flood, landslide, fire) | 4 Loss of business, goods or assets | 5 Road or bridge blocked, route closed | 6 Yatra stopped early or badly disrupted | 7 Sharp fall in customers or prices | 8 Lost the work or the work stopped</t>
+        </is>
+      </c>
       <c r="I171" s="2" t="inlineStr"/>
       <c r="J171" s="2" t="inlineStr">
         <is>
-          <t>VASyR 2025 (exact item wording); WFP rCSI; The reduced Coping Strategy Index (rCSI): five food-coping questions, standard WFP weights (1, 2, 1, 1, 3) applied when the index is built. The Kedarnath instrument otherwise has no food-security module, which is a gap for a poverty-vulnerability survey; these five short questions close it at low cost instead of a full dietary-diversity module, left out to stay inside the 45-minute limit. Kept as day-counts (0-7), not collapsed to yes/no: this is the standard, validated WFP/FAO specification (frequency x severity), and no comparably-standard binary version was found on checking; a day-count also takes about as long to answer as a yes/no in practice, so little interview time is saved by simplifying it.</t>
+          <t>VEP exposure covariate (Azeem et al. 2016); shock inventory following Gunther and Harttgen 2009, via Fujii 2016 section 4</t>
         </is>
       </c>
     </row>
@@ -8276,29 +8284,37 @@
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>cope_borrow_food_yatra_wk</t>
+          <t>shock_worst</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>whole number</t>
+          <t>select one</t>
         </is>
       </c>
       <c r="F172" s="2" t="inlineStr">
         <is>
-          <t>In a normal week during the Yatra season, to cope with a lack of food or money to buy it, how many days did your household borrow food and/or rely on help from friends/relatives? (0-7 days)</t>
+          <t>Of those, which one was hardest for your household?</t>
         </is>
       </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम हफ़्ते में, खाने की या खाना ख़रीदने के पैसे की कमी से निपटने के लिए आपके घर ने कितने दिन खाना उधार लिया या दोस्तों/रिश्तेदारों की मदद ली? (0-7 दिन)</t>
-        </is>
-      </c>
-      <c r="H172" s="2" t="inlineStr"/>
-      <c r="I172" s="2" t="inlineStr"/>
+          <t>इनमें से आपके घर के लिए सबसे मुश्किल कौन सा रहा?</t>
+        </is>
+      </c>
+      <c r="H172" s="2" t="inlineStr">
+        <is>
+          <t>1 Serious illness or death of an earning member | 2 Crop failure or livestock loss | 3 Damage from a natural disaster (flood, landslide, fire) | 4 Loss of business, goods or assets | 5 Road or bridge blocked, route closed | 6 Yatra stopped early or badly disrupted | 7 Sharp fall in customers or prices | 8 Lost the work or the work stopped</t>
+        </is>
+      </c>
+      <c r="I172" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if distress_event_last365d is not empty</t>
+        </is>
+      </c>
       <c r="J172" s="2" t="inlineStr">
         <is>
-          <t>VASyR 2025 (exact item wording); WFP rCSI; The reduced Coping Strategy Index (rCSI): five food-coping questions, standard WFP weights (1, 2, 1, 1, 3) applied when the index is built. The Kedarnath instrument otherwise has no food-security module, which is a gap for a poverty-vulnerability survey; these five short questions close it at low cost instead of a full dietary-diversity module, left out to stay inside the 45-minute limit. Kept as day-counts (0-7), not collapsed to yes/no: this is the standard, validated WFP/FAO specification (frequency x severity), and no comparably-standard binary version was found on checking; a day-count also takes about as long to answer as a yes/no in practice, so little interview time is saved by simplifying it.</t>
+          <t>Project design (anchors the magnitude and timing pair)</t>
         </is>
       </c>
     </row>
@@ -8318,29 +8334,33 @@
       </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t>cope_borrow_food_offseason_wk</t>
+          <t>shock_loss_amount</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr">
         <is>
-          <t>whole number</t>
+          <t>amount (Rs)</t>
         </is>
       </c>
       <c r="F173" s="2" t="inlineStr">
         <is>
-          <t>In a normal week when the Yatra is closed, to cope with a lack of food or money to buy it, how many days did your household borrow food and/or rely on help from friends/relatives? (0-7 days)</t>
+          <t>Because of that, about how much did your household lose in earnings, or have to spend? (Rs)</t>
         </is>
       </c>
       <c r="G173" s="2" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम हफ़्ते में आपके घर ने कितने दिन खाना उधार लिया या दोस्तों/रिश्तेदारों की मदद ली? (0-7 दिन)</t>
+          <t>उसकी वजह से आपके घर की कितनी कमाई गई, या कितना ख़र्च करना पड़ा? (रुपये)</t>
         </is>
       </c>
       <c r="H173" s="2" t="inlineStr"/>
-      <c r="I173" s="2" t="inlineStr"/>
+      <c r="I173" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if distress_event_last365d is not empty</t>
+        </is>
+      </c>
       <c r="J173" s="2" t="inlineStr">
         <is>
-          <t>VASyR 2025 (exact item wording); WFP rCSI; The reduced Coping Strategy Index (rCSI): five food-coping questions, standard WFP weights (1, 2, 1, 1, 3) applied when the index is built. The Kedarnath instrument otherwise has no food-security module, which is a gap for a poverty-vulnerability survey; these five short questions close it at low cost instead of a full dietary-diversity module, left out to stay inside the 45-minute limit. Kept as day-counts (0-7), not collapsed to yes/no: this is the standard, validated WFP/FAO specification (frequency x severity), and no comparably-standard binary version was found on checking; a day-count also takes about as long to answer as a yes/no in practice, so little interview time is saved by simplifying it.</t>
+          <t>Ligon and Schechter 2003; Dercon and Krishnan 2000 (VER needs shock magnitude, not only incidence)</t>
         </is>
       </c>
     </row>
@@ -8360,29 +8380,37 @@
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>cope_reduce_meals_yatra_wk</t>
+          <t>shock_month</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>whole number</t>
+          <t>select one</t>
         </is>
       </c>
       <c r="F174" s="2" t="inlineStr">
         <is>
-          <t>In a normal week during the Yatra season, to cope with a lack of food or money to buy it, how many days did your household reduce the number of meals eaten per day? (0-7 days)</t>
+          <t>In which month did that happen?</t>
         </is>
       </c>
       <c r="G174" s="2" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम हफ़्ते में, खाने की या खाना ख़रीदने के पैसे की कमी से निपटने के लिए आपके घर ने कितने दिन दिन में कम बार खाना खाया? (0-7 दिन)</t>
-        </is>
-      </c>
-      <c r="H174" s="2" t="inlineStr"/>
-      <c r="I174" s="2" t="inlineStr"/>
+          <t>वह किस महीने हुआ था?</t>
+        </is>
+      </c>
+      <c r="H174" s="2" t="inlineStr">
+        <is>
+          <t>1 January | 2 February | 3 March | 4 April | 5 May | 6 June | 7 July | 8 August | 9 September | 10 October | 11 November | 12 December</t>
+        </is>
+      </c>
+      <c r="I174" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if distress_event_last365d is not empty</t>
+        </is>
+      </c>
       <c r="J174" s="2" t="inlineStr">
         <is>
-          <t>VASyR 2025 (exact item wording); WFP rCSI; The reduced Coping Strategy Index (rCSI): five food-coping questions, standard WFP weights (1, 2, 1, 1, 3) applied when the index is built. The Kedarnath instrument otherwise has no food-security module, which is a gap for a poverty-vulnerability survey; these five short questions close it at low cost instead of a full dietary-diversity module, left out to stay inside the 45-minute limit. Kept as day-counts (0-7), not collapsed to yes/no: this is the standard, validated WFP/FAO specification (frequency x severity), and no comparably-standard binary version was found on checking; a day-count also takes about as long to answer as a yes/no in practice, so little interview time is saved by simplifying it.</t>
+          <t>Dercon and Krishnan 2000 (seasonal timing of shocks); project design</t>
         </is>
       </c>
     </row>
@@ -8402,29 +8430,37 @@
       </c>
       <c r="D175" s="2" t="inlineStr">
         <is>
-          <t>cope_reduce_meals_offseason_wk</t>
+          <t>shock_coping</t>
         </is>
       </c>
       <c r="E175" s="2" t="inlineStr">
         <is>
-          <t>whole number</t>
+          <t>select multiple</t>
         </is>
       </c>
       <c r="F175" s="2" t="inlineStr">
         <is>
-          <t>In a normal week when the Yatra is closed, to cope with a lack of food or money to buy it, how many days did your household reduce the number of meals eaten per day? (0-7 days)</t>
+          <t>How did your household manage? Check every one they used.</t>
         </is>
       </c>
       <c r="G175" s="2" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम हफ़्ते में आपके घर ने कितने दिन दिन में कम बार खाना खाया? (0-7 दिन)</t>
-        </is>
-      </c>
-      <c r="H175" s="2" t="inlineStr"/>
-      <c r="I175" s="2" t="inlineStr"/>
+          <t>आपके घर ने कैसे सँभाला? उन्होंने जो-जो किया, सब चुनिए।</t>
+        </is>
+      </c>
+      <c r="H175" s="2" t="inlineStr">
+        <is>
+          <t>1 Used savings | 2 Borrowed money | 3 Sold or pawned assets | 4 Cut consumption | 5 Help from relatives/community | 6 Did nothing/other</t>
+        </is>
+      </c>
+      <c r="I175" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if any shock was reported</t>
+        </is>
+      </c>
       <c r="J175" s="2" t="inlineStr">
         <is>
-          <t>VASyR 2025 (exact item wording); WFP rCSI; The reduced Coping Strategy Index (rCSI): five food-coping questions, standard WFP weights (1, 2, 1, 1, 3) applied when the index is built. The Kedarnath instrument otherwise has no food-security module, which is a gap for a poverty-vulnerability survey; these five short questions close it at low cost instead of a full dietary-diversity module, left out to stay inside the 45-minute limit. Kept as day-counts (0-7), not collapsed to yes/no: this is the standard, validated WFP/FAO specification (frequency x severity), and no comparably-standard binary version was found on checking; a day-count also takes about as long to answer as a yes/no in practice, so little interview time is saved by simplifying it.</t>
+          <t>Coping strategies in VEP studies; Carter and Zimmerman 2000 on asset versus consumption smoothing</t>
         </is>
       </c>
     </row>
@@ -8444,7 +8480,7 @@
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>cope_reduce_portion_yatra_wk</t>
+          <t>cope_less_pref_food_yatra_wk</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr">
@@ -8454,12 +8490,12 @@
       </c>
       <c r="F176" s="2" t="inlineStr">
         <is>
-          <t>In a normal week during the Yatra season, to cope with a lack of food or money to buy it, how many days did your household reduce portion size of meals? (0-7 days)</t>
+          <t>In a normal week during the Yatra season, to cope with a lack of food or money to buy it, how many days did your household rely on less expensive/less preferred food? (0-7 days)</t>
         </is>
       </c>
       <c r="G176" s="2" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम हफ़्ते में, खाने की या खाना ख़रीदने के पैसे की कमी से निपटने के लिए आपके घर ने कितने दिन खाने की मात्रा घटाई? (0-7 दिन)</t>
+          <t>यात्रा के मौसम के आम हफ़्ते में, खाने की या खाना ख़रीदने के पैसे की कमी से निपटने के लिए आपके घर ने कितने दिन सस्ता या कम पसंद का खाना खाया? (0-7 दिन)</t>
         </is>
       </c>
       <c r="H176" s="2" t="inlineStr"/>
@@ -8486,7 +8522,7 @@
       </c>
       <c r="D177" s="2" t="inlineStr">
         <is>
-          <t>cope_reduce_portion_offseason_wk</t>
+          <t>cope_less_pref_food_offseason_wk</t>
         </is>
       </c>
       <c r="E177" s="2" t="inlineStr">
@@ -8496,12 +8532,12 @@
       </c>
       <c r="F177" s="2" t="inlineStr">
         <is>
-          <t>In a normal week when the Yatra is closed, to cope with a lack of food or money to buy it, how many days did your household reduce portion size of meals? (0-7 days)</t>
+          <t>In a normal week when the Yatra is closed, to cope with a lack of food or money to buy it, how many days did your household rely on less expensive/less preferred food? (0-7 days)</t>
         </is>
       </c>
       <c r="G177" s="2" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम हफ़्ते में आपके घर ने कितने दिन खाने की मात्रा घटाई? (0-7 दिन)</t>
+          <t>जब यात्रा बंद रहती है, उस आम हफ़्ते में आपके घर ने कितने दिन सस्ता या कम पसंद का खाना खाया? (0-7 दिन)</t>
         </is>
       </c>
       <c r="H177" s="2" t="inlineStr"/>
@@ -8528,7 +8564,7 @@
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>cope_restrict_adult_yatra_wk</t>
+          <t>cope_borrow_food_yatra_wk</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr">
@@ -8538,12 +8574,12 @@
       </c>
       <c r="F178" s="2" t="inlineStr">
         <is>
-          <t>In a normal week during the Yatra season, to cope with a lack of food or money to buy it, how many days did your household restrict consumption of adults/mothers in order for young children to eat? (0-7 days)</t>
+          <t>In a normal week during the Yatra season, to cope with a lack of food or money to buy it, how many days did your household borrow food and/or rely on help from friends/relatives? (0-7 days)</t>
         </is>
       </c>
       <c r="G178" s="2" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम हफ़्ते में, खाने की या खाना ख़रीदने के पैसे की कमी से निपटने के लिए आपके घर ने कितने दिन बड़ों ने कम खाया ताकि छोटे बच्चे खा सकें? (0-7 दिन)</t>
+          <t>यात्रा के मौसम के आम हफ़्ते में, खाने की या खाना ख़रीदने के पैसे की कमी से निपटने के लिए आपके घर ने कितने दिन खाना उधार लिया या दोस्तों/रिश्तेदारों की मदद ली? (0-7 दिन)</t>
         </is>
       </c>
       <c r="H178" s="2" t="inlineStr"/>
@@ -8570,7 +8606,7 @@
       </c>
       <c r="D179" s="2" t="inlineStr">
         <is>
-          <t>cope_restrict_adult_offseason_wk</t>
+          <t>cope_borrow_food_offseason_wk</t>
         </is>
       </c>
       <c r="E179" s="2" t="inlineStr">
@@ -8580,12 +8616,12 @@
       </c>
       <c r="F179" s="2" t="inlineStr">
         <is>
-          <t>In a normal week when the Yatra is closed, to cope with a lack of food or money to buy it, how many days did your household restrict consumption of adults/mothers in order for young children to eat? (0-7 days)</t>
+          <t>In a normal week when the Yatra is closed, to cope with a lack of food or money to buy it, how many days did your household borrow food and/or rely on help from friends/relatives? (0-7 days)</t>
         </is>
       </c>
       <c r="G179" s="2" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम हफ़्ते में आपके घर ने कितने दिन बड़ों ने कम खाया ताकि छोटे बच्चे खा सकें? (0-7 दिन)</t>
+          <t>जब यात्रा बंद रहती है, उस आम हफ़्ते में आपके घर ने कितने दिन खाना उधार लिया या दोस्तों/रिश्तेदारों की मदद ली? (0-7 दिन)</t>
         </is>
       </c>
       <c r="H179" s="2" t="inlineStr"/>
@@ -8602,43 +8638,39 @@
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>Ropeway</t>
+          <t>Food security, shocks and coping</t>
         </is>
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>ropeway_stance</t>
+          <t>cope_reduce_meals_yatra_wk</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>select one</t>
+          <t>whole number</t>
         </is>
       </c>
       <c r="F180" s="2" t="inlineStr">
         <is>
-          <t>A ropeway is proposed between Gaurikund and Kedarnath. Are you in favour, neutral, or against?</t>
+          <t>In a normal week during the Yatra season, to cope with a lack of food or money to buy it, how many days did your household reduce the number of meals eaten per day? (0-7 days)</t>
         </is>
       </c>
       <c r="G180" s="2" t="inlineStr">
         <is>
-          <t>गौरीकुंड से केदारनाथ तक रोपवे बनाने की बात चल रही है। आप इसके पक्ष में हैं, बीच में हैं, या ख़िलाफ़ हैं?</t>
-        </is>
-      </c>
-      <c r="H180" s="2" t="inlineStr">
-        <is>
-          <t>1 Support | 2 Neutral | 3 Oppose | 98 Prefer not to say</t>
-        </is>
-      </c>
+          <t>यात्रा के मौसम के आम हफ़्ते में, खाने की या खाना ख़रीदने के पैसे की कमी से निपटने के लिए आपके घर ने कितने दिन दिन में कम बार खाना खाया? (0-7 दिन)</t>
+        </is>
+      </c>
+      <c r="H180" s="2" t="inlineStr"/>
       <c r="I180" s="2" t="inlineStr"/>
       <c r="J180" s="2" t="inlineStr">
         <is>
-          <t>Project design</t>
+          <t>VASyR 2025 (exact item wording); WFP rCSI; The reduced Coping Strategy Index (rCSI): five food-coping questions, standard WFP weights (1, 2, 1, 1, 3) applied when the index is built. The Kedarnath instrument otherwise has no food-security module, which is a gap for a poverty-vulnerability survey; these five short questions close it at low cost instead of a full dietary-diversity module, left out to stay inside the 45-minute limit. Kept as day-counts (0-7), not collapsed to yes/no: this is the standard, validated WFP/FAO specification (frequency x severity), and no comparably-standard binary version was found on checking; a day-count also takes about as long to answer as a yes/no in practice, so little interview time is saved by simplifying it.</t>
         </is>
       </c>
     </row>
@@ -8648,43 +8680,39 @@
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t>Ropeway</t>
+          <t>Food security, shocks and coping</t>
         </is>
       </c>
       <c r="D181" s="2" t="inlineStr">
         <is>
-          <t>trek_dependent</t>
+          <t>cope_reduce_meals_offseason_wk</t>
         </is>
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
-          <t>yes/no</t>
+          <t>whole number</t>
         </is>
       </c>
       <c r="F181" s="2" t="inlineStr">
         <is>
-          <t>Is your main Yatra work carrying, transporting or guiding people or goods on the Gaurikund to Kedarnath trek?</t>
+          <t>In a normal week when the Yatra is closed, to cope with a lack of food or money to buy it, how many days did your household reduce the number of meals eaten per day? (0-7 days)</t>
         </is>
       </c>
       <c r="G181" s="2" t="inlineStr">
         <is>
-          <t>क्या आपका मुख्य यात्रा-काम गौरीकुंड से केदारनाथ के पैदल रास्ते पर लोगों या सामान को ले जाना, पहुँचाना या रास्ता दिखाना है?</t>
-        </is>
-      </c>
-      <c r="H181" s="2" t="inlineStr">
-        <is>
-          <t>0 No | 1 Yes</t>
-        </is>
-      </c>
+          <t>जब यात्रा बंद रहती है, उस आम हफ़्ते में आपके घर ने कितने दिन दिन में कम बार खाना खाया? (0-7 दिन)</t>
+        </is>
+      </c>
+      <c r="H181" s="2" t="inlineStr"/>
       <c r="I181" s="2" t="inlineStr"/>
       <c r="J181" s="2" t="inlineStr">
         <is>
-          <t>Project design (see tasks_module W4: exposure must be asked directly)</t>
+          <t>VASyR 2025 (exact item wording); WFP rCSI; The reduced Coping Strategy Index (rCSI): five food-coping questions, standard WFP weights (1, 2, 1, 1, 3) applied when the index is built. The Kedarnath instrument otherwise has no food-security module, which is a gap for a poverty-vulnerability survey; these five short questions close it at low cost instead of a full dietary-diversity module, left out to stay inside the 45-minute limit. Kept as day-counts (0-7), not collapsed to yes/no: this is the standard, validated WFP/FAO specification (frequency x severity), and no comparably-standard binary version was found on checking; a day-count also takes about as long to answer as a yes/no in practice, so little interview time is saved by simplifying it.</t>
         </is>
       </c>
     </row>
@@ -8694,43 +8722,39 @@
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>Job quality (Apablaza et al. 2026 questions)</t>
+          <t>Food security, shocks and coping</t>
         </is>
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>job_situation</t>
+          <t>cope_reduce_portion_yatra_wk</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>select one</t>
+          <t>whole number</t>
         </is>
       </c>
       <c r="F182" s="2" t="inlineStr">
         <is>
-          <t>Which best describes your situation during the last month: you work for pay full-time; you work for pay part-time or do occasional jobs; you study and work; you only study; you are only being trained for work; you are retired or pensioned; you do unpaid household tasks or care for others; you are unemployed and actively looking for work; you are sick or disabled and cannot work; or none of these?</t>
+          <t>In a normal week during the Yatra season, to cope with a lack of food or money to buy it, how many days did your household reduce portion size of meals? (0-7 days)</t>
         </is>
       </c>
       <c r="G182" s="2" t="inlineStr">
         <is>
-          <t>पिछले महीने आपकी हालत इनमें से किससे सबसे मिलती है: पूरे समय पैसे के लिए काम; कुछ समय या कभी-कभार का काम; पढ़ाई के साथ काम; सिर्फ़ पढ़ाई; सिर्फ़ काम की ट्रेनिंग; रिटायर या पेंशन पर; घर का बिना पैसे का काम या किसी की देखभाल; काम नहीं है और ढूँढ रहे हैं; बीमारी या विकलांगता से काम नहीं कर सकते; या इनमें से कुछ नहीं?</t>
-        </is>
-      </c>
-      <c r="H182" s="2" t="inlineStr">
-        <is>
-          <t>1 Works for pay full-time | 2 Works for pay part-time or occasional jobs | 3 Studies and works | 4 Only studies | 5 Being trained for work only | 6 Retired or pensioned | 7 Unpaid household tasks or caring for others | 8 Unemployed, actively seeking work | 9 Sick or disabled, cannot work | 10 Neither studying, working nor seeking work | 97 Does not know</t>
-        </is>
-      </c>
+          <t>यात्रा के मौसम के आम हफ़्ते में, खाने की या खाना ख़रीदने के पैसे की कमी से निपटने के लिए आपके घर ने कितने दिन खाने की मात्रा घटाई? (0-7 दिन)</t>
+        </is>
+      </c>
+      <c r="H182" s="2" t="inlineStr"/>
       <c r="I182" s="2" t="inlineStr"/>
       <c r="J182" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q5 (all eleven categories, with its own three-way routing)</t>
+          <t>VASyR 2025 (exact item wording); WFP rCSI; The reduced Coping Strategy Index (rCSI): five food-coping questions, standard WFP weights (1, 2, 1, 1, 3) applied when the index is built. The Kedarnath instrument otherwise has no food-security module, which is a gap for a poverty-vulnerability survey; these five short questions close it at low cost instead of a full dietary-diversity module, left out to stay inside the 45-minute limit. Kept as day-counts (0-7), not collapsed to yes/no: this is the standard, validated WFP/FAO specification (frequency x severity), and no comparably-standard binary version was found on checking; a day-count also takes about as long to answer as a yes/no in practice, so little interview time is saved by simplifying it.</t>
         </is>
       </c>
     </row>
@@ -8740,47 +8764,39 @@
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t>Job quality (Apablaza et al. 2026 questions)</t>
+          <t>Food security, shocks and coping</t>
         </is>
       </c>
       <c r="D183" s="2" t="inlineStr">
         <is>
-          <t>job_permanence</t>
+          <t>cope_reduce_portion_offseason_wk</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>select one</t>
+          <t>whole number</t>
         </is>
       </c>
       <c r="F183" s="2" t="inlineStr">
         <is>
-          <t>Is your job: permanent; seasonal or temporary; occasional or casual; on probation; or fixed-term?</t>
+          <t>In a normal week when the Yatra is closed, to cope with a lack of food or money to buy it, how many days did your household reduce portion size of meals? (0-7 days)</t>
         </is>
       </c>
       <c r="G183" s="2" t="inlineStr">
         <is>
-          <t>आपका काम कैसा है: पक्का; मौसमी या कुछ समय का; कभी-कभार का; परखने की अवधि पर; या तय समय के लिए?</t>
-        </is>
-      </c>
-      <c r="H183" s="2" t="inlineStr">
-        <is>
-          <t>1 Permanent | 2 Seasonal or temporary | 3 Occasional or casual | 4 On probation | 5 Fixed-term</t>
-        </is>
-      </c>
-      <c r="I183" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if job_situation is 1, 2 or 3 (currently working)</t>
-        </is>
-      </c>
+          <t>जब यात्रा बंद रहती है, उस आम हफ़्ते में आपके घर ने कितने दिन खाने की मात्रा घटाई? (0-7 दिन)</t>
+        </is>
+      </c>
+      <c r="H183" s="2" t="inlineStr"/>
+      <c r="I183" s="2" t="inlineStr"/>
       <c r="J183" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q9</t>
+          <t>VASyR 2025 (exact item wording); WFP rCSI; The reduced Coping Strategy Index (rCSI): five food-coping questions, standard WFP weights (1, 2, 1, 1, 3) applied when the index is built. The Kedarnath instrument otherwise has no food-security module, which is a gap for a poverty-vulnerability survey; these five short questions close it at low cost instead of a full dietary-diversity module, left out to stay inside the 45-minute limit. Kept as day-counts (0-7), not collapsed to yes/no: this is the standard, validated WFP/FAO specification (frequency x severity), and no comparably-standard binary version was found on checking; a day-count also takes about as long to answer as a yes/no in practice, so little interview time is saved by simplifying it.</t>
         </is>
       </c>
     </row>
@@ -8790,47 +8806,39 @@
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>Job quality (Apablaza et al. 2026 questions)</t>
+          <t>Food security, shocks and coping</t>
         </is>
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t>contract_status</t>
+          <t>cope_restrict_adult_yatra_wk</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>select one</t>
+          <t>whole number</t>
         </is>
       </c>
       <c r="F184" s="2" t="inlineStr">
         <is>
-          <t>Do you have a signed contract? Yes, signed; yes but not yet signed; no contract.</t>
+          <t>In a normal week during the Yatra season, to cope with a lack of food or money to buy it, how many days did your household restrict consumption of adults/mothers in order for young children to eat? (0-7 days)</t>
         </is>
       </c>
       <c r="G184" s="2" t="inlineStr">
         <is>
-          <t>क्या आपका दस्तख़त किया हुआ अनुबंध (कॉन्ट्रैक्ट) है? हाँ, दस्तख़त किया; हाँ, पर अभी दस्तख़त नहीं हुआ; कोई अनुबंध नहीं।</t>
-        </is>
-      </c>
-      <c r="H184" s="2" t="inlineStr">
-        <is>
-          <t>1 Yes, signed | 2 Yes, but not yet signed | 3 No contract</t>
-        </is>
-      </c>
-      <c r="I184" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if job_situation is 1, 2 or 3 (currently working); and employment_type is 3 or 4 (wage workers) -- self-employed skip to the next question</t>
-        </is>
-      </c>
+          <t>यात्रा के मौसम के आम हफ़्ते में, खाने की या खाना ख़रीदने के पैसे की कमी से निपटने के लिए आपके घर ने कितने दिन बड़ों ने कम खाया ताकि छोटे बच्चे खा सकें? (0-7 दिन)</t>
+        </is>
+      </c>
+      <c r="H184" s="2" t="inlineStr"/>
+      <c r="I184" s="2" t="inlineStr"/>
       <c r="J184" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q11</t>
+          <t>VASyR 2025 (exact item wording); WFP rCSI; The reduced Coping Strategy Index (rCSI): five food-coping questions, standard WFP weights (1, 2, 1, 1, 3) applied when the index is built. The Kedarnath instrument otherwise has no food-security module, which is a gap for a poverty-vulnerability survey; these five short questions close it at low cost instead of a full dietary-diversity module, left out to stay inside the 45-minute limit. Kept as day-counts (0-7), not collapsed to yes/no: this is the standard, validated WFP/FAO specification (frequency x severity), and no comparably-standard binary version was found on checking; a day-count also takes about as long to answer as a yes/no in practice, so little interview time is saved by simplifying it.</t>
         </is>
       </c>
     </row>
@@ -8840,47 +8848,39 @@
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C185" s="2" t="inlineStr">
         <is>
-          <t>Job quality (Apablaza et al. 2026 questions)</t>
+          <t>Food security, shocks and coping</t>
         </is>
       </c>
       <c r="D185" s="2" t="inlineStr">
         <is>
-          <t>workplace_registered</t>
+          <t>cope_restrict_adult_offseason_wk</t>
         </is>
       </c>
       <c r="E185" s="2" t="inlineStr">
         <is>
-          <t>yes/no</t>
+          <t>whole number</t>
         </is>
       </c>
       <c r="F185" s="2" t="inlineStr">
         <is>
-          <t>Is your workplace or business registered, for example with a taxpayer or GST number, a shop or trade licence, the Yatra registration, or a union?</t>
+          <t>In a normal week when the Yatra is closed, to cope with a lack of food or money to buy it, how many days did your household restrict consumption of adults/mothers in order for young children to eat? (0-7 days)</t>
         </is>
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>क्या आपका काम या धंधा रजिस्टर्ड है, जैसे GST या टैक्स नंबर, दुकान का लाइसेंस, यात्रा का रजिस्ट्रेशन, या कोई यूनियन?</t>
-        </is>
-      </c>
-      <c r="H185" s="2" t="inlineStr">
-        <is>
-          <t>0 No | 1 Yes</t>
-        </is>
-      </c>
-      <c r="I185" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if job_situation is 1, 2 or 3 (currently working)</t>
-        </is>
-      </c>
+          <t>जब यात्रा बंद रहती है, उस आम हफ़्ते में आपके घर ने कितने दिन बड़ों ने कम खाया ताकि छोटे बच्चे खा सकें? (0-7 दिन)</t>
+        </is>
+      </c>
+      <c r="H185" s="2" t="inlineStr"/>
+      <c r="I185" s="2" t="inlineStr"/>
       <c r="J185" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q12 (widened to local registrations)</t>
+          <t>VASyR 2025 (exact item wording); WFP rCSI; The reduced Coping Strategy Index (rCSI): five food-coping questions, standard WFP weights (1, 2, 1, 1, 3) applied when the index is built. The Kedarnath instrument otherwise has no food-security module, which is a gap for a poverty-vulnerability survey; these five short questions close it at low cost instead of a full dietary-diversity module, left out to stay inside the 45-minute limit. Kept as day-counts (0-7), not collapsed to yes/no: this is the standard, validated WFP/FAO specification (frequency x severity), and no comparably-standard binary version was found on checking; a day-count also takes about as long to answer as a yes/no in practice, so little interview time is saved by simplifying it.</t>
         </is>
       </c>
     </row>
@@ -8890,17 +8890,17 @@
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>Job quality (Apablaza et al. 2026 questions)</t>
+          <t>Ropeway</t>
         </is>
       </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
-          <t>pension_contrib</t>
+          <t>ropeway_stance</t>
         </is>
       </c>
       <c r="E186" s="2" t="inlineStr">
@@ -8910,27 +8910,23 @@
       </c>
       <c r="F186" s="2" t="inlineStr">
         <is>
-          <t>Do you contribute to any pension system? Yes, the employer deducts it; yes, voluntarily; no.</t>
+          <t>A ropeway is proposed between Gaurikund and Kedarnath. Are you in favour, neutral, or against?</t>
         </is>
       </c>
       <c r="G186" s="2" t="inlineStr">
         <is>
-          <t>क्या आप किसी पेंशन में पैसा डालते हैं? हाँ, मालिक तनख़्वाह से काटता है; हाँ, अपनी मर्ज़ी से डालते हैं; नहीं।</t>
+          <t>गौरीकुंड से केदारनाथ तक रोपवे बनाने की बात चल रही है। आप इसके पक्ष में हैं, बीच में हैं, या ख़िलाफ़ हैं?</t>
         </is>
       </c>
       <c r="H186" s="2" t="inlineStr">
         <is>
-          <t>1 Yes, employer deducts it | 2 Yes, contributes voluntarily | 3 No</t>
-        </is>
-      </c>
-      <c r="I186" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if job_situation is 1, 2 or 3 (currently working)</t>
-        </is>
-      </c>
+          <t>1 Support | 2 Neutral | 3 Oppose | 98 Prefer not to say</t>
+        </is>
+      </c>
+      <c r="I186" s="2" t="inlineStr"/>
       <c r="J186" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q16</t>
+          <t>Project design</t>
         </is>
       </c>
     </row>
@@ -8940,47 +8936,43 @@
       </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C187" s="2" t="inlineStr">
         <is>
-          <t>Job quality (Apablaza et al. 2026 questions)</t>
+          <t>Ropeway</t>
         </is>
       </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t>work_health_ins</t>
+          <t>trek_dependent</t>
         </is>
       </c>
       <c r="E187" s="2" t="inlineStr">
         <is>
-          <t>select one</t>
+          <t>yes/no</t>
         </is>
       </c>
       <c r="F187" s="2" t="inlineStr">
         <is>
-          <t>Do you have health insurance through your work? Yes; only private or other insurance; none; don't know.</t>
+          <t>Is your main Yatra work carrying, transporting or guiding people or goods on the Gaurikund to Kedarnath trek?</t>
         </is>
       </c>
       <c r="G187" s="2" t="inlineStr">
         <is>
-          <t>क्या काम की तरफ़ से आपका स्वास्थ्य बीमा है? हाँ; सिर्फ़ अपना या कोई और बीमा; कोई नहीं; पता नहीं।</t>
+          <t>क्या आपका मुख्य यात्रा-काम गौरीकुंड से केदारनाथ के पैदल रास्ते पर लोगों या सामान को ले जाना, पहुँचाना या रास्ता दिखाना है?</t>
         </is>
       </c>
       <c r="H187" s="2" t="inlineStr">
         <is>
-          <t>1 Yes, through work | 2 Only private or other insurance | 3 None | 4 Don't know</t>
-        </is>
-      </c>
-      <c r="I187" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if job_situation is 1, 2 or 3 (currently working)</t>
-        </is>
-      </c>
+          <t>0 No | 1 Yes</t>
+        </is>
+      </c>
+      <c r="I187" s="2" t="inlineStr"/>
       <c r="J187" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q17</t>
+          <t>Project design (see tasks_module W4: exposure must be asked directly)</t>
         </is>
       </c>
     </row>
@@ -9000,7 +8992,7 @@
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
-          <t>leave_rights</t>
+          <t>job_situation</t>
         </is>
       </c>
       <c r="E188" s="2" t="inlineStr">
@@ -9010,27 +9002,23 @@
       </c>
       <c r="F188" s="2" t="inlineStr">
         <is>
-          <t>Do you have the right to paid holiday, sick or maternity leave?</t>
+          <t>Which best describes your situation during the last month: you work for pay full-time; you work for pay part-time or do occasional jobs; you study and work; you only study; you are only being trained for work; you are retired or pensioned; you do unpaid household tasks or care for others; you are unemployed and actively looking for work; you are sick or disabled and cannot work; or none of these?</t>
         </is>
       </c>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t>क्या आपको पैसे वाली छुट्टी मिलती है — त्योहार, बीमारी या ज़च्चगी की?</t>
+          <t>पिछले महीने आपकी हालत इनमें से किससे सबसे मिलती है: पूरे समय पैसे के लिए काम; कुछ समय या कभी-कभार का काम; पढ़ाई के साथ काम; सिर्फ़ पढ़ाई; सिर्फ़ काम की ट्रेनिंग; रिटायर या पेंशन पर; घर का बिना पैसे का काम या किसी की देखभाल; काम नहीं है और ढूँढ रहे हैं; बीमारी या विकलांगता से काम नहीं कर सकते; या इनमें से कुछ नहीं?</t>
         </is>
       </c>
       <c r="H188" s="2" t="inlineStr">
         <is>
-          <t>0 No | 1 Yes | 97 Don't know</t>
-        </is>
-      </c>
-      <c r="I188" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if job_situation is 1, 2 or 3 (currently working)</t>
-        </is>
-      </c>
+          <t>1 Works for pay full-time | 2 Works for pay part-time or occasional jobs | 3 Studies and works | 4 Only studies | 5 Being trained for work only | 6 Retired or pensioned | 7 Unpaid household tasks or caring for others | 8 Unemployed, actively seeking work | 9 Sick or disabled, cannot work | 10 Neither studying, working nor seeking work | 97 Does not know</t>
+        </is>
+      </c>
+      <c r="I188" s="2" t="inlineStr"/>
       <c r="J188" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q18</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q5 (all eleven categories, with its own three-way routing)</t>
         </is>
       </c>
     </row>
@@ -9050,7 +9038,7 @@
       </c>
       <c r="D189" s="2" t="inlineStr">
         <is>
-          <t>injured_ever</t>
+          <t>job_permanence</t>
         </is>
       </c>
       <c r="E189" s="2" t="inlineStr">
@@ -9060,17 +9048,17 @@
       </c>
       <c r="F189" s="2" t="inlineStr">
         <is>
-          <t>Have you ever been physically injured at your workplace?</t>
+          <t>Is your job: permanent; seasonal or temporary; occasional or casual; on probation; or fixed-term?</t>
         </is>
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>क्या आपको कभी काम की जगह पर चोट लगी है?</t>
+          <t>आपका काम कैसा है: पक्का; मौसमी या कुछ समय का; कभी-कभार का; परखने की अवधि पर; या तय समय के लिए?</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr">
         <is>
-          <t>0 No | 1 Yes | 97 Don't know</t>
+          <t>1 Permanent | 2 Seasonal or temporary | 3 Occasional or casual | 4 On probation | 5 Fixed-term</t>
         </is>
       </c>
       <c r="I189" s="2" t="inlineStr">
@@ -9080,7 +9068,7 @@
       </c>
       <c r="J189" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q19</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q9</t>
         </is>
       </c>
     </row>
@@ -9100,7 +9088,7 @@
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>workplace_injury_12m</t>
+          <t>contract_status</t>
         </is>
       </c>
       <c r="E190" s="2" t="inlineStr">
@@ -9110,27 +9098,27 @@
       </c>
       <c r="F190" s="2" t="inlineStr">
         <is>
-          <t>In the last 12 months, was anyone physically injured or killed at your workplace because of work?</t>
+          <t>Do you have a signed contract? Yes, signed; yes but not yet signed; no contract.</t>
         </is>
       </c>
       <c r="G190" s="2" t="inlineStr">
         <is>
-          <t>पिछले 12 महीनों में क्या आपके काम की जगह पर काम की वजह से किसी को चोट लगी या किसी की मौत हुई?</t>
+          <t>क्या आपका दस्तख़त किया हुआ अनुबंध (कॉन्ट्रैक्ट) है? हाँ, दस्तख़त किया; हाँ, पर अभी दस्तख़त नहीं हुआ; कोई अनुबंध नहीं।</t>
         </is>
       </c>
       <c r="H190" s="2" t="inlineStr">
         <is>
-          <t>0 No | 1 Yes | 97 Don't know</t>
+          <t>1 Yes, signed | 2 Yes, but not yet signed | 3 No contract</t>
         </is>
       </c>
       <c r="I190" s="2" t="inlineStr">
         <is>
-          <t>Ask only if job_situation is 1, 2 or 3 (currently working)</t>
+          <t>Ask only if job_situation is 1, 2 or 3 (currently working); and employment_type is 3 or 4 (wage workers) -- self-employed skip to the next question</t>
         </is>
       </c>
       <c r="J190" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q20</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q11</t>
         </is>
       </c>
     </row>
@@ -9150,37 +9138,37 @@
       </c>
       <c r="D191" s="2" t="inlineStr">
         <is>
-          <t>wants_more_work</t>
+          <t>workplace_registered</t>
         </is>
       </c>
       <c r="E191" s="2" t="inlineStr">
         <is>
-          <t>select one</t>
+          <t>yes/no</t>
         </is>
       </c>
       <c r="F191" s="2" t="inlineStr">
         <is>
-          <t>Would you like to work more hours than you do?</t>
+          <t>Is your workplace or business registered, for example with a taxpayer or GST number, a shop or trade licence, the Yatra registration, or a union?</t>
         </is>
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>क्या आप अभी से ज़्यादा घंटे काम करना चाहेंगे?</t>
+          <t>क्या आपका काम या धंधा रजिस्टर्ड है, जैसे GST या टैक्स नंबर, दुकान का लाइसेंस, यात्रा का रजिस्ट्रेशन, या कोई यूनियन?</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
         <is>
-          <t>0 No | 1 Yes | 97 Don't know</t>
+          <t>0 No | 1 Yes</t>
         </is>
       </c>
       <c r="I191" s="2" t="inlineStr">
         <is>
-          <t>Ask if job_situation is 1 to 7 (Apablaza routes codes 4-7 straight to this question)</t>
+          <t>Ask only if job_situation is 1, 2 or 3 (currently working)</t>
         </is>
       </c>
       <c r="J191" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q21</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q12 (widened to local registrations)</t>
         </is>
       </c>
     </row>
@@ -9200,33 +9188,37 @@
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>more_hours_day</t>
+          <t>pension_contrib</t>
         </is>
       </c>
       <c r="E192" s="2" t="inlineStr">
         <is>
-          <t>whole number</t>
+          <t>select one</t>
         </is>
       </c>
       <c r="F192" s="2" t="inlineStr">
         <is>
-          <t>On a working day, how many MORE hours would you like to work?</t>
+          <t>Do you contribute to any pension system? Yes, the employer deducts it; yes, voluntarily; no.</t>
         </is>
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>काम के दिन में आप कितने घंटे और काम करना चाहेंगे?</t>
-        </is>
-      </c>
-      <c r="H192" s="2" t="inlineStr"/>
+          <t>क्या आप किसी पेंशन में पैसा डालते हैं? हाँ, मालिक तनख़्वाह से काटता है; हाँ, अपनी मर्ज़ी से डालते हैं; नहीं।</t>
+        </is>
+      </c>
+      <c r="H192" s="2" t="inlineStr">
+        <is>
+          <t>1 Yes, employer deducts it | 2 Yes, contributes voluntarily | 3 No</t>
+        </is>
+      </c>
       <c r="I192" s="2" t="inlineStr">
         <is>
-          <t>Ask if wants_more_work = 1, or if job_situation = 8 (Apablaza routes the unemployed-and-seeking category here directly)</t>
+          <t>Ask only if job_situation is 1, 2 or 3 (currently working)</t>
         </is>
       </c>
       <c r="J192" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q22</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q16</t>
         </is>
       </c>
     </row>
@@ -9246,33 +9238,37 @@
       </c>
       <c r="D193" s="2" t="inlineStr">
         <is>
-          <t>months_looked_for_work</t>
+          <t>work_health_ins</t>
         </is>
       </c>
       <c r="E193" s="2" t="inlineStr">
         <is>
-          <t>whole number</t>
+          <t>select one</t>
         </is>
       </c>
       <c r="F193" s="2" t="inlineStr">
         <is>
-          <t>Across the months when you had no paid work, about how many MONTHS in total were you looking for work?</t>
+          <t>Do you have health insurance through your work? Yes; only private or other insurance; none; don't know.</t>
         </is>
       </c>
       <c r="G193" s="2" t="inlineStr">
         <is>
-          <t>जिन महीनों में आपके पास कोई पैसे वाला काम नहीं था, उनमें कुल मिलाकर लगभग कितने महीने आप काम ढूँढते रहे?</t>
-        </is>
-      </c>
-      <c r="H193" s="2" t="inlineStr"/>
+          <t>क्या काम की तरफ़ से आपका स्वास्थ्य बीमा है? हाँ; सिर्फ़ अपना या कोई और बीमा; कोई नहीं; पता नहीं।</t>
+        </is>
+      </c>
+      <c r="H193" s="2" t="inlineStr">
+        <is>
+          <t>1 Yes, through work | 2 Only private or other insurance | 3 None | 4 Don't know</t>
+        </is>
+      </c>
       <c r="I193" s="2" t="inlineStr">
         <is>
-          <t>Ask if any month in the calendar is 'No paid work', or if job_situation = 8</t>
+          <t>Ask only if job_situation is 1, 2 or 3 (currently working)</t>
         </is>
       </c>
       <c r="J193" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q23 (duration in weeks, tied to the calendar instead of a single point in time)</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q17</t>
         </is>
       </c>
     </row>
@@ -9292,7 +9288,7 @@
       </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
-          <t>first_job_ever</t>
+          <t>leave_rights</t>
         </is>
       </c>
       <c r="E194" s="2" t="inlineStr">
@@ -9302,12 +9298,12 @@
       </c>
       <c r="F194" s="2" t="inlineStr">
         <is>
-          <t>Was your current work the first paid job you ever had?</t>
+          <t>Do you have the right to paid holiday, sick or maternity leave?</t>
         </is>
       </c>
       <c r="G194" s="2" t="inlineStr">
         <is>
-          <t>क्या यह आपका पहला पैसे वाला काम है?</t>
+          <t>क्या आपको पैसे वाली छुट्टी मिलती है — त्योहार, बीमारी या ज़च्चगी की?</t>
         </is>
       </c>
       <c r="H194" s="2" t="inlineStr">
@@ -9315,10 +9311,14 @@
           <t>0 No | 1 Yes | 97 Don't know</t>
         </is>
       </c>
-      <c r="I194" s="2" t="inlineStr"/>
+      <c r="I194" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if job_situation is 1, 2 or 3 (currently working)</t>
+        </is>
+      </c>
       <c r="J194" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q24</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q18</t>
         </is>
       </c>
     </row>
@@ -9328,17 +9328,17 @@
       </c>
       <c r="B195" s="2" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C195" s="2" t="inlineStr">
         <is>
-          <t>Tasks and skills (short block)</t>
+          <t>Job quality (Apablaza et al. 2026 questions)</t>
         </is>
       </c>
       <c r="D195" s="2" t="inlineStr">
         <is>
-          <t>tk_load</t>
+          <t>injured_ever</t>
         </is>
       </c>
       <c r="E195" s="2" t="inlineStr">
@@ -9348,23 +9348,27 @@
       </c>
       <c r="F195" s="2" t="inlineStr">
         <is>
-          <t>Do you load, unload, stack or count goods? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
+          <t>Have you ever been physically injured at your workplace?</t>
         </is>
       </c>
       <c r="G195" s="2" t="inlineStr">
         <is>
-          <t>क्या आप सामान चढ़ाना-उतारना, लगाना या गिनना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आपको कभी काम की जगह पर चोट लगी है?</t>
         </is>
       </c>
       <c r="H195" s="2" t="inlineStr">
         <is>
-          <t>1 Yes, regularly in my main Yatra work | 2 Not in my main work, but done before elsewhere | 3 Never done</t>
-        </is>
-      </c>
-      <c r="I195" s="2" t="inlineStr"/>
+          <t>0 No | 1 Yes | 97 Don't know</t>
+        </is>
+      </c>
+      <c r="I195" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if job_situation is 1, 2 or 3 (currently working)</t>
+        </is>
+      </c>
       <c r="J195" s="2" t="inlineStr">
         <is>
-          <t>Gathmann and Schonberg 2010; NCO 9333.0100 loader</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q19</t>
         </is>
       </c>
     </row>
@@ -9374,17 +9378,17 @@
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>Tasks and skills (short block)</t>
+          <t>Job quality (Apablaza et al. 2026 questions)</t>
         </is>
       </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
-          <t>tk_drive</t>
+          <t>workplace_injury_12m</t>
         </is>
       </c>
       <c r="E196" s="2" t="inlineStr">
@@ -9394,23 +9398,27 @@
       </c>
       <c r="F196" s="2" t="inlineStr">
         <is>
-          <t>Do you drive a motor vehicle? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
+          <t>In the last 12 months, was anyone physically injured or killed at your workplace because of work?</t>
         </is>
       </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>क्या आप गाड़ी चलाना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>पिछले 12 महीनों में क्या आपके काम की जगह पर काम की वजह से किसी को चोट लगी या किसी की मौत हुई?</t>
         </is>
       </c>
       <c r="H196" s="2" t="inlineStr">
         <is>
-          <t>1 Yes, regularly in my main Yatra work | 2 Not in my main work, but done before elsewhere | 3 Never done</t>
-        </is>
-      </c>
-      <c r="I196" s="2" t="inlineStr"/>
+          <t>0 No | 1 Yes | 97 Don't know</t>
+        </is>
+      </c>
+      <c r="I196" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if job_situation is 1, 2 or 3 (currently working)</t>
+        </is>
+      </c>
       <c r="J196" s="2" t="inlineStr">
         <is>
-          <t>Spitz-Oener 2006 / STEP; NCO 8322.0100</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q20</t>
         </is>
       </c>
     </row>
@@ -9420,17 +9428,17 @@
       </c>
       <c r="B197" s="2" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C197" s="2" t="inlineStr">
         <is>
-          <t>Tasks and skills (short block)</t>
+          <t>Job quality (Apablaza et al. 2026 questions)</t>
         </is>
       </c>
       <c r="D197" s="2" t="inlineStr">
         <is>
-          <t>tk_engine</t>
+          <t>wants_more_work</t>
         </is>
       </c>
       <c r="E197" s="2" t="inlineStr">
@@ -9440,23 +9448,27 @@
       </c>
       <c r="F197" s="2" t="inlineStr">
         <is>
-          <t>Do you operate an engine or machine? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
+          <t>Would you like to work more hours than you do?</t>
         </is>
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>क्या आप इंजन या मशीन चलाना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप अभी से ज़्यादा घंटे काम करना चाहेंगे?</t>
         </is>
       </c>
       <c r="H197" s="2" t="inlineStr">
         <is>
-          <t>1 Yes, regularly in my main Yatra work | 2 Not in my main work, but done before elsewhere | 3 Never done</t>
-        </is>
-      </c>
-      <c r="I197" s="2" t="inlineStr"/>
+          <t>0 No | 1 Yes | 97 Don't know</t>
+        </is>
+      </c>
+      <c r="I197" s="2" t="inlineStr">
+        <is>
+          <t>Ask if job_situation is 1 to 7 (Apablaza routes codes 4-7 straight to this question)</t>
+        </is>
+      </c>
       <c r="J197" s="2" t="inlineStr">
         <is>
-          <t>Gathmann and Schonberg 2010; NCO 8343.1700 ropeway operator</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q21</t>
         </is>
       </c>
     </row>
@@ -9466,43 +9478,43 @@
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>Tasks and skills (short block)</t>
+          <t>Job quality (Apablaza et al. 2026 questions)</t>
         </is>
       </c>
       <c r="D198" s="2" t="inlineStr">
         <is>
-          <t>tk_electric</t>
+          <t>more_hours_day</t>
         </is>
       </c>
       <c r="E198" s="2" t="inlineStr">
         <is>
-          <t>select one</t>
+          <t>whole number</t>
         </is>
       </c>
       <c r="F198" s="2" t="inlineStr">
         <is>
-          <t>Do you do electrical or wiring work? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
+          <t>On a working day, how many MORE hours would you like to work?</t>
         </is>
       </c>
       <c r="G198" s="2" t="inlineStr">
         <is>
-          <t>क्या आप बिजली या तार का काम करना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
-        </is>
-      </c>
-      <c r="H198" s="2" t="inlineStr">
-        <is>
-          <t>1 Yes, regularly in my main Yatra work | 2 Not in my main work, but done before elsewhere | 3 Never done</t>
-        </is>
-      </c>
-      <c r="I198" s="2" t="inlineStr"/>
+          <t>काम के दिन में आप कितने घंटे और काम करना चाहेंगे?</t>
+        </is>
+      </c>
+      <c r="H198" s="2" t="inlineStr"/>
+      <c r="I198" s="2" t="inlineStr">
+        <is>
+          <t>Ask if wants_more_work = 1, or if job_situation = 8 (Apablaza routes the unemployed-and-seeking category here directly)</t>
+        </is>
+      </c>
       <c r="J198" s="2" t="inlineStr">
         <is>
-          <t>Spitz-Oener 2006; NCO 7411.0301 wireman</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q22</t>
         </is>
       </c>
     </row>
@@ -9512,43 +9524,43 @@
       </c>
       <c r="B199" s="2" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C199" s="2" t="inlineStr">
         <is>
-          <t>Tasks and skills (short block)</t>
+          <t>Job quality (Apablaza et al. 2026 questions)</t>
         </is>
       </c>
       <c r="D199" s="2" t="inlineStr">
         <is>
-          <t>tk_safety</t>
+          <t>months_looked_for_work</t>
         </is>
       </c>
       <c r="E199" s="2" t="inlineStr">
         <is>
-          <t>select one</t>
+          <t>whole number</t>
         </is>
       </c>
       <c r="F199" s="2" t="inlineStr">
         <is>
-          <t>Do you check equipment or the route for safety? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
+          <t>Across the months when you had no paid work, about how many MONTHS in total were you looking for work?</t>
         </is>
       </c>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>क्या आप सामान या रास्ते की सुरक्षा जाँचना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
-        </is>
-      </c>
-      <c r="H199" s="2" t="inlineStr">
-        <is>
-          <t>1 Yes, regularly in my main Yatra work | 2 Not in my main work, but done before elsewhere | 3 Never done</t>
-        </is>
-      </c>
-      <c r="I199" s="2" t="inlineStr"/>
+          <t>जिन महीनों में आपके पास कोई पैसे वाला काम नहीं था, उनमें कुल मिलाकर लगभग कितने महीने आप काम ढूँढते रहे?</t>
+        </is>
+      </c>
+      <c r="H199" s="2" t="inlineStr"/>
+      <c r="I199" s="2" t="inlineStr">
+        <is>
+          <t>Ask if any month in the calendar is 'No paid work', or if job_situation = 8</t>
+        </is>
+      </c>
       <c r="J199" s="2" t="inlineStr">
         <is>
-          <t>Gathmann and Schonberg 2010; NCO 8343.1700</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q23 (duration in weeks, tied to the calendar instead of a single point in time)</t>
         </is>
       </c>
     </row>
@@ -9558,17 +9570,17 @@
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>Tasks and skills (short block)</t>
+          <t>Job quality (Apablaza et al. 2026 questions)</t>
         </is>
       </c>
       <c r="D200" s="2" t="inlineStr">
         <is>
-          <t>tk_sell</t>
+          <t>first_job_ever</t>
         </is>
       </c>
       <c r="E200" s="2" t="inlineStr">
@@ -9578,23 +9590,23 @@
       </c>
       <c r="F200" s="2" t="inlineStr">
         <is>
-          <t>Do you sell goods or services? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
+          <t>Was your current work the first paid job you ever had?</t>
         </is>
       </c>
       <c r="G200" s="2" t="inlineStr">
         <is>
-          <t>क्या आप सामान या सेवा बेचना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या यह आपका पहला पैसे वाला काम है?</t>
         </is>
       </c>
       <c r="H200" s="2" t="inlineStr">
         <is>
-          <t>1 Yes, regularly in my main Yatra work | 2 Not in my main work, but done before elsewhere | 3 Never done</t>
+          <t>0 No | 1 Yes | 97 Don't know</t>
         </is>
       </c>
       <c r="I200" s="2" t="inlineStr"/>
       <c r="J200" s="2" t="inlineStr">
         <is>
-          <t>Gathmann and Schonberg 2010; NCO 5223.0200</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q24</t>
         </is>
       </c>
     </row>
@@ -9614,7 +9626,7 @@
       </c>
       <c r="D201" s="2" t="inlineStr">
         <is>
-          <t>tk_cash</t>
+          <t>tk_load</t>
         </is>
       </c>
       <c r="E201" s="2" t="inlineStr">
@@ -9624,12 +9636,12 @@
       </c>
       <c r="F201" s="2" t="inlineStr">
         <is>
-          <t>Do you handle cash and payments? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
+          <t>Do you load, unload, stack or count goods? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
         </is>
       </c>
       <c r="G201" s="2" t="inlineStr">
         <is>
-          <t>क्या आप पैसे और भुगतान सँभालना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप सामान चढ़ाना-उतारना, लगाना या गिनना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="H201" s="2" t="inlineStr">
@@ -9640,7 +9652,7 @@
       <c r="I201" s="2" t="inlineStr"/>
       <c r="J201" s="2" t="inlineStr">
         <is>
-          <t>Autor and Handel 2013; NCO 5131.0401</t>
+          <t>Gathmann and Schonberg 2010; NCO 9333.0100 loader</t>
         </is>
       </c>
     </row>
@@ -9660,7 +9672,7 @@
       </c>
       <c r="D202" s="2" t="inlineStr">
         <is>
-          <t>tk_cook</t>
+          <t>tk_drive</t>
         </is>
       </c>
       <c r="E202" s="2" t="inlineStr">
@@ -9670,12 +9682,12 @@
       </c>
       <c r="F202" s="2" t="inlineStr">
         <is>
-          <t>Do you cook or prepare food or drink? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
+          <t>Do you drive a motor vehicle? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
         </is>
       </c>
       <c r="G202" s="2" t="inlineStr">
         <is>
-          <t>क्या आप खाना या पीने की चीज़ बनाना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप गाड़ी चलाना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="H202" s="2" t="inlineStr">
@@ -9686,7 +9698,7 @@
       <c r="I202" s="2" t="inlineStr"/>
       <c r="J202" s="2" t="inlineStr">
         <is>
-          <t>NCO 5120.0300 cook</t>
+          <t>Spitz-Oener 2006 / STEP; NCO 8322.0100</t>
         </is>
       </c>
     </row>
@@ -9706,7 +9718,7 @@
       </c>
       <c r="D203" s="2" t="inlineStr">
         <is>
-          <t>tk_serve</t>
+          <t>tk_engine</t>
         </is>
       </c>
       <c r="E203" s="2" t="inlineStr">
@@ -9716,12 +9728,12 @@
       </c>
       <c r="F203" s="2" t="inlineStr">
         <is>
-          <t>Do you serve guests or customers? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
+          <t>Do you operate an engine or machine? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
         </is>
       </c>
       <c r="G203" s="2" t="inlineStr">
         <is>
-          <t>क्या आप मेहमानों या ग्राहकों की सेवा करना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप इंजन या मशीन चलाना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="H203" s="2" t="inlineStr">
@@ -9732,7 +9744,7 @@
       <c r="I203" s="2" t="inlineStr"/>
       <c r="J203" s="2" t="inlineStr">
         <is>
-          <t>NCO 5131.0401 waiter; Pal et al. 2026</t>
+          <t>Gathmann and Schonberg 2010; NCO 8343.1700 ropeway operator</t>
         </is>
       </c>
     </row>
@@ -9752,7 +9764,7 @@
       </c>
       <c r="D204" s="2" t="inlineStr">
         <is>
-          <t>tk_clean</t>
+          <t>tk_electric</t>
         </is>
       </c>
       <c r="E204" s="2" t="inlineStr">
@@ -9762,12 +9774,12 @@
       </c>
       <c r="F204" s="2" t="inlineStr">
         <is>
-          <t>Do you clean rooms or public areas? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
+          <t>Do you do electrical or wiring work? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
         </is>
       </c>
       <c r="G204" s="2" t="inlineStr">
         <is>
-          <t>क्या आप कमरे या सार्वजनिक जगह साफ़ करना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप बिजली या तार का काम करना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="H204" s="2" t="inlineStr">
@@ -9778,7 +9790,7 @@
       <c r="I204" s="2" t="inlineStr"/>
       <c r="J204" s="2" t="inlineStr">
         <is>
-          <t>NCO 5151.0202 room attendant; Autor-Levy-Murnane 2003 (janitorial)</t>
+          <t>Spitz-Oener 2006; NCO 7411.0301 wireman</t>
         </is>
       </c>
     </row>
@@ -9798,7 +9810,7 @@
       </c>
       <c r="D205" s="2" t="inlineStr">
         <is>
-          <t>tk_guide</t>
+          <t>tk_safety</t>
         </is>
       </c>
       <c r="E205" s="2" t="inlineStr">
@@ -9808,12 +9820,12 @@
       </c>
       <c r="F205" s="2" t="inlineStr">
         <is>
-          <t>Do you guide or explain things to visitors? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
+          <t>Do you check equipment or the route for safety? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
         </is>
       </c>
       <c r="G205" s="2" t="inlineStr">
         <is>
-          <t>क्या आप आने वालों को रास्ता या बात समझाना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप सामान या रास्ते की सुरक्षा जाँचना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="H205" s="2" t="inlineStr">
@@ -9824,7 +9836,7 @@
       <c r="I205" s="2" t="inlineStr"/>
       <c r="J205" s="2" t="inlineStr">
         <is>
-          <t>Gathmann and Schonberg 2010; NCO 5113.0200</t>
+          <t>Gathmann and Schonberg 2010; NCO 8343.1700</t>
         </is>
       </c>
     </row>
@@ -9844,7 +9856,7 @@
       </c>
       <c r="D206" s="2" t="inlineStr">
         <is>
-          <t>tk_coord</t>
+          <t>tk_sell</t>
         </is>
       </c>
       <c r="E206" s="2" t="inlineStr">
@@ -9854,12 +9866,12 @@
       </c>
       <c r="F206" s="2" t="inlineStr">
         <is>
-          <t>Do you coordinate work by phone, radio or signals? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
+          <t>Do you sell goods or services? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
         </is>
       </c>
       <c r="G206" s="2" t="inlineStr">
         <is>
-          <t>क्या आप फ़ोन, रेडियो या इशारों से दूसरों के साथ तालमेल करना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप सामान या सेवा बेचना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="H206" s="2" t="inlineStr">
@@ -9870,7 +9882,7 @@
       <c r="I206" s="2" t="inlineStr"/>
       <c r="J206" s="2" t="inlineStr">
         <is>
-          <t>NCO 8343.1700 ropeway operator</t>
+          <t>Gathmann and Schonberg 2010; NCO 5223.0200</t>
         </is>
       </c>
     </row>
@@ -9890,37 +9902,33 @@
       </c>
       <c r="D207" s="2" t="inlineStr">
         <is>
-          <t>drove_twowheeler</t>
+          <t>tk_cash</t>
         </is>
       </c>
       <c r="E207" s="2" t="inlineStr">
         <is>
-          <t>yes/no</t>
+          <t>select one</t>
         </is>
       </c>
       <c r="F207" s="2" t="inlineStr">
         <is>
-          <t>Have you ever driven a motorcycle or scooter, with or without a licence?</t>
+          <t>Do you handle cash and payments? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
         </is>
       </c>
       <c r="G207" s="2" t="inlineStr">
         <is>
-          <t>क्या आपने कभी मोटरसाइकिल या स्कूटर चलाई है, लाइसेंस हो या न हो?</t>
+          <t>क्या आप पैसे और भुगतान सँभालना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="H207" s="2" t="inlineStr">
         <is>
-          <t>0 No | 1 Yes</t>
-        </is>
-      </c>
-      <c r="I207" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if tk_drive is 1 or 2</t>
-        </is>
-      </c>
+          <t>1 Yes, regularly in my main Yatra work | 2 Not in my main work, but done before elsewhere | 3 Never done</t>
+        </is>
+      </c>
+      <c r="I207" s="2" t="inlineStr"/>
       <c r="J207" s="2" t="inlineStr">
         <is>
-          <t>Level ladder without licences: people drive without holding a licence</t>
+          <t>Autor and Handel 2013; NCO 5131.0401</t>
         </is>
       </c>
     </row>
@@ -9940,37 +9948,33 @@
       </c>
       <c r="D208" s="2" t="inlineStr">
         <is>
-          <t>drove_car</t>
+          <t>tk_cook</t>
         </is>
       </c>
       <c r="E208" s="2" t="inlineStr">
         <is>
-          <t>yes/no</t>
+          <t>select one</t>
         </is>
       </c>
       <c r="F208" s="2" t="inlineStr">
         <is>
-          <t>... a car or jeep?</t>
+          <t>Do you cook or prepare food or drink? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
         </is>
       </c>
       <c r="G208" s="2" t="inlineStr">
         <is>
-          <t>...कार या जीप?</t>
+          <t>क्या आप खाना या पीने की चीज़ बनाना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="H208" s="2" t="inlineStr">
         <is>
-          <t>0 No | 1 Yes</t>
-        </is>
-      </c>
-      <c r="I208" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if tk_drive is 1 or 2</t>
-        </is>
-      </c>
+          <t>1 Yes, regularly in my main Yatra work | 2 Not in my main work, but done before elsewhere | 3 Never done</t>
+        </is>
+      </c>
+      <c r="I208" s="2" t="inlineStr"/>
       <c r="J208" s="2" t="inlineStr">
         <is>
-          <t>Level ladder without licences</t>
+          <t>NCO 5120.0300 cook</t>
         </is>
       </c>
     </row>
@@ -9990,37 +9994,33 @@
       </c>
       <c r="D209" s="2" t="inlineStr">
         <is>
-          <t>drove_heavy</t>
+          <t>tk_serve</t>
         </is>
       </c>
       <c r="E209" s="2" t="inlineStr">
         <is>
-          <t>yes/no</t>
+          <t>select one</t>
         </is>
       </c>
       <c r="F209" s="2" t="inlineStr">
         <is>
-          <t>... a truck or bus?</t>
+          <t>Do you serve guests or customers? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
         </is>
       </c>
       <c r="G209" s="2" t="inlineStr">
         <is>
-          <t>...ट्रक या बस?</t>
+          <t>क्या आप मेहमानों या ग्राहकों की सेवा करना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="H209" s="2" t="inlineStr">
         <is>
-          <t>0 No | 1 Yes</t>
-        </is>
-      </c>
-      <c r="I209" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if tk_drive is 1 or 2</t>
-        </is>
-      </c>
+          <t>1 Yes, regularly in my main Yatra work | 2 Not in my main work, but done before elsewhere | 3 Never done</t>
+        </is>
+      </c>
+      <c r="I209" s="2" t="inlineStr"/>
       <c r="J209" s="2" t="inlineStr">
         <is>
-          <t>Level ladder without licences</t>
+          <t>NCO 5131.0401 waiter; Pal et al. 2026</t>
         </is>
       </c>
     </row>
@@ -10040,33 +10040,33 @@
       </c>
       <c r="D210" s="2" t="inlineStr">
         <is>
-          <t>read_at_work</t>
+          <t>tk_clean</t>
         </is>
       </c>
       <c r="E210" s="2" t="inlineStr">
         <is>
-          <t>yes/no</t>
+          <t>select one</t>
         </is>
       </c>
       <c r="F210" s="2" t="inlineStr">
         <is>
-          <t>In your work, do you read anything (notes, rate lists, tickets, messages)?</t>
+          <t>Do you clean rooms or public areas? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
         </is>
       </c>
       <c r="G210" s="2" t="inlineStr">
         <is>
-          <t>अपने काम में क्या आप कुछ पढ़ते हैं (पर्ची, रेट लिस्ट, टिकट, मैसेज)?</t>
+          <t>क्या आप कमरे या सार्वजनिक जगह साफ़ करना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="H210" s="2" t="inlineStr">
         <is>
-          <t>0 No | 1 Yes</t>
+          <t>1 Yes, regularly in my main Yatra work | 2 Not in my main work, but done before elsewhere | 3 Never done</t>
         </is>
       </c>
       <c r="I210" s="2" t="inlineStr"/>
       <c r="J210" s="2" t="inlineStr">
         <is>
-          <t>STEP module 6A</t>
+          <t>NCO 5151.0202 room attendant; Autor-Levy-Murnane 2003 (janitorial)</t>
         </is>
       </c>
     </row>
@@ -10086,38 +10086,326 @@
       </c>
       <c r="D211" s="2" t="inlineStr">
         <is>
-          <t>calc_at_work</t>
+          <t>tk_guide</t>
         </is>
       </c>
       <c r="E211" s="2" t="inlineStr">
         <is>
-          <t>yes/no</t>
+          <t>select one</t>
         </is>
       </c>
       <c r="F211" s="2" t="inlineStr">
         <is>
-          <t>In your work, do you work out prices or costs?</t>
+          <t>Do you guide or explain things to visitors? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
         </is>
       </c>
       <c r="G211" s="2" t="inlineStr">
         <is>
-          <t>अपने काम में क्या आप दाम या ख़र्चा जोड़ते-घटाते हैं?</t>
+          <t>क्या आप आने वालों को रास्ता या बात समझाना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="H211" s="2" t="inlineStr">
         <is>
-          <t>0 No | 1 Yes</t>
+          <t>1 Yes, regularly in my main Yatra work | 2 Not in my main work, but done before elsewhere | 3 Never done</t>
         </is>
       </c>
       <c r="I211" s="2" t="inlineStr"/>
       <c r="J211" s="2" t="inlineStr">
         <is>
+          <t>Gathmann and Schonberg 2010; NCO 5113.0200</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="n">
+        <v>211</v>
+      </c>
+      <c r="B212" s="2" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="C212" s="2" t="inlineStr">
+        <is>
+          <t>Tasks and skills (short block)</t>
+        </is>
+      </c>
+      <c r="D212" s="2" t="inlineStr">
+        <is>
+          <t>tk_coord</t>
+        </is>
+      </c>
+      <c r="E212" s="2" t="inlineStr">
+        <is>
+          <t>select one</t>
+        </is>
+      </c>
+      <c r="F212" s="2" t="inlineStr">
+        <is>
+          <t>Do you coordinate work by phone, radio or signals? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
+        </is>
+      </c>
+      <c r="G212" s="2" t="inlineStr">
+        <is>
+          <t>क्या आप फ़ोन, रेडियो या इशारों से दूसरों के साथ तालमेल करना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+        </is>
+      </c>
+      <c r="H212" s="2" t="inlineStr">
+        <is>
+          <t>1 Yes, regularly in my main Yatra work | 2 Not in my main work, but done before elsewhere | 3 Never done</t>
+        </is>
+      </c>
+      <c r="I212" s="2" t="inlineStr"/>
+      <c r="J212" s="2" t="inlineStr">
+        <is>
+          <t>NCO 8343.1700 ropeway operator</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="n">
+        <v>212</v>
+      </c>
+      <c r="B213" s="2" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="C213" s="2" t="inlineStr">
+        <is>
+          <t>Tasks and skills (short block)</t>
+        </is>
+      </c>
+      <c r="D213" s="2" t="inlineStr">
+        <is>
+          <t>drove_twowheeler</t>
+        </is>
+      </c>
+      <c r="E213" s="2" t="inlineStr">
+        <is>
+          <t>yes/no</t>
+        </is>
+      </c>
+      <c r="F213" s="2" t="inlineStr">
+        <is>
+          <t>Have you ever driven a motorcycle or scooter, with or without a licence?</t>
+        </is>
+      </c>
+      <c r="G213" s="2" t="inlineStr">
+        <is>
+          <t>क्या आपने कभी मोटरसाइकिल या स्कूटर चलाई है, लाइसेंस हो या न हो?</t>
+        </is>
+      </c>
+      <c r="H213" s="2" t="inlineStr">
+        <is>
+          <t>0 No | 1 Yes</t>
+        </is>
+      </c>
+      <c r="I213" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if tk_drive is 1 or 2</t>
+        </is>
+      </c>
+      <c r="J213" s="2" t="inlineStr">
+        <is>
+          <t>Level ladder without licences: people drive without holding a licence</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="n">
+        <v>213</v>
+      </c>
+      <c r="B214" s="2" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="C214" s="2" t="inlineStr">
+        <is>
+          <t>Tasks and skills (short block)</t>
+        </is>
+      </c>
+      <c r="D214" s="2" t="inlineStr">
+        <is>
+          <t>drove_car</t>
+        </is>
+      </c>
+      <c r="E214" s="2" t="inlineStr">
+        <is>
+          <t>yes/no</t>
+        </is>
+      </c>
+      <c r="F214" s="2" t="inlineStr">
+        <is>
+          <t>... a car or jeep?</t>
+        </is>
+      </c>
+      <c r="G214" s="2" t="inlineStr">
+        <is>
+          <t>...कार या जीप?</t>
+        </is>
+      </c>
+      <c r="H214" s="2" t="inlineStr">
+        <is>
+          <t>0 No | 1 Yes</t>
+        </is>
+      </c>
+      <c r="I214" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if tk_drive is 1 or 2</t>
+        </is>
+      </c>
+      <c r="J214" s="2" t="inlineStr">
+        <is>
+          <t>Level ladder without licences</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="2" t="n">
+        <v>214</v>
+      </c>
+      <c r="B215" s="2" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="C215" s="2" t="inlineStr">
+        <is>
+          <t>Tasks and skills (short block)</t>
+        </is>
+      </c>
+      <c r="D215" s="2" t="inlineStr">
+        <is>
+          <t>drove_heavy</t>
+        </is>
+      </c>
+      <c r="E215" s="2" t="inlineStr">
+        <is>
+          <t>yes/no</t>
+        </is>
+      </c>
+      <c r="F215" s="2" t="inlineStr">
+        <is>
+          <t>... a truck or bus?</t>
+        </is>
+      </c>
+      <c r="G215" s="2" t="inlineStr">
+        <is>
+          <t>...ट्रक या बस?</t>
+        </is>
+      </c>
+      <c r="H215" s="2" t="inlineStr">
+        <is>
+          <t>0 No | 1 Yes</t>
+        </is>
+      </c>
+      <c r="I215" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if tk_drive is 1 or 2</t>
+        </is>
+      </c>
+      <c r="J215" s="2" t="inlineStr">
+        <is>
+          <t>Level ladder without licences</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="n">
+        <v>215</v>
+      </c>
+      <c r="B216" s="2" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="C216" s="2" t="inlineStr">
+        <is>
+          <t>Tasks and skills (short block)</t>
+        </is>
+      </c>
+      <c r="D216" s="2" t="inlineStr">
+        <is>
+          <t>read_at_work</t>
+        </is>
+      </c>
+      <c r="E216" s="2" t="inlineStr">
+        <is>
+          <t>yes/no</t>
+        </is>
+      </c>
+      <c r="F216" s="2" t="inlineStr">
+        <is>
+          <t>In your work, do you read anything (notes, rate lists, tickets, messages)?</t>
+        </is>
+      </c>
+      <c r="G216" s="2" t="inlineStr">
+        <is>
+          <t>अपने काम में क्या आप कुछ पढ़ते हैं (पर्ची, रेट लिस्ट, टिकट, मैसेज)?</t>
+        </is>
+      </c>
+      <c r="H216" s="2" t="inlineStr">
+        <is>
+          <t>0 No | 1 Yes</t>
+        </is>
+      </c>
+      <c r="I216" s="2" t="inlineStr"/>
+      <c r="J216" s="2" t="inlineStr">
+        <is>
           <t>STEP module 6A</t>
         </is>
       </c>
     </row>
+    <row r="217">
+      <c r="A217" s="2" t="n">
+        <v>216</v>
+      </c>
+      <c r="B217" s="2" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="C217" s="2" t="inlineStr">
+        <is>
+          <t>Tasks and skills (short block)</t>
+        </is>
+      </c>
+      <c r="D217" s="2" t="inlineStr">
+        <is>
+          <t>calc_at_work</t>
+        </is>
+      </c>
+      <c r="E217" s="2" t="inlineStr">
+        <is>
+          <t>yes/no</t>
+        </is>
+      </c>
+      <c r="F217" s="2" t="inlineStr">
+        <is>
+          <t>In your work, do you work out prices or costs?</t>
+        </is>
+      </c>
+      <c r="G217" s="2" t="inlineStr">
+        <is>
+          <t>अपने काम में क्या आप दाम या ख़र्चा जोड़ते-घटाते हैं?</t>
+        </is>
+      </c>
+      <c r="H217" s="2" t="inlineStr">
+        <is>
+          <t>0 No | 1 Yes</t>
+        </is>
+      </c>
+      <c r="I217" s="2" t="inlineStr"/>
+      <c r="J217" s="2" t="inlineStr">
+        <is>
+          <t>STEP module 6A</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J211"/>
+  <autoFilter ref="A1:J217"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -14053,7 +14341,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C129"/>
+  <dimension ref="A1:C135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="78" customWidth="1" min="1" max="1"/>
@@ -15176,7 +15464,7 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI</t>
+          <t>Lyons et al. 2023, Table 2 (area/settlement conditions), adapted to a labour-migrant setting</t>
         </is>
       </c>
       <c r="B75" s="2" t="n">
@@ -15184,14 +15472,14 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>electricity</t>
+          <t>accom_type_here</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI sanitation indicator (improved/unimproved and shared/not)</t>
+          <t>NITI Aayog National MPI</t>
         </is>
       </c>
       <c r="B76" s="2" t="n">
@@ -15199,14 +15487,14 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>toilet_type</t>
+          <t>electricity</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI drinking-water indicator (JMP improved/unimproved taxonomy)</t>
+          <t>NITI Aayog National MPI sanitation indicator (improved/unimproved and shared/not)</t>
         </is>
       </c>
       <c r="B77" s="2" t="n">
@@ -15214,14 +15502,14 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>drinking_water</t>
+          <t>toilet_type</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>Project design (intra-household burden of water collection; DHS/NFHS ask the same item)</t>
+          <t>NITI Aayog National MPI drinking-water indicator (JMP improved/unimproved taxonomy)</t>
         </is>
       </c>
       <c r="B78" s="2" t="n">
@@ -15229,14 +15517,14 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>water_fetched_by</t>
+          <t>drinking_water</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI cooking-fuel indicator (its own list of dirty fuels)</t>
+          <t>Project design (intra-household burden of water collection; DHS/NFHS ask the same item)</t>
         </is>
       </c>
       <c r="B79" s="2" t="n">
@@ -15244,14 +15532,14 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>cooking_fuel</t>
+          <t>water_fetched_by</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI assets indicator (car or truck limb)</t>
+          <t>NITI Aayog National MPI cooking-fuel indicator (its own list of dirty fuels)</t>
         </is>
       </c>
       <c r="B80" s="2" t="n">
@@ -15259,14 +15547,14 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>owns_car</t>
+          <t>cooking_fuel</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>Project design (pilot livelihood survey)</t>
+          <t>NITI Aayog National MPI assets indicator (car or truck limb)</t>
         </is>
       </c>
       <c r="B81" s="2" t="n">
@@ -15274,14 +15562,14 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>owns_pony_mule</t>
+          <t>owns_car</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI bank-account indicator; VEP adaptive-capacity covariate</t>
+          <t>Project design (pilot livelihood survey)</t>
         </is>
       </c>
       <c r="B82" s="2" t="n">
@@ -15289,14 +15577,14 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>has_bank_account</t>
+          <t>owns_pony_mule</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>VEP adaptive-capacity covariate</t>
+          <t>NITI Aayog National MPI bank-account indicator; VEP adaptive-capacity covariate</t>
         </is>
       </c>
       <c r="B83" s="2" t="n">
@@ -15304,14 +15592,14 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>took_loan_12m</t>
+          <t>has_bank_account</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>VEP adaptive-capacity covariate (lender type)</t>
+          <t>VEP adaptive-capacity covariate</t>
         </is>
       </c>
       <c r="B84" s="2" t="n">
@@ -15319,14 +15607,14 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>credit_source</t>
+          <t>took_loan_12m</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>Islam and Chowdhury 2025 (financial distress and household vulnerability to poverty)</t>
+          <t>VEP adaptive-capacity covariate (lender type)</t>
         </is>
       </c>
       <c r="B85" s="2" t="n">
@@ -15334,14 +15622,14 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>loan_amount</t>
+          <t>credit_source</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>Project design (informal lending is often interest-free)</t>
+          <t>Islam and Chowdhury 2025 (financial distress and household vulnerability to poverty)</t>
         </is>
       </c>
       <c r="B86" s="2" t="n">
@@ -15349,14 +15637,14 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>pays_interest</t>
+          <t>loan_amount</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>Project design (informal-credit pricing as locally quoted)</t>
+          <t>Project design (informal lending is often interest-free)</t>
         </is>
       </c>
       <c r="B87" s="2" t="n">
@@ -15364,14 +15652,14 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>loan_interest_per100_pm</t>
+          <t>pays_interest</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>Carter and Zimmerman 2000; Chiwaula et al. 2011 (asset-based vulnerability)</t>
+          <t>Project design (informal-credit pricing as locally quoted)</t>
         </is>
       </c>
       <c r="B88" s="2" t="n">
@@ -15379,14 +15667,14 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>loan_against_asset</t>
+          <t>loan_interest_per100_pm</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>Carter and Zimmerman 2000; Zimmerman and Carter 2003 (asset-based coping)</t>
+          <t>Carter and Zimmerman 2000; Chiwaula et al. 2011 (asset-based vulnerability)</t>
         </is>
       </c>
       <c r="B89" s="2" t="n">
@@ -15394,14 +15682,14 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>loan_collateral</t>
+          <t>loan_against_asset</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI health-insurance indicator; Lyons et al. 2023</t>
+          <t>Carter and Zimmerman 2000; Zimmerman and Carter 2003 (asset-based coping)</t>
         </is>
       </c>
       <c r="B90" s="2" t="n">
@@ -15409,14 +15697,14 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>n_health_insured</t>
+          <t>loan_collateral</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>Project design; scheme names as administered in Uttarakhand</t>
+          <t>NITI Aayog National MPI health-insurance indicator; Lyons et al. 2023</t>
         </is>
       </c>
       <c r="B91" s="2" t="n">
@@ -15424,14 +15712,14 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>govt_schemes</t>
+          <t>n_health_insured</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>Project design (intra-household financial capability)</t>
+          <t>Project design; scheme names as administered in Uttarakhand</t>
         </is>
       </c>
       <c r="B92" s="2" t="n">
@@ -15439,14 +15727,14 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>n_can_transact_online</t>
+          <t>govt_schemes</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>NSS health module (15-day recall) [source not held by this project; citation unverified as of 2026-09-28]</t>
+          <t>Lyons et al. 2023, Table 2 (legal residency), adapted; One Nation One Ration Card</t>
         </is>
       </c>
       <c r="B93" s="2" t="n">
@@ -15454,14 +15742,14 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>morbidity_15d</t>
+          <t>ration_portable_here</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>Project design (a reported illness with no cost/coping follow-up said nothing about its burden)</t>
+          <t>Project design (intra-household financial capability)</t>
         </is>
       </c>
       <c r="B94" s="2" t="n">
@@ -15469,14 +15757,14 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>morbidity_coping_15d</t>
+          <t>n_can_transact_online</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>NSS health module (365-day recall) [source not held by this project; citation unverified as of 2026-09-28]</t>
+          <t>NSS health module (15-day recall) [source not held by this project; citation unverified as of 2026-09-28]</t>
         </is>
       </c>
       <c r="B95" s="2" t="n">
@@ -15484,14 +15772,14 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>hospitalization_365d</t>
+          <t>morbidity_15d</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>VASyR 2025 barriers_health_case_access_phc_m (primary-care access barriers); Lyons et al. 2023 Table 2 indicator 2 'healthcare access'</t>
+          <t>Project design (a reported illness with no cost/coping follow-up said nothing about its burden)</t>
         </is>
       </c>
       <c r="B96" s="2" t="n">
@@ -15499,14 +15787,14 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>health_access_barrier_3m</t>
+          <t>morbidity_coping_15d</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI, Child and Adolescent Mortality (weight 1/12)</t>
+          <t>Washington Group on Disability Statistics, Short Set item 3 (mobility), verbatim; Lyons et al. 2023 health dimension</t>
         </is>
       </c>
       <c r="B97" s="2" t="n">
@@ -15514,14 +15802,14 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>child_death_5y</t>
+          <t>func_limitation</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI, Maternal Health (weight 1/12)</t>
+          <t>NSS health module (365-day recall) [source not held by this project; citation unverified as of 2026-09-28]</t>
         </is>
       </c>
       <c r="B98" s="2" t="n">
@@ -15529,14 +15817,14 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>birth_last_5y</t>
+          <t>hospitalization_365d</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI, Maternal Health (antenatal care limb)</t>
+          <t>VASyR 2025 barriers_health_case_access_phc_m (primary-care access barriers); Lyons et al. 2023 Table 2 indicator 2 'healthcare access'</t>
         </is>
       </c>
       <c r="B99" s="2" t="n">
@@ -15544,14 +15832,14 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>anc_4_visits</t>
+          <t>health_access_barrier_3m</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI, Maternal Health (assisted delivery limb)</t>
+          <t>NITI Aayog National MPI, Child and Adolescent Mortality (weight 1/12)</t>
         </is>
       </c>
       <c r="B100" s="2" t="n">
@@ -15559,14 +15847,14 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>skilled_birth_attendant</t>
+          <t>child_death_5y</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>VEP exposure covariate (Azeem et al. 2016); shock inventory following Gunther and Harttgen 2009, via Fujii 2016 section 4</t>
+          <t>NITI Aayog National MPI, Maternal Health (weight 1/12)</t>
         </is>
       </c>
       <c r="B101" s="2" t="n">
@@ -15574,14 +15862,14 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>distress_event_last365d</t>
+          <t>birth_last_5y</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>Coping strategies in VEP studies; Carter and Zimmerman 2000 on asset versus consumption smoothing</t>
+          <t>NITI Aayog National MPI, Maternal Health (antenatal care limb)</t>
         </is>
       </c>
       <c r="B102" s="2" t="n">
@@ -15589,14 +15877,14 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>shock_coping</t>
+          <t>anc_4_visits</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>Project design (see tasks_module W4: exposure must be asked directly)</t>
+          <t>NITI Aayog National MPI, Maternal Health (assisted delivery limb)</t>
         </is>
       </c>
       <c r="B103" s="2" t="n">
@@ -15604,14 +15892,14 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>trek_dependent</t>
+          <t>skilled_birth_attendant</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q5 (all eleven categories, with its own three-way routing)</t>
+          <t>VEP exposure covariate (Azeem et al. 2016); shock inventory following Gunther and Harttgen 2009, via Fujii 2016 section 4</t>
         </is>
       </c>
       <c r="B104" s="2" t="n">
@@ -15619,14 +15907,14 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>job_situation</t>
+          <t>distress_event_last365d</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q9</t>
+          <t>Project design (anchors the magnitude and timing pair)</t>
         </is>
       </c>
       <c r="B105" s="2" t="n">
@@ -15634,14 +15922,14 @@
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>job_permanence</t>
+          <t>shock_worst</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q11</t>
+          <t>Ligon and Schechter 2003; Dercon and Krishnan 2000 (VER needs shock magnitude, not only incidence)</t>
         </is>
       </c>
       <c r="B106" s="2" t="n">
@@ -15649,14 +15937,14 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>contract_status</t>
+          <t>shock_loss_amount</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q12 (widened to local registrations)</t>
+          <t>Dercon and Krishnan 2000 (seasonal timing of shocks); project design</t>
         </is>
       </c>
       <c r="B107" s="2" t="n">
@@ -15664,14 +15952,14 @@
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>workplace_registered</t>
+          <t>shock_month</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q16</t>
+          <t>Coping strategies in VEP studies; Carter and Zimmerman 2000 on asset versus consumption smoothing</t>
         </is>
       </c>
       <c r="B108" s="2" t="n">
@@ -15679,14 +15967,14 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>pension_contrib</t>
+          <t>shock_coping</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q17</t>
+          <t>Project design (see tasks_module W4: exposure must be asked directly)</t>
         </is>
       </c>
       <c r="B109" s="2" t="n">
@@ -15694,14 +15982,14 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>work_health_ins</t>
+          <t>trek_dependent</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q18</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q5 (all eleven categories, with its own three-way routing)</t>
         </is>
       </c>
       <c r="B110" s="2" t="n">
@@ -15709,14 +15997,14 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>leave_rights</t>
+          <t>job_situation</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q19</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q9</t>
         </is>
       </c>
       <c r="B111" s="2" t="n">
@@ -15724,14 +16012,14 @@
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>injured_ever</t>
+          <t>job_permanence</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q20</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q11</t>
         </is>
       </c>
       <c r="B112" s="2" t="n">
@@ -15739,14 +16027,14 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>workplace_injury_12m</t>
+          <t>contract_status</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q21</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q12 (widened to local registrations)</t>
         </is>
       </c>
       <c r="B113" s="2" t="n">
@@ -15754,14 +16042,14 @@
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>wants_more_work</t>
+          <t>workplace_registered</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q22</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q16</t>
         </is>
       </c>
       <c r="B114" s="2" t="n">
@@ -15769,14 +16057,14 @@
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>more_hours_day</t>
+          <t>pension_contrib</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q23 (duration in weeks, tied to the calendar instead of a single point in time)</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q17</t>
         </is>
       </c>
       <c r="B115" s="2" t="n">
@@ -15784,14 +16072,14 @@
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>months_looked_for_work</t>
+          <t>work_health_ins</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q24</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q18</t>
         </is>
       </c>
       <c r="B116" s="2" t="n">
@@ -15799,14 +16087,14 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>first_job_ever</t>
+          <t>leave_rights</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>Gathmann and Schonberg 2010; NCO 9333.0100 loader</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q19</t>
         </is>
       </c>
       <c r="B117" s="2" t="n">
@@ -15814,14 +16102,14 @@
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>tk_load</t>
+          <t>injured_ever</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>Spitz-Oener 2006 / STEP; NCO 8322.0100</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q20</t>
         </is>
       </c>
       <c r="B118" s="2" t="n">
@@ -15829,14 +16117,14 @@
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>tk_drive</t>
+          <t>workplace_injury_12m</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>Gathmann and Schonberg 2010; NCO 8343.1700 ropeway operator</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q21</t>
         </is>
       </c>
       <c r="B119" s="2" t="n">
@@ -15844,14 +16132,14 @@
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>tk_engine</t>
+          <t>wants_more_work</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>Spitz-Oener 2006; NCO 7411.0301 wireman</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q22</t>
         </is>
       </c>
       <c r="B120" s="2" t="n">
@@ -15859,14 +16147,14 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>tk_electric</t>
+          <t>more_hours_day</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>Gathmann and Schonberg 2010; NCO 8343.1700</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q23 (duration in weeks, tied to the calendar instead of a single point in time)</t>
         </is>
       </c>
       <c r="B121" s="2" t="n">
@@ -15874,14 +16162,14 @@
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>tk_safety</t>
+          <t>months_looked_for_work</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>Gathmann and Schonberg 2010; NCO 5223.0200</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q24</t>
         </is>
       </c>
       <c r="B122" s="2" t="n">
@@ -15889,14 +16177,14 @@
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>tk_sell</t>
+          <t>first_job_ever</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>Autor and Handel 2013; NCO 5131.0401</t>
+          <t>Gathmann and Schonberg 2010; NCO 9333.0100 loader</t>
         </is>
       </c>
       <c r="B123" s="2" t="n">
@@ -15904,14 +16192,14 @@
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>tk_cash</t>
+          <t>tk_load</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>NCO 5120.0300 cook</t>
+          <t>Spitz-Oener 2006 / STEP; NCO 8322.0100</t>
         </is>
       </c>
       <c r="B124" s="2" t="n">
@@ -15919,14 +16207,14 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>tk_cook</t>
+          <t>tk_drive</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>NCO 5131.0401 waiter; Pal et al. 2026</t>
+          <t>Gathmann and Schonberg 2010; NCO 8343.1700 ropeway operator</t>
         </is>
       </c>
       <c r="B125" s="2" t="n">
@@ -15934,14 +16222,14 @@
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>tk_serve</t>
+          <t>tk_engine</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>NCO 5151.0202 room attendant; Autor-Levy-Murnane 2003 (janitorial)</t>
+          <t>Spitz-Oener 2006; NCO 7411.0301 wireman</t>
         </is>
       </c>
       <c r="B126" s="2" t="n">
@@ -15949,14 +16237,14 @@
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>tk_clean</t>
+          <t>tk_electric</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>Gathmann and Schonberg 2010; NCO 5113.0200</t>
+          <t>Gathmann and Schonberg 2010; NCO 8343.1700</t>
         </is>
       </c>
       <c r="B127" s="2" t="n">
@@ -15964,14 +16252,14 @@
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>tk_guide</t>
+          <t>tk_safety</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>NCO 8343.1700 ropeway operator</t>
+          <t>Gathmann and Schonberg 2010; NCO 5223.0200</t>
         </is>
       </c>
       <c r="B128" s="2" t="n">
@@ -15979,14 +16267,14 @@
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>tk_coord</t>
+          <t>tk_sell</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>Level ladder without licences: people drive without holding a licence</t>
+          <t>Autor and Handel 2013; NCO 5131.0401</t>
         </is>
       </c>
       <c r="B129" s="2" t="n">
@@ -15994,12 +16282,102 @@
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
+          <t>tk_cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>NCO 5120.0300 cook</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>tk_cook</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>NCO 5131.0401 waiter; Pal et al. 2026</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>tk_serve</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>NCO 5151.0202 room attendant; Autor-Levy-Murnane 2003 (janitorial)</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>tk_clean</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>Gathmann and Schonberg 2010; NCO 5113.0200</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>tk_guide</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>NCO 8343.1700 ropeway operator</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>tk_coord</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>Level ladder without licences: people drive without holding a licence</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
           <t>drove_twowheeler</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C129"/>
+  <autoFilter ref="A1:C135"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -16137,7 +16515,7 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9">
@@ -16152,7 +16530,7 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10">
@@ -16167,7 +16545,7 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
@@ -16182,7 +16560,7 @@
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12">
@@ -16238,7 +16616,7 @@
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>210</v>
+        <v>216</v>
       </c>
     </row>
   </sheetData>

--- a/replication/final_instrument/questionnaire/Question_register.xlsx
+++ b/replication/final_instrument/questionnaire/Question_register.xlsx
@@ -13,9 +13,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Modules" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Questions'!$A$1:$J$217</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Questions'!$A$1:$J$212</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Constructed variables'!$A$1:$F$130</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Literature'!$A$1:$C$135</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Literature'!$A$1:$C$133</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Modules'!$A$1:$C$15</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J217"/>
+  <dimension ref="A1:J212"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1908,17 +1908,17 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Work and work history</t>
+          <t>Monthly calendar of work and income; remittances</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>training_type</t>
+          <t>status_m5</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -1928,27 +1928,23 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>What kind of course or training was it?</t>
+          <t>In May, what was your main work or activity?</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>वह किस तरह का कोर्स या ट्रेनिंग थी?</t>
+          <t>मई में आपका मुख्य काम या काम-धंधा क्या था?</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>1 ITI or other trade course | 2 Hotel, catering or tourism | 3 Driving | 4 Mobile, computer or electrical repair | 5 Tailoring or handicraft | 6 Animal handling or veterinary | 7 Construction trade (mason, carpenter, plumber) | 8 Health or first aid | 9 Other</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if training_received = 1</t>
-        </is>
-      </c>
+          <t>1 Yatra work, or getting ready for the season | 2 Farming (crops) | 3 Livestock (animals) | 4 Casual or daily wage labour | 5 Construction work | 6 Own small shop, stall or trade | 7 Salaried job | 8 No paid work</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr"/>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>STEP module 2</t>
+          <t>Monthly work calendar; seasonality of consumption and poverty per Dercon and Krishnan 2000 (their design is a three-round panel, not a monthly recall calendar -- the calendar format is project design)</t>
         </is>
       </c>
     </row>
@@ -1958,43 +1954,43 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Work and work history</t>
+          <t>Monthly calendar of work and income; remittances</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>training_type_other</t>
+          <t>status_m6</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>free text</t>
+          <t>select one</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>What was it? Write what they say.</t>
+          <t>In June, what was your main work or activity?</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>वह क्या थी? जैसा वे बताएँ वैसा लिख लीजिए।</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr"/>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if training_type = 9 (Other); may be left blank</t>
-        </is>
-      </c>
+          <t>जून में आपका मुख्य काम या काम-धंधा क्या था?</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>1 Yatra work, or getting ready for the season | 2 Farming (crops) | 3 Livestock (animals) | 4 Casual or daily wage labour | 5 Construction work | 6 Own small shop, stall or trade | 7 Salaried job | 8 No paid work</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr"/>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>STEP module 2</t>
+          <t>Monthly work calendar; seasonality of consumption and poverty per Dercon and Krishnan 2000 (their design is a three-round panel, not a monthly recall calendar -- the calendar format is project design)</t>
         </is>
       </c>
     </row>
@@ -2014,7 +2010,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>status_m5</t>
+          <t>status_m7</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -2024,12 +2020,12 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>In May, what was your main work or activity?</t>
+          <t>In July, what was your main work or activity?</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>मई में आपका मुख्य काम या काम-धंधा क्या था?</t>
+          <t>जुलाई में आपका मुख्य काम या काम-धंधा क्या था?</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -2060,7 +2056,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>status_m6</t>
+          <t>status_m8</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -2070,12 +2066,12 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>In June, what was your main work or activity?</t>
+          <t>In August, what was your main work or activity?</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>जून में आपका मुख्य काम या काम-धंधा क्या था?</t>
+          <t>अगस्त में आपका मुख्य काम या काम-धंधा क्या था?</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -2106,7 +2102,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>status_m7</t>
+          <t>status_m9</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -2116,12 +2112,12 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>In July, what was your main work or activity?</t>
+          <t>In September, what was your main work or activity?</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>जुलाई में आपका मुख्य काम या काम-धंधा क्या था?</t>
+          <t>सितंबर में आपका मुख्य काम या काम-धंधा क्या था?</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -2152,7 +2148,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>status_m8</t>
+          <t>status_m10</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -2162,12 +2158,12 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>In August, what was your main work or activity?</t>
+          <t>In October, what was your main work or activity?</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>अगस्त में आपका मुख्य काम या काम-धंधा क्या था?</t>
+          <t>अक्टूबर में आपका मुख्य काम या काम-धंधा क्या था?</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -2198,7 +2194,7 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>status_m9</t>
+          <t>status_m11</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -2208,12 +2204,12 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>In September, what was your main work or activity?</t>
+          <t>In November, what was your main work or activity?</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>सितंबर में आपका मुख्य काम या काम-धंधा क्या था?</t>
+          <t>नवंबर में आपका मुख्य काम या काम-धंधा क्या था?</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -2244,7 +2240,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>status_m10</t>
+          <t>status_m12</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -2254,12 +2250,12 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>In October, what was your main work or activity?</t>
+          <t>In December, what was your main work or activity?</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>अक्टूबर में आपका मुख्य काम या काम-धंधा क्या था?</t>
+          <t>दिसंबर में आपका मुख्य काम या काम-धंधा क्या था?</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -2290,7 +2286,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>status_m11</t>
+          <t>status_m1</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -2300,12 +2296,12 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>In November, what was your main work or activity?</t>
+          <t>In January, what was your main work or activity?</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>नवंबर में आपका मुख्य काम या काम-धंधा क्या था?</t>
+          <t>जनवरी में आपका मुख्य काम या काम-धंधा क्या था?</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -2336,7 +2332,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>status_m12</t>
+          <t>status_m2</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -2346,12 +2342,12 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>In December, what was your main work or activity?</t>
+          <t>In February, what was your main work or activity?</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>दिसंबर में आपका मुख्य काम या काम-धंधा क्या था?</t>
+          <t>फ़रवरी में आपका मुख्य काम या काम-धंधा क्या था?</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -2382,7 +2378,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>status_m1</t>
+          <t>status_m3</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -2392,12 +2388,12 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>In January, what was your main work or activity?</t>
+          <t>In March, what was your main work or activity?</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>जनवरी में आपका मुख्य काम या काम-धंधा क्या था?</t>
+          <t>मार्च में आपका मुख्य काम या काम-धंधा क्या था?</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -2428,7 +2424,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>status_m2</t>
+          <t>status_m4</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -2438,12 +2434,12 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>In February, what was your main work or activity?</t>
+          <t>In April, what was your main work or activity?</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>फ़रवरी में आपका मुख्य काम या काम-धंधा क्या था?</t>
+          <t>अप्रैल में आपका मुख्य काम या काम-धंधा क्या था?</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -2474,7 +2470,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>status_m3</t>
+          <t>knows_monthly_income</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -2484,23 +2480,23 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>In March, what was your main work or activity?</t>
+          <t>Can you tell me roughly what you earned in each month of the past year, or would it be easier to give one total for the whole year?</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>मार्च में आपका मुख्य काम या काम-धंधा क्या था?</t>
+          <t>क्या आप हर महीने की कमाई अलग-अलग बता सकते हैं, या पूरे साल का एक जोड़ बताना आसान रहेगा?</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>1 Yatra work, or getting ready for the season | 2 Farming (crops) | 3 Livestock (animals) | 4 Casual or daily wage labour | 5 Construction work | 6 Own small shop, stall or trade | 7 Salaried job | 8 No paid work</t>
+          <t>1 Month by month | 0 One total for the whole year</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr"/>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>Monthly work calendar; seasonality of consumption and poverty per Dercon and Krishnan 2000 (their design is a three-round panel, not a monthly recall calendar -- the calendar format is project design)</t>
+          <t>Apablaza et al. 2026 Q14/Q15 (the 'does not know' route out of monthly earnings)</t>
         </is>
       </c>
     </row>
@@ -2520,33 +2516,33 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>status_m4</t>
+          <t>income_m1</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>select one</t>
+          <t>amount (Rs)</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>In April, what was your main work or activity?</t>
+          <t>How much did you earn from all your work in January, after costs? (Rs)</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>अप्रैल में आपका मुख्य काम या काम-धंधा क्या था?</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>1 Yatra work, or getting ready for the season | 2 Farming (crops) | 3 Livestock (animals) | 4 Casual or daily wage labour | 5 Construction work | 6 Own small shop, stall or trade | 7 Salaried job | 8 No paid work</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="inlineStr"/>
+          <t>जनवरी में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr"/>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if knows_monthly_income = 1; automatic 0 if status_m1 = 8 (no paid work)</t>
+        </is>
+      </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>Monthly work calendar; seasonality of consumption and poverty per Dercon and Krishnan 2000 (their design is a three-round panel, not a monthly recall calendar -- the calendar format is project design)</t>
+          <t>Apablaza et al. 2026 Q14 (monthly earnings), asked month by month to avoid heaping on one typical figure</t>
         </is>
       </c>
     </row>
@@ -2566,33 +2562,33 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>knows_monthly_income</t>
+          <t>income_m2</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>select one</t>
+          <t>amount (Rs)</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>Can you tell me roughly what you earned in each month of the past year, or would it be easier to give one total for the whole year?</t>
+          <t>How much did you earn from all your work in February, after costs? (Rs)</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>क्या आप हर महीने की कमाई अलग-अलग बता सकते हैं, या पूरे साल का एक जोड़ बताना आसान रहेगा?</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>1 Month by month | 0 One total for the whole year</t>
-        </is>
-      </c>
-      <c r="I47" s="2" t="inlineStr"/>
+          <t>फ़रवरी में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr"/>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if knows_monthly_income = 1; automatic 0 if status_m2 = 8 (no paid work)</t>
+        </is>
+      </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026 Q14/Q15 (the 'does not know' route out of monthly earnings)</t>
+          <t>Apablaza et al. 2026 Q14 (monthly earnings), asked month by month to avoid heaping on one typical figure</t>
         </is>
       </c>
     </row>
@@ -2612,7 +2608,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>income_m1</t>
+          <t>income_m3</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -2622,18 +2618,18 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>How much did you earn from all your work in January, after costs? (Rs)</t>
+          <t>How much did you earn from all your work in March, after costs? (Rs)</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>जनवरी में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
+          <t>मार्च में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr"/>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>Ask only if knows_monthly_income = 1; automatic 0 if status_m1 = 8 (no paid work)</t>
+          <t>Ask only if knows_monthly_income = 1; automatic 0 if status_m3 = 8 (no paid work)</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -2658,7 +2654,7 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>income_m2</t>
+          <t>income_m4</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -2668,18 +2664,18 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>How much did you earn from all your work in February, after costs? (Rs)</t>
+          <t>How much did you earn from all your work in April, after costs? (Rs)</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>फ़रवरी में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
+          <t>अप्रैल में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr"/>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>Ask only if knows_monthly_income = 1; automatic 0 if status_m2 = 8 (no paid work)</t>
+          <t>Ask only if knows_monthly_income = 1; automatic 0 if status_m4 = 8 (no paid work)</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -2704,7 +2700,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>income_m3</t>
+          <t>income_m5</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -2714,18 +2710,18 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>How much did you earn from all your work in March, after costs? (Rs)</t>
+          <t>How much did you earn from all your work in May, after costs? (Rs)</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>मार्च में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
+          <t>मई में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr"/>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>Ask only if knows_monthly_income = 1; automatic 0 if status_m3 = 8 (no paid work)</t>
+          <t>Ask only if knows_monthly_income = 1; automatic 0 if status_m5 = 8 (no paid work)</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -2750,7 +2746,7 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>income_m4</t>
+          <t>income_m6</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -2760,18 +2756,18 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>How much did you earn from all your work in April, after costs? (Rs)</t>
+          <t>How much did you earn from all your work in June, after costs? (Rs)</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>अप्रैल में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
+          <t>जून में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr"/>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>Ask only if knows_monthly_income = 1; automatic 0 if status_m4 = 8 (no paid work)</t>
+          <t>Ask only if knows_monthly_income = 1; automatic 0 if status_m6 = 8 (no paid work)</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -2796,7 +2792,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>income_m5</t>
+          <t>income_m7</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -2806,18 +2802,18 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>How much did you earn from all your work in May, after costs? (Rs)</t>
+          <t>How much did you earn from all your work in July, after costs? (Rs)</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>मई में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
+          <t>जुलाई में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr"/>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>Ask only if knows_monthly_income = 1; automatic 0 if status_m5 = 8 (no paid work)</t>
+          <t>Ask only if knows_monthly_income = 1; automatic 0 if status_m7 = 8 (no paid work)</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -2842,7 +2838,7 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>income_m6</t>
+          <t>income_m8</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -2852,18 +2848,18 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>How much did you earn from all your work in June, after costs? (Rs)</t>
+          <t>How much did you earn from all your work in August, after costs? (Rs)</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>जून में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
+          <t>अगस्त में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr"/>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>Ask only if knows_monthly_income = 1; automatic 0 if status_m6 = 8 (no paid work)</t>
+          <t>Ask only if knows_monthly_income = 1; automatic 0 if status_m8 = 8 (no paid work)</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -2888,7 +2884,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>income_m7</t>
+          <t>income_m9</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -2898,18 +2894,18 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>How much did you earn from all your work in July, after costs? (Rs)</t>
+          <t>How much did you earn from all your work in September, after costs? (Rs)</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>जुलाई में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
+          <t>सितंबर में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr"/>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>Ask only if knows_monthly_income = 1; automatic 0 if status_m7 = 8 (no paid work)</t>
+          <t>Ask only if knows_monthly_income = 1; automatic 0 if status_m9 = 8 (no paid work)</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -2934,7 +2930,7 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>income_m8</t>
+          <t>income_m10</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -2944,18 +2940,18 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>How much did you earn from all your work in August, after costs? (Rs)</t>
+          <t>How much did you earn from all your work in October, after costs? (Rs)</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>अगस्त में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
+          <t>अक्टूबर में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr"/>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>Ask only if knows_monthly_income = 1; automatic 0 if status_m8 = 8 (no paid work)</t>
+          <t>Ask only if knows_monthly_income = 1; automatic 0 if status_m10 = 8 (no paid work)</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -2980,7 +2976,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>income_m9</t>
+          <t>income_m11</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -2990,18 +2986,18 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>How much did you earn from all your work in September, after costs? (Rs)</t>
+          <t>How much did you earn from all your work in November, after costs? (Rs)</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>सितंबर में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
+          <t>नवंबर में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr"/>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>Ask only if knows_monthly_income = 1; automatic 0 if status_m9 = 8 (no paid work)</t>
+          <t>Ask only if knows_monthly_income = 1; automatic 0 if status_m11 = 8 (no paid work)</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -3026,7 +3022,7 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>income_m10</t>
+          <t>income_m12</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -3036,18 +3032,18 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>How much did you earn from all your work in October, after costs? (Rs)</t>
+          <t>How much did you earn from all your work in December, after costs? (Rs)</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>अक्टूबर में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
+          <t>दिसंबर में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr"/>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>Ask only if knows_monthly_income = 1; automatic 0 if status_m10 = 8 (no paid work)</t>
+          <t>Ask only if knows_monthly_income = 1; automatic 0 if status_m12 = 8 (no paid work)</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -3072,7 +3068,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>income_m11</t>
+          <t>income_annual_total</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -3082,23 +3078,23 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>How much did you earn from all your work in November, after costs? (Rs)</t>
+          <t>Thinking of the whole past year, about how much did you earn in total from all your work, after costs? (Rs)</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>नवंबर में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
+          <t>पूरे पिछले साल को मिलाकर, सारे काम से ख़र्चा निकालकर आपने कुल कितना कमाया? (रुपये)</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr"/>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>Ask only if knows_monthly_income = 1; automatic 0 if status_m11 = 8 (no paid work)</t>
+          <t>Ask only if knows_monthly_income = 0</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026 Q14 (monthly earnings), asked month by month to avoid heaping on one typical figure</t>
+          <t>Apablaza et al. 2026 Q15 (fallback when monthly earnings are not known), adapted to an annual total for a seasonal workforce</t>
         </is>
       </c>
     </row>
@@ -3118,33 +3114,33 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>income_m12</t>
+          <t>pct_income_yatra</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>amount (Rs)</t>
+          <t>whole number</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>How much did you earn from all your work in December, after costs? (Rs)</t>
+          <t>Out of every 100 rupees you earned in the whole year, how many came from your Yatra work? (The rest is counted as coming from your other work.)</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>दिसंबर में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
+          <t>पूरे साल में आपने जो 100 रुपये कमाए, उनमें से कितने यात्रा के काम से आए? (बाकी दूसरे काम का माना जाएगा।)</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr"/>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>Ask only if knows_monthly_income = 1; automatic 0 if status_m12 = 8 (no paid work)</t>
+          <t>Ask only if knows_monthly_income = 0</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026 Q14 (monthly earnings), asked month by month to avoid heaping on one typical figure</t>
+          <t>Project design (the Yatra / non-Yatra split needed to reweight an annual total onto the work calendar)</t>
         </is>
       </c>
     </row>
@@ -3164,7 +3160,7 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>income_annual_total</t>
+          <t>remit_out_yatra_pm</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -3174,23 +3170,19 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>Thinking of the whole past year, about how much did you earn in total from all your work, after costs? (Rs)</t>
+          <t>In a normal month during the Yatra season, how much money do you usually send to family or others living elsewhere? (Rs, 0 if none)</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>पूरे पिछले साल को मिलाकर, सारे काम से ख़र्चा निकालकर आपने कुल कितना कमाया? (रुपये)</t>
+          <t>यात्रा के मौसम के आम महीने में, आप घर या कहीं और रहने वालों को कितना पैसा भेजते हैं? (रुपये, न भेजते हों तो 0)</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr"/>
-      <c r="I60" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if knows_monthly_income = 0</t>
-        </is>
-      </c>
+      <c r="I60" s="2" t="inlineStr"/>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026 Q15 (fallback when monthly earnings are not known), adapted to an annual total for a seasonal workforce</t>
+          <t>Project design (amount only; frequency dropped for length). A previous citation to NSS 64th Round practice was withdrawn 2026-09-28: no NSS schedule is held by this project and it could not be checked</t>
         </is>
       </c>
     </row>
@@ -3210,33 +3202,29 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>pct_income_yatra</t>
+          <t>remit_out_offseason_pm</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>whole number</t>
+          <t>amount (Rs)</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>Out of every 100 rupees you earned in the whole year, how many came from your Yatra work? (The rest is counted as coming from your other work.)</t>
+          <t>In a normal month when the Yatra is closed, how much do you usually send? (Rs, 0 if none)</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>पूरे साल में आपने जो 100 रुपये कमाए, उनमें से कितने यात्रा के काम से आए? (बाकी दूसरे काम का माना जाएगा।)</t>
+          <t>जब यात्रा बंद रहती है, उस आम महीने में कितना भेजते हैं? (रुपये, न भेजते हों तो 0)</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr"/>
-      <c r="I61" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if knows_monthly_income = 0</t>
-        </is>
-      </c>
+      <c r="I61" s="2" t="inlineStr"/>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>Project design (the Yatra / non-Yatra split needed to reweight an annual total onto the work calendar)</t>
+          <t>Project design (amount only; frequency dropped for length). A previous citation to NSS 64th Round practice was withdrawn 2026-09-28: no NSS schedule is held by this project and it could not be checked</t>
         </is>
       </c>
     </row>
@@ -3256,29 +3244,37 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>remit_out_yatra_pm</t>
+          <t>remit_mode</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>amount (Rs)</t>
+          <t>select one</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>In a normal month during the Yatra season, how much money do you usually send to family or others living elsewhere? (Rs, 0 if none)</t>
+          <t>How do you usually send it?</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम महीने में, आप घर या कहीं और रहने वालों को कितना पैसा भेजते हैं? (रुपये, न भेजते हों तो 0)</t>
-        </is>
-      </c>
-      <c r="H62" s="2" t="inlineStr"/>
-      <c r="I62" s="2" t="inlineStr"/>
+          <t>आप पैसा आम तौर पर कैसे भेजते हैं?</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>1 From my own phone (UPI or net banking) | 2 In person at a bank branch or bank mitra / CSP | 3 Money order or post office | 4 Sent with someone going home | 5 Carried it myself | 6 Through an agent or middleman | 7 Other</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if remit_out_yatra_pm &gt; 0 or remit_out_offseason_pm &gt; 0</t>
+        </is>
+      </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>Project design (amount only; frequency dropped for length). A previous citation to NSS 64th Round practice was withdrawn 2026-09-28: no NSS schedule is held by this project and it could not be checked</t>
+          <t>Project design (remittance channel as a financial-inclusion and cost measure)</t>
         </is>
       </c>
     </row>
@@ -3298,7 +3294,7 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>remit_out_offseason_pm</t>
+          <t>remit_in_yatra_pm</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -3308,12 +3304,12 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>In a normal month when the Yatra is closed, how much do you usually send? (Rs, 0 if none)</t>
+          <t>In a normal month during the Yatra season, how much money do you usually receive from family or others? (Rs, 0 if none)</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम महीने में कितना भेजते हैं? (रुपये, न भेजते हों तो 0)</t>
+          <t>यात्रा के मौसम के आम महीने में, घरवालों या किसी और से आपको कितना पैसा मिलता है? (रुपये, न मिलता हो तो 0)</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr"/>
@@ -3340,37 +3336,29 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>remit_mode</t>
+          <t>remit_in_offseason_pm</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>select one</t>
+          <t>amount (Rs)</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>How do you usually send it?</t>
+          <t>In a normal month when the Yatra is closed, how much do you usually receive? (Rs, 0 if none)</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>आप पैसा आम तौर पर कैसे भेजते हैं?</t>
-        </is>
-      </c>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t>1 From my own phone (UPI or net banking) | 2 In person at a bank branch or bank mitra / CSP | 3 Money order or post office | 4 Sent with someone going home | 5 Carried it myself | 6 Through an agent or middleman | 7 Other</t>
-        </is>
-      </c>
-      <c r="I64" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if remit_out_yatra_pm &gt; 0 or remit_out_offseason_pm &gt; 0</t>
-        </is>
-      </c>
+          <t>जब यात्रा बंद रहती है, उस आम महीने में कितना मिलता है? (रुपये, न मिलता हो तो 0)</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr"/>
+      <c r="I64" s="2" t="inlineStr"/>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>Project design (remittance channel as a financial-inclusion and cost measure)</t>
+          <t>Project design (amount only; frequency dropped for length). A previous citation to NSS 64th Round practice was withdrawn 2026-09-28: no NSS schedule is held by this project and it could not be checked</t>
         </is>
       </c>
     </row>
@@ -3390,29 +3378,33 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>remit_in_yatra_pm</t>
+          <t>hours_day_offseason</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>amount (Rs)</t>
+          <t>whole number</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>In a normal month during the Yatra season, how much money do you usually receive from family or others? (Rs, 0 if none)</t>
+          <t>In the months when the Yatra is closed and you are doing other work, on a normal working day, how many hours do you work in total?</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम महीने में, घरवालों या किसी और से आपको कितना पैसा मिलता है? (रुपये, न मिलता हो तो 0)</t>
+          <t>जिन महीनों में यात्रा बंद रहती है और आप कोई दूसरा काम करते हैं, उनमें आम दिन में आप कुल कितने घंटे काम करते हैं?</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr"/>
-      <c r="I65" s="2" t="inlineStr"/>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if any month in the calendar is other paid work (status 2 to 7)</t>
+        </is>
+      </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>Project design (amount only; frequency dropped for length). A previous citation to NSS 64th Round practice was withdrawn 2026-09-28: no NSS schedule is held by this project and it could not be checked</t>
+          <t>Apablaza et al. 2026 Q13, asked a second time for the off-season (decomposed as hours/day x days/week, as in the Yatra-season pair)</t>
         </is>
       </c>
     </row>
@@ -3432,29 +3424,33 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>remit_in_offseason_pm</t>
+          <t>days_week_offseason</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>amount (Rs)</t>
+          <t>whole number</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>In a normal month when the Yatra is closed, how much do you usually receive? (Rs, 0 if none)</t>
+          <t>In those months, how many days a week do you usually work?</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम महीने में कितना मिलता है? (रुपये, न मिलता हो तो 0)</t>
+          <t>उन महीनों में आप हफ़्ते में कितने दिन काम करते हैं?</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr"/>
-      <c r="I66" s="2" t="inlineStr"/>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if any month in the calendar is other paid work (status 2 to 7)</t>
+        </is>
+      </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>Project design (amount only; frequency dropped for length). A previous citation to NSS 64th Round practice was withdrawn 2026-09-28: no NSS schedule is held by this project and it could not be checked</t>
+          <t>Apablaza et al. 2026 Q13, asked a second time for the off-season</t>
         </is>
       </c>
     </row>
@@ -3464,43 +3460,43 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Monthly calendar of work and income; remittances</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>hours_day_offseason</t>
+          <t>origin</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>whole number</t>
+          <t>select one</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>In the months when the Yatra is closed and you are doing other work, on a normal working day, how many hours do you work in total?</t>
+          <t>Where is your permanent home?</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>जिन महीनों में यात्रा बंद रहती है और आप कोई दूसरा काम करते हैं, उनमें आम दिन में आप कुल कितने घंटे काम करते हैं?</t>
-        </is>
-      </c>
-      <c r="H67" s="2" t="inlineStr"/>
-      <c r="I67" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if any month in the calendar is other paid work (status 2 to 7)</t>
-        </is>
-      </c>
+          <t>आपका पक्का घर कहाँ है?</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>1 Local (same district) | 2 Other Uttarakhand district | 3 Other Indian state | 4 Nepal</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr"/>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026 Q13, asked a second time for the off-season (decomposed as hours/day x days/week, as in the Yatra-season pair)</t>
+          <t>Project design (distance bucket); NOT an NSS classification -- the earlier citation to one was withdrawn 2026-09-28, no NSS schedule is held by this project</t>
         </is>
       </c>
     </row>
@@ -3510,43 +3506,43 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Monthly calendar of work and income; remittances</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>days_week_offseason</t>
+          <t>home_state</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>whole number</t>
+          <t>select one</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>In those months, how many days a week do you usually work?</t>
+          <t>Which state is your permanent home in? (If it is outside India, say so.)</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>उन महीनों में आप हफ़्ते में कितने दिन काम करते हैं?</t>
-        </is>
-      </c>
-      <c r="H68" s="2" t="inlineStr"/>
-      <c r="I68" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if any month in the calendar is other paid work (status 2 to 7)</t>
-        </is>
-      </c>
+          <t>वह घर किस राज्य में है? (अगर भारत से बाहर है तो वह बताइए।)</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>1 Andhra Pradesh | 2 Arunachal Pradesh | 3 Assam | 4 Bihar | 5 Chhattisgarh | 6 Goa | 7 Gujarat | 8 Haryana | 9 Himachal Pradesh | 10 Jharkhand | 11 Karnataka | 12 Kerala | 13 Madhya Pradesh | 14 Maharashtra | 15 Manipur | 16 Meghalaya | 17 Mizoram | 18 Nagaland | 19 Odisha | 20 Punjab | 21 Rajasthan | 22 Sikkim | 23 Tamil Nadu | 24 Telangana | 25 Tripura | 26 Uttar Pradesh | 27 Uttarakhand | 28 West Bengal | 29 Andaman and Nicobar Islands | 30 Chandigarh | 31 Dadra and Nagar Haveli and Daman and Diu | 32 Delhi | 33 Jammu and Kashmir | 34 Ladakh | 35 Lakshadweep | 36 Puducherry | 99 Outside India</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr"/>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026 Q13, asked a second time for the off-season</t>
+          <t>Standard state/UT classification; needed to apply the right poverty line per respondent</t>
         </is>
       </c>
     </row>
@@ -3566,7 +3562,7 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>origin</t>
+          <t>home_rural_urban</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -3576,23 +3572,23 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>Where is your permanent home?</t>
+          <t>Is that home in a village, or in a town or city?</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>आपका पक्का घर कहाँ है?</t>
+          <t>वह घर गाँव में है, या क़स्बे या शहर में?</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>1 Local (same district) | 2 Other Uttarakhand district | 3 Other Indian state | 4 Nepal</t>
+          <t>1 Village (rural) | 2 Town or city (urban)</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr"/>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>Project design (distance bucket); NOT an NSS classification -- the earlier citation to one was withdrawn 2026-09-28, no NSS schedule is held by this project</t>
+          <t>Rural and urban poverty lines (Sethu et al. 2024)</t>
         </is>
       </c>
     </row>
@@ -3612,33 +3608,33 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>home_state</t>
+          <t>resp_returns_at_closure</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>select one</t>
+          <t>yes/no</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>Which state is your permanent home in? (If it is outside India, say so.)</t>
+          <t>When the Yatra closes for the season, do YOU go to your home place?</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>वह घर किस राज्य में है? (अगर भारत से बाहर है तो वह बताइए।)</t>
+          <t>जब यात्रा का मौसम ख़त्म हो जाता है, तो क्या आप अपने घर चले जाते हैं?</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>1 Andhra Pradesh | 2 Arunachal Pradesh | 3 Assam | 4 Bihar | 5 Chhattisgarh | 6 Goa | 7 Gujarat | 8 Haryana | 9 Himachal Pradesh | 10 Jharkhand | 11 Karnataka | 12 Kerala | 13 Madhya Pradesh | 14 Maharashtra | 15 Manipur | 16 Meghalaya | 17 Mizoram | 18 Nagaland | 19 Odisha | 20 Punjab | 21 Rajasthan | 22 Sikkim | 23 Tamil Nadu | 24 Telangana | 25 Tripura | 26 Uttar Pradesh | 27 Uttarakhand | 28 West Bengal | 29 Andaman and Nicobar Islands | 30 Chandigarh | 31 Dadra and Nagar Haveli and Daman and Diu | 32 Delhi | 33 Jammu and Kashmir | 34 Ladakh | 35 Lakshadweep | 36 Puducherry | 99 Outside India</t>
+          <t>0 No | 1 Yes</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr"/>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>Standard state/UT classification; needed to apply the right poverty line per respondent</t>
+          <t>Project design; categories from the pilot's own residency_pattern distribution (n=46)</t>
         </is>
       </c>
     </row>
@@ -3658,33 +3654,33 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>home_rural_urban</t>
+          <t>hh_at_home_place</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>select one</t>
+          <t>yes/no</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>Is that home in a village, or in a town or city?</t>
+          <t>And do the rest of your household live at your home place all year, or are they here with you during the season?</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>वह घर गाँव में है, या क़स्बे या शहर में?</t>
+          <t>और आपके बाक़ी घरवाले — वे साल भर आपके घर वाली जगह पर ही रहते हैं, या सीज़न में आपके साथ यहाँ रहते हैं?</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>1 Village (rural) | 2 Town or city (urban)</t>
+          <t>0 No | 1 Yes</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr"/>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>Rural and urban poverty lines (Sethu et al. 2024)</t>
+          <t>Project design (split-household measurement, underpinning Module E)</t>
         </is>
       </c>
     </row>
@@ -3704,33 +3700,33 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>resp_returns_at_closure</t>
+          <t>n_here_season</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>yes/no</t>
+          <t>whole number</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>When the Yatra closes for the season, do YOU go to your home place?</t>
+          <t>During the Yatra season, how many people are you feeding and spending on here, counting yourself?</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>जब यात्रा का मौसम ख़त्म हो जाता है, तो क्या आप अपने घर चले जाते हैं?</t>
-        </is>
-      </c>
-      <c r="H72" s="2" t="inlineStr">
-        <is>
-          <t>0 No | 1 Yes</t>
-        </is>
-      </c>
-      <c r="I72" s="2" t="inlineStr"/>
+          <t>यात्रा के मौसम में आप यहाँ कितने लोगों का खाना-ख़र्चा चलाते हैं, अपने आप को गिनकर?</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr"/>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if hh_at_home_place = 1</t>
+        </is>
+      </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>Project design; categories from the pilot's own residency_pattern distribution (n=46)</t>
+          <t>Project design (season-specific denominator for per-capita consumption)</t>
         </is>
       </c>
     </row>
@@ -3750,33 +3746,33 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>hh_at_home_place</t>
+          <t>years_coming_here</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>yes/no</t>
+          <t>whole number</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>And do the rest of your household live at your home place all year, or are they here with you during the season?</t>
+          <t>How many years have you been coming here for the Yatra season?</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>और आपके बाक़ी घरवाले — वे साल भर आपके घर वाली जगह पर ही रहते हैं, या सीज़न में आपके साथ यहाँ रहते हैं?</t>
-        </is>
-      </c>
-      <c r="H73" s="2" t="inlineStr">
-        <is>
-          <t>0 No | 1 Yes</t>
-        </is>
-      </c>
-      <c r="I73" s="2" t="inlineStr"/>
+          <t>आप कितने सालों से यात्रा के मौसम में यहाँ आ रहे हैं?</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr"/>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if resp_returns_at_closure = 1</t>
+        </is>
+      </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>Project design (split-household measurement, underpinning Module E)</t>
+          <t>Project design (duration of the seasonal relationship)</t>
         </is>
       </c>
     </row>
@@ -3796,33 +3792,37 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>n_here_season</t>
+          <t>came_here_reason</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>whole number</t>
+          <t>select one</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>During the Yatra season, how many people are you feeding and spending on here, counting yourself?</t>
+          <t>What was the main reason you first came here to work?</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम में आप यहाँ कितने लोगों का खाना-ख़र्चा चलाते हैं, अपने आप को गिनकर?</t>
-        </is>
-      </c>
-      <c r="H74" s="2" t="inlineStr"/>
+          <t>आप सबसे पहले यहाँ काम करने किस मुख्य वजह से आए थे?</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>1 No work at home | 2 Pay is better here | 3 Family or people from my village were already here | 4 Land at home is too little to live on | 5 Debt to repay | 6 A contractor or agent brought me | 7 Married into / moved with family | 8 Some other reason</t>
+        </is>
+      </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>Ask only if hh_at_home_place = 1</t>
+          <t>Ask only if origin is not Local (same district)</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>Project design (season-specific denominator for per-capita consumption)</t>
+          <t>Project design (push/pull as a vulnerability covariate)</t>
         </is>
       </c>
     </row>
@@ -3842,33 +3842,33 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>years_coming_here</t>
+          <t>worked_away_in_closure</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>whole number</t>
+          <t>yes/no</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>How many years have you been coming here for the Yatra season?</t>
+          <t>Last year, in the months when the Yatra was closed, did you go somewhere else for work?</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>आप कितने सालों से यात्रा के मौसम में यहाँ आ रहे हैं?</t>
-        </is>
-      </c>
-      <c r="H75" s="2" t="inlineStr"/>
-      <c r="I75" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if resp_returns_at_closure = 1</t>
-        </is>
-      </c>
+          <t>पिछले साल, जिन महीनों में यात्रा बंद थी, क्या आप काम के लिए कहीं और गए थे?</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>0 No | 1 Yes</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr"/>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>Project design (duration of the seasonal relationship)</t>
+          <t>Project design (off-season labour migration)</t>
         </is>
       </c>
     </row>
@@ -3888,37 +3888,33 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>came_here_reason</t>
+          <t>closure_work_detail</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>select one</t>
+          <t>free text</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>What was the main reason you first came here to work?</t>
+          <t>Where did you go, and what work did you do there? Write what they say.</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>आप सबसे पहले यहाँ काम करने किस मुख्य वजह से आए थे?</t>
-        </is>
-      </c>
-      <c r="H76" s="2" t="inlineStr">
-        <is>
-          <t>1 No work at home | 2 Pay is better here | 3 Family or people from my village were already here | 4 Land at home is too little to live on | 5 Debt to repay | 6 A contractor or agent brought me | 7 Married into / moved with family | 8 Some other reason</t>
-        </is>
-      </c>
+          <t>कहाँ गए थे, और वहाँ क्या काम किया? जैसा वे बताएँ वैसा लिख लीजिए।</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr"/>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>Ask only if origin is not Local (same district)</t>
+          <t>Ask only if worked_away_in_closure = 1; may be left blank</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>Project design (push/pull as a vulnerability covariate)</t>
+          <t>Project design; coded to NCO-2015 in the office</t>
         </is>
       </c>
     </row>
@@ -3938,33 +3934,37 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>worked_away_in_closure</t>
+          <t>left_here_month</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>yes/no</t>
+          <t>select one</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>Last year, in the months when the Yatra was closed, did you go somewhere else for work?</t>
+          <t>In the past year, which month did you last leave here and go to your home place?</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>पिछले साल, जिन महीनों में यात्रा बंद थी, क्या आप काम के लिए कहीं और गए थे?</t>
+          <t>पिछले साल आप यहाँ से आख़िरी बार किस महीने अपने घर गए थे?</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>0 No | 1 Yes</t>
-        </is>
-      </c>
-      <c r="I77" s="2" t="inlineStr"/>
+          <t>1 January | 2 February | 3 March | 4 April | 5 May | 6 June | 7 July | 8 August | 9 September | 10 October | 11 November | 12 December</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if resp_returns_at_closure = 1</t>
+        </is>
+      </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>Project design (off-season labour migration)</t>
+          <t>Project design (measured seasonal base, asked as a spell)</t>
         </is>
       </c>
     </row>
@@ -3984,33 +3984,37 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>closure_work_detail</t>
+          <t>returned_here_month</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>free text</t>
+          <t>select one</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>Where did you go, and what work did you do there? Write what they say.</t>
+          <t>And which month did you come back here?</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>कहाँ गए थे, और वहाँ क्या काम किया? जैसा वे बताएँ वैसा लिख लीजिए।</t>
-        </is>
-      </c>
-      <c r="H78" s="2" t="inlineStr"/>
+          <t>और किस महीने आप वापस यहाँ आए?</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>1 January | 2 February | 3 March | 4 April | 5 May | 6 June | 7 July | 8 August | 9 September | 10 October | 11 November | 12 December</t>
+        </is>
+      </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>Ask only if worked_away_in_closure = 1; may be left blank</t>
+          <t>Ask only if resp_returns_at_closure = 1</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>Project design; coded to NCO-2015 in the office</t>
+          <t>Project design (measured seasonal base, asked as a spell)</t>
         </is>
       </c>
     </row>
@@ -4030,37 +4034,33 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>left_here_month</t>
+          <t>months_away_for_work</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>select one</t>
+          <t>whole number</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>In the past year, which month did you last leave here and go to your home place?</t>
+          <t>In those months away, how many months did you spend working somewhere other than your home place?</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>पिछले साल आप यहाँ से आख़िरी बार किस महीने अपने घर गए थे?</t>
-        </is>
-      </c>
-      <c r="H79" s="2" t="inlineStr">
-        <is>
-          <t>1 January | 2 February | 3 March | 4 April | 5 May | 6 June | 7 July | 8 August | 9 September | 10 October | 11 November | 12 December</t>
-        </is>
-      </c>
+          <t>बाहर रहे उन महीनों में, कितने महीने आपने अपने घर से हटकर कहीं और काम किया?</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr"/>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>Ask only if resp_returns_at_closure = 1</t>
+          <t>Ask only if worked_away_in_closure = 1</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>Project design (measured seasonal base, asked as a spell)</t>
+          <t>Project design (off-season labour migration)</t>
         </is>
       </c>
     </row>
@@ -4080,37 +4080,33 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>returned_here_month</t>
+          <t>worked_other_places</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>select one</t>
+          <t>yes/no</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>And which month did you come back here?</t>
+          <t>Before you started coming here, had you gone anywhere else for work?</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>और किस महीने आप वापस यहाँ आए?</t>
+          <t>यहाँ आना शुरू करने से पहले, क्या आप काम के लिए कहीं और गए थे?</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>1 January | 2 February | 3 March | 4 April | 5 May | 6 June | 7 July | 8 August | 9 September | 10 October | 11 November | 12 December</t>
-        </is>
-      </c>
-      <c r="I80" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if resp_returns_at_closure = 1</t>
-        </is>
-      </c>
+          <t>0 No | 1 Yes</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr"/>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>Project design (measured seasonal base, asked as a spell)</t>
+          <t>Project design (revealed mobility, for the transferability paper)</t>
         </is>
       </c>
     </row>
@@ -4130,33 +4126,33 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>months_away_for_work</t>
+          <t>other_places_detail</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>whole number</t>
+          <t>free text</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>In those months away, how many months did you spend working somewhere other than your home place?</t>
+          <t>Where did you go, and what work did you do? Write what they say.</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>बाहर रहे उन महीनों में, कितने महीने आपने अपने घर से हटकर कहीं और काम किया?</t>
+          <t>कहाँ गए थे, और वहाँ क्या काम किया? जैसा वे बताएँ वैसा लिख लीजिए।</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr"/>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>Ask only if worked_away_in_closure = 1</t>
+          <t>Ask only if worked_other_places = 1; may be left blank</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>Project design (off-season labour migration)</t>
+          <t>Project design; coded to NCO-2015 in the office</t>
         </is>
       </c>
     </row>
@@ -4176,33 +4172,33 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>worked_other_places</t>
+          <t>would_move_for_work</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>yes/no</t>
+          <t>select one</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>Before you started coming here, had you gone anywhere else for work?</t>
+          <t>If this work here ended, would you go away from your home place to look for work in the coming year?</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>यहाँ आना शुरू करने से पहले, क्या आप काम के लिए कहीं और गए थे?</t>
+          <t>अगर यहाँ का यह काम बंद हो जाए, तो क्या आप आने वाले साल में काम ढूँढने अपने घर से बाहर जाएँगे?</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>0 No | 1 Yes</t>
+          <t>0 No | 1 Yes | 97 Don't know</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr"/>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>Project design (revealed mobility, for the transferability paper)</t>
+          <t>Project design; horizoned intention item after VASyR 2025 (move_accom_yesno, asked over a stated 6-month horizon)</t>
         </is>
       </c>
     </row>
@@ -4222,33 +4218,33 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>other_places_detail</t>
+          <t>migration_referral</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>free text</t>
+          <t>select one</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>Where did you go, and what work did you do? Write what they say.</t>
+          <t>Who mainly helped you get this work, or arranged it for you?</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>कहाँ गए थे, और वहाँ क्या काम किया? जैसा वे बताएँ वैसा लिख लीजिए।</t>
-        </is>
-      </c>
-      <c r="H83" s="2" t="inlineStr"/>
-      <c r="I83" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if worked_other_places = 1; may be left blank</t>
-        </is>
-      </c>
+          <t>यहाँ आने या यह काम पकड़ने में मुख्य रूप से किसने मदद की या रास्ता दिखाया: यहाँ पहले से रह रहा कोई घरवाला; कोई दोस्त या जान-पहचान वाला; कोई ठेकेदार या एजेंट; कोई नेता या समाज का बड़ा आदमी; कोई नहीं, आपने खुद ढूँढा; मालिक ने सीधे बुलाया; या कोई और?</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>1 A family member already working here | 2 A friend or someone from the village | 3 A thekedar or contractor I now work for | 4 An agent or middleman who placed me (usually for a fee) | 5 No one; I found it myself | 6 The employer called me directly | 7 Someone else</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr"/>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>Project design; coded to NCO-2015 in the office</t>
+          <t>Project design (referral channel as a proxy for social capital and for placement debt)</t>
         </is>
       </c>
     </row>
@@ -4268,33 +4264,33 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>would_move_for_work</t>
+          <t>migration_referral_other</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>select one</t>
+          <t>free text</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>If this work here ended, would you go away from your home place to look for work in the coming year?</t>
+          <t>Who was it? Write what they say.</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>अगर यहाँ का यह काम बंद हो जाए, तो क्या आप आने वाले साल में काम ढूँढने अपने घर से बाहर जाएँगे?</t>
-        </is>
-      </c>
-      <c r="H84" s="2" t="inlineStr">
-        <is>
-          <t>0 No | 1 Yes | 97 Don't know</t>
-        </is>
-      </c>
-      <c r="I84" s="2" t="inlineStr"/>
+          <t>वे कौन थे? जैसा वे बताएँ वैसा लिख लीजिए।</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr"/>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if migration_referral = 7 (Other); may be left blank</t>
+        </is>
+      </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>Project design; horizoned intention item after VASyR 2025 (move_accom_yesno, asked over a stated 6-month horizon)</t>
+          <t>Standard household-survey item</t>
         </is>
       </c>
     </row>
@@ -4304,43 +4300,43 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Household consumption</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>migration_referral</t>
+          <t>spend_differs_by_season</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>select one</t>
+          <t>yes/no</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>Who mainly helped you get this work, or arranged it for you?</t>
+          <t>Leaving aside money you send home -- is what your household spends in a normal month during the Yatra season different from what it spends when the Yatra is closed?</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>यहाँ आने या यह काम पकड़ने में मुख्य रूप से किसने मदद की या रास्ता दिखाया: यहाँ पहले से रह रहा कोई घरवाला; कोई दोस्त या जान-पहचान वाला; कोई ठेकेदार या एजेंट; कोई नेता या समाज का बड़ा आदमी; कोई नहीं, आपने खुद ढूँढा; मालिक ने सीधे बुलाया; या कोई और?</t>
+          <t>घर भेजे जाने वाले पैसे को छोड़कर — यात्रा के मौसम में आपके घर का महीने का ख़र्च, और जब यात्रा बंद रहती है तब का ख़र्च, क्या अलग-अलग होता है?</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>1 A family member already working here | 2 A friend or someone from the village | 3 A thekedar or contractor I now work for | 4 An agent or middleman who placed me (usually for a fee) | 5 No one; I found it myself | 6 The employer called me directly | 7 Someone else</t>
+          <t>0 No | 1 Yes</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr"/>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>Project design (referral channel as a proxy for social capital and for placement debt)</t>
+          <t>Project design (respondent-gated seasonal recall); the underlying two-season design follows Beegle et al. 2012 and Deaton and Grosh 2000 on usual-period recall</t>
         </is>
       </c>
     </row>
@@ -4350,43 +4346,39 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Household consumption</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>migration_referral_other</t>
+          <t>cons_staples_yatra_pm</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>free text</t>
+          <t>amount (Rs)</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>Who was it? Write what they say.</t>
+          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on cereals (rice, wheat, other grains), pulses, sugar and salt, bought or from your own stock? (Rs)</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>वे कौन थे? जैसा वे बताएँ वैसा लिख लीजिए।</t>
+          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) अनाज (चावल, गेहूँ, दूसरा अनाज), दाल, चीनी और नमक पर, ख़रीदा हुआ या अपने घर का कितना ख़र्च करते हैं? (रुपये)</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr"/>
-      <c r="I86" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if migration_referral = 7 (Other); may be left blank</t>
-        </is>
-      </c>
+      <c r="I86" s="2" t="inlineStr"/>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>Standard household-survey item</t>
+          <t>HCES 2022-23, MoSPI Appendix A, Sections 5.1-5.3 (30-day); IHDS-II Income and Social Capital Questionnaire, Q14 14.1-14.6 (30-day, same items)</t>
         </is>
       </c>
     </row>
@@ -4406,33 +4398,33 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>spend_differs_by_season</t>
+          <t>cons_staples_offseason_pm</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>yes/no</t>
+          <t>amount (Rs)</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>Leaving aside money you send home -- is what your household spends in a normal month during the Yatra season different from what it spends when the Yatra is closed?</t>
+          <t>In a normal month when the Yatra is closed, how much does your household spend on cereals (rice, wheat, other grains), pulses, sugar and salt, bought or from your own stock? (Rs)</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>घर भेजे जाने वाले पैसे को छोड़कर — यात्रा के मौसम में आपके घर का महीने का ख़र्च, और जब यात्रा बंद रहती है तब का ख़र्च, क्या अलग-अलग होता है?</t>
-        </is>
-      </c>
-      <c r="H87" s="2" t="inlineStr">
-        <is>
-          <t>0 No | 1 Yes</t>
-        </is>
-      </c>
-      <c r="I87" s="2" t="inlineStr"/>
+          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर अनाज (चावल, गेहूँ, दूसरा अनाज), दाल, चीनी और नमक पर, ख़रीदा हुआ या अपने घर का कितना ख़र्च करता है? (रुपये)</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr"/>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if spend_differs_by_season = 1</t>
+        </is>
+      </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>Project design (respondent-gated seasonal recall); the underlying two-season design follows Beegle et al. 2012 and Deaton and Grosh 2000 on usual-period recall</t>
+          <t>HCES 2022-23, MoSPI Appendix A, Sections 5.1-5.3 (30-day); IHDS-II Income and Social Capital Questionnaire, Q14 14.1-14.6 (30-day, same items)</t>
         </is>
       </c>
     </row>
@@ -4452,7 +4444,7 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>cons_staples_yatra_pm</t>
+          <t>cons_perishables_yatra_pm</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -4462,19 +4454,19 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on cereals (rice, wheat, other grains), pulses, sugar and salt, bought or from your own stock? (Rs)</t>
+          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on milk and milk products, vegetables, fruit, egg/fish/meat, cooking oil, spices, and tea or coffee, bought or from your own stock? (Rs)</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) अनाज (चावल, गेहूँ, दूसरा अनाज), दाल, चीनी और नमक पर, ख़रीदा हुआ या अपने घर का कितना ख़र्च करते हैं? (रुपये)</t>
+          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) दूध और दूध की चीज़ें, सब्ज़ी, फल, अंडा/मछली/मांस, तेल, मसाले, और चाय पर कितना ख़र्च करते हैं? (रुपये)</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr"/>
       <c r="I88" s="2" t="inlineStr"/>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>HCES 2022-23, MoSPI Appendix A, Sections 5.1-5.3 (30-day); IHDS-II Income and Social Capital Questionnaire, Q14 14.1-14.6 (30-day, same items)</t>
+          <t>HCES 2022-23, MoSPI Appendix A, Sections 6.1-6.8 (7-day actual recall in HCES; asked here as a usual monthly figure instead, for the reason above)</t>
         </is>
       </c>
     </row>
@@ -4494,7 +4486,7 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>cons_staples_offseason_pm</t>
+          <t>cons_perishables_offseason_pm</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
@@ -4504,12 +4496,12 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>In a normal month when the Yatra is closed, how much does your household spend on cereals (rice, wheat, other grains), pulses, sugar and salt, bought or from your own stock? (Rs)</t>
+          <t>In a normal month when the Yatra is closed, how much does your household spend on milk and milk products, vegetables, fruit, egg/fish/meat, cooking oil, spices, and tea or coffee, bought or from your own stock? (Rs)</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर अनाज (चावल, गेहूँ, दूसरा अनाज), दाल, चीनी और नमक पर, ख़रीदा हुआ या अपने घर का कितना ख़र्च करता है? (रुपये)</t>
+          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर दूध और दूध की चीज़ें, सब्ज़ी, फल, अंडा/मछली/मांस, तेल, मसाले, और चाय पर कितना ख़र्च करता है? (रुपये)</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr"/>
@@ -4520,7 +4512,7 @@
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>HCES 2022-23, MoSPI Appendix A, Sections 5.1-5.3 (30-day); IHDS-II Income and Social Capital Questionnaire, Q14 14.1-14.6 (30-day, same items)</t>
+          <t>HCES 2022-23, MoSPI Appendix A, Sections 6.1-6.8 (7-day actual recall in HCES; asked here as a usual monthly figure instead, for the reason above)</t>
         </is>
       </c>
     </row>
@@ -4540,7 +4532,7 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>cons_perishables_yatra_pm</t>
+          <t>cons_food_own_yatra_pm</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -4550,19 +4542,19 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on milk and milk products, vegetables, fruit, egg/fish/meat, cooking oil, spices, and tea or coffee, bought or from your own stock? (Rs)</t>
+          <t>If you (and anyone staying with you here) had not grown, raised or been given any of your food, about how much would it have cost to buy in a normal month during the Yatra season? (Rs, 0 if you buy everything)</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) दूध और दूध की चीज़ें, सब्ज़ी, फल, अंडा/मछली/मांस, तेल, मसाले, और चाय पर कितना ख़र्च करते हैं? (रुपये)</t>
+          <t>अगर आप (और जो यहाँ आपके साथ रहते हैं) अपना खाना ख़ुद न उगाते, न पालते और न किसी से मिलता, तो यात्रा के मौसम के आम महीने में उसे ख़रीदने में लगभग कितना लगता? (रुपये, सब ख़रीदते हों तो 0)</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr"/>
       <c r="I90" s="2" t="inlineStr"/>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>HCES 2022-23, MoSPI Appendix A, Sections 6.1-6.8 (7-day actual recall in HCES; asked here as a usual monthly figure instead, for the reason above)</t>
+          <t>Calvo and Dercon 2007; Eze and Iheonu 2025 (non-purchased food, aggregate approach)</t>
         </is>
       </c>
     </row>
@@ -4582,7 +4574,7 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>cons_perishables_offseason_pm</t>
+          <t>cons_food_own_offseason_pm</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
@@ -4592,12 +4584,12 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>In a normal month when the Yatra is closed, how much does your household spend on milk and milk products, vegetables, fruit, egg/fish/meat, cooking oil, spices, and tea or coffee, bought or from your own stock? (Rs)</t>
+          <t>If your household had not grown, raised or been given any of your food, about how much would it have cost to buy in a normal month when the Yatra is closed? (Rs, 0 if you buy everything)</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर दूध और दूध की चीज़ें, सब्ज़ी, फल, अंडा/मछली/मांस, तेल, मसाले, और चाय पर कितना ख़र्च करता है? (रुपये)</t>
+          <t>अगर आपका घर अपना खाना ख़ुद न उगाता, न पालता और न किसी से मिलता, तो जब यात्रा बंद रहती है उस आम महीने में उसे ख़रीदने में लगभग कितना लगता? (रुपये, सब ख़रीदते हों तो 0)</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr"/>
@@ -4608,7 +4600,7 @@
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>HCES 2022-23, MoSPI Appendix A, Sections 6.1-6.8 (7-day actual recall in HCES; asked here as a usual monthly figure instead, for the reason above)</t>
+          <t>Calvo and Dercon 2007; Eze and Iheonu 2025 (non-purchased food, aggregate approach)</t>
         </is>
       </c>
     </row>
@@ -4628,7 +4620,7 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>cons_food_own_yatra_pm</t>
+          <t>cons_food_out_yatra_pm</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -4638,19 +4630,19 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>If you (and anyone staying with you here) had not grown, raised or been given any of your food, about how much would it have cost to buy in a normal month during the Yatra season? (Rs, 0 if you buy everything)</t>
+          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on meals, tea and snacks eaten outside the home, including any an employer gave free, at their market value? (Rs)</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>अगर आप (और जो यहाँ आपके साथ रहते हैं) अपना खाना ख़ुद न उगाते, न पालते और न किसी से मिलता, तो यात्रा के मौसम के आम महीने में उसे ख़रीदने में लगभग कितना लगता? (रुपये, सब ख़रीदते हों तो 0)</t>
+          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) बाहर खाए गए खाने, चाय और नाश्ते पर, मालिक ने मुफ़्त दिया हो तो उसकी क़ीमत मिलाकर कितना ख़र्च करते हैं? (रुपये)</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr"/>
       <c r="I92" s="2" t="inlineStr"/>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>Calvo and Dercon 2007; Eze and Iheonu 2025 (non-purchased food, aggregate approach)</t>
+          <t>HCES 2022-23, MoSPI Appendix A, Section 7.1 'served processed food' (7-day in HCES; usual monthly here)</t>
         </is>
       </c>
     </row>
@@ -4670,7 +4662,7 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>cons_food_own_offseason_pm</t>
+          <t>cons_food_out_offseason_pm</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
@@ -4680,12 +4672,12 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>If your household had not grown, raised or been given any of your food, about how much would it have cost to buy in a normal month when the Yatra is closed? (Rs, 0 if you buy everything)</t>
+          <t>In a normal month when the Yatra is closed, how much does your household spend on meals, tea and snacks eaten outside the home, including any an employer gave free, at their market value? (Rs)</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>अगर आपका घर अपना खाना ख़ुद न उगाता, न पालता और न किसी से मिलता, तो जब यात्रा बंद रहती है उस आम महीने में उसे ख़रीदने में लगभग कितना लगता? (रुपये, सब ख़रीदते हों तो 0)</t>
+          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर बाहर खाए गए खाने, चाय और नाश्ते पर, मालिक ने मुफ़्त दिया हो तो उसकी क़ीमत मिलाकर कितना ख़र्च करता है? (रुपये)</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr"/>
@@ -4696,7 +4688,7 @@
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>Calvo and Dercon 2007; Eze and Iheonu 2025 (non-purchased food, aggregate approach)</t>
+          <t>HCES 2022-23, MoSPI Appendix A, Section 7.1 'served processed food' (7-day in HCES; usual monthly here)</t>
         </is>
       </c>
     </row>
@@ -4716,7 +4708,7 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>cons_food_out_yatra_pm</t>
+          <t>cons_fuel_yatra_pm</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -4726,19 +4718,19 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on meals, tea and snacks eaten outside the home, including any an employer gave free, at their market value? (Rs)</t>
+          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on fuel and light: cooking fuel, firewood, electricity, kerosene, candles? (Rs)</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) बाहर खाए गए खाने, चाय और नाश्ते पर, मालिक ने मुफ़्त दिया हो तो उसकी क़ीमत मिलाकर कितना ख़र्च करते हैं? (रुपये)</t>
+          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) ईंधन और रोशनी पर: खाना बनाने की गैस, लकड़ी, बिजली, मिट्टी का तेल, मोमबत्ती कितना ख़र्च करते हैं? (रुपये)</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr"/>
       <c r="I94" s="2" t="inlineStr"/>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>HCES 2022-23, MoSPI Appendix A, Section 7.1 'served processed food' (7-day in HCES; usual monthly here)</t>
+          <t>HCES 2022-23, MoSPI Appendix A, Section 8.1 (30-day). IHDS-II Income and Social Capital Questionnaire, Q14 14.21-14.22. Nigeria GHS-Panel Wave 3, Household Questionnaire, Sections 10B/11 (30-day tier)</t>
         </is>
       </c>
     </row>
@@ -4758,7 +4750,7 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>cons_food_out_offseason_pm</t>
+          <t>cons_fuel_offseason_pm</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
@@ -4768,12 +4760,12 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>In a normal month when the Yatra is closed, how much does your household spend on meals, tea and snacks eaten outside the home, including any an employer gave free, at their market value? (Rs)</t>
+          <t>In a normal month when the Yatra is closed, how much does your household spend on fuel and light: cooking fuel, firewood, electricity, kerosene, candles? (Rs)</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर बाहर खाए गए खाने, चाय और नाश्ते पर, मालिक ने मुफ़्त दिया हो तो उसकी क़ीमत मिलाकर कितना ख़र्च करता है? (रुपये)</t>
+          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर ईंधन और रोशनी पर: खाना बनाने की गैस, लकड़ी, बिजली, मिट्टी का तेल, मोमबत्ती कितना ख़र्च करता है? (रुपये)</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr"/>
@@ -4784,7 +4776,7 @@
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>HCES 2022-23, MoSPI Appendix A, Section 7.1 'served processed food' (7-day in HCES; usual monthly here)</t>
+          <t>HCES 2022-23, MoSPI Appendix A, Section 8.1 (30-day). IHDS-II Income and Social Capital Questionnaire, Q14 14.21-14.22. Nigeria GHS-Panel Wave 3, Household Questionnaire, Sections 10B/11 (30-day tier)</t>
         </is>
       </c>
     </row>
@@ -4804,7 +4796,7 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>cons_fuel_yatra_pm</t>
+          <t>cons_routine_misc_yatra_pm</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -4814,19 +4806,19 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on fuel and light: cooking fuel, firewood, electricity, kerosene, candles? (Rs)</t>
+          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on soap, toiletries, cleaning goods and other small household items? (Rs)</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) ईंधन और रोशनी पर: खाना बनाने की गैस, लकड़ी, बिजली, मिट्टी का तेल, मोमबत्ती कितना ख़र्च करते हैं? (रुपये)</t>
+          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) साबुन, नहाने-धोने का सामान, सफ़ाई का सामान और घर की दूसरी छोटी चीज़ों पर कितना ख़र्च करते हैं? (रुपये)</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr"/>
       <c r="I96" s="2" t="inlineStr"/>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>HCES 2022-23, MoSPI Appendix A, Section 8.1 (30-day). IHDS-II Income and Social Capital Questionnaire, Q14 14.21-14.22. Nigeria GHS-Panel Wave 3, Household Questionnaire, Sections 10B/11 (30-day tier)</t>
+          <t>HCES 2022-23, MoSPI Appendix A, Sections 9.1-9.2 (30-day). IHDS-II Income and Social Capital Questionnaire, Q14 14.25-14.27. Nigeria GHS-Panel Wave 3, Household Questionnaire, Sections 10B/11 (30-day tier)</t>
         </is>
       </c>
     </row>
@@ -4846,7 +4838,7 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>cons_fuel_offseason_pm</t>
+          <t>cons_routine_misc_offseason_pm</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
@@ -4856,12 +4848,12 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>In a normal month when the Yatra is closed, how much does your household spend on fuel and light: cooking fuel, firewood, electricity, kerosene, candles? (Rs)</t>
+          <t>In a normal month when the Yatra is closed, how much does your household spend on soap, toiletries, cleaning goods and other small household items? (Rs)</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर ईंधन और रोशनी पर: खाना बनाने की गैस, लकड़ी, बिजली, मिट्टी का तेल, मोमबत्ती कितना ख़र्च करता है? (रुपये)</t>
+          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर साबुन, नहाने-धोने का सामान, सफ़ाई का सामान और घर की दूसरी छोटी चीज़ों पर कितना ख़र्च करता है? (रुपये)</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr"/>
@@ -4872,7 +4864,7 @@
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>HCES 2022-23, MoSPI Appendix A, Section 8.1 (30-day). IHDS-II Income and Social Capital Questionnaire, Q14 14.21-14.22. Nigeria GHS-Panel Wave 3, Household Questionnaire, Sections 10B/11 (30-day tier)</t>
+          <t>HCES 2022-23, MoSPI Appendix A, Sections 9.1-9.2 (30-day). IHDS-II Income and Social Capital Questionnaire, Q14 14.25-14.27. Nigeria GHS-Panel Wave 3, Household Questionnaire, Sections 10B/11 (30-day tier)</t>
         </is>
       </c>
     </row>
@@ -4892,7 +4884,7 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>cons_routine_misc_yatra_pm</t>
+          <t>cons_transport_comm_yatra_pm</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
@@ -4902,19 +4894,19 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on soap, toiletries, cleaning goods and other small household items? (Rs)</t>
+          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on local transport (bus, shared jeep, auto) and phone or internet charges? (Rs)</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) साबुन, नहाने-धोने का सामान, सफ़ाई का सामान और घर की दूसरी छोटी चीज़ों पर कितना ख़र्च करते हैं? (रुपये)</t>
+          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) आने-जाने (बस, जीप, ऑटो) और फ़ोन या इंटरनेट पर कितना ख़र्च करते हैं? (रुपये)</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr"/>
       <c r="I98" s="2" t="inlineStr"/>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>HCES 2022-23, MoSPI Appendix A, Sections 9.1-9.2 (30-day). IHDS-II Income and Social Capital Questionnaire, Q14 14.25-14.27. Nigeria GHS-Panel Wave 3, Household Questionnaire, Sections 10B/11 (30-day tier)</t>
+          <t>HCES 2022-23, MoSPI Appendix A, Sections 11.1-11.2 (30-day). IHDS-II Income and Social Capital Questionnaire, Q14 14.24/14.28. Nigeria GHS-Panel Wave 3, Household Questionnaire, Sections 10B/11 (30-day tier)</t>
         </is>
       </c>
     </row>
@@ -4934,7 +4926,7 @@
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>cons_routine_misc_offseason_pm</t>
+          <t>cons_transport_comm_offseason_pm</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
@@ -4944,12 +4936,12 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>In a normal month when the Yatra is closed, how much does your household spend on soap, toiletries, cleaning goods and other small household items? (Rs)</t>
+          <t>In a normal month when the Yatra is closed, how much does your household spend on local transport (bus, shared jeep, auto) and phone or internet charges? (Rs)</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर साबुन, नहाने-धोने का सामान, सफ़ाई का सामान और घर की दूसरी छोटी चीज़ों पर कितना ख़र्च करता है? (रुपये)</t>
+          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर आने-जाने (बस, जीप, ऑटो) और फ़ोन या इंटरनेट पर कितना ख़र्च करता है? (रुपये)</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr"/>
@@ -4960,7 +4952,7 @@
       </c>
       <c r="J99" s="2" t="inlineStr">
         <is>
-          <t>HCES 2022-23, MoSPI Appendix A, Sections 9.1-9.2 (30-day). IHDS-II Income and Social Capital Questionnaire, Q14 14.25-14.27. Nigeria GHS-Panel Wave 3, Household Questionnaire, Sections 10B/11 (30-day tier)</t>
+          <t>HCES 2022-23, MoSPI Appendix A, Sections 11.1-11.2 (30-day). IHDS-II Income and Social Capital Questionnaire, Q14 14.24/14.28. Nigeria GHS-Panel Wave 3, Household Questionnaire, Sections 10B/11 (30-day tier)</t>
         </is>
       </c>
     </row>
@@ -4980,7 +4972,7 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>cons_transport_comm_yatra_pm</t>
+          <t>cons_rent_yatra_pm</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -4990,19 +4982,19 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on local transport (bus, shared jeep, auto) and phone or internet charges? (Rs)</t>
+          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on rent for the home (0 if owned, and 0 for any period spent living for free)? (Rs)</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) आने-जाने (बस, जीप, ऑटो) और फ़ोन या इंटरनेट पर कितना ख़र्च करते हैं? (रुपये)</t>
+          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) घर के किराये पर (अपना घर हो तो 0, और मुफ़्त रहे हों तो भी 0) कितना ख़र्च करते हैं? (रुपये)</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr"/>
       <c r="I100" s="2" t="inlineStr"/>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t>HCES 2022-23, MoSPI Appendix A, Sections 11.1-11.2 (30-day). IHDS-II Income and Social Capital Questionnaire, Q14 14.24/14.28. Nigeria GHS-Panel Wave 3, Household Questionnaire, Sections 10B/11 (30-day tier)</t>
+          <t>HCES 2022-23, MoSPI Appendix A, Section 11.4 (30-day). IHDS-II Income and Social Capital Questionnaire, Q14 14.30. Nigeria GHS-Panel Wave 3, Household Questionnaire, Sections 10B/11 (30-day tier)</t>
         </is>
       </c>
     </row>
@@ -5022,7 +5014,7 @@
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>cons_transport_comm_offseason_pm</t>
+          <t>cons_rent_offseason_pm</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
@@ -5032,12 +5024,12 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>In a normal month when the Yatra is closed, how much does your household spend on local transport (bus, shared jeep, auto) and phone or internet charges? (Rs)</t>
+          <t>In a normal month when the Yatra is closed, how much does your household spend on rent for the home (0 if owned, and 0 for any period spent living for free)? (Rs)</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर आने-जाने (बस, जीप, ऑटो) और फ़ोन या इंटरनेट पर कितना ख़र्च करता है? (रुपये)</t>
+          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर घर के किराये पर (अपना घर हो तो 0, और मुफ़्त रहे हों तो भी 0) कितना ख़र्च करता है? (रुपये)</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr"/>
@@ -5048,7 +5040,7 @@
       </c>
       <c r="J101" s="2" t="inlineStr">
         <is>
-          <t>HCES 2022-23, MoSPI Appendix A, Sections 11.1-11.2 (30-day). IHDS-II Income and Social Capital Questionnaire, Q14 14.24/14.28. Nigeria GHS-Panel Wave 3, Household Questionnaire, Sections 10B/11 (30-day tier)</t>
+          <t>HCES 2022-23, MoSPI Appendix A, Section 11.4 (30-day). IHDS-II Income and Social Capital Questionnaire, Q14 14.30. Nigeria GHS-Panel Wave 3, Household Questionnaire, Sections 10B/11 (30-day tier)</t>
         </is>
       </c>
     </row>
@@ -5068,7 +5060,7 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>cons_rent_yatra_pm</t>
+          <t>cons_med_nonhosp_yatra_pm</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
@@ -5078,19 +5070,19 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on rent for the home (0 if owned, and 0 for any period spent living for free)? (Rs)</t>
+          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on medicine, doctor's or clinic fees and tests, not counting a hospital stay? (Rs)</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) घर के किराये पर (अपना घर हो तो 0, और मुफ़्त रहे हों तो भी 0) कितना ख़र्च करते हैं? (रुपये)</t>
+          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) दवाई, डॉक्टर या क्लीनिक की फ़ीस और जाँच पर, अस्पताल में भर्ती को छोड़कर कितना ख़र्च करते हैं? (रुपये)</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr"/>
       <c r="I102" s="2" t="inlineStr"/>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>HCES 2022-23, MoSPI Appendix A, Section 11.4 (30-day). IHDS-II Income and Social Capital Questionnaire, Q14 14.30. Nigeria GHS-Panel Wave 3, Household Questionnaire, Sections 10B/11 (30-day tier)</t>
+          <t>HCES 2022-23, MoSPI Appendix A, Section 10.3 (30-day). IHDS-II Income and Social Capital Questionnaire, Q14 14.33 (30-day, out-patient)</t>
         </is>
       </c>
     </row>
@@ -5110,7 +5102,7 @@
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>cons_rent_offseason_pm</t>
+          <t>cons_med_nonhosp_offseason_pm</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
@@ -5120,12 +5112,12 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>In a normal month when the Yatra is closed, how much does your household spend on rent for the home (0 if owned, and 0 for any period spent living for free)? (Rs)</t>
+          <t>In a normal month when the Yatra is closed, how much does your household spend on medicine, doctor's or clinic fees and tests, not counting a hospital stay? (Rs)</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर घर के किराये पर (अपना घर हो तो 0, और मुफ़्त रहे हों तो भी 0) कितना ख़र्च करता है? (रुपये)</t>
+          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर दवाई, डॉक्टर या क्लीनिक की फ़ीस और जाँच पर, अस्पताल में भर्ती को छोड़कर कितना ख़र्च करता है? (रुपये)</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr"/>
@@ -5136,7 +5128,7 @@
       </c>
       <c r="J103" s="2" t="inlineStr">
         <is>
-          <t>HCES 2022-23, MoSPI Appendix A, Section 11.4 (30-day). IHDS-II Income and Social Capital Questionnaire, Q14 14.30. Nigeria GHS-Panel Wave 3, Household Questionnaire, Sections 10B/11 (30-day tier)</t>
+          <t>HCES 2022-23, MoSPI Appendix A, Section 10.3 (30-day). IHDS-II Income and Social Capital Questionnaire, Q14 14.33 (30-day, out-patient)</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5148,7 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>cons_med_nonhosp_yatra_pm</t>
+          <t>cons_packaged_food_yatra_pm</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
@@ -5166,19 +5158,19 @@
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on medicine, doctor's or clinic fees and tests, not counting a hospital stay? (Rs)</t>
+          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on biscuits, namkeen, chips, packaged snacks, cold drinks or bottled water? (Rs)</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) दवाई, डॉक्टर या क्लीनिक की फ़ीस और जाँच पर, अस्पताल में भर्ती को छोड़कर कितना ख़र्च करते हैं? (रुपये)</t>
+          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) बिस्किट, नमकीन, चिप्स, पैकेट वाले नाश्ते, कोल्ड ड्रिंक या बोतलबंद पानी पर कितना ख़र्च करते हैं? (रुपये)</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr"/>
       <c r="I104" s="2" t="inlineStr"/>
       <c r="J104" s="2" t="inlineStr">
         <is>
-          <t>HCES 2022-23, MoSPI Appendix A, Section 10.3 (30-day). IHDS-II Income and Social Capital Questionnaire, Q14 14.33 (30-day, out-patient)</t>
+          <t>HCES 2022-23, MoSPI Appendix A, Section 7.2 (7-day in HCES; usual monthly here, as for every other seasonal item)</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5190,7 @@
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>cons_med_nonhosp_offseason_pm</t>
+          <t>cons_packaged_food_offseason_pm</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
@@ -5208,12 +5200,12 @@
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>In a normal month when the Yatra is closed, how much does your household spend on medicine, doctor's or clinic fees and tests, not counting a hospital stay? (Rs)</t>
+          <t>In a normal month when the Yatra is closed, how much does your household spend on biscuits, namkeen, chips, packaged snacks, cold drinks or bottled water? (Rs)</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर दवाई, डॉक्टर या क्लीनिक की फ़ीस और जाँच पर, अस्पताल में भर्ती को छोड़कर कितना ख़र्च करता है? (रुपये)</t>
+          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर बिस्किट, नमकीन, चिप्स, पैकेट वाले नाश्ते, कोल्ड ड्रिंक या बोतलबंद पानी पर कितना ख़र्च करता है? (रुपये)</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr"/>
@@ -5224,7 +5216,7 @@
       </c>
       <c r="J105" s="2" t="inlineStr">
         <is>
-          <t>HCES 2022-23, MoSPI Appendix A, Section 10.3 (30-day). IHDS-II Income and Social Capital Questionnaire, Q14 14.33 (30-day, out-patient)</t>
+          <t>HCES 2022-23, MoSPI Appendix A, Section 7.2 (7-day in HCES; usual monthly here, as for every other seasonal item)</t>
         </is>
       </c>
     </row>
@@ -5244,7 +5236,7 @@
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>cons_packaged_food_yatra_pm</t>
+          <t>cons_pan_tobacco_yatra_pm</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
@@ -5254,19 +5246,19 @@
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on biscuits, namkeen, chips, packaged snacks, cold drinks or bottled water? (Rs)</t>
+          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on pan, gutka, bidi, cigarettes, tobacco or alcohol? (Rs)</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) बिस्किट, नमकीन, चिप्स, पैकेट वाले नाश्ते, कोल्ड ड्रिंक या बोतलबंद पानी पर कितना ख़र्च करते हैं? (रुपये)</t>
+          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) पान, गुटका, बीड़ी, सिगरेट, तंबाकू या शराब पर कितना ख़र्च करते हैं? (रुपये)</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr"/>
       <c r="I106" s="2" t="inlineStr"/>
       <c r="J106" s="2" t="inlineStr">
         <is>
-          <t>HCES 2022-23, MoSPI Appendix A, Section 7.2 (7-day in HCES; usual monthly here, as for every other seasonal item)</t>
+          <t>HCES 2022-23, MoSPI Appendix A, Sections 12.1-12.3 (7-day in HCES; usual monthly here, and combined into one figure)</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5278,7 @@
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>cons_packaged_food_offseason_pm</t>
+          <t>cons_pan_tobacco_offseason_pm</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
@@ -5296,12 +5288,12 @@
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>In a normal month when the Yatra is closed, how much does your household spend on biscuits, namkeen, chips, packaged snacks, cold drinks or bottled water? (Rs)</t>
+          <t>In a normal month when the Yatra is closed, how much does your household spend on pan, gutka, bidi, cigarettes, tobacco or alcohol? (Rs)</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर बिस्किट, नमकीन, चिप्स, पैकेट वाले नाश्ते, कोल्ड ड्रिंक या बोतलबंद पानी पर कितना ख़र्च करता है? (रुपये)</t>
+          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर पान, गुटका, बीड़ी, सिगरेट, तंबाकू या शराब पर कितना ख़र्च करता है? (रुपये)</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr"/>
@@ -5312,7 +5304,7 @@
       </c>
       <c r="J107" s="2" t="inlineStr">
         <is>
-          <t>HCES 2022-23, MoSPI Appendix A, Section 7.2 (7-day in HCES; usual monthly here, as for every other seasonal item)</t>
+          <t>HCES 2022-23, MoSPI Appendix A, Sections 12.1-12.3 (7-day in HCES; usual monthly here, and combined into one figure)</t>
         </is>
       </c>
     </row>
@@ -5332,7 +5324,7 @@
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>cons_pan_tobacco_yatra_pm</t>
+          <t>cons_clothing_12m</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
@@ -5342,19 +5334,19 @@
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on pan, gutka, bidi, cigarettes, tobacco or alcohol? (Rs)</t>
+          <t>In the last 12 months, how much did your household spend on clothes and footwear? (Rs)</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) पान, गुटका, बीड़ी, सिगरेट, तंबाकू या शराब पर कितना ख़र्च करते हैं? (रुपये)</t>
+          <t>पिछले 12 महीनों में आपके घर ने कपड़ों और जूते-चप्पल पर कितना ख़र्च किया? (रुपये)</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr"/>
       <c r="I108" s="2" t="inlineStr"/>
       <c r="J108" s="2" t="inlineStr">
         <is>
-          <t>HCES 2022-23, MoSPI Appendix A, Sections 12.1-12.3 (7-day in HCES; usual monthly here, and combined into one figure)</t>
+          <t>HCES 2022-23, MoSPI Appendix A, Sections 13.1-13.2 (365-day). IHDS-II Income and Social Capital Questionnaire, Q14 14.38-14.39 (365-day). Nigeria GHS-Panel Wave 3, Household Questionnaire, Sections 10B/11 instead uses a 6-month recall for clothing (items 401-441); we follow the two India sources, since one of them (HCES) underlies our poverty line</t>
         </is>
       </c>
     </row>
@@ -5374,7 +5366,7 @@
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>cons_pan_tobacco_offseason_pm</t>
+          <t>cons_education_12m</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
@@ -5384,23 +5376,19 @@
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>In a normal month when the Yatra is closed, how much does your household spend on pan, gutka, bidi, cigarettes, tobacco or alcohol? (Rs)</t>
+          <t>In the last 12 months, how much on education: fees, books, uniforms, tuition? (Rs)</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर पान, गुटका, बीड़ी, सिगरेट, तंबाकू या शराब पर कितना ख़र्च करता है? (रुपये)</t>
+          <t>पिछले 12 महीनों में पढ़ाई पर कितना ख़र्च हुआ: फ़ीस, किताबें, ड्रेस, ट्यूशन? (रुपये)</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr"/>
-      <c r="I109" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if spend_differs_by_season = 1</t>
-        </is>
-      </c>
+      <c r="I109" s="2" t="inlineStr"/>
       <c r="J109" s="2" t="inlineStr">
         <is>
-          <t>HCES 2022-23, MoSPI Appendix A, Sections 12.1-12.3 (7-day in HCES; usual monthly here, and combined into one figure)</t>
+          <t>HCES 2022-23, MoSPI Appendix A, Section 10.1 (365-day). IHDS-II Income and Social Capital Questionnaire, Q14 14.35-14.37 (365-day, same items). Nigeria GHS-Panel Wave 3, Household Questionnaire, Sections 10B/11 asks school fees inside its education/roster module, per child, not as a household total, so it is not directly comparable</t>
         </is>
       </c>
     </row>
@@ -5420,7 +5408,7 @@
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>cons_clothing_12m</t>
+          <t>cons_medical_hosp_12m</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
@@ -5430,19 +5418,19 @@
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>In the last 12 months, how much did your household spend on clothes and footwear? (Rs)</t>
+          <t>In the last 12 months, how much did your household pay for any hospital admission or stay? (Rs, 0 if none)</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>पिछले 12 महीनों में आपके घर ने कपड़ों और जूते-चप्पल पर कितना ख़र्च किया? (रुपये)</t>
+          <t>पिछले 12 महीनों में अस्पताल में भर्ती होने पर आपके घर का कितना ख़र्च हुआ? (रुपये, न हुआ हो तो 0)</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr"/>
       <c r="I110" s="2" t="inlineStr"/>
       <c r="J110" s="2" t="inlineStr">
         <is>
-          <t>HCES 2022-23, MoSPI Appendix A, Sections 13.1-13.2 (365-day). IHDS-II Income and Social Capital Questionnaire, Q14 14.38-14.39 (365-day). Nigeria GHS-Panel Wave 3, Household Questionnaire, Sections 10B/11 instead uses a 6-month recall for clothing (items 401-441); we follow the two India sources, since one of them (HCES) underlies our poverty line</t>
+          <t>HCES 2022-23, MoSPI Appendix A, Section 10.2 (365-day, hospitalisation). IHDS-II Income and Social Capital Questionnaire, Q14 14.34 (365-day, in-patient). Nigeria GHS-Panel Wave 3, Household Questionnaire, Sections 10B/11 instead uses one combined 6-month medical item (less detail); we follow the matching HCES/IHDS split</t>
         </is>
       </c>
     </row>
@@ -5462,7 +5450,7 @@
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>cons_education_12m</t>
+          <t>cons_durables_12m</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
@@ -5472,19 +5460,19 @@
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>In the last 12 months, how much on education: fees, books, uniforms, tuition? (Rs)</t>
+          <t>In the last 12 months, how much on durable goods: furniture, utensils, cooking appliances, phone, jewellery or ornaments, bicycle or vehicle parts? (Rs)</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>पिछले 12 महीनों में पढ़ाई पर कितना ख़र्च हुआ: फ़ीस, किताबें, ड्रेस, ट्यूशन? (रुपये)</t>
+          <t>पिछले 12 महीनों में सामान पर कितना ख़र्च हुआ: फ़र्नीचर, बर्तन, चूल्हा-मशीन, फ़ोन, गहने, साइकिल या गाड़ी के पुर्ज़े? (रुपये)</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr"/>
       <c r="I111" s="2" t="inlineStr"/>
       <c r="J111" s="2" t="inlineStr">
         <is>
-          <t>HCES 2022-23, MoSPI Appendix A, Section 10.1 (365-day). IHDS-II Income and Social Capital Questionnaire, Q14 14.35-14.37 (365-day, same items). Nigeria GHS-Panel Wave 3, Household Questionnaire, Sections 10B/11 asks school fees inside its education/roster module, per child, not as a household total, so it is not directly comparable</t>
+          <t>HCES 2022-23, MoSPI Appendix A, Section 14 (365-day, 10 sub-groups). IHDS-II Income and Social Capital Questionnaire, Q14 14.40-14.48 (365-day). Nigeria GHS-Panel Wave 3, Household Questionnaire, Sections 10B/11 (12-month tier: durables, appliances, building materials). All three agree on the 12-month recall; insurance premiums, which IHDS (14.50) and the Nigeria survey (items 510-513) count here, are excluded, following HCES and standard national-accounts practice (insurance is a financial item, not consumption) -- premiums are covered instead by the insurance items in Module G</t>
         </is>
       </c>
     </row>
@@ -5494,39 +5482,43 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>Household consumption</t>
+          <t>Housing, amenities and assets</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>cons_medical_hosp_12m</t>
+          <t>floor_material</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>amount (Rs)</t>
+          <t>select one</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>In the last 12 months, how much did your household pay for any hospital admission or stay? (Rs, 0 if none)</t>
+          <t>What is the main material of the floor at your usual home?</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>पिछले 12 महीनों में अस्पताल में भर्ती होने पर आपके घर का कितना ख़र्च हुआ? (रुपये, न हुआ हो तो 0)</t>
-        </is>
-      </c>
-      <c r="H112" s="2" t="inlineStr"/>
+          <t>आपके असली घर में फ़र्श मुख्य रूप से किस चीज़ का है?</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>1 Mud/kaccha | 2 Cement/mud-cement | 3 Tile/mosaic/marble</t>
+        </is>
+      </c>
       <c r="I112" s="2" t="inlineStr"/>
       <c r="J112" s="2" t="inlineStr">
         <is>
-          <t>HCES 2022-23, MoSPI Appendix A, Section 10.2 (365-day, hospitalisation). IHDS-II Income and Social Capital Questionnaire, Q14 14.34 (365-day, in-patient). Nigeria GHS-Panel Wave 3, Household Questionnaire, Sections 10B/11 instead uses one combined 6-month medical item (less detail); we follow the matching HCES/IHDS split</t>
+          <t>NITI Aayog National MPI housing indicator</t>
         </is>
       </c>
     </row>
@@ -5536,39 +5528,43 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>Household consumption</t>
+          <t>Housing, amenities and assets</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>cons_durables_12m</t>
+          <t>roof_material</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>amount (Rs)</t>
+          <t>select one</t>
         </is>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>In the last 12 months, how much on durable goods: furniture, utensils, cooking appliances, phone, jewellery or ornaments, bicycle or vehicle parts? (Rs)</t>
+          <t>What is the main material of the roof at your usual home?</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>पिछले 12 महीनों में सामान पर कितना ख़र्च हुआ: फ़र्नीचर, बर्तन, चूल्हा-मशीन, फ़ोन, गहने, साइकिल या गाड़ी के पुर्ज़े? (रुपये)</t>
-        </is>
-      </c>
-      <c r="H113" s="2" t="inlineStr"/>
+          <t>आपके असली घर की छत मुख्य रूप से किस चीज़ की है?</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>1 Thatch/wood/mud | 2 Tin/GI sheet | 3 Concrete/RCC</t>
+        </is>
+      </c>
       <c r="I113" s="2" t="inlineStr"/>
       <c r="J113" s="2" t="inlineStr">
         <is>
-          <t>HCES 2022-23, MoSPI Appendix A, Section 14 (365-day, 10 sub-groups). IHDS-II Income and Social Capital Questionnaire, Q14 14.40-14.48 (365-day). Nigeria GHS-Panel Wave 3, Household Questionnaire, Sections 10B/11 (12-month tier: durables, appliances, building materials). All three agree on the 12-month recall; insurance premiums, which IHDS (14.50) and the Nigeria survey (items 510-513) count here, are excluded, following HCES and standard national-accounts practice (insurance is a financial item, not consumption) -- premiums are covered instead by the insurance items in Module G</t>
+          <t>NITI Aayog National MPI housing indicator</t>
         </is>
       </c>
     </row>
@@ -5588,7 +5584,7 @@
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>floor_material</t>
+          <t>wall_material</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
@@ -5598,23 +5594,23 @@
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>What is the main material of the floor at your usual home?</t>
+          <t>What are the walls of your usual home mainly made of?</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>आपके असली घर में फ़र्श मुख्य रूप से किस चीज़ का है?</t>
+          <t>आपके असली घर की दीवारें मुख्य रूप से किस चीज़ की बनी हैं?</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>1 Mud/kaccha | 2 Cement/mud-cement | 3 Tile/mosaic/marble</t>
+          <t>1 Mud, thatch, bamboo or other natural material | 2 Unburnt brick, wood or tin | 3 Burnt brick, cement, concrete or stone</t>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr"/>
       <c r="J114" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI housing indicator</t>
+          <t>NITI Aayog National MPI housing indicator (wall limb)</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5630,7 @@
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>roof_material</t>
+          <t>accom_type_here</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
@@ -5644,23 +5640,23 @@
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>What is the main material of the roof at your usual home?</t>
+          <t>While you are here for the season, where do you sleep?</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>आपके असली घर की छत मुख्य रूप से किस चीज़ की है?</t>
+          <t>सीज़न में यहाँ रहते हुए आप कहाँ सोते हैं?</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>1 Thatch/wood/mud | 2 Tin/GI sheet | 3 Concrete/RCC</t>
+          <t>1 Own house here | 2 Rented room or house | 3 Room or dormitory the employer provides | 4 Sleeps at the shop, dhaba or workplace | 5 Tent or temporary shelter | 6 Lodge, dharamshala or ashram | 7 In the open, or a verandah | 8 Somewhere else</t>
         </is>
       </c>
       <c r="I115" s="2" t="inlineStr"/>
       <c r="J115" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI housing indicator</t>
+          <t>Lyons et al. 2023, Table 2 (area/settlement conditions), adapted to a labour-migrant setting</t>
         </is>
       </c>
     </row>
@@ -5680,33 +5676,33 @@
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>wall_material</t>
+          <t>electricity</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>select one</t>
+          <t>yes/no</t>
         </is>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>What are the walls of your usual home mainly made of?</t>
+          <t>Does your usual home have an electricity connection?</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>आपके असली घर की दीवारें मुख्य रूप से किस चीज़ की बनी हैं?</t>
+          <t>क्या आपके असली घर में बिजली का कनेक्शन है?</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>1 Mud, thatch, bamboo or other natural material | 2 Unburnt brick, wood or tin | 3 Burnt brick, cement, concrete or stone</t>
+          <t>0 No | 1 Yes</t>
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr"/>
       <c r="J116" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI housing indicator (wall limb)</t>
+          <t>NITI Aayog National MPI</t>
         </is>
       </c>
     </row>
@@ -5726,7 +5722,7 @@
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>house_type</t>
+          <t>toilet_type</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
@@ -5736,23 +5732,23 @@
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>Would you describe your usual home as kaccha (mud/thatch, temporary), semi-pucca (part-concrete) or pucca (solid, permanent)?</t>
+          <t>What kind of toilet does your household use at your usual home?</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>अपने असली घर को आप क्या कहेंगे: कच्चा (मिट्टी/फूस का, कामचलाऊ), अधपक्का, या पक्का (मज़बूत, स्थायी)?</t>
+          <t>आपका घर अपने असली घर में किस तरह का शौचालय इस्तेमाल करता है?</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>1 Kaccha | 2 Semi-pucca | 3 Pucca</t>
+          <t>1 No toilet / open defecation | 2 Pit latrine without slab or open pit | 3 Improved toilet, but shared with other households | 4 Improved toilet, used only by this household</t>
         </is>
       </c>
       <c r="I117" s="2" t="inlineStr"/>
       <c r="J117" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI housing indicator</t>
+          <t>NITI Aayog National MPI sanitation indicator (improved/unimproved and shared/not)</t>
         </is>
       </c>
     </row>
@@ -5772,7 +5768,7 @@
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>accom_type_here</t>
+          <t>drinking_water</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
@@ -5782,23 +5778,23 @@
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>While you are here for the season, where do you sleep?</t>
+          <t>What is your main source of drinking water at your usual home?</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>सीज़न में यहाँ रहते हुए आप कहाँ सोते हैं?</t>
+          <t>आपके असली घर में पीने का पानी मुख्य रूप से कहाँ से आता है?</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>1 Own house here | 2 Rented room or house | 3 Room or dormitory the employer provides | 4 Sleeps at the shop, dhaba or workplace | 5 Tent or temporary shelter | 6 Lodge, dharamshala or ashram | 7 In the open, or a verandah | 8 Somewhere else</t>
+          <t>1 Piped into the house or yard | 2 Public tap or standpipe | 3 Handpump, tubewell or borewell | 4 Protected well or protected spring | 5 Rainwater collection | 6 Bottled, packaged or community RO | 7 Unprotected well or unprotected spring | 8 River, stream, pond or canal | 9 Tanker truck or cart with drum</t>
         </is>
       </c>
       <c r="I118" s="2" t="inlineStr"/>
       <c r="J118" s="2" t="inlineStr">
         <is>
-          <t>Lyons et al. 2023, Table 2 (area/settlement conditions), adapted to a labour-migrant setting</t>
+          <t>NITI Aayog National MPI drinking-water indicator (JMP improved/unimproved taxonomy)</t>
         </is>
       </c>
     </row>
@@ -5818,7 +5814,7 @@
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>electricity</t>
+          <t>water_on_premises</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
@@ -5828,12 +5824,12 @@
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>Does your usual home have an electricity connection?</t>
+          <t>Is the drinking water available at the house itself?</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>क्या आपके असली घर में बिजली का कनेक्शन है?</t>
+          <t>क्या पीने का पानी घर पर ही मिल जाता है?</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
@@ -5844,7 +5840,7 @@
       <c r="I119" s="2" t="inlineStr"/>
       <c r="J119" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI</t>
+          <t>NITI Aayog National MPI drinking-water indicator (30-minute round-trip rule)</t>
         </is>
       </c>
     </row>
@@ -5864,33 +5860,33 @@
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>toilet_type</t>
+          <t>water_fetch_minutes</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>select one</t>
+          <t>whole number</t>
         </is>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>What kind of toilet does your household use at your usual home?</t>
+          <t>How long does it take to go there, get the water and come back? (minutes, round trip)</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>आपका घर अपने असली घर में किस तरह का शौचालय इस्तेमाल करता है?</t>
-        </is>
-      </c>
-      <c r="H120" s="2" t="inlineStr">
-        <is>
-          <t>1 No toilet / open defecation | 2 Pit latrine without slab or open pit | 3 Improved toilet, but shared with other households | 4 Improved toilet, used only by this household</t>
-        </is>
-      </c>
-      <c r="I120" s="2" t="inlineStr"/>
+          <t>वहाँ जाने, पानी भरने और लौटने में कुल कितना समय लगता है? (मिनट)</t>
+        </is>
+      </c>
+      <c r="H120" s="2" t="inlineStr"/>
+      <c r="I120" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if water_on_premises = 0</t>
+        </is>
+      </c>
       <c r="J120" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI sanitation indicator (improved/unimproved and shared/not)</t>
+          <t>NITI Aayog National MPI drinking-water indicator (30-minute round-trip rule)</t>
         </is>
       </c>
     </row>
@@ -5910,7 +5906,7 @@
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>drinking_water</t>
+          <t>cooking_fuel</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
@@ -5920,23 +5916,23 @@
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>What is your main source of drinking water at your usual home?</t>
+          <t>What does your household mainly use to cook at your usual home?</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>आपके असली घर में पीने का पानी मुख्य रूप से कहाँ से आता है?</t>
+          <t>आपके असली घर में खाना मुख्य रूप से किस चीज़ पर बनता है?</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>1 Piped into the house or yard | 2 Public tap or standpipe | 3 Handpump, tubewell or borewell | 4 Protected well or protected spring | 5 Rainwater collection | 6 Bottled, packaged or community RO | 7 Unprotected well or unprotected spring | 8 River, stream, pond or canal | 9 Tanker truck or cart with drum</t>
+          <t>1 LPG or cylinder gas | 2 Piped natural gas | 3 Electricity | 4 Biogas (gobar gas plant) | 5 Kerosene | 6 Firewood | 7 Dung cakes (gobar) | 8 Crop residue, straw or shrubs | 9 Charcoal | 10 Coal or lignite</t>
         </is>
       </c>
       <c r="I121" s="2" t="inlineStr"/>
       <c r="J121" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI drinking-water indicator (JMP improved/unimproved taxonomy)</t>
+          <t>NITI Aayog National MPI cooking-fuel indicator (its own list of dirty fuels)</t>
         </is>
       </c>
     </row>
@@ -5956,7 +5952,7 @@
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>water_on_premises</t>
+          <t>owns_tv</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
@@ -5966,12 +5962,12 @@
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>Is the drinking water available at the house itself?</t>
+          <t>Does your household own: a television?</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>क्या पीने का पानी घर पर ही मिल जाता है?</t>
+          <t>क्या आपके घर में टीवी है?</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
@@ -5982,7 +5978,7 @@
       <c r="I122" s="2" t="inlineStr"/>
       <c r="J122" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI drinking-water indicator (30-minute round-trip rule)</t>
+          <t>NITI Aayog National MPI assets indicator</t>
         </is>
       </c>
     </row>
@@ -6002,33 +5998,33 @@
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>water_fetch_minutes</t>
+          <t>owns_radio</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>whole number</t>
+          <t>yes/no</t>
         </is>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>How long does it take to go there, get the water and come back? (minutes, round trip)</t>
+          <t>... a radio?</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>वहाँ जाने, पानी भरने और लौटने में कुल कितना समय लगता है? (मिनट)</t>
-        </is>
-      </c>
-      <c r="H123" s="2" t="inlineStr"/>
-      <c r="I123" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if water_on_premises = 0</t>
-        </is>
-      </c>
+          <t>...रेडियो?</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="inlineStr">
+        <is>
+          <t>0 No | 1 Yes</t>
+        </is>
+      </c>
+      <c r="I123" s="2" t="inlineStr"/>
       <c r="J123" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI drinking-water indicator (30-minute round-trip rule)</t>
+          <t>NITI Aayog National MPI assets indicator</t>
         </is>
       </c>
     </row>
@@ -6048,37 +6044,33 @@
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>water_fetched_by</t>
+          <t>owns_bicycle</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>select one</t>
+          <t>yes/no</t>
         </is>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>Who in the household usually goes to fetch it?</t>
+          <t>... a bicycle?</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>घर में आम तौर पर पानी कौन लाता है?</t>
+          <t>...साइकिल?</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>1 An adult woman | 2 An adult man | 3 A girl under 15 | 4 A boy under 15 | 5 It varies / more than one person</t>
-        </is>
-      </c>
-      <c r="I124" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if water_on_premises = 0</t>
-        </is>
-      </c>
+          <t>0 No | 1 Yes</t>
+        </is>
+      </c>
+      <c r="I124" s="2" t="inlineStr"/>
       <c r="J124" s="2" t="inlineStr">
         <is>
-          <t>Project design (intra-household burden of water collection; DHS/NFHS ask the same item)</t>
+          <t>NITI Aayog National MPI assets indicator</t>
         </is>
       </c>
     </row>
@@ -6098,33 +6090,33 @@
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>cooking_fuel</t>
+          <t>owns_motorcycle</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>select one</t>
+          <t>yes/no</t>
         </is>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>What does your household mainly use to cook at your usual home?</t>
+          <t>... a motorcycle or scooter?</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>आपके असली घर में खाना मुख्य रूप से किस चीज़ पर बनता है?</t>
+          <t>...मोटरसाइकिल या स्कूटर?</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>1 LPG or cylinder gas | 2 Piped natural gas | 3 Electricity | 4 Biogas (gobar gas plant) | 5 Kerosene | 6 Firewood | 7 Dung cakes (gobar) | 8 Crop residue, straw or shrubs | 9 Charcoal | 10 Coal or lignite</t>
+          <t>0 No | 1 Yes</t>
         </is>
       </c>
       <c r="I125" s="2" t="inlineStr"/>
       <c r="J125" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI cooking-fuel indicator (its own list of dirty fuels)</t>
+          <t>NITI Aayog National MPI assets indicator</t>
         </is>
       </c>
     </row>
@@ -6144,7 +6136,7 @@
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>owns_tv</t>
+          <t>owns_car</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
@@ -6154,12 +6146,12 @@
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>Does your household own: a television?</t>
+          <t>... a car, jeep or truck?</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>क्या आपके घर में टीवी है?</t>
+          <t>...कार, जीप या ट्रक?</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr">
@@ -6170,7 +6162,7 @@
       <c r="I126" s="2" t="inlineStr"/>
       <c r="J126" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI assets indicator</t>
+          <t>NITI Aayog National MPI assets indicator (car or truck limb)</t>
         </is>
       </c>
     </row>
@@ -6190,7 +6182,7 @@
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>owns_radio</t>
+          <t>owns_phone</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
@@ -6200,12 +6192,12 @@
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>... a radio?</t>
+          <t>... a telephone of any kind, mobile or landline?</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>...रेडियो?</t>
+          <t>...कोई फ़ोन, मोबाइल या लैंडलाइन?</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
@@ -6236,7 +6228,7 @@
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>owns_bicycle</t>
+          <t>owns_computer</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
@@ -6246,12 +6238,12 @@
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>... a bicycle?</t>
+          <t>... a computer or laptop?</t>
         </is>
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>...साइकिल?</t>
+          <t>...कंप्यूटर या लैपटॉप?</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr">
@@ -6282,7 +6274,7 @@
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>owns_motorcycle</t>
+          <t>owns_animal_cart</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
@@ -6292,12 +6284,12 @@
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>... a motorcycle or scooter?</t>
+          <t>... a cart pulled by an animal?</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>...मोटरसाइकिल या स्कूटर?</t>
+          <t>...जानवर से खींची जाने वाली गाड़ी?</t>
         </is>
       </c>
       <c r="H129" s="2" t="inlineStr">
@@ -6328,7 +6320,7 @@
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>owns_car</t>
+          <t>owns_fridge</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
@@ -6338,12 +6330,12 @@
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>... a car, jeep or truck?</t>
+          <t>... a refrigerator?</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>...कार, जीप या ट्रक?</t>
+          <t>...फ़्रिज?</t>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr">
@@ -6354,7 +6346,7 @@
       <c r="I130" s="2" t="inlineStr"/>
       <c r="J130" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI assets indicator (car or truck limb)</t>
+          <t>NITI Aayog National MPI assets indicator</t>
         </is>
       </c>
     </row>
@@ -6374,33 +6366,29 @@
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>owns_phone</t>
+          <t>land_cultivable_acres</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>yes/no</t>
+          <t>number</t>
         </is>
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t>... a telephone of any kind, mobile or landline?</t>
+          <t>How much CULTIVABLE land does your household own or cultivate, in acres? Do not count the land the house stands on. (0 if none)</t>
         </is>
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>...कोई फ़ोन, मोबाइल या लैंडलाइन?</t>
-        </is>
-      </c>
-      <c r="H131" s="2" t="inlineStr">
-        <is>
-          <t>0 No | 1 Yes</t>
-        </is>
-      </c>
+          <t>आपके घर के पास कितनी जोतने लायक़ ज़मीन है, अपनी या जोतने की, एकड़ में? जिस ज़मीन पर घर बना है उसे मत गिनिए। (न हो तो 0)</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="inlineStr"/>
       <c r="I131" s="2" t="inlineStr"/>
       <c r="J131" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI assets indicator</t>
+          <t>Chaudhuri et al. 2002 asset covariate</t>
         </is>
       </c>
     </row>
@@ -6420,7 +6408,7 @@
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>owns_computer</t>
+          <t>owns_cow_buffalo</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
@@ -6430,12 +6418,12 @@
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>... a computer or laptop?</t>
+          <t>Does your household own any cows or buffaloes?</t>
         </is>
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>...कंप्यूटर या लैपटॉप?</t>
+          <t>क्या आपके घर में गाय या भैंस है?</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
@@ -6446,7 +6434,7 @@
       <c r="I132" s="2" t="inlineStr"/>
       <c r="J132" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI assets indicator</t>
+          <t>Chaudhuri et al. 2002 asset covariate</t>
         </is>
       </c>
     </row>
@@ -6466,7 +6454,7 @@
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>owns_animal_cart</t>
+          <t>owns_goat_sheep</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
@@ -6476,12 +6464,12 @@
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>... a cart pulled by an animal?</t>
+          <t>Does your household own any goats or sheep?</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>...जानवर से खींची जाने वाली गाड़ी?</t>
+          <t>क्या आपके घर में बकरी या भेड़ है?</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
@@ -6492,7 +6480,7 @@
       <c r="I133" s="2" t="inlineStr"/>
       <c r="J133" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI assets indicator</t>
+          <t>Chaudhuri et al. 2002 asset covariate</t>
         </is>
       </c>
     </row>
@@ -6512,7 +6500,7 @@
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>owns_fridge</t>
+          <t>owns_pony_mule</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
@@ -6522,12 +6510,12 @@
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>... a refrigerator?</t>
+          <t>Does your household own any ponies or mules?</t>
         </is>
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>...फ़्रिज?</t>
+          <t>क्या आपके घर में घोड़ा या खच्चर है?</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">
@@ -6538,7 +6526,7 @@
       <c r="I134" s="2" t="inlineStr"/>
       <c r="J134" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI assets indicator</t>
+          <t>Project design (pilot livelihood survey)</t>
         </is>
       </c>
     </row>
@@ -6558,25 +6546,29 @@
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>land_cultivable_acres</t>
+          <t>owns_shop_stall</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>yes/no</t>
         </is>
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>How much CULTIVABLE land does your household own or cultivate, in acres? Do not count the land the house stands on. (0 if none)</t>
+          <t>Does your household own a shop or stall that you use to earn?</t>
         </is>
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>आपके घर के पास कितनी जोतने लायक़ ज़मीन है, अपनी या जोतने की, एकड़ में? जिस ज़मीन पर घर बना है उसे मत गिनिए। (न हो तो 0)</t>
-        </is>
-      </c>
-      <c r="H135" s="2" t="inlineStr"/>
+          <t>क्या आपके घर की अपनी दुकान या खोखा है जिससे आप कमाते हैं?</t>
+        </is>
+      </c>
+      <c r="H135" s="2" t="inlineStr">
+        <is>
+          <t>0 No | 1 Yes</t>
+        </is>
+      </c>
       <c r="I135" s="2" t="inlineStr"/>
       <c r="J135" s="2" t="inlineStr">
         <is>
@@ -6600,7 +6592,7 @@
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>owns_cow_buffalo</t>
+          <t>owns_work_vehicle</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
@@ -6610,12 +6602,12 @@
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>Does your household own any cows or buffaloes?</t>
+          <t>Does your household own a vehicle you use to earn (for example a jeep, truck or taxi)?</t>
         </is>
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>क्या आपके घर में गाय या भैंस है?</t>
+          <t>क्या आपके घर की अपनी गाड़ी है जिससे आप कमाते हैं (जैसे जीप, ट्रक या टैक्सी)?</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr">
@@ -6646,7 +6638,7 @@
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>owns_goat_sheep</t>
+          <t>owns_work_equipment</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
@@ -6656,12 +6648,12 @@
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>Does your household own any goats or sheep?</t>
+          <t>Does your household own equipment or tools that you use to earn?</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>क्या आपके घर में बकरी या भेड़ है?</t>
+          <t>क्या आपके घर के पास काम के औज़ार या मशीन है जिससे आप कमाते हैं?</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr">
@@ -6692,33 +6684,33 @@
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>owns_pony_mule</t>
+          <t>work_equipment_detail</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>yes/no</t>
+          <t>free text</t>
         </is>
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>Does your household own any ponies or mules?</t>
+          <t>What are they? Write what they say. Leave blank if they cannot say.</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>क्या आपके घर में घोड़ा या खच्चर है?</t>
-        </is>
-      </c>
-      <c r="H138" s="2" t="inlineStr">
-        <is>
-          <t>0 No | 1 Yes</t>
-        </is>
-      </c>
-      <c r="I138" s="2" t="inlineStr"/>
+          <t>वे क्या हैं? जैसा वे बताएँ वैसा लिख लीजिए। न बता पाएँ तो खाली छोड़ दीजिए।</t>
+        </is>
+      </c>
+      <c r="H138" s="2" t="inlineStr"/>
+      <c r="I138" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if owns_work_equipment = 1; may be left blank</t>
+        </is>
+      </c>
       <c r="J138" s="2" t="inlineStr">
         <is>
-          <t>Project design (pilot livelihood survey)</t>
+          <t>Standard household-survey item</t>
         </is>
       </c>
     </row>
@@ -6728,17 +6720,17 @@
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>Housing, amenities and assets</t>
+          <t>Finance, insurance and schemes</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>owns_shop_stall</t>
+          <t>has_bank_account</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
@@ -6748,12 +6740,12 @@
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>Does your household own a shop or stall that you use to earn?</t>
+          <t>Does anyone in your household have a bank account or a post office account?</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>क्या आपके घर की अपनी दुकान या खोखा है जिससे आप कमाते हैं?</t>
+          <t>क्या आपके घर में किसी का बैंक खाता या डाकघर का खाता है?</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">
@@ -6764,7 +6756,7 @@
       <c r="I139" s="2" t="inlineStr"/>
       <c r="J139" s="2" t="inlineStr">
         <is>
-          <t>Chaudhuri et al. 2002 asset covariate</t>
+          <t>NITI Aayog National MPI bank-account indicator; VEP adaptive-capacity covariate</t>
         </is>
       </c>
     </row>
@@ -6774,17 +6766,17 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>Housing, amenities and assets</t>
+          <t>Finance, insurance and schemes</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>owns_work_vehicle</t>
+          <t>took_loan_12m</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
@@ -6794,12 +6786,12 @@
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>Does your household own a vehicle you use to earn (for example a jeep, truck or taxi)?</t>
+          <t>In the last 12 months, did you or anyone in your household borrow money?</t>
         </is>
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>क्या आपके घर की अपनी गाड़ी है जिससे आप कमाते हैं (जैसे जीप, ट्रक या टैक्सी)?</t>
+          <t>पिछले 12 महीनों में क्या आपने या आपके घर के किसी सदस्य ने पैसा उधार लिया?</t>
         </is>
       </c>
       <c r="H140" s="2" t="inlineStr">
@@ -6810,7 +6802,7 @@
       <c r="I140" s="2" t="inlineStr"/>
       <c r="J140" s="2" t="inlineStr">
         <is>
-          <t>Chaudhuri et al. 2002 asset covariate</t>
+          <t>VEP adaptive-capacity covariate</t>
         </is>
       </c>
     </row>
@@ -6820,43 +6812,47 @@
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>Housing, amenities and assets</t>
+          <t>Finance, insurance and schemes</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>owns_work_equipment</t>
+          <t>credit_source</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>yes/no</t>
+          <t>select one</t>
         </is>
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t>Does your household own equipment or tools that you use to earn?</t>
+          <t>Who was the main lender?</t>
         </is>
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>क्या आपके घर के पास काम के औज़ार या मशीन है जिससे आप कमाते हैं?</t>
+          <t>मुख्य रूप से किससे उधार लिया?</t>
         </is>
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
-          <t>0 No | 1 Yes</t>
-        </is>
-      </c>
-      <c r="I141" s="2" t="inlineStr"/>
+          <t>1 Nationalised or public-sector bank | 2 Private bank | 3 Cooperative bank or RRB | 4 Microfinance institution or SHG | 5 Moneylender | 6 Relative or friend | 7 Employer or contractor (advance) | 8 Other</t>
+        </is>
+      </c>
+      <c r="I141" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if took_loan_12m = 1</t>
+        </is>
+      </c>
       <c r="J141" s="2" t="inlineStr">
         <is>
-          <t>Chaudhuri et al. 2002 asset covariate</t>
+          <t>VEP adaptive-capacity covariate (lender type)</t>
         </is>
       </c>
     </row>
@@ -6866,43 +6862,43 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>Housing, amenities and assets</t>
+          <t>Finance, insurance and schemes</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>work_equipment_detail</t>
+          <t>loan_amount</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>free text</t>
+          <t>amount (Rs)</t>
         </is>
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>What are they? Write what they say. Leave blank if they cannot say.</t>
+          <t>How much of that loan is still left to repay? (Rs)</t>
         </is>
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>वे क्या हैं? जैसा वे बताएँ वैसा लिख लीजिए। न बता पाएँ तो खाली छोड़ दीजिए।</t>
+          <t>उस क़र्ज़ में से अब भी कितना चुकाना बाक़ी है? (रुपये)</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr"/>
       <c r="I142" s="2" t="inlineStr">
         <is>
-          <t>Ask only if owns_work_equipment = 1; may be left blank</t>
+          <t>Ask only if took_loan_12m = 1</t>
         </is>
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
-          <t>Standard household-survey item</t>
+          <t>Islam and Chowdhury 2025 (financial distress and household vulnerability to poverty)</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6918,7 @@
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>has_bank_account</t>
+          <t>pays_interest</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
@@ -6932,12 +6928,12 @@
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
-          <t>Does anyone in your household have a bank account or a post office account?</t>
+          <t>Do you pay interest on it?</t>
         </is>
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>क्या आपके घर में किसी का बैंक खाता या डाकघर का खाता है?</t>
+          <t>क्या आप उस पर ब्याज देते हैं?</t>
         </is>
       </c>
       <c r="H143" s="2" t="inlineStr">
@@ -6945,10 +6941,14 @@
           <t>0 No | 1 Yes</t>
         </is>
       </c>
-      <c r="I143" s="2" t="inlineStr"/>
+      <c r="I143" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if took_loan_12m = 1</t>
+        </is>
+      </c>
       <c r="J143" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI bank-account indicator; VEP adaptive-capacity covariate</t>
+          <t>Project design (informal lending is often interest-free)</t>
         </is>
       </c>
     </row>
@@ -6968,37 +6968,33 @@
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>has_jandhan_account</t>
+          <t>loan_interest_per100_pm</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>yes/no</t>
+          <t>number</t>
         </is>
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>Is any of these a Jan Dhan account?</t>
+          <t>On every 100 rupees you borrowed, about how much interest do you pay in a month? (Rs; 0 if none, leave blank if not known)</t>
         </is>
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>क्या उनमें से कोई जन धन खाता है?</t>
-        </is>
-      </c>
-      <c r="H144" s="2" t="inlineStr">
-        <is>
-          <t>0 No | 1 Yes</t>
-        </is>
-      </c>
+          <t>आपने जो 100 रुपये उधार लिए, उन पर महीने का कितना ब्याज देते हैं? (रुपये; दर पता न हो तो खाली छोड़ दें)</t>
+        </is>
+      </c>
+      <c r="H144" s="2" t="inlineStr"/>
       <c r="I144" s="2" t="inlineStr">
         <is>
-          <t>Ask only if has_bank_account = 1</t>
+          <t>Ask only if took_loan_12m = 1; may be left blank</t>
         </is>
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>Standard household-survey item</t>
+          <t>Project design (informal-credit pricing as locally quoted)</t>
         </is>
       </c>
     </row>
@@ -7018,7 +7014,7 @@
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>took_loan_12m</t>
+          <t>loan_against_asset</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
@@ -7028,12 +7024,12 @@
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
-          <t>In the last 12 months, did you or anyone in your household borrow money?</t>
+          <t>Did you have to give something as security for it -- an animal, a vehicle, jewellery, land or your business?</t>
         </is>
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>पिछले 12 महीनों में क्या आपने या आपके घर के किसी सदस्य ने पैसा उधार लिया?</t>
+          <t>क्या उसके बदले कुछ गिरवी रखना पड़ा — जानवर, गाड़ी, गहने, ज़मीन या आपका धंधा?</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
@@ -7041,10 +7037,14 @@
           <t>0 No | 1 Yes</t>
         </is>
       </c>
-      <c r="I145" s="2" t="inlineStr"/>
+      <c r="I145" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if took_loan_12m = 1</t>
+        </is>
+      </c>
       <c r="J145" s="2" t="inlineStr">
         <is>
-          <t>VEP adaptive-capacity covariate</t>
+          <t>Carter and Zimmerman 2000; Chiwaula et al. 2011 (asset-based vulnerability)</t>
         </is>
       </c>
     </row>
@@ -7064,7 +7064,7 @@
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>credit_source</t>
+          <t>loan_collateral</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
@@ -7074,27 +7074,27 @@
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t>Who was the main lender?</t>
+          <t>What did you have to give as security?</t>
         </is>
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>मुख्य रूप से किससे उधार लिया?</t>
+          <t>आपको क्या गिरवी रखना पड़ा?</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
-          <t>1 Nationalised or public-sector bank | 2 Private bank | 3 Cooperative bank or RRB | 4 Microfinance institution or SHG | 5 Moneylender | 6 Relative or friend | 7 Employer or contractor (advance) | 8 Other</t>
+          <t>1 Jewellery or ornaments | 2 Land | 3 Animals | 4 A vehicle | 5 Shop stock or business goods | 6 House or building | 7 Something else</t>
         </is>
       </c>
       <c r="I146" s="2" t="inlineStr">
         <is>
-          <t>Ask only if took_loan_12m = 1</t>
+          <t>Ask only if loan_against_asset = 1</t>
         </is>
       </c>
       <c r="J146" s="2" t="inlineStr">
         <is>
-          <t>VEP adaptive-capacity covariate (lender type)</t>
+          <t>Carter and Zimmerman 2000; Zimmerman and Carter 2003 (asset-based coping)</t>
         </is>
       </c>
     </row>
@@ -7114,33 +7114,29 @@
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>loan_amount</t>
+          <t>n_health_insured</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>amount (Rs)</t>
+          <t>whole number</t>
         </is>
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
-          <t>How much of that loan is still left to repay? (Rs)</t>
+          <t>How many people in your household are covered by any health insurance or health scheme, including government ones? (0 if none)</t>
         </is>
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>उस क़र्ज़ में से अब भी कितना चुकाना बाक़ी है? (रुपये)</t>
+          <t>आपके घर में कितने लोगों का कोई स्वास्थ्य बीमा या स्वास्थ्य योजना है, सरकारी भी मिलाकर? (कोई नहीं तो 0)</t>
         </is>
       </c>
       <c r="H147" s="2" t="inlineStr"/>
-      <c r="I147" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if took_loan_12m = 1</t>
-        </is>
-      </c>
+      <c r="I147" s="2" t="inlineStr"/>
       <c r="J147" s="2" t="inlineStr">
         <is>
-          <t>Islam and Chowdhury 2025 (financial distress and household vulnerability to poverty)</t>
+          <t>NITI Aayog National MPI health-insurance indicator; Lyons et al. 2023</t>
         </is>
       </c>
     </row>
@@ -7160,37 +7156,29 @@
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>pays_interest</t>
+          <t>n_life_insured</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>yes/no</t>
+          <t>whole number</t>
         </is>
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
-          <t>Do you pay interest on it?</t>
+          <t>How many people in your household have life insurance? (0 if none)</t>
         </is>
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>क्या आप उस पर ब्याज देते हैं?</t>
-        </is>
-      </c>
-      <c r="H148" s="2" t="inlineStr">
-        <is>
-          <t>0 No | 1 Yes</t>
-        </is>
-      </c>
-      <c r="I148" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if took_loan_12m = 1</t>
-        </is>
-      </c>
+          <t>आपके घर में कितने लोगों का जीवन बीमा है? (कोई नहीं तो 0)</t>
+        </is>
+      </c>
+      <c r="H148" s="2" t="inlineStr"/>
+      <c r="I148" s="2" t="inlineStr"/>
       <c r="J148" s="2" t="inlineStr">
         <is>
-          <t>Project design (informal lending is often interest-free)</t>
+          <t>Standard household-survey item</t>
         </is>
       </c>
     </row>
@@ -7210,33 +7198,37 @@
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>loan_interest_per100_pm</t>
+          <t>has_crop_insurance</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>yes/no</t>
         </is>
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
-          <t>On every 100 rupees you borrowed, about how much interest do you pay in a month? (Rs; 0 if none, leave blank if not known)</t>
+          <t>Is your crop insured?</t>
         </is>
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>आपने जो 100 रुपये उधार लिए, उन पर महीने का कितना ब्याज देते हैं? (रुपये; दर पता न हो तो खाली छोड़ दें)</t>
-        </is>
-      </c>
-      <c r="H149" s="2" t="inlineStr"/>
+          <t>क्या आपकी फ़सल का बीमा है?</t>
+        </is>
+      </c>
+      <c r="H149" s="2" t="inlineStr">
+        <is>
+          <t>0 No | 1 Yes</t>
+        </is>
+      </c>
       <c r="I149" s="2" t="inlineStr">
         <is>
-          <t>Ask only if took_loan_12m = 1; may be left blank</t>
+          <t>Ask only if land_cultivable_acres &gt; 0</t>
         </is>
       </c>
       <c r="J149" s="2" t="inlineStr">
         <is>
-          <t>Project design (informal-credit pricing as locally quoted)</t>
+          <t>Standard household-survey item</t>
         </is>
       </c>
     </row>
@@ -7256,37 +7248,33 @@
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>loan_against_asset</t>
+          <t>govt_schemes</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>yes/no</t>
+          <t>select multiple</t>
         </is>
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>Did you have to give something as security for it -- an animal, a vehicle, jewellery, land or your business?</t>
+          <t>In the last 12 months, did your household get anything from any of these? Read the list out and check every one they say yes to.</t>
         </is>
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>क्या उसके बदले कुछ गिरवी रखना पड़ा — जानवर, गाड़ी, गहने, ज़मीन या आपका धंधा?</t>
+          <t>पिछले 12 महीनों में इनमें से किसी से आपके घर को कुछ मिला? सूची पढ़कर सुनाइए और जिन-जिन पर वे हाँ कहें, सब पर निशान लगाइए।</t>
         </is>
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
-          <t>0 No | 1 Yes</t>
-        </is>
-      </c>
-      <c r="I150" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if took_loan_12m = 1</t>
-        </is>
-      </c>
+          <t>1 Ration card / PDS food grain | 2 MGNREGA work or job card | 3 Old-age, widow or disability pension | 4 PM-KISAN (farmer cash transfer) | 5 Ujjwala LPG connection | 6 PM-SYM or Atal Pension Yojana | 7 Ayushman Bharat / health insurance card | 8 Housing scheme (PMAY or state) | 9 Some other scheme | 10 None of these</t>
+        </is>
+      </c>
+      <c r="I150" s="2" t="inlineStr"/>
       <c r="J150" s="2" t="inlineStr">
         <is>
-          <t>Carter and Zimmerman 2000; Chiwaula et al. 2011 (asset-based vulnerability)</t>
+          <t>Project design; scheme names as administered in Uttarakhand</t>
         </is>
       </c>
     </row>
@@ -7306,37 +7294,33 @@
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>loan_collateral</t>
+          <t>govt_scheme_other</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>select one</t>
+          <t>free text</t>
         </is>
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
-          <t>What did you have to give as security?</t>
+          <t>Which scheme was that? Write what they say.</t>
         </is>
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>आपको क्या गिरवी रखना पड़ा?</t>
-        </is>
-      </c>
-      <c r="H151" s="2" t="inlineStr">
-        <is>
-          <t>1 Jewellery or ornaments | 2 Land | 3 Animals | 4 A vehicle | 5 Shop stock or business goods | 6 House or building | 7 Something else</t>
-        </is>
-      </c>
+          <t>वह कौन सी योजना थी? जैसा वे बताएँ वैसा लिख लीजिए।</t>
+        </is>
+      </c>
+      <c r="H151" s="2" t="inlineStr"/>
       <c r="I151" s="2" t="inlineStr">
         <is>
-          <t>Ask only if loan_against_asset = 1</t>
+          <t>Ask only if govt_schemes includes 9 (Some other scheme); may be left blank</t>
         </is>
       </c>
       <c r="J151" s="2" t="inlineStr">
         <is>
-          <t>Carter and Zimmerman 2000; Zimmerman and Carter 2003 (asset-based coping)</t>
+          <t>Standard household-survey item</t>
         </is>
       </c>
     </row>
@@ -7356,29 +7340,37 @@
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>n_health_insured</t>
+          <t>ration_portable_here</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>whole number</t>
+          <t>select one</t>
         </is>
       </c>
       <c r="F152" s="2" t="inlineStr">
         <is>
-          <t>How many people in your household are covered by any health insurance or health scheme, including government ones? (0 if none)</t>
+          <t>Can you draw your ration here, or only at your home place?</t>
         </is>
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>आपके घर में कितने लोगों का कोई स्वास्थ्य बीमा या स्वास्थ्य योजना है, सरकारी भी मिलाकर? (कोई नहीं तो 0)</t>
-        </is>
-      </c>
-      <c r="H152" s="2" t="inlineStr"/>
-      <c r="I152" s="2" t="inlineStr"/>
+          <t>क्या आप अपना राशन यहाँ ले सकते हैं, या सिर्फ़ अपने घर वाली जगह पर?</t>
+        </is>
+      </c>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t>1 Yes, can draw it here | 2 No, only at the home place | 3 Has never tried | 97 Does not know</t>
+        </is>
+      </c>
+      <c r="I152" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if govt_schemes includes 1 (ration card)</t>
+        </is>
+      </c>
       <c r="J152" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI health-insurance indicator; Lyons et al. 2023</t>
+          <t>Lyons et al. 2023, Table 2 (legal residency), adapted; One Nation One Ration Card</t>
         </is>
       </c>
     </row>
@@ -7398,29 +7390,33 @@
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>n_life_insured</t>
+          <t>smartphone_owned</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>whole number</t>
+          <t>yes/no</t>
         </is>
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
-          <t>How many people in your household have life insurance? (0 if none)</t>
+          <t>Do you own a smartphone?</t>
         </is>
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>आपके घर में कितने लोगों का जीवन बीमा है? (कोई नहीं तो 0)</t>
-        </is>
-      </c>
-      <c r="H153" s="2" t="inlineStr"/>
+          <t>क्या आपके पास स्मार्टफ़ोन है?</t>
+        </is>
+      </c>
+      <c r="H153" s="2" t="inlineStr">
+        <is>
+          <t>0 No | 1 Yes</t>
+        </is>
+      </c>
       <c r="I153" s="2" t="inlineStr"/>
       <c r="J153" s="2" t="inlineStr">
         <is>
-          <t>Standard household-survey item</t>
+          <t>VEP adaptive-capacity covariate; STEP digital items</t>
         </is>
       </c>
     </row>
@@ -7440,7 +7436,7 @@
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>has_crop_insurance</t>
+          <t>uses_digital_payment</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
@@ -7450,12 +7446,12 @@
       </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
-          <t>Is your crop insured?</t>
+          <t>Do you ever use UPI or another way of paying by phone?</t>
         </is>
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>क्या आपकी फ़सल का बीमा है?</t>
+          <t>क्या आप कभी UPI या फ़ोन से पैसे का लेन-देन करते हैं?</t>
         </is>
       </c>
       <c r="H154" s="2" t="inlineStr">
@@ -7463,14 +7459,10 @@
           <t>0 No | 1 Yes</t>
         </is>
       </c>
-      <c r="I154" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if land_cultivable_acres &gt; 0</t>
-        </is>
-      </c>
+      <c r="I154" s="2" t="inlineStr"/>
       <c r="J154" s="2" t="inlineStr">
         <is>
-          <t>Standard household-survey item</t>
+          <t>VEP adaptive-capacity covariate; STEP digital items</t>
         </is>
       </c>
     </row>
@@ -7490,33 +7482,29 @@
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>govt_schemes</t>
+          <t>n_can_transact_online</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>select multiple</t>
+          <t>whole number</t>
         </is>
       </c>
       <c r="F155" s="2" t="inlineStr">
         <is>
-          <t>In the last 12 months, did your household get anything from any of these? Read the list out and check every one they say yes to.</t>
+          <t>How many people in your household can make a payment by phone themselves, without help? (0 if none)</t>
         </is>
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>पिछले 12 महीनों में इनमें से किसी से आपके घर को कुछ मिला? सूची पढ़कर सुनाइए और जिन-जिन पर वे हाँ कहें, सब पर निशान लगाइए।</t>
-        </is>
-      </c>
-      <c r="H155" s="2" t="inlineStr">
-        <is>
-          <t>1 Ration card / PDS food grain | 2 MGNREGA work or job card | 3 Old-age, widow or disability pension | 4 PM-KISAN (farmer cash transfer) | 5 Ujjwala LPG connection | 6 PM-SYM or Atal Pension Yojana | 7 Ayushman Bharat / health insurance card | 8 Housing scheme (PMAY or state) | 9 Some other scheme | 10 None of these</t>
-        </is>
-      </c>
+          <t>आपके घर में कितने लोग बिना किसी की मदद के फ़ोन से पैसे भेज सकते हैं? (कोई नहीं तो 0)</t>
+        </is>
+      </c>
+      <c r="H155" s="2" t="inlineStr"/>
       <c r="I155" s="2" t="inlineStr"/>
       <c r="J155" s="2" t="inlineStr">
         <is>
-          <t>Project design; scheme names as administered in Uttarakhand</t>
+          <t>Project design (intra-household financial capability)</t>
         </is>
       </c>
     </row>
@@ -7526,43 +7514,43 @@
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>Finance, insurance and schemes</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>govt_scheme_other</t>
+          <t>morbidity_15d</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>free text</t>
+          <t>yes/no</t>
         </is>
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
-          <t>Which scheme was that? Write what they say.</t>
+          <t>In the last 15 days, was anyone in your household ill?</t>
         </is>
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>वह कौन सी योजना थी? जैसा वे बताएँ वैसा लिख लीजिए।</t>
-        </is>
-      </c>
-      <c r="H156" s="2" t="inlineStr"/>
-      <c r="I156" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if govt_schemes includes 9 (Some other scheme); may be left blank</t>
-        </is>
-      </c>
+          <t>पिछले 15 दिनों में क्या आपके घर में कोई बीमार पड़ा?</t>
+        </is>
+      </c>
+      <c r="H156" s="2" t="inlineStr">
+        <is>
+          <t>0 No | 1 Yes</t>
+        </is>
+      </c>
+      <c r="I156" s="2" t="inlineStr"/>
       <c r="J156" s="2" t="inlineStr">
         <is>
-          <t>Standard household-survey item</t>
+          <t>NSS health module (15-day recall) [source not held by this project; citation unverified as of 2026-09-28]</t>
         </is>
       </c>
     </row>
@@ -7572,17 +7560,17 @@
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>Finance, insurance and schemes</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>ration_portable_here</t>
+          <t>morbidity_coping_15d</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
@@ -7592,27 +7580,27 @@
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
-          <t>Can you draw your ration here, or only at your home place?</t>
+          <t>How did the household mainly cope with the cost of this: used savings; borrowed money; sold or pawned assets; cut other consumption; got help from relatives or community; or something else?</t>
         </is>
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>क्या आप अपना राशन यहाँ ले सकते हैं, या सिर्फ़ अपने घर वाली जगह पर?</t>
+          <t>इसका ख़र्च आपके घर ने मुख्य रूप से कैसे उठाया: जमा पैसे से; उधार लेकर; कुछ बेचकर या गिरवी रखकर; बाकी ख़र्च घटाकर; रिश्तेदारों या गाँव वालों की मदद से; या किसी और तरह?</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
         <is>
-          <t>1 Yes, can draw it here | 2 No, only at the home place | 3 Has never tried | 97 Does not know</t>
+          <t>1 Used savings | 2 Borrowed money | 3 Sold or pawned assets | 4 Cut consumption | 5 Help from relatives/community | 6 Did nothing/other</t>
         </is>
       </c>
       <c r="I157" s="2" t="inlineStr">
         <is>
-          <t>Ask only if govt_schemes includes 1 (ration card)</t>
+          <t>Ask only if morbidity_15d = 1</t>
         </is>
       </c>
       <c r="J157" s="2" t="inlineStr">
         <is>
-          <t>Lyons et al. 2023, Table 2 (legal residency), adapted; One Nation One Ration Card</t>
+          <t>Project design (a reported illness with no cost/coping follow-up said nothing about its burden)</t>
         </is>
       </c>
     </row>
@@ -7622,43 +7610,43 @@
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>Finance, insurance and schemes</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>smartphone_owned</t>
+          <t>morbidity_cost_15d</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>yes/no</t>
+          <t>amount (Rs)</t>
         </is>
       </c>
       <c r="F158" s="2" t="inlineStr">
         <is>
-          <t>Do you own a smartphone?</t>
+          <t>About how much did the household spend on this in the last 15 days (medicine, doctor or clinic fees, travel for care)? (Rs)</t>
         </is>
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>क्या आपके पास स्मार्टफ़ोन है?</t>
-        </is>
-      </c>
-      <c r="H158" s="2" t="inlineStr">
-        <is>
-          <t>0 No | 1 Yes</t>
-        </is>
-      </c>
-      <c r="I158" s="2" t="inlineStr"/>
+          <t>पिछले 15 दिनों में इस पर घर का लगभग कितना ख़र्च हुआ (दवाई, डॉक्टर या क्लीनिक की फ़ीस, आने-जाने का ख़र्च)? (रुपये)</t>
+        </is>
+      </c>
+      <c r="H158" s="2" t="inlineStr"/>
+      <c r="I158" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if morbidity_15d = 1</t>
+        </is>
+      </c>
       <c r="J158" s="2" t="inlineStr">
         <is>
-          <t>VEP adaptive-capacity covariate; STEP digital items</t>
+          <t>Project design</t>
         </is>
       </c>
     </row>
@@ -7668,43 +7656,43 @@
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>Finance, insurance and schemes</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>uses_digital_payment</t>
+          <t>func_limitation</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>yes/no</t>
+          <t>select one</t>
         </is>
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
-          <t>Do you ever use UPI or another way of paying by phone?</t>
+          <t>Do you have difficulty walking or climbing steps?</t>
         </is>
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>क्या आप कभी UPI या फ़ोन से पैसे का लेन-देन करते हैं?</t>
+          <t>क्या आपको चलने या सीढ़ियाँ चढ़ने में दिक़्क़त होती है?</t>
         </is>
       </c>
       <c r="H159" s="2" t="inlineStr">
         <is>
-          <t>0 No | 1 Yes</t>
+          <t>1 No difficulty | 2 Some difficulty | 3 A lot of difficulty | 4 Cannot do it at all</t>
         </is>
       </c>
       <c r="I159" s="2" t="inlineStr"/>
       <c r="J159" s="2" t="inlineStr">
         <is>
-          <t>VEP adaptive-capacity covariate; STEP digital items</t>
+          <t>Washington Group on Disability Statistics, Short Set item 3 (mobility), verbatim; Lyons et al. 2023 health dimension</t>
         </is>
       </c>
     </row>
@@ -7714,39 +7702,43 @@
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>Finance, insurance and schemes</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>n_can_transact_online</t>
+          <t>hospitalization_365d</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>whole number</t>
+          <t>yes/no</t>
         </is>
       </c>
       <c r="F160" s="2" t="inlineStr">
         <is>
-          <t>How many people in your household can make a payment by phone themselves, without help? (0 if none)</t>
+          <t>In the last 12 months, was anyone in your household admitted to hospital overnight?</t>
         </is>
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>आपके घर में कितने लोग बिना किसी की मदद के फ़ोन से पैसे भेज सकते हैं? (कोई नहीं तो 0)</t>
-        </is>
-      </c>
-      <c r="H160" s="2" t="inlineStr"/>
+          <t>पिछले 12 महीनों में क्या आपके घर का कोई रात भर के लिए अस्पताल में भर्ती हुआ?</t>
+        </is>
+      </c>
+      <c r="H160" s="2" t="inlineStr">
+        <is>
+          <t>0 No | 1 Yes</t>
+        </is>
+      </c>
       <c r="I160" s="2" t="inlineStr"/>
       <c r="J160" s="2" t="inlineStr">
         <is>
-          <t>Project design (intra-household financial capability)</t>
+          <t>NSS health module (365-day recall) [source not held by this project; citation unverified as of 2026-09-28]</t>
         </is>
       </c>
     </row>
@@ -7766,7 +7758,7 @@
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>morbidity_15d</t>
+          <t>health_access_barrier_3m</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
@@ -7776,12 +7768,12 @@
       </c>
       <c r="F161" s="2" t="inlineStr">
         <is>
-          <t>In the last 15 days, was anyone in your household ill?</t>
+          <t>In the last 3 months, was there a time when someone in your household needed medical care but could not get it?</t>
         </is>
       </c>
       <c r="G161" s="2" t="inlineStr">
         <is>
-          <t>पिछले 15 दिनों में क्या आपके घर में कोई बीमार पड़ा?</t>
+          <t>पिछले 3 महीनों में क्या कभी ऐसा हुआ कि आपके घर में किसी को इलाज की ज़रूरत थी पर मिल नहीं पाया?</t>
         </is>
       </c>
       <c r="H161" s="2" t="inlineStr">
@@ -7792,7 +7784,7 @@
       <c r="I161" s="2" t="inlineStr"/>
       <c r="J161" s="2" t="inlineStr">
         <is>
-          <t>NSS health module (15-day recall) [source not held by this project; citation unverified as of 2026-09-28]</t>
+          <t>VASyR 2025 barriers_health_case_access_phc_m (primary-care access barriers); Lyons et al. 2023 Table 2 indicator 2 'healthcare access'</t>
         </is>
       </c>
     </row>
@@ -7812,37 +7804,33 @@
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>morbidity_coping_15d</t>
+          <t>child_death_5y</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>select one</t>
+          <t>yes/no</t>
         </is>
       </c>
       <c r="F162" s="2" t="inlineStr">
         <is>
-          <t>How did the household mainly cope with the cost of this: used savings; borrowed money; sold or pawned assets; cut other consumption; got help from relatives or community; or something else?</t>
+          <t>In the last five years, has any child or young person under 18 in your household died?</t>
         </is>
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>इसका ख़र्च आपके घर ने मुख्य रूप से कैसे उठाया: जमा पैसे से; उधार लेकर; कुछ बेचकर या गिरवी रखकर; बाकी ख़र्च घटाकर; रिश्तेदारों या गाँव वालों की मदद से; या किसी और तरह?</t>
+          <t>पिछले पाँच साल में क्या आपके घर के 18 साल से छोटे किसी बच्चे या किशोर की मृत्यु हुई?</t>
         </is>
       </c>
       <c r="H162" s="2" t="inlineStr">
         <is>
-          <t>1 Used savings | 2 Borrowed money | 3 Sold or pawned assets | 4 Cut consumption | 5 Help from relatives/community | 6 Did nothing/other</t>
-        </is>
-      </c>
-      <c r="I162" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if morbidity_15d = 1</t>
-        </is>
-      </c>
+          <t>0 No | 1 Yes</t>
+        </is>
+      </c>
+      <c r="I162" s="2" t="inlineStr"/>
       <c r="J162" s="2" t="inlineStr">
         <is>
-          <t>Project design (a reported illness with no cost/coping follow-up said nothing about its burden)</t>
+          <t>NITI Aayog National MPI, Child and Adolescent Mortality (weight 1/12)</t>
         </is>
       </c>
     </row>
@@ -7862,33 +7850,33 @@
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>morbidity_cost_15d</t>
+          <t>birth_last_5y</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>amount (Rs)</t>
+          <t>yes/no</t>
         </is>
       </c>
       <c r="F163" s="2" t="inlineStr">
         <is>
-          <t>About how much did the household spend on this in the last 15 days (medicine, doctor or clinic fees, travel for care)? (Rs)</t>
+          <t>In the last five years, did any woman in your household give birth?</t>
         </is>
       </c>
       <c r="G163" s="2" t="inlineStr">
         <is>
-          <t>पिछले 15 दिनों में इस पर घर का लगभग कितना ख़र्च हुआ (दवाई, डॉक्टर या क्लीनिक की फ़ीस, आने-जाने का ख़र्च)? (रुपये)</t>
-        </is>
-      </c>
-      <c r="H163" s="2" t="inlineStr"/>
-      <c r="I163" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if morbidity_15d = 1</t>
-        </is>
-      </c>
+          <t>पिछले पाँच साल में क्या आपके घर की किसी महिला ने बच्चे को जन्म दिया?</t>
+        </is>
+      </c>
+      <c r="H163" s="2" t="inlineStr">
+        <is>
+          <t>0 No | 1 Yes</t>
+        </is>
+      </c>
+      <c r="I163" s="2" t="inlineStr"/>
       <c r="J163" s="2" t="inlineStr">
         <is>
-          <t>Project design</t>
+          <t>NITI Aayog National MPI, Maternal Health (weight 1/12)</t>
         </is>
       </c>
     </row>
@@ -7908,7 +7896,7 @@
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>func_limitation</t>
+          <t>anc_4_visits</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
@@ -7918,23 +7906,27 @@
       </c>
       <c r="F164" s="2" t="inlineStr">
         <is>
-          <t>Do you have difficulty walking or climbing steps?</t>
+          <t>For the most recent birth, did she have at least four check-ups before the delivery?</t>
         </is>
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>क्या आपको चलने या सीढ़ियाँ चढ़ने में दिक़्क़त होती है?</t>
+          <t>सबसे हाल के जन्म के लिए, क्या डिलीवरी से पहले उनकी कम से कम चार बार जाँच हुई थी?</t>
         </is>
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
-          <t>1 No difficulty | 2 Some difficulty | 3 A lot of difficulty | 4 Cannot do it at all</t>
-        </is>
-      </c>
-      <c r="I164" s="2" t="inlineStr"/>
+          <t>0 No | 1 Yes | 97 Don't know</t>
+        </is>
+      </c>
+      <c r="I164" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if birth_last_5y = 1</t>
+        </is>
+      </c>
       <c r="J164" s="2" t="inlineStr">
         <is>
-          <t>Washington Group on Disability Statistics, Short Set item 3 (mobility), verbatim; Lyons et al. 2023 health dimension</t>
+          <t>NITI Aayog National MPI, Maternal Health (antenatal care limb)</t>
         </is>
       </c>
     </row>
@@ -7954,33 +7946,37 @@
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t>hospitalization_365d</t>
+          <t>skilled_birth_attendant</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>yes/no</t>
+          <t>select one</t>
         </is>
       </c>
       <c r="F165" s="2" t="inlineStr">
         <is>
-          <t>In the last 12 months, was anyone in your household admitted to hospital overnight?</t>
+          <t>Was that delivery done with the help of a doctor, nurse or trained midwife?</t>
         </is>
       </c>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>पिछले 12 महीनों में क्या आपके घर का कोई रात भर के लिए अस्पताल में भर्ती हुआ?</t>
+          <t>क्या वह डिलीवरी डॉक्टर, नर्स या प्रशिक्षित दाई की मदद से हुई थी?</t>
         </is>
       </c>
       <c r="H165" s="2" t="inlineStr">
         <is>
-          <t>0 No | 1 Yes</t>
-        </is>
-      </c>
-      <c r="I165" s="2" t="inlineStr"/>
+          <t>0 No | 1 Yes | 97 Don't know</t>
+        </is>
+      </c>
+      <c r="I165" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if birth_last_5y = 1</t>
+        </is>
+      </c>
       <c r="J165" s="2" t="inlineStr">
         <is>
-          <t>NSS health module (365-day recall) [source not held by this project; citation unverified as of 2026-09-28]</t>
+          <t>NITI Aayog National MPI, Maternal Health (assisted delivery limb)</t>
         </is>
       </c>
     </row>
@@ -7990,43 +7986,43 @@
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Food security, shocks and coping</t>
         </is>
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>health_access_barrier_3m</t>
+          <t>distress_event_last365d</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>yes/no</t>
+          <t>select multiple</t>
         </is>
       </c>
       <c r="F166" s="2" t="inlineStr">
         <is>
-          <t>In the last 3 months, was there a time when someone in your household needed medical care but could not get it?</t>
+          <t>In the last 12 months, did any of these happen -- to your household, or to the Yatra route you work on? Check every one that applies.</t>
         </is>
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>पिछले 3 महीनों में क्या कभी ऐसा हुआ कि आपके घर में किसी को इलाज की ज़रूरत थी पर मिल नहीं पाया?</t>
+          <t>पिछले 12 महीनों में इनमें से क्या-क्या हुआ — आपके घर के साथ, या जिस यात्रा मार्ग पर आप काम करते हैं उस पर? जो-जो हुआ, सब चुनिए।</t>
         </is>
       </c>
       <c r="H166" s="2" t="inlineStr">
         <is>
-          <t>0 No | 1 Yes</t>
+          <t>1 Serious illness or death of an earning member | 2 Crop failure or livestock loss | 3 Damage from a natural disaster (flood, landslide, fire) | 4 Loss of business, goods or assets | 5 Road or bridge blocked, route closed | 6 Yatra stopped early or badly disrupted | 7 Sharp fall in customers or prices | 8 Lost the work or the work stopped</t>
         </is>
       </c>
       <c r="I166" s="2" t="inlineStr"/>
       <c r="J166" s="2" t="inlineStr">
         <is>
-          <t>VASyR 2025 barriers_health_case_access_phc_m (primary-care access barriers); Lyons et al. 2023 Table 2 indicator 2 'healthcare access'</t>
+          <t>VEP exposure covariate (Azeem et al. 2016); shock inventory following Gunther and Harttgen 2009, via Fujii 2016 section 4</t>
         </is>
       </c>
     </row>
@@ -8036,43 +8032,47 @@
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Food security, shocks and coping</t>
         </is>
       </c>
       <c r="D167" s="2" t="inlineStr">
         <is>
-          <t>child_death_5y</t>
+          <t>shock_worst</t>
         </is>
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>yes/no</t>
+          <t>select one</t>
         </is>
       </c>
       <c r="F167" s="2" t="inlineStr">
         <is>
-          <t>In the last five years, has any child or young person under 18 in your household died?</t>
+          <t>Of those, which one was hardest for your household?</t>
         </is>
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>पिछले पाँच साल में क्या आपके घर के 18 साल से छोटे किसी बच्चे या किशोर की मृत्यु हुई?</t>
+          <t>इनमें से आपके घर के लिए सबसे मुश्किल कौन सा रहा?</t>
         </is>
       </c>
       <c r="H167" s="2" t="inlineStr">
         <is>
-          <t>0 No | 1 Yes</t>
-        </is>
-      </c>
-      <c r="I167" s="2" t="inlineStr"/>
+          <t>1 Serious illness or death of an earning member | 2 Crop failure or livestock loss | 3 Damage from a natural disaster (flood, landslide, fire) | 4 Loss of business, goods or assets | 5 Road or bridge blocked, route closed | 6 Yatra stopped early or badly disrupted | 7 Sharp fall in customers or prices | 8 Lost the work or the work stopped</t>
+        </is>
+      </c>
+      <c r="I167" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if distress_event_last365d is not empty</t>
+        </is>
+      </c>
       <c r="J167" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI, Child and Adolescent Mortality (weight 1/12)</t>
+          <t>Project design (anchors the magnitude and timing pair)</t>
         </is>
       </c>
     </row>
@@ -8082,43 +8082,43 @@
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Food security, shocks and coping</t>
         </is>
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>birth_last_5y</t>
+          <t>shock_loss_amount</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>yes/no</t>
+          <t>amount (Rs)</t>
         </is>
       </c>
       <c r="F168" s="2" t="inlineStr">
         <is>
-          <t>In the last five years, did any woman in your household give birth?</t>
+          <t>Because of that, about how much did your household lose in earnings, or have to spend? (Rs)</t>
         </is>
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>पिछले पाँच साल में क्या आपके घर की किसी महिला ने बच्चे को जन्म दिया?</t>
-        </is>
-      </c>
-      <c r="H168" s="2" t="inlineStr">
-        <is>
-          <t>0 No | 1 Yes</t>
-        </is>
-      </c>
-      <c r="I168" s="2" t="inlineStr"/>
+          <t>उसकी वजह से आपके घर की कितनी कमाई गई, या कितना ख़र्च करना पड़ा? (रुपये)</t>
+        </is>
+      </c>
+      <c r="H168" s="2" t="inlineStr"/>
+      <c r="I168" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if distress_event_last365d is not empty</t>
+        </is>
+      </c>
       <c r="J168" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI, Maternal Health (weight 1/12)</t>
+          <t>Ligon and Schechter 2003; Dercon and Krishnan 2000 (VER needs shock magnitude, not only incidence)</t>
         </is>
       </c>
     </row>
@@ -8128,17 +8128,17 @@
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Food security, shocks and coping</t>
         </is>
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t>anc_4_visits</t>
+          <t>shock_month</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr">
@@ -8148,27 +8148,27 @@
       </c>
       <c r="F169" s="2" t="inlineStr">
         <is>
-          <t>For the most recent birth, did she have at least four check-ups before the delivery?</t>
+          <t>In which month did that happen?</t>
         </is>
       </c>
       <c r="G169" s="2" t="inlineStr">
         <is>
-          <t>सबसे हाल के जन्म के लिए, क्या डिलीवरी से पहले उनकी कम से कम चार बार जाँच हुई थी?</t>
+          <t>वह किस महीने हुआ था?</t>
         </is>
       </c>
       <c r="H169" s="2" t="inlineStr">
         <is>
-          <t>0 No | 1 Yes | 97 Don't know</t>
+          <t>1 January | 2 February | 3 March | 4 April | 5 May | 6 June | 7 July | 8 August | 9 September | 10 October | 11 November | 12 December</t>
         </is>
       </c>
       <c r="I169" s="2" t="inlineStr">
         <is>
-          <t>Ask only if birth_last_5y = 1</t>
+          <t>Ask only if distress_event_last365d is not empty</t>
         </is>
       </c>
       <c r="J169" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI, Maternal Health (antenatal care limb)</t>
+          <t>Dercon and Krishnan 2000 (seasonal timing of shocks); project design</t>
         </is>
       </c>
     </row>
@@ -8178,47 +8178,47 @@
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Food security, shocks and coping</t>
         </is>
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>skilled_birth_attendant</t>
+          <t>shock_coping</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>select one</t>
+          <t>select multiple</t>
         </is>
       </c>
       <c r="F170" s="2" t="inlineStr">
         <is>
-          <t>Was that delivery done with the help of a doctor, nurse or trained midwife?</t>
+          <t>How did your household manage? Check every one they used.</t>
         </is>
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>क्या वह डिलीवरी डॉक्टर, नर्स या प्रशिक्षित दाई की मदद से हुई थी?</t>
+          <t>आपके घर ने कैसे सँभाला? उन्होंने जो-जो किया, सब चुनिए।</t>
         </is>
       </c>
       <c r="H170" s="2" t="inlineStr">
         <is>
-          <t>0 No | 1 Yes | 97 Don't know</t>
+          <t>1 Used savings | 2 Borrowed money | 3 Sold or pawned assets | 4 Cut consumption | 5 Help from relatives/community | 6 Did nothing/other</t>
         </is>
       </c>
       <c r="I170" s="2" t="inlineStr">
         <is>
-          <t>Ask only if birth_last_5y = 1</t>
+          <t>Ask only if any shock was reported</t>
         </is>
       </c>
       <c r="J170" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI, Maternal Health (assisted delivery limb)</t>
+          <t>Coping strategies in VEP studies; Carter and Zimmerman 2000 on asset versus consumption smoothing</t>
         </is>
       </c>
     </row>
@@ -8238,33 +8238,29 @@
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t>distress_event_last365d</t>
+          <t>cope_less_pref_food_yatra_wk</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
-          <t>select multiple</t>
+          <t>whole number</t>
         </is>
       </c>
       <c r="F171" s="2" t="inlineStr">
         <is>
-          <t>In the last 12 months, did any of these happen -- to your household, or to the Yatra route you work on? Check every one that applies.</t>
+          <t>In a normal week during the Yatra season, to cope with a lack of food or money to buy it, how many days did your household rely on less expensive/less preferred food? (0-7 days)</t>
         </is>
       </c>
       <c r="G171" s="2" t="inlineStr">
         <is>
-          <t>पिछले 12 महीनों में इनमें से क्या-क्या हुआ — आपके घर के साथ, या जिस यात्रा मार्ग पर आप काम करते हैं उस पर? जो-जो हुआ, सब चुनिए।</t>
-        </is>
-      </c>
-      <c r="H171" s="2" t="inlineStr">
-        <is>
-          <t>1 Serious illness or death of an earning member | 2 Crop failure or livestock loss | 3 Damage from a natural disaster (flood, landslide, fire) | 4 Loss of business, goods or assets | 5 Road or bridge blocked, route closed | 6 Yatra stopped early or badly disrupted | 7 Sharp fall in customers or prices | 8 Lost the work or the work stopped</t>
-        </is>
-      </c>
+          <t>यात्रा के मौसम के आम हफ़्ते में, खाने की या खाना ख़रीदने के पैसे की कमी से निपटने के लिए आपके घर ने कितने दिन सस्ता या कम पसंद का खाना खाया? (0-7 दिन)</t>
+        </is>
+      </c>
+      <c r="H171" s="2" t="inlineStr"/>
       <c r="I171" s="2" t="inlineStr"/>
       <c r="J171" s="2" t="inlineStr">
         <is>
-          <t>VEP exposure covariate (Azeem et al. 2016); shock inventory following Gunther and Harttgen 2009, via Fujii 2016 section 4</t>
+          <t>VASyR 2025 (exact item wording); WFP rCSI; The reduced Coping Strategy Index (rCSI): five food-coping questions, standard WFP weights (1, 2, 1, 1, 3) applied when the index is built. The Kedarnath instrument otherwise has no food-security module, which is a gap for a poverty-vulnerability survey; these five short questions close it at low cost instead of a full dietary-diversity module, left out to stay inside the 45-minute limit. Kept as day-counts (0-7), not collapsed to yes/no: this is the standard, validated WFP/FAO specification (frequency x severity), and no comparably-standard binary version was found on checking; a day-count also takes about as long to answer as a yes/no in practice, so little interview time is saved by simplifying it.</t>
         </is>
       </c>
     </row>
@@ -8284,37 +8280,29 @@
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>shock_worst</t>
+          <t>cope_less_pref_food_offseason_wk</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>select one</t>
+          <t>whole number</t>
         </is>
       </c>
       <c r="F172" s="2" t="inlineStr">
         <is>
-          <t>Of those, which one was hardest for your household?</t>
+          <t>In a normal week when the Yatra is closed, to cope with a lack of food or money to buy it, how many days did your household rely on less expensive/less preferred food? (0-7 days)</t>
         </is>
       </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t>इनमें से आपके घर के लिए सबसे मुश्किल कौन सा रहा?</t>
-        </is>
-      </c>
-      <c r="H172" s="2" t="inlineStr">
-        <is>
-          <t>1 Serious illness or death of an earning member | 2 Crop failure or livestock loss | 3 Damage from a natural disaster (flood, landslide, fire) | 4 Loss of business, goods or assets | 5 Road or bridge blocked, route closed | 6 Yatra stopped early or badly disrupted | 7 Sharp fall in customers or prices | 8 Lost the work or the work stopped</t>
-        </is>
-      </c>
-      <c r="I172" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if distress_event_last365d is not empty</t>
-        </is>
-      </c>
+          <t>जब यात्रा बंद रहती है, उस आम हफ़्ते में आपके घर ने कितने दिन सस्ता या कम पसंद का खाना खाया? (0-7 दिन)</t>
+        </is>
+      </c>
+      <c r="H172" s="2" t="inlineStr"/>
+      <c r="I172" s="2" t="inlineStr"/>
       <c r="J172" s="2" t="inlineStr">
         <is>
-          <t>Project design (anchors the magnitude and timing pair)</t>
+          <t>VASyR 2025 (exact item wording); WFP rCSI; The reduced Coping Strategy Index (rCSI): five food-coping questions, standard WFP weights (1, 2, 1, 1, 3) applied when the index is built. The Kedarnath instrument otherwise has no food-security module, which is a gap for a poverty-vulnerability survey; these five short questions close it at low cost instead of a full dietary-diversity module, left out to stay inside the 45-minute limit. Kept as day-counts (0-7), not collapsed to yes/no: this is the standard, validated WFP/FAO specification (frequency x severity), and no comparably-standard binary version was found on checking; a day-count also takes about as long to answer as a yes/no in practice, so little interview time is saved by simplifying it.</t>
         </is>
       </c>
     </row>
@@ -8334,33 +8322,29 @@
       </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t>shock_loss_amount</t>
+          <t>cope_borrow_food_yatra_wk</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr">
         <is>
-          <t>amount (Rs)</t>
+          <t>whole number</t>
         </is>
       </c>
       <c r="F173" s="2" t="inlineStr">
         <is>
-          <t>Because of that, about how much did your household lose in earnings, or have to spend? (Rs)</t>
+          <t>In a normal week during the Yatra season, to cope with a lack of food or money to buy it, how many days did your household borrow food and/or rely on help from friends/relatives? (0-7 days)</t>
         </is>
       </c>
       <c r="G173" s="2" t="inlineStr">
         <is>
-          <t>उसकी वजह से आपके घर की कितनी कमाई गई, या कितना ख़र्च करना पड़ा? (रुपये)</t>
+          <t>यात्रा के मौसम के आम हफ़्ते में, खाने की या खाना ख़रीदने के पैसे की कमी से निपटने के लिए आपके घर ने कितने दिन खाना उधार लिया या दोस्तों/रिश्तेदारों की मदद ली? (0-7 दिन)</t>
         </is>
       </c>
       <c r="H173" s="2" t="inlineStr"/>
-      <c r="I173" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if distress_event_last365d is not empty</t>
-        </is>
-      </c>
+      <c r="I173" s="2" t="inlineStr"/>
       <c r="J173" s="2" t="inlineStr">
         <is>
-          <t>Ligon and Schechter 2003; Dercon and Krishnan 2000 (VER needs shock magnitude, not only incidence)</t>
+          <t>VASyR 2025 (exact item wording); WFP rCSI; The reduced Coping Strategy Index (rCSI): five food-coping questions, standard WFP weights (1, 2, 1, 1, 3) applied when the index is built. The Kedarnath instrument otherwise has no food-security module, which is a gap for a poverty-vulnerability survey; these five short questions close it at low cost instead of a full dietary-diversity module, left out to stay inside the 45-minute limit. Kept as day-counts (0-7), not collapsed to yes/no: this is the standard, validated WFP/FAO specification (frequency x severity), and no comparably-standard binary version was found on checking; a day-count also takes about as long to answer as a yes/no in practice, so little interview time is saved by simplifying it.</t>
         </is>
       </c>
     </row>
@@ -8380,37 +8364,29 @@
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>shock_month</t>
+          <t>cope_borrow_food_offseason_wk</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>select one</t>
+          <t>whole number</t>
         </is>
       </c>
       <c r="F174" s="2" t="inlineStr">
         <is>
-          <t>In which month did that happen?</t>
+          <t>In a normal week when the Yatra is closed, to cope with a lack of food or money to buy it, how many days did your household borrow food and/or rely on help from friends/relatives? (0-7 days)</t>
         </is>
       </c>
       <c r="G174" s="2" t="inlineStr">
         <is>
-          <t>वह किस महीने हुआ था?</t>
-        </is>
-      </c>
-      <c r="H174" s="2" t="inlineStr">
-        <is>
-          <t>1 January | 2 February | 3 March | 4 April | 5 May | 6 June | 7 July | 8 August | 9 September | 10 October | 11 November | 12 December</t>
-        </is>
-      </c>
-      <c r="I174" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if distress_event_last365d is not empty</t>
-        </is>
-      </c>
+          <t>जब यात्रा बंद रहती है, उस आम हफ़्ते में आपके घर ने कितने दिन खाना उधार लिया या दोस्तों/रिश्तेदारों की मदद ली? (0-7 दिन)</t>
+        </is>
+      </c>
+      <c r="H174" s="2" t="inlineStr"/>
+      <c r="I174" s="2" t="inlineStr"/>
       <c r="J174" s="2" t="inlineStr">
         <is>
-          <t>Dercon and Krishnan 2000 (seasonal timing of shocks); project design</t>
+          <t>VASyR 2025 (exact item wording); WFP rCSI; The reduced Coping Strategy Index (rCSI): five food-coping questions, standard WFP weights (1, 2, 1, 1, 3) applied when the index is built. The Kedarnath instrument otherwise has no food-security module, which is a gap for a poverty-vulnerability survey; these five short questions close it at low cost instead of a full dietary-diversity module, left out to stay inside the 45-minute limit. Kept as day-counts (0-7), not collapsed to yes/no: this is the standard, validated WFP/FAO specification (frequency x severity), and no comparably-standard binary version was found on checking; a day-count also takes about as long to answer as a yes/no in practice, so little interview time is saved by simplifying it.</t>
         </is>
       </c>
     </row>
@@ -8430,37 +8406,29 @@
       </c>
       <c r="D175" s="2" t="inlineStr">
         <is>
-          <t>shock_coping</t>
+          <t>cope_reduce_meals_yatra_wk</t>
         </is>
       </c>
       <c r="E175" s="2" t="inlineStr">
         <is>
-          <t>select multiple</t>
+          <t>whole number</t>
         </is>
       </c>
       <c r="F175" s="2" t="inlineStr">
         <is>
-          <t>How did your household manage? Check every one they used.</t>
+          <t>In a normal week during the Yatra season, to cope with a lack of food or money to buy it, how many days did your household reduce the number of meals eaten per day? (0-7 days)</t>
         </is>
       </c>
       <c r="G175" s="2" t="inlineStr">
         <is>
-          <t>आपके घर ने कैसे सँभाला? उन्होंने जो-जो किया, सब चुनिए।</t>
-        </is>
-      </c>
-      <c r="H175" s="2" t="inlineStr">
-        <is>
-          <t>1 Used savings | 2 Borrowed money | 3 Sold or pawned assets | 4 Cut consumption | 5 Help from relatives/community | 6 Did nothing/other</t>
-        </is>
-      </c>
-      <c r="I175" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if any shock was reported</t>
-        </is>
-      </c>
+          <t>यात्रा के मौसम के आम हफ़्ते में, खाने की या खाना ख़रीदने के पैसे की कमी से निपटने के लिए आपके घर ने कितने दिन दिन में कम बार खाना खाया? (0-7 दिन)</t>
+        </is>
+      </c>
+      <c r="H175" s="2" t="inlineStr"/>
+      <c r="I175" s="2" t="inlineStr"/>
       <c r="J175" s="2" t="inlineStr">
         <is>
-          <t>Coping strategies in VEP studies; Carter and Zimmerman 2000 on asset versus consumption smoothing</t>
+          <t>VASyR 2025 (exact item wording); WFP rCSI; The reduced Coping Strategy Index (rCSI): five food-coping questions, standard WFP weights (1, 2, 1, 1, 3) applied when the index is built. The Kedarnath instrument otherwise has no food-security module, which is a gap for a poverty-vulnerability survey; these five short questions close it at low cost instead of a full dietary-diversity module, left out to stay inside the 45-minute limit. Kept as day-counts (0-7), not collapsed to yes/no: this is the standard, validated WFP/FAO specification (frequency x severity), and no comparably-standard binary version was found on checking; a day-count also takes about as long to answer as a yes/no in practice, so little interview time is saved by simplifying it.</t>
         </is>
       </c>
     </row>
@@ -8480,7 +8448,7 @@
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>cope_less_pref_food_yatra_wk</t>
+          <t>cope_reduce_meals_offseason_wk</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr">
@@ -8490,12 +8458,12 @@
       </c>
       <c r="F176" s="2" t="inlineStr">
         <is>
-          <t>In a normal week during the Yatra season, to cope with a lack of food or money to buy it, how many days did your household rely on less expensive/less preferred food? (0-7 days)</t>
+          <t>In a normal week when the Yatra is closed, to cope with a lack of food or money to buy it, how many days did your household reduce the number of meals eaten per day? (0-7 days)</t>
         </is>
       </c>
       <c r="G176" s="2" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम हफ़्ते में, खाने की या खाना ख़रीदने के पैसे की कमी से निपटने के लिए आपके घर ने कितने दिन सस्ता या कम पसंद का खाना खाया? (0-7 दिन)</t>
+          <t>जब यात्रा बंद रहती है, उस आम हफ़्ते में आपके घर ने कितने दिन दिन में कम बार खाना खाया? (0-7 दिन)</t>
         </is>
       </c>
       <c r="H176" s="2" t="inlineStr"/>
@@ -8522,7 +8490,7 @@
       </c>
       <c r="D177" s="2" t="inlineStr">
         <is>
-          <t>cope_less_pref_food_offseason_wk</t>
+          <t>cope_reduce_portion_yatra_wk</t>
         </is>
       </c>
       <c r="E177" s="2" t="inlineStr">
@@ -8532,12 +8500,12 @@
       </c>
       <c r="F177" s="2" t="inlineStr">
         <is>
-          <t>In a normal week when the Yatra is closed, to cope with a lack of food or money to buy it, how many days did your household rely on less expensive/less preferred food? (0-7 days)</t>
+          <t>In a normal week during the Yatra season, to cope with a lack of food or money to buy it, how many days did your household reduce portion size of meals? (0-7 days)</t>
         </is>
       </c>
       <c r="G177" s="2" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम हफ़्ते में आपके घर ने कितने दिन सस्ता या कम पसंद का खाना खाया? (0-7 दिन)</t>
+          <t>यात्रा के मौसम के आम हफ़्ते में, खाने की या खाना ख़रीदने के पैसे की कमी से निपटने के लिए आपके घर ने कितने दिन खाने की मात्रा घटाई? (0-7 दिन)</t>
         </is>
       </c>
       <c r="H177" s="2" t="inlineStr"/>
@@ -8564,7 +8532,7 @@
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>cope_borrow_food_yatra_wk</t>
+          <t>cope_reduce_portion_offseason_wk</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr">
@@ -8574,12 +8542,12 @@
       </c>
       <c r="F178" s="2" t="inlineStr">
         <is>
-          <t>In a normal week during the Yatra season, to cope with a lack of food or money to buy it, how many days did your household borrow food and/or rely on help from friends/relatives? (0-7 days)</t>
+          <t>In a normal week when the Yatra is closed, to cope with a lack of food or money to buy it, how many days did your household reduce portion size of meals? (0-7 days)</t>
         </is>
       </c>
       <c r="G178" s="2" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम हफ़्ते में, खाने की या खाना ख़रीदने के पैसे की कमी से निपटने के लिए आपके घर ने कितने दिन खाना उधार लिया या दोस्तों/रिश्तेदारों की मदद ली? (0-7 दिन)</t>
+          <t>जब यात्रा बंद रहती है, उस आम हफ़्ते में आपके घर ने कितने दिन खाने की मात्रा घटाई? (0-7 दिन)</t>
         </is>
       </c>
       <c r="H178" s="2" t="inlineStr"/>
@@ -8606,7 +8574,7 @@
       </c>
       <c r="D179" s="2" t="inlineStr">
         <is>
-          <t>cope_borrow_food_offseason_wk</t>
+          <t>cope_restrict_adult_yatra_wk</t>
         </is>
       </c>
       <c r="E179" s="2" t="inlineStr">
@@ -8616,12 +8584,12 @@
       </c>
       <c r="F179" s="2" t="inlineStr">
         <is>
-          <t>In a normal week when the Yatra is closed, to cope with a lack of food or money to buy it, how many days did your household borrow food and/or rely on help from friends/relatives? (0-7 days)</t>
+          <t>In a normal week during the Yatra season, to cope with a lack of food or money to buy it, how many days did your household restrict consumption of adults/mothers in order for young children to eat? (0-7 days)</t>
         </is>
       </c>
       <c r="G179" s="2" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम हफ़्ते में आपके घर ने कितने दिन खाना उधार लिया या दोस्तों/रिश्तेदारों की मदद ली? (0-7 दिन)</t>
+          <t>यात्रा के मौसम के आम हफ़्ते में, खाने की या खाना ख़रीदने के पैसे की कमी से निपटने के लिए आपके घर ने कितने दिन बड़ों ने कम खाया ताकि छोटे बच्चे खा सकें? (0-7 दिन)</t>
         </is>
       </c>
       <c r="H179" s="2" t="inlineStr"/>
@@ -8648,7 +8616,7 @@
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>cope_reduce_meals_yatra_wk</t>
+          <t>cope_restrict_adult_offseason_wk</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr">
@@ -8658,12 +8626,12 @@
       </c>
       <c r="F180" s="2" t="inlineStr">
         <is>
-          <t>In a normal week during the Yatra season, to cope with a lack of food or money to buy it, how many days did your household reduce the number of meals eaten per day? (0-7 days)</t>
+          <t>In a normal week when the Yatra is closed, to cope with a lack of food or money to buy it, how many days did your household restrict consumption of adults/mothers in order for young children to eat? (0-7 days)</t>
         </is>
       </c>
       <c r="G180" s="2" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम हफ़्ते में, खाने की या खाना ख़रीदने के पैसे की कमी से निपटने के लिए आपके घर ने कितने दिन दिन में कम बार खाना खाया? (0-7 दिन)</t>
+          <t>जब यात्रा बंद रहती है, उस आम हफ़्ते में आपके घर ने कितने दिन बड़ों ने कम खाया ताकि छोटे बच्चे खा सकें? (0-7 दिन)</t>
         </is>
       </c>
       <c r="H180" s="2" t="inlineStr"/>
@@ -8680,39 +8648,43 @@
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t>Food security, shocks and coping</t>
+          <t>Ropeway</t>
         </is>
       </c>
       <c r="D181" s="2" t="inlineStr">
         <is>
-          <t>cope_reduce_meals_offseason_wk</t>
+          <t>ropeway_stance</t>
         </is>
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
-          <t>whole number</t>
+          <t>select one</t>
         </is>
       </c>
       <c r="F181" s="2" t="inlineStr">
         <is>
-          <t>In a normal week when the Yatra is closed, to cope with a lack of food or money to buy it, how many days did your household reduce the number of meals eaten per day? (0-7 days)</t>
+          <t>A ropeway is proposed between Gaurikund and Kedarnath. Are you in favour, neutral, or against?</t>
         </is>
       </c>
       <c r="G181" s="2" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम हफ़्ते में आपके घर ने कितने दिन दिन में कम बार खाना खाया? (0-7 दिन)</t>
-        </is>
-      </c>
-      <c r="H181" s="2" t="inlineStr"/>
+          <t>गौरीकुंड से केदारनाथ तक रोपवे बनाने की बात चल रही है। आप इसके पक्ष में हैं, बीच में हैं, या ख़िलाफ़ हैं?</t>
+        </is>
+      </c>
+      <c r="H181" s="2" t="inlineStr">
+        <is>
+          <t>1 Support | 2 Neutral | 3 Oppose | 98 Prefer not to say</t>
+        </is>
+      </c>
       <c r="I181" s="2" t="inlineStr"/>
       <c r="J181" s="2" t="inlineStr">
         <is>
-          <t>VASyR 2025 (exact item wording); WFP rCSI; The reduced Coping Strategy Index (rCSI): five food-coping questions, standard WFP weights (1, 2, 1, 1, 3) applied when the index is built. The Kedarnath instrument otherwise has no food-security module, which is a gap for a poverty-vulnerability survey; these five short questions close it at low cost instead of a full dietary-diversity module, left out to stay inside the 45-minute limit. Kept as day-counts (0-7), not collapsed to yes/no: this is the standard, validated WFP/FAO specification (frequency x severity), and no comparably-standard binary version was found on checking; a day-count also takes about as long to answer as a yes/no in practice, so little interview time is saved by simplifying it.</t>
+          <t>Project design</t>
         </is>
       </c>
     </row>
@@ -8722,39 +8694,43 @@
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>Food security, shocks and coping</t>
+          <t>Ropeway</t>
         </is>
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>cope_reduce_portion_yatra_wk</t>
+          <t>trek_dependent</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>whole number</t>
+          <t>yes/no</t>
         </is>
       </c>
       <c r="F182" s="2" t="inlineStr">
         <is>
-          <t>In a normal week during the Yatra season, to cope with a lack of food or money to buy it, how many days did your household reduce portion size of meals? (0-7 days)</t>
+          <t>Is your main Yatra work carrying, transporting or guiding people or goods on the Gaurikund to Kedarnath trek?</t>
         </is>
       </c>
       <c r="G182" s="2" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम हफ़्ते में, खाने की या खाना ख़रीदने के पैसे की कमी से निपटने के लिए आपके घर ने कितने दिन खाने की मात्रा घटाई? (0-7 दिन)</t>
-        </is>
-      </c>
-      <c r="H182" s="2" t="inlineStr"/>
+          <t>क्या आपका मुख्य यात्रा-काम गौरीकुंड से केदारनाथ के पैदल रास्ते पर लोगों या सामान को ले जाना, पहुँचाना या रास्ता दिखाना है?</t>
+        </is>
+      </c>
+      <c r="H182" s="2" t="inlineStr">
+        <is>
+          <t>0 No | 1 Yes</t>
+        </is>
+      </c>
       <c r="I182" s="2" t="inlineStr"/>
       <c r="J182" s="2" t="inlineStr">
         <is>
-          <t>VASyR 2025 (exact item wording); WFP rCSI; The reduced Coping Strategy Index (rCSI): five food-coping questions, standard WFP weights (1, 2, 1, 1, 3) applied when the index is built. The Kedarnath instrument otherwise has no food-security module, which is a gap for a poverty-vulnerability survey; these five short questions close it at low cost instead of a full dietary-diversity module, left out to stay inside the 45-minute limit. Kept as day-counts (0-7), not collapsed to yes/no: this is the standard, validated WFP/FAO specification (frequency x severity), and no comparably-standard binary version was found on checking; a day-count also takes about as long to answer as a yes/no in practice, so little interview time is saved by simplifying it.</t>
+          <t>Project design (see tasks_module W4: exposure must be asked directly)</t>
         </is>
       </c>
     </row>
@@ -8764,39 +8740,43 @@
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t>Food security, shocks and coping</t>
+          <t>Job quality (Apablaza et al. 2026 questions)</t>
         </is>
       </c>
       <c r="D183" s="2" t="inlineStr">
         <is>
-          <t>cope_reduce_portion_offseason_wk</t>
+          <t>job_situation</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>whole number</t>
+          <t>select one</t>
         </is>
       </c>
       <c r="F183" s="2" t="inlineStr">
         <is>
-          <t>In a normal week when the Yatra is closed, to cope with a lack of food or money to buy it, how many days did your household reduce portion size of meals? (0-7 days)</t>
+          <t>Which best describes your situation during the last month: you work for pay full-time; you work for pay part-time or do occasional jobs; you study and work; you only study; you are only being trained for work; you are retired or pensioned; you do unpaid household tasks or care for others; you are unemployed and actively looking for work; you are sick or disabled and cannot work; or none of these?</t>
         </is>
       </c>
       <c r="G183" s="2" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम हफ़्ते में आपके घर ने कितने दिन खाने की मात्रा घटाई? (0-7 दिन)</t>
-        </is>
-      </c>
-      <c r="H183" s="2" t="inlineStr"/>
+          <t>पिछले महीने आपकी हालत इनमें से किससे सबसे मिलती है: पूरे समय पैसे के लिए काम; कुछ समय या कभी-कभार का काम; पढ़ाई के साथ काम; सिर्फ़ पढ़ाई; सिर्फ़ काम की ट्रेनिंग; रिटायर या पेंशन पर; घर का बिना पैसे का काम या किसी की देखभाल; काम नहीं है और ढूँढ रहे हैं; बीमारी या विकलांगता से काम नहीं कर सकते; या इनमें से कुछ नहीं?</t>
+        </is>
+      </c>
+      <c r="H183" s="2" t="inlineStr">
+        <is>
+          <t>1 Works for pay full-time | 2 Works for pay part-time or occasional jobs | 3 Studies and works | 4 Only studies | 5 Being trained for work only | 6 Retired or pensioned | 7 Unpaid household tasks or caring for others | 8 Unemployed, actively seeking work | 9 Sick or disabled, cannot work | 10 Neither studying, working nor seeking work | 97 Does not know</t>
+        </is>
+      </c>
       <c r="I183" s="2" t="inlineStr"/>
       <c r="J183" s="2" t="inlineStr">
         <is>
-          <t>VASyR 2025 (exact item wording); WFP rCSI; The reduced Coping Strategy Index (rCSI): five food-coping questions, standard WFP weights (1, 2, 1, 1, 3) applied when the index is built. The Kedarnath instrument otherwise has no food-security module, which is a gap for a poverty-vulnerability survey; these five short questions close it at low cost instead of a full dietary-diversity module, left out to stay inside the 45-minute limit. Kept as day-counts (0-7), not collapsed to yes/no: this is the standard, validated WFP/FAO specification (frequency x severity), and no comparably-standard binary version was found on checking; a day-count also takes about as long to answer as a yes/no in practice, so little interview time is saved by simplifying it.</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q5 (all eleven categories, with its own three-way routing)</t>
         </is>
       </c>
     </row>
@@ -8806,39 +8786,47 @@
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>Food security, shocks and coping</t>
+          <t>Job quality (Apablaza et al. 2026 questions)</t>
         </is>
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t>cope_restrict_adult_yatra_wk</t>
+          <t>job_permanence</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>whole number</t>
+          <t>select one</t>
         </is>
       </c>
       <c r="F184" s="2" t="inlineStr">
         <is>
-          <t>In a normal week during the Yatra season, to cope with a lack of food or money to buy it, how many days did your household restrict consumption of adults/mothers in order for young children to eat? (0-7 days)</t>
+          <t>Is your job: permanent; seasonal or temporary; occasional or casual; on probation; or fixed-term?</t>
         </is>
       </c>
       <c r="G184" s="2" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम हफ़्ते में, खाने की या खाना ख़रीदने के पैसे की कमी से निपटने के लिए आपके घर ने कितने दिन बड़ों ने कम खाया ताकि छोटे बच्चे खा सकें? (0-7 दिन)</t>
-        </is>
-      </c>
-      <c r="H184" s="2" t="inlineStr"/>
-      <c r="I184" s="2" t="inlineStr"/>
+          <t>आपका काम कैसा है: पक्का; मौसमी या कुछ समय का; कभी-कभार का; परखने की अवधि पर; या तय समय के लिए?</t>
+        </is>
+      </c>
+      <c r="H184" s="2" t="inlineStr">
+        <is>
+          <t>1 Permanent | 2 Seasonal or temporary | 3 Occasional or casual | 4 On probation | 5 Fixed-term</t>
+        </is>
+      </c>
+      <c r="I184" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if job_situation is 1, 2 or 3 (currently working)</t>
+        </is>
+      </c>
       <c r="J184" s="2" t="inlineStr">
         <is>
-          <t>VASyR 2025 (exact item wording); WFP rCSI; The reduced Coping Strategy Index (rCSI): five food-coping questions, standard WFP weights (1, 2, 1, 1, 3) applied when the index is built. The Kedarnath instrument otherwise has no food-security module, which is a gap for a poverty-vulnerability survey; these five short questions close it at low cost instead of a full dietary-diversity module, left out to stay inside the 45-minute limit. Kept as day-counts (0-7), not collapsed to yes/no: this is the standard, validated WFP/FAO specification (frequency x severity), and no comparably-standard binary version was found on checking; a day-count also takes about as long to answer as a yes/no in practice, so little interview time is saved by simplifying it.</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q9</t>
         </is>
       </c>
     </row>
@@ -8848,39 +8836,47 @@
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C185" s="2" t="inlineStr">
         <is>
-          <t>Food security, shocks and coping</t>
+          <t>Job quality (Apablaza et al. 2026 questions)</t>
         </is>
       </c>
       <c r="D185" s="2" t="inlineStr">
         <is>
-          <t>cope_restrict_adult_offseason_wk</t>
+          <t>contract_status</t>
         </is>
       </c>
       <c r="E185" s="2" t="inlineStr">
         <is>
-          <t>whole number</t>
+          <t>select one</t>
         </is>
       </c>
       <c r="F185" s="2" t="inlineStr">
         <is>
-          <t>In a normal week when the Yatra is closed, to cope with a lack of food or money to buy it, how many days did your household restrict consumption of adults/mothers in order for young children to eat? (0-7 days)</t>
+          <t>Do you have a signed contract? Yes, signed; yes but not yet signed; no contract.</t>
         </is>
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम हफ़्ते में आपके घर ने कितने दिन बड़ों ने कम खाया ताकि छोटे बच्चे खा सकें? (0-7 दिन)</t>
-        </is>
-      </c>
-      <c r="H185" s="2" t="inlineStr"/>
-      <c r="I185" s="2" t="inlineStr"/>
+          <t>क्या आपका दस्तख़त किया हुआ अनुबंध (कॉन्ट्रैक्ट) है? हाँ, दस्तख़त किया; हाँ, पर अभी दस्तख़त नहीं हुआ; कोई अनुबंध नहीं।</t>
+        </is>
+      </c>
+      <c r="H185" s="2" t="inlineStr">
+        <is>
+          <t>1 Yes, signed | 2 Yes, but not yet signed | 3 No contract</t>
+        </is>
+      </c>
+      <c r="I185" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if job_situation is 1, 2 or 3 (currently working); and employment_type is 3 or 4 (wage workers) -- self-employed skip to the next question</t>
+        </is>
+      </c>
       <c r="J185" s="2" t="inlineStr">
         <is>
-          <t>VASyR 2025 (exact item wording); WFP rCSI; The reduced Coping Strategy Index (rCSI): five food-coping questions, standard WFP weights (1, 2, 1, 1, 3) applied when the index is built. The Kedarnath instrument otherwise has no food-security module, which is a gap for a poverty-vulnerability survey; these five short questions close it at low cost instead of a full dietary-diversity module, left out to stay inside the 45-minute limit. Kept as day-counts (0-7), not collapsed to yes/no: this is the standard, validated WFP/FAO specification (frequency x severity), and no comparably-standard binary version was found on checking; a day-count also takes about as long to answer as a yes/no in practice, so little interview time is saved by simplifying it.</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q11</t>
         </is>
       </c>
     </row>
@@ -8890,43 +8886,47 @@
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>Ropeway</t>
+          <t>Job quality (Apablaza et al. 2026 questions)</t>
         </is>
       </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
-          <t>ropeway_stance</t>
+          <t>workplace_registered</t>
         </is>
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>select one</t>
+          <t>yes/no</t>
         </is>
       </c>
       <c r="F186" s="2" t="inlineStr">
         <is>
-          <t>A ropeway is proposed between Gaurikund and Kedarnath. Are you in favour, neutral, or against?</t>
+          <t>Is your workplace or business registered, for example with a taxpayer or GST number, a shop or trade licence, the Yatra registration, or a union?</t>
         </is>
       </c>
       <c r="G186" s="2" t="inlineStr">
         <is>
-          <t>गौरीकुंड से केदारनाथ तक रोपवे बनाने की बात चल रही है। आप इसके पक्ष में हैं, बीच में हैं, या ख़िलाफ़ हैं?</t>
+          <t>क्या आपका काम या धंधा रजिस्टर्ड है, जैसे GST या टैक्स नंबर, दुकान का लाइसेंस, यात्रा का रजिस्ट्रेशन, या कोई यूनियन?</t>
         </is>
       </c>
       <c r="H186" s="2" t="inlineStr">
         <is>
-          <t>1 Support | 2 Neutral | 3 Oppose | 98 Prefer not to say</t>
-        </is>
-      </c>
-      <c r="I186" s="2" t="inlineStr"/>
+          <t>0 No | 1 Yes</t>
+        </is>
+      </c>
+      <c r="I186" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if job_situation is 1, 2 or 3 (currently working)</t>
+        </is>
+      </c>
       <c r="J186" s="2" t="inlineStr">
         <is>
-          <t>Project design</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q12 (widened to local registrations)</t>
         </is>
       </c>
     </row>
@@ -8936,43 +8936,47 @@
       </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C187" s="2" t="inlineStr">
         <is>
-          <t>Ropeway</t>
+          <t>Job quality (Apablaza et al. 2026 questions)</t>
         </is>
       </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t>trek_dependent</t>
+          <t>pension_contrib</t>
         </is>
       </c>
       <c r="E187" s="2" t="inlineStr">
         <is>
-          <t>yes/no</t>
+          <t>select one</t>
         </is>
       </c>
       <c r="F187" s="2" t="inlineStr">
         <is>
-          <t>Is your main Yatra work carrying, transporting or guiding people or goods on the Gaurikund to Kedarnath trek?</t>
+          <t>Do you contribute to any pension system? Yes, the employer deducts it; yes, voluntarily; no.</t>
         </is>
       </c>
       <c r="G187" s="2" t="inlineStr">
         <is>
-          <t>क्या आपका मुख्य यात्रा-काम गौरीकुंड से केदारनाथ के पैदल रास्ते पर लोगों या सामान को ले जाना, पहुँचाना या रास्ता दिखाना है?</t>
+          <t>क्या आप किसी पेंशन में पैसा डालते हैं? हाँ, मालिक तनख़्वाह से काटता है; हाँ, अपनी मर्ज़ी से डालते हैं; नहीं।</t>
         </is>
       </c>
       <c r="H187" s="2" t="inlineStr">
         <is>
-          <t>0 No | 1 Yes</t>
-        </is>
-      </c>
-      <c r="I187" s="2" t="inlineStr"/>
+          <t>1 Yes, employer deducts it | 2 Yes, contributes voluntarily | 3 No</t>
+        </is>
+      </c>
+      <c r="I187" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if job_situation is 1, 2 or 3 (currently working)</t>
+        </is>
+      </c>
       <c r="J187" s="2" t="inlineStr">
         <is>
-          <t>Project design (see tasks_module W4: exposure must be asked directly)</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q16</t>
         </is>
       </c>
     </row>
@@ -8992,7 +8996,7 @@
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
-          <t>job_situation</t>
+          <t>work_health_ins</t>
         </is>
       </c>
       <c r="E188" s="2" t="inlineStr">
@@ -9002,23 +9006,27 @@
       </c>
       <c r="F188" s="2" t="inlineStr">
         <is>
-          <t>Which best describes your situation during the last month: you work for pay full-time; you work for pay part-time or do occasional jobs; you study and work; you only study; you are only being trained for work; you are retired or pensioned; you do unpaid household tasks or care for others; you are unemployed and actively looking for work; you are sick or disabled and cannot work; or none of these?</t>
+          <t>Do you have health insurance through your work? Yes; only private or other insurance; none; don't know.</t>
         </is>
       </c>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t>पिछले महीने आपकी हालत इनमें से किससे सबसे मिलती है: पूरे समय पैसे के लिए काम; कुछ समय या कभी-कभार का काम; पढ़ाई के साथ काम; सिर्फ़ पढ़ाई; सिर्फ़ काम की ट्रेनिंग; रिटायर या पेंशन पर; घर का बिना पैसे का काम या किसी की देखभाल; काम नहीं है और ढूँढ रहे हैं; बीमारी या विकलांगता से काम नहीं कर सकते; या इनमें से कुछ नहीं?</t>
+          <t>क्या काम की तरफ़ से आपका स्वास्थ्य बीमा है? हाँ; सिर्फ़ अपना या कोई और बीमा; कोई नहीं; पता नहीं।</t>
         </is>
       </c>
       <c r="H188" s="2" t="inlineStr">
         <is>
-          <t>1 Works for pay full-time | 2 Works for pay part-time or occasional jobs | 3 Studies and works | 4 Only studies | 5 Being trained for work only | 6 Retired or pensioned | 7 Unpaid household tasks or caring for others | 8 Unemployed, actively seeking work | 9 Sick or disabled, cannot work | 10 Neither studying, working nor seeking work | 97 Does not know</t>
-        </is>
-      </c>
-      <c r="I188" s="2" t="inlineStr"/>
+          <t>1 Yes, through work | 2 Only private or other insurance | 3 None | 4 Don't know</t>
+        </is>
+      </c>
+      <c r="I188" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if job_situation is 1, 2 or 3 (currently working)</t>
+        </is>
+      </c>
       <c r="J188" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q5 (all eleven categories, with its own three-way routing)</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q17</t>
         </is>
       </c>
     </row>
@@ -9038,7 +9046,7 @@
       </c>
       <c r="D189" s="2" t="inlineStr">
         <is>
-          <t>job_permanence</t>
+          <t>leave_rights</t>
         </is>
       </c>
       <c r="E189" s="2" t="inlineStr">
@@ -9048,17 +9056,17 @@
       </c>
       <c r="F189" s="2" t="inlineStr">
         <is>
-          <t>Is your job: permanent; seasonal or temporary; occasional or casual; on probation; or fixed-term?</t>
+          <t>Do you have the right to paid holiday, sick or maternity leave?</t>
         </is>
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>आपका काम कैसा है: पक्का; मौसमी या कुछ समय का; कभी-कभार का; परखने की अवधि पर; या तय समय के लिए?</t>
+          <t>क्या आपको पैसे वाली छुट्टी मिलती है — त्योहार, बीमारी या ज़च्चगी की?</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr">
         <is>
-          <t>1 Permanent | 2 Seasonal or temporary | 3 Occasional or casual | 4 On probation | 5 Fixed-term</t>
+          <t>0 No | 1 Yes | 97 Don't know</t>
         </is>
       </c>
       <c r="I189" s="2" t="inlineStr">
@@ -9068,7 +9076,7 @@
       </c>
       <c r="J189" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q9</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q18</t>
         </is>
       </c>
     </row>
@@ -9088,7 +9096,7 @@
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>contract_status</t>
+          <t>injured_ever</t>
         </is>
       </c>
       <c r="E190" s="2" t="inlineStr">
@@ -9098,27 +9106,27 @@
       </c>
       <c r="F190" s="2" t="inlineStr">
         <is>
-          <t>Do you have a signed contract? Yes, signed; yes but not yet signed; no contract.</t>
+          <t>Have you ever been physically injured at your workplace?</t>
         </is>
       </c>
       <c r="G190" s="2" t="inlineStr">
         <is>
-          <t>क्या आपका दस्तख़त किया हुआ अनुबंध (कॉन्ट्रैक्ट) है? हाँ, दस्तख़त किया; हाँ, पर अभी दस्तख़त नहीं हुआ; कोई अनुबंध नहीं।</t>
+          <t>क्या आपको कभी काम की जगह पर चोट लगी है?</t>
         </is>
       </c>
       <c r="H190" s="2" t="inlineStr">
         <is>
-          <t>1 Yes, signed | 2 Yes, but not yet signed | 3 No contract</t>
+          <t>0 No | 1 Yes | 97 Don't know</t>
         </is>
       </c>
       <c r="I190" s="2" t="inlineStr">
         <is>
-          <t>Ask only if job_situation is 1, 2 or 3 (currently working); and employment_type is 3 or 4 (wage workers) -- self-employed skip to the next question</t>
+          <t>Ask only if job_situation is 1, 2 or 3 (currently working)</t>
         </is>
       </c>
       <c r="J190" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q11</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q19</t>
         </is>
       </c>
     </row>
@@ -9138,27 +9146,27 @@
       </c>
       <c r="D191" s="2" t="inlineStr">
         <is>
-          <t>workplace_registered</t>
+          <t>workplace_injury_12m</t>
         </is>
       </c>
       <c r="E191" s="2" t="inlineStr">
         <is>
-          <t>yes/no</t>
+          <t>select one</t>
         </is>
       </c>
       <c r="F191" s="2" t="inlineStr">
         <is>
-          <t>Is your workplace or business registered, for example with a taxpayer or GST number, a shop or trade licence, the Yatra registration, or a union?</t>
+          <t>In the last 12 months, was anyone physically injured or killed at your workplace because of work?</t>
         </is>
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>क्या आपका काम या धंधा रजिस्टर्ड है, जैसे GST या टैक्स नंबर, दुकान का लाइसेंस, यात्रा का रजिस्ट्रेशन, या कोई यूनियन?</t>
+          <t>पिछले 12 महीनों में क्या आपके काम की जगह पर काम की वजह से किसी को चोट लगी या किसी की मौत हुई?</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
         <is>
-          <t>0 No | 1 Yes</t>
+          <t>0 No | 1 Yes | 97 Don't know</t>
         </is>
       </c>
       <c r="I191" s="2" t="inlineStr">
@@ -9168,7 +9176,7 @@
       </c>
       <c r="J191" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q12 (widened to local registrations)</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q20</t>
         </is>
       </c>
     </row>
@@ -9188,7 +9196,7 @@
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>pension_contrib</t>
+          <t>wants_more_work</t>
         </is>
       </c>
       <c r="E192" s="2" t="inlineStr">
@@ -9198,27 +9206,27 @@
       </c>
       <c r="F192" s="2" t="inlineStr">
         <is>
-          <t>Do you contribute to any pension system? Yes, the employer deducts it; yes, voluntarily; no.</t>
+          <t>Would you like to work more hours than you do?</t>
         </is>
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>क्या आप किसी पेंशन में पैसा डालते हैं? हाँ, मालिक तनख़्वाह से काटता है; हाँ, अपनी मर्ज़ी से डालते हैं; नहीं।</t>
+          <t>क्या आप अभी से ज़्यादा घंटे काम करना चाहेंगे?</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
         <is>
-          <t>1 Yes, employer deducts it | 2 Yes, contributes voluntarily | 3 No</t>
+          <t>0 No | 1 Yes | 97 Don't know</t>
         </is>
       </c>
       <c r="I192" s="2" t="inlineStr">
         <is>
-          <t>Ask only if job_situation is 1, 2 or 3 (currently working)</t>
+          <t>Ask if job_situation is 1 to 7 (Apablaza routes codes 4-7 straight to this question)</t>
         </is>
       </c>
       <c r="J192" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q16</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q21</t>
         </is>
       </c>
     </row>
@@ -9238,37 +9246,33 @@
       </c>
       <c r="D193" s="2" t="inlineStr">
         <is>
-          <t>work_health_ins</t>
+          <t>more_hours_day</t>
         </is>
       </c>
       <c r="E193" s="2" t="inlineStr">
         <is>
-          <t>select one</t>
+          <t>whole number</t>
         </is>
       </c>
       <c r="F193" s="2" t="inlineStr">
         <is>
-          <t>Do you have health insurance through your work? Yes; only private or other insurance; none; don't know.</t>
+          <t>On a working day, how many MORE hours would you like to work?</t>
         </is>
       </c>
       <c r="G193" s="2" t="inlineStr">
         <is>
-          <t>क्या काम की तरफ़ से आपका स्वास्थ्य बीमा है? हाँ; सिर्फ़ अपना या कोई और बीमा; कोई नहीं; पता नहीं।</t>
-        </is>
-      </c>
-      <c r="H193" s="2" t="inlineStr">
-        <is>
-          <t>1 Yes, through work | 2 Only private or other insurance | 3 None | 4 Don't know</t>
-        </is>
-      </c>
+          <t>काम के दिन में आप कितने घंटे और काम करना चाहेंगे?</t>
+        </is>
+      </c>
+      <c r="H193" s="2" t="inlineStr"/>
       <c r="I193" s="2" t="inlineStr">
         <is>
-          <t>Ask only if job_situation is 1, 2 or 3 (currently working)</t>
+          <t>Ask if wants_more_work = 1, or if job_situation = 8 (Apablaza routes the unemployed-and-seeking category here directly)</t>
         </is>
       </c>
       <c r="J193" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q17</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q22</t>
         </is>
       </c>
     </row>
@@ -9288,37 +9292,33 @@
       </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
-          <t>leave_rights</t>
+          <t>months_looked_for_work</t>
         </is>
       </c>
       <c r="E194" s="2" t="inlineStr">
         <is>
-          <t>select one</t>
+          <t>whole number</t>
         </is>
       </c>
       <c r="F194" s="2" t="inlineStr">
         <is>
-          <t>Do you have the right to paid holiday, sick or maternity leave?</t>
+          <t>Across the months when you had no paid work, about how many MONTHS in total were you looking for work?</t>
         </is>
       </c>
       <c r="G194" s="2" t="inlineStr">
         <is>
-          <t>क्या आपको पैसे वाली छुट्टी मिलती है — त्योहार, बीमारी या ज़च्चगी की?</t>
-        </is>
-      </c>
-      <c r="H194" s="2" t="inlineStr">
-        <is>
-          <t>0 No | 1 Yes | 97 Don't know</t>
-        </is>
-      </c>
+          <t>जिन महीनों में आपके पास कोई पैसे वाला काम नहीं था, उनमें कुल मिलाकर लगभग कितने महीने आप काम ढूँढते रहे?</t>
+        </is>
+      </c>
+      <c r="H194" s="2" t="inlineStr"/>
       <c r="I194" s="2" t="inlineStr">
         <is>
-          <t>Ask only if job_situation is 1, 2 or 3 (currently working)</t>
+          <t>Ask if any month in the calendar is 'No paid work', or if job_situation = 8</t>
         </is>
       </c>
       <c r="J194" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q18</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q23 (duration in weeks, tied to the calendar instead of a single point in time)</t>
         </is>
       </c>
     </row>
@@ -9338,7 +9338,7 @@
       </c>
       <c r="D195" s="2" t="inlineStr">
         <is>
-          <t>injured_ever</t>
+          <t>first_job_ever</t>
         </is>
       </c>
       <c r="E195" s="2" t="inlineStr">
@@ -9348,12 +9348,12 @@
       </c>
       <c r="F195" s="2" t="inlineStr">
         <is>
-          <t>Have you ever been physically injured at your workplace?</t>
+          <t>Was your current work the first paid job you ever had?</t>
         </is>
       </c>
       <c r="G195" s="2" t="inlineStr">
         <is>
-          <t>क्या आपको कभी काम की जगह पर चोट लगी है?</t>
+          <t>क्या यह आपका पहला पैसे वाला काम है?</t>
         </is>
       </c>
       <c r="H195" s="2" t="inlineStr">
@@ -9361,14 +9361,10 @@
           <t>0 No | 1 Yes | 97 Don't know</t>
         </is>
       </c>
-      <c r="I195" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if job_situation is 1, 2 or 3 (currently working)</t>
-        </is>
-      </c>
+      <c r="I195" s="2" t="inlineStr"/>
       <c r="J195" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q19</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q24</t>
         </is>
       </c>
     </row>
@@ -9378,17 +9374,17 @@
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>Job quality (Apablaza et al. 2026 questions)</t>
+          <t>Tasks and skills (short block)</t>
         </is>
       </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
-          <t>workplace_injury_12m</t>
+          <t>tk_load</t>
         </is>
       </c>
       <c r="E196" s="2" t="inlineStr">
@@ -9398,27 +9394,23 @@
       </c>
       <c r="F196" s="2" t="inlineStr">
         <is>
-          <t>In the last 12 months, was anyone physically injured or killed at your workplace because of work?</t>
+          <t>Do you load, unload, stack or count goods? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
         </is>
       </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>पिछले 12 महीनों में क्या आपके काम की जगह पर काम की वजह से किसी को चोट लगी या किसी की मौत हुई?</t>
+          <t>क्या आप सामान चढ़ाना-उतारना, लगाना या गिनना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="H196" s="2" t="inlineStr">
         <is>
-          <t>0 No | 1 Yes | 97 Don't know</t>
-        </is>
-      </c>
-      <c r="I196" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if job_situation is 1, 2 or 3 (currently working)</t>
-        </is>
-      </c>
+          <t>1 Yes, regularly in my main Yatra work | 2 Not in my main work, but done before elsewhere | 3 Never done</t>
+        </is>
+      </c>
+      <c r="I196" s="2" t="inlineStr"/>
       <c r="J196" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q20</t>
+          <t>Gathmann and Schonberg 2010; NCO 9333.0100 loader</t>
         </is>
       </c>
     </row>
@@ -9428,17 +9420,17 @@
       </c>
       <c r="B197" s="2" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C197" s="2" t="inlineStr">
         <is>
-          <t>Job quality (Apablaza et al. 2026 questions)</t>
+          <t>Tasks and skills (short block)</t>
         </is>
       </c>
       <c r="D197" s="2" t="inlineStr">
         <is>
-          <t>wants_more_work</t>
+          <t>tk_drive</t>
         </is>
       </c>
       <c r="E197" s="2" t="inlineStr">
@@ -9448,27 +9440,23 @@
       </c>
       <c r="F197" s="2" t="inlineStr">
         <is>
-          <t>Would you like to work more hours than you do?</t>
+          <t>Do you drive a motor vehicle? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
         </is>
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>क्या आप अभी से ज़्यादा घंटे काम करना चाहेंगे?</t>
+          <t>क्या आप गाड़ी चलाना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="H197" s="2" t="inlineStr">
         <is>
-          <t>0 No | 1 Yes | 97 Don't know</t>
-        </is>
-      </c>
-      <c r="I197" s="2" t="inlineStr">
-        <is>
-          <t>Ask if job_situation is 1 to 7 (Apablaza routes codes 4-7 straight to this question)</t>
-        </is>
-      </c>
+          <t>1 Yes, regularly in my main Yatra work | 2 Not in my main work, but done before elsewhere | 3 Never done</t>
+        </is>
+      </c>
+      <c r="I197" s="2" t="inlineStr"/>
       <c r="J197" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q21</t>
+          <t>Spitz-Oener 2006 / STEP; NCO 8322.0100</t>
         </is>
       </c>
     </row>
@@ -9478,43 +9466,43 @@
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>Job quality (Apablaza et al. 2026 questions)</t>
+          <t>Tasks and skills (short block)</t>
         </is>
       </c>
       <c r="D198" s="2" t="inlineStr">
         <is>
-          <t>more_hours_day</t>
+          <t>tk_engine</t>
         </is>
       </c>
       <c r="E198" s="2" t="inlineStr">
         <is>
-          <t>whole number</t>
+          <t>select one</t>
         </is>
       </c>
       <c r="F198" s="2" t="inlineStr">
         <is>
-          <t>On a working day, how many MORE hours would you like to work?</t>
+          <t>Do you operate an engine or machine? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
         </is>
       </c>
       <c r="G198" s="2" t="inlineStr">
         <is>
-          <t>काम के दिन में आप कितने घंटे और काम करना चाहेंगे?</t>
-        </is>
-      </c>
-      <c r="H198" s="2" t="inlineStr"/>
-      <c r="I198" s="2" t="inlineStr">
-        <is>
-          <t>Ask if wants_more_work = 1, or if job_situation = 8 (Apablaza routes the unemployed-and-seeking category here directly)</t>
-        </is>
-      </c>
+          <t>क्या आप इंजन या मशीन चलाना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+        </is>
+      </c>
+      <c r="H198" s="2" t="inlineStr">
+        <is>
+          <t>1 Yes, regularly in my main Yatra work | 2 Not in my main work, but done before elsewhere | 3 Never done</t>
+        </is>
+      </c>
+      <c r="I198" s="2" t="inlineStr"/>
       <c r="J198" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q22</t>
+          <t>Gathmann and Schonberg 2010; NCO 8343.1700 ropeway operator</t>
         </is>
       </c>
     </row>
@@ -9524,43 +9512,43 @@
       </c>
       <c r="B199" s="2" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C199" s="2" t="inlineStr">
         <is>
-          <t>Job quality (Apablaza et al. 2026 questions)</t>
+          <t>Tasks and skills (short block)</t>
         </is>
       </c>
       <c r="D199" s="2" t="inlineStr">
         <is>
-          <t>months_looked_for_work</t>
+          <t>tk_electric</t>
         </is>
       </c>
       <c r="E199" s="2" t="inlineStr">
         <is>
-          <t>whole number</t>
+          <t>select one</t>
         </is>
       </c>
       <c r="F199" s="2" t="inlineStr">
         <is>
-          <t>Across the months when you had no paid work, about how many MONTHS in total were you looking for work?</t>
+          <t>Do you do electrical or wiring work? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
         </is>
       </c>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>जिन महीनों में आपके पास कोई पैसे वाला काम नहीं था, उनमें कुल मिलाकर लगभग कितने महीने आप काम ढूँढते रहे?</t>
-        </is>
-      </c>
-      <c r="H199" s="2" t="inlineStr"/>
-      <c r="I199" s="2" t="inlineStr">
-        <is>
-          <t>Ask if any month in the calendar is 'No paid work', or if job_situation = 8</t>
-        </is>
-      </c>
+          <t>क्या आप बिजली या तार का काम करना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+        </is>
+      </c>
+      <c r="H199" s="2" t="inlineStr">
+        <is>
+          <t>1 Yes, regularly in my main Yatra work | 2 Not in my main work, but done before elsewhere | 3 Never done</t>
+        </is>
+      </c>
+      <c r="I199" s="2" t="inlineStr"/>
       <c r="J199" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q23 (duration in weeks, tied to the calendar instead of a single point in time)</t>
+          <t>Spitz-Oener 2006; NCO 7411.0301 wireman</t>
         </is>
       </c>
     </row>
@@ -9570,17 +9558,17 @@
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>Job quality (Apablaza et al. 2026 questions)</t>
+          <t>Tasks and skills (short block)</t>
         </is>
       </c>
       <c r="D200" s="2" t="inlineStr">
         <is>
-          <t>first_job_ever</t>
+          <t>tk_safety</t>
         </is>
       </c>
       <c r="E200" s="2" t="inlineStr">
@@ -9590,23 +9578,23 @@
       </c>
       <c r="F200" s="2" t="inlineStr">
         <is>
-          <t>Was your current work the first paid job you ever had?</t>
+          <t>Do you check equipment or the route for safety? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
         </is>
       </c>
       <c r="G200" s="2" t="inlineStr">
         <is>
-          <t>क्या यह आपका पहला पैसे वाला काम है?</t>
+          <t>क्या आप सामान या रास्ते की सुरक्षा जाँचना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="H200" s="2" t="inlineStr">
         <is>
-          <t>0 No | 1 Yes | 97 Don't know</t>
+          <t>1 Yes, regularly in my main Yatra work | 2 Not in my main work, but done before elsewhere | 3 Never done</t>
         </is>
       </c>
       <c r="I200" s="2" t="inlineStr"/>
       <c r="J200" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q24</t>
+          <t>Gathmann and Schonberg 2010; NCO 8343.1700</t>
         </is>
       </c>
     </row>
@@ -9626,7 +9614,7 @@
       </c>
       <c r="D201" s="2" t="inlineStr">
         <is>
-          <t>tk_load</t>
+          <t>tk_sell</t>
         </is>
       </c>
       <c r="E201" s="2" t="inlineStr">
@@ -9636,12 +9624,12 @@
       </c>
       <c r="F201" s="2" t="inlineStr">
         <is>
-          <t>Do you load, unload, stack or count goods? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
+          <t>Do you sell goods or services? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
         </is>
       </c>
       <c r="G201" s="2" t="inlineStr">
         <is>
-          <t>क्या आप सामान चढ़ाना-उतारना, लगाना या गिनना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप सामान या सेवा बेचना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="H201" s="2" t="inlineStr">
@@ -9652,7 +9640,7 @@
       <c r="I201" s="2" t="inlineStr"/>
       <c r="J201" s="2" t="inlineStr">
         <is>
-          <t>Gathmann and Schonberg 2010; NCO 9333.0100 loader</t>
+          <t>Gathmann and Schonberg 2010; NCO 5223.0200</t>
         </is>
       </c>
     </row>
@@ -9672,7 +9660,7 @@
       </c>
       <c r="D202" s="2" t="inlineStr">
         <is>
-          <t>tk_drive</t>
+          <t>tk_cash</t>
         </is>
       </c>
       <c r="E202" s="2" t="inlineStr">
@@ -9682,12 +9670,12 @@
       </c>
       <c r="F202" s="2" t="inlineStr">
         <is>
-          <t>Do you drive a motor vehicle? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
+          <t>Do you handle cash and payments? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
         </is>
       </c>
       <c r="G202" s="2" t="inlineStr">
         <is>
-          <t>क्या आप गाड़ी चलाना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप पैसे और भुगतान सँभालना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="H202" s="2" t="inlineStr">
@@ -9698,7 +9686,7 @@
       <c r="I202" s="2" t="inlineStr"/>
       <c r="J202" s="2" t="inlineStr">
         <is>
-          <t>Spitz-Oener 2006 / STEP; NCO 8322.0100</t>
+          <t>Autor and Handel 2013; NCO 5131.0401</t>
         </is>
       </c>
     </row>
@@ -9718,7 +9706,7 @@
       </c>
       <c r="D203" s="2" t="inlineStr">
         <is>
-          <t>tk_engine</t>
+          <t>tk_cook</t>
         </is>
       </c>
       <c r="E203" s="2" t="inlineStr">
@@ -9728,12 +9716,12 @@
       </c>
       <c r="F203" s="2" t="inlineStr">
         <is>
-          <t>Do you operate an engine or machine? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
+          <t>Do you cook or prepare food or drink? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
         </is>
       </c>
       <c r="G203" s="2" t="inlineStr">
         <is>
-          <t>क्या आप इंजन या मशीन चलाना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप खाना या पीने की चीज़ बनाना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="H203" s="2" t="inlineStr">
@@ -9744,7 +9732,7 @@
       <c r="I203" s="2" t="inlineStr"/>
       <c r="J203" s="2" t="inlineStr">
         <is>
-          <t>Gathmann and Schonberg 2010; NCO 8343.1700 ropeway operator</t>
+          <t>NCO 5120.0300 cook</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9752,7 @@
       </c>
       <c r="D204" s="2" t="inlineStr">
         <is>
-          <t>tk_electric</t>
+          <t>tk_serve</t>
         </is>
       </c>
       <c r="E204" s="2" t="inlineStr">
@@ -9774,12 +9762,12 @@
       </c>
       <c r="F204" s="2" t="inlineStr">
         <is>
-          <t>Do you do electrical or wiring work? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
+          <t>Do you serve guests or customers? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
         </is>
       </c>
       <c r="G204" s="2" t="inlineStr">
         <is>
-          <t>क्या आप बिजली या तार का काम करना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप मेहमानों या ग्राहकों की सेवा करना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="H204" s="2" t="inlineStr">
@@ -9790,7 +9778,7 @@
       <c r="I204" s="2" t="inlineStr"/>
       <c r="J204" s="2" t="inlineStr">
         <is>
-          <t>Spitz-Oener 2006; NCO 7411.0301 wireman</t>
+          <t>NCO 5131.0401 waiter; Pal et al. 2026</t>
         </is>
       </c>
     </row>
@@ -9810,7 +9798,7 @@
       </c>
       <c r="D205" s="2" t="inlineStr">
         <is>
-          <t>tk_safety</t>
+          <t>tk_clean</t>
         </is>
       </c>
       <c r="E205" s="2" t="inlineStr">
@@ -9820,12 +9808,12 @@
       </c>
       <c r="F205" s="2" t="inlineStr">
         <is>
-          <t>Do you check equipment or the route for safety? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
+          <t>Do you clean rooms or public areas? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
         </is>
       </c>
       <c r="G205" s="2" t="inlineStr">
         <is>
-          <t>क्या आप सामान या रास्ते की सुरक्षा जाँचना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप कमरे या सार्वजनिक जगह साफ़ करना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="H205" s="2" t="inlineStr">
@@ -9836,7 +9824,7 @@
       <c r="I205" s="2" t="inlineStr"/>
       <c r="J205" s="2" t="inlineStr">
         <is>
-          <t>Gathmann and Schonberg 2010; NCO 8343.1700</t>
+          <t>NCO 5151.0202 room attendant; Autor-Levy-Murnane 2003 (janitorial)</t>
         </is>
       </c>
     </row>
@@ -9856,7 +9844,7 @@
       </c>
       <c r="D206" s="2" t="inlineStr">
         <is>
-          <t>tk_sell</t>
+          <t>tk_guide</t>
         </is>
       </c>
       <c r="E206" s="2" t="inlineStr">
@@ -9866,12 +9854,12 @@
       </c>
       <c r="F206" s="2" t="inlineStr">
         <is>
-          <t>Do you sell goods or services? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
+          <t>Do you guide or explain things to visitors? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
         </is>
       </c>
       <c r="G206" s="2" t="inlineStr">
         <is>
-          <t>क्या आप सामान या सेवा बेचना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप आने वालों को रास्ता या बात समझाना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="H206" s="2" t="inlineStr">
@@ -9882,7 +9870,7 @@
       <c r="I206" s="2" t="inlineStr"/>
       <c r="J206" s="2" t="inlineStr">
         <is>
-          <t>Gathmann and Schonberg 2010; NCO 5223.0200</t>
+          <t>Gathmann and Schonberg 2010; NCO 5113.0200</t>
         </is>
       </c>
     </row>
@@ -9902,7 +9890,7 @@
       </c>
       <c r="D207" s="2" t="inlineStr">
         <is>
-          <t>tk_cash</t>
+          <t>tk_coord</t>
         </is>
       </c>
       <c r="E207" s="2" t="inlineStr">
@@ -9912,12 +9900,12 @@
       </c>
       <c r="F207" s="2" t="inlineStr">
         <is>
-          <t>Do you handle cash and payments? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
+          <t>Do you coordinate work by phone, radio or signals? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
         </is>
       </c>
       <c r="G207" s="2" t="inlineStr">
         <is>
-          <t>क्या आप पैसे और भुगतान सँभालना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप फ़ोन, रेडियो या इशारों से दूसरों के साथ तालमेल करना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="H207" s="2" t="inlineStr">
@@ -9928,7 +9916,7 @@
       <c r="I207" s="2" t="inlineStr"/>
       <c r="J207" s="2" t="inlineStr">
         <is>
-          <t>Autor and Handel 2013; NCO 5131.0401</t>
+          <t>NCO 8343.1700 ropeway operator</t>
         </is>
       </c>
     </row>
@@ -9948,33 +9936,37 @@
       </c>
       <c r="D208" s="2" t="inlineStr">
         <is>
-          <t>tk_cook</t>
+          <t>drove_twowheeler</t>
         </is>
       </c>
       <c r="E208" s="2" t="inlineStr">
         <is>
-          <t>select one</t>
+          <t>yes/no</t>
         </is>
       </c>
       <c r="F208" s="2" t="inlineStr">
         <is>
-          <t>Do you cook or prepare food or drink? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
+          <t>Have you ever driven a motorcycle or scooter, with or without a licence?</t>
         </is>
       </c>
       <c r="G208" s="2" t="inlineStr">
         <is>
-          <t>क्या आप खाना या पीने की चीज़ बनाना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आपने कभी मोटरसाइकिल या स्कूटर चलाई है, लाइसेंस हो या न हो?</t>
         </is>
       </c>
       <c r="H208" s="2" t="inlineStr">
         <is>
-          <t>1 Yes, regularly in my main Yatra work | 2 Not in my main work, but done before elsewhere | 3 Never done</t>
-        </is>
-      </c>
-      <c r="I208" s="2" t="inlineStr"/>
+          <t>0 No | 1 Yes</t>
+        </is>
+      </c>
+      <c r="I208" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if tk_drive is 1 or 2</t>
+        </is>
+      </c>
       <c r="J208" s="2" t="inlineStr">
         <is>
-          <t>NCO 5120.0300 cook</t>
+          <t>Level ladder without licences: people drive without holding a licence</t>
         </is>
       </c>
     </row>
@@ -9994,33 +9986,37 @@
       </c>
       <c r="D209" s="2" t="inlineStr">
         <is>
-          <t>tk_serve</t>
+          <t>drove_car</t>
         </is>
       </c>
       <c r="E209" s="2" t="inlineStr">
         <is>
-          <t>select one</t>
+          <t>yes/no</t>
         </is>
       </c>
       <c r="F209" s="2" t="inlineStr">
         <is>
-          <t>Do you serve guests or customers? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
+          <t>... a car or jeep?</t>
         </is>
       </c>
       <c r="G209" s="2" t="inlineStr">
         <is>
-          <t>क्या आप मेहमानों या ग्राहकों की सेवा करना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>...कार या जीप?</t>
         </is>
       </c>
       <c r="H209" s="2" t="inlineStr">
         <is>
-          <t>1 Yes, regularly in my main Yatra work | 2 Not in my main work, but done before elsewhere | 3 Never done</t>
-        </is>
-      </c>
-      <c r="I209" s="2" t="inlineStr"/>
+          <t>0 No | 1 Yes</t>
+        </is>
+      </c>
+      <c r="I209" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if tk_drive is 1 or 2</t>
+        </is>
+      </c>
       <c r="J209" s="2" t="inlineStr">
         <is>
-          <t>NCO 5131.0401 waiter; Pal et al. 2026</t>
+          <t>Level ladder without licences</t>
         </is>
       </c>
     </row>
@@ -10040,33 +10036,37 @@
       </c>
       <c r="D210" s="2" t="inlineStr">
         <is>
-          <t>tk_clean</t>
+          <t>drove_heavy</t>
         </is>
       </c>
       <c r="E210" s="2" t="inlineStr">
         <is>
-          <t>select one</t>
+          <t>yes/no</t>
         </is>
       </c>
       <c r="F210" s="2" t="inlineStr">
         <is>
-          <t>Do you clean rooms or public areas? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
+          <t>... a truck or bus?</t>
         </is>
       </c>
       <c r="G210" s="2" t="inlineStr">
         <is>
-          <t>क्या आप कमरे या सार्वजनिक जगह साफ़ करना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>...ट्रक या बस?</t>
         </is>
       </c>
       <c r="H210" s="2" t="inlineStr">
         <is>
-          <t>1 Yes, regularly in my main Yatra work | 2 Not in my main work, but done before elsewhere | 3 Never done</t>
-        </is>
-      </c>
-      <c r="I210" s="2" t="inlineStr"/>
+          <t>0 No | 1 Yes</t>
+        </is>
+      </c>
+      <c r="I210" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if tk_drive is 1 or 2</t>
+        </is>
+      </c>
       <c r="J210" s="2" t="inlineStr">
         <is>
-          <t>NCO 5151.0202 room attendant; Autor-Levy-Murnane 2003 (janitorial)</t>
+          <t>Level ladder without licences</t>
         </is>
       </c>
     </row>
@@ -10086,33 +10086,33 @@
       </c>
       <c r="D211" s="2" t="inlineStr">
         <is>
-          <t>tk_guide</t>
+          <t>read_at_work</t>
         </is>
       </c>
       <c r="E211" s="2" t="inlineStr">
         <is>
-          <t>select one</t>
+          <t>yes/no</t>
         </is>
       </c>
       <c r="F211" s="2" t="inlineStr">
         <is>
-          <t>Do you guide or explain things to visitors? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
+          <t>In your work, do you read anything (notes, rate lists, tickets, messages)?</t>
         </is>
       </c>
       <c r="G211" s="2" t="inlineStr">
         <is>
-          <t>क्या आप आने वालों को रास्ता या बात समझाना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>अपने काम में क्या आप कुछ पढ़ते हैं (पर्ची, रेट लिस्ट, टिकट, मैसेज)?</t>
         </is>
       </c>
       <c r="H211" s="2" t="inlineStr">
         <is>
-          <t>1 Yes, regularly in my main Yatra work | 2 Not in my main work, but done before elsewhere | 3 Never done</t>
+          <t>0 No | 1 Yes</t>
         </is>
       </c>
       <c r="I211" s="2" t="inlineStr"/>
       <c r="J211" s="2" t="inlineStr">
         <is>
-          <t>Gathmann and Schonberg 2010; NCO 5113.0200</t>
+          <t>STEP module 6A</t>
         </is>
       </c>
     </row>
@@ -10132,280 +10132,38 @@
       </c>
       <c r="D212" s="2" t="inlineStr">
         <is>
-          <t>tk_coord</t>
+          <t>calc_at_work</t>
         </is>
       </c>
       <c r="E212" s="2" t="inlineStr">
         <is>
-          <t>select one</t>
+          <t>yes/no</t>
         </is>
       </c>
       <c r="F212" s="2" t="inlineStr">
         <is>
-          <t>Do you coordinate work by phone, radio or signals? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
+          <t>In your work, do you work out prices or costs?</t>
         </is>
       </c>
       <c r="G212" s="2" t="inlineStr">
         <is>
-          <t>क्या आप फ़ोन, रेडियो या इशारों से दूसरों के साथ तालमेल करना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>अपने काम में क्या आप दाम या ख़र्चा जोड़ते-घटाते हैं?</t>
         </is>
       </c>
       <c r="H212" s="2" t="inlineStr">
         <is>
-          <t>1 Yes, regularly in my main Yatra work | 2 Not in my main work, but done before elsewhere | 3 Never done</t>
+          <t>0 No | 1 Yes</t>
         </is>
       </c>
       <c r="I212" s="2" t="inlineStr"/>
       <c r="J212" s="2" t="inlineStr">
         <is>
-          <t>NCO 8343.1700 ropeway operator</t>
-        </is>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" s="2" t="n">
-        <v>212</v>
-      </c>
-      <c r="B213" s="2" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="C213" s="2" t="inlineStr">
-        <is>
-          <t>Tasks and skills (short block)</t>
-        </is>
-      </c>
-      <c r="D213" s="2" t="inlineStr">
-        <is>
-          <t>drove_twowheeler</t>
-        </is>
-      </c>
-      <c r="E213" s="2" t="inlineStr">
-        <is>
-          <t>yes/no</t>
-        </is>
-      </c>
-      <c r="F213" s="2" t="inlineStr">
-        <is>
-          <t>Have you ever driven a motorcycle or scooter, with or without a licence?</t>
-        </is>
-      </c>
-      <c r="G213" s="2" t="inlineStr">
-        <is>
-          <t>क्या आपने कभी मोटरसाइकिल या स्कूटर चलाई है, लाइसेंस हो या न हो?</t>
-        </is>
-      </c>
-      <c r="H213" s="2" t="inlineStr">
-        <is>
-          <t>0 No | 1 Yes</t>
-        </is>
-      </c>
-      <c r="I213" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if tk_drive is 1 or 2</t>
-        </is>
-      </c>
-      <c r="J213" s="2" t="inlineStr">
-        <is>
-          <t>Level ladder without licences: people drive without holding a licence</t>
-        </is>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" s="2" t="n">
-        <v>213</v>
-      </c>
-      <c r="B214" s="2" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="C214" s="2" t="inlineStr">
-        <is>
-          <t>Tasks and skills (short block)</t>
-        </is>
-      </c>
-      <c r="D214" s="2" t="inlineStr">
-        <is>
-          <t>drove_car</t>
-        </is>
-      </c>
-      <c r="E214" s="2" t="inlineStr">
-        <is>
-          <t>yes/no</t>
-        </is>
-      </c>
-      <c r="F214" s="2" t="inlineStr">
-        <is>
-          <t>... a car or jeep?</t>
-        </is>
-      </c>
-      <c r="G214" s="2" t="inlineStr">
-        <is>
-          <t>...कार या जीप?</t>
-        </is>
-      </c>
-      <c r="H214" s="2" t="inlineStr">
-        <is>
-          <t>0 No | 1 Yes</t>
-        </is>
-      </c>
-      <c r="I214" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if tk_drive is 1 or 2</t>
-        </is>
-      </c>
-      <c r="J214" s="2" t="inlineStr">
-        <is>
-          <t>Level ladder without licences</t>
-        </is>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" s="2" t="n">
-        <v>214</v>
-      </c>
-      <c r="B215" s="2" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="C215" s="2" t="inlineStr">
-        <is>
-          <t>Tasks and skills (short block)</t>
-        </is>
-      </c>
-      <c r="D215" s="2" t="inlineStr">
-        <is>
-          <t>drove_heavy</t>
-        </is>
-      </c>
-      <c r="E215" s="2" t="inlineStr">
-        <is>
-          <t>yes/no</t>
-        </is>
-      </c>
-      <c r="F215" s="2" t="inlineStr">
-        <is>
-          <t>... a truck or bus?</t>
-        </is>
-      </c>
-      <c r="G215" s="2" t="inlineStr">
-        <is>
-          <t>...ट्रक या बस?</t>
-        </is>
-      </c>
-      <c r="H215" s="2" t="inlineStr">
-        <is>
-          <t>0 No | 1 Yes</t>
-        </is>
-      </c>
-      <c r="I215" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if tk_drive is 1 or 2</t>
-        </is>
-      </c>
-      <c r="J215" s="2" t="inlineStr">
-        <is>
-          <t>Level ladder without licences</t>
-        </is>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" s="2" t="n">
-        <v>215</v>
-      </c>
-      <c r="B216" s="2" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="C216" s="2" t="inlineStr">
-        <is>
-          <t>Tasks and skills (short block)</t>
-        </is>
-      </c>
-      <c r="D216" s="2" t="inlineStr">
-        <is>
-          <t>read_at_work</t>
-        </is>
-      </c>
-      <c r="E216" s="2" t="inlineStr">
-        <is>
-          <t>yes/no</t>
-        </is>
-      </c>
-      <c r="F216" s="2" t="inlineStr">
-        <is>
-          <t>In your work, do you read anything (notes, rate lists, tickets, messages)?</t>
-        </is>
-      </c>
-      <c r="G216" s="2" t="inlineStr">
-        <is>
-          <t>अपने काम में क्या आप कुछ पढ़ते हैं (पर्ची, रेट लिस्ट, टिकट, मैसेज)?</t>
-        </is>
-      </c>
-      <c r="H216" s="2" t="inlineStr">
-        <is>
-          <t>0 No | 1 Yes</t>
-        </is>
-      </c>
-      <c r="I216" s="2" t="inlineStr"/>
-      <c r="J216" s="2" t="inlineStr">
-        <is>
           <t>STEP module 6A</t>
         </is>
       </c>
     </row>
-    <row r="217">
-      <c r="A217" s="2" t="n">
-        <v>216</v>
-      </c>
-      <c r="B217" s="2" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="C217" s="2" t="inlineStr">
-        <is>
-          <t>Tasks and skills (short block)</t>
-        </is>
-      </c>
-      <c r="D217" s="2" t="inlineStr">
-        <is>
-          <t>calc_at_work</t>
-        </is>
-      </c>
-      <c r="E217" s="2" t="inlineStr">
-        <is>
-          <t>yes/no</t>
-        </is>
-      </c>
-      <c r="F217" s="2" t="inlineStr">
-        <is>
-          <t>In your work, do you work out prices or costs?</t>
-        </is>
-      </c>
-      <c r="G217" s="2" t="inlineStr">
-        <is>
-          <t>अपने काम में क्या आप दाम या ख़र्चा जोड़ते-घटाते हैं?</t>
-        </is>
-      </c>
-      <c r="H217" s="2" t="inlineStr">
-        <is>
-          <t>0 No | 1 Yes</t>
-        </is>
-      </c>
-      <c r="I217" s="2" t="inlineStr"/>
-      <c r="J217" s="2" t="inlineStr">
-        <is>
-          <t>STEP module 6A</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J217"/>
+  <autoFilter ref="A1:J212"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -14341,7 +14099,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C135"/>
+  <dimension ref="A1:C133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="78" customWidth="1" min="1" max="1"/>
@@ -14403,11 +14161,11 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>female, hoh_relation, marital_status, knows_years_schooling, family_structure, migration_referral_other, work_equipment_detail, has_jandhan_account, n_life_insured, has_crop_insurance, govt_scheme_other</t>
+          <t>female, hoh_relation, marital_status, knows_years_schooling, family_structure, migration_referral_other, work_equipment_detail, n_life_insured, has_crop_insurance, govt_scheme_other</t>
         </is>
       </c>
     </row>
@@ -14474,22 +14232,22 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI housing indicator</t>
+          <t>NITI Aayog National MPI (years of schooling); Chaudhuri et al. 2002 covariate</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>floor_material, roof_material, house_type</t>
+          <t>years_schooling, education_level_cat</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI (years of schooling); Chaudhuri et al. 2002 covariate</t>
+          <t>NITI Aayog National MPI school-attendance indicator</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -14497,14 +14255,14 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>years_schooling, education_level_cat</t>
+          <t>n_children_6_14, n_children_out_school</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI school-attendance indicator</t>
+          <t>Project design (multiple job-holding, common in the Yatra economy)</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -14512,14 +14270,14 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>n_children_6_14, n_children_out_school</t>
+          <t>n_other_activities, other_activity_types</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Project design (multiple job-holding, common in the Yatra economy)</t>
+          <t>Apablaza et al. 2026 Q13 (decomposed into hours/day x days/week rather than asked as one weekly figure, for ease of recall)</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -14527,14 +14285,14 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>n_other_activities, other_activity_types</t>
+          <t>hours_day_yatra, days_week_yatra</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026 Q13 (decomposed into hours/day x days/week rather than asked as one weekly figure, for ease of recall)</t>
+          <t>Project design (off-season labour migration)</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
@@ -14542,14 +14300,14 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>hours_day_yatra, days_week_yatra</t>
+          <t>worked_away_in_closure, months_away_for_work</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>STEP module 2</t>
+          <t>Project design; coded to NCO-2015 in the office</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -14557,14 +14315,14 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>training_type, training_type_other</t>
+          <t>closure_work_detail, other_places_detail</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Project design (off-season labour migration)</t>
+          <t>Project design (measured seasonal base, asked as a spell)</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -14572,14 +14330,14 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>worked_away_in_closure, months_away_for_work</t>
+          <t>left_here_month, returned_here_month</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Project design; coded to NCO-2015 in the office</t>
+          <t>HCES 2022-23, MoSPI Appendix A, Sections 5.1-5.3 (30-day); IHDS-II Income and Social Capital Questionnaire, Q14 14.1-14.6 (30-day, same items)</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -14587,14 +14345,14 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>closure_work_detail, other_places_detail</t>
+          <t>cons_staples_yatra_pm, cons_staples_offseason_pm</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Project design (measured seasonal base, asked as a spell)</t>
+          <t>HCES 2022-23, MoSPI Appendix A, Sections 6.1-6.8 (7-day actual recall in HCES; asked here as a usual monthly figure instead, for the reason above)</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
@@ -14602,14 +14360,14 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>left_here_month, returned_here_month</t>
+          <t>cons_perishables_yatra_pm, cons_perishables_offseason_pm</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>HCES 2022-23, MoSPI Appendix A, Sections 5.1-5.3 (30-day); IHDS-II Income and Social Capital Questionnaire, Q14 14.1-14.6 (30-day, same items)</t>
+          <t>Calvo and Dercon 2007; Eze and Iheonu 2025 (non-purchased food, aggregate approach)</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -14617,14 +14375,14 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>cons_staples_yatra_pm, cons_staples_offseason_pm</t>
+          <t>cons_food_own_yatra_pm, cons_food_own_offseason_pm</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>HCES 2022-23, MoSPI Appendix A, Sections 6.1-6.8 (7-day actual recall in HCES; asked here as a usual monthly figure instead, for the reason above)</t>
+          <t>HCES 2022-23, MoSPI Appendix A, Section 7.1 'served processed food' (7-day in HCES; usual monthly here)</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
@@ -14632,14 +14390,14 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>cons_perishables_yatra_pm, cons_perishables_offseason_pm</t>
+          <t>cons_food_out_yatra_pm, cons_food_out_offseason_pm</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Calvo and Dercon 2007; Eze and Iheonu 2025 (non-purchased food, aggregate approach)</t>
+          <t>HCES 2022-23, MoSPI Appendix A, Section 8.1 (30-day). IHDS-II Income and Social Capital Questionnaire, Q14 14.21-14.22. Nigeria GHS-Panel Wave 3, Household Questionnaire, Sections 10B/11 (30-day tier)</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -14647,14 +14405,14 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>cons_food_own_yatra_pm, cons_food_own_offseason_pm</t>
+          <t>cons_fuel_yatra_pm, cons_fuel_offseason_pm</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>HCES 2022-23, MoSPI Appendix A, Section 7.1 'served processed food' (7-day in HCES; usual monthly here)</t>
+          <t>HCES 2022-23, MoSPI Appendix A, Sections 9.1-9.2 (30-day). IHDS-II Income and Social Capital Questionnaire, Q14 14.25-14.27. Nigeria GHS-Panel Wave 3, Household Questionnaire, Sections 10B/11 (30-day tier)</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
@@ -14662,14 +14420,14 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>cons_food_out_yatra_pm, cons_food_out_offseason_pm</t>
+          <t>cons_routine_misc_yatra_pm, cons_routine_misc_offseason_pm</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>HCES 2022-23, MoSPI Appendix A, Section 8.1 (30-day). IHDS-II Income and Social Capital Questionnaire, Q14 14.21-14.22. Nigeria GHS-Panel Wave 3, Household Questionnaire, Sections 10B/11 (30-day tier)</t>
+          <t>HCES 2022-23, MoSPI Appendix A, Sections 11.1-11.2 (30-day). IHDS-II Income and Social Capital Questionnaire, Q14 14.24/14.28. Nigeria GHS-Panel Wave 3, Household Questionnaire, Sections 10B/11 (30-day tier)</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -14677,14 +14435,14 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>cons_fuel_yatra_pm, cons_fuel_offseason_pm</t>
+          <t>cons_transport_comm_yatra_pm, cons_transport_comm_offseason_pm</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>HCES 2022-23, MoSPI Appendix A, Sections 9.1-9.2 (30-day). IHDS-II Income and Social Capital Questionnaire, Q14 14.25-14.27. Nigeria GHS-Panel Wave 3, Household Questionnaire, Sections 10B/11 (30-day tier)</t>
+          <t>HCES 2022-23, MoSPI Appendix A, Section 11.4 (30-day). IHDS-II Income and Social Capital Questionnaire, Q14 14.30. Nigeria GHS-Panel Wave 3, Household Questionnaire, Sections 10B/11 (30-day tier)</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
@@ -14692,14 +14450,14 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>cons_routine_misc_yatra_pm, cons_routine_misc_offseason_pm</t>
+          <t>cons_rent_yatra_pm, cons_rent_offseason_pm</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>HCES 2022-23, MoSPI Appendix A, Sections 11.1-11.2 (30-day). IHDS-II Income and Social Capital Questionnaire, Q14 14.24/14.28. Nigeria GHS-Panel Wave 3, Household Questionnaire, Sections 10B/11 (30-day tier)</t>
+          <t>HCES 2022-23, MoSPI Appendix A, Section 10.3 (30-day). IHDS-II Income and Social Capital Questionnaire, Q14 14.33 (30-day, out-patient)</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -14707,14 +14465,14 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>cons_transport_comm_yatra_pm, cons_transport_comm_offseason_pm</t>
+          <t>cons_med_nonhosp_yatra_pm, cons_med_nonhosp_offseason_pm</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>HCES 2022-23, MoSPI Appendix A, Section 11.4 (30-day). IHDS-II Income and Social Capital Questionnaire, Q14 14.30. Nigeria GHS-Panel Wave 3, Household Questionnaire, Sections 10B/11 (30-day tier)</t>
+          <t>HCES 2022-23, MoSPI Appendix A, Section 7.2 (7-day in HCES; usual monthly here, as for every other seasonal item)</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
@@ -14722,14 +14480,14 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>cons_rent_yatra_pm, cons_rent_offseason_pm</t>
+          <t>cons_packaged_food_yatra_pm, cons_packaged_food_offseason_pm</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>HCES 2022-23, MoSPI Appendix A, Section 10.3 (30-day). IHDS-II Income and Social Capital Questionnaire, Q14 14.33 (30-day, out-patient)</t>
+          <t>HCES 2022-23, MoSPI Appendix A, Sections 12.1-12.3 (7-day in HCES; usual monthly here, and combined into one figure)</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -14737,14 +14495,14 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>cons_med_nonhosp_yatra_pm, cons_med_nonhosp_offseason_pm</t>
+          <t>cons_pan_tobacco_yatra_pm, cons_pan_tobacco_offseason_pm</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>HCES 2022-23, MoSPI Appendix A, Section 7.2 (7-day in HCES; usual monthly here, as for every other seasonal item)</t>
+          <t>NITI Aayog National MPI housing indicator</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
@@ -14752,14 +14510,14 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>cons_packaged_food_yatra_pm, cons_packaged_food_offseason_pm</t>
+          <t>floor_material, roof_material</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>HCES 2022-23, MoSPI Appendix A, Sections 12.1-12.3 (7-day in HCES; usual monthly here, and combined into one figure)</t>
+          <t>NITI Aayog National MPI drinking-water indicator (30-minute round-trip rule)</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -14767,14 +14525,14 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>cons_pan_tobacco_yatra_pm, cons_pan_tobacco_offseason_pm</t>
+          <t>water_on_premises, water_fetch_minutes</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI drinking-water indicator (30-minute round-trip rule)</t>
+          <t>VEP adaptive-capacity covariate; STEP digital items</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
@@ -14782,14 +14540,14 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>water_on_premises, water_fetch_minutes</t>
+          <t>smartphone_owned, uses_digital_payment</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>VEP adaptive-capacity covariate; STEP digital items</t>
+          <t>Project design</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -14797,14 +14555,14 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>smartphone_owned, uses_digital_payment</t>
+          <t>morbidity_cost_15d, ropeway_stance</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Project design</t>
+          <t>Level ladder without licences</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
@@ -14812,14 +14570,14 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>morbidity_cost_15d, ropeway_stance</t>
+          <t>drove_car, drove_heavy</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Level ladder without licences</t>
+          <t>STEP module 6A</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -14827,29 +14585,29 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>drove_car, drove_heavy</t>
+          <t>read_at_work, calc_at_work</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>STEP module 6A</t>
+          <t>Standard; sensitivity covariate in the VEP model (Azeem et al. 2016 structure)</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>read_at_work, calc_at_work</t>
+          <t>age</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Standard; sensitivity covariate in the VEP model (Azeem et al. 2016 structure)</t>
+          <t>Project design (language proxy for regional/socioeconomic origin; avoids a sensitive caste question and covers out-of-country migrants)</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -14857,14 +14615,14 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>native_language</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Project design (language proxy for regional/socioeconomic origin; avoids a sensitive caste question and covers out-of-country migrants)</t>
+          <t>Project design (the language item stands in for caste; an uncoded 'other' is a real loss)</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
@@ -14872,14 +14630,14 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>native_language</t>
+          <t>native_language_other</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Project design (the language item stands in for caste; an uncoded 'other' is a real loss)</t>
+          <t>Chaudhuri et al. 2002; used to get per-capita consumption</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -14887,14 +14645,14 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>native_language_other</t>
+          <t>hhsize</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Chaudhuri et al. 2002; used to get per-capita consumption</t>
+          <t>NITI Aayog National MPI, Years of Schooling (weight 1/6)</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
@@ -14902,14 +14660,14 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>hhsize</t>
+          <t>any_member_6yr_schooling</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI, Years of Schooling (weight 1/6)</t>
+          <t>Dependency measure used in VEP studies (Azeem et al. 2016)</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -14917,14 +14675,14 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>any_member_6yr_schooling</t>
+          <t>n_earners</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Dependency measure used in VEP studies (Azeem et al. 2016)</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q4 (adapted to a single-respondent report: 'who is the main contributor' becomes 'are you the main contributor')</t>
         </is>
       </c>
       <c r="B39" s="2" t="n">
@@ -14932,14 +14690,14 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>n_earners</t>
+          <t>main_income_earner</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q4 (adapted to a single-respondent report: 'who is the main contributor' becomes 'are you the main contributor')</t>
+          <t>Adult-equivalent scales (Claro et al. 2010; Awuni et al. 2023)</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -14947,14 +14705,14 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>main_income_earner</t>
+          <t>n_children_u15</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Adult-equivalent scales (Claro et al. 2010; Awuni et al. 2023)</t>
+          <t>Project quota design, mapped to NCO-2015 families</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
@@ -14962,14 +14720,14 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>n_children_u15</t>
+          <t>occupation</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Project quota design, mapped to NCO-2015 families</t>
+          <t>Project design (coarse quota group + verbatim detail, coded to NCO-2015 in the office)</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -14977,14 +14735,14 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>occupation</t>
+          <t>occupation_detail</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Project design (coarse quota group + verbatim detail, coded to NCO-2015 in the office)</t>
+          <t>PLFS / NSS employment status classification [source not held by this project; citation unverified as of 2026-09-28]</t>
         </is>
       </c>
       <c r="B43" s="2" t="n">
@@ -14992,14 +14750,14 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>occupation_detail</t>
+          <t>employment_type</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>PLFS / NSS employment status classification [source not held by this project; citation unverified as of 2026-09-28]</t>
+          <t>Project design (multiple job-holding)</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -15007,14 +14765,14 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>employment_type</t>
+          <t>other_activity_income_pm</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Project design (multiple job-holding)</t>
+          <t>Chaudhuri et al. 2002 sensitivity covariate; Apablaza et al. 2026 Q10 (tenure in this job)</t>
         </is>
       </c>
       <c r="B45" s="2" t="n">
@@ -15022,14 +14780,14 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>other_activity_income_pm</t>
+          <t>years_in_yatra_work</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Chaudhuri et al. 2002 sensitivity covariate; Apablaza et al. 2026 Q10 (tenure in this job)</t>
+          <t>Occupational mobility check; job-history item</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -15037,14 +14795,14 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>years_in_yatra_work</t>
+          <t>prev_occ_change</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Occupational mobility check; job-history item</t>
+          <t>Gathmann and Schonberg 2010 (observed moves are systematically shorter than random moves -- the validation test for a task-distance measure); coded to NCO-2015 in the office</t>
         </is>
       </c>
       <c r="B47" s="2" t="n">
@@ -15052,14 +14810,14 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>prev_occ_change</t>
+          <t>prev_occ</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Gathmann and Schonberg 2010 (observed moves are systematically shorter than random moves -- the validation test for a task-distance measure); coded to NCO-2015 in the office</t>
+          <t>Project design (stated destination, for the structural-displacement analysis); coded to NCO-2015 in the office</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -15067,14 +14825,14 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>prev_occ</t>
+          <t>target_occ</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Project design (stated destination, for the structural-displacement analysis); coded to NCO-2015 in the office</t>
+          <t>Job-history item</t>
         </is>
       </c>
       <c r="B49" s="2" t="n">
@@ -15082,14 +14840,14 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>target_occ</t>
+          <t>prev_occ_reason</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Job-history item</t>
+          <t>STEP module 2; Chaudhuri et al. 2002 adaptive-capacity covariate</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -15097,14 +14855,14 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>prev_occ_reason</t>
+          <t>training_received</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>STEP module 2; Chaudhuri et al. 2002 adaptive-capacity covariate</t>
+          <t>Apablaza et al. 2026 Q14/Q15 (the 'does not know' route out of monthly earnings)</t>
         </is>
       </c>
       <c r="B51" s="2" t="n">
@@ -15112,14 +14870,14 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>training_received</t>
+          <t>knows_monthly_income</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026 Q14/Q15 (the 'does not know' route out of monthly earnings)</t>
+          <t>Apablaza et al. 2026 Q15 (fallback when monthly earnings are not known), adapted to an annual total for a seasonal workforce</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
@@ -15127,14 +14885,14 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>knows_monthly_income</t>
+          <t>income_annual_total</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026 Q15 (fallback when monthly earnings are not known), adapted to an annual total for a seasonal workforce</t>
+          <t>Project design (the Yatra / non-Yatra split needed to reweight an annual total onto the work calendar)</t>
         </is>
       </c>
       <c r="B53" s="2" t="n">
@@ -15142,14 +14900,14 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>income_annual_total</t>
+          <t>pct_income_yatra</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Project design (the Yatra / non-Yatra split needed to reweight an annual total onto the work calendar)</t>
+          <t>Project design (remittance channel as a financial-inclusion and cost measure)</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
@@ -15157,14 +14915,14 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>pct_income_yatra</t>
+          <t>remit_mode</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>Project design (remittance channel as a financial-inclusion and cost measure)</t>
+          <t>Apablaza et al. 2026 Q13, asked a second time for the off-season (decomposed as hours/day x days/week, as in the Yatra-season pair)</t>
         </is>
       </c>
       <c r="B55" s="2" t="n">
@@ -15172,14 +14930,14 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>remit_mode</t>
+          <t>hours_day_offseason</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026 Q13, asked a second time for the off-season (decomposed as hours/day x days/week, as in the Yatra-season pair)</t>
+          <t>Apablaza et al. 2026 Q13, asked a second time for the off-season</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
@@ -15187,14 +14945,14 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>hours_day_offseason</t>
+          <t>days_week_offseason</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026 Q13, asked a second time for the off-season</t>
+          <t>Project design (distance bucket); NOT an NSS classification -- the earlier citation to one was withdrawn 2026-09-28, no NSS schedule is held by this project</t>
         </is>
       </c>
       <c r="B57" s="2" t="n">
@@ -15202,14 +14960,14 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>days_week_offseason</t>
+          <t>origin</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>Project design (distance bucket); NOT an NSS classification -- the earlier citation to one was withdrawn 2026-09-28, no NSS schedule is held by this project</t>
+          <t>Standard state/UT classification; needed to apply the right poverty line per respondent</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
@@ -15217,14 +14975,14 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>origin</t>
+          <t>home_state</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>Standard state/UT classification; needed to apply the right poverty line per respondent</t>
+          <t>Rural and urban poverty lines (Sethu et al. 2024)</t>
         </is>
       </c>
       <c r="B59" s="2" t="n">
@@ -15232,14 +14990,14 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>home_state</t>
+          <t>home_rural_urban</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>Rural and urban poverty lines (Sethu et al. 2024)</t>
+          <t>Project design; categories from the pilot's own residency_pattern distribution (n=46)</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
@@ -15247,14 +15005,14 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>home_rural_urban</t>
+          <t>resp_returns_at_closure</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>Project design; categories from the pilot's own residency_pattern distribution (n=46)</t>
+          <t>Project design (split-household measurement, underpinning Module E)</t>
         </is>
       </c>
       <c r="B61" s="2" t="n">
@@ -15262,14 +15020,14 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>resp_returns_at_closure</t>
+          <t>hh_at_home_place</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>Project design (split-household measurement, underpinning Module E)</t>
+          <t>Project design (season-specific denominator for per-capita consumption)</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
@@ -15277,14 +15035,14 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>hh_at_home_place</t>
+          <t>n_here_season</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>Project design (season-specific denominator for per-capita consumption)</t>
+          <t>Project design (duration of the seasonal relationship)</t>
         </is>
       </c>
       <c r="B63" s="2" t="n">
@@ -15292,14 +15050,14 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>n_here_season</t>
+          <t>years_coming_here</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>Project design (duration of the seasonal relationship)</t>
+          <t>Project design (push/pull as a vulnerability covariate)</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
@@ -15307,14 +15065,14 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>years_coming_here</t>
+          <t>came_here_reason</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>Project design (push/pull as a vulnerability covariate)</t>
+          <t>Project design (revealed mobility, for the transferability paper)</t>
         </is>
       </c>
       <c r="B65" s="2" t="n">
@@ -15322,14 +15080,14 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>came_here_reason</t>
+          <t>worked_other_places</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>Project design (revealed mobility, for the transferability paper)</t>
+          <t>Project design; horizoned intention item after VASyR 2025 (move_accom_yesno, asked over a stated 6-month horizon)</t>
         </is>
       </c>
       <c r="B66" s="2" t="n">
@@ -15337,14 +15095,14 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>worked_other_places</t>
+          <t>would_move_for_work</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>Project design; horizoned intention item after VASyR 2025 (move_accom_yesno, asked over a stated 6-month horizon)</t>
+          <t>Project design (referral channel as a proxy for social capital and for placement debt)</t>
         </is>
       </c>
       <c r="B67" s="2" t="n">
@@ -15352,14 +15110,14 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>would_move_for_work</t>
+          <t>migration_referral</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>Project design (referral channel as a proxy for social capital and for placement debt)</t>
+          <t>Project design (respondent-gated seasonal recall); the underlying two-season design follows Beegle et al. 2012 and Deaton and Grosh 2000 on usual-period recall</t>
         </is>
       </c>
       <c r="B68" s="2" t="n">
@@ -15367,14 +15125,14 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>migration_referral</t>
+          <t>spend_differs_by_season</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>Project design (respondent-gated seasonal recall); the underlying two-season design follows Beegle et al. 2012 and Deaton and Grosh 2000 on usual-period recall</t>
+          <t>HCES 2022-23, MoSPI Appendix A, Sections 13.1-13.2 (365-day). IHDS-II Income and Social Capital Questionnaire, Q14 14.38-14.39 (365-day). Nigeria GHS-Panel Wave 3, Household Questionnaire, Sections 10B/11 instead uses a 6-month recall for clothing (items 401-441); we follow the two India sources, since one of them (HCES) underlies our poverty line</t>
         </is>
       </c>
       <c r="B69" s="2" t="n">
@@ -15382,14 +15140,14 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>spend_differs_by_season</t>
+          <t>cons_clothing_12m</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>HCES 2022-23, MoSPI Appendix A, Sections 13.1-13.2 (365-day). IHDS-II Income and Social Capital Questionnaire, Q14 14.38-14.39 (365-day). Nigeria GHS-Panel Wave 3, Household Questionnaire, Sections 10B/11 instead uses a 6-month recall for clothing (items 401-441); we follow the two India sources, since one of them (HCES) underlies our poverty line</t>
+          <t>HCES 2022-23, MoSPI Appendix A, Section 10.1 (365-day). IHDS-II Income and Social Capital Questionnaire, Q14 14.35-14.37 (365-day, same items). Nigeria GHS-Panel Wave 3, Household Questionnaire, Sections 10B/11 asks school fees inside its education/roster module, per child, not as a household total, so it is not directly comparable</t>
         </is>
       </c>
       <c r="B70" s="2" t="n">
@@ -15397,14 +15155,14 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>cons_clothing_12m</t>
+          <t>cons_education_12m</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>HCES 2022-23, MoSPI Appendix A, Section 10.1 (365-day). IHDS-II Income and Social Capital Questionnaire, Q14 14.35-14.37 (365-day, same items). Nigeria GHS-Panel Wave 3, Household Questionnaire, Sections 10B/11 asks school fees inside its education/roster module, per child, not as a household total, so it is not directly comparable</t>
+          <t>HCES 2022-23, MoSPI Appendix A, Section 10.2 (365-day, hospitalisation). IHDS-II Income and Social Capital Questionnaire, Q14 14.34 (365-day, in-patient). Nigeria GHS-Panel Wave 3, Household Questionnaire, Sections 10B/11 instead uses one combined 6-month medical item (less detail); we follow the matching HCES/IHDS split</t>
         </is>
       </c>
       <c r="B71" s="2" t="n">
@@ -15412,14 +15170,14 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>cons_education_12m</t>
+          <t>cons_medical_hosp_12m</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>HCES 2022-23, MoSPI Appendix A, Section 10.2 (365-day, hospitalisation). IHDS-II Income and Social Capital Questionnaire, Q14 14.34 (365-day, in-patient). Nigeria GHS-Panel Wave 3, Household Questionnaire, Sections 10B/11 instead uses one combined 6-month medical item (less detail); we follow the matching HCES/IHDS split</t>
+          <t>HCES 2022-23, MoSPI Appendix A, Section 14 (365-day, 10 sub-groups). IHDS-II Income and Social Capital Questionnaire, Q14 14.40-14.48 (365-day). Nigeria GHS-Panel Wave 3, Household Questionnaire, Sections 10B/11 (12-month tier: durables, appliances, building materials). All three agree on the 12-month recall; insurance premiums, which IHDS (14.50) and the Nigeria survey (items 510-513) count here, are excluded, following HCES and standard national-accounts practice (insurance is a financial item, not consumption) -- premiums are covered instead by the insurance items in Module G</t>
         </is>
       </c>
       <c r="B72" s="2" t="n">
@@ -15427,14 +15185,14 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>cons_medical_hosp_12m</t>
+          <t>cons_durables_12m</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>HCES 2022-23, MoSPI Appendix A, Section 14 (365-day, 10 sub-groups). IHDS-II Income and Social Capital Questionnaire, Q14 14.40-14.48 (365-day). Nigeria GHS-Panel Wave 3, Household Questionnaire, Sections 10B/11 (12-month tier: durables, appliances, building materials). All three agree on the 12-month recall; insurance premiums, which IHDS (14.50) and the Nigeria survey (items 510-513) count here, are excluded, following HCES and standard national-accounts practice (insurance is a financial item, not consumption) -- premiums are covered instead by the insurance items in Module G</t>
+          <t>NITI Aayog National MPI housing indicator (wall limb)</t>
         </is>
       </c>
       <c r="B73" s="2" t="n">
@@ -15442,14 +15200,14 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>cons_durables_12m</t>
+          <t>wall_material</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI housing indicator (wall limb)</t>
+          <t>Lyons et al. 2023, Table 2 (area/settlement conditions), adapted to a labour-migrant setting</t>
         </is>
       </c>
       <c r="B74" s="2" t="n">
@@ -15457,14 +15215,14 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>wall_material</t>
+          <t>accom_type_here</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>Lyons et al. 2023, Table 2 (area/settlement conditions), adapted to a labour-migrant setting</t>
+          <t>NITI Aayog National MPI</t>
         </is>
       </c>
       <c r="B75" s="2" t="n">
@@ -15472,14 +15230,14 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>accom_type_here</t>
+          <t>electricity</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI</t>
+          <t>NITI Aayog National MPI sanitation indicator (improved/unimproved and shared/not)</t>
         </is>
       </c>
       <c r="B76" s="2" t="n">
@@ -15487,14 +15245,14 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>electricity</t>
+          <t>toilet_type</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI sanitation indicator (improved/unimproved and shared/not)</t>
+          <t>NITI Aayog National MPI drinking-water indicator (JMP improved/unimproved taxonomy)</t>
         </is>
       </c>
       <c r="B77" s="2" t="n">
@@ -15502,14 +15260,14 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>toilet_type</t>
+          <t>drinking_water</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI drinking-water indicator (JMP improved/unimproved taxonomy)</t>
+          <t>NITI Aayog National MPI cooking-fuel indicator (its own list of dirty fuels)</t>
         </is>
       </c>
       <c r="B78" s="2" t="n">
@@ -15517,14 +15275,14 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>drinking_water</t>
+          <t>cooking_fuel</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>Project design (intra-household burden of water collection; DHS/NFHS ask the same item)</t>
+          <t>NITI Aayog National MPI assets indicator (car or truck limb)</t>
         </is>
       </c>
       <c r="B79" s="2" t="n">
@@ -15532,14 +15290,14 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>water_fetched_by</t>
+          <t>owns_car</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI cooking-fuel indicator (its own list of dirty fuels)</t>
+          <t>Project design (pilot livelihood survey)</t>
         </is>
       </c>
       <c r="B80" s="2" t="n">
@@ -15547,14 +15305,14 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>cooking_fuel</t>
+          <t>owns_pony_mule</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI assets indicator (car or truck limb)</t>
+          <t>NITI Aayog National MPI bank-account indicator; VEP adaptive-capacity covariate</t>
         </is>
       </c>
       <c r="B81" s="2" t="n">
@@ -15562,14 +15320,14 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>owns_car</t>
+          <t>has_bank_account</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>Project design (pilot livelihood survey)</t>
+          <t>VEP adaptive-capacity covariate</t>
         </is>
       </c>
       <c r="B82" s="2" t="n">
@@ -15577,14 +15335,14 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>owns_pony_mule</t>
+          <t>took_loan_12m</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI bank-account indicator; VEP adaptive-capacity covariate</t>
+          <t>VEP adaptive-capacity covariate (lender type)</t>
         </is>
       </c>
       <c r="B83" s="2" t="n">
@@ -15592,14 +15350,14 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>has_bank_account</t>
+          <t>credit_source</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>VEP adaptive-capacity covariate</t>
+          <t>Islam and Chowdhury 2025 (financial distress and household vulnerability to poverty)</t>
         </is>
       </c>
       <c r="B84" s="2" t="n">
@@ -15607,14 +15365,14 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>took_loan_12m</t>
+          <t>loan_amount</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>VEP adaptive-capacity covariate (lender type)</t>
+          <t>Project design (informal lending is often interest-free)</t>
         </is>
       </c>
       <c r="B85" s="2" t="n">
@@ -15622,14 +15380,14 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>credit_source</t>
+          <t>pays_interest</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>Islam and Chowdhury 2025 (financial distress and household vulnerability to poverty)</t>
+          <t>Project design (informal-credit pricing as locally quoted)</t>
         </is>
       </c>
       <c r="B86" s="2" t="n">
@@ -15637,14 +15395,14 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>loan_amount</t>
+          <t>loan_interest_per100_pm</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>Project design (informal lending is often interest-free)</t>
+          <t>Carter and Zimmerman 2000; Chiwaula et al. 2011 (asset-based vulnerability)</t>
         </is>
       </c>
       <c r="B87" s="2" t="n">
@@ -15652,14 +15410,14 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>pays_interest</t>
+          <t>loan_against_asset</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>Project design (informal-credit pricing as locally quoted)</t>
+          <t>Carter and Zimmerman 2000; Zimmerman and Carter 2003 (asset-based coping)</t>
         </is>
       </c>
       <c r="B88" s="2" t="n">
@@ -15667,14 +15425,14 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>loan_interest_per100_pm</t>
+          <t>loan_collateral</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>Carter and Zimmerman 2000; Chiwaula et al. 2011 (asset-based vulnerability)</t>
+          <t>NITI Aayog National MPI health-insurance indicator; Lyons et al. 2023</t>
         </is>
       </c>
       <c r="B89" s="2" t="n">
@@ -15682,14 +15440,14 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>loan_against_asset</t>
+          <t>n_health_insured</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>Carter and Zimmerman 2000; Zimmerman and Carter 2003 (asset-based coping)</t>
+          <t>Project design; scheme names as administered in Uttarakhand</t>
         </is>
       </c>
       <c r="B90" s="2" t="n">
@@ -15697,14 +15455,14 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>loan_collateral</t>
+          <t>govt_schemes</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI health-insurance indicator; Lyons et al. 2023</t>
+          <t>Lyons et al. 2023, Table 2 (legal residency), adapted; One Nation One Ration Card</t>
         </is>
       </c>
       <c r="B91" s="2" t="n">
@@ -15712,14 +15470,14 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>n_health_insured</t>
+          <t>ration_portable_here</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>Project design; scheme names as administered in Uttarakhand</t>
+          <t>Project design (intra-household financial capability)</t>
         </is>
       </c>
       <c r="B92" s="2" t="n">
@@ -15727,14 +15485,14 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>govt_schemes</t>
+          <t>n_can_transact_online</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>Lyons et al. 2023, Table 2 (legal residency), adapted; One Nation One Ration Card</t>
+          <t>NSS health module (15-day recall) [source not held by this project; citation unverified as of 2026-09-28]</t>
         </is>
       </c>
       <c r="B93" s="2" t="n">
@@ -15742,14 +15500,14 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>ration_portable_here</t>
+          <t>morbidity_15d</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>Project design (intra-household financial capability)</t>
+          <t>Project design (a reported illness with no cost/coping follow-up said nothing about its burden)</t>
         </is>
       </c>
       <c r="B94" s="2" t="n">
@@ -15757,14 +15515,14 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>n_can_transact_online</t>
+          <t>morbidity_coping_15d</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>NSS health module (15-day recall) [source not held by this project; citation unverified as of 2026-09-28]</t>
+          <t>Washington Group on Disability Statistics, Short Set item 3 (mobility), verbatim; Lyons et al. 2023 health dimension</t>
         </is>
       </c>
       <c r="B95" s="2" t="n">
@@ -15772,14 +15530,14 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>morbidity_15d</t>
+          <t>func_limitation</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>Project design (a reported illness with no cost/coping follow-up said nothing about its burden)</t>
+          <t>NSS health module (365-day recall) [source not held by this project; citation unverified as of 2026-09-28]</t>
         </is>
       </c>
       <c r="B96" s="2" t="n">
@@ -15787,14 +15545,14 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>morbidity_coping_15d</t>
+          <t>hospitalization_365d</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>Washington Group on Disability Statistics, Short Set item 3 (mobility), verbatim; Lyons et al. 2023 health dimension</t>
+          <t>VASyR 2025 barriers_health_case_access_phc_m (primary-care access barriers); Lyons et al. 2023 Table 2 indicator 2 'healthcare access'</t>
         </is>
       </c>
       <c r="B97" s="2" t="n">
@@ -15802,14 +15560,14 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>func_limitation</t>
+          <t>health_access_barrier_3m</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>NSS health module (365-day recall) [source not held by this project; citation unverified as of 2026-09-28]</t>
+          <t>NITI Aayog National MPI, Child and Adolescent Mortality (weight 1/12)</t>
         </is>
       </c>
       <c r="B98" s="2" t="n">
@@ -15817,14 +15575,14 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>hospitalization_365d</t>
+          <t>child_death_5y</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>VASyR 2025 barriers_health_case_access_phc_m (primary-care access barriers); Lyons et al. 2023 Table 2 indicator 2 'healthcare access'</t>
+          <t>NITI Aayog National MPI, Maternal Health (weight 1/12)</t>
         </is>
       </c>
       <c r="B99" s="2" t="n">
@@ -15832,14 +15590,14 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>health_access_barrier_3m</t>
+          <t>birth_last_5y</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI, Child and Adolescent Mortality (weight 1/12)</t>
+          <t>NITI Aayog National MPI, Maternal Health (antenatal care limb)</t>
         </is>
       </c>
       <c r="B100" s="2" t="n">
@@ -15847,14 +15605,14 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>child_death_5y</t>
+          <t>anc_4_visits</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI, Maternal Health (weight 1/12)</t>
+          <t>NITI Aayog National MPI, Maternal Health (assisted delivery limb)</t>
         </is>
       </c>
       <c r="B101" s="2" t="n">
@@ -15862,14 +15620,14 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>birth_last_5y</t>
+          <t>skilled_birth_attendant</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI, Maternal Health (antenatal care limb)</t>
+          <t>VEP exposure covariate (Azeem et al. 2016); shock inventory following Gunther and Harttgen 2009, via Fujii 2016 section 4</t>
         </is>
       </c>
       <c r="B102" s="2" t="n">
@@ -15877,14 +15635,14 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>anc_4_visits</t>
+          <t>distress_event_last365d</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI, Maternal Health (assisted delivery limb)</t>
+          <t>Project design (anchors the magnitude and timing pair)</t>
         </is>
       </c>
       <c r="B103" s="2" t="n">
@@ -15892,14 +15650,14 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>skilled_birth_attendant</t>
+          <t>shock_worst</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>VEP exposure covariate (Azeem et al. 2016); shock inventory following Gunther and Harttgen 2009, via Fujii 2016 section 4</t>
+          <t>Ligon and Schechter 2003; Dercon and Krishnan 2000 (VER needs shock magnitude, not only incidence)</t>
         </is>
       </c>
       <c r="B104" s="2" t="n">
@@ -15907,14 +15665,14 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>distress_event_last365d</t>
+          <t>shock_loss_amount</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>Project design (anchors the magnitude and timing pair)</t>
+          <t>Dercon and Krishnan 2000 (seasonal timing of shocks); project design</t>
         </is>
       </c>
       <c r="B105" s="2" t="n">
@@ -15922,14 +15680,14 @@
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>shock_worst</t>
+          <t>shock_month</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>Ligon and Schechter 2003; Dercon and Krishnan 2000 (VER needs shock magnitude, not only incidence)</t>
+          <t>Coping strategies in VEP studies; Carter and Zimmerman 2000 on asset versus consumption smoothing</t>
         </is>
       </c>
       <c r="B106" s="2" t="n">
@@ -15937,14 +15695,14 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>shock_loss_amount</t>
+          <t>shock_coping</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>Dercon and Krishnan 2000 (seasonal timing of shocks); project design</t>
+          <t>Project design (see tasks_module W4: exposure must be asked directly)</t>
         </is>
       </c>
       <c r="B107" s="2" t="n">
@@ -15952,14 +15710,14 @@
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>shock_month</t>
+          <t>trek_dependent</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>Coping strategies in VEP studies; Carter and Zimmerman 2000 on asset versus consumption smoothing</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q5 (all eleven categories, with its own three-way routing)</t>
         </is>
       </c>
       <c r="B108" s="2" t="n">
@@ -15967,14 +15725,14 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>shock_coping</t>
+          <t>job_situation</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>Project design (see tasks_module W4: exposure must be asked directly)</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q9</t>
         </is>
       </c>
       <c r="B109" s="2" t="n">
@@ -15982,14 +15740,14 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>trek_dependent</t>
+          <t>job_permanence</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q5 (all eleven categories, with its own three-way routing)</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q11</t>
         </is>
       </c>
       <c r="B110" s="2" t="n">
@@ -15997,14 +15755,14 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>job_situation</t>
+          <t>contract_status</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q9</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q12 (widened to local registrations)</t>
         </is>
       </c>
       <c r="B111" s="2" t="n">
@@ -16012,14 +15770,14 @@
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>job_permanence</t>
+          <t>workplace_registered</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q11</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q16</t>
         </is>
       </c>
       <c r="B112" s="2" t="n">
@@ -16027,14 +15785,14 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>contract_status</t>
+          <t>pension_contrib</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q12 (widened to local registrations)</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q17</t>
         </is>
       </c>
       <c r="B113" s="2" t="n">
@@ -16042,14 +15800,14 @@
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>workplace_registered</t>
+          <t>work_health_ins</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q16</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q18</t>
         </is>
       </c>
       <c r="B114" s="2" t="n">
@@ -16057,14 +15815,14 @@
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>pension_contrib</t>
+          <t>leave_rights</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q17</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q19</t>
         </is>
       </c>
       <c r="B115" s="2" t="n">
@@ -16072,14 +15830,14 @@
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>work_health_ins</t>
+          <t>injured_ever</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q18</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q20</t>
         </is>
       </c>
       <c r="B116" s="2" t="n">
@@ -16087,14 +15845,14 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>leave_rights</t>
+          <t>workplace_injury_12m</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q19</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q21</t>
         </is>
       </c>
       <c r="B117" s="2" t="n">
@@ -16102,14 +15860,14 @@
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>injured_ever</t>
+          <t>wants_more_work</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q20</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q22</t>
         </is>
       </c>
       <c r="B118" s="2" t="n">
@@ -16117,14 +15875,14 @@
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>workplace_injury_12m</t>
+          <t>more_hours_day</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q21</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q23 (duration in weeks, tied to the calendar instead of a single point in time)</t>
         </is>
       </c>
       <c r="B119" s="2" t="n">
@@ -16132,14 +15890,14 @@
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>wants_more_work</t>
+          <t>months_looked_for_work</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q22</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q24</t>
         </is>
       </c>
       <c r="B120" s="2" t="n">
@@ -16147,14 +15905,14 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>more_hours_day</t>
+          <t>first_job_ever</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q23 (duration in weeks, tied to the calendar instead of a single point in time)</t>
+          <t>Gathmann and Schonberg 2010; NCO 9333.0100 loader</t>
         </is>
       </c>
       <c r="B121" s="2" t="n">
@@ -16162,14 +15920,14 @@
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>months_looked_for_work</t>
+          <t>tk_load</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q24</t>
+          <t>Spitz-Oener 2006 / STEP; NCO 8322.0100</t>
         </is>
       </c>
       <c r="B122" s="2" t="n">
@@ -16177,14 +15935,14 @@
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>first_job_ever</t>
+          <t>tk_drive</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>Gathmann and Schonberg 2010; NCO 9333.0100 loader</t>
+          <t>Gathmann and Schonberg 2010; NCO 8343.1700 ropeway operator</t>
         </is>
       </c>
       <c r="B123" s="2" t="n">
@@ -16192,14 +15950,14 @@
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>tk_load</t>
+          <t>tk_engine</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>Spitz-Oener 2006 / STEP; NCO 8322.0100</t>
+          <t>Spitz-Oener 2006; NCO 7411.0301 wireman</t>
         </is>
       </c>
       <c r="B124" s="2" t="n">
@@ -16207,14 +15965,14 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>tk_drive</t>
+          <t>tk_electric</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>Gathmann and Schonberg 2010; NCO 8343.1700 ropeway operator</t>
+          <t>Gathmann and Schonberg 2010; NCO 8343.1700</t>
         </is>
       </c>
       <c r="B125" s="2" t="n">
@@ -16222,14 +15980,14 @@
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>tk_engine</t>
+          <t>tk_safety</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>Spitz-Oener 2006; NCO 7411.0301 wireman</t>
+          <t>Gathmann and Schonberg 2010; NCO 5223.0200</t>
         </is>
       </c>
       <c r="B126" s="2" t="n">
@@ -16237,14 +15995,14 @@
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>tk_electric</t>
+          <t>tk_sell</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>Gathmann and Schonberg 2010; NCO 8343.1700</t>
+          <t>Autor and Handel 2013; NCO 5131.0401</t>
         </is>
       </c>
       <c r="B127" s="2" t="n">
@@ -16252,14 +16010,14 @@
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>tk_safety</t>
+          <t>tk_cash</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>Gathmann and Schonberg 2010; NCO 5223.0200</t>
+          <t>NCO 5120.0300 cook</t>
         </is>
       </c>
       <c r="B128" s="2" t="n">
@@ -16267,14 +16025,14 @@
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>tk_sell</t>
+          <t>tk_cook</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>Autor and Handel 2013; NCO 5131.0401</t>
+          <t>NCO 5131.0401 waiter; Pal et al. 2026</t>
         </is>
       </c>
       <c r="B129" s="2" t="n">
@@ -16282,14 +16040,14 @@
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>tk_cash</t>
+          <t>tk_serve</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>NCO 5120.0300 cook</t>
+          <t>NCO 5151.0202 room attendant; Autor-Levy-Murnane 2003 (janitorial)</t>
         </is>
       </c>
       <c r="B130" s="2" t="n">
@@ -16297,14 +16055,14 @@
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>tk_cook</t>
+          <t>tk_clean</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>NCO 5131.0401 waiter; Pal et al. 2026</t>
+          <t>Gathmann and Schonberg 2010; NCO 5113.0200</t>
         </is>
       </c>
       <c r="B131" s="2" t="n">
@@ -16312,14 +16070,14 @@
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>tk_serve</t>
+          <t>tk_guide</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>NCO 5151.0202 room attendant; Autor-Levy-Murnane 2003 (janitorial)</t>
+          <t>NCO 8343.1700 ropeway operator</t>
         </is>
       </c>
       <c r="B132" s="2" t="n">
@@ -16327,14 +16085,14 @@
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>tk_clean</t>
+          <t>tk_coord</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>Gathmann and Schonberg 2010; NCO 5113.0200</t>
+          <t>Level ladder without licences: people drive without holding a licence</t>
         </is>
       </c>
       <c r="B133" s="2" t="n">
@@ -16342,42 +16100,12 @@
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>tk_guide</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
-        <is>
-          <t>NCO 8343.1700 ropeway operator</t>
-        </is>
-      </c>
-      <c r="B134" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>tk_coord</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
-        <is>
-          <t>Level ladder without licences: people drive without holding a licence</t>
-        </is>
-      </c>
-      <c r="B135" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C135" s="2" t="inlineStr">
-        <is>
           <t>drove_twowheeler</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C135"/>
+  <autoFilter ref="A1:C133"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -16455,7 +16183,7 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5">
@@ -16515,7 +16243,7 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9">
@@ -16530,7 +16258,7 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
@@ -16616,7 +16344,7 @@
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>216</v>
+        <v>211</v>
       </c>
     </row>
   </sheetData>

--- a/replication/final_instrument/questionnaire/Question_register.xlsx
+++ b/replication/final_instrument/questionnaire/Question_register.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Questions'!$A$1:$J$212</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Constructed variables'!$A$1:$F$130</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Constructed variables'!$A$1:$F$131</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Literature'!$A$1:$C$133</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Modules'!$A$1:$C$15</definedName>
   </definedNames>
@@ -8016,7 +8016,7 @@
       </c>
       <c r="H166" s="2" t="inlineStr">
         <is>
-          <t>1 Serious illness or death of an earning member | 2 Crop failure or livestock loss | 3 Damage from a natural disaster (flood, landslide, fire) | 4 Loss of business, goods or assets | 5 Road or bridge blocked, route closed | 6 Yatra stopped early or badly disrupted | 7 Sharp fall in customers or prices | 8 Lost the work or the work stopped</t>
+          <t>9 Nothing of this kind happened | 1 Serious illness or death of an earning member | 2 Crop failure or livestock loss | 3 Damage from a natural disaster (flood, landslide, fire) | 4 Loss of business, goods or assets | 5 Road or bridge blocked, route closed | 6 Yatra stopped early or badly disrupted | 7 Sharp fall in customers or prices | 8 Lost the work or the work stopped</t>
         </is>
       </c>
       <c r="I166" s="2" t="inlineStr"/>
@@ -8062,12 +8062,12 @@
       </c>
       <c r="H167" s="2" t="inlineStr">
         <is>
-          <t>1 Serious illness or death of an earning member | 2 Crop failure or livestock loss | 3 Damage from a natural disaster (flood, landslide, fire) | 4 Loss of business, goods or assets | 5 Road or bridge blocked, route closed | 6 Yatra stopped early or badly disrupted | 7 Sharp fall in customers or prices | 8 Lost the work or the work stopped</t>
+          <t>9 Nothing of this kind happened | 1 Serious illness or death of an earning member | 2 Crop failure or livestock loss | 3 Damage from a natural disaster (flood, landslide, fire) | 4 Loss of business, goods or assets | 5 Road or bridge blocked, route closed | 6 Yatra stopped early or badly disrupted | 7 Sharp fall in customers or prices | 8 Lost the work or the work stopped</t>
         </is>
       </c>
       <c r="I167" s="2" t="inlineStr">
         <is>
-          <t>Ask only if distress_event_last365d is not empty</t>
+          <t>Ask only if distress_event_last365d names a real shock (not code 9, nothing happened)</t>
         </is>
       </c>
       <c r="J167" s="2" t="inlineStr">
@@ -8113,7 +8113,7 @@
       <c r="H168" s="2" t="inlineStr"/>
       <c r="I168" s="2" t="inlineStr">
         <is>
-          <t>Ask only if distress_event_last365d is not empty</t>
+          <t>Ask only if distress_event_last365d names a real shock (not code 9, nothing happened)</t>
         </is>
       </c>
       <c r="J168" s="2" t="inlineStr">
@@ -8163,7 +8163,7 @@
       </c>
       <c r="I169" s="2" t="inlineStr">
         <is>
-          <t>Ask only if distress_event_last365d is not empty</t>
+          <t>Ask only if distress_event_last365d names a real shock (not code 9, nothing happened)</t>
         </is>
       </c>
       <c r="J169" s="2" t="inlineStr">
@@ -10174,7 +10174,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F130"/>
+  <dimension ref="A1:F131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -12293,27 +12293,27 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>cope_1</t>
+          <t>no_shock_reported</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Coping: Used savings</t>
+          <t>Explicitly reported that nothing of this kind happened</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>shock_coping contains 1</t>
+          <t>distress_event_last365d contains 9</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>1 if 'Used savings' was ticked.</t>
+          <t>1 if code 9 was ticked. Distinct from an empty list, which the form can no longer produce: the item is required and code 9 is how a household with no shock answers it.</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>Split from the select_multiple export</t>
+          <t>Project design (escape option on a required check-all)</t>
         </is>
       </c>
     </row>
@@ -12323,22 +12323,22 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>cope_2</t>
+          <t>cope_1</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Coping: Borrowed money</t>
+          <t>Coping: Used savings</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>shock_coping contains 2</t>
+          <t>shock_coping contains 1</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>1 if 'Borrowed money' was ticked.</t>
+          <t>1 if 'Used savings' was ticked.</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -12353,22 +12353,22 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>cope_3</t>
+          <t>cope_2</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Coping: Sold or pawned assets</t>
+          <t>Coping: Borrowed money</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>shock_coping contains 3</t>
+          <t>shock_coping contains 2</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>1 if 'Sold or pawned assets' was ticked.</t>
+          <t>1 if 'Borrowed money' was ticked.</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -12383,22 +12383,22 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>cope_4</t>
+          <t>cope_3</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Coping: Cut consumption</t>
+          <t>Coping: Sold or pawned assets</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>shock_coping contains 4</t>
+          <t>shock_coping contains 3</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>1 if 'Cut consumption' was ticked.</t>
+          <t>1 if 'Sold or pawned assets' was ticked.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -12413,22 +12413,22 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>cope_5</t>
+          <t>cope_4</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Coping: Help from relatives/community</t>
+          <t>Coping: Cut consumption</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>shock_coping contains 5</t>
+          <t>shock_coping contains 4</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>1 if 'Help from relatives/community' was ticked.</t>
+          <t>1 if 'Cut consumption' was ticked.</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -12443,22 +12443,22 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>cope_6</t>
+          <t>cope_5</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Coping: Did nothing/other</t>
+          <t>Coping: Help from relatives/community</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>shock_coping contains 6</t>
+          <t>shock_coping contains 5</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>1 if 'Did nothing/other' was ticked.</t>
+          <t>1 if 'Help from relatives/community' was ticked.</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -12473,27 +12473,27 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>shock_count</t>
+          <t>cope_6</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Number of distinct shocks reported (0-8)</t>
+          <t>Coping: Did nothing/other</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>sum of shock_1..8</t>
+          <t>shock_coping contains 6</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>Count of shock types ticked. The old single-answer item could only ever be 0 or 1.</t>
+          <t>1 if 'Did nothing/other' was ticked.</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>Constructed</t>
+          <t>Split from the select_multiple export</t>
         </is>
       </c>
     </row>
@@ -12503,22 +12503,22 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>shock_any</t>
+          <t>shock_count</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Suffered any shock in the last 12 months</t>
+          <t>Number of distinct shocks reported (0-8)</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>shock_count &gt; 0</t>
+          <t>sum of shock_1..8</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>1 if any shock was ticked.</t>
+          <t>Count of shock types ticked. The old single-answer item could only ever be 0 or 1.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -12533,27 +12533,27 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>shock_covariate</t>
+          <t>shock_any</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Suffered a COVARIATE shock</t>
+          <t>Suffered any shock in the last 12 months</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>any of shock_3 shock_5 shock_6 shock_7</t>
+          <t>shock_count &gt; 0</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>1 if any of: natural disaster, road or bridge blocked, Yatra stopped or disrupted, sharp fall in customers or prices (codes 3, 5, 6, 7). These hit the whole route at once, so they are the shocks a ropeway -- or a flood year -- delivers to everyone simultaneously. Separating them from idiosyncratic shocks is what makes the covariate/idiosyncratic variance decomposition identifiable.</t>
+          <t>1 if any shock was ticked.</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>Gunther and Harttgen 2009, via Fujii 2016 section 2.2</t>
+          <t>Constructed</t>
         </is>
       </c>
     </row>
@@ -12563,22 +12563,22 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>shock_idiosyncratic</t>
+          <t>shock_covariate</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Suffered an IDIOSYNCRATIC shock</t>
+          <t>Suffered a COVARIATE shock</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>any of shock_1 shock_2 shock_4 shock_8</t>
+          <t>any of shock_3 shock_5 shock_6 shock_7</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>1 if any of: illness or death of an earning member, crop or livestock loss, loss of business or assets, lost the work (codes 1, 2, 4, 8). These hit one household at a time.</t>
+          <t>1 if any of: natural disaster, road or bridge blocked, Yatra stopped or disrupted, sharp fall in customers or prices (codes 3, 5, 6, 7). These hit the whole route at once, so they are the shocks a ropeway -- or a flood year -- delivers to everyone simultaneously. Separating them from idiosyncratic shocks is what makes the covariate/idiosyncratic variance decomposition identifiable.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -12593,27 +12593,27 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>coped_sold_assets</t>
+          <t>shock_idiosyncratic</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Coped by selling or pawning assets</t>
+          <t>Suffered an IDIOSYNCRATIC shock</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>cope_3</t>
+          <t>any of shock_1 shock_2 shock_4 shock_8</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>1 if selling or pawning assets was among the responses. Kept as its own variable because the asset-smoothing test compares it directly against cutting consumption, and the two are no longer mutually exclusive.</t>
+          <t>1 if any of: illness or death of an earning member, crop or livestock loss, loss of business or assets, lost the work (codes 1, 2, 4, 8). These hit one household at a time.</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>Carter and Zimmerman 2000</t>
+          <t>Gunther and Harttgen 2009, via Fujii 2016 section 2.2</t>
         </is>
       </c>
     </row>
@@ -12623,27 +12623,27 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>coped_cut_consumption</t>
+          <t>coped_sold_assets</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Coped by cutting consumption</t>
+          <t>Coped by selling or pawning assets</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>cope_4</t>
+          <t>cope_3</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>1 if cutting consumption was among the responses. See coped_sold_assets -- a household doing BOTH, or cutting consumption precisely in order to avoid selling, is the case the single-answer item could not represent.</t>
+          <t>1 if selling or pawning assets was among the responses. Kept as its own variable because the asset-smoothing test compares it directly against cutting consumption, and the two are no longer mutually exclusive.</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>Carter and Zimmerman 2000; Zimmerman and Carter 2003</t>
+          <t>Carter and Zimmerman 2000</t>
         </is>
       </c>
     </row>
@@ -12653,27 +12653,27 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>mpi_mortality_dep</t>
+          <t>coped_cut_consumption</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>MPI: child or adolescent mortality</t>
+          <t>Coped by cutting consumption</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>child_death_5y == 1</t>
+          <t>cope_4</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>NITI: a child or adolescent under 18 died in the household in the last five years.</t>
+          <t>1 if cutting consumption was among the responses. See coped_sold_assets -- a household doing BOTH, or cutting consumption precisely in order to avoid selling, is the case the single-answer item could not represent.</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI (1/12)</t>
+          <t>Carter and Zimmerman 2000; Zimmerman and Carter 2003</t>
         </is>
       </c>
     </row>
@@ -12683,22 +12683,22 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>mpi_maternal_dep</t>
+          <t>mpi_mortality_dep</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>MPI: maternal health</t>
+          <t>MPI: child or adolescent mortality</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>birth_last_5y==1 &amp; (anc_4_visits!=1 | skilled_birth_attendant!=1)</t>
+          <t>child_death_5y == 1</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>NITI: a woman who gave birth in the last five years did not have at least four antenatal visits for the most recent birth, OR was not assisted by trained personnel at that birth. Households with no birth in the window are NOT deprived, per NITI's own treatment.</t>
+          <t>NITI: a child or adolescent under 18 died in the household in the last five years.</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -12713,27 +12713,27 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>mpi_schooling_dep</t>
+          <t>mpi_maternal_dep</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>MPI: years of schooling</t>
+          <t>MPI: maternal health</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>any_member_6yr_schooling == 0</t>
+          <t>birth_last_5y==1 &amp; (anc_4_visits!=1 | skilled_birth_attendant!=1)</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>NITI: not even one household member aged 10 or older has completed six years of schooling.</t>
+          <t>NITI: a woman who gave birth in the last five years did not have at least four antenatal visits for the most recent birth, OR was not assisted by trained personnel at that birth. Households with no birth in the window are NOT deprived, per NITI's own treatment.</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI (1/6)</t>
+          <t>NITI Aayog National MPI (1/12)</t>
         </is>
       </c>
     </row>
@@ -12743,22 +12743,22 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>mpi_attendance_dep</t>
+          <t>mpi_schooling_dep</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>MPI: school attendance</t>
+          <t>MPI: years of schooling</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>n_children_out_school &gt; 0 if n_children_6_14 &gt; 0</t>
+          <t>any_member_6yr_schooling == 0</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>NITI: any school-aged child is not attending school up to the age at which they would complete class 8. Not deprived where the household has no child in that range.</t>
+          <t>NITI: not even one household member aged 10 or older has completed six years of schooling.</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -12773,27 +12773,27 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>mpi_housing_dep</t>
+          <t>mpi_attendance_dep</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>MPI: housing</t>
+          <t>MPI: school attendance</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>floor_material==1 | roof_material==1 | wall_material==1</t>
+          <t>n_children_out_school &gt; 0 if n_children_6_14 &gt; 0</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>NITI: the floor is natural material, OR the roof OR the wall is rudimentary. All three limbs are now collected; the wall limb was previously missing entirely.</t>
+          <t>NITI: any school-aged child is not attending school up to the age at which they would complete class 8. Not deprived where the household has no child in that range.</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI (1/21)</t>
+          <t>NITI Aayog National MPI (1/6)</t>
         </is>
       </c>
     </row>
@@ -12803,22 +12803,22 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>mpi_sanitation_dep</t>
+          <t>mpi_housing_dep</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>MPI: sanitation</t>
+          <t>MPI: housing</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>inlist(toilet_type,1,2,3)</t>
+          <t>floor_material==1 | roof_material==1 | wall_material==1</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>NITI: unimproved or no facility, OR improved but shared with other households.</t>
+          <t>NITI: the floor is natural material, OR the roof OR the wall is rudimentary. All three limbs are now collected; the wall limb was previously missing entirely.</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
@@ -12833,22 +12833,22 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>mpi_electricity_dep</t>
+          <t>mpi_sanitation_dep</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>MPI: electricity</t>
+          <t>MPI: sanitation</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>electricity == 0</t>
+          <t>inlist(toilet_type,1,2,3)</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>NITI: the household has no electricity.</t>
+          <t>NITI: unimproved or no facility, OR improved but shared with other households.</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
@@ -12863,22 +12863,22 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>mpi_bank_dep</t>
+          <t>mpi_electricity_dep</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>MPI: bank account</t>
+          <t>MPI: electricity</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>has_bank_account == 0</t>
+          <t>electricity == 0</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>NITI: no household member has a bank account or a post office account.</t>
+          <t>NITI: the household has no electricity.</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
@@ -12893,27 +12893,27 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>mpi_score</t>
+          <t>mpi_bank_dep</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>MPI deprivation score (10 of NITI's 12 indicators, reweighted)</t>
+          <t>MPI: bank account</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>(1/12*mortality + 1/12*maternal + 1/6*schooling + 1/6*attendance + 1/21*(fuel+sanitation+water+electricity+housing+assets+bank)) / (1 - 1/6)</t>
+          <t>has_bank_account == 0</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>Weighted sum of the ten collected indicators. Nutrition (1/6) cannot be collected without anthropometry, so the remaining weights are scaled up proportionally to sum to 1. REPORT THIS AS AN ADAPTATION, never as the National MPI -- and state which indicator is absent.</t>
+          <t>NITI: no household member has a bank account or a post office account.</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI structure, nutrition omitted</t>
+          <t>NITI Aayog National MPI (1/21)</t>
         </is>
       </c>
     </row>
@@ -12923,27 +12923,27 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>mpi_poor</t>
+          <t>mpi_score</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>MPI-poor (deprivation score at or above 1/3)</t>
+          <t>MPI deprivation score (10 of NITI's 12 indicators, reweighted)</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>mpi_score &gt;= 1/3</t>
+          <t>(1/12*mortality + 1/12*maternal + 1/6*schooling + 1/6*attendance + 1/21*(fuel+sanitation+water+electricity+housing+assets+bank)) / (1 - 1/6)</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>Alkire-Foster identification at the standard k = 33.3 percent cutoff.</t>
+          <t>Weighted sum of the ten collected indicators. Nutrition (1/6) cannot be collected without anthropometry, so the remaining weights are scaled up proportionally to sum to 1. REPORT THIS AS AN ADAPTATION, never as the National MPI -- and state which indicator is absent.</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>Alkire and Foster 2011; NITI Aayog National MPI</t>
+          <t>NITI Aayog National MPI structure, nutrition omitted</t>
         </is>
       </c>
     </row>
@@ -12953,27 +12953,27 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>rcsi_yatra_wk</t>
+          <t>mpi_poor</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>rCSI, Yatra-season usual week</t>
+          <t>MPI-poor (deprivation score at or above 1/3)</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>cope_less_pref_food_yatra_wk + 2*cope_borrow_food_yatra_wk + cope_reduce_meals_yatra_wk + cope_reduce_portion_yatra_wk + 3*cope_restrict_adult_yatra_wk</t>
+          <t>mpi_score &gt;= 1/3</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>Weighted sum of the five Yatra-season food-coping day-counts, standard WFP weights (1,2,1,1,3).</t>
+          <t>Alkire-Foster identification at the standard k = 33.3 percent cutoff.</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>WFP reduced Coping Strategy Index</t>
+          <t>Alkire and Foster 2011; NITI Aayog National MPI</t>
         </is>
       </c>
     </row>
@@ -12983,22 +12983,22 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>rcsi_offseason_wk</t>
+          <t>rcsi_yatra_wk</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>rCSI, off-season usual week</t>
+          <t>rCSI, Yatra-season usual week</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>cope_less_pref_food_offseason_wk + 2*cope_borrow_food_offseason_wk + cope_reduce_meals_offseason_wk + cope_reduce_portion_offseason_wk + 3*cope_restrict_adult_offseason_wk</t>
+          <t>cope_less_pref_food_yatra_wk + 2*cope_borrow_food_yatra_wk + cope_reduce_meals_yatra_wk + cope_reduce_portion_yatra_wk + 3*cope_restrict_adult_yatra_wk</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>Weighted sum of the five off-season food-coping day-counts, standard WFP weights (1,2,1,1,3).</t>
+          <t>Weighted sum of the five Yatra-season food-coping day-counts, standard WFP weights (1,2,1,1,3).</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
@@ -13013,27 +13013,27 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>rcsi_score</t>
+          <t>rcsi_offseason_wk</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Reduced Coping Strategy Index (rCSI), annual average</t>
+          <t>rCSI, off-season usual week</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>(yatra_months*rcsi_yatra_wk + (12-yatra_months)*rcsi_offseason_wk)/12</t>
+          <t>cope_less_pref_food_offseason_wk + 2*cope_borrow_food_offseason_wk + cope_reduce_meals_offseason_wk + cope_reduce_portion_offseason_wk + 3*cope_restrict_adult_offseason_wk</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>Yatra-season and off-season weekly rCSI, weighted by the length of each season from the work calendar -- the same weighting already used for income and consumption.</t>
+          <t>Weighted sum of the five off-season food-coping day-counts, standard WFP weights (1,2,1,1,3).</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>WFP reduced Coping Strategy Index; season-weighting as in Module E/C</t>
+          <t>WFP reduced Coping Strategy Index</t>
         </is>
       </c>
     </row>
@@ -13043,27 +13043,27 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>food_coping_deprived</t>
+          <t>rcsi_score</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Food-coping deprived (rCSI above 20)</t>
+          <t>Reduced Coping Strategy Index (rCSI), annual average</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>rcsi_score &gt; 20</t>
+          <t>(yatra_months*rcsi_yatra_wk + (12-yatra_months)*rcsi_offseason_wk)/12</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>1 if annual-average rCSI exceeds 20, the cutoff used by Lyons et al. 2023 (from VASyR).</t>
+          <t>Yatra-season and off-season weekly rCSI, weighted by the length of each season from the work calendar -- the same weighting already used for income and consumption.</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>Lyons et al. 2023 Table 2 indicator 3 cutoff</t>
+          <t>WFP reduced Coping Strategy Index; season-weighting as in Module E/C</t>
         </is>
       </c>
     </row>
@@ -13073,27 +13073,27 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>hours_week_yatra</t>
+          <t>food_coping_deprived</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Hours worked per week in the Yatra season</t>
+          <t>Food-coping deprived (rCSI above 20)</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>hours_day_yatra * days_week_yatra</t>
+          <t>rcsi_score &gt; 20</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>Hours per day times days per week.</t>
+          <t>1 if annual-average rCSI exceeds 20, the cutoff used by Lyons et al. 2023 (from VASyR).</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026 Q13 (decomposed into hours/day x days/week when asked, for ease of recall)</t>
+          <t>Lyons et al. 2023 Table 2 indicator 3 cutoff</t>
         </is>
       </c>
     </row>
@@ -13103,27 +13103,27 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>hours_week_offseason</t>
+          <t>hours_week_yatra</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Hours worked per week outside the Yatra season</t>
+          <t>Hours worked per week in the Yatra season</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>hours_day_offseason * days_week_offseason</t>
+          <t>hours_day_yatra * days_week_yatra</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>Hours per day times days per week, off-season. Missing for respondents with no off-season paid work at all.</t>
+          <t>Hours per day times days per week.</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026 Q13</t>
+          <t>Apablaza et al. 2026 Q13 (decomposed into hours/day x days/week when asked, for ease of recall)</t>
         </is>
       </c>
     </row>
@@ -13133,27 +13133,27 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>hours_week_annual</t>
+          <t>hours_week_offseason</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>Average weekly hours across the months actually worked</t>
+          <t>Hours worked per week outside the Yatra season</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>(yatra_months*hours_week_yatra + offseason_months_worked*hours_week_offseason) / (yatra_months + offseason_months_worked)</t>
+          <t>hours_day_offseason * days_week_offseason</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>Yatra-season and off-season weekly hours, weighted by how many months of each the calendar records. Averaged over WORKED months only, so idle months do not drag the figure to zero -- idleness is measured by months_no_work, and counting it here too would penalise it twice.</t>
+          <t>Hours per day times days per week, off-season. Missing for respondents with no off-season paid work at all.</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026 Q13, weighted onto the work calendar</t>
+          <t>Apablaza et al. 2026 Q13</t>
         </is>
       </c>
     </row>
@@ -13163,27 +13163,27 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>work_income_pm</t>
+          <t>hours_week_annual</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Average monthly work income over the year (Rs)</t>
+          <t>Average weekly hours across the months actually worked</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>(yatra_income + non_yatra_income)/12</t>
+          <t>(yatra_months*hours_week_yatra + offseason_months_worked*hours_week_offseason) / (yatra_months + offseason_months_worked)</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>(Yatra income + other work income) divided by 12.</t>
+          <t>Yatra-season and off-season weekly hours, weighted by how many months of each the calendar records. Averaged over WORKED months only, so idle months do not drag the figure to zero -- idleness is measured by months_no_work, and counting it here too would penalise it twice.</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026 Q14</t>
+          <t>Apablaza et al. 2026 Q13, weighted onto the work calendar</t>
         </is>
       </c>
     </row>
@@ -13193,27 +13193,27 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>emp_dep_access</t>
+          <t>work_income_pm</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>Employment deprivation: access</t>
+          <t>Average monthly work income over the year (Rs)</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>(months_no_work&gt;6 &amp; weeks_looked_for_work&gt;0) | (wants_more_work==1 &amp; (hours_week_yatra&lt;20 | hours_week_offseason&lt;20))</t>
+          <t>(yatra_income + non_yatra_income)/12</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>1 if idle more than 6 months and spent any weeks looking for work, or wants more work while working under 20 hours a week in EITHER season. The under-20 limb previously tested Yatra-season hours only, where this workforce runs 60-90 hours a week, so it could never fire and the indicator collapsed onto its other limb.</t>
+          <t>(Yatra income + other work income) divided by 12.</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Table 3 (five-domain core; thresholds from the table, inputs from Appendix 2): unemployed &gt;6 months OR &lt;20 h/week involuntary</t>
+          <t>Apablaza et al. 2026 Q14</t>
         </is>
       </c>
     </row>
@@ -13223,27 +13223,27 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>emp_dep_comp</t>
+          <t>emp_dep_access</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Employment deprivation: compensation</t>
+          <t>Employment deprivation: access</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>work_income_pm &lt; 0.67 * median(work_income_pm)</t>
+          <t>(months_no_work&gt;6 &amp; weeks_looked_for_work&gt;0) | (wants_more_work==1 &amp; (hours_week_yatra&lt;20 | hours_week_offseason&lt;20))</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>1 if average monthly work income is below 67 percent of the sample median (the fallback threshold in Table 3).</t>
+          <t>1 if idle more than 6 months and spent any weeks looking for work, or wants more work while working under 20 hours a week in EITHER season. The under-20 limb previously tested Yatra-season hours only, where this workforce runs 60-90 hours a week, so it could never fire and the indicator collapsed onto its other limb.</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Table 3 (five-domain core; thresholds from the table, inputs from Appendix 2): fallback &lt;67% of median; the PPP-line version needs a checked conversion factor</t>
+          <t>Apablaza et al. 2026, Table 3 (five-domain core; thresholds from the table, inputs from Appendix 2): unemployed &gt;6 months OR &lt;20 h/week involuntary</t>
         </is>
       </c>
     </row>
@@ -13253,27 +13253,27 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>emp_dep_sec</t>
+          <t>emp_dep_comp</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>Employment deprivation: security</t>
+          <t>Employment deprivation: compensation</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>wage: contract_status != 1; self-employed: workplace_registered == 0</t>
+          <t>work_income_pm &lt; 0.67 * median(work_income_pm)</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>1 if a wage worker has no signed contract, or a self-employed worker's business is not registered.</t>
+          <t>1 if average monthly work income is below 67 percent of the sample median (the fallback threshold in Table 3).</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Table 3 (five-domain core; thresholds from the table, inputs from Appendix 2): no written contract (registration for the self-employed)</t>
+          <t>Apablaza et al. 2026, Table 3 (five-domain core; thresholds from the table, inputs from Appendix 2): fallback &lt;67% of median; the PPP-line version needs a checked conversion factor</t>
         </is>
       </c>
     </row>
@@ -13283,27 +13283,27 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>emp_dep_stab</t>
+          <t>emp_dep_sec</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Employment deprivation: stability</t>
+          <t>Employment deprivation: security</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>wage (employment_type 3/4): years_in_yatra_work &lt; 1; self-employed (1/2): &lt; 2; OR job_permanence == 3</t>
+          <t>wage: contract_status != 1; self-employed: workplace_registered == 0</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>Apablaza Table 3 sets TWO tenure thresholds -- wage workers deprived under 6 months, self-employed under 12 months -- where this file previously applied a single under-1-year rule to everyone, which marked wage workers with 6 to 12 months of tenure as deprived when Table 3 would not. Tenure here is counted in Yatra SEASONS, and one season is roughly six months of work, so the two thresholds map cleanly onto under 1 season for wage workers and under 2 for the self-employed. The casual-job limb is an ADDITION to Table 3, whose fallback (temporary/casual) is meant for use only when tenure is unavailable; it is kept because occasional work is a real instability here, but note it covers code 3 only -- code 2 (seasonal) would mark almost this entire sample deprived and would measure the season, not the job.</t>
+          <t>1 if a wage worker has no signed contract, or a self-employed worker's business is not registered.</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Table 3 (five-domain core; thresholds from the table, inputs from Appendix 2): tenure, wage &lt;6mo and self-employed &lt;12mo; casual limb is a project addition</t>
+          <t>Apablaza et al. 2026, Table 3 (five-domain core; thresholds from the table, inputs from Appendix 2): no written contract (registration for the self-employed)</t>
         </is>
       </c>
     </row>
@@ -13313,27 +13313,27 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>emp_dep_cond</t>
+          <t>emp_dep_stab</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>Employment deprivation: working conditions</t>
+          <t>Employment deprivation: stability</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>workplace_injury_12m==1 | (work_health_ins==3 &amp; pension_contrib==3)</t>
+          <t>wage (employment_type 3/4): years_in_yatra_work &lt; 1; self-employed (1/2): &lt; 2; OR job_permanence == 3</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>1 if someone was injured or killed at the workplace in the last 12 months, or the worker has neither work health insurance nor a pension.</t>
+          <t>Apablaza Table 3 sets TWO tenure thresholds -- wage workers deprived under 6 months, self-employed under 12 months -- where this file previously applied a single under-1-year rule to everyone, which marked wage workers with 6 to 12 months of tenure as deprived when Table 3 would not. Tenure here is counted in Yatra SEASONS, and one season is roughly six months of work, so the two thresholds map cleanly onto under 1 season for wage workers and under 2 for the self-employed. The casual-job limb is an ADDITION to Table 3, whose fallback (temporary/casual) is meant for use only when tenure is unavailable; it is kept because occasional work is a real instability here, but note it covers code 3 only -- code 2 (seasonal) would mark almost this entire sample deprived and would measure the season, not the job.</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Table 3 (five-domain core; thresholds from the table, inputs from Appendix 2): hazards OR (no health insurance AND no pension); injury is the hazard evidence in Appendix 2</t>
+          <t>Apablaza et al. 2026, Table 3 (five-domain core; thresholds from the table, inputs from Appendix 2): tenure, wage &lt;6mo and self-employed &lt;12mo; casual limb is a project addition</t>
         </is>
       </c>
     </row>
@@ -13343,27 +13343,27 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>emp_dep_count</t>
+          <t>emp_dep_cond</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Employment deprivations (count of 5)</t>
+          <t>Employment deprivation: working conditions</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>sum of the five emp_dep_ indicators</t>
+          <t>workplace_injury_12m==1 | (work_health_ins==3 &amp; pension_contrib==3)</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>Number of the five employment indicators in which the worker is deprived.</t>
+          <t>1 if someone was injured or killed at the workplace in the last 12 months, or the worker has neither work health insurance nor a pension.</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Table 3 (five-domain core; thresholds from the table, inputs from Appendix 2)</t>
+          <t>Apablaza et al. 2026, Table 3 (five-domain core; thresholds from the table, inputs from Appendix 2): hazards OR (no health insurance AND no pension); injury is the hazard evidence in Appendix 2</t>
         </is>
       </c>
     </row>
@@ -13373,22 +13373,22 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>emp_dep_score</t>
+          <t>emp_dep_count</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>Employment deprivation score (equal weights, 0-1)</t>
+          <t>Employment deprivations (count of 5)</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>emp_dep_count / 5</t>
+          <t>sum of the five emp_dep_ indicators</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>Count divided by 5.</t>
+          <t>Number of the five employment indicators in which the worker is deprived.</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
@@ -13403,27 +13403,27 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>emp_poor_k2</t>
+          <t>emp_dep_score</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Employment-poor: deprived in 2 or more of 5</t>
+          <t>Employment deprivation score (equal weights, 0-1)</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>emp_dep_count &gt;= 2</t>
+          <t>emp_dep_count / 5</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>1 if two or more indicators; k = 2 of 5 is the project's choice, to be varied in robustness.</t>
+          <t>Count divided by 5.</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Table 3 (five-domain core; thresholds from the table, inputs from Appendix 2); cut-off is the project's choice</t>
+          <t>Apablaza et al. 2026, Table 3 (five-domain core; thresholds from the table, inputs from Appendix 2)</t>
         </is>
       </c>
     </row>
@@ -13433,27 +13433,27 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>tk_regular_n</t>
+          <t>emp_poor_k2</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>Number of the 12 tasks done regularly</t>
+          <t>Employment-poor: deprived in 2 or more of 5</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>count of tk_* == 1</t>
+          <t>emp_dep_count &gt;= 2</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>Count of task answers equal to 1.</t>
+          <t>1 if two or more indicators; k = 2 of 5 is the project's choice, to be varied in robustness.</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>Constructed</t>
+          <t>Apablaza et al. 2026, Table 3 (five-domain core; thresholds from the table, inputs from Appendix 2); cut-off is the project's choice</t>
         </is>
       </c>
     </row>
@@ -13463,22 +13463,22 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>tk_prior_n</t>
+          <t>tk_regular_n</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Number of the 12 tasks done before elsewhere</t>
+          <t>Number of the 12 tasks done regularly</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>count of tk_* == 2</t>
+          <t>count of tk_* == 1</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>Count of task answers equal to 2.</t>
+          <t>Count of task answers equal to 1.</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
@@ -13493,27 +13493,27 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>other_act_1</t>
+          <t>tk_prior_n</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>Other activity: Pony/mule worker (works the animals, does not own them)</t>
+          <t>Number of the 12 tasks done before elsewhere</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>other_activity_types contains 1</t>
+          <t>count of tk_* == 2</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>1 if 'Pony/mule worker (works the animals, does not own them)' was ticked in the check-all list of other paid activities.</t>
+          <t>Count of task answers equal to 2.</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>Split from the select_multiple export</t>
+          <t>Constructed</t>
         </is>
       </c>
     </row>
@@ -13523,22 +13523,22 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>other_act_2</t>
+          <t>other_act_1</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>Other activity: Pony/mule owner (owns the animals)</t>
+          <t>Other activity: Pony/mule worker (works the animals, does not own them)</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>other_activity_types contains 2</t>
+          <t>other_activity_types contains 1</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>1 if 'Pony/mule owner (owns the animals)' was ticked in the check-all list of other paid activities.</t>
+          <t>1 if 'Pony/mule worker (works the animals, does not own them)' was ticked in the check-all list of other paid activities.</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr">
@@ -13553,22 +13553,22 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>other_act_3</t>
+          <t>other_act_2</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>Other activity: Porter (carries on own back/shoulders - goods, luggage, or a per</t>
+          <t>Other activity: Pony/mule owner (owns the animals)</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>other_activity_types contains 3</t>
+          <t>other_activity_types contains 2</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>1 if 'Porter (carries on own back/shoulders - goods, luggage, or a person in a kandi)' was ticked in the check-all list of other paid activities.</t>
+          <t>1 if 'Pony/mule owner (owns the animals)' was ticked in the check-all list of other paid activities.</t>
         </is>
       </c>
       <c r="F113" s="2" t="inlineStr">
@@ -13583,22 +13583,22 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>other_act_4</t>
+          <t>other_act_3</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>Other activity: Palki / dandi bearer (carries a person on a palanquin, as part o</t>
+          <t>Other activity: Porter (carries on own back/shoulders - goods, luggage, or a per</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>other_activity_types contains 4</t>
+          <t>other_activity_types contains 3</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>1 if 'Palki / dandi bearer (carries a person on a palanquin, as part of a team)' was ticked in the check-all list of other paid activities.</t>
+          <t>1 if 'Porter (carries on own back/shoulders - goods, luggage, or a person in a kandi)' was ticked in the check-all list of other paid activities.</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr">
@@ -13613,22 +13613,22 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>other_act_5</t>
+          <t>other_act_4</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>Other activity: Dhaba, tea stall or food stall WORKER (prepared food or tea)</t>
+          <t>Other activity: Palki / dandi bearer (carries a person on a palanquin, as part o</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>other_activity_types contains 5</t>
+          <t>other_activity_types contains 4</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>1 if 'Dhaba, tea stall or food stall WORKER (prepared food or tea)' was ticked in the check-all list of other paid activities.</t>
+          <t>1 if 'Palki / dandi bearer (carries a person on a palanquin, as part of a team)' was ticked in the check-all list of other paid activities.</t>
         </is>
       </c>
       <c r="F115" s="2" t="inlineStr">
@@ -13643,22 +13643,22 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>other_act_6</t>
+          <t>other_act_5</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>Other activity: Dhaba, tea stall or food stall OWNER (prepared food or tea)</t>
+          <t>Other activity: Dhaba, tea stall or food stall WORKER (prepared food or tea)</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>other_activity_types contains 6</t>
+          <t>other_activity_types contains 5</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>1 if 'Dhaba, tea stall or food stall OWNER (prepared food or tea)' was ticked in the check-all list of other paid activities.</t>
+          <t>1 if 'Dhaba, tea stall or food stall WORKER (prepared food or tea)' was ticked in the check-all list of other paid activities.</t>
         </is>
       </c>
       <c r="F116" s="2" t="inlineStr">
@@ -13673,22 +13673,22 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>other_act_7</t>
+          <t>other_act_6</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>Other activity: Shop WORKER (goods: prasad, puja items, clothes, general store)</t>
+          <t>Other activity: Dhaba, tea stall or food stall OWNER (prepared food or tea)</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>other_activity_types contains 7</t>
+          <t>other_activity_types contains 6</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>1 if 'Shop WORKER (goods: prasad, puja items, clothes, general store)' was ticked in the check-all list of other paid activities.</t>
+          <t>1 if 'Dhaba, tea stall or food stall OWNER (prepared food or tea)' was ticked in the check-all list of other paid activities.</t>
         </is>
       </c>
       <c r="F117" s="2" t="inlineStr">
@@ -13703,22 +13703,22 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>other_act_8</t>
+          <t>other_act_7</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>Other activity: Shop OWNER (goods, not prepared food)</t>
+          <t>Other activity: Shop WORKER (goods: prasad, puja items, clothes, general store)</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>other_activity_types contains 8</t>
+          <t>other_activity_types contains 7</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>1 if 'Shop OWNER (goods, not prepared food)' was ticked in the check-all list of other paid activities.</t>
+          <t>1 if 'Shop WORKER (goods: prasad, puja items, clothes, general store)' was ticked in the check-all list of other paid activities.</t>
         </is>
       </c>
       <c r="F118" s="2" t="inlineStr">
@@ -13733,22 +13733,22 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>other_act_9</t>
+          <t>other_act_8</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>Other activity: Hotel / lodge WORKER</t>
+          <t>Other activity: Shop OWNER (goods, not prepared food)</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>other_activity_types contains 9</t>
+          <t>other_activity_types contains 8</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>1 if 'Hotel / lodge WORKER' was ticked in the check-all list of other paid activities.</t>
+          <t>1 if 'Shop OWNER (goods, not prepared food)' was ticked in the check-all list of other paid activities.</t>
         </is>
       </c>
       <c r="F119" s="2" t="inlineStr">
@@ -13763,22 +13763,22 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>other_act_10</t>
+          <t>other_act_9</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>Other activity: Hotel / lodge OWNER</t>
+          <t>Other activity: Hotel / lodge WORKER</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>other_activity_types contains 10</t>
+          <t>other_activity_types contains 9</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>1 if 'Hotel / lodge OWNER' was ticked in the check-all list of other paid activities.</t>
+          <t>1 if 'Hotel / lodge WORKER' was ticked in the check-all list of other paid activities.</t>
         </is>
       </c>
       <c r="F120" s="2" t="inlineStr">
@@ -13793,22 +13793,22 @@
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>other_act_11</t>
+          <t>other_act_10</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>Other activity: Driver (any motor vehicle)</t>
+          <t>Other activity: Hotel / lodge OWNER</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>other_activity_types contains 11</t>
+          <t>other_activity_types contains 10</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>1 if 'Driver (any motor vehicle)' was ticked in the check-all list of other paid activities.</t>
+          <t>1 if 'Hotel / lodge OWNER' was ticked in the check-all list of other paid activities.</t>
         </is>
       </c>
       <c r="F121" s="2" t="inlineStr">
@@ -13823,22 +13823,22 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>other_act_12</t>
+          <t>other_act_11</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>Other activity: Guide</t>
+          <t>Other activity: Driver (any motor vehicle)</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>other_activity_types contains 12</t>
+          <t>other_activity_types contains 11</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>1 if 'Guide' was ticked in the check-all list of other paid activities.</t>
+          <t>1 if 'Driver (any motor vehicle)' was ticked in the check-all list of other paid activities.</t>
         </is>
       </c>
       <c r="F122" s="2" t="inlineStr">
@@ -13853,22 +13853,22 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>other_act_13</t>
+          <t>other_act_12</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>Other activity: Wage labourer (construction, loading, odd jobs)</t>
+          <t>Other activity: Guide</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>other_activity_types contains 13</t>
+          <t>other_activity_types contains 12</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>1 if 'Wage labourer (construction, loading, odd jobs)' was ticked in the check-all list of other paid activities.</t>
+          <t>1 if 'Guide' was ticked in the check-all list of other paid activities.</t>
         </is>
       </c>
       <c r="F123" s="2" t="inlineStr">
@@ -13883,22 +13883,22 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>other_act_14</t>
+          <t>other_act_13</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>Other activity: Other</t>
+          <t>Other activity: Wage labourer (construction, loading, odd jobs)</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>other_activity_types contains 14</t>
+          <t>other_activity_types contains 13</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>1 if 'Other' was ticked in the check-all list of other paid activities.</t>
+          <t>1 if 'Wage labourer (construction, loading, odd jobs)' was ticked in the check-all list of other paid activities.</t>
         </is>
       </c>
       <c r="F124" s="2" t="inlineStr">
@@ -13913,27 +13913,27 @@
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>n_other_act_checked</t>
+          <t>other_act_14</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>Number of other activities actually ticked</t>
+          <t>Other activity: Other</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>sum of other_act_1..13</t>
+          <t>other_activity_types contains 14</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>Count of the boxes ticked in the check-all list. Compared against the respondent's own count (n_other_activities); a mismatch is a data-quality flag, not a silent loss.</t>
+          <t>1 if 'Other' was ticked in the check-all list of other paid activities.</t>
         </is>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>Constructed</t>
+          <t>Split from the select_multiple export</t>
         </is>
       </c>
     </row>
@@ -13943,22 +13943,22 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>other_act_mismatch</t>
+          <t>n_other_act_checked</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>Ticked count differs from the stated count</t>
+          <t>Number of other activities actually ticked</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>n_other_act_checked != n_other_activities</t>
+          <t>sum of other_act_1..13</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>1 if the number of activities ticked does not equal the number the respondent said they had. Expected to be small; if it is not, the item needs rewording before scale-up.</t>
+          <t>Count of the boxes ticked in the check-all list. Compared against the respondent's own count (n_other_activities); a mismatch is a data-quality flag, not a silent loss.</t>
         </is>
       </c>
       <c r="F126" s="2" t="inlineStr">
@@ -13973,27 +13973,27 @@
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>best_alt_occupation</t>
+          <t>other_act_mismatch</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>Closest alternative occupation in task space</t>
+          <t>Ticked count differs from the stated count</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>argmax over j != own occupation of cosine(worker profile, q_j)</t>
+          <t>n_other_act_checked != n_other_activities</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>Of the 13 occupations, the one (other than the respondent's own) whose task profile is closest to the respondent's. Worker's own task profile uses codes 1 AND 2 (does it now, or has done it before elsewhere) -- prior capability outside the current job is exactly what a transfer question is about. Destination profiles are the occupation-level share of workers doing each task (Gathmann and Schonberg's q_oj).</t>
+          <t>1 if the number of activities ticked does not equal the number the respondent said they had. Expected to be small; if it is not, the item needs rewording before scale-up.</t>
         </is>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>Gathmann and Schonberg 2010</t>
+          <t>Constructed</t>
         </is>
       </c>
     </row>
@@ -14003,27 +14003,27 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>task_cover_best</t>
+          <t>best_alt_occupation</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>Share of the closest alternative's tasks the worker already does</t>
+          <t>Closest alternative occupation in task space</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>sum(q_best * worker) / sum(q_best)</t>
+          <t>argmax over j != own occupation of cosine(worker profile, q_j)</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>Coverage: of the tasks that alternative occupation requires, the share this worker can already perform. Ormiston's t_ji direction -- can the worker step in?</t>
+          <t>Of the 13 occupations, the one (other than the respondent's own) whose task profile is closest to the respondent's. Worker's own task profile uses codes 1 AND 2 (does it now, or has done it before elsewhere) -- prior capability outside the current job is exactly what a transfer question is about. Destination profiles are the occupation-level share of workers doing each task (Gathmann and Schonberg's q_oj).</t>
         </is>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>Nawakitphaitoon and Ormiston 2016 (Ormiston 2014 transferability)</t>
+          <t>Gathmann and Schonberg 2010</t>
         </is>
       </c>
     </row>
@@ -14033,22 +14033,22 @@
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>task_retain_best</t>
+          <t>task_cover_best</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>Share of the worker's own tasks the closest alternative uses</t>
+          <t>Share of the closest alternative's tasks the worker already does</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>sum(q_best * worker) / sum(worker)</t>
+          <t>sum(q_best * worker) / sum(q_best)</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>Retention: of the tasks this worker can perform, the share that alternative occupation would actually use. Ormiston's t_ij direction -- how much of their skill survives the move?</t>
+          <t>Coverage: of the tasks that alternative occupation requires, the share this worker can already perform. Ormiston's t_ji direction -- can the worker step in?</t>
         </is>
       </c>
       <c r="F129" s="2" t="inlineStr">
@@ -14063,32 +14063,62 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
+          <t>task_retain_best</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>Share of the worker's own tasks the closest alternative uses</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>sum(q_best * worker) / sum(worker)</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>Retention: of the tasks this worker can perform, the share that alternative occupation would actually use. Ormiston's t_ij direction -- how much of their skill survives the move?</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>Nawakitphaitoon and Ormiston 2016 (Ormiston 2014 transferability)</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>130</v>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
           <t>skill_move_type</t>
         </is>
       </c>
-      <c r="C130" s="2" t="inlineStr">
+      <c r="C131" s="2" t="inlineStr">
         <is>
           <t>Ex-ante type of skill move required</t>
         </is>
       </c>
-      <c r="D130" s="2" t="inlineStr">
+      <c r="D131" s="2" t="inlineStr">
         <is>
           <t>from (task_cover_best, task_retain_best), each split at 0.5</t>
         </is>
       </c>
-      <c r="E130" s="2" t="inlineStr">
+      <c r="E131" s="2" t="inlineStr">
         <is>
           <t>Direction of the move implied by the coverage/retention pair, both split at 0.5: high-high lateral (move needs little retraining); low coverage but high retention means the destination needs skills the worker lacks while their own still count, i.e. UPSKILLING; high coverage but low retention means the worker has more than the destination uses and much of it goes idle, i.e. DOWNSKILLING; low-low means the skill sets barely overlap, i.e. RESKILLING. Worker's own task profile uses codes 1 AND 2 (does it now, or has done it before elsewhere) -- prior capability outside the current job is exactly what a transfer question is about. Destination profiles are the occupation-level share of workers doing each task (Gathmann and Schonberg's q_oj).</t>
         </is>
       </c>
-      <c r="F130" s="2" t="inlineStr">
+      <c r="F131" s="2" t="inlineStr">
         <is>
           <t>Nawakitphaitoon and Ormiston 2016, section 2.2 (asymmetry of T_ij read as direction)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F130"/>
+  <autoFilter ref="A1:F131"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/replication/final_instrument/questionnaire/Question_register.xlsx
+++ b/replication/final_instrument/questionnaire/Question_register.xlsx
@@ -13,9 +13,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Modules" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Questions'!$A$1:$J$212</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Questions'!$A$1:$J$211</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Constructed variables'!$A$1:$F$131</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Literature'!$A$1:$C$133</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Literature'!$A$1:$C$132</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Modules'!$A$1:$C$15</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J212"/>
+  <dimension ref="A1:J211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -8042,29 +8042,25 @@
       </c>
       <c r="D167" s="2" t="inlineStr">
         <is>
-          <t>shock_worst</t>
+          <t>shock_loss_amount</t>
         </is>
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>select one</t>
+          <t>amount (Rs)</t>
         </is>
       </c>
       <c r="F167" s="2" t="inlineStr">
         <is>
-          <t>Of those, which one was hardest for your household?</t>
+          <t>Thinking of whichever of those hit you hardest -- about how much did your household lose in earnings, or have to spend because of it? (Rs)</t>
         </is>
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>इनमें से आपके घर के लिए सबसे मुश्किल कौन सा रहा?</t>
-        </is>
-      </c>
-      <c r="H167" s="2" t="inlineStr">
-        <is>
-          <t>9 Nothing of this kind happened | 1 Serious illness or death of an earning member | 2 Crop failure or livestock loss | 3 Damage from a natural disaster (flood, landslide, fire) | 4 Loss of business, goods or assets | 5 Road or bridge blocked, route closed | 6 Yatra stopped early or badly disrupted | 7 Sharp fall in customers or prices | 8 Lost the work or the work stopped</t>
-        </is>
-      </c>
+          <t>इनमें से जो सबसे भारी पड़ा — उसकी वजह से आपके घर की कितनी कमाई गई, या कितना ख़र्च करना पड़ा? (रुपये)</t>
+        </is>
+      </c>
+      <c r="H167" s="2" t="inlineStr"/>
       <c r="I167" s="2" t="inlineStr">
         <is>
           <t>Ask only if distress_event_last365d names a real shock (not code 9, nothing happened)</t>
@@ -8072,7 +8068,7 @@
       </c>
       <c r="J167" s="2" t="inlineStr">
         <is>
-          <t>Project design (anchors the magnitude and timing pair)</t>
+          <t>Ligon and Schechter 2003; Dercon and Krishnan 2000 (VER needs shock magnitude, not only incidence)</t>
         </is>
       </c>
     </row>
@@ -8092,25 +8088,29 @@
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>shock_loss_amount</t>
+          <t>shock_month</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>amount (Rs)</t>
+          <t>select one</t>
         </is>
       </c>
       <c r="F168" s="2" t="inlineStr">
         <is>
-          <t>Because of that, about how much did your household lose in earnings, or have to spend? (Rs)</t>
+          <t>And in which month did that one happen?</t>
         </is>
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>उसकी वजह से आपके घर की कितनी कमाई गई, या कितना ख़र्च करना पड़ा? (रुपये)</t>
-        </is>
-      </c>
-      <c r="H168" s="2" t="inlineStr"/>
+          <t>और वह किस महीने हुआ था?</t>
+        </is>
+      </c>
+      <c r="H168" s="2" t="inlineStr">
+        <is>
+          <t>1 January | 2 February | 3 March | 4 April | 5 May | 6 June | 7 July | 8 August | 9 September | 10 October | 11 November | 12 December</t>
+        </is>
+      </c>
       <c r="I168" s="2" t="inlineStr">
         <is>
           <t>Ask only if distress_event_last365d names a real shock (not code 9, nothing happened)</t>
@@ -8118,7 +8118,7 @@
       </c>
       <c r="J168" s="2" t="inlineStr">
         <is>
-          <t>Ligon and Schechter 2003; Dercon and Krishnan 2000 (VER needs shock magnitude, not only incidence)</t>
+          <t>Dercon and Krishnan 2000 (seasonal timing of shocks); project design</t>
         </is>
       </c>
     </row>
@@ -8138,37 +8138,37 @@
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t>shock_month</t>
+          <t>shock_coping</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>select one</t>
+          <t>select multiple</t>
         </is>
       </c>
       <c r="F169" s="2" t="inlineStr">
         <is>
-          <t>In which month did that happen?</t>
+          <t>How did your household manage? Check every one they used.</t>
         </is>
       </c>
       <c r="G169" s="2" t="inlineStr">
         <is>
-          <t>वह किस महीने हुआ था?</t>
+          <t>आपके घर ने कैसे सँभाला? उन्होंने जो-जो किया, सब चुनिए।</t>
         </is>
       </c>
       <c r="H169" s="2" t="inlineStr">
         <is>
-          <t>1 January | 2 February | 3 March | 4 April | 5 May | 6 June | 7 July | 8 August | 9 September | 10 October | 11 November | 12 December</t>
+          <t>1 Used savings | 2 Borrowed money | 3 Sold or pawned assets | 4 Cut consumption | 5 Help from relatives/community | 6 Did nothing/other</t>
         </is>
       </c>
       <c r="I169" s="2" t="inlineStr">
         <is>
-          <t>Ask only if distress_event_last365d names a real shock (not code 9, nothing happened)</t>
+          <t>Ask only if any shock was reported</t>
         </is>
       </c>
       <c r="J169" s="2" t="inlineStr">
         <is>
-          <t>Dercon and Krishnan 2000 (seasonal timing of shocks); project design</t>
+          <t>Coping strategies in VEP studies; Carter and Zimmerman 2000 on asset versus consumption smoothing</t>
         </is>
       </c>
     </row>
@@ -8188,37 +8188,29 @@
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>shock_coping</t>
+          <t>cope_less_pref_food_yatra_wk</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>select multiple</t>
+          <t>whole number</t>
         </is>
       </c>
       <c r="F170" s="2" t="inlineStr">
         <is>
-          <t>How did your household manage? Check every one they used.</t>
+          <t>In a normal week during the Yatra season, to cope with a lack of food or money to buy it, how many days did your household rely on less expensive/less preferred food? (0-7 days)</t>
         </is>
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>आपके घर ने कैसे सँभाला? उन्होंने जो-जो किया, सब चुनिए।</t>
-        </is>
-      </c>
-      <c r="H170" s="2" t="inlineStr">
-        <is>
-          <t>1 Used savings | 2 Borrowed money | 3 Sold or pawned assets | 4 Cut consumption | 5 Help from relatives/community | 6 Did nothing/other</t>
-        </is>
-      </c>
-      <c r="I170" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if any shock was reported</t>
-        </is>
-      </c>
+          <t>यात्रा के मौसम के आम हफ़्ते में, खाने की या खाना ख़रीदने के पैसे की कमी से निपटने के लिए आपके घर ने कितने दिन सस्ता या कम पसंद का खाना खाया? (0-7 दिन)</t>
+        </is>
+      </c>
+      <c r="H170" s="2" t="inlineStr"/>
+      <c r="I170" s="2" t="inlineStr"/>
       <c r="J170" s="2" t="inlineStr">
         <is>
-          <t>Coping strategies in VEP studies; Carter and Zimmerman 2000 on asset versus consumption smoothing</t>
+          <t>VASyR 2025 (exact item wording); WFP rCSI; The reduced Coping Strategy Index (rCSI): five food-coping questions, standard WFP weights (1, 2, 1, 1, 3) applied when the index is built. The Kedarnath instrument otherwise has no food-security module, which is a gap for a poverty-vulnerability survey; these five short questions close it at low cost instead of a full dietary-diversity module, left out to stay inside the 45-minute limit. Kept as day-counts (0-7), not collapsed to yes/no: this is the standard, validated WFP/FAO specification (frequency x severity), and no comparably-standard binary version was found on checking; a day-count also takes about as long to answer as a yes/no in practice, so little interview time is saved by simplifying it.</t>
         </is>
       </c>
     </row>
@@ -8238,7 +8230,7 @@
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t>cope_less_pref_food_yatra_wk</t>
+          <t>cope_less_pref_food_offseason_wk</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr">
@@ -8248,12 +8240,12 @@
       </c>
       <c r="F171" s="2" t="inlineStr">
         <is>
-          <t>In a normal week during the Yatra season, to cope with a lack of food or money to buy it, how many days did your household rely on less expensive/less preferred food? (0-7 days)</t>
+          <t>In a normal week when the Yatra is closed, to cope with a lack of food or money to buy it, how many days did your household rely on less expensive/less preferred food? (0-7 days)</t>
         </is>
       </c>
       <c r="G171" s="2" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम हफ़्ते में, खाने की या खाना ख़रीदने के पैसे की कमी से निपटने के लिए आपके घर ने कितने दिन सस्ता या कम पसंद का खाना खाया? (0-7 दिन)</t>
+          <t>जब यात्रा बंद रहती है, उस आम हफ़्ते में आपके घर ने कितने दिन सस्ता या कम पसंद का खाना खाया? (0-7 दिन)</t>
         </is>
       </c>
       <c r="H171" s="2" t="inlineStr"/>
@@ -8280,7 +8272,7 @@
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>cope_less_pref_food_offseason_wk</t>
+          <t>cope_borrow_food_yatra_wk</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr">
@@ -8290,12 +8282,12 @@
       </c>
       <c r="F172" s="2" t="inlineStr">
         <is>
-          <t>In a normal week when the Yatra is closed, to cope with a lack of food or money to buy it, how many days did your household rely on less expensive/less preferred food? (0-7 days)</t>
+          <t>In a normal week during the Yatra season, to cope with a lack of food or money to buy it, how many days did your household borrow food and/or rely on help from friends/relatives? (0-7 days)</t>
         </is>
       </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम हफ़्ते में आपके घर ने कितने दिन सस्ता या कम पसंद का खाना खाया? (0-7 दिन)</t>
+          <t>यात्रा के मौसम के आम हफ़्ते में, खाने की या खाना ख़रीदने के पैसे की कमी से निपटने के लिए आपके घर ने कितने दिन खाना उधार लिया या दोस्तों/रिश्तेदारों की मदद ली? (0-7 दिन)</t>
         </is>
       </c>
       <c r="H172" s="2" t="inlineStr"/>
@@ -8322,7 +8314,7 @@
       </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t>cope_borrow_food_yatra_wk</t>
+          <t>cope_borrow_food_offseason_wk</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr">
@@ -8332,12 +8324,12 @@
       </c>
       <c r="F173" s="2" t="inlineStr">
         <is>
-          <t>In a normal week during the Yatra season, to cope with a lack of food or money to buy it, how many days did your household borrow food and/or rely on help from friends/relatives? (0-7 days)</t>
+          <t>In a normal week when the Yatra is closed, to cope with a lack of food or money to buy it, how many days did your household borrow food and/or rely on help from friends/relatives? (0-7 days)</t>
         </is>
       </c>
       <c r="G173" s="2" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम हफ़्ते में, खाने की या खाना ख़रीदने के पैसे की कमी से निपटने के लिए आपके घर ने कितने दिन खाना उधार लिया या दोस्तों/रिश्तेदारों की मदद ली? (0-7 दिन)</t>
+          <t>जब यात्रा बंद रहती है, उस आम हफ़्ते में आपके घर ने कितने दिन खाना उधार लिया या दोस्तों/रिश्तेदारों की मदद ली? (0-7 दिन)</t>
         </is>
       </c>
       <c r="H173" s="2" t="inlineStr"/>
@@ -8364,7 +8356,7 @@
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>cope_borrow_food_offseason_wk</t>
+          <t>cope_reduce_meals_yatra_wk</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
@@ -8374,12 +8366,12 @@
       </c>
       <c r="F174" s="2" t="inlineStr">
         <is>
-          <t>In a normal week when the Yatra is closed, to cope with a lack of food or money to buy it, how many days did your household borrow food and/or rely on help from friends/relatives? (0-7 days)</t>
+          <t>In a normal week during the Yatra season, to cope with a lack of food or money to buy it, how many days did your household reduce the number of meals eaten per day? (0-7 days)</t>
         </is>
       </c>
       <c r="G174" s="2" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम हफ़्ते में आपके घर ने कितने दिन खाना उधार लिया या दोस्तों/रिश्तेदारों की मदद ली? (0-7 दिन)</t>
+          <t>यात्रा के मौसम के आम हफ़्ते में, खाने की या खाना ख़रीदने के पैसे की कमी से निपटने के लिए आपके घर ने कितने दिन दिन में कम बार खाना खाया? (0-7 दिन)</t>
         </is>
       </c>
       <c r="H174" s="2" t="inlineStr"/>
@@ -8406,7 +8398,7 @@
       </c>
       <c r="D175" s="2" t="inlineStr">
         <is>
-          <t>cope_reduce_meals_yatra_wk</t>
+          <t>cope_reduce_meals_offseason_wk</t>
         </is>
       </c>
       <c r="E175" s="2" t="inlineStr">
@@ -8416,12 +8408,12 @@
       </c>
       <c r="F175" s="2" t="inlineStr">
         <is>
-          <t>In a normal week during the Yatra season, to cope with a lack of food or money to buy it, how many days did your household reduce the number of meals eaten per day? (0-7 days)</t>
+          <t>In a normal week when the Yatra is closed, to cope with a lack of food or money to buy it, how many days did your household reduce the number of meals eaten per day? (0-7 days)</t>
         </is>
       </c>
       <c r="G175" s="2" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम हफ़्ते में, खाने की या खाना ख़रीदने के पैसे की कमी से निपटने के लिए आपके घर ने कितने दिन दिन में कम बार खाना खाया? (0-7 दिन)</t>
+          <t>जब यात्रा बंद रहती है, उस आम हफ़्ते में आपके घर ने कितने दिन दिन में कम बार खाना खाया? (0-7 दिन)</t>
         </is>
       </c>
       <c r="H175" s="2" t="inlineStr"/>
@@ -8448,7 +8440,7 @@
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>cope_reduce_meals_offseason_wk</t>
+          <t>cope_reduce_portion_yatra_wk</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr">
@@ -8458,12 +8450,12 @@
       </c>
       <c r="F176" s="2" t="inlineStr">
         <is>
-          <t>In a normal week when the Yatra is closed, to cope with a lack of food or money to buy it, how many days did your household reduce the number of meals eaten per day? (0-7 days)</t>
+          <t>In a normal week during the Yatra season, to cope with a lack of food or money to buy it, how many days did your household reduce portion size of meals? (0-7 days)</t>
         </is>
       </c>
       <c r="G176" s="2" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम हफ़्ते में आपके घर ने कितने दिन दिन में कम बार खाना खाया? (0-7 दिन)</t>
+          <t>यात्रा के मौसम के आम हफ़्ते में, खाने की या खाना ख़रीदने के पैसे की कमी से निपटने के लिए आपके घर ने कितने दिन खाने की मात्रा घटाई? (0-7 दिन)</t>
         </is>
       </c>
       <c r="H176" s="2" t="inlineStr"/>
@@ -8490,7 +8482,7 @@
       </c>
       <c r="D177" s="2" t="inlineStr">
         <is>
-          <t>cope_reduce_portion_yatra_wk</t>
+          <t>cope_reduce_portion_offseason_wk</t>
         </is>
       </c>
       <c r="E177" s="2" t="inlineStr">
@@ -8500,12 +8492,12 @@
       </c>
       <c r="F177" s="2" t="inlineStr">
         <is>
-          <t>In a normal week during the Yatra season, to cope with a lack of food or money to buy it, how many days did your household reduce portion size of meals? (0-7 days)</t>
+          <t>In a normal week when the Yatra is closed, to cope with a lack of food or money to buy it, how many days did your household reduce portion size of meals? (0-7 days)</t>
         </is>
       </c>
       <c r="G177" s="2" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम हफ़्ते में, खाने की या खाना ख़रीदने के पैसे की कमी से निपटने के लिए आपके घर ने कितने दिन खाने की मात्रा घटाई? (0-7 दिन)</t>
+          <t>जब यात्रा बंद रहती है, उस आम हफ़्ते में आपके घर ने कितने दिन खाने की मात्रा घटाई? (0-7 दिन)</t>
         </is>
       </c>
       <c r="H177" s="2" t="inlineStr"/>
@@ -8532,7 +8524,7 @@
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>cope_reduce_portion_offseason_wk</t>
+          <t>cope_restrict_adult_yatra_wk</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr">
@@ -8542,12 +8534,12 @@
       </c>
       <c r="F178" s="2" t="inlineStr">
         <is>
-          <t>In a normal week when the Yatra is closed, to cope with a lack of food or money to buy it, how many days did your household reduce portion size of meals? (0-7 days)</t>
+          <t>In a normal week during the Yatra season, to cope with a lack of food or money to buy it, how many days did your household restrict consumption of adults/mothers in order for young children to eat? (0-7 days)</t>
         </is>
       </c>
       <c r="G178" s="2" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम हफ़्ते में आपके घर ने कितने दिन खाने की मात्रा घटाई? (0-7 दिन)</t>
+          <t>यात्रा के मौसम के आम हफ़्ते में, खाने की या खाना ख़रीदने के पैसे की कमी से निपटने के लिए आपके घर ने कितने दिन बड़ों ने कम खाया ताकि छोटे बच्चे खा सकें? (0-7 दिन)</t>
         </is>
       </c>
       <c r="H178" s="2" t="inlineStr"/>
@@ -8574,7 +8566,7 @@
       </c>
       <c r="D179" s="2" t="inlineStr">
         <is>
-          <t>cope_restrict_adult_yatra_wk</t>
+          <t>cope_restrict_adult_offseason_wk</t>
         </is>
       </c>
       <c r="E179" s="2" t="inlineStr">
@@ -8584,12 +8576,12 @@
       </c>
       <c r="F179" s="2" t="inlineStr">
         <is>
-          <t>In a normal week during the Yatra season, to cope with a lack of food or money to buy it, how many days did your household restrict consumption of adults/mothers in order for young children to eat? (0-7 days)</t>
+          <t>In a normal week when the Yatra is closed, to cope with a lack of food or money to buy it, how many days did your household restrict consumption of adults/mothers in order for young children to eat? (0-7 days)</t>
         </is>
       </c>
       <c r="G179" s="2" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम हफ़्ते में, खाने की या खाना ख़रीदने के पैसे की कमी से निपटने के लिए आपके घर ने कितने दिन बड़ों ने कम खाया ताकि छोटे बच्चे खा सकें? (0-7 दिन)</t>
+          <t>जब यात्रा बंद रहती है, उस आम हफ़्ते में आपके घर ने कितने दिन बड़ों ने कम खाया ताकि छोटे बच्चे खा सकें? (0-7 दिन)</t>
         </is>
       </c>
       <c r="H179" s="2" t="inlineStr"/>
@@ -8606,39 +8598,43 @@
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>Food security, shocks and coping</t>
+          <t>Ropeway</t>
         </is>
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>cope_restrict_adult_offseason_wk</t>
+          <t>ropeway_stance</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>whole number</t>
+          <t>select one</t>
         </is>
       </c>
       <c r="F180" s="2" t="inlineStr">
         <is>
-          <t>In a normal week when the Yatra is closed, to cope with a lack of food or money to buy it, how many days did your household restrict consumption of adults/mothers in order for young children to eat? (0-7 days)</t>
+          <t>A ropeway is proposed between Gaurikund and Kedarnath. Are you in favour, neutral, or against?</t>
         </is>
       </c>
       <c r="G180" s="2" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम हफ़्ते में आपके घर ने कितने दिन बड़ों ने कम खाया ताकि छोटे बच्चे खा सकें? (0-7 दिन)</t>
-        </is>
-      </c>
-      <c r="H180" s="2" t="inlineStr"/>
+          <t>गौरीकुंड से केदारनाथ तक रोपवे बनाने की बात चल रही है। आप इसके पक्ष में हैं, बीच में हैं, या ख़िलाफ़ हैं?</t>
+        </is>
+      </c>
+      <c r="H180" s="2" t="inlineStr">
+        <is>
+          <t>1 Support | 2 Neutral | 3 Oppose | 98 Prefer not to say</t>
+        </is>
+      </c>
       <c r="I180" s="2" t="inlineStr"/>
       <c r="J180" s="2" t="inlineStr">
         <is>
-          <t>VASyR 2025 (exact item wording); WFP rCSI; The reduced Coping Strategy Index (rCSI): five food-coping questions, standard WFP weights (1, 2, 1, 1, 3) applied when the index is built. The Kedarnath instrument otherwise has no food-security module, which is a gap for a poverty-vulnerability survey; these five short questions close it at low cost instead of a full dietary-diversity module, left out to stay inside the 45-minute limit. Kept as day-counts (0-7), not collapsed to yes/no: this is the standard, validated WFP/FAO specification (frequency x severity), and no comparably-standard binary version was found on checking; a day-count also takes about as long to answer as a yes/no in practice, so little interview time is saved by simplifying it.</t>
+          <t>Project design</t>
         </is>
       </c>
     </row>
@@ -8658,33 +8654,33 @@
       </c>
       <c r="D181" s="2" t="inlineStr">
         <is>
-          <t>ropeway_stance</t>
+          <t>trek_dependent</t>
         </is>
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
-          <t>select one</t>
+          <t>yes/no</t>
         </is>
       </c>
       <c r="F181" s="2" t="inlineStr">
         <is>
-          <t>A ropeway is proposed between Gaurikund and Kedarnath. Are you in favour, neutral, or against?</t>
+          <t>Is your main Yatra work carrying, transporting or guiding people or goods on the Gaurikund to Kedarnath trek?</t>
         </is>
       </c>
       <c r="G181" s="2" t="inlineStr">
         <is>
-          <t>गौरीकुंड से केदारनाथ तक रोपवे बनाने की बात चल रही है। आप इसके पक्ष में हैं, बीच में हैं, या ख़िलाफ़ हैं?</t>
+          <t>क्या आपका मुख्य यात्रा-काम गौरीकुंड से केदारनाथ के पैदल रास्ते पर लोगों या सामान को ले जाना, पहुँचाना या रास्ता दिखाना है?</t>
         </is>
       </c>
       <c r="H181" s="2" t="inlineStr">
         <is>
-          <t>1 Support | 2 Neutral | 3 Oppose | 98 Prefer not to say</t>
+          <t>0 No | 1 Yes</t>
         </is>
       </c>
       <c r="I181" s="2" t="inlineStr"/>
       <c r="J181" s="2" t="inlineStr">
         <is>
-          <t>Project design</t>
+          <t>Project design (see tasks_module W4: exposure must be asked directly)</t>
         </is>
       </c>
     </row>
@@ -8694,43 +8690,43 @@
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>Ropeway</t>
+          <t>Job quality (Apablaza et al. 2026 questions)</t>
         </is>
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>trek_dependent</t>
+          <t>job_situation</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>yes/no</t>
+          <t>select one</t>
         </is>
       </c>
       <c r="F182" s="2" t="inlineStr">
         <is>
-          <t>Is your main Yatra work carrying, transporting or guiding people or goods on the Gaurikund to Kedarnath trek?</t>
+          <t>Which best describes your situation during the last month: you work for pay full-time; you work for pay part-time or do occasional jobs; you study and work; you only study; you are only being trained for work; you are retired or pensioned; you do unpaid household tasks or care for others; you are unemployed and actively looking for work; you are sick or disabled and cannot work; or none of these?</t>
         </is>
       </c>
       <c r="G182" s="2" t="inlineStr">
         <is>
-          <t>क्या आपका मुख्य यात्रा-काम गौरीकुंड से केदारनाथ के पैदल रास्ते पर लोगों या सामान को ले जाना, पहुँचाना या रास्ता दिखाना है?</t>
+          <t>पिछले महीने आपकी हालत इनमें से किससे सबसे मिलती है: पूरे समय पैसे के लिए काम; कुछ समय या कभी-कभार का काम; पढ़ाई के साथ काम; सिर्फ़ पढ़ाई; सिर्फ़ काम की ट्रेनिंग; रिटायर या पेंशन पर; घर का बिना पैसे का काम या किसी की देखभाल; काम नहीं है और ढूँढ रहे हैं; बीमारी या विकलांगता से काम नहीं कर सकते; या इनमें से कुछ नहीं?</t>
         </is>
       </c>
       <c r="H182" s="2" t="inlineStr">
         <is>
-          <t>0 No | 1 Yes</t>
+          <t>1 Works for pay full-time | 2 Works for pay part-time or occasional jobs | 3 Studies and works | 4 Only studies | 5 Being trained for work only | 6 Retired or pensioned | 7 Unpaid household tasks or caring for others | 8 Unemployed, actively seeking work | 9 Sick or disabled, cannot work | 10 Neither studying, working nor seeking work | 97 Does not know</t>
         </is>
       </c>
       <c r="I182" s="2" t="inlineStr"/>
       <c r="J182" s="2" t="inlineStr">
         <is>
-          <t>Project design (see tasks_module W4: exposure must be asked directly)</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q5 (all eleven categories, with its own three-way routing)</t>
         </is>
       </c>
     </row>
@@ -8750,7 +8746,7 @@
       </c>
       <c r="D183" s="2" t="inlineStr">
         <is>
-          <t>job_situation</t>
+          <t>job_permanence</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr">
@@ -8760,23 +8756,27 @@
       </c>
       <c r="F183" s="2" t="inlineStr">
         <is>
-          <t>Which best describes your situation during the last month: you work for pay full-time; you work for pay part-time or do occasional jobs; you study and work; you only study; you are only being trained for work; you are retired or pensioned; you do unpaid household tasks or care for others; you are unemployed and actively looking for work; you are sick or disabled and cannot work; or none of these?</t>
+          <t>Is your job: permanent; seasonal or temporary; occasional or casual; on probation; or fixed-term?</t>
         </is>
       </c>
       <c r="G183" s="2" t="inlineStr">
         <is>
-          <t>पिछले महीने आपकी हालत इनमें से किससे सबसे मिलती है: पूरे समय पैसे के लिए काम; कुछ समय या कभी-कभार का काम; पढ़ाई के साथ काम; सिर्फ़ पढ़ाई; सिर्फ़ काम की ट्रेनिंग; रिटायर या पेंशन पर; घर का बिना पैसे का काम या किसी की देखभाल; काम नहीं है और ढूँढ रहे हैं; बीमारी या विकलांगता से काम नहीं कर सकते; या इनमें से कुछ नहीं?</t>
+          <t>आपका काम कैसा है: पक्का; मौसमी या कुछ समय का; कभी-कभार का; परखने की अवधि पर; या तय समय के लिए?</t>
         </is>
       </c>
       <c r="H183" s="2" t="inlineStr">
         <is>
-          <t>1 Works for pay full-time | 2 Works for pay part-time or occasional jobs | 3 Studies and works | 4 Only studies | 5 Being trained for work only | 6 Retired or pensioned | 7 Unpaid household tasks or caring for others | 8 Unemployed, actively seeking work | 9 Sick or disabled, cannot work | 10 Neither studying, working nor seeking work | 97 Does not know</t>
-        </is>
-      </c>
-      <c r="I183" s="2" t="inlineStr"/>
+          <t>1 Permanent | 2 Seasonal or temporary | 3 Occasional or casual | 4 On probation | 5 Fixed-term</t>
+        </is>
+      </c>
+      <c r="I183" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if job_situation is 1, 2 or 3 (currently working)</t>
+        </is>
+      </c>
       <c r="J183" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q5 (all eleven categories, with its own three-way routing)</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q9</t>
         </is>
       </c>
     </row>
@@ -8796,7 +8796,7 @@
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t>job_permanence</t>
+          <t>contract_status</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
@@ -8806,27 +8806,27 @@
       </c>
       <c r="F184" s="2" t="inlineStr">
         <is>
-          <t>Is your job: permanent; seasonal or temporary; occasional or casual; on probation; or fixed-term?</t>
+          <t>Do you have a signed contract? Yes, signed; yes but not yet signed; no contract.</t>
         </is>
       </c>
       <c r="G184" s="2" t="inlineStr">
         <is>
-          <t>आपका काम कैसा है: पक्का; मौसमी या कुछ समय का; कभी-कभार का; परखने की अवधि पर; या तय समय के लिए?</t>
+          <t>क्या आपका दस्तख़त किया हुआ अनुबंध (कॉन्ट्रैक्ट) है? हाँ, दस्तख़त किया; हाँ, पर अभी दस्तख़त नहीं हुआ; कोई अनुबंध नहीं।</t>
         </is>
       </c>
       <c r="H184" s="2" t="inlineStr">
         <is>
-          <t>1 Permanent | 2 Seasonal or temporary | 3 Occasional or casual | 4 On probation | 5 Fixed-term</t>
+          <t>1 Yes, signed | 2 Yes, but not yet signed | 3 No contract</t>
         </is>
       </c>
       <c r="I184" s="2" t="inlineStr">
         <is>
-          <t>Ask only if job_situation is 1, 2 or 3 (currently working)</t>
+          <t>Ask only if job_situation is 1, 2 or 3 (currently working); and employment_type is 3 or 4 (wage workers) -- self-employed skip to the next question</t>
         </is>
       </c>
       <c r="J184" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q9</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q11</t>
         </is>
       </c>
     </row>
@@ -8846,37 +8846,37 @@
       </c>
       <c r="D185" s="2" t="inlineStr">
         <is>
-          <t>contract_status</t>
+          <t>workplace_registered</t>
         </is>
       </c>
       <c r="E185" s="2" t="inlineStr">
         <is>
-          <t>select one</t>
+          <t>yes/no</t>
         </is>
       </c>
       <c r="F185" s="2" t="inlineStr">
         <is>
-          <t>Do you have a signed contract? Yes, signed; yes but not yet signed; no contract.</t>
+          <t>Is your workplace or business registered, for example with a taxpayer or GST number, a shop or trade licence, the Yatra registration, or a union?</t>
         </is>
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>क्या आपका दस्तख़त किया हुआ अनुबंध (कॉन्ट्रैक्ट) है? हाँ, दस्तख़त किया; हाँ, पर अभी दस्तख़त नहीं हुआ; कोई अनुबंध नहीं।</t>
+          <t>क्या आपका काम या धंधा रजिस्टर्ड है, जैसे GST या टैक्स नंबर, दुकान का लाइसेंस, यात्रा का रजिस्ट्रेशन, या कोई यूनियन?</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
         <is>
-          <t>1 Yes, signed | 2 Yes, but not yet signed | 3 No contract</t>
+          <t>0 No | 1 Yes</t>
         </is>
       </c>
       <c r="I185" s="2" t="inlineStr">
         <is>
-          <t>Ask only if job_situation is 1, 2 or 3 (currently working); and employment_type is 3 or 4 (wage workers) -- self-employed skip to the next question</t>
+          <t>Ask only if job_situation is 1, 2 or 3 (currently working)</t>
         </is>
       </c>
       <c r="J185" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q11</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q12 (widened to local registrations)</t>
         </is>
       </c>
     </row>
@@ -8896,27 +8896,27 @@
       </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
-          <t>workplace_registered</t>
+          <t>pension_contrib</t>
         </is>
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>yes/no</t>
+          <t>select one</t>
         </is>
       </c>
       <c r="F186" s="2" t="inlineStr">
         <is>
-          <t>Is your workplace or business registered, for example with a taxpayer or GST number, a shop or trade licence, the Yatra registration, or a union?</t>
+          <t>Do you contribute to any pension system? Yes, the employer deducts it; yes, voluntarily; no.</t>
         </is>
       </c>
       <c r="G186" s="2" t="inlineStr">
         <is>
-          <t>क्या आपका काम या धंधा रजिस्टर्ड है, जैसे GST या टैक्स नंबर, दुकान का लाइसेंस, यात्रा का रजिस्ट्रेशन, या कोई यूनियन?</t>
+          <t>क्या आप किसी पेंशन में पैसा डालते हैं? हाँ, मालिक तनख़्वाह से काटता है; हाँ, अपनी मर्ज़ी से डालते हैं; नहीं।</t>
         </is>
       </c>
       <c r="H186" s="2" t="inlineStr">
         <is>
-          <t>0 No | 1 Yes</t>
+          <t>1 Yes, employer deducts it | 2 Yes, contributes voluntarily | 3 No</t>
         </is>
       </c>
       <c r="I186" s="2" t="inlineStr">
@@ -8926,7 +8926,7 @@
       </c>
       <c r="J186" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q12 (widened to local registrations)</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q16</t>
         </is>
       </c>
     </row>
@@ -8946,7 +8946,7 @@
       </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t>pension_contrib</t>
+          <t>work_health_ins</t>
         </is>
       </c>
       <c r="E187" s="2" t="inlineStr">
@@ -8956,17 +8956,17 @@
       </c>
       <c r="F187" s="2" t="inlineStr">
         <is>
-          <t>Do you contribute to any pension system? Yes, the employer deducts it; yes, voluntarily; no.</t>
+          <t>Do you have health insurance through your work? Yes; only private or other insurance; none; don't know.</t>
         </is>
       </c>
       <c r="G187" s="2" t="inlineStr">
         <is>
-          <t>क्या आप किसी पेंशन में पैसा डालते हैं? हाँ, मालिक तनख़्वाह से काटता है; हाँ, अपनी मर्ज़ी से डालते हैं; नहीं।</t>
+          <t>क्या काम की तरफ़ से आपका स्वास्थ्य बीमा है? हाँ; सिर्फ़ अपना या कोई और बीमा; कोई नहीं; पता नहीं।</t>
         </is>
       </c>
       <c r="H187" s="2" t="inlineStr">
         <is>
-          <t>1 Yes, employer deducts it | 2 Yes, contributes voluntarily | 3 No</t>
+          <t>1 Yes, through work | 2 Only private or other insurance | 3 None | 4 Don't know</t>
         </is>
       </c>
       <c r="I187" s="2" t="inlineStr">
@@ -8976,7 +8976,7 @@
       </c>
       <c r="J187" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q16</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q17</t>
         </is>
       </c>
     </row>
@@ -8996,7 +8996,7 @@
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
-          <t>work_health_ins</t>
+          <t>leave_rights</t>
         </is>
       </c>
       <c r="E188" s="2" t="inlineStr">
@@ -9006,17 +9006,17 @@
       </c>
       <c r="F188" s="2" t="inlineStr">
         <is>
-          <t>Do you have health insurance through your work? Yes; only private or other insurance; none; don't know.</t>
+          <t>Do you have the right to paid holiday, sick or maternity leave?</t>
         </is>
       </c>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t>क्या काम की तरफ़ से आपका स्वास्थ्य बीमा है? हाँ; सिर्फ़ अपना या कोई और बीमा; कोई नहीं; पता नहीं।</t>
+          <t>क्या आपको पैसे वाली छुट्टी मिलती है — त्योहार, बीमारी या ज़च्चगी की?</t>
         </is>
       </c>
       <c r="H188" s="2" t="inlineStr">
         <is>
-          <t>1 Yes, through work | 2 Only private or other insurance | 3 None | 4 Don't know</t>
+          <t>0 No | 1 Yes | 97 Don't know</t>
         </is>
       </c>
       <c r="I188" s="2" t="inlineStr">
@@ -9026,7 +9026,7 @@
       </c>
       <c r="J188" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q17</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q18</t>
         </is>
       </c>
     </row>
@@ -9046,7 +9046,7 @@
       </c>
       <c r="D189" s="2" t="inlineStr">
         <is>
-          <t>leave_rights</t>
+          <t>injured_ever</t>
         </is>
       </c>
       <c r="E189" s="2" t="inlineStr">
@@ -9056,12 +9056,12 @@
       </c>
       <c r="F189" s="2" t="inlineStr">
         <is>
-          <t>Do you have the right to paid holiday, sick or maternity leave?</t>
+          <t>Have you ever been physically injured at your workplace?</t>
         </is>
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>क्या आपको पैसे वाली छुट्टी मिलती है — त्योहार, बीमारी या ज़च्चगी की?</t>
+          <t>क्या आपको कभी काम की जगह पर चोट लगी है?</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr">
@@ -9076,7 +9076,7 @@
       </c>
       <c r="J189" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q18</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q19</t>
         </is>
       </c>
     </row>
@@ -9096,7 +9096,7 @@
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>injured_ever</t>
+          <t>workplace_injury_12m</t>
         </is>
       </c>
       <c r="E190" s="2" t="inlineStr">
@@ -9106,12 +9106,12 @@
       </c>
       <c r="F190" s="2" t="inlineStr">
         <is>
-          <t>Have you ever been physically injured at your workplace?</t>
+          <t>In the last 12 months, was anyone physically injured or killed at your workplace because of work?</t>
         </is>
       </c>
       <c r="G190" s="2" t="inlineStr">
         <is>
-          <t>क्या आपको कभी काम की जगह पर चोट लगी है?</t>
+          <t>पिछले 12 महीनों में क्या आपके काम की जगह पर काम की वजह से किसी को चोट लगी या किसी की मौत हुई?</t>
         </is>
       </c>
       <c r="H190" s="2" t="inlineStr">
@@ -9126,7 +9126,7 @@
       </c>
       <c r="J190" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q19</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q20</t>
         </is>
       </c>
     </row>
@@ -9146,7 +9146,7 @@
       </c>
       <c r="D191" s="2" t="inlineStr">
         <is>
-          <t>workplace_injury_12m</t>
+          <t>wants_more_work</t>
         </is>
       </c>
       <c r="E191" s="2" t="inlineStr">
@@ -9156,12 +9156,12 @@
       </c>
       <c r="F191" s="2" t="inlineStr">
         <is>
-          <t>In the last 12 months, was anyone physically injured or killed at your workplace because of work?</t>
+          <t>Would you like to work more hours than you do?</t>
         </is>
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>पिछले 12 महीनों में क्या आपके काम की जगह पर काम की वजह से किसी को चोट लगी या किसी की मौत हुई?</t>
+          <t>क्या आप अभी से ज़्यादा घंटे काम करना चाहेंगे?</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
@@ -9171,12 +9171,12 @@
       </c>
       <c r="I191" s="2" t="inlineStr">
         <is>
-          <t>Ask only if job_situation is 1, 2 or 3 (currently working)</t>
+          <t>Ask if job_situation is 1 to 7 (Apablaza routes codes 4-7 straight to this question)</t>
         </is>
       </c>
       <c r="J191" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q20</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q21</t>
         </is>
       </c>
     </row>
@@ -9196,37 +9196,33 @@
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>wants_more_work</t>
+          <t>more_hours_day</t>
         </is>
       </c>
       <c r="E192" s="2" t="inlineStr">
         <is>
-          <t>select one</t>
+          <t>whole number</t>
         </is>
       </c>
       <c r="F192" s="2" t="inlineStr">
         <is>
-          <t>Would you like to work more hours than you do?</t>
+          <t>On a working day, how many MORE hours would you like to work?</t>
         </is>
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>क्या आप अभी से ज़्यादा घंटे काम करना चाहेंगे?</t>
-        </is>
-      </c>
-      <c r="H192" s="2" t="inlineStr">
-        <is>
-          <t>0 No | 1 Yes | 97 Don't know</t>
-        </is>
-      </c>
+          <t>काम के दिन में आप कितने घंटे और काम करना चाहेंगे?</t>
+        </is>
+      </c>
+      <c r="H192" s="2" t="inlineStr"/>
       <c r="I192" s="2" t="inlineStr">
         <is>
-          <t>Ask if job_situation is 1 to 7 (Apablaza routes codes 4-7 straight to this question)</t>
+          <t>Ask if wants_more_work = 1, or if job_situation = 8 (Apablaza routes the unemployed-and-seeking category here directly)</t>
         </is>
       </c>
       <c r="J192" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q21</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q22</t>
         </is>
       </c>
     </row>
@@ -9246,7 +9242,7 @@
       </c>
       <c r="D193" s="2" t="inlineStr">
         <is>
-          <t>more_hours_day</t>
+          <t>months_looked_for_work</t>
         </is>
       </c>
       <c r="E193" s="2" t="inlineStr">
@@ -9256,23 +9252,23 @@
       </c>
       <c r="F193" s="2" t="inlineStr">
         <is>
-          <t>On a working day, how many MORE hours would you like to work?</t>
+          <t>Across the months when you had no paid work, about how many MONTHS in total were you looking for work?</t>
         </is>
       </c>
       <c r="G193" s="2" t="inlineStr">
         <is>
-          <t>काम के दिन में आप कितने घंटे और काम करना चाहेंगे?</t>
+          <t>जिन महीनों में आपके पास कोई पैसे वाला काम नहीं था, उनमें कुल मिलाकर लगभग कितने महीने आप काम ढूँढते रहे?</t>
         </is>
       </c>
       <c r="H193" s="2" t="inlineStr"/>
       <c r="I193" s="2" t="inlineStr">
         <is>
-          <t>Ask if wants_more_work = 1, or if job_situation = 8 (Apablaza routes the unemployed-and-seeking category here directly)</t>
+          <t>Ask if any month in the calendar is 'No paid work', or if job_situation = 8</t>
         </is>
       </c>
       <c r="J193" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q22</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q23 (duration in weeks, tied to the calendar instead of a single point in time)</t>
         </is>
       </c>
     </row>
@@ -9292,33 +9288,33 @@
       </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
-          <t>months_looked_for_work</t>
+          <t>first_job_ever</t>
         </is>
       </c>
       <c r="E194" s="2" t="inlineStr">
         <is>
-          <t>whole number</t>
+          <t>select one</t>
         </is>
       </c>
       <c r="F194" s="2" t="inlineStr">
         <is>
-          <t>Across the months when you had no paid work, about how many MONTHS in total were you looking for work?</t>
+          <t>Was your current work the first paid job you ever had?</t>
         </is>
       </c>
       <c r="G194" s="2" t="inlineStr">
         <is>
-          <t>जिन महीनों में आपके पास कोई पैसे वाला काम नहीं था, उनमें कुल मिलाकर लगभग कितने महीने आप काम ढूँढते रहे?</t>
-        </is>
-      </c>
-      <c r="H194" s="2" t="inlineStr"/>
-      <c r="I194" s="2" t="inlineStr">
-        <is>
-          <t>Ask if any month in the calendar is 'No paid work', or if job_situation = 8</t>
-        </is>
-      </c>
+          <t>क्या यह आपका पहला पैसे वाला काम है?</t>
+        </is>
+      </c>
+      <c r="H194" s="2" t="inlineStr">
+        <is>
+          <t>0 No | 1 Yes | 97 Don't know</t>
+        </is>
+      </c>
+      <c r="I194" s="2" t="inlineStr"/>
       <c r="J194" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q23 (duration in weeks, tied to the calendar instead of a single point in time)</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q24</t>
         </is>
       </c>
     </row>
@@ -9328,17 +9324,17 @@
       </c>
       <c r="B195" s="2" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C195" s="2" t="inlineStr">
         <is>
-          <t>Job quality (Apablaza et al. 2026 questions)</t>
+          <t>Tasks and skills (short block)</t>
         </is>
       </c>
       <c r="D195" s="2" t="inlineStr">
         <is>
-          <t>first_job_ever</t>
+          <t>tk_load</t>
         </is>
       </c>
       <c r="E195" s="2" t="inlineStr">
@@ -9348,23 +9344,23 @@
       </c>
       <c r="F195" s="2" t="inlineStr">
         <is>
-          <t>Was your current work the first paid job you ever had?</t>
+          <t>Do you load, unload, stack or count goods? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
         </is>
       </c>
       <c r="G195" s="2" t="inlineStr">
         <is>
-          <t>क्या यह आपका पहला पैसे वाला काम है?</t>
+          <t>क्या आप सामान चढ़ाना-उतारना, लगाना या गिनना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="H195" s="2" t="inlineStr">
         <is>
-          <t>0 No | 1 Yes | 97 Don't know</t>
+          <t>1 Yes, regularly in my main Yatra work | 2 Not in my main work, but done before elsewhere | 3 Never done</t>
         </is>
       </c>
       <c r="I195" s="2" t="inlineStr"/>
       <c r="J195" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q24</t>
+          <t>Gathmann and Schonberg 2010; NCO 9333.0100 loader</t>
         </is>
       </c>
     </row>
@@ -9384,7 +9380,7 @@
       </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
-          <t>tk_load</t>
+          <t>tk_drive</t>
         </is>
       </c>
       <c r="E196" s="2" t="inlineStr">
@@ -9394,12 +9390,12 @@
       </c>
       <c r="F196" s="2" t="inlineStr">
         <is>
-          <t>Do you load, unload, stack or count goods? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
+          <t>Do you drive a motor vehicle? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
         </is>
       </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>क्या आप सामान चढ़ाना-उतारना, लगाना या गिनना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप गाड़ी चलाना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="H196" s="2" t="inlineStr">
@@ -9410,7 +9406,7 @@
       <c r="I196" s="2" t="inlineStr"/>
       <c r="J196" s="2" t="inlineStr">
         <is>
-          <t>Gathmann and Schonberg 2010; NCO 9333.0100 loader</t>
+          <t>Spitz-Oener 2006 / STEP; NCO 8322.0100</t>
         </is>
       </c>
     </row>
@@ -9430,7 +9426,7 @@
       </c>
       <c r="D197" s="2" t="inlineStr">
         <is>
-          <t>tk_drive</t>
+          <t>tk_engine</t>
         </is>
       </c>
       <c r="E197" s="2" t="inlineStr">
@@ -9440,12 +9436,12 @@
       </c>
       <c r="F197" s="2" t="inlineStr">
         <is>
-          <t>Do you drive a motor vehicle? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
+          <t>Do you operate an engine or machine? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
         </is>
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>क्या आप गाड़ी चलाना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप इंजन या मशीन चलाना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="H197" s="2" t="inlineStr">
@@ -9456,7 +9452,7 @@
       <c r="I197" s="2" t="inlineStr"/>
       <c r="J197" s="2" t="inlineStr">
         <is>
-          <t>Spitz-Oener 2006 / STEP; NCO 8322.0100</t>
+          <t>Gathmann and Schonberg 2010; NCO 8343.1700 ropeway operator</t>
         </is>
       </c>
     </row>
@@ -9476,7 +9472,7 @@
       </c>
       <c r="D198" s="2" t="inlineStr">
         <is>
-          <t>tk_engine</t>
+          <t>tk_electric</t>
         </is>
       </c>
       <c r="E198" s="2" t="inlineStr">
@@ -9486,12 +9482,12 @@
       </c>
       <c r="F198" s="2" t="inlineStr">
         <is>
-          <t>Do you operate an engine or machine? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
+          <t>Do you do electrical or wiring work? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
         </is>
       </c>
       <c r="G198" s="2" t="inlineStr">
         <is>
-          <t>क्या आप इंजन या मशीन चलाना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप बिजली या तार का काम करना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="H198" s="2" t="inlineStr">
@@ -9502,7 +9498,7 @@
       <c r="I198" s="2" t="inlineStr"/>
       <c r="J198" s="2" t="inlineStr">
         <is>
-          <t>Gathmann and Schonberg 2010; NCO 8343.1700 ropeway operator</t>
+          <t>Spitz-Oener 2006; NCO 7411.0301 wireman</t>
         </is>
       </c>
     </row>
@@ -9522,7 +9518,7 @@
       </c>
       <c r="D199" s="2" t="inlineStr">
         <is>
-          <t>tk_electric</t>
+          <t>tk_safety</t>
         </is>
       </c>
       <c r="E199" s="2" t="inlineStr">
@@ -9532,12 +9528,12 @@
       </c>
       <c r="F199" s="2" t="inlineStr">
         <is>
-          <t>Do you do electrical or wiring work? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
+          <t>Do you check equipment or the route for safety? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
         </is>
       </c>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>क्या आप बिजली या तार का काम करना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप सामान या रास्ते की सुरक्षा जाँचना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="H199" s="2" t="inlineStr">
@@ -9548,7 +9544,7 @@
       <c r="I199" s="2" t="inlineStr"/>
       <c r="J199" s="2" t="inlineStr">
         <is>
-          <t>Spitz-Oener 2006; NCO 7411.0301 wireman</t>
+          <t>Gathmann and Schonberg 2010; NCO 8343.1700</t>
         </is>
       </c>
     </row>
@@ -9568,7 +9564,7 @@
       </c>
       <c r="D200" s="2" t="inlineStr">
         <is>
-          <t>tk_safety</t>
+          <t>tk_sell</t>
         </is>
       </c>
       <c r="E200" s="2" t="inlineStr">
@@ -9578,12 +9574,12 @@
       </c>
       <c r="F200" s="2" t="inlineStr">
         <is>
-          <t>Do you check equipment or the route for safety? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
+          <t>Do you sell goods or services? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
         </is>
       </c>
       <c r="G200" s="2" t="inlineStr">
         <is>
-          <t>क्या आप सामान या रास्ते की सुरक्षा जाँचना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप सामान या सेवा बेचना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="H200" s="2" t="inlineStr">
@@ -9594,7 +9590,7 @@
       <c r="I200" s="2" t="inlineStr"/>
       <c r="J200" s="2" t="inlineStr">
         <is>
-          <t>Gathmann and Schonberg 2010; NCO 8343.1700</t>
+          <t>Gathmann and Schonberg 2010; NCO 5223.0200</t>
         </is>
       </c>
     </row>
@@ -9614,7 +9610,7 @@
       </c>
       <c r="D201" s="2" t="inlineStr">
         <is>
-          <t>tk_sell</t>
+          <t>tk_cash</t>
         </is>
       </c>
       <c r="E201" s="2" t="inlineStr">
@@ -9624,12 +9620,12 @@
       </c>
       <c r="F201" s="2" t="inlineStr">
         <is>
-          <t>Do you sell goods or services? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
+          <t>Do you handle cash and payments? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
         </is>
       </c>
       <c r="G201" s="2" t="inlineStr">
         <is>
-          <t>क्या आप सामान या सेवा बेचना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप पैसे और भुगतान सँभालना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="H201" s="2" t="inlineStr">
@@ -9640,7 +9636,7 @@
       <c r="I201" s="2" t="inlineStr"/>
       <c r="J201" s="2" t="inlineStr">
         <is>
-          <t>Gathmann and Schonberg 2010; NCO 5223.0200</t>
+          <t>Autor and Handel 2013; NCO 5131.0401</t>
         </is>
       </c>
     </row>
@@ -9660,7 +9656,7 @@
       </c>
       <c r="D202" s="2" t="inlineStr">
         <is>
-          <t>tk_cash</t>
+          <t>tk_cook</t>
         </is>
       </c>
       <c r="E202" s="2" t="inlineStr">
@@ -9670,12 +9666,12 @@
       </c>
       <c r="F202" s="2" t="inlineStr">
         <is>
-          <t>Do you handle cash and payments? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
+          <t>Do you cook or prepare food or drink? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
         </is>
       </c>
       <c r="G202" s="2" t="inlineStr">
         <is>
-          <t>क्या आप पैसे और भुगतान सँभालना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप खाना या पीने की चीज़ बनाना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="H202" s="2" t="inlineStr">
@@ -9686,7 +9682,7 @@
       <c r="I202" s="2" t="inlineStr"/>
       <c r="J202" s="2" t="inlineStr">
         <is>
-          <t>Autor and Handel 2013; NCO 5131.0401</t>
+          <t>NCO 5120.0300 cook</t>
         </is>
       </c>
     </row>
@@ -9706,7 +9702,7 @@
       </c>
       <c r="D203" s="2" t="inlineStr">
         <is>
-          <t>tk_cook</t>
+          <t>tk_serve</t>
         </is>
       </c>
       <c r="E203" s="2" t="inlineStr">
@@ -9716,12 +9712,12 @@
       </c>
       <c r="F203" s="2" t="inlineStr">
         <is>
-          <t>Do you cook or prepare food or drink? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
+          <t>Do you serve guests or customers? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
         </is>
       </c>
       <c r="G203" s="2" t="inlineStr">
         <is>
-          <t>क्या आप खाना या पीने की चीज़ बनाना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप मेहमानों या ग्राहकों की सेवा करना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="H203" s="2" t="inlineStr">
@@ -9732,7 +9728,7 @@
       <c r="I203" s="2" t="inlineStr"/>
       <c r="J203" s="2" t="inlineStr">
         <is>
-          <t>NCO 5120.0300 cook</t>
+          <t>NCO 5131.0401 waiter; Pal et al. 2026</t>
         </is>
       </c>
     </row>
@@ -9752,7 +9748,7 @@
       </c>
       <c r="D204" s="2" t="inlineStr">
         <is>
-          <t>tk_serve</t>
+          <t>tk_clean</t>
         </is>
       </c>
       <c r="E204" s="2" t="inlineStr">
@@ -9762,12 +9758,12 @@
       </c>
       <c r="F204" s="2" t="inlineStr">
         <is>
-          <t>Do you serve guests or customers? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
+          <t>Do you clean rooms or public areas? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
         </is>
       </c>
       <c r="G204" s="2" t="inlineStr">
         <is>
-          <t>क्या आप मेहमानों या ग्राहकों की सेवा करना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप कमरे या सार्वजनिक जगह साफ़ करना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="H204" s="2" t="inlineStr">
@@ -9778,7 +9774,7 @@
       <c r="I204" s="2" t="inlineStr"/>
       <c r="J204" s="2" t="inlineStr">
         <is>
-          <t>NCO 5131.0401 waiter; Pal et al. 2026</t>
+          <t>NCO 5151.0202 room attendant; Autor-Levy-Murnane 2003 (janitorial)</t>
         </is>
       </c>
     </row>
@@ -9798,7 +9794,7 @@
       </c>
       <c r="D205" s="2" t="inlineStr">
         <is>
-          <t>tk_clean</t>
+          <t>tk_guide</t>
         </is>
       </c>
       <c r="E205" s="2" t="inlineStr">
@@ -9808,12 +9804,12 @@
       </c>
       <c r="F205" s="2" t="inlineStr">
         <is>
-          <t>Do you clean rooms or public areas? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
+          <t>Do you guide or explain things to visitors? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
         </is>
       </c>
       <c r="G205" s="2" t="inlineStr">
         <is>
-          <t>क्या आप कमरे या सार्वजनिक जगह साफ़ करना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप आने वालों को रास्ता या बात समझाना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="H205" s="2" t="inlineStr">
@@ -9824,7 +9820,7 @@
       <c r="I205" s="2" t="inlineStr"/>
       <c r="J205" s="2" t="inlineStr">
         <is>
-          <t>NCO 5151.0202 room attendant; Autor-Levy-Murnane 2003 (janitorial)</t>
+          <t>Gathmann and Schonberg 2010; NCO 5113.0200</t>
         </is>
       </c>
     </row>
@@ -9844,7 +9840,7 @@
       </c>
       <c r="D206" s="2" t="inlineStr">
         <is>
-          <t>tk_guide</t>
+          <t>tk_coord</t>
         </is>
       </c>
       <c r="E206" s="2" t="inlineStr">
@@ -9854,12 +9850,12 @@
       </c>
       <c r="F206" s="2" t="inlineStr">
         <is>
-          <t>Do you guide or explain things to visitors? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
+          <t>Do you coordinate work by phone, radio or signals? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
         </is>
       </c>
       <c r="G206" s="2" t="inlineStr">
         <is>
-          <t>क्या आप आने वालों को रास्ता या बात समझाना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप फ़ोन, रेडियो या इशारों से दूसरों के साथ तालमेल करना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="H206" s="2" t="inlineStr">
@@ -9870,7 +9866,7 @@
       <c r="I206" s="2" t="inlineStr"/>
       <c r="J206" s="2" t="inlineStr">
         <is>
-          <t>Gathmann and Schonberg 2010; NCO 5113.0200</t>
+          <t>NCO 8343.1700 ropeway operator</t>
         </is>
       </c>
     </row>
@@ -9890,33 +9886,37 @@
       </c>
       <c r="D207" s="2" t="inlineStr">
         <is>
-          <t>tk_coord</t>
+          <t>drove_twowheeler</t>
         </is>
       </c>
       <c r="E207" s="2" t="inlineStr">
         <is>
-          <t>select one</t>
+          <t>yes/no</t>
         </is>
       </c>
       <c r="F207" s="2" t="inlineStr">
         <is>
-          <t>Do you coordinate work by phone, radio or signals? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
+          <t>Have you ever driven a motorcycle or scooter, with or without a licence?</t>
         </is>
       </c>
       <c r="G207" s="2" t="inlineStr">
         <is>
-          <t>क्या आप फ़ोन, रेडियो या इशारों से दूसरों के साथ तालमेल करना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आपने कभी मोटरसाइकिल या स्कूटर चलाई है, लाइसेंस हो या न हो?</t>
         </is>
       </c>
       <c r="H207" s="2" t="inlineStr">
         <is>
-          <t>1 Yes, regularly in my main Yatra work | 2 Not in my main work, but done before elsewhere | 3 Never done</t>
-        </is>
-      </c>
-      <c r="I207" s="2" t="inlineStr"/>
+          <t>0 No | 1 Yes</t>
+        </is>
+      </c>
+      <c r="I207" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if tk_drive is 1 or 2</t>
+        </is>
+      </c>
       <c r="J207" s="2" t="inlineStr">
         <is>
-          <t>NCO 8343.1700 ropeway operator</t>
+          <t>Level ladder without licences: people drive without holding a licence</t>
         </is>
       </c>
     </row>
@@ -9936,7 +9936,7 @@
       </c>
       <c r="D208" s="2" t="inlineStr">
         <is>
-          <t>drove_twowheeler</t>
+          <t>drove_car</t>
         </is>
       </c>
       <c r="E208" s="2" t="inlineStr">
@@ -9946,12 +9946,12 @@
       </c>
       <c r="F208" s="2" t="inlineStr">
         <is>
-          <t>Have you ever driven a motorcycle or scooter, with or without a licence?</t>
+          <t>... a car or jeep?</t>
         </is>
       </c>
       <c r="G208" s="2" t="inlineStr">
         <is>
-          <t>क्या आपने कभी मोटरसाइकिल या स्कूटर चलाई है, लाइसेंस हो या न हो?</t>
+          <t>...कार या जीप?</t>
         </is>
       </c>
       <c r="H208" s="2" t="inlineStr">
@@ -9966,7 +9966,7 @@
       </c>
       <c r="J208" s="2" t="inlineStr">
         <is>
-          <t>Level ladder without licences: people drive without holding a licence</t>
+          <t>Level ladder without licences</t>
         </is>
       </c>
     </row>
@@ -9986,7 +9986,7 @@
       </c>
       <c r="D209" s="2" t="inlineStr">
         <is>
-          <t>drove_car</t>
+          <t>drove_heavy</t>
         </is>
       </c>
       <c r="E209" s="2" t="inlineStr">
@@ -9996,12 +9996,12 @@
       </c>
       <c r="F209" s="2" t="inlineStr">
         <is>
-          <t>... a car or jeep?</t>
+          <t>... a truck or bus?</t>
         </is>
       </c>
       <c r="G209" s="2" t="inlineStr">
         <is>
-          <t>...कार या जीप?</t>
+          <t>...ट्रक या बस?</t>
         </is>
       </c>
       <c r="H209" s="2" t="inlineStr">
@@ -10036,7 +10036,7 @@
       </c>
       <c r="D210" s="2" t="inlineStr">
         <is>
-          <t>drove_heavy</t>
+          <t>read_at_work</t>
         </is>
       </c>
       <c r="E210" s="2" t="inlineStr">
@@ -10046,12 +10046,12 @@
       </c>
       <c r="F210" s="2" t="inlineStr">
         <is>
-          <t>... a truck or bus?</t>
+          <t>In your work, do you read anything (notes, rate lists, tickets, messages)?</t>
         </is>
       </c>
       <c r="G210" s="2" t="inlineStr">
         <is>
-          <t>...ट्रक या बस?</t>
+          <t>अपने काम में क्या आप कुछ पढ़ते हैं (पर्ची, रेट लिस्ट, टिकट, मैसेज)?</t>
         </is>
       </c>
       <c r="H210" s="2" t="inlineStr">
@@ -10059,14 +10059,10 @@
           <t>0 No | 1 Yes</t>
         </is>
       </c>
-      <c r="I210" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if tk_drive is 1 or 2</t>
-        </is>
-      </c>
+      <c r="I210" s="2" t="inlineStr"/>
       <c r="J210" s="2" t="inlineStr">
         <is>
-          <t>Level ladder without licences</t>
+          <t>STEP module 6A</t>
         </is>
       </c>
     </row>
@@ -10086,7 +10082,7 @@
       </c>
       <c r="D211" s="2" t="inlineStr">
         <is>
-          <t>read_at_work</t>
+          <t>calc_at_work</t>
         </is>
       </c>
       <c r="E211" s="2" t="inlineStr">
@@ -10096,12 +10092,12 @@
       </c>
       <c r="F211" s="2" t="inlineStr">
         <is>
-          <t>In your work, do you read anything (notes, rate lists, tickets, messages)?</t>
+          <t>In your work, do you work out prices or costs?</t>
         </is>
       </c>
       <c r="G211" s="2" t="inlineStr">
         <is>
-          <t>अपने काम में क्या आप कुछ पढ़ते हैं (पर्ची, रेट लिस्ट, टिकट, मैसेज)?</t>
+          <t>अपने काम में क्या आप दाम या ख़र्चा जोड़ते-घटाते हैं?</t>
         </is>
       </c>
       <c r="H211" s="2" t="inlineStr">
@@ -10116,54 +10112,8 @@
         </is>
       </c>
     </row>
-    <row r="212">
-      <c r="A212" s="2" t="n">
-        <v>211</v>
-      </c>
-      <c r="B212" s="2" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="C212" s="2" t="inlineStr">
-        <is>
-          <t>Tasks and skills (short block)</t>
-        </is>
-      </c>
-      <c r="D212" s="2" t="inlineStr">
-        <is>
-          <t>calc_at_work</t>
-        </is>
-      </c>
-      <c r="E212" s="2" t="inlineStr">
-        <is>
-          <t>yes/no</t>
-        </is>
-      </c>
-      <c r="F212" s="2" t="inlineStr">
-        <is>
-          <t>In your work, do you work out prices or costs?</t>
-        </is>
-      </c>
-      <c r="G212" s="2" t="inlineStr">
-        <is>
-          <t>अपने काम में क्या आप दाम या ख़र्चा जोड़ते-घटाते हैं?</t>
-        </is>
-      </c>
-      <c r="H212" s="2" t="inlineStr">
-        <is>
-          <t>0 No | 1 Yes</t>
-        </is>
-      </c>
-      <c r="I212" s="2" t="inlineStr"/>
-      <c r="J212" s="2" t="inlineStr">
-        <is>
-          <t>STEP module 6A</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J212"/>
+  <autoFilter ref="A1:J211"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -14129,7 +14079,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C133"/>
+  <dimension ref="A1:C132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="78" customWidth="1" min="1" max="1"/>
@@ -15672,7 +15622,7 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>Project design (anchors the magnitude and timing pair)</t>
+          <t>Ligon and Schechter 2003; Dercon and Krishnan 2000 (VER needs shock magnitude, not only incidence)</t>
         </is>
       </c>
       <c r="B103" s="2" t="n">
@@ -15680,14 +15630,14 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>shock_worst</t>
+          <t>shock_loss_amount</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>Ligon and Schechter 2003; Dercon and Krishnan 2000 (VER needs shock magnitude, not only incidence)</t>
+          <t>Dercon and Krishnan 2000 (seasonal timing of shocks); project design</t>
         </is>
       </c>
       <c r="B104" s="2" t="n">
@@ -15695,14 +15645,14 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>shock_loss_amount</t>
+          <t>shock_month</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>Dercon and Krishnan 2000 (seasonal timing of shocks); project design</t>
+          <t>Coping strategies in VEP studies; Carter and Zimmerman 2000 on asset versus consumption smoothing</t>
         </is>
       </c>
       <c r="B105" s="2" t="n">
@@ -15710,14 +15660,14 @@
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>shock_month</t>
+          <t>shock_coping</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>Coping strategies in VEP studies; Carter and Zimmerman 2000 on asset versus consumption smoothing</t>
+          <t>Project design (see tasks_module W4: exposure must be asked directly)</t>
         </is>
       </c>
       <c r="B106" s="2" t="n">
@@ -15725,14 +15675,14 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>shock_coping</t>
+          <t>trek_dependent</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>Project design (see tasks_module W4: exposure must be asked directly)</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q5 (all eleven categories, with its own three-way routing)</t>
         </is>
       </c>
       <c r="B107" s="2" t="n">
@@ -15740,14 +15690,14 @@
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>trek_dependent</t>
+          <t>job_situation</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q5 (all eleven categories, with its own three-way routing)</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q9</t>
         </is>
       </c>
       <c r="B108" s="2" t="n">
@@ -15755,14 +15705,14 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>job_situation</t>
+          <t>job_permanence</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q9</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q11</t>
         </is>
       </c>
       <c r="B109" s="2" t="n">
@@ -15770,14 +15720,14 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>job_permanence</t>
+          <t>contract_status</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q11</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q12 (widened to local registrations)</t>
         </is>
       </c>
       <c r="B110" s="2" t="n">
@@ -15785,14 +15735,14 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>contract_status</t>
+          <t>workplace_registered</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q12 (widened to local registrations)</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q16</t>
         </is>
       </c>
       <c r="B111" s="2" t="n">
@@ -15800,14 +15750,14 @@
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>workplace_registered</t>
+          <t>pension_contrib</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q16</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q17</t>
         </is>
       </c>
       <c r="B112" s="2" t="n">
@@ -15815,14 +15765,14 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>pension_contrib</t>
+          <t>work_health_ins</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q17</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q18</t>
         </is>
       </c>
       <c r="B113" s="2" t="n">
@@ -15830,14 +15780,14 @@
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>work_health_ins</t>
+          <t>leave_rights</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q18</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q19</t>
         </is>
       </c>
       <c r="B114" s="2" t="n">
@@ -15845,14 +15795,14 @@
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>leave_rights</t>
+          <t>injured_ever</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q19</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q20</t>
         </is>
       </c>
       <c r="B115" s="2" t="n">
@@ -15860,14 +15810,14 @@
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>injured_ever</t>
+          <t>workplace_injury_12m</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q20</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q21</t>
         </is>
       </c>
       <c r="B116" s="2" t="n">
@@ -15875,14 +15825,14 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>workplace_injury_12m</t>
+          <t>wants_more_work</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q21</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q22</t>
         </is>
       </c>
       <c r="B117" s="2" t="n">
@@ -15890,14 +15840,14 @@
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>wants_more_work</t>
+          <t>more_hours_day</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q22</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q23 (duration in weeks, tied to the calendar instead of a single point in time)</t>
         </is>
       </c>
       <c r="B118" s="2" t="n">
@@ -15905,14 +15855,14 @@
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>more_hours_day</t>
+          <t>months_looked_for_work</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q23 (duration in weeks, tied to the calendar instead of a single point in time)</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q24</t>
         </is>
       </c>
       <c r="B119" s="2" t="n">
@@ -15920,14 +15870,14 @@
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>months_looked_for_work</t>
+          <t>first_job_ever</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q24</t>
+          <t>Gathmann and Schonberg 2010; NCO 9333.0100 loader</t>
         </is>
       </c>
       <c r="B120" s="2" t="n">
@@ -15935,14 +15885,14 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>first_job_ever</t>
+          <t>tk_load</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>Gathmann and Schonberg 2010; NCO 9333.0100 loader</t>
+          <t>Spitz-Oener 2006 / STEP; NCO 8322.0100</t>
         </is>
       </c>
       <c r="B121" s="2" t="n">
@@ -15950,14 +15900,14 @@
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>tk_load</t>
+          <t>tk_drive</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>Spitz-Oener 2006 / STEP; NCO 8322.0100</t>
+          <t>Gathmann and Schonberg 2010; NCO 8343.1700 ropeway operator</t>
         </is>
       </c>
       <c r="B122" s="2" t="n">
@@ -15965,14 +15915,14 @@
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>tk_drive</t>
+          <t>tk_engine</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>Gathmann and Schonberg 2010; NCO 8343.1700 ropeway operator</t>
+          <t>Spitz-Oener 2006; NCO 7411.0301 wireman</t>
         </is>
       </c>
       <c r="B123" s="2" t="n">
@@ -15980,14 +15930,14 @@
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>tk_engine</t>
+          <t>tk_electric</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>Spitz-Oener 2006; NCO 7411.0301 wireman</t>
+          <t>Gathmann and Schonberg 2010; NCO 8343.1700</t>
         </is>
       </c>
       <c r="B124" s="2" t="n">
@@ -15995,14 +15945,14 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>tk_electric</t>
+          <t>tk_safety</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>Gathmann and Schonberg 2010; NCO 8343.1700</t>
+          <t>Gathmann and Schonberg 2010; NCO 5223.0200</t>
         </is>
       </c>
       <c r="B125" s="2" t="n">
@@ -16010,14 +15960,14 @@
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>tk_safety</t>
+          <t>tk_sell</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>Gathmann and Schonberg 2010; NCO 5223.0200</t>
+          <t>Autor and Handel 2013; NCO 5131.0401</t>
         </is>
       </c>
       <c r="B126" s="2" t="n">
@@ -16025,14 +15975,14 @@
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>tk_sell</t>
+          <t>tk_cash</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>Autor and Handel 2013; NCO 5131.0401</t>
+          <t>NCO 5120.0300 cook</t>
         </is>
       </c>
       <c r="B127" s="2" t="n">
@@ -16040,14 +15990,14 @@
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>tk_cash</t>
+          <t>tk_cook</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>NCO 5120.0300 cook</t>
+          <t>NCO 5131.0401 waiter; Pal et al. 2026</t>
         </is>
       </c>
       <c r="B128" s="2" t="n">
@@ -16055,14 +16005,14 @@
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>tk_cook</t>
+          <t>tk_serve</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>NCO 5131.0401 waiter; Pal et al. 2026</t>
+          <t>NCO 5151.0202 room attendant; Autor-Levy-Murnane 2003 (janitorial)</t>
         </is>
       </c>
       <c r="B129" s="2" t="n">
@@ -16070,14 +16020,14 @@
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>tk_serve</t>
+          <t>tk_clean</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>NCO 5151.0202 room attendant; Autor-Levy-Murnane 2003 (janitorial)</t>
+          <t>Gathmann and Schonberg 2010; NCO 5113.0200</t>
         </is>
       </c>
       <c r="B130" s="2" t="n">
@@ -16085,14 +16035,14 @@
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>tk_clean</t>
+          <t>tk_guide</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>Gathmann and Schonberg 2010; NCO 5113.0200</t>
+          <t>NCO 8343.1700 ropeway operator</t>
         </is>
       </c>
       <c r="B131" s="2" t="n">
@@ -16100,14 +16050,14 @@
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>tk_guide</t>
+          <t>tk_coord</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>NCO 8343.1700 ropeway operator</t>
+          <t>Level ladder without licences: people drive without holding a licence</t>
         </is>
       </c>
       <c r="B132" s="2" t="n">
@@ -16115,27 +16065,12 @@
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>tk_coord</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
-        <is>
-          <t>Level ladder without licences: people drive without holding a licence</t>
-        </is>
-      </c>
-      <c r="B133" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C133" s="2" t="inlineStr">
-        <is>
           <t>drove_twowheeler</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C133"/>
+  <autoFilter ref="A1:C132"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -16318,7 +16253,7 @@
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12">
@@ -16374,7 +16309,7 @@
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
   </sheetData>

--- a/replication/final_instrument/questionnaire/Question_register.xlsx
+++ b/replication/final_instrument/questionnaire/Question_register.xlsx
@@ -13,9 +13,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Modules" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Questions'!$A$1:$J$211</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Questions'!$A$1:$J$214</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Constructed variables'!$A$1:$F$131</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Literature'!$A$1:$C$132</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Literature'!$A$1:$C$135</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Modules'!$A$1:$C$15</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J211"/>
+  <dimension ref="A1:J214"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2516,7 +2516,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>income_m1</t>
+          <t>income_m5</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -2526,18 +2526,18 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>How much did you earn from all your work in January, after costs? (Rs)</t>
+          <t>How much did you earn from all your work in May, after costs? (Rs)</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>जनवरी में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
+          <t>मई में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr"/>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>Ask only if knows_monthly_income = 1; automatic 0 if status_m1 = 8 (no paid work)</t>
+          <t>Ask only if knows_monthly_income = 1; automatic 0 if status_m5 = 8 (no paid work)</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>income_m2</t>
+          <t>income_m6</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -2572,18 +2572,18 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>How much did you earn from all your work in February, after costs? (Rs)</t>
+          <t>How much did you earn from all your work in June, after costs? (Rs)</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>फ़रवरी में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
+          <t>जून में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr"/>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>Ask only if knows_monthly_income = 1; automatic 0 if status_m2 = 8 (no paid work)</t>
+          <t>Ask only if knows_monthly_income = 1; automatic 0 if status_m6 = 8 (no paid work)</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -2608,7 +2608,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>income_m3</t>
+          <t>income_m7</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -2618,18 +2618,18 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>How much did you earn from all your work in March, after costs? (Rs)</t>
+          <t>How much did you earn from all your work in July, after costs? (Rs)</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>मार्च में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
+          <t>जुलाई में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr"/>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>Ask only if knows_monthly_income = 1; automatic 0 if status_m3 = 8 (no paid work)</t>
+          <t>Ask only if knows_monthly_income = 1; automatic 0 if status_m7 = 8 (no paid work)</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -2654,7 +2654,7 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>income_m4</t>
+          <t>income_m8</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -2664,18 +2664,18 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>How much did you earn from all your work in April, after costs? (Rs)</t>
+          <t>How much did you earn from all your work in August, after costs? (Rs)</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>अप्रैल में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
+          <t>अगस्त में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr"/>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>Ask only if knows_monthly_income = 1; automatic 0 if status_m4 = 8 (no paid work)</t>
+          <t>Ask only if knows_monthly_income = 1; automatic 0 if status_m8 = 8 (no paid work)</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>income_m5</t>
+          <t>income_m9</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -2710,18 +2710,18 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>How much did you earn from all your work in May, after costs? (Rs)</t>
+          <t>How much did you earn from all your work in September, after costs? (Rs)</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>मई में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
+          <t>सितंबर में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr"/>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>Ask only if knows_monthly_income = 1; automatic 0 if status_m5 = 8 (no paid work)</t>
+          <t>Ask only if knows_monthly_income = 1; automatic 0 if status_m9 = 8 (no paid work)</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>income_m6</t>
+          <t>income_m10</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -2756,18 +2756,18 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>How much did you earn from all your work in June, after costs? (Rs)</t>
+          <t>How much did you earn from all your work in October, after costs? (Rs)</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>जून में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
+          <t>अक्टूबर में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr"/>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>Ask only if knows_monthly_income = 1; automatic 0 if status_m6 = 8 (no paid work)</t>
+          <t>Ask only if knows_monthly_income = 1; automatic 0 if status_m10 = 8 (no paid work)</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -2792,7 +2792,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>income_m7</t>
+          <t>income_m11</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -2802,18 +2802,18 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>How much did you earn from all your work in July, after costs? (Rs)</t>
+          <t>How much did you earn from all your work in November, after costs? (Rs)</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>जुलाई में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
+          <t>नवंबर में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr"/>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>Ask only if knows_monthly_income = 1; automatic 0 if status_m7 = 8 (no paid work)</t>
+          <t>Ask only if knows_monthly_income = 1; automatic 0 if status_m11 = 8 (no paid work)</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>income_m8</t>
+          <t>income_m12</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -2848,18 +2848,18 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>How much did you earn from all your work in August, after costs? (Rs)</t>
+          <t>How much did you earn from all your work in December, after costs? (Rs)</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>अगस्त में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
+          <t>दिसंबर में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr"/>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>Ask only if knows_monthly_income = 1; automatic 0 if status_m8 = 8 (no paid work)</t>
+          <t>Ask only if knows_monthly_income = 1; automatic 0 if status_m12 = 8 (no paid work)</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>income_m9</t>
+          <t>income_m1</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -2894,18 +2894,18 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>How much did you earn from all your work in September, after costs? (Rs)</t>
+          <t>How much did you earn from all your work in January, after costs? (Rs)</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>सितंबर में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
+          <t>जनवरी में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr"/>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>Ask only if knows_monthly_income = 1; automatic 0 if status_m9 = 8 (no paid work)</t>
+          <t>Ask only if knows_monthly_income = 1; automatic 0 if status_m1 = 8 (no paid work)</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>income_m10</t>
+          <t>income_m2</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -2940,18 +2940,18 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>How much did you earn from all your work in October, after costs? (Rs)</t>
+          <t>How much did you earn from all your work in February, after costs? (Rs)</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>अक्टूबर में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
+          <t>फ़रवरी में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr"/>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>Ask only if knows_monthly_income = 1; automatic 0 if status_m10 = 8 (no paid work)</t>
+          <t>Ask only if knows_monthly_income = 1; automatic 0 if status_m2 = 8 (no paid work)</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>income_m11</t>
+          <t>income_m3</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -2986,18 +2986,18 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>How much did you earn from all your work in November, after costs? (Rs)</t>
+          <t>How much did you earn from all your work in March, after costs? (Rs)</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>नवंबर में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
+          <t>मार्च में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr"/>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>Ask only if knows_monthly_income = 1; automatic 0 if status_m11 = 8 (no paid work)</t>
+          <t>Ask only if knows_monthly_income = 1; automatic 0 if status_m3 = 8 (no paid work)</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -3022,7 +3022,7 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>income_m12</t>
+          <t>income_m4</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -3032,18 +3032,18 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>How much did you earn from all your work in December, after costs? (Rs)</t>
+          <t>How much did you earn from all your work in April, after costs? (Rs)</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>दिसंबर में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
+          <t>अप्रैल में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr"/>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>Ask only if knows_monthly_income = 1; automatic 0 if status_m12 = 8 (no paid work)</t>
+          <t>Ask only if knows_monthly_income = 1; automatic 0 if status_m4 = 8 (no paid work)</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -3526,7 +3526,7 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>Which state is your permanent home in? (If it is outside India, say so.)</t>
+          <t>Which state is your permanent home in?</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -3539,7 +3539,11 @@
           <t>1 Andhra Pradesh | 2 Arunachal Pradesh | 3 Assam | 4 Bihar | 5 Chhattisgarh | 6 Goa | 7 Gujarat | 8 Haryana | 9 Himachal Pradesh | 10 Jharkhand | 11 Karnataka | 12 Kerala | 13 Madhya Pradesh | 14 Maharashtra | 15 Manipur | 16 Meghalaya | 17 Mizoram | 18 Nagaland | 19 Odisha | 20 Punjab | 21 Rajasthan | 22 Sikkim | 23 Tamil Nadu | 24 Telangana | 25 Tripura | 26 Uttar Pradesh | 27 Uttarakhand | 28 West Bengal | 29 Andaman and Nicobar Islands | 30 Chandigarh | 31 Dadra and Nagar Haveli and Daman and Diu | 32 Delhi | 33 Jammu and Kashmir | 34 Ladakh | 35 Lakshadweep | 36 Puducherry | 99 Outside India</t>
         </is>
       </c>
-      <c r="I68" s="2" t="inlineStr"/>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if origin = 3 (another Indian state)</t>
+        </is>
+      </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
           <t>Standard state/UT classification; needed to apply the right poverty line per respondent</t>
@@ -5650,7 +5654,7 @@
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>1 Own house here | 2 Rented room or house | 3 Room or dormitory the employer provides | 4 Sleeps at the shop, dhaba or workplace | 5 Tent or temporary shelter | 6 Lodge, dharamshala or ashram | 7 In the open, or a verandah | 8 Somewhere else</t>
+          <t>1 At my own usual home (I live here) | 2 Rented room or house | 3 Room or dormitory the employer provides | 4 Sleeps at the shop, dhaba or workplace | 5 Tent or temporary shelter | 6 Lodge, dharamshala or ashram | 7 In the open, or a verandah | 8 Somewhere else</t>
         </is>
       </c>
       <c r="I115" s="2" t="inlineStr"/>
@@ -6366,29 +6370,33 @@
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>land_cultivable_acres</t>
+          <t>land_unit</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>select one</t>
         </is>
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t>How much CULTIVABLE land does your household own or cultivate, in acres? Do not count the land the house stands on. (0 if none)</t>
+          <t>In what unit do you count your land -- nali, bigha, acres or hectares?</t>
         </is>
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>आपके घर के पास कितनी जोतने लायक़ ज़मीन है, अपनी या जोतने की, एकड़ में? जिस ज़मीन पर घर बना है उसे मत गिनिए। (न हो तो 0)</t>
-        </is>
-      </c>
-      <c r="H131" s="2" t="inlineStr"/>
+          <t>आप अपनी ज़मीन किस हिसाब से गिनते हैं — नाली, बीघा, एकड़ या हेक्टेयर?</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t>1 Nali | 2 Bigha | 3 Acres | 4 Hectares | 5 No land</t>
+        </is>
+      </c>
       <c r="I131" s="2" t="inlineStr"/>
       <c r="J131" s="2" t="inlineStr">
         <is>
-          <t>Chaudhuri et al. 2002 asset covariate</t>
+          <t>Project design (local land units, Uttarakhand)</t>
         </is>
       </c>
     </row>
@@ -6408,29 +6416,25 @@
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>owns_cow_buffalo</t>
+          <t>land_cultivable_acres</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>yes/no</t>
+          <t>number</t>
         </is>
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>Does your household own any cows or buffaloes?</t>
+          <t>And how much CULTIVABLE land is that? Do not count the land the house stands on.</t>
         </is>
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>क्या आपके घर में गाय या भैंस है?</t>
-        </is>
-      </c>
-      <c r="H132" s="2" t="inlineStr">
-        <is>
-          <t>0 No | 1 Yes</t>
-        </is>
-      </c>
+          <t>आपके घर के पास कितनी जोतने लायक़ ज़मीन है, अपनी या जोतने की, एकड़ में? जिस ज़मीन पर घर बना है उसे मत गिनिए। (न हो तो 0)</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="inlineStr"/>
       <c r="I132" s="2" t="inlineStr"/>
       <c r="J132" s="2" t="inlineStr">
         <is>
@@ -6454,7 +6458,7 @@
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>owns_goat_sheep</t>
+          <t>owns_cow_buffalo</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
@@ -6464,12 +6468,12 @@
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>Does your household own any goats or sheep?</t>
+          <t>Does your household own any cows or buffaloes?</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>क्या आपके घर में बकरी या भेड़ है?</t>
+          <t>क्या आपके घर में गाय या भैंस है?</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
@@ -6500,7 +6504,7 @@
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>owns_pony_mule</t>
+          <t>owns_goat_sheep</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
@@ -6510,12 +6514,12 @@
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>Does your household own any ponies or mules?</t>
+          <t>Does your household own any goats or sheep?</t>
         </is>
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>क्या आपके घर में घोड़ा या खच्चर है?</t>
+          <t>क्या आपके घर में बकरी या भेड़ है?</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">
@@ -6526,7 +6530,7 @@
       <c r="I134" s="2" t="inlineStr"/>
       <c r="J134" s="2" t="inlineStr">
         <is>
-          <t>Project design (pilot livelihood survey)</t>
+          <t>Chaudhuri et al. 2002 asset covariate</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6550,7 @@
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>owns_shop_stall</t>
+          <t>owns_pony_mule</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
@@ -6556,12 +6560,12 @@
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>Does your household own a shop or stall that you use to earn?</t>
+          <t>Does your household own any ponies or mules?</t>
         </is>
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>क्या आपके घर की अपनी दुकान या खोखा है जिससे आप कमाते हैं?</t>
+          <t>क्या आपके घर में घोड़ा या खच्चर है?</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr">
@@ -6572,7 +6576,7 @@
       <c r="I135" s="2" t="inlineStr"/>
       <c r="J135" s="2" t="inlineStr">
         <is>
-          <t>Chaudhuri et al. 2002 asset covariate</t>
+          <t>Project design (pilot livelihood survey)</t>
         </is>
       </c>
     </row>
@@ -6592,7 +6596,7 @@
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>owns_work_vehicle</t>
+          <t>owns_shop_stall</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
@@ -6602,12 +6606,12 @@
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>Does your household own a vehicle you use to earn (for example a jeep, truck or taxi)?</t>
+          <t>Does your household own a shop or stall that you use to earn?</t>
         </is>
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>क्या आपके घर की अपनी गाड़ी है जिससे आप कमाते हैं (जैसे जीप, ट्रक या टैक्सी)?</t>
+          <t>क्या आपके घर की अपनी दुकान या खोखा है जिससे आप कमाते हैं?</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr">
@@ -6638,7 +6642,7 @@
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>owns_work_equipment</t>
+          <t>owns_work_vehicle</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
@@ -6648,12 +6652,12 @@
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>Does your household own equipment or tools that you use to earn?</t>
+          <t>Does your household own a vehicle you use to earn (for example a jeep, truck or taxi)?</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>क्या आपके घर के पास काम के औज़ार या मशीन है जिससे आप कमाते हैं?</t>
+          <t>क्या आपके घर की अपनी गाड़ी है जिससे आप कमाते हैं (जैसे जीप, ट्रक या टैक्सी)?</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr">
@@ -6684,33 +6688,33 @@
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>work_equipment_detail</t>
+          <t>owns_work_equipment</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>free text</t>
+          <t>yes/no</t>
         </is>
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>What are they? Write what they say. Leave blank if they cannot say.</t>
+          <t>Does your household own equipment or tools that you use to earn?</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>वे क्या हैं? जैसा वे बताएँ वैसा लिख लीजिए। न बता पाएँ तो खाली छोड़ दीजिए।</t>
-        </is>
-      </c>
-      <c r="H138" s="2" t="inlineStr"/>
-      <c r="I138" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if owns_work_equipment = 1; may be left blank</t>
-        </is>
-      </c>
+          <t>क्या आपके घर के पास काम के औज़ार या मशीन है जिससे आप कमाते हैं?</t>
+        </is>
+      </c>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>0 No | 1 Yes</t>
+        </is>
+      </c>
+      <c r="I138" s="2" t="inlineStr"/>
       <c r="J138" s="2" t="inlineStr">
         <is>
-          <t>Standard household-survey item</t>
+          <t>Chaudhuri et al. 2002 asset covariate</t>
         </is>
       </c>
     </row>
@@ -6720,43 +6724,43 @@
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>Finance, insurance and schemes</t>
+          <t>Housing, amenities and assets</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>has_bank_account</t>
+          <t>work_equipment_detail</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>yes/no</t>
+          <t>free text</t>
         </is>
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>Does anyone in your household have a bank account or a post office account?</t>
+          <t>What are they? Write what they say. Leave blank if they cannot say.</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>क्या आपके घर में किसी का बैंक खाता या डाकघर का खाता है?</t>
-        </is>
-      </c>
-      <c r="H139" s="2" t="inlineStr">
-        <is>
-          <t>0 No | 1 Yes</t>
-        </is>
-      </c>
-      <c r="I139" s="2" t="inlineStr"/>
+          <t>वे क्या हैं? जैसा वे बताएँ वैसा लिख लीजिए। न बता पाएँ तो खाली छोड़ दीजिए।</t>
+        </is>
+      </c>
+      <c r="H139" s="2" t="inlineStr"/>
+      <c r="I139" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if owns_work_equipment = 1; may be left blank</t>
+        </is>
+      </c>
       <c r="J139" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI bank-account indicator; VEP adaptive-capacity covariate</t>
+          <t>Standard household-survey item</t>
         </is>
       </c>
     </row>
@@ -6776,7 +6780,7 @@
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>took_loan_12m</t>
+          <t>has_bank_account</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
@@ -6786,12 +6790,12 @@
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>In the last 12 months, did you or anyone in your household borrow money?</t>
+          <t>Does anyone in your household have a bank account or a post office account?</t>
         </is>
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>पिछले 12 महीनों में क्या आपने या आपके घर के किसी सदस्य ने पैसा उधार लिया?</t>
+          <t>क्या आपके घर में किसी का बैंक खाता या डाकघर का खाता है?</t>
         </is>
       </c>
       <c r="H140" s="2" t="inlineStr">
@@ -6802,7 +6806,7 @@
       <c r="I140" s="2" t="inlineStr"/>
       <c r="J140" s="2" t="inlineStr">
         <is>
-          <t>VEP adaptive-capacity covariate</t>
+          <t>NITI Aayog National MPI bank-account indicator; VEP adaptive-capacity covariate</t>
         </is>
       </c>
     </row>
@@ -6822,37 +6826,33 @@
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>credit_source</t>
+          <t>took_loan_12m</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>select one</t>
+          <t>yes/no</t>
         </is>
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t>Who was the main lender?</t>
+          <t>In the last 12 months, did you or anyone in your household borrow money?</t>
         </is>
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>मुख्य रूप से किससे उधार लिया?</t>
+          <t>पिछले 12 महीनों में क्या आपने या आपके घर के किसी सदस्य ने पैसा उधार लिया?</t>
         </is>
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
-          <t>1 Nationalised or public-sector bank | 2 Private bank | 3 Cooperative bank or RRB | 4 Microfinance institution or SHG | 5 Moneylender | 6 Relative or friend | 7 Employer or contractor (advance) | 8 Other</t>
-        </is>
-      </c>
-      <c r="I141" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if took_loan_12m = 1</t>
-        </is>
-      </c>
+          <t>0 No | 1 Yes</t>
+        </is>
+      </c>
+      <c r="I141" s="2" t="inlineStr"/>
       <c r="J141" s="2" t="inlineStr">
         <is>
-          <t>VEP adaptive-capacity covariate (lender type)</t>
+          <t>VEP adaptive-capacity covariate</t>
         </is>
       </c>
     </row>
@@ -6872,25 +6872,29 @@
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>loan_amount</t>
+          <t>credit_source</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>amount (Rs)</t>
+          <t>select one</t>
         </is>
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>How much of that loan is still left to repay? (Rs)</t>
+          <t>Who was the main lender?</t>
         </is>
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>उस क़र्ज़ में से अब भी कितना चुकाना बाक़ी है? (रुपये)</t>
-        </is>
-      </c>
-      <c r="H142" s="2" t="inlineStr"/>
+          <t>मुख्य रूप से किससे उधार लिया?</t>
+        </is>
+      </c>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>1 Nationalised or public-sector bank | 2 Private bank | 3 Cooperative bank or RRB | 4 Microfinance institution or SHG | 5 Moneylender | 6 Relative or friend | 7 Employer or contractor (advance) | 8 Other</t>
+        </is>
+      </c>
       <c r="I142" s="2" t="inlineStr">
         <is>
           <t>Ask only if took_loan_12m = 1</t>
@@ -6898,7 +6902,7 @@
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
-          <t>Islam and Chowdhury 2025 (financial distress and household vulnerability to poverty)</t>
+          <t>VEP adaptive-capacity covariate (lender type)</t>
         </is>
       </c>
     </row>
@@ -6918,27 +6922,27 @@
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>pays_interest</t>
+          <t>loan_purpose</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>yes/no</t>
+          <t>select one</t>
         </is>
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
-          <t>Do you pay interest on it?</t>
+          <t>What did you take it for?</t>
         </is>
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>क्या आप उस पर ब्याज देते हैं?</t>
+          <t>वह क़र्ज़ आपने किस काम के लिए लिया था?</t>
         </is>
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
-          <t>0 No | 1 Yes</t>
+          <t>1 Medical or hospital costs | 2 Buying an animal, vehicle or equipment for work | 3 Shop stock or business | 4 Food or daily household needs | 5 A wedding, funeral or ceremony | 6 House building or repair | 7 Education | 8 Repaying another loan | 9 Something else</t>
         </is>
       </c>
       <c r="I143" s="2" t="inlineStr">
@@ -6948,7 +6952,7 @@
       </c>
       <c r="J143" s="2" t="inlineStr">
         <is>
-          <t>Project design (informal lending is often interest-free)</t>
+          <t>Project design (investment against distress borrowing)</t>
         </is>
       </c>
     </row>
@@ -6968,33 +6972,33 @@
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>loan_interest_per100_pm</t>
+          <t>loan_amount_borrowed</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>amount (Rs)</t>
         </is>
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>On every 100 rupees you borrowed, about how much interest do you pay in a month? (Rs; 0 if none, leave blank if not known)</t>
+          <t>How much did you borrow in total? (Rs)</t>
         </is>
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>आपने जो 100 रुपये उधार लिए, उन पर महीने का कितना ब्याज देते हैं? (रुपये; दर पता न हो तो खाली छोड़ दें)</t>
+          <t>आपने कुल कितना क़र्ज़ लिया था? (रुपये)</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr"/>
       <c r="I144" s="2" t="inlineStr">
         <is>
-          <t>Ask only if took_loan_12m = 1; may be left blank</t>
+          <t>Ask only if took_loan_12m = 1</t>
         </is>
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>Project design (informal-credit pricing as locally quoted)</t>
+          <t>Project design (loan size, for the debt-burden measures)</t>
         </is>
       </c>
     </row>
@@ -7014,29 +7018,25 @@
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>loan_against_asset</t>
+          <t>loan_amount</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>yes/no</t>
+          <t>amount (Rs)</t>
         </is>
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
-          <t>Did you have to give something as security for it -- an animal, a vehicle, jewellery, land or your business?</t>
+          <t>How much of that loan is still left to repay? (Rs)</t>
         </is>
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>क्या उसके बदले कुछ गिरवी रखना पड़ा — जानवर, गाड़ी, गहने, ज़मीन या आपका धंधा?</t>
-        </is>
-      </c>
-      <c r="H145" s="2" t="inlineStr">
-        <is>
-          <t>0 No | 1 Yes</t>
-        </is>
-      </c>
+          <t>उस क़र्ज़ में से अब भी कितना चुकाना बाक़ी है? (रुपये)</t>
+        </is>
+      </c>
+      <c r="H145" s="2" t="inlineStr"/>
       <c r="I145" s="2" t="inlineStr">
         <is>
           <t>Ask only if took_loan_12m = 1</t>
@@ -7044,7 +7044,7 @@
       </c>
       <c r="J145" s="2" t="inlineStr">
         <is>
-          <t>Carter and Zimmerman 2000; Chiwaula et al. 2011 (asset-based vulnerability)</t>
+          <t>Islam and Chowdhury 2025 (financial distress and household vulnerability to poverty)</t>
         </is>
       </c>
     </row>
@@ -7064,37 +7064,37 @@
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>loan_collateral</t>
+          <t>pays_interest</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>select one</t>
+          <t>yes/no</t>
         </is>
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t>What did you have to give as security?</t>
+          <t>Do you pay interest on it?</t>
         </is>
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>आपको क्या गिरवी रखना पड़ा?</t>
+          <t>क्या आप उस पर ब्याज देते हैं?</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
-          <t>1 Jewellery or ornaments | 2 Land | 3 Animals | 4 A vehicle | 5 Shop stock or business goods | 6 House or building | 7 Something else</t>
+          <t>0 No | 1 Yes</t>
         </is>
       </c>
       <c r="I146" s="2" t="inlineStr">
         <is>
-          <t>Ask only if loan_against_asset = 1</t>
+          <t>Ask only if took_loan_12m = 1</t>
         </is>
       </c>
       <c r="J146" s="2" t="inlineStr">
         <is>
-          <t>Carter and Zimmerman 2000; Zimmerman and Carter 2003 (asset-based coping)</t>
+          <t>Project design (informal lending is often interest-free)</t>
         </is>
       </c>
     </row>
@@ -7114,29 +7114,33 @@
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>n_health_insured</t>
+          <t>loan_interest_per100_pm</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>whole number</t>
+          <t>number</t>
         </is>
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
-          <t>How many people in your household are covered by any health insurance or health scheme, including government ones? (0 if none)</t>
+          <t>On every 100 rupees you borrowed, about how much interest do you pay in a month? (Rs; 0 if none, leave blank if not known)</t>
         </is>
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>आपके घर में कितने लोगों का कोई स्वास्थ्य बीमा या स्वास्थ्य योजना है, सरकारी भी मिलाकर? (कोई नहीं तो 0)</t>
+          <t>आपने जो 100 रुपये उधार लिए, उन पर महीने का कितना ब्याज देते हैं? (रुपये; दर पता न हो तो खाली छोड़ दें)</t>
         </is>
       </c>
       <c r="H147" s="2" t="inlineStr"/>
-      <c r="I147" s="2" t="inlineStr"/>
+      <c r="I147" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if took_loan_12m = 1; may be left blank</t>
+        </is>
+      </c>
       <c r="J147" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI health-insurance indicator; Lyons et al. 2023</t>
+          <t>Project design (informal-credit pricing as locally quoted)</t>
         </is>
       </c>
     </row>
@@ -7156,29 +7160,37 @@
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>n_life_insured</t>
+          <t>loan_against_asset</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>whole number</t>
+          <t>yes/no</t>
         </is>
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
-          <t>How many people in your household have life insurance? (0 if none)</t>
+          <t>Did you have to give something as security for it -- an animal, a vehicle, jewellery, land or your business?</t>
         </is>
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>आपके घर में कितने लोगों का जीवन बीमा है? (कोई नहीं तो 0)</t>
-        </is>
-      </c>
-      <c r="H148" s="2" t="inlineStr"/>
-      <c r="I148" s="2" t="inlineStr"/>
+          <t>क्या उसके बदले कुछ गिरवी रखना पड़ा — जानवर, गाड़ी, गहने, ज़मीन या आपका धंधा?</t>
+        </is>
+      </c>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>0 No | 1 Yes</t>
+        </is>
+      </c>
+      <c r="I148" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if took_loan_12m = 1</t>
+        </is>
+      </c>
       <c r="J148" s="2" t="inlineStr">
         <is>
-          <t>Standard household-survey item</t>
+          <t>Carter and Zimmerman 2000; Chiwaula et al. 2011 (asset-based vulnerability)</t>
         </is>
       </c>
     </row>
@@ -7198,37 +7210,37 @@
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>has_crop_insurance</t>
+          <t>loan_collateral</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>yes/no</t>
+          <t>select one</t>
         </is>
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
-          <t>Is your crop insured?</t>
+          <t>What did you have to give as security?</t>
         </is>
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>क्या आपकी फ़सल का बीमा है?</t>
+          <t>आपको क्या गिरवी रखना पड़ा?</t>
         </is>
       </c>
       <c r="H149" s="2" t="inlineStr">
         <is>
-          <t>0 No | 1 Yes</t>
+          <t>1 Jewellery or ornaments | 2 Land | 3 Animals | 4 A vehicle | 5 Shop stock or business goods | 6 House or building | 7 Something else</t>
         </is>
       </c>
       <c r="I149" s="2" t="inlineStr">
         <is>
-          <t>Ask only if land_cultivable_acres &gt; 0</t>
+          <t>Ask only if loan_against_asset = 1</t>
         </is>
       </c>
       <c r="J149" s="2" t="inlineStr">
         <is>
-          <t>Standard household-survey item</t>
+          <t>Carter and Zimmerman 2000; Zimmerman and Carter 2003 (asset-based coping)</t>
         </is>
       </c>
     </row>
@@ -7248,33 +7260,29 @@
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>govt_schemes</t>
+          <t>n_health_insured</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>select multiple</t>
+          <t>whole number</t>
         </is>
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>In the last 12 months, did your household get anything from any of these? Read the list out and check every one they say yes to.</t>
+          <t>How many people in your household are covered by any health insurance or health scheme, including government ones? (0 if none)</t>
         </is>
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>पिछले 12 महीनों में इनमें से किसी से आपके घर को कुछ मिला? सूची पढ़कर सुनाइए और जिन-जिन पर वे हाँ कहें, सब पर निशान लगाइए।</t>
-        </is>
-      </c>
-      <c r="H150" s="2" t="inlineStr">
-        <is>
-          <t>1 Ration card / PDS food grain | 2 MGNREGA work or job card | 3 Old-age, widow or disability pension | 4 PM-KISAN (farmer cash transfer) | 5 Ujjwala LPG connection | 6 PM-SYM or Atal Pension Yojana | 7 Ayushman Bharat / health insurance card | 8 Housing scheme (PMAY or state) | 9 Some other scheme | 10 None of these</t>
-        </is>
-      </c>
+          <t>आपके घर में कितने लोगों का कोई स्वास्थ्य बीमा या स्वास्थ्य योजना है, सरकारी भी मिलाकर? (कोई नहीं तो 0)</t>
+        </is>
+      </c>
+      <c r="H150" s="2" t="inlineStr"/>
       <c r="I150" s="2" t="inlineStr"/>
       <c r="J150" s="2" t="inlineStr">
         <is>
-          <t>Project design; scheme names as administered in Uttarakhand</t>
+          <t>NITI Aayog National MPI health-insurance indicator; Lyons et al. 2023</t>
         </is>
       </c>
     </row>
@@ -7294,30 +7302,26 @@
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>govt_scheme_other</t>
+          <t>n_life_insured</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>free text</t>
+          <t>whole number</t>
         </is>
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
-          <t>Which scheme was that? Write what they say.</t>
+          <t>How many people in your household have life insurance? (0 if none)</t>
         </is>
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>वह कौन सी योजना थी? जैसा वे बताएँ वैसा लिख लीजिए।</t>
+          <t>आपके घर में कितने लोगों का जीवन बीमा है? (कोई नहीं तो 0)</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr"/>
-      <c r="I151" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if govt_schemes includes 9 (Some other scheme); may be left blank</t>
-        </is>
-      </c>
+      <c r="I151" s="2" t="inlineStr"/>
       <c r="J151" s="2" t="inlineStr">
         <is>
           <t>Standard household-survey item</t>
@@ -7340,37 +7344,37 @@
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>ration_portable_here</t>
+          <t>has_crop_insurance</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>select one</t>
+          <t>yes/no</t>
         </is>
       </c>
       <c r="F152" s="2" t="inlineStr">
         <is>
-          <t>Can you draw your ration here, or only at your home place?</t>
+          <t>Is your crop insured?</t>
         </is>
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>क्या आप अपना राशन यहाँ ले सकते हैं, या सिर्फ़ अपने घर वाली जगह पर?</t>
+          <t>क्या आपकी फ़सल का बीमा है?</t>
         </is>
       </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
-          <t>1 Yes, can draw it here | 2 No, only at the home place | 3 Has never tried | 97 Does not know</t>
+          <t>0 No | 1 Yes</t>
         </is>
       </c>
       <c r="I152" s="2" t="inlineStr">
         <is>
-          <t>Ask only if govt_schemes includes 1 (ration card)</t>
+          <t>Ask only if land_cultivable_acres &gt; 0</t>
         </is>
       </c>
       <c r="J152" s="2" t="inlineStr">
         <is>
-          <t>Lyons et al. 2023, Table 2 (legal residency), adapted; One Nation One Ration Card</t>
+          <t>Standard household-survey item</t>
         </is>
       </c>
     </row>
@@ -7390,33 +7394,33 @@
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>smartphone_owned</t>
+          <t>govt_schemes</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>yes/no</t>
+          <t>select multiple</t>
         </is>
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
-          <t>Do you own a smartphone?</t>
+          <t>In the last 12 months, did your household get anything from any of these? Read the list out and check every one they say yes to.</t>
         </is>
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>क्या आपके पास स्मार्टफ़ोन है?</t>
+          <t>पिछले 12 महीनों में इनमें से किसी से आपके घर को कुछ मिला? सूची पढ़कर सुनाइए और जिन-जिन पर वे हाँ कहें, सब पर निशान लगाइए।</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr">
         <is>
-          <t>0 No | 1 Yes</t>
+          <t>1 Ration card / PDS food grain | 2 MGNREGA work or job card | 3 Old-age, widow or disability pension | 4 PM-KISAN (farmer cash transfer) | 5 Ujjwala LPG connection | 6 PM-SYM or Atal Pension Yojana | 7 Ayushman Bharat / health insurance card | 8 Housing scheme (PMAY or state) | 9 Some other scheme | 10 None of these</t>
         </is>
       </c>
       <c r="I153" s="2" t="inlineStr"/>
       <c r="J153" s="2" t="inlineStr">
         <is>
-          <t>VEP adaptive-capacity covariate; STEP digital items</t>
+          <t>Project design; scheme names as administered in Uttarakhand</t>
         </is>
       </c>
     </row>
@@ -7436,33 +7440,33 @@
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>uses_digital_payment</t>
+          <t>govt_scheme_other</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>yes/no</t>
+          <t>free text</t>
         </is>
       </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
-          <t>Do you ever use UPI or another way of paying by phone?</t>
+          <t>Which scheme was that? Write what they say.</t>
         </is>
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>क्या आप कभी UPI या फ़ोन से पैसे का लेन-देन करते हैं?</t>
-        </is>
-      </c>
-      <c r="H154" s="2" t="inlineStr">
-        <is>
-          <t>0 No | 1 Yes</t>
-        </is>
-      </c>
-      <c r="I154" s="2" t="inlineStr"/>
+          <t>वह कौन सी योजना थी? जैसा वे बताएँ वैसा लिख लीजिए।</t>
+        </is>
+      </c>
+      <c r="H154" s="2" t="inlineStr"/>
+      <c r="I154" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if govt_schemes includes 9 (Some other scheme); may be left blank</t>
+        </is>
+      </c>
       <c r="J154" s="2" t="inlineStr">
         <is>
-          <t>VEP adaptive-capacity covariate; STEP digital items</t>
+          <t>Standard household-survey item</t>
         </is>
       </c>
     </row>
@@ -7482,29 +7486,37 @@
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>n_can_transact_online</t>
+          <t>ration_portable_here</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>whole number</t>
+          <t>select one</t>
         </is>
       </c>
       <c r="F155" s="2" t="inlineStr">
         <is>
-          <t>How many people in your household can make a payment by phone themselves, without help? (0 if none)</t>
+          <t>Can you draw your ration here, or only at your home place?</t>
         </is>
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>आपके घर में कितने लोग बिना किसी की मदद के फ़ोन से पैसे भेज सकते हैं? (कोई नहीं तो 0)</t>
-        </is>
-      </c>
-      <c r="H155" s="2" t="inlineStr"/>
-      <c r="I155" s="2" t="inlineStr"/>
+          <t>क्या आप अपना राशन यहाँ ले सकते हैं, या सिर्फ़ अपने घर वाली जगह पर?</t>
+        </is>
+      </c>
+      <c r="H155" s="2" t="inlineStr">
+        <is>
+          <t>1 Yes, can draw it here | 2 No, only at the home place | 3 Has never tried | 97 Does not know</t>
+        </is>
+      </c>
+      <c r="I155" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if govt_schemes includes 1 (ration card)</t>
+        </is>
+      </c>
       <c r="J155" s="2" t="inlineStr">
         <is>
-          <t>Project design (intra-household financial capability)</t>
+          <t>Lyons et al. 2023, Table 2 (legal residency), adapted; One Nation One Ration Card</t>
         </is>
       </c>
     </row>
@@ -7514,17 +7526,17 @@
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Finance, insurance and schemes</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>morbidity_15d</t>
+          <t>smartphone_owned</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
@@ -7534,12 +7546,12 @@
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
-          <t>In the last 15 days, was anyone in your household ill?</t>
+          <t>Do you own a smartphone?</t>
         </is>
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>पिछले 15 दिनों में क्या आपके घर में कोई बीमार पड़ा?</t>
+          <t>क्या आपके पास स्मार्टफ़ोन है?</t>
         </is>
       </c>
       <c r="H156" s="2" t="inlineStr">
@@ -7550,7 +7562,7 @@
       <c r="I156" s="2" t="inlineStr"/>
       <c r="J156" s="2" t="inlineStr">
         <is>
-          <t>NSS health module (15-day recall) [source not held by this project; citation unverified as of 2026-09-28]</t>
+          <t>VEP adaptive-capacity covariate; STEP digital items</t>
         </is>
       </c>
     </row>
@@ -7560,47 +7572,43 @@
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Finance, insurance and schemes</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>morbidity_coping_15d</t>
+          <t>uses_digital_payment</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>select one</t>
+          <t>yes/no</t>
         </is>
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
-          <t>How did the household mainly cope with the cost of this: used savings; borrowed money; sold or pawned assets; cut other consumption; got help from relatives or community; or something else?</t>
+          <t>Do you ever use UPI or another way of paying by phone?</t>
         </is>
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>इसका ख़र्च आपके घर ने मुख्य रूप से कैसे उठाया: जमा पैसे से; उधार लेकर; कुछ बेचकर या गिरवी रखकर; बाकी ख़र्च घटाकर; रिश्तेदारों या गाँव वालों की मदद से; या किसी और तरह?</t>
+          <t>क्या आप कभी UPI या फ़ोन से पैसे का लेन-देन करते हैं?</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
         <is>
-          <t>1 Used savings | 2 Borrowed money | 3 Sold or pawned assets | 4 Cut consumption | 5 Help from relatives/community | 6 Did nothing/other</t>
-        </is>
-      </c>
-      <c r="I157" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if morbidity_15d = 1</t>
-        </is>
-      </c>
+          <t>0 No | 1 Yes</t>
+        </is>
+      </c>
+      <c r="I157" s="2" t="inlineStr"/>
       <c r="J157" s="2" t="inlineStr">
         <is>
-          <t>Project design (a reported illness with no cost/coping follow-up said nothing about its burden)</t>
+          <t>VEP adaptive-capacity covariate; STEP digital items</t>
         </is>
       </c>
     </row>
@@ -7610,43 +7618,39 @@
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Finance, insurance and schemes</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>morbidity_cost_15d</t>
+          <t>n_can_transact_online</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>amount (Rs)</t>
+          <t>whole number</t>
         </is>
       </c>
       <c r="F158" s="2" t="inlineStr">
         <is>
-          <t>About how much did the household spend on this in the last 15 days (medicine, doctor or clinic fees, travel for care)? (Rs)</t>
+          <t>How many people in your household can make a payment by phone themselves, without help? (0 if none)</t>
         </is>
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>पिछले 15 दिनों में इस पर घर का लगभग कितना ख़र्च हुआ (दवाई, डॉक्टर या क्लीनिक की फ़ीस, आने-जाने का ख़र्च)? (रुपये)</t>
+          <t>आपके घर में कितने लोग बिना किसी की मदद के फ़ोन से पैसे भेज सकते हैं? (कोई नहीं तो 0)</t>
         </is>
       </c>
       <c r="H158" s="2" t="inlineStr"/>
-      <c r="I158" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if morbidity_15d = 1</t>
-        </is>
-      </c>
+      <c r="I158" s="2" t="inlineStr"/>
       <c r="J158" s="2" t="inlineStr">
         <is>
-          <t>Project design</t>
+          <t>Project design (intra-household financial capability)</t>
         </is>
       </c>
     </row>
@@ -7666,33 +7670,33 @@
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>func_limitation</t>
+          <t>morbidity_15d</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>select one</t>
+          <t>yes/no</t>
         </is>
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
-          <t>Do you have difficulty walking or climbing steps?</t>
+          <t>In the last 15 days, was anyone in your household ill?</t>
         </is>
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>क्या आपको चलने या सीढ़ियाँ चढ़ने में दिक़्क़त होती है?</t>
+          <t>पिछले 15 दिनों में क्या आपके घर में कोई बीमार पड़ा?</t>
         </is>
       </c>
       <c r="H159" s="2" t="inlineStr">
         <is>
-          <t>1 No difficulty | 2 Some difficulty | 3 A lot of difficulty | 4 Cannot do it at all</t>
+          <t>0 No | 1 Yes</t>
         </is>
       </c>
       <c r="I159" s="2" t="inlineStr"/>
       <c r="J159" s="2" t="inlineStr">
         <is>
-          <t>Washington Group on Disability Statistics, Short Set item 3 (mobility), verbatim; Lyons et al. 2023 health dimension</t>
+          <t>NSS health module (15-day recall) [source not held by this project; citation unverified as of 2026-09-28]</t>
         </is>
       </c>
     </row>
@@ -7712,33 +7716,37 @@
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>hospitalization_365d</t>
+          <t>morbidity_coping_15d</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>yes/no</t>
+          <t>select one</t>
         </is>
       </c>
       <c r="F160" s="2" t="inlineStr">
         <is>
-          <t>In the last 12 months, was anyone in your household admitted to hospital overnight?</t>
+          <t>How did the household mainly cope with the cost of this: used savings; borrowed money; sold or pawned assets; cut other consumption; got help from relatives or community; or something else?</t>
         </is>
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>पिछले 12 महीनों में क्या आपके घर का कोई रात भर के लिए अस्पताल में भर्ती हुआ?</t>
+          <t>इसका ख़र्च आपके घर ने मुख्य रूप से कैसे उठाया: जमा पैसे से; उधार लेकर; कुछ बेचकर या गिरवी रखकर; बाकी ख़र्च घटाकर; रिश्तेदारों या गाँव वालों की मदद से; या किसी और तरह?</t>
         </is>
       </c>
       <c r="H160" s="2" t="inlineStr">
         <is>
-          <t>0 No | 1 Yes</t>
-        </is>
-      </c>
-      <c r="I160" s="2" t="inlineStr"/>
+          <t>1 Used savings | 2 Borrowed money | 3 Sold or pawned assets | 4 Cut consumption | 5 Help from relatives/community | 6 Did nothing/other</t>
+        </is>
+      </c>
+      <c r="I160" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if morbidity_15d = 1</t>
+        </is>
+      </c>
       <c r="J160" s="2" t="inlineStr">
         <is>
-          <t>NSS health module (365-day recall) [source not held by this project; citation unverified as of 2026-09-28]</t>
+          <t>Project design (a reported illness with no cost/coping follow-up said nothing about its burden)</t>
         </is>
       </c>
     </row>
@@ -7758,33 +7766,33 @@
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>health_access_barrier_3m</t>
+          <t>morbidity_cost_15d</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>yes/no</t>
+          <t>amount (Rs)</t>
         </is>
       </c>
       <c r="F161" s="2" t="inlineStr">
         <is>
-          <t>In the last 3 months, was there a time when someone in your household needed medical care but could not get it?</t>
+          <t>About how much did the household spend on this in the last 15 days (medicine, doctor or clinic fees, travel for care)? (Rs)</t>
         </is>
       </c>
       <c r="G161" s="2" t="inlineStr">
         <is>
-          <t>पिछले 3 महीनों में क्या कभी ऐसा हुआ कि आपके घर में किसी को इलाज की ज़रूरत थी पर मिल नहीं पाया?</t>
-        </is>
-      </c>
-      <c r="H161" s="2" t="inlineStr">
-        <is>
-          <t>0 No | 1 Yes</t>
-        </is>
-      </c>
-      <c r="I161" s="2" t="inlineStr"/>
+          <t>पिछले 15 दिनों में इस पर घर का लगभग कितना ख़र्च हुआ (दवाई, डॉक्टर या क्लीनिक की फ़ीस, आने-जाने का ख़र्च)? (रुपये)</t>
+        </is>
+      </c>
+      <c r="H161" s="2" t="inlineStr"/>
+      <c r="I161" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if morbidity_15d = 1</t>
+        </is>
+      </c>
       <c r="J161" s="2" t="inlineStr">
         <is>
-          <t>VASyR 2025 barriers_health_case_access_phc_m (primary-care access barriers); Lyons et al. 2023 Table 2 indicator 2 'healthcare access'</t>
+          <t>Project design</t>
         </is>
       </c>
     </row>
@@ -7804,33 +7812,33 @@
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>child_death_5y</t>
+          <t>func_limitation</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>yes/no</t>
+          <t>select one</t>
         </is>
       </c>
       <c r="F162" s="2" t="inlineStr">
         <is>
-          <t>In the last five years, has any child or young person under 18 in your household died?</t>
+          <t>Do you have difficulty walking or climbing steps?</t>
         </is>
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>पिछले पाँच साल में क्या आपके घर के 18 साल से छोटे किसी बच्चे या किशोर की मृत्यु हुई?</t>
+          <t>क्या आपको चलने या सीढ़ियाँ चढ़ने में दिक़्क़त होती है?</t>
         </is>
       </c>
       <c r="H162" s="2" t="inlineStr">
         <is>
-          <t>0 No | 1 Yes</t>
+          <t>1 No difficulty | 2 Some difficulty | 3 A lot of difficulty | 4 Cannot do it at all</t>
         </is>
       </c>
       <c r="I162" s="2" t="inlineStr"/>
       <c r="J162" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI, Child and Adolescent Mortality (weight 1/12)</t>
+          <t>Washington Group on Disability Statistics, Short Set item 3 (mobility), verbatim; Lyons et al. 2023 health dimension</t>
         </is>
       </c>
     </row>
@@ -7850,7 +7858,7 @@
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>birth_last_5y</t>
+          <t>hospitalization_365d</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
@@ -7860,12 +7868,12 @@
       </c>
       <c r="F163" s="2" t="inlineStr">
         <is>
-          <t>In the last five years, did any woman in your household give birth?</t>
+          <t>In the last 12 months, was anyone in your household admitted to hospital overnight?</t>
         </is>
       </c>
       <c r="G163" s="2" t="inlineStr">
         <is>
-          <t>पिछले पाँच साल में क्या आपके घर की किसी महिला ने बच्चे को जन्म दिया?</t>
+          <t>पिछले 12 महीनों में क्या आपके घर का कोई रात भर के लिए अस्पताल में भर्ती हुआ?</t>
         </is>
       </c>
       <c r="H163" s="2" t="inlineStr">
@@ -7876,7 +7884,7 @@
       <c r="I163" s="2" t="inlineStr"/>
       <c r="J163" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI, Maternal Health (weight 1/12)</t>
+          <t>NSS health module (365-day recall) [source not held by this project; citation unverified as of 2026-09-28]</t>
         </is>
       </c>
     </row>
@@ -7896,37 +7904,33 @@
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>anc_4_visits</t>
+          <t>health_access_barrier_3m</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>select one</t>
+          <t>yes/no</t>
         </is>
       </c>
       <c r="F164" s="2" t="inlineStr">
         <is>
-          <t>For the most recent birth, did she have at least four check-ups before the delivery?</t>
+          <t>In the last 3 months, was there a time when someone in your household needed medical care but could not get it?</t>
         </is>
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>सबसे हाल के जन्म के लिए, क्या डिलीवरी से पहले उनकी कम से कम चार बार जाँच हुई थी?</t>
+          <t>पिछले 3 महीनों में क्या कभी ऐसा हुआ कि आपके घर में किसी को इलाज की ज़रूरत थी पर मिल नहीं पाया?</t>
         </is>
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
-          <t>0 No | 1 Yes | 97 Don't know</t>
-        </is>
-      </c>
-      <c r="I164" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if birth_last_5y = 1</t>
-        </is>
-      </c>
+          <t>0 No | 1 Yes</t>
+        </is>
+      </c>
+      <c r="I164" s="2" t="inlineStr"/>
       <c r="J164" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI, Maternal Health (antenatal care limb)</t>
+          <t>VASyR 2025 barriers_health_case_access_phc_m (primary-care access barriers); Lyons et al. 2023 Table 2 indicator 2 'healthcare access'</t>
         </is>
       </c>
     </row>
@@ -7946,37 +7950,33 @@
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t>skilled_birth_attendant</t>
+          <t>child_death_5y</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>select one</t>
+          <t>yes/no</t>
         </is>
       </c>
       <c r="F165" s="2" t="inlineStr">
         <is>
-          <t>Was that delivery done with the help of a doctor, nurse or trained midwife?</t>
+          <t>In the last five years, has any child or young person under 18 in your household died?</t>
         </is>
       </c>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>क्या वह डिलीवरी डॉक्टर, नर्स या प्रशिक्षित दाई की मदद से हुई थी?</t>
+          <t>पिछले पाँच साल में क्या आपके घर के 18 साल से छोटे किसी बच्चे या किशोर की मृत्यु हुई?</t>
         </is>
       </c>
       <c r="H165" s="2" t="inlineStr">
         <is>
-          <t>0 No | 1 Yes | 97 Don't know</t>
-        </is>
-      </c>
-      <c r="I165" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if birth_last_5y = 1</t>
-        </is>
-      </c>
+          <t>0 No | 1 Yes</t>
+        </is>
+      </c>
+      <c r="I165" s="2" t="inlineStr"/>
       <c r="J165" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI, Maternal Health (assisted delivery limb)</t>
+          <t>NITI Aayog National MPI, Child and Adolescent Mortality (weight 1/12)</t>
         </is>
       </c>
     </row>
@@ -7986,43 +7986,43 @@
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>Food security, shocks and coping</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>distress_event_last365d</t>
+          <t>birth_last_5y</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>select multiple</t>
+          <t>yes/no</t>
         </is>
       </c>
       <c r="F166" s="2" t="inlineStr">
         <is>
-          <t>In the last 12 months, did any of these happen -- to your household, or to the Yatra route you work on? Check every one that applies.</t>
+          <t>In the last five years, did any woman in your household give birth?</t>
         </is>
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>पिछले 12 महीनों में इनमें से क्या-क्या हुआ — आपके घर के साथ, या जिस यात्रा मार्ग पर आप काम करते हैं उस पर? जो-जो हुआ, सब चुनिए।</t>
+          <t>पिछले पाँच साल में क्या आपके घर की किसी महिला ने बच्चे को जन्म दिया?</t>
         </is>
       </c>
       <c r="H166" s="2" t="inlineStr">
         <is>
-          <t>9 Nothing of this kind happened | 1 Serious illness or death of an earning member | 2 Crop failure or livestock loss | 3 Damage from a natural disaster (flood, landslide, fire) | 4 Loss of business, goods or assets | 5 Road or bridge blocked, route closed | 6 Yatra stopped early or badly disrupted | 7 Sharp fall in customers or prices | 8 Lost the work or the work stopped</t>
+          <t>0 No | 1 Yes</t>
         </is>
       </c>
       <c r="I166" s="2" t="inlineStr"/>
       <c r="J166" s="2" t="inlineStr">
         <is>
-          <t>VEP exposure covariate (Azeem et al. 2016); shock inventory following Gunther and Harttgen 2009, via Fujii 2016 section 4</t>
+          <t>NITI Aayog National MPI, Maternal Health (weight 1/12)</t>
         </is>
       </c>
     </row>
@@ -8032,43 +8032,47 @@
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t>Food security, shocks and coping</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="D167" s="2" t="inlineStr">
         <is>
-          <t>shock_loss_amount</t>
+          <t>anc_4_visits</t>
         </is>
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>amount (Rs)</t>
+          <t>select one</t>
         </is>
       </c>
       <c r="F167" s="2" t="inlineStr">
         <is>
-          <t>Thinking of whichever of those hit you hardest -- about how much did your household lose in earnings, or have to spend because of it? (Rs)</t>
+          <t>For the most recent birth, did she have at least four check-ups before the delivery?</t>
         </is>
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>इनमें से जो सबसे भारी पड़ा — उसकी वजह से आपके घर की कितनी कमाई गई, या कितना ख़र्च करना पड़ा? (रुपये)</t>
-        </is>
-      </c>
-      <c r="H167" s="2" t="inlineStr"/>
+          <t>सबसे हाल के जन्म के लिए, क्या डिलीवरी से पहले उनकी कम से कम चार बार जाँच हुई थी?</t>
+        </is>
+      </c>
+      <c r="H167" s="2" t="inlineStr">
+        <is>
+          <t>0 No | 1 Yes | 97 Don't know</t>
+        </is>
+      </c>
       <c r="I167" s="2" t="inlineStr">
         <is>
-          <t>Ask only if distress_event_last365d names a real shock (not code 9, nothing happened)</t>
+          <t>Ask only if birth_last_5y = 1</t>
         </is>
       </c>
       <c r="J167" s="2" t="inlineStr">
         <is>
-          <t>Ligon and Schechter 2003; Dercon and Krishnan 2000 (VER needs shock magnitude, not only incidence)</t>
+          <t>NITI Aayog National MPI, Maternal Health (antenatal care limb)</t>
         </is>
       </c>
     </row>
@@ -8078,17 +8082,17 @@
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>Food security, shocks and coping</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>shock_month</t>
+          <t>skilled_birth_attendant</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
@@ -8098,27 +8102,27 @@
       </c>
       <c r="F168" s="2" t="inlineStr">
         <is>
-          <t>And in which month did that one happen?</t>
+          <t>Was that delivery done with the help of a doctor, nurse or trained midwife?</t>
         </is>
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>और वह किस महीने हुआ था?</t>
+          <t>क्या वह डिलीवरी डॉक्टर, नर्स या प्रशिक्षित दाई की मदद से हुई थी?</t>
         </is>
       </c>
       <c r="H168" s="2" t="inlineStr">
         <is>
-          <t>1 January | 2 February | 3 March | 4 April | 5 May | 6 June | 7 July | 8 August | 9 September | 10 October | 11 November | 12 December</t>
+          <t>0 No | 1 Yes | 97 Don't know</t>
         </is>
       </c>
       <c r="I168" s="2" t="inlineStr">
         <is>
-          <t>Ask only if distress_event_last365d names a real shock (not code 9, nothing happened)</t>
+          <t>Ask only if birth_last_5y = 1</t>
         </is>
       </c>
       <c r="J168" s="2" t="inlineStr">
         <is>
-          <t>Dercon and Krishnan 2000 (seasonal timing of shocks); project design</t>
+          <t>NITI Aayog National MPI, Maternal Health (assisted delivery limb)</t>
         </is>
       </c>
     </row>
@@ -8138,7 +8142,7 @@
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t>shock_coping</t>
+          <t>distress_event_last365d</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr">
@@ -8148,27 +8152,23 @@
       </c>
       <c r="F169" s="2" t="inlineStr">
         <is>
-          <t>How did your household manage? Check every one they used.</t>
+          <t>In the last 12 months, did any of these happen -- to your household, or to the Yatra route you work on? Check every one that applies.</t>
         </is>
       </c>
       <c r="G169" s="2" t="inlineStr">
         <is>
-          <t>आपके घर ने कैसे सँभाला? उन्होंने जो-जो किया, सब चुनिए।</t>
+          <t>पिछले 12 महीनों में इनमें से क्या-क्या हुआ — आपके घर के साथ, या जिस यात्रा मार्ग पर आप काम करते हैं उस पर? जो-जो हुआ, सब चुनिए।</t>
         </is>
       </c>
       <c r="H169" s="2" t="inlineStr">
         <is>
-          <t>1 Used savings | 2 Borrowed money | 3 Sold or pawned assets | 4 Cut consumption | 5 Help from relatives/community | 6 Did nothing/other</t>
-        </is>
-      </c>
-      <c r="I169" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if any shock was reported</t>
-        </is>
-      </c>
+          <t>9 Nothing of this kind happened | 1 Serious illness or death of an earning member | 2 Crop failure or livestock loss | 3 Damage from a natural disaster (flood, landslide, fire) | 4 Loss of business, goods or assets | 5 Road or bridge blocked, route closed | 6 Yatra stopped early or badly disrupted | 7 Sharp fall in customers or prices | 8 Lost the work or the work stopped</t>
+        </is>
+      </c>
+      <c r="I169" s="2" t="inlineStr"/>
       <c r="J169" s="2" t="inlineStr">
         <is>
-          <t>Coping strategies in VEP studies; Carter and Zimmerman 2000 on asset versus consumption smoothing</t>
+          <t>VEP exposure covariate (Azeem et al. 2016); shock inventory following Gunther and Harttgen 2009, via Fujii 2016 section 4</t>
         </is>
       </c>
     </row>
@@ -8188,29 +8188,33 @@
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>cope_less_pref_food_yatra_wk</t>
+          <t>shock_loss_amount</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>whole number</t>
+          <t>amount (Rs)</t>
         </is>
       </c>
       <c r="F170" s="2" t="inlineStr">
         <is>
-          <t>In a normal week during the Yatra season, to cope with a lack of food or money to buy it, how many days did your household rely on less expensive/less preferred food? (0-7 days)</t>
+          <t>Thinking of whichever of those hit you hardest -- what did it cost your household in all? Count both earnings lost and money spent because of it. (Rs)</t>
         </is>
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम हफ़्ते में, खाने की या खाना ख़रीदने के पैसे की कमी से निपटने के लिए आपके घर ने कितने दिन सस्ता या कम पसंद का खाना खाया? (0-7 दिन)</t>
+          <t>इनमें से जो सबसे भारी पड़ा — उससे आपके घर का कुल कितना नुक़सान हुआ? कमाई का घाटा और ख़र्च, दोनों मिलाकर। (रुपये)</t>
         </is>
       </c>
       <c r="H170" s="2" t="inlineStr"/>
-      <c r="I170" s="2" t="inlineStr"/>
+      <c r="I170" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if distress_event_last365d names a real shock (not code 9, nothing happened)</t>
+        </is>
+      </c>
       <c r="J170" s="2" t="inlineStr">
         <is>
-          <t>VASyR 2025 (exact item wording); WFP rCSI; The reduced Coping Strategy Index (rCSI): five food-coping questions, standard WFP weights (1, 2, 1, 1, 3) applied when the index is built. The Kedarnath instrument otherwise has no food-security module, which is a gap for a poverty-vulnerability survey; these five short questions close it at low cost instead of a full dietary-diversity module, left out to stay inside the 45-minute limit. Kept as day-counts (0-7), not collapsed to yes/no: this is the standard, validated WFP/FAO specification (frequency x severity), and no comparably-standard binary version was found on checking; a day-count also takes about as long to answer as a yes/no in practice, so little interview time is saved by simplifying it.</t>
+          <t>Ligon and Schechter 2003; Dercon and Krishnan 2000 (VER needs shock magnitude, not only incidence)</t>
         </is>
       </c>
     </row>
@@ -8230,29 +8234,37 @@
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t>cope_less_pref_food_offseason_wk</t>
+          <t>shock_month</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
-          <t>whole number</t>
+          <t>select one</t>
         </is>
       </c>
       <c r="F171" s="2" t="inlineStr">
         <is>
-          <t>In a normal week when the Yatra is closed, to cope with a lack of food or money to buy it, how many days did your household rely on less expensive/less preferred food? (0-7 days)</t>
+          <t>And in which month did that one happen?</t>
         </is>
       </c>
       <c r="G171" s="2" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम हफ़्ते में आपके घर ने कितने दिन सस्ता या कम पसंद का खाना खाया? (0-7 दिन)</t>
-        </is>
-      </c>
-      <c r="H171" s="2" t="inlineStr"/>
-      <c r="I171" s="2" t="inlineStr"/>
+          <t>और वह किस महीने हुआ था?</t>
+        </is>
+      </c>
+      <c r="H171" s="2" t="inlineStr">
+        <is>
+          <t>1 January | 2 February | 3 March | 4 April | 5 May | 6 June | 7 July | 8 August | 9 September | 10 October | 11 November | 12 December</t>
+        </is>
+      </c>
+      <c r="I171" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if distress_event_last365d names a real shock (not code 9, nothing happened)</t>
+        </is>
+      </c>
       <c r="J171" s="2" t="inlineStr">
         <is>
-          <t>VASyR 2025 (exact item wording); WFP rCSI; The reduced Coping Strategy Index (rCSI): five food-coping questions, standard WFP weights (1, 2, 1, 1, 3) applied when the index is built. The Kedarnath instrument otherwise has no food-security module, which is a gap for a poverty-vulnerability survey; these five short questions close it at low cost instead of a full dietary-diversity module, left out to stay inside the 45-minute limit. Kept as day-counts (0-7), not collapsed to yes/no: this is the standard, validated WFP/FAO specification (frequency x severity), and no comparably-standard binary version was found on checking; a day-count also takes about as long to answer as a yes/no in practice, so little interview time is saved by simplifying it.</t>
+          <t>Dercon and Krishnan 2000 (seasonal timing of shocks); project design</t>
         </is>
       </c>
     </row>
@@ -8272,29 +8284,37 @@
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>cope_borrow_food_yatra_wk</t>
+          <t>shock_coping</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>whole number</t>
+          <t>select multiple</t>
         </is>
       </c>
       <c r="F172" s="2" t="inlineStr">
         <is>
-          <t>In a normal week during the Yatra season, to cope with a lack of food or money to buy it, how many days did your household borrow food and/or rely on help from friends/relatives? (0-7 days)</t>
+          <t>How did your household manage? Check every one they used.</t>
         </is>
       </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम हफ़्ते में, खाने की या खाना ख़रीदने के पैसे की कमी से निपटने के लिए आपके घर ने कितने दिन खाना उधार लिया या दोस्तों/रिश्तेदारों की मदद ली? (0-7 दिन)</t>
-        </is>
-      </c>
-      <c r="H172" s="2" t="inlineStr"/>
-      <c r="I172" s="2" t="inlineStr"/>
+          <t>आपके घर ने कैसे सँभाला? उन्होंने जो-जो किया, सब चुनिए।</t>
+        </is>
+      </c>
+      <c r="H172" s="2" t="inlineStr">
+        <is>
+          <t>1 Used savings | 2 Borrowed money | 3 Sold or pawned assets | 4 Cut consumption | 5 Help from relatives/community | 6 Did nothing/other</t>
+        </is>
+      </c>
+      <c r="I172" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if any shock was reported</t>
+        </is>
+      </c>
       <c r="J172" s="2" t="inlineStr">
         <is>
-          <t>VASyR 2025 (exact item wording); WFP rCSI; The reduced Coping Strategy Index (rCSI): five food-coping questions, standard WFP weights (1, 2, 1, 1, 3) applied when the index is built. The Kedarnath instrument otherwise has no food-security module, which is a gap for a poverty-vulnerability survey; these five short questions close it at low cost instead of a full dietary-diversity module, left out to stay inside the 45-minute limit. Kept as day-counts (0-7), not collapsed to yes/no: this is the standard, validated WFP/FAO specification (frequency x severity), and no comparably-standard binary version was found on checking; a day-count also takes about as long to answer as a yes/no in practice, so little interview time is saved by simplifying it.</t>
+          <t>Coping strategies in VEP studies; Carter and Zimmerman 2000 on asset versus consumption smoothing</t>
         </is>
       </c>
     </row>
@@ -8314,7 +8334,7 @@
       </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t>cope_borrow_food_offseason_wk</t>
+          <t>cope_less_pref_food_yatra_wk</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr">
@@ -8324,12 +8344,12 @@
       </c>
       <c r="F173" s="2" t="inlineStr">
         <is>
-          <t>In a normal week when the Yatra is closed, to cope with a lack of food or money to buy it, how many days did your household borrow food and/or rely on help from friends/relatives? (0-7 days)</t>
+          <t>In a normal week during the Yatra season, to cope with a lack of food or money to buy it, how many days did your household rely on less expensive/less preferred food? (0-7 days)</t>
         </is>
       </c>
       <c r="G173" s="2" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम हफ़्ते में आपके घर ने कितने दिन खाना उधार लिया या दोस्तों/रिश्तेदारों की मदद ली? (0-7 दिन)</t>
+          <t>यात्रा के मौसम के आम हफ़्ते में, खाने की या खाना ख़रीदने के पैसे की कमी से निपटने के लिए आपके घर ने कितने दिन सस्ता या कम पसंद का खाना खाया? (0-7 दिन)</t>
         </is>
       </c>
       <c r="H173" s="2" t="inlineStr"/>
@@ -8356,7 +8376,7 @@
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>cope_reduce_meals_yatra_wk</t>
+          <t>cope_less_pref_food_offseason_wk</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
@@ -8366,12 +8386,12 @@
       </c>
       <c r="F174" s="2" t="inlineStr">
         <is>
-          <t>In a normal week during the Yatra season, to cope with a lack of food or money to buy it, how many days did your household reduce the number of meals eaten per day? (0-7 days)</t>
+          <t>In a normal week when the Yatra is closed, to cope with a lack of food or money to buy it, how many days did your household rely on less expensive/less preferred food? (0-7 days)</t>
         </is>
       </c>
       <c r="G174" s="2" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम हफ़्ते में, खाने की या खाना ख़रीदने के पैसे की कमी से निपटने के लिए आपके घर ने कितने दिन दिन में कम बार खाना खाया? (0-7 दिन)</t>
+          <t>जब यात्रा बंद रहती है, उस आम हफ़्ते में आपके घर ने कितने दिन सस्ता या कम पसंद का खाना खाया? (0-7 दिन)</t>
         </is>
       </c>
       <c r="H174" s="2" t="inlineStr"/>
@@ -8398,7 +8418,7 @@
       </c>
       <c r="D175" s="2" t="inlineStr">
         <is>
-          <t>cope_reduce_meals_offseason_wk</t>
+          <t>cope_borrow_food_yatra_wk</t>
         </is>
       </c>
       <c r="E175" s="2" t="inlineStr">
@@ -8408,12 +8428,12 @@
       </c>
       <c r="F175" s="2" t="inlineStr">
         <is>
-          <t>In a normal week when the Yatra is closed, to cope with a lack of food or money to buy it, how many days did your household reduce the number of meals eaten per day? (0-7 days)</t>
+          <t>In a normal week during the Yatra season, to cope with a lack of food or money to buy it, how many days did your household borrow food and/or rely on help from friends/relatives? (0-7 days)</t>
         </is>
       </c>
       <c r="G175" s="2" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम हफ़्ते में आपके घर ने कितने दिन दिन में कम बार खाना खाया? (0-7 दिन)</t>
+          <t>यात्रा के मौसम के आम हफ़्ते में, खाने की या खाना ख़रीदने के पैसे की कमी से निपटने के लिए आपके घर ने कितने दिन खाना उधार लिया या दोस्तों/रिश्तेदारों की मदद ली? (0-7 दिन)</t>
         </is>
       </c>
       <c r="H175" s="2" t="inlineStr"/>
@@ -8440,7 +8460,7 @@
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>cope_reduce_portion_yatra_wk</t>
+          <t>cope_borrow_food_offseason_wk</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr">
@@ -8450,12 +8470,12 @@
       </c>
       <c r="F176" s="2" t="inlineStr">
         <is>
-          <t>In a normal week during the Yatra season, to cope with a lack of food or money to buy it, how many days did your household reduce portion size of meals? (0-7 days)</t>
+          <t>In a normal week when the Yatra is closed, to cope with a lack of food or money to buy it, how many days did your household borrow food and/or rely on help from friends/relatives? (0-7 days)</t>
         </is>
       </c>
       <c r="G176" s="2" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम हफ़्ते में, खाने की या खाना ख़रीदने के पैसे की कमी से निपटने के लिए आपके घर ने कितने दिन खाने की मात्रा घटाई? (0-7 दिन)</t>
+          <t>जब यात्रा बंद रहती है, उस आम हफ़्ते में आपके घर ने कितने दिन खाना उधार लिया या दोस्तों/रिश्तेदारों की मदद ली? (0-7 दिन)</t>
         </is>
       </c>
       <c r="H176" s="2" t="inlineStr"/>
@@ -8482,7 +8502,7 @@
       </c>
       <c r="D177" s="2" t="inlineStr">
         <is>
-          <t>cope_reduce_portion_offseason_wk</t>
+          <t>cope_reduce_meals_yatra_wk</t>
         </is>
       </c>
       <c r="E177" s="2" t="inlineStr">
@@ -8492,12 +8512,12 @@
       </c>
       <c r="F177" s="2" t="inlineStr">
         <is>
-          <t>In a normal week when the Yatra is closed, to cope with a lack of food or money to buy it, how many days did your household reduce portion size of meals? (0-7 days)</t>
+          <t>In a normal week during the Yatra season, to cope with a lack of food or money to buy it, how many days did your household reduce the number of meals eaten per day? (0-7 days)</t>
         </is>
       </c>
       <c r="G177" s="2" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम हफ़्ते में आपके घर ने कितने दिन खाने की मात्रा घटाई? (0-7 दिन)</t>
+          <t>यात्रा के मौसम के आम हफ़्ते में, खाने की या खाना ख़रीदने के पैसे की कमी से निपटने के लिए आपके घर ने कितने दिन दिन में कम बार खाना खाया? (0-7 दिन)</t>
         </is>
       </c>
       <c r="H177" s="2" t="inlineStr"/>
@@ -8524,7 +8544,7 @@
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>cope_restrict_adult_yatra_wk</t>
+          <t>cope_reduce_meals_offseason_wk</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr">
@@ -8534,12 +8554,12 @@
       </c>
       <c r="F178" s="2" t="inlineStr">
         <is>
-          <t>In a normal week during the Yatra season, to cope with a lack of food or money to buy it, how many days did your household restrict consumption of adults/mothers in order for young children to eat? (0-7 days)</t>
+          <t>In a normal week when the Yatra is closed, to cope with a lack of food or money to buy it, how many days did your household reduce the number of meals eaten per day? (0-7 days)</t>
         </is>
       </c>
       <c r="G178" s="2" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम हफ़्ते में, खाने की या खाना ख़रीदने के पैसे की कमी से निपटने के लिए आपके घर ने कितने दिन बड़ों ने कम खाया ताकि छोटे बच्चे खा सकें? (0-7 दिन)</t>
+          <t>जब यात्रा बंद रहती है, उस आम हफ़्ते में आपके घर ने कितने दिन दिन में कम बार खाना खाया? (0-7 दिन)</t>
         </is>
       </c>
       <c r="H178" s="2" t="inlineStr"/>
@@ -8566,7 +8586,7 @@
       </c>
       <c r="D179" s="2" t="inlineStr">
         <is>
-          <t>cope_restrict_adult_offseason_wk</t>
+          <t>cope_reduce_portion_yatra_wk</t>
         </is>
       </c>
       <c r="E179" s="2" t="inlineStr">
@@ -8576,12 +8596,12 @@
       </c>
       <c r="F179" s="2" t="inlineStr">
         <is>
-          <t>In a normal week when the Yatra is closed, to cope with a lack of food or money to buy it, how many days did your household restrict consumption of adults/mothers in order for young children to eat? (0-7 days)</t>
+          <t>In a normal week during the Yatra season, to cope with a lack of food or money to buy it, how many days did your household reduce portion size of meals? (0-7 days)</t>
         </is>
       </c>
       <c r="G179" s="2" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम हफ़्ते में आपके घर ने कितने दिन बड़ों ने कम खाया ताकि छोटे बच्चे खा सकें? (0-7 दिन)</t>
+          <t>यात्रा के मौसम के आम हफ़्ते में, खाने की या खाना ख़रीदने के पैसे की कमी से निपटने के लिए आपके घर ने कितने दिन खाने की मात्रा घटाई? (0-7 दिन)</t>
         </is>
       </c>
       <c r="H179" s="2" t="inlineStr"/>
@@ -8598,43 +8618,39 @@
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>Ropeway</t>
+          <t>Food security, shocks and coping</t>
         </is>
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>ropeway_stance</t>
+          <t>cope_reduce_portion_offseason_wk</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>select one</t>
+          <t>whole number</t>
         </is>
       </c>
       <c r="F180" s="2" t="inlineStr">
         <is>
-          <t>A ropeway is proposed between Gaurikund and Kedarnath. Are you in favour, neutral, or against?</t>
+          <t>In a normal week when the Yatra is closed, to cope with a lack of food or money to buy it, how many days did your household reduce portion size of meals? (0-7 days)</t>
         </is>
       </c>
       <c r="G180" s="2" t="inlineStr">
         <is>
-          <t>गौरीकुंड से केदारनाथ तक रोपवे बनाने की बात चल रही है। आप इसके पक्ष में हैं, बीच में हैं, या ख़िलाफ़ हैं?</t>
-        </is>
-      </c>
-      <c r="H180" s="2" t="inlineStr">
-        <is>
-          <t>1 Support | 2 Neutral | 3 Oppose | 98 Prefer not to say</t>
-        </is>
-      </c>
+          <t>जब यात्रा बंद रहती है, उस आम हफ़्ते में आपके घर ने कितने दिन खाने की मात्रा घटाई? (0-7 दिन)</t>
+        </is>
+      </c>
+      <c r="H180" s="2" t="inlineStr"/>
       <c r="I180" s="2" t="inlineStr"/>
       <c r="J180" s="2" t="inlineStr">
         <is>
-          <t>Project design</t>
+          <t>VASyR 2025 (exact item wording); WFP rCSI; The reduced Coping Strategy Index (rCSI): five food-coping questions, standard WFP weights (1, 2, 1, 1, 3) applied when the index is built. The Kedarnath instrument otherwise has no food-security module, which is a gap for a poverty-vulnerability survey; these five short questions close it at low cost instead of a full dietary-diversity module, left out to stay inside the 45-minute limit. Kept as day-counts (0-7), not collapsed to yes/no: this is the standard, validated WFP/FAO specification (frequency x severity), and no comparably-standard binary version was found on checking; a day-count also takes about as long to answer as a yes/no in practice, so little interview time is saved by simplifying it.</t>
         </is>
       </c>
     </row>
@@ -8644,43 +8660,39 @@
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t>Ropeway</t>
+          <t>Food security, shocks and coping</t>
         </is>
       </c>
       <c r="D181" s="2" t="inlineStr">
         <is>
-          <t>trek_dependent</t>
+          <t>cope_restrict_adult_yatra_wk</t>
         </is>
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
-          <t>yes/no</t>
+          <t>whole number</t>
         </is>
       </c>
       <c r="F181" s="2" t="inlineStr">
         <is>
-          <t>Is your main Yatra work carrying, transporting or guiding people or goods on the Gaurikund to Kedarnath trek?</t>
+          <t>In a normal week during the Yatra season, to cope with a lack of food or money to buy it, how many days did your household restrict consumption of adults/mothers in order for young children to eat? (0-7 days)</t>
         </is>
       </c>
       <c r="G181" s="2" t="inlineStr">
         <is>
-          <t>क्या आपका मुख्य यात्रा-काम गौरीकुंड से केदारनाथ के पैदल रास्ते पर लोगों या सामान को ले जाना, पहुँचाना या रास्ता दिखाना है?</t>
-        </is>
-      </c>
-      <c r="H181" s="2" t="inlineStr">
-        <is>
-          <t>0 No | 1 Yes</t>
-        </is>
-      </c>
+          <t>यात्रा के मौसम के आम हफ़्ते में, खाने की या खाना ख़रीदने के पैसे की कमी से निपटने के लिए आपके घर ने कितने दिन बड़ों ने कम खाया ताकि छोटे बच्चे खा सकें? (0-7 दिन)</t>
+        </is>
+      </c>
+      <c r="H181" s="2" t="inlineStr"/>
       <c r="I181" s="2" t="inlineStr"/>
       <c r="J181" s="2" t="inlineStr">
         <is>
-          <t>Project design (see tasks_module W4: exposure must be asked directly)</t>
+          <t>VASyR 2025 (exact item wording); WFP rCSI; The reduced Coping Strategy Index (rCSI): five food-coping questions, standard WFP weights (1, 2, 1, 1, 3) applied when the index is built. The Kedarnath instrument otherwise has no food-security module, which is a gap for a poverty-vulnerability survey; these five short questions close it at low cost instead of a full dietary-diversity module, left out to stay inside the 45-minute limit. Kept as day-counts (0-7), not collapsed to yes/no: this is the standard, validated WFP/FAO specification (frequency x severity), and no comparably-standard binary version was found on checking; a day-count also takes about as long to answer as a yes/no in practice, so little interview time is saved by simplifying it.</t>
         </is>
       </c>
     </row>
@@ -8690,43 +8702,39 @@
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>Job quality (Apablaza et al. 2026 questions)</t>
+          <t>Food security, shocks and coping</t>
         </is>
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>job_situation</t>
+          <t>cope_restrict_adult_offseason_wk</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>select one</t>
+          <t>whole number</t>
         </is>
       </c>
       <c r="F182" s="2" t="inlineStr">
         <is>
-          <t>Which best describes your situation during the last month: you work for pay full-time; you work for pay part-time or do occasional jobs; you study and work; you only study; you are only being trained for work; you are retired or pensioned; you do unpaid household tasks or care for others; you are unemployed and actively looking for work; you are sick or disabled and cannot work; or none of these?</t>
+          <t>In a normal week when the Yatra is closed, to cope with a lack of food or money to buy it, how many days did your household restrict consumption of adults/mothers in order for young children to eat? (0-7 days)</t>
         </is>
       </c>
       <c r="G182" s="2" t="inlineStr">
         <is>
-          <t>पिछले महीने आपकी हालत इनमें से किससे सबसे मिलती है: पूरे समय पैसे के लिए काम; कुछ समय या कभी-कभार का काम; पढ़ाई के साथ काम; सिर्फ़ पढ़ाई; सिर्फ़ काम की ट्रेनिंग; रिटायर या पेंशन पर; घर का बिना पैसे का काम या किसी की देखभाल; काम नहीं है और ढूँढ रहे हैं; बीमारी या विकलांगता से काम नहीं कर सकते; या इनमें से कुछ नहीं?</t>
-        </is>
-      </c>
-      <c r="H182" s="2" t="inlineStr">
-        <is>
-          <t>1 Works for pay full-time | 2 Works for pay part-time or occasional jobs | 3 Studies and works | 4 Only studies | 5 Being trained for work only | 6 Retired or pensioned | 7 Unpaid household tasks or caring for others | 8 Unemployed, actively seeking work | 9 Sick or disabled, cannot work | 10 Neither studying, working nor seeking work | 97 Does not know</t>
-        </is>
-      </c>
+          <t>जब यात्रा बंद रहती है, उस आम हफ़्ते में आपके घर ने कितने दिन बड़ों ने कम खाया ताकि छोटे बच्चे खा सकें? (0-7 दिन)</t>
+        </is>
+      </c>
+      <c r="H182" s="2" t="inlineStr"/>
       <c r="I182" s="2" t="inlineStr"/>
       <c r="J182" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q5 (all eleven categories, with its own three-way routing)</t>
+          <t>VASyR 2025 (exact item wording); WFP rCSI; The reduced Coping Strategy Index (rCSI): five food-coping questions, standard WFP weights (1, 2, 1, 1, 3) applied when the index is built. The Kedarnath instrument otherwise has no food-security module, which is a gap for a poverty-vulnerability survey; these five short questions close it at low cost instead of a full dietary-diversity module, left out to stay inside the 45-minute limit. Kept as day-counts (0-7), not collapsed to yes/no: this is the standard, validated WFP/FAO specification (frequency x severity), and no comparably-standard binary version was found on checking; a day-count also takes about as long to answer as a yes/no in practice, so little interview time is saved by simplifying it.</t>
         </is>
       </c>
     </row>
@@ -8736,17 +8744,17 @@
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t>Job quality (Apablaza et al. 2026 questions)</t>
+          <t>Ropeway</t>
         </is>
       </c>
       <c r="D183" s="2" t="inlineStr">
         <is>
-          <t>job_permanence</t>
+          <t>ropeway_stance</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr">
@@ -8756,27 +8764,23 @@
       </c>
       <c r="F183" s="2" t="inlineStr">
         <is>
-          <t>Is your job: permanent; seasonal or temporary; occasional or casual; on probation; or fixed-term?</t>
+          <t>A ropeway is proposed between Gaurikund and Kedarnath. Are you in favour, neutral, or against?</t>
         </is>
       </c>
       <c r="G183" s="2" t="inlineStr">
         <is>
-          <t>आपका काम कैसा है: पक्का; मौसमी या कुछ समय का; कभी-कभार का; परखने की अवधि पर; या तय समय के लिए?</t>
+          <t>गौरीकुंड से केदारनाथ तक रोपवे बनाने की बात चल रही है। आप इसके पक्ष में हैं, बीच में हैं, या ख़िलाफ़ हैं?</t>
         </is>
       </c>
       <c r="H183" s="2" t="inlineStr">
         <is>
-          <t>1 Permanent | 2 Seasonal or temporary | 3 Occasional or casual | 4 On probation | 5 Fixed-term</t>
-        </is>
-      </c>
-      <c r="I183" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if job_situation is 1, 2 or 3 (currently working)</t>
-        </is>
-      </c>
+          <t>1 Support | 2 Neutral | 3 Oppose | 98 Prefer not to say</t>
+        </is>
+      </c>
+      <c r="I183" s="2" t="inlineStr"/>
       <c r="J183" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q9</t>
+          <t>Project design</t>
         </is>
       </c>
     </row>
@@ -8786,47 +8790,43 @@
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>Job quality (Apablaza et al. 2026 questions)</t>
+          <t>Ropeway</t>
         </is>
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t>contract_status</t>
+          <t>trek_dependent</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>select one</t>
+          <t>yes/no</t>
         </is>
       </c>
       <c r="F184" s="2" t="inlineStr">
         <is>
-          <t>Do you have a signed contract? Yes, signed; yes but not yet signed; no contract.</t>
+          <t>Is your main Yatra work carrying, transporting or guiding people or goods on the Gaurikund to Kedarnath trek?</t>
         </is>
       </c>
       <c r="G184" s="2" t="inlineStr">
         <is>
-          <t>क्या आपका दस्तख़त किया हुआ अनुबंध (कॉन्ट्रैक्ट) है? हाँ, दस्तख़त किया; हाँ, पर अभी दस्तख़त नहीं हुआ; कोई अनुबंध नहीं।</t>
+          <t>क्या आपका मुख्य यात्रा-काम गौरीकुंड से केदारनाथ के पैदल रास्ते पर लोगों या सामान को ले जाना, पहुँचाना या रास्ता दिखाना है?</t>
         </is>
       </c>
       <c r="H184" s="2" t="inlineStr">
         <is>
-          <t>1 Yes, signed | 2 Yes, but not yet signed | 3 No contract</t>
-        </is>
-      </c>
-      <c r="I184" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if job_situation is 1, 2 or 3 (currently working); and employment_type is 3 or 4 (wage workers) -- self-employed skip to the next question</t>
-        </is>
-      </c>
+          <t>0 No | 1 Yes</t>
+        </is>
+      </c>
+      <c r="I184" s="2" t="inlineStr"/>
       <c r="J184" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q11</t>
+          <t>Project design (see tasks_module W4: exposure must be asked directly)</t>
         </is>
       </c>
     </row>
@@ -8846,37 +8846,33 @@
       </c>
       <c r="D185" s="2" t="inlineStr">
         <is>
-          <t>workplace_registered</t>
+          <t>job_situation</t>
         </is>
       </c>
       <c r="E185" s="2" t="inlineStr">
         <is>
-          <t>yes/no</t>
+          <t>select one</t>
         </is>
       </c>
       <c r="F185" s="2" t="inlineStr">
         <is>
-          <t>Is your workplace or business registered, for example with a taxpayer or GST number, a shop or trade licence, the Yatra registration, or a union?</t>
+          <t>Which best describes your situation during the last month: you work for pay full-time; you work for pay part-time or do occasional jobs; you study and work; you only study; you are only being trained for work; you are retired or pensioned; you do unpaid household tasks or care for others; you are unemployed and actively looking for work; you are sick or disabled and cannot work; or none of these?</t>
         </is>
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>क्या आपका काम या धंधा रजिस्टर्ड है, जैसे GST या टैक्स नंबर, दुकान का लाइसेंस, यात्रा का रजिस्ट्रेशन, या कोई यूनियन?</t>
+          <t>पिछले महीने आपकी हालत इनमें से किससे सबसे मिलती है: पूरे समय पैसे के लिए काम; कुछ समय या कभी-कभार का काम; पढ़ाई के साथ काम; सिर्फ़ पढ़ाई; सिर्फ़ काम की ट्रेनिंग; रिटायर या पेंशन पर; घर का बिना पैसे का काम या किसी की देखभाल; काम नहीं है और ढूँढ रहे हैं; बीमारी या विकलांगता से काम नहीं कर सकते; या इनमें से कुछ नहीं?</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
         <is>
-          <t>0 No | 1 Yes</t>
-        </is>
-      </c>
-      <c r="I185" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if job_situation is 1, 2 or 3 (currently working)</t>
-        </is>
-      </c>
+          <t>1 Works for pay full-time | 2 Works for pay part-time or occasional jobs | 3 Studies and works | 4 Only studies | 5 Being trained for work only | 6 Retired or pensioned | 7 Unpaid household tasks or caring for others | 8 Unemployed, actively seeking work | 9 Sick or disabled, cannot work | 10 Neither studying, working nor seeking work | 97 Does not know</t>
+        </is>
+      </c>
+      <c r="I185" s="2" t="inlineStr"/>
       <c r="J185" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q12 (widened to local registrations)</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q5 (all eleven categories, with its own three-way routing)</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8892,7 @@
       </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
-          <t>pension_contrib</t>
+          <t>job_permanence</t>
         </is>
       </c>
       <c r="E186" s="2" t="inlineStr">
@@ -8906,17 +8902,17 @@
       </c>
       <c r="F186" s="2" t="inlineStr">
         <is>
-          <t>Do you contribute to any pension system? Yes, the employer deducts it; yes, voluntarily; no.</t>
+          <t>Is your job: permanent; seasonal or temporary; occasional or casual; on probation; or fixed-term?</t>
         </is>
       </c>
       <c r="G186" s="2" t="inlineStr">
         <is>
-          <t>क्या आप किसी पेंशन में पैसा डालते हैं? हाँ, मालिक तनख़्वाह से काटता है; हाँ, अपनी मर्ज़ी से डालते हैं; नहीं।</t>
+          <t>आपका काम कैसा है: पक्का; मौसमी या कुछ समय का; कभी-कभार का; परखने की अवधि पर; या तय समय के लिए?</t>
         </is>
       </c>
       <c r="H186" s="2" t="inlineStr">
         <is>
-          <t>1 Yes, employer deducts it | 2 Yes, contributes voluntarily | 3 No</t>
+          <t>1 Permanent | 2 Seasonal or temporary | 3 Occasional or casual | 4 On probation | 5 Fixed-term</t>
         </is>
       </c>
       <c r="I186" s="2" t="inlineStr">
@@ -8926,7 +8922,7 @@
       </c>
       <c r="J186" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q16</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q9</t>
         </is>
       </c>
     </row>
@@ -8946,7 +8942,7 @@
       </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t>work_health_ins</t>
+          <t>contract_status</t>
         </is>
       </c>
       <c r="E187" s="2" t="inlineStr">
@@ -8956,27 +8952,27 @@
       </c>
       <c r="F187" s="2" t="inlineStr">
         <is>
-          <t>Do you have health insurance through your work? Yes; only private or other insurance; none; don't know.</t>
+          <t>Do you have a signed contract? Yes, signed; yes but not yet signed; no contract.</t>
         </is>
       </c>
       <c r="G187" s="2" t="inlineStr">
         <is>
-          <t>क्या काम की तरफ़ से आपका स्वास्थ्य बीमा है? हाँ; सिर्फ़ अपना या कोई और बीमा; कोई नहीं; पता नहीं।</t>
+          <t>क्या आपका दस्तख़त किया हुआ अनुबंध (कॉन्ट्रैक्ट) है? हाँ, दस्तख़त किया; हाँ, पर अभी दस्तख़त नहीं हुआ; कोई अनुबंध नहीं।</t>
         </is>
       </c>
       <c r="H187" s="2" t="inlineStr">
         <is>
-          <t>1 Yes, through work | 2 Only private or other insurance | 3 None | 4 Don't know</t>
+          <t>1 Yes, signed | 2 Yes, but not yet signed | 3 No contract</t>
         </is>
       </c>
       <c r="I187" s="2" t="inlineStr">
         <is>
-          <t>Ask only if job_situation is 1, 2 or 3 (currently working)</t>
+          <t>Ask only if job_situation is 1, 2 or 3 (currently working); and employment_type is 3 or 4 (wage workers) -- self-employed skip to the next question</t>
         </is>
       </c>
       <c r="J187" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q17</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q11</t>
         </is>
       </c>
     </row>
@@ -8996,27 +8992,27 @@
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
-          <t>leave_rights</t>
+          <t>workplace_registered</t>
         </is>
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
-          <t>select one</t>
+          <t>yes/no</t>
         </is>
       </c>
       <c r="F188" s="2" t="inlineStr">
         <is>
-          <t>Do you have the right to paid holiday, sick or maternity leave?</t>
+          <t>Is your workplace or business registered, for example with a taxpayer or GST number, a shop or trade licence, the Yatra registration, or a union?</t>
         </is>
       </c>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t>क्या आपको पैसे वाली छुट्टी मिलती है — त्योहार, बीमारी या ज़च्चगी की?</t>
+          <t>क्या आपका काम या धंधा रजिस्टर्ड है, जैसे GST या टैक्स नंबर, दुकान का लाइसेंस, यात्रा का रजिस्ट्रेशन, या कोई यूनियन?</t>
         </is>
       </c>
       <c r="H188" s="2" t="inlineStr">
         <is>
-          <t>0 No | 1 Yes | 97 Don't know</t>
+          <t>0 No | 1 Yes</t>
         </is>
       </c>
       <c r="I188" s="2" t="inlineStr">
@@ -9026,7 +9022,7 @@
       </c>
       <c r="J188" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q18</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q12 (widened to local registrations)</t>
         </is>
       </c>
     </row>
@@ -9046,7 +9042,7 @@
       </c>
       <c r="D189" s="2" t="inlineStr">
         <is>
-          <t>injured_ever</t>
+          <t>pension_contrib</t>
         </is>
       </c>
       <c r="E189" s="2" t="inlineStr">
@@ -9056,17 +9052,17 @@
       </c>
       <c r="F189" s="2" t="inlineStr">
         <is>
-          <t>Have you ever been physically injured at your workplace?</t>
+          <t>Do you contribute to any pension system? Yes, the employer deducts it; yes, voluntarily; no.</t>
         </is>
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>क्या आपको कभी काम की जगह पर चोट लगी है?</t>
+          <t>क्या आप किसी पेंशन में पैसा डालते हैं? हाँ, मालिक तनख़्वाह से काटता है; हाँ, अपनी मर्ज़ी से डालते हैं; नहीं।</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr">
         <is>
-          <t>0 No | 1 Yes | 97 Don't know</t>
+          <t>1 Yes, employer deducts it | 2 Yes, contributes voluntarily | 3 No</t>
         </is>
       </c>
       <c r="I189" s="2" t="inlineStr">
@@ -9076,7 +9072,7 @@
       </c>
       <c r="J189" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q19</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q16</t>
         </is>
       </c>
     </row>
@@ -9096,7 +9092,7 @@
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>workplace_injury_12m</t>
+          <t>work_health_ins</t>
         </is>
       </c>
       <c r="E190" s="2" t="inlineStr">
@@ -9106,17 +9102,17 @@
       </c>
       <c r="F190" s="2" t="inlineStr">
         <is>
-          <t>In the last 12 months, was anyone physically injured or killed at your workplace because of work?</t>
+          <t>Do you have health insurance through your work? Yes; only private or other insurance; none; don't know.</t>
         </is>
       </c>
       <c r="G190" s="2" t="inlineStr">
         <is>
-          <t>पिछले 12 महीनों में क्या आपके काम की जगह पर काम की वजह से किसी को चोट लगी या किसी की मौत हुई?</t>
+          <t>क्या काम की तरफ़ से आपका स्वास्थ्य बीमा है? हाँ; सिर्फ़ अपना या कोई और बीमा; कोई नहीं; पता नहीं।</t>
         </is>
       </c>
       <c r="H190" s="2" t="inlineStr">
         <is>
-          <t>0 No | 1 Yes | 97 Don't know</t>
+          <t>1 Yes, through work | 2 Only private or other insurance | 3 None | 4 Don't know</t>
         </is>
       </c>
       <c r="I190" s="2" t="inlineStr">
@@ -9126,7 +9122,7 @@
       </c>
       <c r="J190" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q20</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q17</t>
         </is>
       </c>
     </row>
@@ -9146,7 +9142,7 @@
       </c>
       <c r="D191" s="2" t="inlineStr">
         <is>
-          <t>wants_more_work</t>
+          <t>leave_rights</t>
         </is>
       </c>
       <c r="E191" s="2" t="inlineStr">
@@ -9156,12 +9152,12 @@
       </c>
       <c r="F191" s="2" t="inlineStr">
         <is>
-          <t>Would you like to work more hours than you do?</t>
+          <t>Do you have the right to paid holiday, sick or maternity leave?</t>
         </is>
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>क्या आप अभी से ज़्यादा घंटे काम करना चाहेंगे?</t>
+          <t>क्या आपको पैसे वाली छुट्टी मिलती है — त्योहार, बीमारी या ज़च्चगी की?</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
@@ -9171,12 +9167,12 @@
       </c>
       <c r="I191" s="2" t="inlineStr">
         <is>
-          <t>Ask if job_situation is 1 to 7 (Apablaza routes codes 4-7 straight to this question)</t>
+          <t>Ask only if job_situation is 1, 2 or 3 (currently working)</t>
         </is>
       </c>
       <c r="J191" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q21</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q18</t>
         </is>
       </c>
     </row>
@@ -9196,33 +9192,37 @@
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>more_hours_day</t>
+          <t>injured_ever</t>
         </is>
       </c>
       <c r="E192" s="2" t="inlineStr">
         <is>
-          <t>whole number</t>
+          <t>select one</t>
         </is>
       </c>
       <c r="F192" s="2" t="inlineStr">
         <is>
-          <t>On a working day, how many MORE hours would you like to work?</t>
+          <t>Have you ever been physically injured at your workplace?</t>
         </is>
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>काम के दिन में आप कितने घंटे और काम करना चाहेंगे?</t>
-        </is>
-      </c>
-      <c r="H192" s="2" t="inlineStr"/>
+          <t>क्या आपको कभी काम की जगह पर चोट लगी है?</t>
+        </is>
+      </c>
+      <c r="H192" s="2" t="inlineStr">
+        <is>
+          <t>0 No | 1 Yes | 97 Don't know</t>
+        </is>
+      </c>
       <c r="I192" s="2" t="inlineStr">
         <is>
-          <t>Ask if wants_more_work = 1, or if job_situation = 8 (Apablaza routes the unemployed-and-seeking category here directly)</t>
+          <t>Ask only if job_situation is 1, 2 or 3 (currently working)</t>
         </is>
       </c>
       <c r="J192" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q22</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q19</t>
         </is>
       </c>
     </row>
@@ -9242,33 +9242,37 @@
       </c>
       <c r="D193" s="2" t="inlineStr">
         <is>
-          <t>months_looked_for_work</t>
+          <t>workplace_injury_12m</t>
         </is>
       </c>
       <c r="E193" s="2" t="inlineStr">
         <is>
-          <t>whole number</t>
+          <t>select one</t>
         </is>
       </c>
       <c r="F193" s="2" t="inlineStr">
         <is>
-          <t>Across the months when you had no paid work, about how many MONTHS in total were you looking for work?</t>
+          <t>In the last 12 months, was anyone physically injured or killed at your workplace because of work?</t>
         </is>
       </c>
       <c r="G193" s="2" t="inlineStr">
         <is>
-          <t>जिन महीनों में आपके पास कोई पैसे वाला काम नहीं था, उनमें कुल मिलाकर लगभग कितने महीने आप काम ढूँढते रहे?</t>
-        </is>
-      </c>
-      <c r="H193" s="2" t="inlineStr"/>
+          <t>पिछले 12 महीनों में क्या आपके काम की जगह पर काम की वजह से किसी को चोट लगी या किसी की मौत हुई?</t>
+        </is>
+      </c>
+      <c r="H193" s="2" t="inlineStr">
+        <is>
+          <t>0 No | 1 Yes | 97 Don't know</t>
+        </is>
+      </c>
       <c r="I193" s="2" t="inlineStr">
         <is>
-          <t>Ask if any month in the calendar is 'No paid work', or if job_situation = 8</t>
+          <t>Ask only if job_situation is 1, 2 or 3 (currently working)</t>
         </is>
       </c>
       <c r="J193" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q23 (duration in weeks, tied to the calendar instead of a single point in time)</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q20</t>
         </is>
       </c>
     </row>
@@ -9288,7 +9292,7 @@
       </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
-          <t>first_job_ever</t>
+          <t>wants_more_work</t>
         </is>
       </c>
       <c r="E194" s="2" t="inlineStr">
@@ -9298,12 +9302,12 @@
       </c>
       <c r="F194" s="2" t="inlineStr">
         <is>
-          <t>Was your current work the first paid job you ever had?</t>
+          <t>Would you like to work more hours than you do?</t>
         </is>
       </c>
       <c r="G194" s="2" t="inlineStr">
         <is>
-          <t>क्या यह आपका पहला पैसे वाला काम है?</t>
+          <t>क्या आप अभी से ज़्यादा घंटे काम करना चाहेंगे?</t>
         </is>
       </c>
       <c r="H194" s="2" t="inlineStr">
@@ -9311,10 +9315,14 @@
           <t>0 No | 1 Yes | 97 Don't know</t>
         </is>
       </c>
-      <c r="I194" s="2" t="inlineStr"/>
+      <c r="I194" s="2" t="inlineStr">
+        <is>
+          <t>Ask if job_situation is 1 to 7 (Apablaza routes codes 4-7 straight to this question)</t>
+        </is>
+      </c>
       <c r="J194" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q24</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q21</t>
         </is>
       </c>
     </row>
@@ -9324,43 +9332,43 @@
       </c>
       <c r="B195" s="2" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C195" s="2" t="inlineStr">
         <is>
-          <t>Tasks and skills (short block)</t>
+          <t>Job quality (Apablaza et al. 2026 questions)</t>
         </is>
       </c>
       <c r="D195" s="2" t="inlineStr">
         <is>
-          <t>tk_load</t>
+          <t>more_hours_day</t>
         </is>
       </c>
       <c r="E195" s="2" t="inlineStr">
         <is>
-          <t>select one</t>
+          <t>whole number</t>
         </is>
       </c>
       <c r="F195" s="2" t="inlineStr">
         <is>
-          <t>Do you load, unload, stack or count goods? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
+          <t>On a working day, how many MORE hours would you like to work?</t>
         </is>
       </c>
       <c r="G195" s="2" t="inlineStr">
         <is>
-          <t>क्या आप सामान चढ़ाना-उतारना, लगाना या गिनना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
-        </is>
-      </c>
-      <c r="H195" s="2" t="inlineStr">
-        <is>
-          <t>1 Yes, regularly in my main Yatra work | 2 Not in my main work, but done before elsewhere | 3 Never done</t>
-        </is>
-      </c>
-      <c r="I195" s="2" t="inlineStr"/>
+          <t>काम के दिन में आप कितने घंटे और काम करना चाहेंगे?</t>
+        </is>
+      </c>
+      <c r="H195" s="2" t="inlineStr"/>
+      <c r="I195" s="2" t="inlineStr">
+        <is>
+          <t>Ask if wants_more_work = 1, or if job_situation = 8 (Apablaza routes the unemployed-and-seeking category here directly)</t>
+        </is>
+      </c>
       <c r="J195" s="2" t="inlineStr">
         <is>
-          <t>Gathmann and Schonberg 2010; NCO 9333.0100 loader</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q22</t>
         </is>
       </c>
     </row>
@@ -9370,43 +9378,43 @@
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>Tasks and skills (short block)</t>
+          <t>Job quality (Apablaza et al. 2026 questions)</t>
         </is>
       </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
-          <t>tk_drive</t>
+          <t>months_looked_for_work</t>
         </is>
       </c>
       <c r="E196" s="2" t="inlineStr">
         <is>
-          <t>select one</t>
+          <t>whole number</t>
         </is>
       </c>
       <c r="F196" s="2" t="inlineStr">
         <is>
-          <t>Do you drive a motor vehicle? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
+          <t>Across the months when you had no paid work, about how many MONTHS in total were you looking for work?</t>
         </is>
       </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>क्या आप गाड़ी चलाना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
-        </is>
-      </c>
-      <c r="H196" s="2" t="inlineStr">
-        <is>
-          <t>1 Yes, regularly in my main Yatra work | 2 Not in my main work, but done before elsewhere | 3 Never done</t>
-        </is>
-      </c>
-      <c r="I196" s="2" t="inlineStr"/>
+          <t>जिन महीनों में आपके पास कोई पैसे वाला काम नहीं था, उनमें कुल मिलाकर लगभग कितने महीने आप काम ढूँढते रहे?</t>
+        </is>
+      </c>
+      <c r="H196" s="2" t="inlineStr"/>
+      <c r="I196" s="2" t="inlineStr">
+        <is>
+          <t>Ask if any month in the calendar is 'No paid work', or if job_situation = 8</t>
+        </is>
+      </c>
       <c r="J196" s="2" t="inlineStr">
         <is>
-          <t>Spitz-Oener 2006 / STEP; NCO 8322.0100</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q23 (duration in weeks, tied to the calendar instead of a single point in time)</t>
         </is>
       </c>
     </row>
@@ -9416,17 +9424,17 @@
       </c>
       <c r="B197" s="2" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C197" s="2" t="inlineStr">
         <is>
-          <t>Tasks and skills (short block)</t>
+          <t>Job quality (Apablaza et al. 2026 questions)</t>
         </is>
       </c>
       <c r="D197" s="2" t="inlineStr">
         <is>
-          <t>tk_engine</t>
+          <t>first_job_ever</t>
         </is>
       </c>
       <c r="E197" s="2" t="inlineStr">
@@ -9436,23 +9444,23 @@
       </c>
       <c r="F197" s="2" t="inlineStr">
         <is>
-          <t>Do you operate an engine or machine? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
+          <t>Was your current work the first paid job you ever had?</t>
         </is>
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>क्या आप इंजन या मशीन चलाना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या यह आपका पहला पैसे वाला काम है?</t>
         </is>
       </c>
       <c r="H197" s="2" t="inlineStr">
         <is>
-          <t>1 Yes, regularly in my main Yatra work | 2 Not in my main work, but done before elsewhere | 3 Never done</t>
+          <t>0 No | 1 Yes | 97 Don't know</t>
         </is>
       </c>
       <c r="I197" s="2" t="inlineStr"/>
       <c r="J197" s="2" t="inlineStr">
         <is>
-          <t>Gathmann and Schonberg 2010; NCO 8343.1700 ropeway operator</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q24</t>
         </is>
       </c>
     </row>
@@ -9472,7 +9480,7 @@
       </c>
       <c r="D198" s="2" t="inlineStr">
         <is>
-          <t>tk_electric</t>
+          <t>tk_load</t>
         </is>
       </c>
       <c r="E198" s="2" t="inlineStr">
@@ -9482,12 +9490,12 @@
       </c>
       <c r="F198" s="2" t="inlineStr">
         <is>
-          <t>Do you do electrical or wiring work? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
+          <t xml:space="preserve">Do you load, unload, stack or count goods? </t>
         </is>
       </c>
       <c r="G198" s="2" t="inlineStr">
         <is>
-          <t>क्या आप बिजली या तार का काम करना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप सामान चढ़ाना-उतारना, लगाना या गिनना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="H198" s="2" t="inlineStr">
@@ -9498,7 +9506,7 @@
       <c r="I198" s="2" t="inlineStr"/>
       <c r="J198" s="2" t="inlineStr">
         <is>
-          <t>Spitz-Oener 2006; NCO 7411.0301 wireman</t>
+          <t>Gathmann and Schonberg 2010; NCO 9333.0100 loader</t>
         </is>
       </c>
     </row>
@@ -9518,7 +9526,7 @@
       </c>
       <c r="D199" s="2" t="inlineStr">
         <is>
-          <t>tk_safety</t>
+          <t>tk_drive</t>
         </is>
       </c>
       <c r="E199" s="2" t="inlineStr">
@@ -9528,12 +9536,12 @@
       </c>
       <c r="F199" s="2" t="inlineStr">
         <is>
-          <t>Do you check equipment or the route for safety? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
+          <t xml:space="preserve">Do you drive a motor vehicle? </t>
         </is>
       </c>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>क्या आप सामान या रास्ते की सुरक्षा जाँचना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप गाड़ी चलाना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="H199" s="2" t="inlineStr">
@@ -9544,7 +9552,7 @@
       <c r="I199" s="2" t="inlineStr"/>
       <c r="J199" s="2" t="inlineStr">
         <is>
-          <t>Gathmann and Schonberg 2010; NCO 8343.1700</t>
+          <t>Spitz-Oener 2006 / STEP; NCO 8322.0100</t>
         </is>
       </c>
     </row>
@@ -9564,7 +9572,7 @@
       </c>
       <c r="D200" s="2" t="inlineStr">
         <is>
-          <t>tk_sell</t>
+          <t>tk_engine</t>
         </is>
       </c>
       <c r="E200" s="2" t="inlineStr">
@@ -9574,12 +9582,12 @@
       </c>
       <c r="F200" s="2" t="inlineStr">
         <is>
-          <t>Do you sell goods or services? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
+          <t xml:space="preserve">Do you operate an engine or machine? </t>
         </is>
       </c>
       <c r="G200" s="2" t="inlineStr">
         <is>
-          <t>क्या आप सामान या सेवा बेचना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप इंजन या मशीन चलाना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="H200" s="2" t="inlineStr">
@@ -9590,7 +9598,7 @@
       <c r="I200" s="2" t="inlineStr"/>
       <c r="J200" s="2" t="inlineStr">
         <is>
-          <t>Gathmann and Schonberg 2010; NCO 5223.0200</t>
+          <t>Gathmann and Schonberg 2010; NCO 8343.1700 ropeway operator</t>
         </is>
       </c>
     </row>
@@ -9610,7 +9618,7 @@
       </c>
       <c r="D201" s="2" t="inlineStr">
         <is>
-          <t>tk_cash</t>
+          <t>tk_electric</t>
         </is>
       </c>
       <c r="E201" s="2" t="inlineStr">
@@ -9620,12 +9628,12 @@
       </c>
       <c r="F201" s="2" t="inlineStr">
         <is>
-          <t>Do you handle cash and payments? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
+          <t xml:space="preserve">Do you do electrical or wiring work? </t>
         </is>
       </c>
       <c r="G201" s="2" t="inlineStr">
         <is>
-          <t>क्या आप पैसे और भुगतान सँभालना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप बिजली या तार का काम करना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="H201" s="2" t="inlineStr">
@@ -9636,7 +9644,7 @@
       <c r="I201" s="2" t="inlineStr"/>
       <c r="J201" s="2" t="inlineStr">
         <is>
-          <t>Autor and Handel 2013; NCO 5131.0401</t>
+          <t>Spitz-Oener 2006; NCO 7411.0301 wireman</t>
         </is>
       </c>
     </row>
@@ -9656,7 +9664,7 @@
       </c>
       <c r="D202" s="2" t="inlineStr">
         <is>
-          <t>tk_cook</t>
+          <t>tk_safety</t>
         </is>
       </c>
       <c r="E202" s="2" t="inlineStr">
@@ -9666,12 +9674,12 @@
       </c>
       <c r="F202" s="2" t="inlineStr">
         <is>
-          <t>Do you cook or prepare food or drink? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
+          <t xml:space="preserve">Do you check equipment or the route for safety? </t>
         </is>
       </c>
       <c r="G202" s="2" t="inlineStr">
         <is>
-          <t>क्या आप खाना या पीने की चीज़ बनाना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप सामान या रास्ते की सुरक्षा जाँचना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="H202" s="2" t="inlineStr">
@@ -9682,7 +9690,7 @@
       <c r="I202" s="2" t="inlineStr"/>
       <c r="J202" s="2" t="inlineStr">
         <is>
-          <t>NCO 5120.0300 cook</t>
+          <t>Gathmann and Schonberg 2010; NCO 8343.1700</t>
         </is>
       </c>
     </row>
@@ -9702,7 +9710,7 @@
       </c>
       <c r="D203" s="2" t="inlineStr">
         <is>
-          <t>tk_serve</t>
+          <t>tk_sell</t>
         </is>
       </c>
       <c r="E203" s="2" t="inlineStr">
@@ -9712,12 +9720,12 @@
       </c>
       <c r="F203" s="2" t="inlineStr">
         <is>
-          <t>Do you serve guests or customers? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
+          <t xml:space="preserve">Do you sell goods or services? </t>
         </is>
       </c>
       <c r="G203" s="2" t="inlineStr">
         <is>
-          <t>क्या आप मेहमानों या ग्राहकों की सेवा करना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप सामान या सेवा बेचना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="H203" s="2" t="inlineStr">
@@ -9728,7 +9736,7 @@
       <c r="I203" s="2" t="inlineStr"/>
       <c r="J203" s="2" t="inlineStr">
         <is>
-          <t>NCO 5131.0401 waiter; Pal et al. 2026</t>
+          <t>Gathmann and Schonberg 2010; NCO 5223.0200</t>
         </is>
       </c>
     </row>
@@ -9748,7 +9756,7 @@
       </c>
       <c r="D204" s="2" t="inlineStr">
         <is>
-          <t>tk_clean</t>
+          <t>tk_cash</t>
         </is>
       </c>
       <c r="E204" s="2" t="inlineStr">
@@ -9758,12 +9766,12 @@
       </c>
       <c r="F204" s="2" t="inlineStr">
         <is>
-          <t>Do you clean rooms or public areas? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
+          <t xml:space="preserve">Do you handle cash and payments? </t>
         </is>
       </c>
       <c r="G204" s="2" t="inlineStr">
         <is>
-          <t>क्या आप कमरे या सार्वजनिक जगह साफ़ करना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप पैसे और भुगतान सँभालना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="H204" s="2" t="inlineStr">
@@ -9774,7 +9782,7 @@
       <c r="I204" s="2" t="inlineStr"/>
       <c r="J204" s="2" t="inlineStr">
         <is>
-          <t>NCO 5151.0202 room attendant; Autor-Levy-Murnane 2003 (janitorial)</t>
+          <t>Autor and Handel 2013; NCO 5131.0401</t>
         </is>
       </c>
     </row>
@@ -9794,7 +9802,7 @@
       </c>
       <c r="D205" s="2" t="inlineStr">
         <is>
-          <t>tk_guide</t>
+          <t>tk_cook</t>
         </is>
       </c>
       <c r="E205" s="2" t="inlineStr">
@@ -9804,12 +9812,12 @@
       </c>
       <c r="F205" s="2" t="inlineStr">
         <is>
-          <t>Do you guide or explain things to visitors? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
+          <t xml:space="preserve">Do you cook or prepare food or drink? </t>
         </is>
       </c>
       <c r="G205" s="2" t="inlineStr">
         <is>
-          <t>क्या आप आने वालों को रास्ता या बात समझाना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप खाना या पीने की चीज़ बनाना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="H205" s="2" t="inlineStr">
@@ -9820,7 +9828,7 @@
       <c r="I205" s="2" t="inlineStr"/>
       <c r="J205" s="2" t="inlineStr">
         <is>
-          <t>Gathmann and Schonberg 2010; NCO 5113.0200</t>
+          <t>NCO 5120.0300 cook</t>
         </is>
       </c>
     </row>
@@ -9840,7 +9848,7 @@
       </c>
       <c r="D206" s="2" t="inlineStr">
         <is>
-          <t>tk_coord</t>
+          <t>tk_serve</t>
         </is>
       </c>
       <c r="E206" s="2" t="inlineStr">
@@ -9850,12 +9858,12 @@
       </c>
       <c r="F206" s="2" t="inlineStr">
         <is>
-          <t>Do you coordinate work by phone, radio or signals? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
+          <t xml:space="preserve">Do you serve guests or customers? </t>
         </is>
       </c>
       <c r="G206" s="2" t="inlineStr">
         <is>
-          <t>क्या आप फ़ोन, रेडियो या इशारों से दूसरों के साथ तालमेल करना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप मेहमानों या ग्राहकों की सेवा करना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="H206" s="2" t="inlineStr">
@@ -9866,7 +9874,7 @@
       <c r="I206" s="2" t="inlineStr"/>
       <c r="J206" s="2" t="inlineStr">
         <is>
-          <t>NCO 8343.1700 ropeway operator</t>
+          <t>NCO 5131.0401 waiter; Pal et al. 2026</t>
         </is>
       </c>
     </row>
@@ -9886,37 +9894,33 @@
       </c>
       <c r="D207" s="2" t="inlineStr">
         <is>
-          <t>drove_twowheeler</t>
+          <t>tk_clean</t>
         </is>
       </c>
       <c r="E207" s="2" t="inlineStr">
         <is>
-          <t>yes/no</t>
+          <t>select one</t>
         </is>
       </c>
       <c r="F207" s="2" t="inlineStr">
         <is>
-          <t>Have you ever driven a motorcycle or scooter, with or without a licence?</t>
+          <t xml:space="preserve">Do you clean rooms or public areas? </t>
         </is>
       </c>
       <c r="G207" s="2" t="inlineStr">
         <is>
-          <t>क्या आपने कभी मोटरसाइकिल या स्कूटर चलाई है, लाइसेंस हो या न हो?</t>
+          <t>क्या आप कमरे या सार्वजनिक जगह साफ़ करना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="H207" s="2" t="inlineStr">
         <is>
-          <t>0 No | 1 Yes</t>
-        </is>
-      </c>
-      <c r="I207" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if tk_drive is 1 or 2</t>
-        </is>
-      </c>
+          <t>1 Yes, regularly in my main Yatra work | 2 Not in my main work, but done before elsewhere | 3 Never done</t>
+        </is>
+      </c>
+      <c r="I207" s="2" t="inlineStr"/>
       <c r="J207" s="2" t="inlineStr">
         <is>
-          <t>Level ladder without licences: people drive without holding a licence</t>
+          <t>NCO 5151.0202 room attendant; Autor-Levy-Murnane 2003 (janitorial)</t>
         </is>
       </c>
     </row>
@@ -9936,37 +9940,33 @@
       </c>
       <c r="D208" s="2" t="inlineStr">
         <is>
-          <t>drove_car</t>
+          <t>tk_guide</t>
         </is>
       </c>
       <c r="E208" s="2" t="inlineStr">
         <is>
-          <t>yes/no</t>
+          <t>select one</t>
         </is>
       </c>
       <c r="F208" s="2" t="inlineStr">
         <is>
-          <t>... a car or jeep?</t>
+          <t xml:space="preserve">Do you guide or explain things to visitors? </t>
         </is>
       </c>
       <c r="G208" s="2" t="inlineStr">
         <is>
-          <t>...कार या जीप?</t>
+          <t>क्या आप आने वालों को रास्ता या बात समझाना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="H208" s="2" t="inlineStr">
         <is>
-          <t>0 No | 1 Yes</t>
-        </is>
-      </c>
-      <c r="I208" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if tk_drive is 1 or 2</t>
-        </is>
-      </c>
+          <t>1 Yes, regularly in my main Yatra work | 2 Not in my main work, but done before elsewhere | 3 Never done</t>
+        </is>
+      </c>
+      <c r="I208" s="2" t="inlineStr"/>
       <c r="J208" s="2" t="inlineStr">
         <is>
-          <t>Level ladder without licences</t>
+          <t>Gathmann and Schonberg 2010; NCO 5113.0200</t>
         </is>
       </c>
     </row>
@@ -9986,37 +9986,33 @@
       </c>
       <c r="D209" s="2" t="inlineStr">
         <is>
-          <t>drove_heavy</t>
+          <t>tk_coord</t>
         </is>
       </c>
       <c r="E209" s="2" t="inlineStr">
         <is>
-          <t>yes/no</t>
+          <t>select one</t>
         </is>
       </c>
       <c r="F209" s="2" t="inlineStr">
         <is>
-          <t>... a truck or bus?</t>
+          <t xml:space="preserve">Do you coordinate work by phone, radio or signals? </t>
         </is>
       </c>
       <c r="G209" s="2" t="inlineStr">
         <is>
-          <t>...ट्रक या बस?</t>
+          <t>क्या आप फ़ोन, रेडियो या इशारों से दूसरों के साथ तालमेल करना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="H209" s="2" t="inlineStr">
         <is>
-          <t>0 No | 1 Yes</t>
-        </is>
-      </c>
-      <c r="I209" s="2" t="inlineStr">
-        <is>
-          <t>Ask only if tk_drive is 1 or 2</t>
-        </is>
-      </c>
+          <t>1 Yes, regularly in my main Yatra work | 2 Not in my main work, but done before elsewhere | 3 Never done</t>
+        </is>
+      </c>
+      <c r="I209" s="2" t="inlineStr"/>
       <c r="J209" s="2" t="inlineStr">
         <is>
-          <t>Level ladder without licences</t>
+          <t>NCO 8343.1700 ropeway operator</t>
         </is>
       </c>
     </row>
@@ -10036,7 +10032,7 @@
       </c>
       <c r="D210" s="2" t="inlineStr">
         <is>
-          <t>read_at_work</t>
+          <t>drove_twowheeler</t>
         </is>
       </c>
       <c r="E210" s="2" t="inlineStr">
@@ -10046,12 +10042,12 @@
       </c>
       <c r="F210" s="2" t="inlineStr">
         <is>
-          <t>In your work, do you read anything (notes, rate lists, tickets, messages)?</t>
+          <t>Have you ever driven a motorcycle or scooter, with or without a licence?</t>
         </is>
       </c>
       <c r="G210" s="2" t="inlineStr">
         <is>
-          <t>अपने काम में क्या आप कुछ पढ़ते हैं (पर्ची, रेट लिस्ट, टिकट, मैसेज)?</t>
+          <t>क्या आपने कभी मोटरसाइकिल या स्कूटर चलाई है, लाइसेंस हो या न हो?</t>
         </is>
       </c>
       <c r="H210" s="2" t="inlineStr">
@@ -10059,10 +10055,14 @@
           <t>0 No | 1 Yes</t>
         </is>
       </c>
-      <c r="I210" s="2" t="inlineStr"/>
+      <c r="I210" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if tk_drive is 1 or 2</t>
+        </is>
+      </c>
       <c r="J210" s="2" t="inlineStr">
         <is>
-          <t>STEP module 6A</t>
+          <t>Level ladder without licences: people drive without holding a licence</t>
         </is>
       </c>
     </row>
@@ -10082,38 +10082,184 @@
       </c>
       <c r="D211" s="2" t="inlineStr">
         <is>
+          <t>drove_car</t>
+        </is>
+      </c>
+      <c r="E211" s="2" t="inlineStr">
+        <is>
+          <t>yes/no</t>
+        </is>
+      </c>
+      <c r="F211" s="2" t="inlineStr">
+        <is>
+          <t>... a car or jeep?</t>
+        </is>
+      </c>
+      <c r="G211" s="2" t="inlineStr">
+        <is>
+          <t>...कार या जीप?</t>
+        </is>
+      </c>
+      <c r="H211" s="2" t="inlineStr">
+        <is>
+          <t>0 No | 1 Yes</t>
+        </is>
+      </c>
+      <c r="I211" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if tk_drive is 1 or 2</t>
+        </is>
+      </c>
+      <c r="J211" s="2" t="inlineStr">
+        <is>
+          <t>Level ladder without licences</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="n">
+        <v>211</v>
+      </c>
+      <c r="B212" s="2" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="C212" s="2" t="inlineStr">
+        <is>
+          <t>Tasks and skills (short block)</t>
+        </is>
+      </c>
+      <c r="D212" s="2" t="inlineStr">
+        <is>
+          <t>drove_heavy</t>
+        </is>
+      </c>
+      <c r="E212" s="2" t="inlineStr">
+        <is>
+          <t>yes/no</t>
+        </is>
+      </c>
+      <c r="F212" s="2" t="inlineStr">
+        <is>
+          <t>... a truck or bus?</t>
+        </is>
+      </c>
+      <c r="G212" s="2" t="inlineStr">
+        <is>
+          <t>...ट्रक या बस?</t>
+        </is>
+      </c>
+      <c r="H212" s="2" t="inlineStr">
+        <is>
+          <t>0 No | 1 Yes</t>
+        </is>
+      </c>
+      <c r="I212" s="2" t="inlineStr">
+        <is>
+          <t>Ask only if tk_drive is 1 or 2</t>
+        </is>
+      </c>
+      <c r="J212" s="2" t="inlineStr">
+        <is>
+          <t>Level ladder without licences</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="n">
+        <v>212</v>
+      </c>
+      <c r="B213" s="2" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="C213" s="2" t="inlineStr">
+        <is>
+          <t>Tasks and skills (short block)</t>
+        </is>
+      </c>
+      <c r="D213" s="2" t="inlineStr">
+        <is>
+          <t>read_at_work</t>
+        </is>
+      </c>
+      <c r="E213" s="2" t="inlineStr">
+        <is>
+          <t>yes/no</t>
+        </is>
+      </c>
+      <c r="F213" s="2" t="inlineStr">
+        <is>
+          <t>In your work, do you read anything (notes, rate lists, tickets, messages)?</t>
+        </is>
+      </c>
+      <c r="G213" s="2" t="inlineStr">
+        <is>
+          <t>अपने काम में क्या आप कुछ पढ़ते हैं (पर्ची, रेट लिस्ट, टिकट, मैसेज)?</t>
+        </is>
+      </c>
+      <c r="H213" s="2" t="inlineStr">
+        <is>
+          <t>0 No | 1 Yes</t>
+        </is>
+      </c>
+      <c r="I213" s="2" t="inlineStr"/>
+      <c r="J213" s="2" t="inlineStr">
+        <is>
+          <t>STEP module 6A</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="n">
+        <v>213</v>
+      </c>
+      <c r="B214" s="2" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="C214" s="2" t="inlineStr">
+        <is>
+          <t>Tasks and skills (short block)</t>
+        </is>
+      </c>
+      <c r="D214" s="2" t="inlineStr">
+        <is>
           <t>calc_at_work</t>
         </is>
       </c>
-      <c r="E211" s="2" t="inlineStr">
+      <c r="E214" s="2" t="inlineStr">
         <is>
           <t>yes/no</t>
         </is>
       </c>
-      <c r="F211" s="2" t="inlineStr">
+      <c r="F214" s="2" t="inlineStr">
         <is>
           <t>In your work, do you work out prices or costs?</t>
         </is>
       </c>
-      <c r="G211" s="2" t="inlineStr">
+      <c r="G214" s="2" t="inlineStr">
         <is>
           <t>अपने काम में क्या आप दाम या ख़र्चा जोड़ते-घटाते हैं?</t>
         </is>
       </c>
-      <c r="H211" s="2" t="inlineStr">
+      <c r="H214" s="2" t="inlineStr">
         <is>
           <t>0 No | 1 Yes</t>
         </is>
       </c>
-      <c r="I211" s="2" t="inlineStr"/>
-      <c r="J211" s="2" t="inlineStr">
+      <c r="I214" s="2" t="inlineStr"/>
+      <c r="J214" s="2" t="inlineStr">
         <is>
           <t>STEP module 6A</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J211"/>
+  <autoFilter ref="A1:J214"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -14079,7 +14225,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C132"/>
+  <dimension ref="A1:C135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="78" customWidth="1" min="1" max="1"/>
@@ -14130,7 +14276,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>income_m1, income_m2, income_m3, income_m4, income_m5, income_m6, income_m7, income_m8, income_m9, income_m10, income_m11, income_m12</t>
+          <t>income_m5, income_m6, income_m7, income_m8, income_m9, income_m10, income_m11, income_m12, income_m1, income_m2, income_m3, income_m4</t>
         </is>
       </c>
     </row>
@@ -15277,7 +15423,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>Project design (pilot livelihood survey)</t>
+          <t>Project design (local land units, Uttarakhand)</t>
         </is>
       </c>
       <c r="B80" s="2" t="n">
@@ -15285,14 +15431,14 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>owns_pony_mule</t>
+          <t>land_unit</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI bank-account indicator; VEP adaptive-capacity covariate</t>
+          <t>Project design (pilot livelihood survey)</t>
         </is>
       </c>
       <c r="B81" s="2" t="n">
@@ -15300,14 +15446,14 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>has_bank_account</t>
+          <t>owns_pony_mule</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>VEP adaptive-capacity covariate</t>
+          <t>NITI Aayog National MPI bank-account indicator; VEP adaptive-capacity covariate</t>
         </is>
       </c>
       <c r="B82" s="2" t="n">
@@ -15315,14 +15461,14 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>took_loan_12m</t>
+          <t>has_bank_account</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>VEP adaptive-capacity covariate (lender type)</t>
+          <t>VEP adaptive-capacity covariate</t>
         </is>
       </c>
       <c r="B83" s="2" t="n">
@@ -15330,14 +15476,14 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>credit_source</t>
+          <t>took_loan_12m</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>Islam and Chowdhury 2025 (financial distress and household vulnerability to poverty)</t>
+          <t>VEP adaptive-capacity covariate (lender type)</t>
         </is>
       </c>
       <c r="B84" s="2" t="n">
@@ -15345,14 +15491,14 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>loan_amount</t>
+          <t>credit_source</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>Project design (informal lending is often interest-free)</t>
+          <t>Project design (investment against distress borrowing)</t>
         </is>
       </c>
       <c r="B85" s="2" t="n">
@@ -15360,14 +15506,14 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>pays_interest</t>
+          <t>loan_purpose</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>Project design (informal-credit pricing as locally quoted)</t>
+          <t>Project design (loan size, for the debt-burden measures)</t>
         </is>
       </c>
       <c r="B86" s="2" t="n">
@@ -15375,14 +15521,14 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>loan_interest_per100_pm</t>
+          <t>loan_amount_borrowed</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>Carter and Zimmerman 2000; Chiwaula et al. 2011 (asset-based vulnerability)</t>
+          <t>Islam and Chowdhury 2025 (financial distress and household vulnerability to poverty)</t>
         </is>
       </c>
       <c r="B87" s="2" t="n">
@@ -15390,14 +15536,14 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>loan_against_asset</t>
+          <t>loan_amount</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>Carter and Zimmerman 2000; Zimmerman and Carter 2003 (asset-based coping)</t>
+          <t>Project design (informal lending is often interest-free)</t>
         </is>
       </c>
       <c r="B88" s="2" t="n">
@@ -15405,14 +15551,14 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>loan_collateral</t>
+          <t>pays_interest</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI health-insurance indicator; Lyons et al. 2023</t>
+          <t>Project design (informal-credit pricing as locally quoted)</t>
         </is>
       </c>
       <c r="B89" s="2" t="n">
@@ -15420,14 +15566,14 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>n_health_insured</t>
+          <t>loan_interest_per100_pm</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>Project design; scheme names as administered in Uttarakhand</t>
+          <t>Carter and Zimmerman 2000; Chiwaula et al. 2011 (asset-based vulnerability)</t>
         </is>
       </c>
       <c r="B90" s="2" t="n">
@@ -15435,14 +15581,14 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>govt_schemes</t>
+          <t>loan_against_asset</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>Lyons et al. 2023, Table 2 (legal residency), adapted; One Nation One Ration Card</t>
+          <t>Carter and Zimmerman 2000; Zimmerman and Carter 2003 (asset-based coping)</t>
         </is>
       </c>
       <c r="B91" s="2" t="n">
@@ -15450,14 +15596,14 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>ration_portable_here</t>
+          <t>loan_collateral</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>Project design (intra-household financial capability)</t>
+          <t>NITI Aayog National MPI health-insurance indicator; Lyons et al. 2023</t>
         </is>
       </c>
       <c r="B92" s="2" t="n">
@@ -15465,14 +15611,14 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>n_can_transact_online</t>
+          <t>n_health_insured</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>NSS health module (15-day recall) [source not held by this project; citation unverified as of 2026-09-28]</t>
+          <t>Project design; scheme names as administered in Uttarakhand</t>
         </is>
       </c>
       <c r="B93" s="2" t="n">
@@ -15480,14 +15626,14 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>morbidity_15d</t>
+          <t>govt_schemes</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>Project design (a reported illness with no cost/coping follow-up said nothing about its burden)</t>
+          <t>Lyons et al. 2023, Table 2 (legal residency), adapted; One Nation One Ration Card</t>
         </is>
       </c>
       <c r="B94" s="2" t="n">
@@ -15495,14 +15641,14 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>morbidity_coping_15d</t>
+          <t>ration_portable_here</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>Washington Group on Disability Statistics, Short Set item 3 (mobility), verbatim; Lyons et al. 2023 health dimension</t>
+          <t>Project design (intra-household financial capability)</t>
         </is>
       </c>
       <c r="B95" s="2" t="n">
@@ -15510,14 +15656,14 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>func_limitation</t>
+          <t>n_can_transact_online</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>NSS health module (365-day recall) [source not held by this project; citation unverified as of 2026-09-28]</t>
+          <t>NSS health module (15-day recall) [source not held by this project; citation unverified as of 2026-09-28]</t>
         </is>
       </c>
       <c r="B96" s="2" t="n">
@@ -15525,14 +15671,14 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>hospitalization_365d</t>
+          <t>morbidity_15d</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>VASyR 2025 barriers_health_case_access_phc_m (primary-care access barriers); Lyons et al. 2023 Table 2 indicator 2 'healthcare access'</t>
+          <t>Project design (a reported illness with no cost/coping follow-up said nothing about its burden)</t>
         </is>
       </c>
       <c r="B97" s="2" t="n">
@@ -15540,14 +15686,14 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>health_access_barrier_3m</t>
+          <t>morbidity_coping_15d</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI, Child and Adolescent Mortality (weight 1/12)</t>
+          <t>Washington Group on Disability Statistics, Short Set item 3 (mobility), verbatim; Lyons et al. 2023 health dimension</t>
         </is>
       </c>
       <c r="B98" s="2" t="n">
@@ -15555,14 +15701,14 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>child_death_5y</t>
+          <t>func_limitation</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI, Maternal Health (weight 1/12)</t>
+          <t>NSS health module (365-day recall) [source not held by this project; citation unverified as of 2026-09-28]</t>
         </is>
       </c>
       <c r="B99" s="2" t="n">
@@ -15570,14 +15716,14 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>birth_last_5y</t>
+          <t>hospitalization_365d</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI, Maternal Health (antenatal care limb)</t>
+          <t>VASyR 2025 barriers_health_case_access_phc_m (primary-care access barriers); Lyons et al. 2023 Table 2 indicator 2 'healthcare access'</t>
         </is>
       </c>
       <c r="B100" s="2" t="n">
@@ -15585,14 +15731,14 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>anc_4_visits</t>
+          <t>health_access_barrier_3m</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>NITI Aayog National MPI, Maternal Health (assisted delivery limb)</t>
+          <t>NITI Aayog National MPI, Child and Adolescent Mortality (weight 1/12)</t>
         </is>
       </c>
       <c r="B101" s="2" t="n">
@@ -15600,14 +15746,14 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>skilled_birth_attendant</t>
+          <t>child_death_5y</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>VEP exposure covariate (Azeem et al. 2016); shock inventory following Gunther and Harttgen 2009, via Fujii 2016 section 4</t>
+          <t>NITI Aayog National MPI, Maternal Health (weight 1/12)</t>
         </is>
       </c>
       <c r="B102" s="2" t="n">
@@ -15615,14 +15761,14 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>distress_event_last365d</t>
+          <t>birth_last_5y</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>Ligon and Schechter 2003; Dercon and Krishnan 2000 (VER needs shock magnitude, not only incidence)</t>
+          <t>NITI Aayog National MPI, Maternal Health (antenatal care limb)</t>
         </is>
       </c>
       <c r="B103" s="2" t="n">
@@ -15630,14 +15776,14 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>shock_loss_amount</t>
+          <t>anc_4_visits</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>Dercon and Krishnan 2000 (seasonal timing of shocks); project design</t>
+          <t>NITI Aayog National MPI, Maternal Health (assisted delivery limb)</t>
         </is>
       </c>
       <c r="B104" s="2" t="n">
@@ -15645,14 +15791,14 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>shock_month</t>
+          <t>skilled_birth_attendant</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>Coping strategies in VEP studies; Carter and Zimmerman 2000 on asset versus consumption smoothing</t>
+          <t>VEP exposure covariate (Azeem et al. 2016); shock inventory following Gunther and Harttgen 2009, via Fujii 2016 section 4</t>
         </is>
       </c>
       <c r="B105" s="2" t="n">
@@ -15660,14 +15806,14 @@
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>shock_coping</t>
+          <t>distress_event_last365d</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>Project design (see tasks_module W4: exposure must be asked directly)</t>
+          <t>Ligon and Schechter 2003; Dercon and Krishnan 2000 (VER needs shock magnitude, not only incidence)</t>
         </is>
       </c>
       <c r="B106" s="2" t="n">
@@ -15675,14 +15821,14 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>trek_dependent</t>
+          <t>shock_loss_amount</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q5 (all eleven categories, with its own three-way routing)</t>
+          <t>Dercon and Krishnan 2000 (seasonal timing of shocks); project design</t>
         </is>
       </c>
       <c r="B107" s="2" t="n">
@@ -15690,14 +15836,14 @@
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>job_situation</t>
+          <t>shock_month</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q9</t>
+          <t>Coping strategies in VEP studies; Carter and Zimmerman 2000 on asset versus consumption smoothing</t>
         </is>
       </c>
       <c r="B108" s="2" t="n">
@@ -15705,14 +15851,14 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>job_permanence</t>
+          <t>shock_coping</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q11</t>
+          <t>Project design (see tasks_module W4: exposure must be asked directly)</t>
         </is>
       </c>
       <c r="B109" s="2" t="n">
@@ -15720,14 +15866,14 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>contract_status</t>
+          <t>trek_dependent</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q12 (widened to local registrations)</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q5 (all eleven categories, with its own three-way routing)</t>
         </is>
       </c>
       <c r="B110" s="2" t="n">
@@ -15735,14 +15881,14 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>workplace_registered</t>
+          <t>job_situation</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q16</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q9</t>
         </is>
       </c>
       <c r="B111" s="2" t="n">
@@ -15750,14 +15896,14 @@
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>pension_contrib</t>
+          <t>job_permanence</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q17</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q11</t>
         </is>
       </c>
       <c r="B112" s="2" t="n">
@@ -15765,14 +15911,14 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>work_health_ins</t>
+          <t>contract_status</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q18</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q12 (widened to local registrations)</t>
         </is>
       </c>
       <c r="B113" s="2" t="n">
@@ -15780,14 +15926,14 @@
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>leave_rights</t>
+          <t>workplace_registered</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q19</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q16</t>
         </is>
       </c>
       <c r="B114" s="2" t="n">
@@ -15795,14 +15941,14 @@
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>injured_ever</t>
+          <t>pension_contrib</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q20</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q17</t>
         </is>
       </c>
       <c r="B115" s="2" t="n">
@@ -15810,14 +15956,14 @@
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>workplace_injury_12m</t>
+          <t>work_health_ins</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q21</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q18</t>
         </is>
       </c>
       <c r="B116" s="2" t="n">
@@ -15825,14 +15971,14 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>wants_more_work</t>
+          <t>leave_rights</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q22</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q19</t>
         </is>
       </c>
       <c r="B117" s="2" t="n">
@@ -15840,14 +15986,14 @@
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>more_hours_day</t>
+          <t>injured_ever</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q23 (duration in weeks, tied to the calendar instead of a single point in time)</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q20</t>
         </is>
       </c>
       <c r="B118" s="2" t="n">
@@ -15855,14 +16001,14 @@
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>months_looked_for_work</t>
+          <t>workplace_injury_12m</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>Apablaza et al. 2026, Appendix 2 Q24</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q21</t>
         </is>
       </c>
       <c r="B119" s="2" t="n">
@@ -15870,14 +16016,14 @@
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>first_job_ever</t>
+          <t>wants_more_work</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>Gathmann and Schonberg 2010; NCO 9333.0100 loader</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q22</t>
         </is>
       </c>
       <c r="B120" s="2" t="n">
@@ -15885,14 +16031,14 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>tk_load</t>
+          <t>more_hours_day</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>Spitz-Oener 2006 / STEP; NCO 8322.0100</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q23 (duration in weeks, tied to the calendar instead of a single point in time)</t>
         </is>
       </c>
       <c r="B121" s="2" t="n">
@@ -15900,14 +16046,14 @@
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>tk_drive</t>
+          <t>months_looked_for_work</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>Gathmann and Schonberg 2010; NCO 8343.1700 ropeway operator</t>
+          <t>Apablaza et al. 2026, Appendix 2 Q24</t>
         </is>
       </c>
       <c r="B122" s="2" t="n">
@@ -15915,14 +16061,14 @@
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>tk_engine</t>
+          <t>first_job_ever</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>Spitz-Oener 2006; NCO 7411.0301 wireman</t>
+          <t>Gathmann and Schonberg 2010; NCO 9333.0100 loader</t>
         </is>
       </c>
       <c r="B123" s="2" t="n">
@@ -15930,14 +16076,14 @@
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>tk_electric</t>
+          <t>tk_load</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>Gathmann and Schonberg 2010; NCO 8343.1700</t>
+          <t>Spitz-Oener 2006 / STEP; NCO 8322.0100</t>
         </is>
       </c>
       <c r="B124" s="2" t="n">
@@ -15945,14 +16091,14 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>tk_safety</t>
+          <t>tk_drive</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>Gathmann and Schonberg 2010; NCO 5223.0200</t>
+          <t>Gathmann and Schonberg 2010; NCO 8343.1700 ropeway operator</t>
         </is>
       </c>
       <c r="B125" s="2" t="n">
@@ -15960,14 +16106,14 @@
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>tk_sell</t>
+          <t>tk_engine</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>Autor and Handel 2013; NCO 5131.0401</t>
+          <t>Spitz-Oener 2006; NCO 7411.0301 wireman</t>
         </is>
       </c>
       <c r="B126" s="2" t="n">
@@ -15975,14 +16121,14 @@
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>tk_cash</t>
+          <t>tk_electric</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>NCO 5120.0300 cook</t>
+          <t>Gathmann and Schonberg 2010; NCO 8343.1700</t>
         </is>
       </c>
       <c r="B127" s="2" t="n">
@@ -15990,14 +16136,14 @@
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>tk_cook</t>
+          <t>tk_safety</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>NCO 5131.0401 waiter; Pal et al. 2026</t>
+          <t>Gathmann and Schonberg 2010; NCO 5223.0200</t>
         </is>
       </c>
       <c r="B128" s="2" t="n">
@@ -16005,14 +16151,14 @@
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>tk_serve</t>
+          <t>tk_sell</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>NCO 5151.0202 room attendant; Autor-Levy-Murnane 2003 (janitorial)</t>
+          <t>Autor and Handel 2013; NCO 5131.0401</t>
         </is>
       </c>
       <c r="B129" s="2" t="n">
@@ -16020,14 +16166,14 @@
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>tk_clean</t>
+          <t>tk_cash</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>Gathmann and Schonberg 2010; NCO 5113.0200</t>
+          <t>NCO 5120.0300 cook</t>
         </is>
       </c>
       <c r="B130" s="2" t="n">
@@ -16035,14 +16181,14 @@
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>tk_guide</t>
+          <t>tk_cook</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>NCO 8343.1700 ropeway operator</t>
+          <t>NCO 5131.0401 waiter; Pal et al. 2026</t>
         </is>
       </c>
       <c r="B131" s="2" t="n">
@@ -16050,14 +16196,14 @@
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>tk_coord</t>
+          <t>tk_serve</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>Level ladder without licences: people drive without holding a licence</t>
+          <t>NCO 5151.0202 room attendant; Autor-Levy-Murnane 2003 (janitorial)</t>
         </is>
       </c>
       <c r="B132" s="2" t="n">
@@ -16065,12 +16211,57 @@
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
+          <t>tk_clean</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>Gathmann and Schonberg 2010; NCO 5113.0200</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>tk_guide</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>NCO 8343.1700 ropeway operator</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>tk_coord</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>Level ladder without licences: people drive without holding a licence</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
           <t>drove_twowheeler</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C132"/>
+  <autoFilter ref="A1:C135"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -16208,7 +16399,7 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9">
@@ -16223,7 +16414,7 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10">
@@ -16309,7 +16500,7 @@
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>210</v>
+        <v>213</v>
       </c>
     </row>
   </sheetData>

--- a/replication/final_instrument/questionnaire/Question_register.xlsx
+++ b/replication/final_instrument/questionnaire/Question_register.xlsx
@@ -8810,7 +8810,7 @@
       </c>
       <c r="F184" s="2" t="inlineStr">
         <is>
-          <t>Is your main Yatra work carrying, transporting or guiding people or goods on the Gaurikund to Kedarnath trek?</t>
+          <t>Is your main work carrying, transporting or guiding people or goods on foot along the pilgrimage trek?</t>
         </is>
       </c>
       <c r="G184" s="2" t="inlineStr">
